--- a/가공도_도면_1.xlsx
+++ b/가공도_도면_1.xlsx
@@ -254,7 +254,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -338,6 +338,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3302,16 +3305,12 @@
       <c r="P26" s="14" t="n"/>
       <c r="T26" s="16" t="n"/>
       <c r="U26" s="32" t="n"/>
-      <c r="V26" s="32" t="n"/>
-      <c r="W26" s="32" t="n"/>
-      <c r="X26" s="32" t="n"/>
-      <c r="Y26" s="32" t="n"/>
-      <c r="Z26" s="32" t="n"/>
-      <c r="AA26" s="32" t="n"/>
-      <c r="AB26" s="32" t="n"/>
-      <c r="AC26" s="32" t="n"/>
-      <c r="AD26" s="32" t="n"/>
-      <c r="CE26" t="inlineStr">
+      <c r="V26" s="34" t="inlineStr">
+        <is>
+          <t>{Input_200}</t>
+        </is>
+      </c>
+      <c r="CE26" s="32" t="inlineStr">
         <is>
           <t>{View_1}</t>
         </is>
@@ -3437,15 +3436,6 @@
       <c r="P27" s="14" t="n"/>
       <c r="T27" s="16" t="n"/>
       <c r="U27" s="32" t="n"/>
-      <c r="V27" s="32" t="n"/>
-      <c r="W27" s="32" t="n"/>
-      <c r="X27" s="32" t="n"/>
-      <c r="Y27" s="32" t="n"/>
-      <c r="Z27" s="32" t="n"/>
-      <c r="AA27" s="32" t="n"/>
-      <c r="AB27" s="32" t="n"/>
-      <c r="AC27" s="32" t="n"/>
-      <c r="AD27" s="32" t="n"/>
       <c r="GW27" s="14" t="n"/>
       <c r="HB27" s="16" t="n"/>
       <c r="HC27" s="14" t="n"/>
@@ -3471,15 +3461,6 @@
       <c r="P28" s="14" t="n"/>
       <c r="T28" s="16" t="n"/>
       <c r="U28" s="32" t="n"/>
-      <c r="V28" s="32" t="n"/>
-      <c r="W28" s="32" t="n"/>
-      <c r="X28" s="32" t="n"/>
-      <c r="Y28" s="32" t="n"/>
-      <c r="Z28" s="32" t="n"/>
-      <c r="AA28" s="32" t="n"/>
-      <c r="AB28" s="32" t="n"/>
-      <c r="AC28" s="32" t="n"/>
-      <c r="AD28" s="32" t="n"/>
       <c r="GW28" s="14" t="n"/>
       <c r="HB28" s="16" t="n"/>
       <c r="HC28" s="14" t="n"/>
@@ -3505,15 +3486,6 @@
       <c r="P29" s="14" t="n"/>
       <c r="T29" s="16" t="n"/>
       <c r="U29" s="32" t="n"/>
-      <c r="V29" s="32" t="n"/>
-      <c r="W29" s="32" t="n"/>
-      <c r="X29" s="32" t="n"/>
-      <c r="Y29" s="32" t="n"/>
-      <c r="Z29" s="32" t="n"/>
-      <c r="AA29" s="32" t="n"/>
-      <c r="AB29" s="32" t="n"/>
-      <c r="AC29" s="32" t="n"/>
-      <c r="AD29" s="32" t="n"/>
       <c r="GW29" s="17" t="n"/>
       <c r="GX29" s="18" t="n"/>
       <c r="GY29" s="18" t="n"/>
@@ -3603,15 +3575,6 @@
       <c r="P30" s="14" t="n"/>
       <c r="T30" s="16" t="n"/>
       <c r="U30" s="32" t="n"/>
-      <c r="V30" s="32" t="n"/>
-      <c r="W30" s="32" t="n"/>
-      <c r="X30" s="32" t="n"/>
-      <c r="Y30" s="32" t="n"/>
-      <c r="Z30" s="32" t="n"/>
-      <c r="AA30" s="32" t="n"/>
-      <c r="AB30" s="32" t="n"/>
-      <c r="AC30" s="32" t="n"/>
-      <c r="AD30" s="32" t="n"/>
       <c r="GW30" s="11" t="inlineStr">
         <is>
           <t>{Input_6}</t>
@@ -3733,15 +3696,6 @@
       <c r="P31" s="14" t="n"/>
       <c r="T31" s="16" t="n"/>
       <c r="U31" s="32" t="n"/>
-      <c r="V31" s="32" t="n"/>
-      <c r="W31" s="32" t="n"/>
-      <c r="X31" s="32" t="n"/>
-      <c r="Y31" s="32" t="n"/>
-      <c r="Z31" s="32" t="n"/>
-      <c r="AA31" s="32" t="n"/>
-      <c r="AB31" s="32" t="n"/>
-      <c r="AC31" s="32" t="n"/>
-      <c r="AD31" s="32" t="n"/>
       <c r="GW31" s="14" t="n"/>
       <c r="HB31" s="16" t="n"/>
       <c r="HC31" s="14" t="n"/>
@@ -3767,15 +3721,6 @@
       <c r="P32" s="14" t="n"/>
       <c r="T32" s="16" t="n"/>
       <c r="U32" s="32" t="n"/>
-      <c r="V32" s="32" t="n"/>
-      <c r="W32" s="32" t="n"/>
-      <c r="X32" s="32" t="n"/>
-      <c r="Y32" s="32" t="n"/>
-      <c r="Z32" s="32" t="n"/>
-      <c r="AA32" s="32" t="n"/>
-      <c r="AB32" s="32" t="n"/>
-      <c r="AC32" s="32" t="n"/>
-      <c r="AD32" s="32" t="n"/>
       <c r="GW32" s="14" t="n"/>
       <c r="HB32" s="16" t="n"/>
       <c r="HC32" s="14" t="n"/>
@@ -3801,15 +3746,6 @@
       <c r="P33" s="14" t="n"/>
       <c r="T33" s="16" t="n"/>
       <c r="U33" s="32" t="n"/>
-      <c r="V33" s="32" t="n"/>
-      <c r="W33" s="32" t="n"/>
-      <c r="X33" s="32" t="n"/>
-      <c r="Y33" s="32" t="n"/>
-      <c r="Z33" s="32" t="n"/>
-      <c r="AA33" s="32" t="n"/>
-      <c r="AB33" s="32" t="n"/>
-      <c r="AC33" s="32" t="n"/>
-      <c r="AD33" s="32" t="n"/>
       <c r="GW33" s="17" t="n"/>
       <c r="GX33" s="18" t="n"/>
       <c r="GY33" s="18" t="n"/>
@@ -3899,15 +3835,6 @@
       <c r="P34" s="14" t="n"/>
       <c r="T34" s="16" t="n"/>
       <c r="U34" s="32" t="n"/>
-      <c r="V34" s="32" t="n"/>
-      <c r="W34" s="32" t="n"/>
-      <c r="X34" s="32" t="n"/>
-      <c r="Y34" s="32" t="n"/>
-      <c r="Z34" s="32" t="n"/>
-      <c r="AA34" s="32" t="n"/>
-      <c r="AB34" s="32" t="n"/>
-      <c r="AC34" s="32" t="n"/>
-      <c r="AD34" s="32" t="n"/>
       <c r="GW34" s="11" t="inlineStr">
         <is>
           <t>{Input_7}</t>
@@ -4029,15 +3956,6 @@
       <c r="P35" s="14" t="n"/>
       <c r="T35" s="16" t="n"/>
       <c r="U35" s="32" t="n"/>
-      <c r="V35" s="32" t="n"/>
-      <c r="W35" s="32" t="n"/>
-      <c r="X35" s="32" t="n"/>
-      <c r="Y35" s="32" t="n"/>
-      <c r="Z35" s="32" t="n"/>
-      <c r="AA35" s="32" t="n"/>
-      <c r="AB35" s="32" t="n"/>
-      <c r="AC35" s="32" t="n"/>
-      <c r="AD35" s="32" t="n"/>
       <c r="GW35" s="14" t="n"/>
       <c r="HB35" s="16" t="n"/>
       <c r="HC35" s="14" t="n"/>
@@ -4063,15 +3981,6 @@
       <c r="P36" s="14" t="n"/>
       <c r="T36" s="16" t="n"/>
       <c r="U36" s="32" t="n"/>
-      <c r="V36" s="32" t="n"/>
-      <c r="W36" s="32" t="n"/>
-      <c r="X36" s="32" t="n"/>
-      <c r="Y36" s="32" t="n"/>
-      <c r="Z36" s="32" t="n"/>
-      <c r="AA36" s="32" t="n"/>
-      <c r="AB36" s="32" t="n"/>
-      <c r="AC36" s="32" t="n"/>
-      <c r="AD36" s="32" t="n"/>
       <c r="GW36" s="14" t="n"/>
       <c r="HB36" s="16" t="n"/>
       <c r="HC36" s="14" t="n"/>
@@ -4097,15 +4006,6 @@
       <c r="P37" s="14" t="n"/>
       <c r="T37" s="16" t="n"/>
       <c r="U37" s="32" t="n"/>
-      <c r="V37" s="32" t="n"/>
-      <c r="W37" s="32" t="n"/>
-      <c r="X37" s="32" t="n"/>
-      <c r="Y37" s="32" t="n"/>
-      <c r="Z37" s="32" t="n"/>
-      <c r="AA37" s="32" t="n"/>
-      <c r="AB37" s="32" t="n"/>
-      <c r="AC37" s="32" t="n"/>
-      <c r="AD37" s="32" t="n"/>
       <c r="GW37" s="17" t="n"/>
       <c r="GX37" s="18" t="n"/>
       <c r="GY37" s="18" t="n"/>
@@ -4195,15 +4095,6 @@
       <c r="P38" s="14" t="n"/>
       <c r="T38" s="16" t="n"/>
       <c r="U38" s="32" t="n"/>
-      <c r="V38" s="32" t="n"/>
-      <c r="W38" s="32" t="n"/>
-      <c r="X38" s="32" t="n"/>
-      <c r="Y38" s="32" t="n"/>
-      <c r="Z38" s="32" t="n"/>
-      <c r="AA38" s="32" t="n"/>
-      <c r="AB38" s="32" t="n"/>
-      <c r="AC38" s="32" t="n"/>
-      <c r="AD38" s="32" t="n"/>
       <c r="GW38" s="11" t="inlineStr">
         <is>
           <t>{Input_8}</t>
@@ -4325,15 +4216,6 @@
       <c r="P39" s="14" t="n"/>
       <c r="T39" s="16" t="n"/>
       <c r="U39" s="32" t="n"/>
-      <c r="V39" s="32" t="n"/>
-      <c r="W39" s="32" t="n"/>
-      <c r="X39" s="32" t="n"/>
-      <c r="Y39" s="32" t="n"/>
-      <c r="Z39" s="32" t="n"/>
-      <c r="AA39" s="32" t="n"/>
-      <c r="AB39" s="32" t="n"/>
-      <c r="AC39" s="32" t="n"/>
-      <c r="AD39" s="32" t="n"/>
       <c r="GW39" s="14" t="n"/>
       <c r="HB39" s="16" t="n"/>
       <c r="HC39" s="14" t="n"/>
@@ -4359,15 +4241,6 @@
       <c r="P40" s="14" t="n"/>
       <c r="T40" s="16" t="n"/>
       <c r="U40" s="32" t="n"/>
-      <c r="V40" s="32" t="n"/>
-      <c r="W40" s="32" t="n"/>
-      <c r="X40" s="32" t="n"/>
-      <c r="Y40" s="32" t="n"/>
-      <c r="Z40" s="32" t="n"/>
-      <c r="AA40" s="32" t="n"/>
-      <c r="AB40" s="32" t="n"/>
-      <c r="AC40" s="32" t="n"/>
-      <c r="AD40" s="32" t="n"/>
       <c r="GW40" s="14" t="n"/>
       <c r="HB40" s="16" t="n"/>
       <c r="HC40" s="14" t="n"/>
@@ -4393,15 +4266,6 @@
       <c r="P41" s="14" t="n"/>
       <c r="T41" s="16" t="n"/>
       <c r="U41" s="32" t="n"/>
-      <c r="V41" s="32" t="n"/>
-      <c r="W41" s="32" t="n"/>
-      <c r="X41" s="32" t="n"/>
-      <c r="Y41" s="32" t="n"/>
-      <c r="Z41" s="32" t="n"/>
-      <c r="AA41" s="32" t="n"/>
-      <c r="AB41" s="32" t="n"/>
-      <c r="AC41" s="32" t="n"/>
-      <c r="AD41" s="32" t="n"/>
       <c r="GM41" s="32" t="n"/>
       <c r="GN41" s="32" t="n"/>
       <c r="GO41" s="32" t="n"/>
@@ -6401,16 +6265,12 @@
       <c r="P62" s="14" t="n"/>
       <c r="T62" s="16" t="n"/>
       <c r="U62" s="32" t="n"/>
-      <c r="V62" s="32" t="n"/>
-      <c r="W62" s="32" t="n"/>
-      <c r="X62" s="32" t="n"/>
-      <c r="Y62" s="32" t="n"/>
-      <c r="Z62" s="32" t="n"/>
-      <c r="AA62" s="32" t="n"/>
-      <c r="AB62" s="32" t="n"/>
-      <c r="AC62" s="32" t="n"/>
-      <c r="AD62" s="32" t="n"/>
-      <c r="CE62" t="inlineStr">
+      <c r="V62" s="34" t="inlineStr">
+        <is>
+          <t>{Input_201}</t>
+        </is>
+      </c>
+      <c r="CE62" s="32" t="inlineStr">
         <is>
           <t>{View_2}</t>
         </is>
@@ -6546,15 +6406,6 @@
       <c r="P63" s="14" t="n"/>
       <c r="T63" s="16" t="n"/>
       <c r="U63" s="32" t="n"/>
-      <c r="V63" s="32" t="n"/>
-      <c r="W63" s="32" t="n"/>
-      <c r="X63" s="32" t="n"/>
-      <c r="Y63" s="32" t="n"/>
-      <c r="Z63" s="32" t="n"/>
-      <c r="AA63" s="32" t="n"/>
-      <c r="AB63" s="32" t="n"/>
-      <c r="AC63" s="32" t="n"/>
-      <c r="AD63" s="32" t="n"/>
       <c r="GM63" s="32" t="n"/>
       <c r="GN63" s="32" t="n"/>
       <c r="GO63" s="32" t="n"/>
@@ -6590,15 +6441,6 @@
       <c r="P64" s="14" t="n"/>
       <c r="T64" s="16" t="n"/>
       <c r="U64" s="32" t="n"/>
-      <c r="V64" s="32" t="n"/>
-      <c r="W64" s="32" t="n"/>
-      <c r="X64" s="32" t="n"/>
-      <c r="Y64" s="32" t="n"/>
-      <c r="Z64" s="32" t="n"/>
-      <c r="AA64" s="32" t="n"/>
-      <c r="AB64" s="32" t="n"/>
-      <c r="AC64" s="32" t="n"/>
-      <c r="AD64" s="32" t="n"/>
       <c r="GM64" s="32" t="n"/>
       <c r="GN64" s="32" t="n"/>
       <c r="GO64" s="32" t="n"/>
@@ -6634,15 +6476,6 @@
       <c r="P65" s="14" t="n"/>
       <c r="T65" s="16" t="n"/>
       <c r="U65" s="32" t="n"/>
-      <c r="V65" s="32" t="n"/>
-      <c r="W65" s="32" t="n"/>
-      <c r="X65" s="32" t="n"/>
-      <c r="Y65" s="32" t="n"/>
-      <c r="Z65" s="32" t="n"/>
-      <c r="AA65" s="32" t="n"/>
-      <c r="AB65" s="32" t="n"/>
-      <c r="AC65" s="32" t="n"/>
-      <c r="AD65" s="32" t="n"/>
       <c r="GM65" s="32" t="n"/>
       <c r="GN65" s="32" t="n"/>
       <c r="GO65" s="32" t="n"/>
@@ -6742,15 +6575,6 @@
       <c r="P66" s="14" t="n"/>
       <c r="T66" s="16" t="n"/>
       <c r="U66" s="32" t="n"/>
-      <c r="V66" s="32" t="n"/>
-      <c r="W66" s="32" t="n"/>
-      <c r="X66" s="32" t="n"/>
-      <c r="Y66" s="32" t="n"/>
-      <c r="Z66" s="32" t="n"/>
-      <c r="AA66" s="32" t="n"/>
-      <c r="AB66" s="32" t="n"/>
-      <c r="AC66" s="32" t="n"/>
-      <c r="AD66" s="32" t="n"/>
       <c r="GM66" s="32" t="n"/>
       <c r="GN66" s="32" t="n"/>
       <c r="GO66" s="32" t="n"/>
@@ -6882,15 +6706,6 @@
       <c r="P67" s="14" t="n"/>
       <c r="T67" s="16" t="n"/>
       <c r="U67" s="32" t="n"/>
-      <c r="V67" s="32" t="n"/>
-      <c r="W67" s="32" t="n"/>
-      <c r="X67" s="32" t="n"/>
-      <c r="Y67" s="32" t="n"/>
-      <c r="Z67" s="32" t="n"/>
-      <c r="AA67" s="32" t="n"/>
-      <c r="AB67" s="32" t="n"/>
-      <c r="AC67" s="32" t="n"/>
-      <c r="AD67" s="32" t="n"/>
       <c r="GM67" s="32" t="n"/>
       <c r="GN67" s="32" t="n"/>
       <c r="GO67" s="32" t="n"/>
@@ -6926,15 +6741,6 @@
       <c r="P68" s="14" t="n"/>
       <c r="T68" s="16" t="n"/>
       <c r="U68" s="32" t="n"/>
-      <c r="V68" s="32" t="n"/>
-      <c r="W68" s="32" t="n"/>
-      <c r="X68" s="32" t="n"/>
-      <c r="Y68" s="32" t="n"/>
-      <c r="Z68" s="32" t="n"/>
-      <c r="AA68" s="32" t="n"/>
-      <c r="AB68" s="32" t="n"/>
-      <c r="AC68" s="32" t="n"/>
-      <c r="AD68" s="32" t="n"/>
       <c r="GM68" s="32" t="n"/>
       <c r="GN68" s="32" t="n"/>
       <c r="GO68" s="32" t="n"/>
@@ -6970,15 +6776,6 @@
       <c r="P69" s="14" t="n"/>
       <c r="T69" s="16" t="n"/>
       <c r="U69" s="32" t="n"/>
-      <c r="V69" s="32" t="n"/>
-      <c r="W69" s="32" t="n"/>
-      <c r="X69" s="32" t="n"/>
-      <c r="Y69" s="32" t="n"/>
-      <c r="Z69" s="32" t="n"/>
-      <c r="AA69" s="32" t="n"/>
-      <c r="AB69" s="32" t="n"/>
-      <c r="AC69" s="32" t="n"/>
-      <c r="AD69" s="32" t="n"/>
       <c r="GM69" s="32" t="n"/>
       <c r="GN69" s="32" t="n"/>
       <c r="GO69" s="32" t="n"/>
@@ -7078,15 +6875,6 @@
       <c r="P70" s="14" t="n"/>
       <c r="T70" s="16" t="n"/>
       <c r="U70" s="32" t="n"/>
-      <c r="V70" s="32" t="n"/>
-      <c r="W70" s="32" t="n"/>
-      <c r="X70" s="32" t="n"/>
-      <c r="Y70" s="32" t="n"/>
-      <c r="Z70" s="32" t="n"/>
-      <c r="AA70" s="32" t="n"/>
-      <c r="AB70" s="32" t="n"/>
-      <c r="AC70" s="32" t="n"/>
-      <c r="AD70" s="32" t="n"/>
       <c r="GM70" s="32" t="n"/>
       <c r="GN70" s="32" t="n"/>
       <c r="GO70" s="32" t="n"/>
@@ -7218,15 +7006,6 @@
       <c r="P71" s="14" t="n"/>
       <c r="T71" s="16" t="n"/>
       <c r="U71" s="32" t="n"/>
-      <c r="V71" s="32" t="n"/>
-      <c r="W71" s="32" t="n"/>
-      <c r="X71" s="32" t="n"/>
-      <c r="Y71" s="32" t="n"/>
-      <c r="Z71" s="32" t="n"/>
-      <c r="AA71" s="32" t="n"/>
-      <c r="AB71" s="32" t="n"/>
-      <c r="AC71" s="32" t="n"/>
-      <c r="AD71" s="32" t="n"/>
       <c r="GM71" s="32" t="n"/>
       <c r="GN71" s="32" t="n"/>
       <c r="GO71" s="32" t="n"/>
@@ -7262,15 +7041,6 @@
       <c r="P72" s="14" t="n"/>
       <c r="T72" s="16" t="n"/>
       <c r="U72" s="32" t="n"/>
-      <c r="V72" s="32" t="n"/>
-      <c r="W72" s="32" t="n"/>
-      <c r="X72" s="32" t="n"/>
-      <c r="Y72" s="32" t="n"/>
-      <c r="Z72" s="32" t="n"/>
-      <c r="AA72" s="32" t="n"/>
-      <c r="AB72" s="32" t="n"/>
-      <c r="AC72" s="32" t="n"/>
-      <c r="AD72" s="32" t="n"/>
       <c r="GM72" s="32" t="n"/>
       <c r="GN72" s="32" t="n"/>
       <c r="GO72" s="32" t="n"/>
@@ -7306,15 +7076,6 @@
       <c r="P73" s="14" t="n"/>
       <c r="T73" s="16" t="n"/>
       <c r="U73" s="32" t="n"/>
-      <c r="V73" s="32" t="n"/>
-      <c r="W73" s="32" t="n"/>
-      <c r="X73" s="32" t="n"/>
-      <c r="Y73" s="32" t="n"/>
-      <c r="Z73" s="32" t="n"/>
-      <c r="AA73" s="32" t="n"/>
-      <c r="AB73" s="32" t="n"/>
-      <c r="AC73" s="32" t="n"/>
-      <c r="AD73" s="32" t="n"/>
       <c r="GM73" s="32" t="n"/>
       <c r="GN73" s="32" t="n"/>
       <c r="GO73" s="32" t="n"/>
@@ -7414,15 +7175,6 @@
       <c r="P74" s="14" t="n"/>
       <c r="T74" s="16" t="n"/>
       <c r="U74" s="32" t="n"/>
-      <c r="V74" s="32" t="n"/>
-      <c r="W74" s="32" t="n"/>
-      <c r="X74" s="32" t="n"/>
-      <c r="Y74" s="32" t="n"/>
-      <c r="Z74" s="32" t="n"/>
-      <c r="AA74" s="32" t="n"/>
-      <c r="AB74" s="32" t="n"/>
-      <c r="AC74" s="32" t="n"/>
-      <c r="AD74" s="32" t="n"/>
       <c r="GM74" s="32" t="n"/>
       <c r="GN74" s="32" t="n"/>
       <c r="GO74" s="32" t="n"/>
@@ -7554,15 +7306,6 @@
       <c r="P75" s="14" t="n"/>
       <c r="T75" s="16" t="n"/>
       <c r="U75" s="32" t="n"/>
-      <c r="V75" s="32" t="n"/>
-      <c r="W75" s="32" t="n"/>
-      <c r="X75" s="32" t="n"/>
-      <c r="Y75" s="32" t="n"/>
-      <c r="Z75" s="32" t="n"/>
-      <c r="AA75" s="32" t="n"/>
-      <c r="AB75" s="32" t="n"/>
-      <c r="AC75" s="32" t="n"/>
-      <c r="AD75" s="32" t="n"/>
       <c r="GM75" s="32" t="n"/>
       <c r="GN75" s="32" t="n"/>
       <c r="GO75" s="32" t="n"/>
@@ -7598,15 +7341,6 @@
       <c r="P76" s="14" t="n"/>
       <c r="T76" s="16" t="n"/>
       <c r="U76" s="32" t="n"/>
-      <c r="V76" s="32" t="n"/>
-      <c r="W76" s="32" t="n"/>
-      <c r="X76" s="32" t="n"/>
-      <c r="Y76" s="32" t="n"/>
-      <c r="Z76" s="32" t="n"/>
-      <c r="AA76" s="32" t="n"/>
-      <c r="AB76" s="32" t="n"/>
-      <c r="AC76" s="32" t="n"/>
-      <c r="AD76" s="32" t="n"/>
       <c r="GM76" s="32" t="n"/>
       <c r="GN76" s="32" t="n"/>
       <c r="GO76" s="32" t="n"/>
@@ -7642,15 +7376,6 @@
       <c r="P77" s="14" t="n"/>
       <c r="T77" s="16" t="n"/>
       <c r="U77" s="32" t="n"/>
-      <c r="V77" s="32" t="n"/>
-      <c r="W77" s="32" t="n"/>
-      <c r="X77" s="32" t="n"/>
-      <c r="Y77" s="32" t="n"/>
-      <c r="Z77" s="32" t="n"/>
-      <c r="AA77" s="32" t="n"/>
-      <c r="AB77" s="32" t="n"/>
-      <c r="AC77" s="32" t="n"/>
-      <c r="AD77" s="32" t="n"/>
       <c r="GM77" s="32" t="n"/>
       <c r="GN77" s="32" t="n"/>
       <c r="GO77" s="32" t="n"/>
@@ -9630,16 +9355,12 @@
       <c r="P98" s="14" t="n"/>
       <c r="T98" s="16" t="n"/>
       <c r="U98" s="32" t="n"/>
-      <c r="V98" s="32" t="n"/>
-      <c r="W98" s="32" t="n"/>
-      <c r="X98" s="32" t="n"/>
-      <c r="Y98" s="32" t="n"/>
-      <c r="Z98" s="32" t="n"/>
-      <c r="AA98" s="32" t="n"/>
-      <c r="AB98" s="32" t="n"/>
-      <c r="AC98" s="32" t="n"/>
-      <c r="AD98" s="32" t="n"/>
-      <c r="CE98" t="inlineStr">
+      <c r="V98" s="34" t="inlineStr">
+        <is>
+          <t>{Input_202}</t>
+        </is>
+      </c>
+      <c r="CE98" s="32" t="inlineStr">
         <is>
           <t>{View_3}</t>
         </is>
@@ -9775,15 +9496,6 @@
       <c r="P99" s="14" t="n"/>
       <c r="T99" s="16" t="n"/>
       <c r="U99" s="32" t="n"/>
-      <c r="V99" s="32" t="n"/>
-      <c r="W99" s="32" t="n"/>
-      <c r="X99" s="32" t="n"/>
-      <c r="Y99" s="32" t="n"/>
-      <c r="Z99" s="32" t="n"/>
-      <c r="AA99" s="32" t="n"/>
-      <c r="AB99" s="32" t="n"/>
-      <c r="AC99" s="32" t="n"/>
-      <c r="AD99" s="32" t="n"/>
       <c r="GM99" s="32" t="n"/>
       <c r="GN99" s="32" t="n"/>
       <c r="GO99" s="32" t="n"/>
@@ -9819,47 +9531,6 @@
       <c r="P100" s="14" t="n"/>
       <c r="T100" s="16" t="n"/>
       <c r="U100" s="32" t="n"/>
-      <c r="V100" s="32" t="n"/>
-      <c r="W100" s="32" t="n"/>
-      <c r="X100" s="32" t="n"/>
-      <c r="Y100" s="32" t="n"/>
-      <c r="Z100" s="32" t="n"/>
-      <c r="AA100" s="32" t="n"/>
-      <c r="AB100" s="32" t="n"/>
-      <c r="AC100" s="32" t="n"/>
-      <c r="AD100" s="32" t="n"/>
-      <c r="AE100" s="32" t="n"/>
-      <c r="AF100" s="32" t="n"/>
-      <c r="AG100" s="32" t="n"/>
-      <c r="AH100" s="32" t="n"/>
-      <c r="AI100" s="32" t="n"/>
-      <c r="AJ100" s="32" t="n"/>
-      <c r="AK100" s="32" t="n"/>
-      <c r="AL100" s="32" t="n"/>
-      <c r="AM100" s="32" t="n"/>
-      <c r="AN100" s="32" t="n"/>
-      <c r="AO100" s="32" t="n"/>
-      <c r="AP100" s="32" t="n"/>
-      <c r="AQ100" s="32" t="n"/>
-      <c r="AR100" s="32" t="n"/>
-      <c r="AS100" s="32" t="n"/>
-      <c r="AT100" s="32" t="n"/>
-      <c r="AU100" s="32" t="n"/>
-      <c r="AV100" s="32" t="n"/>
-      <c r="AW100" s="32" t="n"/>
-      <c r="AX100" s="32" t="n"/>
-      <c r="AY100" s="32" t="n"/>
-      <c r="AZ100" s="32" t="n"/>
-      <c r="BA100" s="32" t="n"/>
-      <c r="BB100" s="32" t="n"/>
-      <c r="BC100" s="32" t="n"/>
-      <c r="BD100" s="33" t="n"/>
-      <c r="BX100" s="32" t="n"/>
-      <c r="BY100" s="32" t="n"/>
-      <c r="BZ100" s="32" t="n"/>
-      <c r="CA100" s="32" t="n"/>
-      <c r="CB100" s="32" t="n"/>
-      <c r="CC100" s="32" t="n"/>
       <c r="CD100" s="32" t="n"/>
       <c r="EM100" s="32" t="n"/>
       <c r="EN100" s="32" t="n"/>
@@ -9929,46 +9600,6 @@
       <c r="P101" s="14" t="n"/>
       <c r="T101" s="16" t="n"/>
       <c r="U101" s="32" t="n"/>
-      <c r="V101" s="32" t="n"/>
-      <c r="W101" s="32" t="n"/>
-      <c r="X101" s="32" t="n"/>
-      <c r="Y101" s="32" t="n"/>
-      <c r="Z101" s="32" t="n"/>
-      <c r="AA101" s="32" t="n"/>
-      <c r="AB101" s="32" t="n"/>
-      <c r="AC101" s="32" t="n"/>
-      <c r="AD101" s="32" t="n"/>
-      <c r="AE101" s="32" t="n"/>
-      <c r="AF101" s="32" t="n"/>
-      <c r="AG101" s="32" t="n"/>
-      <c r="AH101" s="32" t="n"/>
-      <c r="AI101" s="32" t="n"/>
-      <c r="AJ101" s="32" t="n"/>
-      <c r="AK101" s="32" t="n"/>
-      <c r="AL101" s="32" t="n"/>
-      <c r="AM101" s="32" t="n"/>
-      <c r="AN101" s="32" t="n"/>
-      <c r="AO101" s="32" t="n"/>
-      <c r="AP101" s="32" t="n"/>
-      <c r="AQ101" s="32" t="n"/>
-      <c r="AR101" s="32" t="n"/>
-      <c r="AS101" s="32" t="n"/>
-      <c r="AT101" s="32" t="n"/>
-      <c r="AU101" s="32" t="n"/>
-      <c r="AV101" s="32" t="n"/>
-      <c r="AW101" s="32" t="n"/>
-      <c r="AX101" s="32" t="n"/>
-      <c r="AY101" s="32" t="n"/>
-      <c r="AZ101" s="32" t="n"/>
-      <c r="BA101" s="32" t="n"/>
-      <c r="BB101" s="32" t="n"/>
-      <c r="BC101" s="32" t="n"/>
-      <c r="BX101" s="32" t="n"/>
-      <c r="BY101" s="32" t="n"/>
-      <c r="BZ101" s="32" t="n"/>
-      <c r="CA101" s="32" t="n"/>
-      <c r="CB101" s="32" t="n"/>
-      <c r="CC101" s="32" t="n"/>
       <c r="CD101" s="32" t="n"/>
       <c r="EM101" s="32" t="n"/>
       <c r="EN101" s="32" t="n"/>
@@ -10101,46 +9732,6 @@
       <c r="P102" s="14" t="n"/>
       <c r="T102" s="16" t="n"/>
       <c r="U102" s="32" t="n"/>
-      <c r="V102" s="32" t="n"/>
-      <c r="W102" s="32" t="n"/>
-      <c r="X102" s="32" t="n"/>
-      <c r="Y102" s="32" t="n"/>
-      <c r="Z102" s="32" t="n"/>
-      <c r="AA102" s="32" t="n"/>
-      <c r="AB102" s="32" t="n"/>
-      <c r="AC102" s="32" t="n"/>
-      <c r="AD102" s="32" t="n"/>
-      <c r="AE102" s="32" t="n"/>
-      <c r="AF102" s="32" t="n"/>
-      <c r="AG102" s="32" t="n"/>
-      <c r="AH102" s="32" t="n"/>
-      <c r="AI102" s="32" t="n"/>
-      <c r="AJ102" s="32" t="n"/>
-      <c r="AK102" s="32" t="n"/>
-      <c r="AL102" s="32" t="n"/>
-      <c r="AM102" s="32" t="n"/>
-      <c r="AN102" s="32" t="n"/>
-      <c r="AO102" s="32" t="n"/>
-      <c r="AP102" s="32" t="n"/>
-      <c r="AQ102" s="32" t="n"/>
-      <c r="AR102" s="32" t="n"/>
-      <c r="AS102" s="32" t="n"/>
-      <c r="AT102" s="32" t="n"/>
-      <c r="AU102" s="32" t="n"/>
-      <c r="AV102" s="32" t="n"/>
-      <c r="AW102" s="32" t="n"/>
-      <c r="AX102" s="32" t="n"/>
-      <c r="AY102" s="32" t="n"/>
-      <c r="AZ102" s="32" t="n"/>
-      <c r="BA102" s="32" t="n"/>
-      <c r="BB102" s="32" t="n"/>
-      <c r="BC102" s="32" t="n"/>
-      <c r="BX102" s="32" t="n"/>
-      <c r="BY102" s="32" t="n"/>
-      <c r="BZ102" s="32" t="n"/>
-      <c r="CA102" s="32" t="n"/>
-      <c r="CB102" s="32" t="n"/>
-      <c r="CC102" s="32" t="n"/>
       <c r="CD102" s="32" t="n"/>
       <c r="EM102" s="32" t="n"/>
       <c r="EN102" s="32" t="n"/>
@@ -10193,46 +9784,6 @@
       <c r="P103" s="14" t="n"/>
       <c r="T103" s="16" t="n"/>
       <c r="U103" s="32" t="n"/>
-      <c r="V103" s="32" t="n"/>
-      <c r="W103" s="32" t="n"/>
-      <c r="X103" s="32" t="n"/>
-      <c r="Y103" s="32" t="n"/>
-      <c r="Z103" s="32" t="n"/>
-      <c r="AA103" s="32" t="n"/>
-      <c r="AB103" s="32" t="n"/>
-      <c r="AC103" s="32" t="n"/>
-      <c r="AD103" s="32" t="n"/>
-      <c r="AE103" s="32" t="n"/>
-      <c r="AF103" s="32" t="n"/>
-      <c r="AG103" s="32" t="n"/>
-      <c r="AH103" s="32" t="n"/>
-      <c r="AI103" s="32" t="n"/>
-      <c r="AJ103" s="32" t="n"/>
-      <c r="AK103" s="32" t="n"/>
-      <c r="AL103" s="32" t="n"/>
-      <c r="AM103" s="32" t="n"/>
-      <c r="AN103" s="32" t="n"/>
-      <c r="AO103" s="32" t="n"/>
-      <c r="AP103" s="32" t="n"/>
-      <c r="AQ103" s="32" t="n"/>
-      <c r="AR103" s="32" t="n"/>
-      <c r="AS103" s="32" t="n"/>
-      <c r="AT103" s="32" t="n"/>
-      <c r="AU103" s="32" t="n"/>
-      <c r="AV103" s="32" t="n"/>
-      <c r="AW103" s="32" t="n"/>
-      <c r="AX103" s="32" t="n"/>
-      <c r="AY103" s="32" t="n"/>
-      <c r="AZ103" s="32" t="n"/>
-      <c r="BA103" s="32" t="n"/>
-      <c r="BB103" s="32" t="n"/>
-      <c r="BC103" s="32" t="n"/>
-      <c r="BX103" s="32" t="n"/>
-      <c r="BY103" s="32" t="n"/>
-      <c r="BZ103" s="32" t="n"/>
-      <c r="CA103" s="32" t="n"/>
-      <c r="CB103" s="32" t="n"/>
-      <c r="CC103" s="32" t="n"/>
       <c r="CD103" s="32" t="n"/>
       <c r="EM103" s="32" t="n"/>
       <c r="EN103" s="32" t="n"/>
@@ -10288,46 +9839,6 @@
       <c r="S104" s="18" t="n"/>
       <c r="T104" s="19" t="n"/>
       <c r="U104" s="32" t="n"/>
-      <c r="V104" s="32" t="n"/>
-      <c r="W104" s="32" t="n"/>
-      <c r="X104" s="32" t="n"/>
-      <c r="Y104" s="32" t="n"/>
-      <c r="Z104" s="32" t="n"/>
-      <c r="AA104" s="32" t="n"/>
-      <c r="AB104" s="32" t="n"/>
-      <c r="AC104" s="32" t="n"/>
-      <c r="AD104" s="32" t="n"/>
-      <c r="AE104" s="32" t="n"/>
-      <c r="AF104" s="32" t="n"/>
-      <c r="AG104" s="32" t="n"/>
-      <c r="AH104" s="32" t="n"/>
-      <c r="AI104" s="32" t="n"/>
-      <c r="AJ104" s="32" t="n"/>
-      <c r="AK104" s="32" t="n"/>
-      <c r="AL104" s="32" t="n"/>
-      <c r="AM104" s="32" t="n"/>
-      <c r="AN104" s="32" t="n"/>
-      <c r="AO104" s="32" t="n"/>
-      <c r="AP104" s="32" t="n"/>
-      <c r="AQ104" s="32" t="n"/>
-      <c r="AR104" s="32" t="n"/>
-      <c r="AS104" s="32" t="n"/>
-      <c r="AT104" s="32" t="n"/>
-      <c r="AU104" s="32" t="n"/>
-      <c r="AV104" s="32" t="n"/>
-      <c r="AW104" s="32" t="n"/>
-      <c r="AX104" s="32" t="n"/>
-      <c r="AY104" s="32" t="n"/>
-      <c r="AZ104" s="32" t="n"/>
-      <c r="BA104" s="32" t="n"/>
-      <c r="BB104" s="32" t="n"/>
-      <c r="BC104" s="32" t="n"/>
-      <c r="BX104" s="32" t="n"/>
-      <c r="BY104" s="32" t="n"/>
-      <c r="BZ104" s="32" t="n"/>
-      <c r="CA104" s="32" t="n"/>
-      <c r="CB104" s="32" t="n"/>
-      <c r="CC104" s="32" t="n"/>
       <c r="CD104" s="32" t="n"/>
       <c r="EM104" s="32" t="n"/>
       <c r="EN104" s="32" t="n"/>
@@ -10390,66 +9901,6 @@
       <c r="S105" s="12" t="n"/>
       <c r="T105" s="13" t="n"/>
       <c r="U105" s="32" t="n"/>
-      <c r="V105" s="32" t="n"/>
-      <c r="W105" s="32" t="n"/>
-      <c r="X105" s="32" t="n"/>
-      <c r="Y105" s="32" t="n"/>
-      <c r="Z105" s="32" t="n"/>
-      <c r="AA105" s="32" t="n"/>
-      <c r="AB105" s="32" t="n"/>
-      <c r="AC105" s="32" t="n"/>
-      <c r="AD105" s="32" t="n"/>
-      <c r="AE105" s="32" t="n"/>
-      <c r="AF105" s="32" t="n"/>
-      <c r="AG105" s="32" t="n"/>
-      <c r="AH105" s="32" t="n"/>
-      <c r="AI105" s="32" t="n"/>
-      <c r="AJ105" s="32" t="n"/>
-      <c r="AK105" s="32" t="n"/>
-      <c r="AL105" s="32" t="n"/>
-      <c r="AM105" s="32" t="n"/>
-      <c r="AN105" s="32" t="n"/>
-      <c r="AO105" s="32" t="n"/>
-      <c r="AP105" s="32" t="n"/>
-      <c r="AQ105" s="32" t="n"/>
-      <c r="AR105" s="32" t="n"/>
-      <c r="AS105" s="32" t="n"/>
-      <c r="AT105" s="32" t="n"/>
-      <c r="AU105" s="32" t="n"/>
-      <c r="AV105" s="32" t="n"/>
-      <c r="AW105" s="32" t="n"/>
-      <c r="AX105" s="32" t="n"/>
-      <c r="AY105" s="32" t="n"/>
-      <c r="AZ105" s="32" t="n"/>
-      <c r="BA105" s="32" t="n"/>
-      <c r="BB105" s="32" t="n"/>
-      <c r="BC105" s="32" t="n"/>
-      <c r="BD105" s="32" t="n"/>
-      <c r="BE105" s="32" t="n"/>
-      <c r="BF105" s="32" t="n"/>
-      <c r="BG105" s="32" t="n"/>
-      <c r="BH105" s="32" t="n"/>
-      <c r="BI105" s="32" t="n"/>
-      <c r="BJ105" s="32" t="n"/>
-      <c r="BK105" s="32" t="n"/>
-      <c r="BL105" s="32" t="n"/>
-      <c r="BM105" s="32" t="n"/>
-      <c r="BN105" s="32" t="n"/>
-      <c r="BO105" s="32" t="n"/>
-      <c r="BP105" s="32" t="n"/>
-      <c r="BQ105" s="32" t="n"/>
-      <c r="BR105" s="32" t="n"/>
-      <c r="BS105" s="32" t="n"/>
-      <c r="BT105" s="32" t="n"/>
-      <c r="BU105" s="32" t="n"/>
-      <c r="BV105" s="32" t="n"/>
-      <c r="BW105" s="32" t="n"/>
-      <c r="BX105" s="32" t="n"/>
-      <c r="BY105" s="32" t="n"/>
-      <c r="BZ105" s="32" t="n"/>
-      <c r="CA105" s="32" t="n"/>
-      <c r="CB105" s="32" t="n"/>
-      <c r="CC105" s="32" t="n"/>
       <c r="CD105" s="32" t="n"/>
       <c r="EM105" s="32" t="n"/>
       <c r="EN105" s="32" t="n"/>
@@ -10529,66 +9980,6 @@
       <c r="P106" s="14" t="n"/>
       <c r="T106" s="16" t="n"/>
       <c r="U106" s="32" t="n"/>
-      <c r="V106" s="32" t="n"/>
-      <c r="W106" s="32" t="n"/>
-      <c r="X106" s="32" t="n"/>
-      <c r="Y106" s="32" t="n"/>
-      <c r="Z106" s="32" t="n"/>
-      <c r="AA106" s="32" t="n"/>
-      <c r="AB106" s="32" t="n"/>
-      <c r="AC106" s="32" t="n"/>
-      <c r="AD106" s="32" t="n"/>
-      <c r="AE106" s="32" t="n"/>
-      <c r="AF106" s="32" t="n"/>
-      <c r="AG106" s="32" t="n"/>
-      <c r="AH106" s="32" t="n"/>
-      <c r="AI106" s="32" t="n"/>
-      <c r="AJ106" s="32" t="n"/>
-      <c r="AK106" s="32" t="n"/>
-      <c r="AL106" s="32" t="n"/>
-      <c r="AM106" s="32" t="n"/>
-      <c r="AN106" s="32" t="n"/>
-      <c r="AO106" s="32" t="n"/>
-      <c r="AP106" s="32" t="n"/>
-      <c r="AQ106" s="32" t="n"/>
-      <c r="AR106" s="32" t="n"/>
-      <c r="AS106" s="32" t="n"/>
-      <c r="AT106" s="32" t="n"/>
-      <c r="AU106" s="32" t="n"/>
-      <c r="AV106" s="32" t="n"/>
-      <c r="AW106" s="32" t="n"/>
-      <c r="AX106" s="32" t="n"/>
-      <c r="AY106" s="32" t="n"/>
-      <c r="AZ106" s="32" t="n"/>
-      <c r="BA106" s="32" t="n"/>
-      <c r="BB106" s="32" t="n"/>
-      <c r="BC106" s="32" t="n"/>
-      <c r="BD106" s="32" t="n"/>
-      <c r="BE106" s="32" t="n"/>
-      <c r="BF106" s="32" t="n"/>
-      <c r="BG106" s="32" t="n"/>
-      <c r="BH106" s="32" t="n"/>
-      <c r="BI106" s="32" t="n"/>
-      <c r="BJ106" s="32" t="n"/>
-      <c r="BK106" s="32" t="n"/>
-      <c r="BL106" s="32" t="n"/>
-      <c r="BM106" s="32" t="n"/>
-      <c r="BN106" s="32" t="n"/>
-      <c r="BO106" s="32" t="n"/>
-      <c r="BP106" s="32" t="n"/>
-      <c r="BQ106" s="32" t="n"/>
-      <c r="BR106" s="32" t="n"/>
-      <c r="BS106" s="32" t="n"/>
-      <c r="BT106" s="32" t="n"/>
-      <c r="BU106" s="32" t="n"/>
-      <c r="BV106" s="32" t="n"/>
-      <c r="BW106" s="32" t="n"/>
-      <c r="BX106" s="32" t="n"/>
-      <c r="BY106" s="32" t="n"/>
-      <c r="BZ106" s="32" t="n"/>
-      <c r="CA106" s="32" t="n"/>
-      <c r="CB106" s="32" t="n"/>
-      <c r="CC106" s="32" t="n"/>
       <c r="CD106" s="32" t="n"/>
       <c r="EM106" s="32" t="n"/>
       <c r="EN106" s="32" t="n"/>
@@ -10661,66 +10052,6 @@
       <c r="P107" s="14" t="n"/>
       <c r="T107" s="16" t="n"/>
       <c r="U107" s="32" t="n"/>
-      <c r="V107" s="32" t="n"/>
-      <c r="W107" s="32" t="n"/>
-      <c r="X107" s="32" t="n"/>
-      <c r="Y107" s="32" t="n"/>
-      <c r="Z107" s="32" t="n"/>
-      <c r="AA107" s="32" t="n"/>
-      <c r="AB107" s="32" t="n"/>
-      <c r="AC107" s="32" t="n"/>
-      <c r="AD107" s="32" t="n"/>
-      <c r="AE107" s="32" t="n"/>
-      <c r="AF107" s="32" t="n"/>
-      <c r="AG107" s="32" t="n"/>
-      <c r="AH107" s="32" t="n"/>
-      <c r="AI107" s="32" t="n"/>
-      <c r="AJ107" s="32" t="n"/>
-      <c r="AK107" s="32" t="n"/>
-      <c r="AL107" s="32" t="n"/>
-      <c r="AM107" s="32" t="n"/>
-      <c r="AN107" s="32" t="n"/>
-      <c r="AO107" s="32" t="n"/>
-      <c r="AP107" s="32" t="n"/>
-      <c r="AQ107" s="32" t="n"/>
-      <c r="AR107" s="32" t="n"/>
-      <c r="AS107" s="32" t="n"/>
-      <c r="AT107" s="32" t="n"/>
-      <c r="AU107" s="32" t="n"/>
-      <c r="AV107" s="32" t="n"/>
-      <c r="AW107" s="32" t="n"/>
-      <c r="AX107" s="32" t="n"/>
-      <c r="AY107" s="32" t="n"/>
-      <c r="AZ107" s="32" t="n"/>
-      <c r="BA107" s="32" t="n"/>
-      <c r="BB107" s="32" t="n"/>
-      <c r="BC107" s="32" t="n"/>
-      <c r="BD107" s="32" t="n"/>
-      <c r="BE107" s="32" t="n"/>
-      <c r="BF107" s="32" t="n"/>
-      <c r="BG107" s="32" t="n"/>
-      <c r="BH107" s="32" t="n"/>
-      <c r="BI107" s="32" t="n"/>
-      <c r="BJ107" s="32" t="n"/>
-      <c r="BK107" s="32" t="n"/>
-      <c r="BL107" s="32" t="n"/>
-      <c r="BM107" s="32" t="n"/>
-      <c r="BN107" s="32" t="n"/>
-      <c r="BO107" s="32" t="n"/>
-      <c r="BP107" s="32" t="n"/>
-      <c r="BQ107" s="32" t="n"/>
-      <c r="BR107" s="32" t="n"/>
-      <c r="BS107" s="32" t="n"/>
-      <c r="BT107" s="32" t="n"/>
-      <c r="BU107" s="32" t="n"/>
-      <c r="BV107" s="32" t="n"/>
-      <c r="BW107" s="32" t="n"/>
-      <c r="BX107" s="32" t="n"/>
-      <c r="BY107" s="32" t="n"/>
-      <c r="BZ107" s="32" t="n"/>
-      <c r="CA107" s="32" t="n"/>
-      <c r="CB107" s="32" t="n"/>
-      <c r="CC107" s="32" t="n"/>
       <c r="CD107" s="32" t="n"/>
       <c r="EM107" s="32" t="n"/>
       <c r="EN107" s="32" t="n"/>
@@ -10793,66 +10124,6 @@
       <c r="P108" s="14" t="n"/>
       <c r="T108" s="16" t="n"/>
       <c r="U108" s="32" t="n"/>
-      <c r="V108" s="32" t="n"/>
-      <c r="W108" s="32" t="n"/>
-      <c r="X108" s="32" t="n"/>
-      <c r="Y108" s="32" t="n"/>
-      <c r="Z108" s="32" t="n"/>
-      <c r="AA108" s="32" t="n"/>
-      <c r="AB108" s="32" t="n"/>
-      <c r="AC108" s="32" t="n"/>
-      <c r="AD108" s="32" t="n"/>
-      <c r="AE108" s="32" t="n"/>
-      <c r="AF108" s="32" t="n"/>
-      <c r="AG108" s="32" t="n"/>
-      <c r="AH108" s="32" t="n"/>
-      <c r="AI108" s="32" t="n"/>
-      <c r="AJ108" s="32" t="n"/>
-      <c r="AK108" s="32" t="n"/>
-      <c r="AL108" s="32" t="n"/>
-      <c r="AM108" s="32" t="n"/>
-      <c r="AN108" s="32" t="n"/>
-      <c r="AO108" s="32" t="n"/>
-      <c r="AP108" s="32" t="n"/>
-      <c r="AQ108" s="32" t="n"/>
-      <c r="AR108" s="32" t="n"/>
-      <c r="AS108" s="32" t="n"/>
-      <c r="AT108" s="32" t="n"/>
-      <c r="AU108" s="32" t="n"/>
-      <c r="AV108" s="32" t="n"/>
-      <c r="AW108" s="32" t="n"/>
-      <c r="AX108" s="32" t="n"/>
-      <c r="AY108" s="32" t="n"/>
-      <c r="AZ108" s="32" t="n"/>
-      <c r="BA108" s="32" t="n"/>
-      <c r="BB108" s="32" t="n"/>
-      <c r="BC108" s="32" t="n"/>
-      <c r="BD108" s="32" t="n"/>
-      <c r="BE108" s="32" t="n"/>
-      <c r="BF108" s="32" t="n"/>
-      <c r="BG108" s="32" t="n"/>
-      <c r="BH108" s="32" t="n"/>
-      <c r="BI108" s="32" t="n"/>
-      <c r="BJ108" s="32" t="n"/>
-      <c r="BK108" s="32" t="n"/>
-      <c r="BL108" s="32" t="n"/>
-      <c r="BM108" s="32" t="n"/>
-      <c r="BN108" s="32" t="n"/>
-      <c r="BO108" s="32" t="n"/>
-      <c r="BP108" s="32" t="n"/>
-      <c r="BQ108" s="32" t="n"/>
-      <c r="BR108" s="32" t="n"/>
-      <c r="BS108" s="32" t="n"/>
-      <c r="BT108" s="32" t="n"/>
-      <c r="BU108" s="32" t="n"/>
-      <c r="BV108" s="32" t="n"/>
-      <c r="BW108" s="32" t="n"/>
-      <c r="BX108" s="32" t="n"/>
-      <c r="BY108" s="32" t="n"/>
-      <c r="BZ108" s="32" t="n"/>
-      <c r="CA108" s="32" t="n"/>
-      <c r="CB108" s="32" t="n"/>
-      <c r="CC108" s="32" t="n"/>
       <c r="CD108" s="32" t="n"/>
       <c r="EM108" s="32" t="n"/>
       <c r="EN108" s="32" t="n"/>
@@ -10925,66 +10196,6 @@
       <c r="P109" s="14" t="n"/>
       <c r="T109" s="16" t="n"/>
       <c r="U109" s="32" t="n"/>
-      <c r="V109" s="32" t="n"/>
-      <c r="W109" s="32" t="n"/>
-      <c r="X109" s="32" t="n"/>
-      <c r="Y109" s="32" t="n"/>
-      <c r="Z109" s="32" t="n"/>
-      <c r="AA109" s="32" t="n"/>
-      <c r="AB109" s="32" t="n"/>
-      <c r="AC109" s="32" t="n"/>
-      <c r="AD109" s="32" t="n"/>
-      <c r="AE109" s="32" t="n"/>
-      <c r="AF109" s="32" t="n"/>
-      <c r="AG109" s="32" t="n"/>
-      <c r="AH109" s="32" t="n"/>
-      <c r="AI109" s="32" t="n"/>
-      <c r="AJ109" s="32" t="n"/>
-      <c r="AK109" s="32" t="n"/>
-      <c r="AL109" s="32" t="n"/>
-      <c r="AM109" s="32" t="n"/>
-      <c r="AN109" s="32" t="n"/>
-      <c r="AO109" s="32" t="n"/>
-      <c r="AP109" s="32" t="n"/>
-      <c r="AQ109" s="32" t="n"/>
-      <c r="AR109" s="32" t="n"/>
-      <c r="AS109" s="32" t="n"/>
-      <c r="AT109" s="32" t="n"/>
-      <c r="AU109" s="32" t="n"/>
-      <c r="AV109" s="32" t="n"/>
-      <c r="AW109" s="32" t="n"/>
-      <c r="AX109" s="32" t="n"/>
-      <c r="AY109" s="32" t="n"/>
-      <c r="AZ109" s="32" t="n"/>
-      <c r="BA109" s="32" t="n"/>
-      <c r="BB109" s="32" t="n"/>
-      <c r="BC109" s="32" t="n"/>
-      <c r="BD109" s="32" t="n"/>
-      <c r="BE109" s="32" t="n"/>
-      <c r="BF109" s="32" t="n"/>
-      <c r="BG109" s="32" t="n"/>
-      <c r="BH109" s="32" t="n"/>
-      <c r="BI109" s="32" t="n"/>
-      <c r="BJ109" s="32" t="n"/>
-      <c r="BK109" s="32" t="n"/>
-      <c r="BL109" s="32" t="n"/>
-      <c r="BM109" s="32" t="n"/>
-      <c r="BN109" s="32" t="n"/>
-      <c r="BO109" s="32" t="n"/>
-      <c r="BP109" s="32" t="n"/>
-      <c r="BQ109" s="32" t="n"/>
-      <c r="BR109" s="32" t="n"/>
-      <c r="BS109" s="32" t="n"/>
-      <c r="BT109" s="32" t="n"/>
-      <c r="BU109" s="32" t="n"/>
-      <c r="BV109" s="32" t="n"/>
-      <c r="BW109" s="32" t="n"/>
-      <c r="BX109" s="32" t="n"/>
-      <c r="BY109" s="32" t="n"/>
-      <c r="BZ109" s="32" t="n"/>
-      <c r="CA109" s="32" t="n"/>
-      <c r="CB109" s="32" t="n"/>
-      <c r="CC109" s="32" t="n"/>
       <c r="CD109" s="32" t="n"/>
       <c r="EM109" s="32" t="n"/>
       <c r="EN109" s="32" t="n"/>
@@ -11145,16 +10356,6 @@
       <c r="P110" s="14" t="n"/>
       <c r="T110" s="16" t="n"/>
       <c r="U110" s="32" t="n"/>
-      <c r="V110" s="32" t="n"/>
-      <c r="W110" s="32" t="n"/>
-      <c r="X110" s="32" t="n"/>
-      <c r="Y110" s="32" t="n"/>
-      <c r="Z110" s="32" t="n"/>
-      <c r="AA110" s="32" t="n"/>
-      <c r="AB110" s="32" t="n"/>
-      <c r="AC110" s="32" t="n"/>
-      <c r="AD110" s="32" t="n"/>
-      <c r="AE110" s="32" t="n"/>
       <c r="GM110" s="32" t="n"/>
       <c r="GN110" s="32" t="n"/>
       <c r="GO110" s="32" t="n"/>
@@ -11176,15 +10377,6 @@
       <c r="P111" s="14" t="n"/>
       <c r="T111" s="16" t="n"/>
       <c r="U111" s="32" t="n"/>
-      <c r="V111" s="32" t="n"/>
-      <c r="W111" s="32" t="n"/>
-      <c r="X111" s="32" t="n"/>
-      <c r="Y111" s="32" t="n"/>
-      <c r="Z111" s="32" t="n"/>
-      <c r="AA111" s="32" t="n"/>
-      <c r="AB111" s="32" t="n"/>
-      <c r="AC111" s="32" t="n"/>
-      <c r="AD111" s="32" t="n"/>
       <c r="GM111" s="32" t="n"/>
       <c r="GN111" s="32" t="n"/>
       <c r="GO111" s="32" t="n"/>
@@ -11206,15 +10398,6 @@
       <c r="P112" s="14" t="n"/>
       <c r="T112" s="16" t="n"/>
       <c r="U112" s="32" t="n"/>
-      <c r="V112" s="32" t="n"/>
-      <c r="W112" s="32" t="n"/>
-      <c r="X112" s="32" t="n"/>
-      <c r="Y112" s="32" t="n"/>
-      <c r="Z112" s="32" t="n"/>
-      <c r="AA112" s="32" t="n"/>
-      <c r="AB112" s="32" t="n"/>
-      <c r="AC112" s="32" t="n"/>
-      <c r="AD112" s="32" t="n"/>
       <c r="GM112" s="32" t="n"/>
       <c r="GN112" s="32" t="n"/>
       <c r="GO112" s="32" t="n"/>
@@ -11236,15 +10419,6 @@
       <c r="P113" s="14" t="n"/>
       <c r="T113" s="16" t="n"/>
       <c r="U113" s="32" t="n"/>
-      <c r="V113" s="32" t="n"/>
-      <c r="W113" s="32" t="n"/>
-      <c r="X113" s="32" t="n"/>
-      <c r="Y113" s="32" t="n"/>
-      <c r="Z113" s="32" t="n"/>
-      <c r="AA113" s="32" t="n"/>
-      <c r="AB113" s="32" t="n"/>
-      <c r="AC113" s="32" t="n"/>
-      <c r="AD113" s="32" t="n"/>
       <c r="GM113" s="32" t="n"/>
       <c r="GN113" s="32" t="n"/>
       <c r="GO113" s="32" t="n"/>
@@ -12126,16 +11300,12 @@
       <c r="P134" s="14" t="n"/>
       <c r="T134" s="16" t="n"/>
       <c r="U134" s="32" t="n"/>
-      <c r="V134" s="32" t="n"/>
-      <c r="W134" s="32" t="n"/>
-      <c r="X134" s="32" t="n"/>
-      <c r="Y134" s="32" t="n"/>
-      <c r="Z134" s="32" t="n"/>
-      <c r="AA134" s="32" t="n"/>
-      <c r="AB134" s="32" t="n"/>
-      <c r="AC134" s="32" t="n"/>
-      <c r="AD134" s="32" t="n"/>
-      <c r="CE134" t="inlineStr">
+      <c r="V134" s="34" t="inlineStr">
+        <is>
+          <t>{Input_203}</t>
+        </is>
+      </c>
+      <c r="CE134" s="32" t="inlineStr">
         <is>
           <t>{View_4}</t>
         </is>
@@ -12159,15 +11329,6 @@
       <c r="P135" s="14" t="n"/>
       <c r="T135" s="16" t="n"/>
       <c r="U135" s="32" t="n"/>
-      <c r="V135" s="32" t="n"/>
-      <c r="W135" s="32" t="n"/>
-      <c r="X135" s="32" t="n"/>
-      <c r="Y135" s="32" t="n"/>
-      <c r="Z135" s="32" t="n"/>
-      <c r="AA135" s="32" t="n"/>
-      <c r="AB135" s="32" t="n"/>
-      <c r="AC135" s="32" t="n"/>
-      <c r="AD135" s="32" t="n"/>
       <c r="GM135" s="32" t="n"/>
       <c r="GN135" s="32" t="n"/>
       <c r="GO135" s="32" t="n"/>
@@ -12187,15 +11348,6 @@
       <c r="P136" s="14" t="n"/>
       <c r="T136" s="16" t="n"/>
       <c r="U136" s="32" t="n"/>
-      <c r="V136" s="32" t="n"/>
-      <c r="W136" s="32" t="n"/>
-      <c r="X136" s="32" t="n"/>
-      <c r="Y136" s="32" t="n"/>
-      <c r="Z136" s="32" t="n"/>
-      <c r="AA136" s="32" t="n"/>
-      <c r="AB136" s="32" t="n"/>
-      <c r="AC136" s="32" t="n"/>
-      <c r="AD136" s="32" t="n"/>
       <c r="GM136" s="32" t="n"/>
       <c r="GN136" s="32" t="n"/>
       <c r="GO136" s="32" t="n"/>
@@ -12215,15 +11367,6 @@
       <c r="P137" s="14" t="n"/>
       <c r="T137" s="16" t="n"/>
       <c r="U137" s="32" t="n"/>
-      <c r="V137" s="32" t="n"/>
-      <c r="W137" s="32" t="n"/>
-      <c r="X137" s="32" t="n"/>
-      <c r="Y137" s="32" t="n"/>
-      <c r="Z137" s="32" t="n"/>
-      <c r="AA137" s="32" t="n"/>
-      <c r="AB137" s="32" t="n"/>
-      <c r="AC137" s="32" t="n"/>
-      <c r="AD137" s="32" t="n"/>
       <c r="GM137" s="32" t="n"/>
       <c r="GN137" s="32" t="n"/>
       <c r="GO137" s="32" t="n"/>
@@ -12243,15 +11386,6 @@
       <c r="P138" s="14" t="n"/>
       <c r="T138" s="16" t="n"/>
       <c r="U138" s="32" t="n"/>
-      <c r="V138" s="32" t="n"/>
-      <c r="W138" s="32" t="n"/>
-      <c r="X138" s="32" t="n"/>
-      <c r="Y138" s="32" t="n"/>
-      <c r="Z138" s="32" t="n"/>
-      <c r="AA138" s="32" t="n"/>
-      <c r="AB138" s="32" t="n"/>
-      <c r="AC138" s="32" t="n"/>
-      <c r="AD138" s="32" t="n"/>
       <c r="GM138" s="32" t="n"/>
       <c r="GN138" s="32" t="n"/>
       <c r="GO138" s="32" t="n"/>
@@ -12375,15 +11509,6 @@
       <c r="P139" s="14" t="n"/>
       <c r="T139" s="16" t="n"/>
       <c r="U139" s="32" t="n"/>
-      <c r="V139" s="32" t="n"/>
-      <c r="W139" s="32" t="n"/>
-      <c r="X139" s="32" t="n"/>
-      <c r="Y139" s="32" t="n"/>
-      <c r="Z139" s="32" t="n"/>
-      <c r="AA139" s="32" t="n"/>
-      <c r="AB139" s="32" t="n"/>
-      <c r="AC139" s="32" t="n"/>
-      <c r="AD139" s="32" t="n"/>
       <c r="GM139" s="32" t="n"/>
       <c r="GN139" s="32" t="n"/>
       <c r="GO139" s="32" t="n"/>
@@ -12415,15 +11540,6 @@
       <c r="P140" s="14" t="n"/>
       <c r="T140" s="16" t="n"/>
       <c r="U140" s="32" t="n"/>
-      <c r="V140" s="32" t="n"/>
-      <c r="W140" s="32" t="n"/>
-      <c r="X140" s="32" t="n"/>
-      <c r="Y140" s="32" t="n"/>
-      <c r="Z140" s="32" t="n"/>
-      <c r="AA140" s="32" t="n"/>
-      <c r="AB140" s="32" t="n"/>
-      <c r="AC140" s="32" t="n"/>
-      <c r="AD140" s="32" t="n"/>
       <c r="GM140" s="32" t="n"/>
       <c r="GN140" s="32" t="n"/>
       <c r="GO140" s="32" t="n"/>
@@ -12523,15 +11639,6 @@
       <c r="P141" s="14" t="n"/>
       <c r="T141" s="16" t="n"/>
       <c r="U141" s="32" t="n"/>
-      <c r="V141" s="32" t="n"/>
-      <c r="W141" s="32" t="n"/>
-      <c r="X141" s="32" t="n"/>
-      <c r="Y141" s="32" t="n"/>
-      <c r="Z141" s="32" t="n"/>
-      <c r="AA141" s="32" t="n"/>
-      <c r="AB141" s="32" t="n"/>
-      <c r="AC141" s="32" t="n"/>
-      <c r="AD141" s="32" t="n"/>
       <c r="GM141" s="32" t="n"/>
       <c r="GN141" s="32" t="n"/>
       <c r="GO141" s="32" t="n"/>
@@ -12655,15 +11762,6 @@
       <c r="P142" s="14" t="n"/>
       <c r="T142" s="16" t="n"/>
       <c r="U142" s="32" t="n"/>
-      <c r="V142" s="32" t="n"/>
-      <c r="W142" s="32" t="n"/>
-      <c r="X142" s="32" t="n"/>
-      <c r="Y142" s="32" t="n"/>
-      <c r="Z142" s="32" t="n"/>
-      <c r="AA142" s="32" t="n"/>
-      <c r="AB142" s="32" t="n"/>
-      <c r="AC142" s="32" t="n"/>
-      <c r="AD142" s="32" t="n"/>
       <c r="GM142" s="32" t="n"/>
       <c r="GN142" s="32" t="n"/>
       <c r="GO142" s="32" t="n"/>
@@ -12695,15 +11793,6 @@
       <c r="P143" s="14" t="n"/>
       <c r="T143" s="16" t="n"/>
       <c r="U143" s="32" t="n"/>
-      <c r="V143" s="32" t="n"/>
-      <c r="W143" s="32" t="n"/>
-      <c r="X143" s="32" t="n"/>
-      <c r="Y143" s="32" t="n"/>
-      <c r="Z143" s="32" t="n"/>
-      <c r="AA143" s="32" t="n"/>
-      <c r="AB143" s="32" t="n"/>
-      <c r="AC143" s="32" t="n"/>
-      <c r="AD143" s="32" t="n"/>
       <c r="GM143" s="32" t="n"/>
       <c r="GN143" s="32" t="n"/>
       <c r="GO143" s="32" t="n"/>
@@ -12803,15 +11892,6 @@
       <c r="P144" s="14" t="n"/>
       <c r="T144" s="16" t="n"/>
       <c r="U144" s="32" t="n"/>
-      <c r="V144" s="32" t="n"/>
-      <c r="W144" s="32" t="n"/>
-      <c r="X144" s="32" t="n"/>
-      <c r="Y144" s="32" t="n"/>
-      <c r="Z144" s="32" t="n"/>
-      <c r="AA144" s="32" t="n"/>
-      <c r="AB144" s="32" t="n"/>
-      <c r="AC144" s="32" t="n"/>
-      <c r="AD144" s="32" t="n"/>
       <c r="GM144" s="32" t="n"/>
       <c r="GN144" s="32" t="n"/>
       <c r="GO144" s="32" t="n"/>
@@ -12935,15 +12015,6 @@
       <c r="P145" s="14" t="n"/>
       <c r="T145" s="16" t="n"/>
       <c r="U145" s="32" t="n"/>
-      <c r="V145" s="32" t="n"/>
-      <c r="W145" s="32" t="n"/>
-      <c r="X145" s="32" t="n"/>
-      <c r="Y145" s="32" t="n"/>
-      <c r="Z145" s="32" t="n"/>
-      <c r="AA145" s="32" t="n"/>
-      <c r="AB145" s="32" t="n"/>
-      <c r="AC145" s="32" t="n"/>
-      <c r="AD145" s="32" t="n"/>
       <c r="GM145" s="32" t="n"/>
       <c r="GN145" s="32" t="n"/>
       <c r="GO145" s="32" t="n"/>
@@ -12975,15 +12046,6 @@
       <c r="P146" s="14" t="n"/>
       <c r="T146" s="16" t="n"/>
       <c r="U146" s="32" t="n"/>
-      <c r="V146" s="32" t="n"/>
-      <c r="W146" s="32" t="n"/>
-      <c r="X146" s="32" t="n"/>
-      <c r="Y146" s="32" t="n"/>
-      <c r="Z146" s="32" t="n"/>
-      <c r="AA146" s="32" t="n"/>
-      <c r="AB146" s="32" t="n"/>
-      <c r="AC146" s="32" t="n"/>
-      <c r="AD146" s="32" t="n"/>
       <c r="GM146" s="32" t="n"/>
       <c r="GN146" s="32" t="n"/>
       <c r="GO146" s="32" t="n"/>
@@ -13083,15 +12145,6 @@
       <c r="P147" s="14" t="n"/>
       <c r="T147" s="16" t="n"/>
       <c r="U147" s="32" t="n"/>
-      <c r="V147" s="32" t="n"/>
-      <c r="W147" s="32" t="n"/>
-      <c r="X147" s="32" t="n"/>
-      <c r="Y147" s="32" t="n"/>
-      <c r="Z147" s="32" t="n"/>
-      <c r="AA147" s="32" t="n"/>
-      <c r="AB147" s="32" t="n"/>
-      <c r="AC147" s="32" t="n"/>
-      <c r="AD147" s="32" t="n"/>
       <c r="GM147" s="32" t="n"/>
       <c r="GN147" s="32" t="n"/>
       <c r="GO147" s="32" t="n"/>
@@ -13215,15 +12268,6 @@
       <c r="P148" s="14" t="n"/>
       <c r="T148" s="16" t="n"/>
       <c r="U148" s="32" t="n"/>
-      <c r="V148" s="32" t="n"/>
-      <c r="W148" s="32" t="n"/>
-      <c r="X148" s="32" t="n"/>
-      <c r="Y148" s="32" t="n"/>
-      <c r="Z148" s="32" t="n"/>
-      <c r="AA148" s="32" t="n"/>
-      <c r="AB148" s="32" t="n"/>
-      <c r="AC148" s="32" t="n"/>
-      <c r="AD148" s="32" t="n"/>
       <c r="GM148" s="32" t="n"/>
       <c r="GN148" s="32" t="n"/>
       <c r="GO148" s="32" t="n"/>
@@ -13255,15 +12299,6 @@
       <c r="P149" s="14" t="n"/>
       <c r="T149" s="16" t="n"/>
       <c r="U149" s="32" t="n"/>
-      <c r="V149" s="32" t="n"/>
-      <c r="W149" s="32" t="n"/>
-      <c r="X149" s="32" t="n"/>
-      <c r="Y149" s="32" t="n"/>
-      <c r="Z149" s="32" t="n"/>
-      <c r="AA149" s="32" t="n"/>
-      <c r="AB149" s="32" t="n"/>
-      <c r="AC149" s="32" t="n"/>
-      <c r="AD149" s="32" t="n"/>
       <c r="GM149" s="32" t="n"/>
       <c r="GN149" s="32" t="n"/>
       <c r="GO149" s="32" t="n"/>
@@ -14927,16 +13962,12 @@
       <c r="P169" s="14" t="n"/>
       <c r="T169" s="16" t="n"/>
       <c r="U169" s="32" t="n"/>
-      <c r="V169" s="32" t="n"/>
-      <c r="W169" s="32" t="n"/>
-      <c r="X169" s="32" t="n"/>
-      <c r="Y169" s="32" t="n"/>
-      <c r="Z169" s="32" t="n"/>
-      <c r="AA169" s="32" t="n"/>
-      <c r="AB169" s="32" t="n"/>
-      <c r="AC169" s="32" t="n"/>
-      <c r="AD169" s="32" t="n"/>
-      <c r="CE169" t="inlineStr">
+      <c r="V169" s="34" t="inlineStr">
+        <is>
+          <t>{Input_204}</t>
+        </is>
+      </c>
+      <c r="CE169" s="32" t="inlineStr">
         <is>
           <t>{View_5}</t>
         </is>
@@ -14964,15 +13995,6 @@
       <c r="P170" s="14" t="n"/>
       <c r="T170" s="16" t="n"/>
       <c r="U170" s="32" t="n"/>
-      <c r="V170" s="32" t="n"/>
-      <c r="W170" s="32" t="n"/>
-      <c r="X170" s="32" t="n"/>
-      <c r="Y170" s="32" t="n"/>
-      <c r="Z170" s="32" t="n"/>
-      <c r="AA170" s="32" t="n"/>
-      <c r="AB170" s="32" t="n"/>
-      <c r="AC170" s="32" t="n"/>
-      <c r="AD170" s="32" t="n"/>
       <c r="GM170" s="32" t="n"/>
       <c r="GN170" s="32" t="n"/>
       <c r="GO170" s="32" t="n"/>
@@ -14996,15 +14018,6 @@
       <c r="P171" s="14" t="n"/>
       <c r="T171" s="16" t="n"/>
       <c r="U171" s="32" t="n"/>
-      <c r="V171" s="32" t="n"/>
-      <c r="W171" s="32" t="n"/>
-      <c r="X171" s="32" t="n"/>
-      <c r="Y171" s="32" t="n"/>
-      <c r="Z171" s="32" t="n"/>
-      <c r="AA171" s="32" t="n"/>
-      <c r="AB171" s="32" t="n"/>
-      <c r="AC171" s="32" t="n"/>
-      <c r="AD171" s="32" t="n"/>
       <c r="GM171" s="32" t="n"/>
       <c r="GN171" s="32" t="n"/>
       <c r="GO171" s="32" t="n"/>
@@ -15076,15 +14089,6 @@
       <c r="P172" s="14" t="n"/>
       <c r="T172" s="16" t="n"/>
       <c r="U172" s="32" t="n"/>
-      <c r="V172" s="32" t="n"/>
-      <c r="W172" s="32" t="n"/>
-      <c r="X172" s="32" t="n"/>
-      <c r="Y172" s="32" t="n"/>
-      <c r="Z172" s="32" t="n"/>
-      <c r="AA172" s="32" t="n"/>
-      <c r="AB172" s="32" t="n"/>
-      <c r="AC172" s="32" t="n"/>
-      <c r="AD172" s="32" t="n"/>
       <c r="GM172" s="32" t="n"/>
       <c r="GN172" s="32" t="n"/>
       <c r="GO172" s="32" t="n"/>
@@ -15160,15 +14164,6 @@
       <c r="P173" s="14" t="n"/>
       <c r="T173" s="16" t="n"/>
       <c r="U173" s="32" t="n"/>
-      <c r="V173" s="32" t="n"/>
-      <c r="W173" s="32" t="n"/>
-      <c r="X173" s="32" t="n"/>
-      <c r="Y173" s="32" t="n"/>
-      <c r="Z173" s="32" t="n"/>
-      <c r="AA173" s="32" t="n"/>
-      <c r="AB173" s="32" t="n"/>
-      <c r="AC173" s="32" t="n"/>
-      <c r="AD173" s="32" t="n"/>
       <c r="GM173" s="32" t="n"/>
       <c r="GN173" s="32" t="n"/>
       <c r="GO173" s="32" t="n"/>
@@ -15192,15 +14187,6 @@
       <c r="P174" s="14" t="n"/>
       <c r="T174" s="16" t="n"/>
       <c r="U174" s="32" t="n"/>
-      <c r="V174" s="32" t="n"/>
-      <c r="W174" s="32" t="n"/>
-      <c r="X174" s="32" t="n"/>
-      <c r="Y174" s="32" t="n"/>
-      <c r="Z174" s="32" t="n"/>
-      <c r="AA174" s="32" t="n"/>
-      <c r="AB174" s="32" t="n"/>
-      <c r="AC174" s="32" t="n"/>
-      <c r="AD174" s="32" t="n"/>
       <c r="GM174" s="32" t="n"/>
       <c r="GN174" s="32" t="n"/>
       <c r="GO174" s="32" t="n"/>
@@ -15224,15 +14210,6 @@
       <c r="P175" s="14" t="n"/>
       <c r="T175" s="16" t="n"/>
       <c r="U175" s="32" t="n"/>
-      <c r="V175" s="32" t="n"/>
-      <c r="W175" s="32" t="n"/>
-      <c r="X175" s="32" t="n"/>
-      <c r="Y175" s="32" t="n"/>
-      <c r="Z175" s="32" t="n"/>
-      <c r="AA175" s="32" t="n"/>
-      <c r="AB175" s="32" t="n"/>
-      <c r="AC175" s="32" t="n"/>
-      <c r="AD175" s="32" t="n"/>
       <c r="GM175" s="32" t="n"/>
       <c r="GN175" s="32" t="n"/>
       <c r="GO175" s="32" t="n"/>
@@ -15256,15 +14233,6 @@
       <c r="P176" s="14" t="n"/>
       <c r="T176" s="16" t="n"/>
       <c r="U176" s="32" t="n"/>
-      <c r="V176" s="32" t="n"/>
-      <c r="W176" s="32" t="n"/>
-      <c r="X176" s="32" t="n"/>
-      <c r="Y176" s="32" t="n"/>
-      <c r="Z176" s="32" t="n"/>
-      <c r="AA176" s="32" t="n"/>
-      <c r="AB176" s="32" t="n"/>
-      <c r="AC176" s="32" t="n"/>
-      <c r="AD176" s="32" t="n"/>
       <c r="GM176" s="32" t="n"/>
       <c r="GN176" s="32" t="n"/>
       <c r="GO176" s="32" t="n"/>
@@ -15288,15 +14256,6 @@
       <c r="P177" s="14" t="n"/>
       <c r="T177" s="16" t="n"/>
       <c r="U177" s="32" t="n"/>
-      <c r="V177" s="32" t="n"/>
-      <c r="W177" s="32" t="n"/>
-      <c r="X177" s="32" t="n"/>
-      <c r="Y177" s="32" t="n"/>
-      <c r="Z177" s="32" t="n"/>
-      <c r="AA177" s="32" t="n"/>
-      <c r="AB177" s="32" t="n"/>
-      <c r="AC177" s="32" t="n"/>
-      <c r="AD177" s="32" t="n"/>
       <c r="GM177" s="32" t="n"/>
       <c r="GN177" s="32" t="n"/>
       <c r="GO177" s="32" t="n"/>
@@ -15320,15 +14279,6 @@
       <c r="P178" s="14" t="n"/>
       <c r="T178" s="16" t="n"/>
       <c r="U178" s="32" t="n"/>
-      <c r="V178" s="32" t="n"/>
-      <c r="W178" s="32" t="n"/>
-      <c r="X178" s="32" t="n"/>
-      <c r="Y178" s="32" t="n"/>
-      <c r="Z178" s="32" t="n"/>
-      <c r="AA178" s="32" t="n"/>
-      <c r="AB178" s="32" t="n"/>
-      <c r="AC178" s="32" t="n"/>
-      <c r="AD178" s="32" t="n"/>
       <c r="GM178" s="32" t="n"/>
       <c r="GN178" s="32" t="n"/>
       <c r="GO178" s="32" t="n"/>
@@ -15428,15 +14378,6 @@
       <c r="P179" s="14" t="n"/>
       <c r="T179" s="16" t="n"/>
       <c r="U179" s="32" t="n"/>
-      <c r="V179" s="32" t="n"/>
-      <c r="W179" s="32" t="n"/>
-      <c r="X179" s="32" t="n"/>
-      <c r="Y179" s="32" t="n"/>
-      <c r="Z179" s="32" t="n"/>
-      <c r="AA179" s="32" t="n"/>
-      <c r="AB179" s="32" t="n"/>
-      <c r="AC179" s="32" t="n"/>
-      <c r="AD179" s="32" t="n"/>
       <c r="GM179" s="32" t="n"/>
       <c r="GN179" s="32" t="n"/>
       <c r="GO179" s="32" t="n"/>
@@ -15544,15 +14485,6 @@
       <c r="P180" s="14" t="n"/>
       <c r="T180" s="16" t="n"/>
       <c r="U180" s="32" t="n"/>
-      <c r="V180" s="32" t="n"/>
-      <c r="W180" s="32" t="n"/>
-      <c r="X180" s="32" t="n"/>
-      <c r="Y180" s="32" t="n"/>
-      <c r="Z180" s="32" t="n"/>
-      <c r="AA180" s="32" t="n"/>
-      <c r="AB180" s="32" t="n"/>
-      <c r="AC180" s="32" t="n"/>
-      <c r="AD180" s="32" t="n"/>
       <c r="GM180" s="32" t="n"/>
       <c r="GN180" s="32" t="n"/>
       <c r="GO180" s="32" t="n"/>
@@ -15576,15 +14508,6 @@
       <c r="P181" s="14" t="n"/>
       <c r="T181" s="16" t="n"/>
       <c r="U181" s="32" t="n"/>
-      <c r="V181" s="32" t="n"/>
-      <c r="W181" s="32" t="n"/>
-      <c r="X181" s="32" t="n"/>
-      <c r="Y181" s="32" t="n"/>
-      <c r="Z181" s="32" t="n"/>
-      <c r="AA181" s="32" t="n"/>
-      <c r="AB181" s="32" t="n"/>
-      <c r="AC181" s="32" t="n"/>
-      <c r="AD181" s="32" t="n"/>
       <c r="GM181" s="32" t="n"/>
       <c r="GN181" s="32" t="n"/>
       <c r="GO181" s="32" t="n"/>
@@ -15608,15 +14531,6 @@
       <c r="P182" s="14" t="n"/>
       <c r="T182" s="16" t="n"/>
       <c r="U182" s="32" t="n"/>
-      <c r="V182" s="32" t="n"/>
-      <c r="W182" s="32" t="n"/>
-      <c r="X182" s="32" t="n"/>
-      <c r="Y182" s="32" t="n"/>
-      <c r="Z182" s="32" t="n"/>
-      <c r="AA182" s="32" t="n"/>
-      <c r="AB182" s="32" t="n"/>
-      <c r="AC182" s="32" t="n"/>
-      <c r="AD182" s="32" t="n"/>
       <c r="GM182" s="32" t="n"/>
       <c r="GN182" s="32" t="n"/>
       <c r="GO182" s="32" t="n"/>
@@ -15644,15 +14558,6 @@
       <c r="P183" s="14" t="n"/>
       <c r="T183" s="16" t="n"/>
       <c r="U183" s="32" t="n"/>
-      <c r="V183" s="32" t="n"/>
-      <c r="W183" s="32" t="n"/>
-      <c r="X183" s="32" t="n"/>
-      <c r="Y183" s="32" t="n"/>
-      <c r="Z183" s="32" t="n"/>
-      <c r="AA183" s="32" t="n"/>
-      <c r="AB183" s="32" t="n"/>
-      <c r="AC183" s="32" t="n"/>
-      <c r="AD183" s="32" t="n"/>
       <c r="GM183" s="32" t="n"/>
       <c r="GN183" s="32" t="n"/>
       <c r="GO183" s="32" t="n"/>
@@ -15676,15 +14581,6 @@
       <c r="P184" s="14" t="n"/>
       <c r="T184" s="16" t="n"/>
       <c r="U184" s="32" t="n"/>
-      <c r="V184" s="32" t="n"/>
-      <c r="W184" s="32" t="n"/>
-      <c r="X184" s="32" t="n"/>
-      <c r="Y184" s="32" t="n"/>
-      <c r="Z184" s="32" t="n"/>
-      <c r="AA184" s="32" t="n"/>
-      <c r="AB184" s="32" t="n"/>
-      <c r="AC184" s="32" t="n"/>
-      <c r="AD184" s="32" t="n"/>
       <c r="GM184" s="32" t="n"/>
       <c r="GN184" s="32" t="n"/>
       <c r="GO184" s="32" t="n"/>
@@ -18019,7 +16915,7 @@
       <c r="KK210" s="7" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="249">
+  <mergeCells count="254">
     <mergeCell ref="JG74:JN77"/>
     <mergeCell ref="HC109:JX129"/>
     <mergeCell ref="JB18:JF21"/>
@@ -18030,6 +16926,7 @@
     <mergeCell ref="IQ147:JA149"/>
     <mergeCell ref="GW54:HB57"/>
     <mergeCell ref="JG58:JN61"/>
+    <mergeCell ref="V62:CC77"/>
     <mergeCell ref="HR34:ID37"/>
     <mergeCell ref="HC86:HQ89"/>
     <mergeCell ref="GW78:HB81"/>
@@ -18133,6 +17030,7 @@
     <mergeCell ref="JO46:JS49"/>
     <mergeCell ref="IE54:JA57"/>
     <mergeCell ref="JB150:JL152"/>
+    <mergeCell ref="V26:CC41"/>
     <mergeCell ref="GW153:HA155"/>
     <mergeCell ref="GW98:HB101"/>
     <mergeCell ref="HC90:HQ93"/>
@@ -18183,6 +17081,7 @@
     <mergeCell ref="U199:BL203"/>
     <mergeCell ref="IQ150:JA152"/>
     <mergeCell ref="JO58:JS61"/>
+    <mergeCell ref="V98:CC113"/>
     <mergeCell ref="BM199:DD203"/>
     <mergeCell ref="JT54:JX57"/>
     <mergeCell ref="HC30:HQ33"/>
@@ -18201,9 +17100,11 @@
     <mergeCell ref="JB82:JF85"/>
     <mergeCell ref="GO199:IF203"/>
     <mergeCell ref="IE86:JA89"/>
+    <mergeCell ref="V169:CC184"/>
     <mergeCell ref="JO50:JS53"/>
     <mergeCell ref="HC22:HQ25"/>
     <mergeCell ref="HR62:ID65"/>
+    <mergeCell ref="V134:CC149"/>
     <mergeCell ref="JB66:JF69"/>
     <mergeCell ref="HC62:HQ65"/>
     <mergeCell ref="JO22:JS25"/>

--- a/가공도_도면_1.xlsx
+++ b/가공도_도면_1.xlsx
@@ -745,7 +745,7 @@
     <col width="3.09765625" customWidth="1" style="15" min="1" max="297"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.95" customHeight="1" s="15">
+    <row r="1" ht="4" customHeight="1" s="15">
       <c r="U1" s="1" t="n"/>
       <c r="V1" s="1" t="n"/>
       <c r="W1" s="1" t="n"/>
@@ -1024,19 +1024,19 @@
       <c r="KJ1" s="1" t="n"/>
       <c r="KK1" s="2" t="n"/>
     </row>
-    <row r="2" ht="16.95" customHeight="1" s="15">
+    <row r="2" ht="4" customHeight="1" s="15">
       <c r="KK2" s="4" t="n"/>
     </row>
-    <row r="3" ht="16.95" customHeight="1" s="15">
+    <row r="3" ht="4" customHeight="1" s="15">
       <c r="KK3" s="4" t="n"/>
     </row>
-    <row r="4" ht="16.95" customHeight="1" s="15">
+    <row r="4" ht="4" customHeight="1" s="15">
       <c r="KK4" s="4" t="n"/>
     </row>
-    <row r="5" ht="16.95" customHeight="1" s="15" thickBot="1">
+    <row r="5" ht="4" customHeight="1" s="15" thickBot="1">
       <c r="KK5" s="4" t="n"/>
     </row>
-    <row r="6" ht="16.95" customHeight="1" s="15">
+    <row r="6" ht="4" customHeight="1" s="15">
       <c r="U6" s="25" t="n">
         <v>1</v>
       </c>
@@ -1317,7 +1317,7 @@
       <c r="JZ6" s="33" t="n"/>
       <c r="KK6" s="4" t="n"/>
     </row>
-    <row r="7" ht="16.95" customHeight="1" s="15">
+    <row r="7" ht="4" customHeight="1" s="15">
       <c r="U7" s="14" t="n"/>
       <c r="BL7" s="16" t="n"/>
       <c r="BM7" s="14" t="n"/>
@@ -1334,7 +1334,7 @@
       <c r="JZ7" s="33" t="n"/>
       <c r="KK7" s="4" t="n"/>
     </row>
-    <row r="8" ht="16.95" customHeight="1" s="15">
+    <row r="8" ht="4" customHeight="1" s="15">
       <c r="U8" s="14" t="n"/>
       <c r="BL8" s="16" t="n"/>
       <c r="BM8" s="14" t="n"/>
@@ -1351,7 +1351,7 @@
       <c r="JZ8" s="33" t="n"/>
       <c r="KK8" s="4" t="n"/>
     </row>
-    <row r="9" ht="16.95" customHeight="1" s="15">
+    <row r="9" ht="4" customHeight="1" s="15">
       <c r="U9" s="14" t="n"/>
       <c r="BL9" s="16" t="n"/>
       <c r="BM9" s="14" t="n"/>
@@ -1368,7 +1368,7 @@
       <c r="JZ9" s="33" t="n"/>
       <c r="KK9" s="4" t="n"/>
     </row>
-    <row r="10" ht="16.95" customHeight="1" s="15" thickBot="1">
+    <row r="10" ht="4" customHeight="1" s="15" thickBot="1">
       <c r="U10" s="17" t="n"/>
       <c r="V10" s="18" t="n"/>
       <c r="W10" s="18" t="n"/>
@@ -1638,7 +1638,7 @@
       <c r="KA10" s="6" t="n"/>
       <c r="KK10" s="4" t="n"/>
     </row>
-    <row r="11" ht="16.95" customHeight="1" s="15">
+    <row r="11" ht="4" customHeight="1" s="15">
       <c r="A11" s="3" t="n"/>
       <c r="P11" s="25" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
       <c r="R11" s="12" t="n"/>
       <c r="S11" s="12" t="n"/>
       <c r="T11" s="13" t="n"/>
-      <c r="U11" s="23" t="inlineStr">
+      <c r="U11" s="34" t="inlineStr">
         <is>
           <t>{View_7}</t>
         </is>
@@ -1822,7 +1822,7 @@
       <c r="GJ11" s="32" t="n"/>
       <c r="GK11" s="32" t="n"/>
       <c r="GL11" s="32" t="n"/>
-      <c r="GM11" s="23" t="inlineStr">
+      <c r="GM11" s="34" t="inlineStr">
         <is>
           <t>{View_8}</t>
         </is>
@@ -1844,7 +1844,7 @@
       <c r="KC11" s="13" t="n"/>
       <c r="KK11" s="4" t="n"/>
     </row>
-    <row r="12" ht="16.95" customHeight="1" s="15">
+    <row r="12" ht="4" customHeight="1" s="15">
       <c r="A12" s="3" t="n"/>
       <c r="P12" s="14" t="n"/>
       <c r="T12" s="16" t="n"/>
@@ -2018,7 +2018,7 @@
       <c r="KC12" s="16" t="n"/>
       <c r="KK12" s="4" t="n"/>
     </row>
-    <row r="13" ht="16.95" customHeight="1" s="15">
+    <row r="13" ht="4" customHeight="1" s="15">
       <c r="A13" s="3" t="n"/>
       <c r="P13" s="14" t="n"/>
       <c r="T13" s="16" t="n"/>
@@ -2192,7 +2192,7 @@
       <c r="KC13" s="16" t="n"/>
       <c r="KK13" s="4" t="n"/>
     </row>
-    <row r="14" ht="16.95" customHeight="1" s="15">
+    <row r="14" ht="4" customHeight="1" s="15">
       <c r="A14" s="3" t="n"/>
       <c r="P14" s="14" t="n"/>
       <c r="T14" s="16" t="n"/>
@@ -2366,7 +2366,7 @@
       <c r="KC14" s="16" t="n"/>
       <c r="KK14" s="4" t="n"/>
     </row>
-    <row r="15" ht="16.95" customHeight="1" s="15">
+    <row r="15" ht="4" customHeight="1" s="15">
       <c r="A15" s="3" t="n"/>
       <c r="P15" s="14" t="n"/>
       <c r="T15" s="16" t="n"/>
@@ -2540,7 +2540,7 @@
       <c r="KC15" s="16" t="n"/>
       <c r="KK15" s="4" t="n"/>
     </row>
-    <row r="16" ht="16.95" customHeight="1" s="15">
+    <row r="16" ht="4" customHeight="1" s="15">
       <c r="A16" s="3" t="n"/>
       <c r="P16" s="14" t="n"/>
       <c r="T16" s="16" t="n"/>
@@ -2562,7 +2562,7 @@
       <c r="KC16" s="16" t="n"/>
       <c r="KK16" s="4" t="n"/>
     </row>
-    <row r="17" ht="16.95" customHeight="1" s="15" thickBot="1">
+    <row r="17" ht="4" customHeight="1" s="15" thickBot="1">
       <c r="A17" s="3" t="n"/>
       <c r="P17" s="14" t="n"/>
       <c r="T17" s="16" t="n"/>
@@ -2660,7 +2660,7 @@
       <c r="KC17" s="16" t="n"/>
       <c r="KK17" s="4" t="n"/>
     </row>
-    <row r="18" ht="16.95" customHeight="1" s="15" thickBot="1">
+    <row r="18" ht="4" customHeight="1" s="15" thickBot="1">
       <c r="A18" s="3" t="n"/>
       <c r="P18" s="14" t="n"/>
       <c r="T18" s="16" t="n"/>
@@ -2790,7 +2790,7 @@
       <c r="KC18" s="16" t="n"/>
       <c r="KK18" s="4" t="n"/>
     </row>
-    <row r="19" ht="16.95" customHeight="1" s="15">
+    <row r="19" ht="4" customHeight="1" s="15">
       <c r="A19" s="3" t="n"/>
       <c r="P19" s="14" t="n"/>
       <c r="T19" s="16" t="n"/>
@@ -2823,7 +2823,7 @@
       <c r="KC19" s="16" t="n"/>
       <c r="KK19" s="4" t="n"/>
     </row>
-    <row r="20" ht="16.95" customHeight="1" s="15">
+    <row r="20" ht="4" customHeight="1" s="15">
       <c r="A20" s="3" t="n"/>
       <c r="P20" s="14" t="n"/>
       <c r="T20" s="16" t="n"/>
@@ -2856,7 +2856,7 @@
       <c r="KC20" s="16" t="n"/>
       <c r="KK20" s="4" t="n"/>
     </row>
-    <row r="21" ht="16.95" customHeight="1" s="15" thickBot="1">
+    <row r="21" ht="4" customHeight="1" s="15" thickBot="1">
       <c r="A21" s="3" t="n"/>
       <c r="P21" s="14" t="n"/>
       <c r="T21" s="16" t="n"/>
@@ -2964,7 +2964,7 @@
       <c r="KC21" s="16" t="n"/>
       <c r="KK21" s="4" t="n"/>
     </row>
-    <row r="22" ht="16.95" customHeight="1" s="15" thickBot="1">
+    <row r="22" ht="4" customHeight="1" s="15" thickBot="1">
       <c r="A22" s="3" t="n"/>
       <c r="P22" s="14" t="n"/>
       <c r="T22" s="16" t="n"/>
@@ -3104,7 +3104,7 @@
       <c r="KC22" s="16" t="n"/>
       <c r="KK22" s="4" t="n"/>
     </row>
-    <row r="23" ht="16.95" customHeight="1" s="15">
+    <row r="23" ht="4" customHeight="1" s="15">
       <c r="A23" s="3" t="n"/>
       <c r="P23" s="14" t="n"/>
       <c r="T23" s="16" t="n"/>
@@ -3148,7 +3148,7 @@
       <c r="KC23" s="16" t="n"/>
       <c r="KK23" s="4" t="n"/>
     </row>
-    <row r="24" ht="16.95" customHeight="1" s="15">
+    <row r="24" ht="4" customHeight="1" s="15">
       <c r="A24" s="3" t="n"/>
       <c r="P24" s="14" t="n"/>
       <c r="T24" s="16" t="n"/>
@@ -3192,7 +3192,7 @@
       <c r="KC24" s="16" t="n"/>
       <c r="KK24" s="4" t="n"/>
     </row>
-    <row r="25" ht="16.95" customHeight="1" s="15" thickBot="1">
+    <row r="25" ht="4" customHeight="1" s="15" thickBot="1">
       <c r="A25" s="3" t="n"/>
       <c r="P25" s="14" t="n"/>
       <c r="T25" s="16" t="n"/>
@@ -3300,7 +3300,7 @@
       <c r="KC25" s="16" t="n"/>
       <c r="KK25" s="4" t="n"/>
     </row>
-    <row r="26" ht="16.95" customHeight="1" s="15" thickBot="1">
+    <row r="26" ht="4" customHeight="1" s="15" thickBot="1">
       <c r="A26" s="3" t="n"/>
       <c r="P26" s="14" t="n"/>
       <c r="T26" s="16" t="n"/>
@@ -3431,7 +3431,7 @@
       <c r="KC26" s="16" t="n"/>
       <c r="KK26" s="4" t="n"/>
     </row>
-    <row r="27" ht="16.95" customHeight="1" s="15">
+    <row r="27" ht="4" customHeight="1" s="15">
       <c r="A27" s="3" t="n"/>
       <c r="P27" s="14" t="n"/>
       <c r="T27" s="16" t="n"/>
@@ -3456,7 +3456,7 @@
       <c r="KC27" s="16" t="n"/>
       <c r="KK27" s="4" t="n"/>
     </row>
-    <row r="28" ht="16.95" customHeight="1" s="15">
+    <row r="28" ht="4" customHeight="1" s="15">
       <c r="A28" s="3" t="n"/>
       <c r="P28" s="14" t="n"/>
       <c r="T28" s="16" t="n"/>
@@ -3481,7 +3481,7 @@
       <c r="KC28" s="16" t="n"/>
       <c r="KK28" s="4" t="n"/>
     </row>
-    <row r="29" ht="16.95" customHeight="1" s="15" thickBot="1">
+    <row r="29" ht="4" customHeight="1" s="15" thickBot="1">
       <c r="A29" s="3" t="n"/>
       <c r="P29" s="14" t="n"/>
       <c r="T29" s="16" t="n"/>
@@ -3570,7 +3570,7 @@
       <c r="KC29" s="16" t="n"/>
       <c r="KK29" s="4" t="n"/>
     </row>
-    <row r="30" ht="16.95" customHeight="1" s="15" thickBot="1">
+    <row r="30" ht="4" customHeight="1" s="15" thickBot="1">
       <c r="A30" s="3" t="n"/>
       <c r="P30" s="14" t="n"/>
       <c r="T30" s="16" t="n"/>
@@ -3691,7 +3691,7 @@
       <c r="KC30" s="16" t="n"/>
       <c r="KK30" s="4" t="n"/>
     </row>
-    <row r="31" ht="16.95" customHeight="1" s="15">
+    <row r="31" ht="4" customHeight="1" s="15">
       <c r="A31" s="3" t="n"/>
       <c r="P31" s="14" t="n"/>
       <c r="T31" s="16" t="n"/>
@@ -3716,7 +3716,7 @@
       <c r="KC31" s="16" t="n"/>
       <c r="KK31" s="4" t="n"/>
     </row>
-    <row r="32" ht="16.95" customHeight="1" s="15">
+    <row r="32" ht="4" customHeight="1" s="15">
       <c r="A32" s="3" t="n"/>
       <c r="P32" s="14" t="n"/>
       <c r="T32" s="16" t="n"/>
@@ -3741,7 +3741,7 @@
       <c r="KC32" s="16" t="n"/>
       <c r="KK32" s="4" t="n"/>
     </row>
-    <row r="33" ht="16.95" customHeight="1" s="15" thickBot="1">
+    <row r="33" ht="4" customHeight="1" s="15" thickBot="1">
       <c r="A33" s="3" t="n"/>
       <c r="P33" s="14" t="n"/>
       <c r="T33" s="16" t="n"/>
@@ -3830,7 +3830,7 @@
       <c r="KC33" s="16" t="n"/>
       <c r="KK33" s="4" t="n"/>
     </row>
-    <row r="34" ht="16.95" customHeight="1" s="15" thickBot="1">
+    <row r="34" ht="4" customHeight="1" s="15" thickBot="1">
       <c r="A34" s="3" t="n"/>
       <c r="P34" s="14" t="n"/>
       <c r="T34" s="16" t="n"/>
@@ -3951,7 +3951,7 @@
       <c r="KC34" s="16" t="n"/>
       <c r="KK34" s="4" t="n"/>
     </row>
-    <row r="35" ht="16.95" customHeight="1" s="15">
+    <row r="35" ht="4" customHeight="1" s="15">
       <c r="A35" s="3" t="n"/>
       <c r="P35" s="14" t="n"/>
       <c r="T35" s="16" t="n"/>
@@ -3976,7 +3976,7 @@
       <c r="KC35" s="16" t="n"/>
       <c r="KK35" s="4" t="n"/>
     </row>
-    <row r="36" ht="16.95" customHeight="1" s="15">
+    <row r="36" ht="4" customHeight="1" s="15">
       <c r="A36" s="3" t="n"/>
       <c r="P36" s="14" t="n"/>
       <c r="T36" s="16" t="n"/>
@@ -4001,7 +4001,7 @@
       <c r="KC36" s="16" t="n"/>
       <c r="KK36" s="4" t="n"/>
     </row>
-    <row r="37" ht="16.95" customHeight="1" s="15" thickBot="1">
+    <row r="37" ht="4" customHeight="1" s="15" thickBot="1">
       <c r="A37" s="3" t="n"/>
       <c r="P37" s="14" t="n"/>
       <c r="T37" s="16" t="n"/>
@@ -4090,7 +4090,7 @@
       <c r="KC37" s="16" t="n"/>
       <c r="KK37" s="4" t="n"/>
     </row>
-    <row r="38" ht="16.95" customHeight="1" s="15" thickBot="1">
+    <row r="38" ht="4" customHeight="1" s="15" thickBot="1">
       <c r="A38" s="3" t="n"/>
       <c r="P38" s="14" t="n"/>
       <c r="T38" s="16" t="n"/>
@@ -4211,7 +4211,7 @@
       <c r="KC38" s="16" t="n"/>
       <c r="KK38" s="4" t="n"/>
     </row>
-    <row r="39" ht="16.95" customHeight="1" s="15">
+    <row r="39" ht="4" customHeight="1" s="15">
       <c r="A39" s="3" t="n"/>
       <c r="P39" s="14" t="n"/>
       <c r="T39" s="16" t="n"/>
@@ -4236,7 +4236,7 @@
       <c r="KC39" s="16" t="n"/>
       <c r="KK39" s="4" t="n"/>
     </row>
-    <row r="40" ht="16.95" customHeight="1" s="15">
+    <row r="40" ht="4" customHeight="1" s="15">
       <c r="A40" s="3" t="n"/>
       <c r="P40" s="14" t="n"/>
       <c r="T40" s="16" t="n"/>
@@ -4261,7 +4261,7 @@
       <c r="KC40" s="16" t="n"/>
       <c r="KK40" s="4" t="n"/>
     </row>
-    <row r="41" ht="16.95" customHeight="1" s="15" thickBot="1">
+    <row r="41" ht="4" customHeight="1" s="15" thickBot="1">
       <c r="A41" s="3" t="n"/>
       <c r="P41" s="14" t="n"/>
       <c r="T41" s="16" t="n"/>
@@ -4360,7 +4360,7 @@
       <c r="KC41" s="16" t="n"/>
       <c r="KK41" s="4" t="n"/>
     </row>
-    <row r="42" ht="16.95" customHeight="1" s="15" thickBot="1">
+    <row r="42" ht="4" customHeight="1" s="15" thickBot="1">
       <c r="A42" s="3" t="n"/>
       <c r="P42" s="14" t="n"/>
       <c r="T42" s="16" t="n"/>
@@ -4510,7 +4510,7 @@
       <c r="KC42" s="16" t="n"/>
       <c r="KK42" s="4" t="n"/>
     </row>
-    <row r="43" ht="16.95" customHeight="1" s="15">
+    <row r="43" ht="4" customHeight="1" s="15">
       <c r="A43" s="3" t="n"/>
       <c r="P43" s="14" t="n"/>
       <c r="T43" s="16" t="n"/>
@@ -4564,7 +4564,7 @@
       <c r="KC43" s="16" t="n"/>
       <c r="KK43" s="4" t="n"/>
     </row>
-    <row r="44" ht="16.95" customHeight="1" s="15">
+    <row r="44" ht="4" customHeight="1" s="15">
       <c r="A44" s="3" t="n"/>
       <c r="P44" s="14" t="n"/>
       <c r="T44" s="16" t="n"/>
@@ -4618,7 +4618,7 @@
       <c r="KC44" s="16" t="n"/>
       <c r="KK44" s="4" t="n"/>
     </row>
-    <row r="45" ht="16.95" customHeight="1" s="15" thickBot="1">
+    <row r="45" ht="4" customHeight="1" s="15" thickBot="1">
       <c r="A45" s="3" t="n"/>
       <c r="P45" s="14" t="n"/>
       <c r="T45" s="16" t="n"/>
@@ -4736,7 +4736,7 @@
       <c r="KC45" s="16" t="n"/>
       <c r="KK45" s="4" t="n"/>
     </row>
-    <row r="46" ht="16.95" customHeight="1" s="15" thickBot="1">
+    <row r="46" ht="4" customHeight="1" s="15" thickBot="1">
       <c r="A46" s="3" t="n"/>
       <c r="P46" s="14" t="n"/>
       <c r="T46" s="16" t="n"/>
@@ -4886,7 +4886,7 @@
       <c r="KC46" s="16" t="n"/>
       <c r="KK46" s="4" t="n"/>
     </row>
-    <row r="47" ht="16.95" customHeight="1" s="15">
+    <row r="47" ht="4" customHeight="1" s="15">
       <c r="A47" s="3" t="n"/>
       <c r="P47" s="14" t="n"/>
       <c r="T47" s="16" t="n"/>
@@ -4940,7 +4940,7 @@
       <c r="KC47" s="16" t="n"/>
       <c r="KK47" s="4" t="n"/>
     </row>
-    <row r="48" ht="16.95" customHeight="1" s="15">
+    <row r="48" ht="4" customHeight="1" s="15">
       <c r="A48" s="3" t="n"/>
       <c r="P48" s="14" t="n"/>
       <c r="T48" s="16" t="n"/>
@@ -4994,7 +4994,7 @@
       <c r="KC48" s="16" t="n"/>
       <c r="KK48" s="4" t="n"/>
     </row>
-    <row r="49" ht="16.95" customHeight="1" s="15" thickBot="1">
+    <row r="49" ht="4" customHeight="1" s="15" thickBot="1">
       <c r="A49" s="3" t="n"/>
       <c r="P49" s="14" t="n"/>
       <c r="T49" s="16" t="n"/>
@@ -5112,7 +5112,7 @@
       <c r="KC49" s="16" t="n"/>
       <c r="KK49" s="4" t="n"/>
     </row>
-    <row r="50" ht="16.95" customHeight="1" s="15" thickBot="1">
+    <row r="50" ht="4" customHeight="1" s="15" thickBot="1">
       <c r="A50" s="3" t="n"/>
       <c r="P50" s="14" t="n"/>
       <c r="T50" s="16" t="n"/>
@@ -5262,7 +5262,7 @@
       <c r="KC50" s="16" t="n"/>
       <c r="KK50" s="4" t="n"/>
     </row>
-    <row r="51" ht="16.95" customHeight="1" s="15">
+    <row r="51" ht="4" customHeight="1" s="15">
       <c r="A51" s="3" t="n"/>
       <c r="P51" s="14" t="n"/>
       <c r="T51" s="16" t="n"/>
@@ -5316,7 +5316,7 @@
       <c r="KC51" s="16" t="n"/>
       <c r="KK51" s="4" t="n"/>
     </row>
-    <row r="52" ht="16.95" customHeight="1" s="15">
+    <row r="52" ht="4" customHeight="1" s="15">
       <c r="A52" s="3" t="n"/>
       <c r="P52" s="14" t="n"/>
       <c r="T52" s="16" t="n"/>
@@ -5370,7 +5370,7 @@
       <c r="KC52" s="16" t="n"/>
       <c r="KK52" s="4" t="n"/>
     </row>
-    <row r="53" ht="16.95" customHeight="1" s="15" thickBot="1">
+    <row r="53" ht="4" customHeight="1" s="15" thickBot="1">
       <c r="A53" s="3" t="n"/>
       <c r="P53" s="14" t="n"/>
       <c r="T53" s="16" t="n"/>
@@ -5488,7 +5488,7 @@
       <c r="KC53" s="16" t="n"/>
       <c r="KK53" s="4" t="n"/>
     </row>
-    <row r="54" ht="16.95" customHeight="1" s="15" thickBot="1">
+    <row r="54" ht="4" customHeight="1" s="15" thickBot="1">
       <c r="A54" s="3" t="n"/>
       <c r="P54" s="14" t="n"/>
       <c r="T54" s="16" t="n"/>
@@ -5638,7 +5638,7 @@
       <c r="KC54" s="16" t="n"/>
       <c r="KK54" s="4" t="n"/>
     </row>
-    <row r="55" ht="16.95" customHeight="1" s="15">
+    <row r="55" ht="4" customHeight="1" s="15">
       <c r="A55" s="3" t="n"/>
       <c r="P55" s="14" t="n"/>
       <c r="T55" s="16" t="n"/>
@@ -5692,7 +5692,7 @@
       <c r="KC55" s="16" t="n"/>
       <c r="KK55" s="4" t="n"/>
     </row>
-    <row r="56" ht="16.95" customHeight="1" s="15">
+    <row r="56" ht="4" customHeight="1" s="15">
       <c r="A56" s="3" t="n"/>
       <c r="P56" s="14" t="n"/>
       <c r="T56" s="16" t="n"/>
@@ -5746,7 +5746,7 @@
       <c r="KC56" s="16" t="n"/>
       <c r="KK56" s="4" t="n"/>
     </row>
-    <row r="57" ht="16.95" customHeight="1" s="15" thickBot="1">
+    <row r="57" ht="4" customHeight="1" s="15" thickBot="1">
       <c r="A57" s="3" t="n"/>
       <c r="P57" s="17" t="n"/>
       <c r="Q57" s="18" t="n"/>
@@ -5870,7 +5870,7 @@
       <c r="KC57" s="19" t="n"/>
       <c r="KK57" s="4" t="n"/>
     </row>
-    <row r="58" ht="16.95" customHeight="1" s="15" thickBot="1">
+    <row r="58" ht="4" customHeight="1" s="15" thickBot="1">
       <c r="A58" s="3" t="n"/>
       <c r="P58" s="25" t="inlineStr">
         <is>
@@ -6034,7 +6034,7 @@
       <c r="KC58" s="13" t="n"/>
       <c r="KK58" s="4" t="n"/>
     </row>
-    <row r="59" ht="16.95" customHeight="1" s="15">
+    <row r="59" ht="4" customHeight="1" s="15">
       <c r="A59" s="3" t="n"/>
       <c r="P59" s="14" t="n"/>
       <c r="T59" s="16" t="n"/>
@@ -6088,7 +6088,7 @@
       <c r="KC59" s="16" t="n"/>
       <c r="KK59" s="4" t="n"/>
     </row>
-    <row r="60" ht="16.95" customHeight="1" s="15">
+    <row r="60" ht="4" customHeight="1" s="15">
       <c r="A60" s="3" t="n"/>
       <c r="P60" s="14" t="n"/>
       <c r="T60" s="16" t="n"/>
@@ -6142,7 +6142,7 @@
       <c r="KC60" s="16" t="n"/>
       <c r="KK60" s="4" t="n"/>
     </row>
-    <row r="61" ht="16.95" customHeight="1" s="15" thickBot="1">
+    <row r="61" ht="4" customHeight="1" s="15" thickBot="1">
       <c r="A61" s="3" t="n"/>
       <c r="P61" s="14" t="n"/>
       <c r="T61" s="16" t="n"/>
@@ -6260,7 +6260,7 @@
       <c r="KC61" s="16" t="n"/>
       <c r="KK61" s="4" t="n"/>
     </row>
-    <row r="62" ht="16.95" customHeight="1" s="15" thickBot="1">
+    <row r="62" ht="4" customHeight="1" s="15" thickBot="1">
       <c r="A62" s="3" t="n"/>
       <c r="P62" s="14" t="n"/>
       <c r="T62" s="16" t="n"/>
@@ -6401,7 +6401,7 @@
       <c r="KC62" s="16" t="n"/>
       <c r="KK62" s="4" t="n"/>
     </row>
-    <row r="63" ht="16.95" customHeight="1" s="15">
+    <row r="63" ht="4" customHeight="1" s="15">
       <c r="A63" s="3" t="n"/>
       <c r="P63" s="14" t="n"/>
       <c r="T63" s="16" t="n"/>
@@ -6436,7 +6436,7 @@
       <c r="KC63" s="16" t="n"/>
       <c r="KK63" s="4" t="n"/>
     </row>
-    <row r="64" ht="16.95" customHeight="1" s="15">
+    <row r="64" ht="4" customHeight="1" s="15">
       <c r="A64" s="3" t="n"/>
       <c r="P64" s="14" t="n"/>
       <c r="T64" s="16" t="n"/>
@@ -6471,7 +6471,7 @@
       <c r="KC64" s="16" t="n"/>
       <c r="KK64" s="4" t="n"/>
     </row>
-    <row r="65" ht="16.95" customHeight="1" s="15" thickBot="1">
+    <row r="65" ht="4" customHeight="1" s="15" thickBot="1">
       <c r="A65" s="3" t="n"/>
       <c r="P65" s="14" t="n"/>
       <c r="T65" s="16" t="n"/>
@@ -6570,7 +6570,7 @@
       <c r="KC65" s="16" t="n"/>
       <c r="KK65" s="4" t="n"/>
     </row>
-    <row r="66" ht="16.95" customHeight="1" s="15" thickBot="1">
+    <row r="66" ht="4" customHeight="1" s="15" thickBot="1">
       <c r="A66" s="3" t="n"/>
       <c r="P66" s="14" t="n"/>
       <c r="T66" s="16" t="n"/>
@@ -6701,7 +6701,7 @@
       <c r="KC66" s="16" t="n"/>
       <c r="KK66" s="4" t="n"/>
     </row>
-    <row r="67" ht="16.95" customHeight="1" s="15">
+    <row r="67" ht="4" customHeight="1" s="15">
       <c r="A67" s="3" t="n"/>
       <c r="P67" s="14" t="n"/>
       <c r="T67" s="16" t="n"/>
@@ -6736,7 +6736,7 @@
       <c r="KC67" s="16" t="n"/>
       <c r="KK67" s="4" t="n"/>
     </row>
-    <row r="68" ht="16.95" customHeight="1" s="15">
+    <row r="68" ht="4" customHeight="1" s="15">
       <c r="A68" s="3" t="n"/>
       <c r="P68" s="14" t="n"/>
       <c r="T68" s="16" t="n"/>
@@ -6771,7 +6771,7 @@
       <c r="KC68" s="16" t="n"/>
       <c r="KK68" s="4" t="n"/>
     </row>
-    <row r="69" ht="16.95" customHeight="1" s="15" thickBot="1">
+    <row r="69" ht="4" customHeight="1" s="15" thickBot="1">
       <c r="A69" s="3" t="n"/>
       <c r="P69" s="14" t="n"/>
       <c r="T69" s="16" t="n"/>
@@ -6870,7 +6870,7 @@
       <c r="KC69" s="16" t="n"/>
       <c r="KK69" s="4" t="n"/>
     </row>
-    <row r="70" ht="16.95" customHeight="1" s="15" thickBot="1">
+    <row r="70" ht="4" customHeight="1" s="15" thickBot="1">
       <c r="A70" s="3" t="n"/>
       <c r="P70" s="14" t="n"/>
       <c r="T70" s="16" t="n"/>
@@ -7001,7 +7001,7 @@
       <c r="KC70" s="16" t="n"/>
       <c r="KK70" s="4" t="n"/>
     </row>
-    <row r="71" ht="16.95" customHeight="1" s="15">
+    <row r="71" ht="4" customHeight="1" s="15">
       <c r="A71" s="3" t="n"/>
       <c r="P71" s="14" t="n"/>
       <c r="T71" s="16" t="n"/>
@@ -7036,7 +7036,7 @@
       <c r="KC71" s="16" t="n"/>
       <c r="KK71" s="4" t="n"/>
     </row>
-    <row r="72" ht="16.95" customHeight="1" s="15">
+    <row r="72" ht="4" customHeight="1" s="15">
       <c r="A72" s="3" t="n"/>
       <c r="P72" s="14" t="n"/>
       <c r="T72" s="16" t="n"/>
@@ -7071,7 +7071,7 @@
       <c r="KC72" s="16" t="n"/>
       <c r="KK72" s="4" t="n"/>
     </row>
-    <row r="73" ht="16.95" customHeight="1" s="15" thickBot="1">
+    <row r="73" ht="4" customHeight="1" s="15" thickBot="1">
       <c r="A73" s="3" t="n"/>
       <c r="P73" s="14" t="n"/>
       <c r="T73" s="16" t="n"/>
@@ -7170,7 +7170,7 @@
       <c r="KC73" s="16" t="n"/>
       <c r="KK73" s="4" t="n"/>
     </row>
-    <row r="74" ht="16.95" customHeight="1" s="15" thickBot="1">
+    <row r="74" ht="4" customHeight="1" s="15" thickBot="1">
       <c r="A74" s="3" t="n"/>
       <c r="P74" s="14" t="n"/>
       <c r="T74" s="16" t="n"/>
@@ -7301,7 +7301,7 @@
       <c r="KC74" s="16" t="n"/>
       <c r="KK74" s="4" t="n"/>
     </row>
-    <row r="75" ht="16.95" customHeight="1" s="15">
+    <row r="75" ht="4" customHeight="1" s="15">
       <c r="A75" s="3" t="n"/>
       <c r="P75" s="14" t="n"/>
       <c r="T75" s="16" t="n"/>
@@ -7336,7 +7336,7 @@
       <c r="KC75" s="16" t="n"/>
       <c r="KK75" s="4" t="n"/>
     </row>
-    <row r="76" ht="16.95" customHeight="1" s="15">
+    <row r="76" ht="4" customHeight="1" s="15">
       <c r="A76" s="3" t="n"/>
       <c r="P76" s="14" t="n"/>
       <c r="T76" s="16" t="n"/>
@@ -7371,7 +7371,7 @@
       <c r="KC76" s="16" t="n"/>
       <c r="KK76" s="4" t="n"/>
     </row>
-    <row r="77" ht="16.95" customHeight="1" s="15" thickBot="1">
+    <row r="77" ht="4" customHeight="1" s="15" thickBot="1">
       <c r="A77" s="3" t="n"/>
       <c r="P77" s="14" t="n"/>
       <c r="T77" s="16" t="n"/>
@@ -7470,7 +7470,7 @@
       <c r="KC77" s="16" t="n"/>
       <c r="KK77" s="4" t="n"/>
     </row>
-    <row r="78" ht="16.95" customHeight="1" s="15" thickBot="1">
+    <row r="78" ht="4" customHeight="1" s="15" thickBot="1">
       <c r="A78" s="3" t="n"/>
       <c r="P78" s="14" t="n"/>
       <c r="T78" s="16" t="n"/>
@@ -7620,7 +7620,7 @@
       <c r="KC78" s="16" t="n"/>
       <c r="KK78" s="4" t="n"/>
     </row>
-    <row r="79" ht="16.95" customHeight="1" s="15">
+    <row r="79" ht="4" customHeight="1" s="15">
       <c r="A79" s="3" t="n"/>
       <c r="P79" s="14" t="n"/>
       <c r="T79" s="16" t="n"/>
@@ -7674,7 +7674,7 @@
       <c r="KC79" s="16" t="n"/>
       <c r="KK79" s="4" t="n"/>
     </row>
-    <row r="80" ht="16.95" customHeight="1" s="15">
+    <row r="80" ht="4" customHeight="1" s="15">
       <c r="A80" s="3" t="n"/>
       <c r="P80" s="14" t="n"/>
       <c r="T80" s="16" t="n"/>
@@ -7728,7 +7728,7 @@
       <c r="KC80" s="16" t="n"/>
       <c r="KK80" s="4" t="n"/>
     </row>
-    <row r="81" ht="16.95" customHeight="1" s="15" thickBot="1">
+    <row r="81" ht="4" customHeight="1" s="15" thickBot="1">
       <c r="A81" s="3" t="n"/>
       <c r="P81" s="14" t="n"/>
       <c r="T81" s="16" t="n"/>
@@ -7846,7 +7846,7 @@
       <c r="KC81" s="16" t="n"/>
       <c r="KK81" s="4" t="n"/>
     </row>
-    <row r="82" ht="16.95" customHeight="1" s="15" thickBot="1">
+    <row r="82" ht="4" customHeight="1" s="15" thickBot="1">
       <c r="A82" s="3" t="n"/>
       <c r="P82" s="14" t="n"/>
       <c r="T82" s="16" t="n"/>
@@ -7996,7 +7996,7 @@
       <c r="KC82" s="16" t="n"/>
       <c r="KK82" s="4" t="n"/>
     </row>
-    <row r="83" ht="16.95" customHeight="1" s="15">
+    <row r="83" ht="4" customHeight="1" s="15">
       <c r="A83" s="3" t="n"/>
       <c r="P83" s="14" t="n"/>
       <c r="T83" s="16" t="n"/>
@@ -8050,7 +8050,7 @@
       <c r="KC83" s="16" t="n"/>
       <c r="KK83" s="4" t="n"/>
     </row>
-    <row r="84" ht="16.95" customHeight="1" s="15">
+    <row r="84" ht="4" customHeight="1" s="15">
       <c r="A84" s="3" t="n"/>
       <c r="P84" s="14" t="n"/>
       <c r="T84" s="16" t="n"/>
@@ -8104,7 +8104,7 @@
       <c r="KC84" s="16" t="n"/>
       <c r="KK84" s="4" t="n"/>
     </row>
-    <row r="85" ht="16.95" customHeight="1" s="15" thickBot="1">
+    <row r="85" ht="4" customHeight="1" s="15" thickBot="1">
       <c r="A85" s="3" t="n"/>
       <c r="P85" s="14" t="n"/>
       <c r="T85" s="16" t="n"/>
@@ -8222,7 +8222,7 @@
       <c r="KC85" s="16" t="n"/>
       <c r="KK85" s="4" t="n"/>
     </row>
-    <row r="86" ht="16.95" customHeight="1" s="15" thickBot="1">
+    <row r="86" ht="4" customHeight="1" s="15" thickBot="1">
       <c r="A86" s="3" t="n"/>
       <c r="P86" s="14" t="n"/>
       <c r="T86" s="16" t="n"/>
@@ -8372,7 +8372,7 @@
       <c r="KC86" s="16" t="n"/>
       <c r="KK86" s="4" t="n"/>
     </row>
-    <row r="87" ht="16.95" customHeight="1" s="15">
+    <row r="87" ht="4" customHeight="1" s="15">
       <c r="A87" s="3" t="n"/>
       <c r="P87" s="14" t="n"/>
       <c r="T87" s="16" t="n"/>
@@ -8426,7 +8426,7 @@
       <c r="KC87" s="16" t="n"/>
       <c r="KK87" s="4" t="n"/>
     </row>
-    <row r="88" ht="16.95" customHeight="1" s="15">
+    <row r="88" ht="4" customHeight="1" s="15">
       <c r="A88" s="3" t="n"/>
       <c r="P88" s="14" t="n"/>
       <c r="T88" s="16" t="n"/>
@@ -8480,7 +8480,7 @@
       <c r="KC88" s="16" t="n"/>
       <c r="KK88" s="4" t="n"/>
     </row>
-    <row r="89" ht="16.95" customHeight="1" s="15" thickBot="1">
+    <row r="89" ht="4" customHeight="1" s="15" thickBot="1">
       <c r="A89" s="3" t="n"/>
       <c r="P89" s="14" t="n"/>
       <c r="T89" s="16" t="n"/>
@@ -8598,7 +8598,7 @@
       <c r="KC89" s="16" t="n"/>
       <c r="KK89" s="4" t="n"/>
     </row>
-    <row r="90" ht="16.95" customHeight="1" s="15" thickBot="1">
+    <row r="90" ht="4" customHeight="1" s="15" thickBot="1">
       <c r="A90" s="3" t="n"/>
       <c r="P90" s="14" t="n"/>
       <c r="T90" s="16" t="n"/>
@@ -8748,7 +8748,7 @@
       <c r="KC90" s="16" t="n"/>
       <c r="KK90" s="4" t="n"/>
     </row>
-    <row r="91" ht="16.95" customHeight="1" s="15">
+    <row r="91" ht="4" customHeight="1" s="15">
       <c r="A91" s="3" t="n"/>
       <c r="P91" s="14" t="n"/>
       <c r="T91" s="16" t="n"/>
@@ -8802,7 +8802,7 @@
       <c r="KC91" s="16" t="n"/>
       <c r="KK91" s="4" t="n"/>
     </row>
-    <row r="92" ht="16.95" customHeight="1" s="15">
+    <row r="92" ht="4" customHeight="1" s="15">
       <c r="A92" s="3" t="n"/>
       <c r="P92" s="14" t="n"/>
       <c r="T92" s="16" t="n"/>
@@ -8856,7 +8856,7 @@
       <c r="KC92" s="16" t="n"/>
       <c r="KK92" s="4" t="n"/>
     </row>
-    <row r="93" ht="16.95" customHeight="1" s="15" thickBot="1">
+    <row r="93" ht="4" customHeight="1" s="15" thickBot="1">
       <c r="A93" s="3" t="n"/>
       <c r="P93" s="14" t="n"/>
       <c r="T93" s="16" t="n"/>
@@ -8974,7 +8974,7 @@
       <c r="KC93" s="16" t="n"/>
       <c r="KK93" s="4" t="n"/>
     </row>
-    <row r="94" ht="16.95" customHeight="1" s="15" thickBot="1">
+    <row r="94" ht="4" customHeight="1" s="15" thickBot="1">
       <c r="A94" s="3" t="n"/>
       <c r="P94" s="14" t="n"/>
       <c r="T94" s="16" t="n"/>
@@ -9124,7 +9124,7 @@
       <c r="KC94" s="16" t="n"/>
       <c r="KK94" s="4" t="n"/>
     </row>
-    <row r="95" ht="16.95" customHeight="1" s="15">
+    <row r="95" ht="4" customHeight="1" s="15">
       <c r="A95" s="3" t="n"/>
       <c r="P95" s="14" t="n"/>
       <c r="T95" s="16" t="n"/>
@@ -9178,7 +9178,7 @@
       <c r="KC95" s="16" t="n"/>
       <c r="KK95" s="4" t="n"/>
     </row>
-    <row r="96" ht="16.95" customHeight="1" s="15">
+    <row r="96" ht="4" customHeight="1" s="15">
       <c r="A96" s="3" t="n"/>
       <c r="P96" s="14" t="n"/>
       <c r="T96" s="16" t="n"/>
@@ -9232,7 +9232,7 @@
       <c r="KC96" s="16" t="n"/>
       <c r="KK96" s="4" t="n"/>
     </row>
-    <row r="97" ht="16.95" customHeight="1" s="15" thickBot="1">
+    <row r="97" ht="4" customHeight="1" s="15" thickBot="1">
       <c r="A97" s="3" t="n"/>
       <c r="P97" s="14" t="n"/>
       <c r="T97" s="16" t="n"/>
@@ -9350,7 +9350,7 @@
       <c r="KC97" s="16" t="n"/>
       <c r="KK97" s="4" t="n"/>
     </row>
-    <row r="98" ht="16.95" customHeight="1" s="15" thickBot="1">
+    <row r="98" ht="4" customHeight="1" s="15" thickBot="1">
       <c r="A98" s="3" t="n"/>
       <c r="P98" s="14" t="n"/>
       <c r="T98" s="16" t="n"/>
@@ -9491,7 +9491,7 @@
       <c r="KC98" s="16" t="n"/>
       <c r="KK98" s="4" t="n"/>
     </row>
-    <row r="99" ht="16.95" customHeight="1" s="15">
+    <row r="99" ht="4" customHeight="1" s="15">
       <c r="A99" s="3" t="n"/>
       <c r="P99" s="14" t="n"/>
       <c r="T99" s="16" t="n"/>
@@ -9526,7 +9526,7 @@
       <c r="KC99" s="16" t="n"/>
       <c r="KK99" s="4" t="n"/>
     </row>
-    <row r="100" ht="16.95" customHeight="1" s="15">
+    <row r="100" ht="4" customHeight="1" s="15">
       <c r="A100" s="3" t="n"/>
       <c r="P100" s="14" t="n"/>
       <c r="T100" s="16" t="n"/>
@@ -9595,7 +9595,7 @@
       <c r="KC100" s="16" t="n"/>
       <c r="KK100" s="4" t="n"/>
     </row>
-    <row r="101" ht="16.95" customHeight="1" s="15" thickBot="1">
+    <row r="101" ht="4" customHeight="1" s="15" thickBot="1">
       <c r="A101" s="3" t="n"/>
       <c r="P101" s="14" t="n"/>
       <c r="T101" s="16" t="n"/>
@@ -9727,7 +9727,7 @@
       <c r="KC101" s="16" t="n"/>
       <c r="KK101" s="4" t="n"/>
     </row>
-    <row r="102" ht="16.95" customHeight="1" s="15">
+    <row r="102" ht="4" customHeight="1" s="15">
       <c r="A102" s="3" t="n"/>
       <c r="P102" s="14" t="n"/>
       <c r="T102" s="16" t="n"/>
@@ -9779,7 +9779,7 @@
       <c r="KC102" s="16" t="n"/>
       <c r="KK102" s="4" t="n"/>
     </row>
-    <row r="103" ht="16.95" customHeight="1" s="15">
+    <row r="103" ht="4" customHeight="1" s="15">
       <c r="A103" s="3" t="n"/>
       <c r="P103" s="14" t="n"/>
       <c r="T103" s="16" t="n"/>
@@ -9831,7 +9831,7 @@
       <c r="KC103" s="16" t="n"/>
       <c r="KK103" s="4" t="n"/>
     </row>
-    <row r="104" ht="16.95" customHeight="1" s="15" thickBot="1">
+    <row r="104" ht="4" customHeight="1" s="15" thickBot="1">
       <c r="A104" s="3" t="n"/>
       <c r="P104" s="17" t="n"/>
       <c r="Q104" s="18" t="n"/>
@@ -9889,7 +9889,7 @@
       <c r="KC104" s="19" t="n"/>
       <c r="KK104" s="4" t="n"/>
     </row>
-    <row r="105" ht="16.95" customHeight="1" s="15" thickBot="1">
+    <row r="105" ht="4" customHeight="1" s="15" thickBot="1">
       <c r="A105" s="3" t="n"/>
       <c r="P105" s="25" t="inlineStr">
         <is>
@@ -9975,7 +9975,7 @@
       <c r="KC105" s="13" t="n"/>
       <c r="KK105" s="4" t="n"/>
     </row>
-    <row r="106" ht="16.95" customHeight="1" s="15">
+    <row r="106" ht="4" customHeight="1" s="15">
       <c r="A106" s="3" t="n"/>
       <c r="P106" s="14" t="n"/>
       <c r="T106" s="16" t="n"/>
@@ -10047,7 +10047,7 @@
       <c r="KC106" s="16" t="n"/>
       <c r="KK106" s="4" t="n"/>
     </row>
-    <row r="107" ht="16.95" customHeight="1" s="15">
+    <row r="107" ht="4" customHeight="1" s="15">
       <c r="A107" s="3" t="n"/>
       <c r="P107" s="14" t="n"/>
       <c r="T107" s="16" t="n"/>
@@ -10119,7 +10119,7 @@
       <c r="KC107" s="16" t="n"/>
       <c r="KK107" s="4" t="n"/>
     </row>
-    <row r="108" ht="16.95" customHeight="1" s="15" thickBot="1">
+    <row r="108" ht="4" customHeight="1" s="15" thickBot="1">
       <c r="A108" s="3" t="n"/>
       <c r="P108" s="14" t="n"/>
       <c r="T108" s="16" t="n"/>
@@ -10191,7 +10191,7 @@
       <c r="KC108" s="16" t="n"/>
       <c r="KK108" s="4" t="n"/>
     </row>
-    <row r="109" ht="16.95" customHeight="1" s="15" thickBot="1">
+    <row r="109" ht="4" customHeight="1" s="15" thickBot="1">
       <c r="A109" s="3" t="n"/>
       <c r="P109" s="14" t="n"/>
       <c r="T109" s="16" t="n"/>
@@ -10351,7 +10351,7 @@
       <c r="KC109" s="16" t="n"/>
       <c r="KK109" s="4" t="n"/>
     </row>
-    <row r="110" ht="16.95" customHeight="1" s="15">
+    <row r="110" ht="4" customHeight="1" s="15">
       <c r="A110" s="3" t="n"/>
       <c r="P110" s="14" t="n"/>
       <c r="T110" s="16" t="n"/>
@@ -10372,7 +10372,7 @@
       <c r="KC110" s="16" t="n"/>
       <c r="KK110" s="4" t="n"/>
     </row>
-    <row r="111" ht="16.95" customHeight="1" s="15">
+    <row r="111" ht="4" customHeight="1" s="15">
       <c r="A111" s="3" t="n"/>
       <c r="P111" s="14" t="n"/>
       <c r="T111" s="16" t="n"/>
@@ -10393,7 +10393,7 @@
       <c r="KC111" s="16" t="n"/>
       <c r="KK111" s="4" t="n"/>
     </row>
-    <row r="112" ht="16.95" customHeight="1" s="15">
+    <row r="112" ht="4" customHeight="1" s="15">
       <c r="A112" s="3" t="n"/>
       <c r="P112" s="14" t="n"/>
       <c r="T112" s="16" t="n"/>
@@ -10414,7 +10414,7 @@
       <c r="KC112" s="16" t="n"/>
       <c r="KK112" s="4" t="n"/>
     </row>
-    <row r="113" ht="16.95" customHeight="1" s="15">
+    <row r="113" ht="4" customHeight="1" s="15">
       <c r="A113" s="3" t="n"/>
       <c r="P113" s="14" t="n"/>
       <c r="T113" s="16" t="n"/>
@@ -10435,7 +10435,7 @@
       <c r="KC113" s="16" t="n"/>
       <c r="KK113" s="4" t="n"/>
     </row>
-    <row r="114" ht="16.95" customHeight="1" s="15">
+    <row r="114" ht="4" customHeight="1" s="15">
       <c r="A114" s="3" t="n"/>
       <c r="P114" s="14" t="n"/>
       <c r="T114" s="16" t="n"/>
@@ -10475,7 +10475,7 @@
       <c r="KC114" s="16" t="n"/>
       <c r="KK114" s="4" t="n"/>
     </row>
-    <row r="115" ht="16.95" customHeight="1" s="15">
+    <row r="115" ht="4" customHeight="1" s="15">
       <c r="A115" s="3" t="n"/>
       <c r="P115" s="14" t="n"/>
       <c r="T115" s="16" t="n"/>
@@ -10505,7 +10505,7 @@
       <c r="KC115" s="16" t="n"/>
       <c r="KK115" s="4" t="n"/>
     </row>
-    <row r="116" ht="16.95" customHeight="1" s="15">
+    <row r="116" ht="4" customHeight="1" s="15">
       <c r="A116" s="3" t="n"/>
       <c r="P116" s="14" t="n"/>
       <c r="T116" s="16" t="n"/>
@@ -10545,7 +10545,7 @@
       <c r="KC116" s="16" t="n"/>
       <c r="KK116" s="4" t="n"/>
     </row>
-    <row r="117" ht="16.95" customHeight="1" s="15">
+    <row r="117" ht="4" customHeight="1" s="15">
       <c r="A117" s="3" t="n"/>
       <c r="P117" s="14" t="n"/>
       <c r="T117" s="16" t="n"/>
@@ -10585,7 +10585,7 @@
       <c r="KC117" s="16" t="n"/>
       <c r="KK117" s="4" t="n"/>
     </row>
-    <row r="118" ht="16.95" customHeight="1" s="15">
+    <row r="118" ht="4" customHeight="1" s="15">
       <c r="A118" s="3" t="n"/>
       <c r="P118" s="14" t="n"/>
       <c r="T118" s="16" t="n"/>
@@ -10625,7 +10625,7 @@
       <c r="KC118" s="16" t="n"/>
       <c r="KK118" s="4" t="n"/>
     </row>
-    <row r="119" ht="16.95" customHeight="1" s="15">
+    <row r="119" ht="4" customHeight="1" s="15">
       <c r="A119" s="3" t="n"/>
       <c r="P119" s="14" t="n"/>
       <c r="T119" s="16" t="n"/>
@@ -10665,7 +10665,7 @@
       <c r="KC119" s="16" t="n"/>
       <c r="KK119" s="4" t="n"/>
     </row>
-    <row r="120" ht="16.95" customHeight="1" s="15">
+    <row r="120" ht="4" customHeight="1" s="15">
       <c r="A120" s="3" t="n"/>
       <c r="P120" s="14" t="n"/>
       <c r="T120" s="16" t="n"/>
@@ -10705,7 +10705,7 @@
       <c r="KC120" s="16" t="n"/>
       <c r="KK120" s="4" t="n"/>
     </row>
-    <row r="121" ht="16.95" customHeight="1" s="15">
+    <row r="121" ht="4" customHeight="1" s="15">
       <c r="A121" s="3" t="n"/>
       <c r="P121" s="14" t="n"/>
       <c r="T121" s="16" t="n"/>
@@ -10745,7 +10745,7 @@
       <c r="KC121" s="16" t="n"/>
       <c r="KK121" s="4" t="n"/>
     </row>
-    <row r="122" ht="16.95" customHeight="1" s="15">
+    <row r="122" ht="4" customHeight="1" s="15">
       <c r="A122" s="3" t="n"/>
       <c r="P122" s="14" t="n"/>
       <c r="T122" s="16" t="n"/>
@@ -10785,7 +10785,7 @@
       <c r="KC122" s="16" t="n"/>
       <c r="KK122" s="4" t="n"/>
     </row>
-    <row r="123" ht="16.95" customHeight="1" s="15">
+    <row r="123" ht="4" customHeight="1" s="15">
       <c r="A123" s="3" t="n"/>
       <c r="P123" s="14" t="n"/>
       <c r="T123" s="16" t="n"/>
@@ -10825,7 +10825,7 @@
       <c r="KC123" s="16" t="n"/>
       <c r="KK123" s="4" t="n"/>
     </row>
-    <row r="124" ht="16.95" customHeight="1" s="15">
+    <row r="124" ht="4" customHeight="1" s="15">
       <c r="A124" s="3" t="n"/>
       <c r="P124" s="14" t="n"/>
       <c r="T124" s="16" t="n"/>
@@ -10865,7 +10865,7 @@
       <c r="KC124" s="16" t="n"/>
       <c r="KK124" s="4" t="n"/>
     </row>
-    <row r="125" ht="16.95" customHeight="1" s="15">
+    <row r="125" ht="4" customHeight="1" s="15">
       <c r="A125" s="3" t="n"/>
       <c r="P125" s="14" t="n"/>
       <c r="T125" s="16" t="n"/>
@@ -10905,7 +10905,7 @@
       <c r="KC125" s="16" t="n"/>
       <c r="KK125" s="4" t="n"/>
     </row>
-    <row r="126" ht="16.95" customHeight="1" s="15">
+    <row r="126" ht="4" customHeight="1" s="15">
       <c r="A126" s="3" t="n"/>
       <c r="P126" s="14" t="n"/>
       <c r="T126" s="16" t="n"/>
@@ -10945,7 +10945,7 @@
       <c r="KC126" s="16" t="n"/>
       <c r="KK126" s="4" t="n"/>
     </row>
-    <row r="127" ht="16.95" customHeight="1" s="15">
+    <row r="127" ht="4" customHeight="1" s="15">
       <c r="A127" s="3" t="n"/>
       <c r="P127" s="14" t="n"/>
       <c r="T127" s="16" t="n"/>
@@ -10985,7 +10985,7 @@
       <c r="KC127" s="16" t="n"/>
       <c r="KK127" s="4" t="n"/>
     </row>
-    <row r="128" ht="16.95" customHeight="1" s="15">
+    <row r="128" ht="4" customHeight="1" s="15">
       <c r="A128" s="3" t="n"/>
       <c r="P128" s="14" t="n"/>
       <c r="T128" s="16" t="n"/>
@@ -11025,7 +11025,7 @@
       <c r="KC128" s="16" t="n"/>
       <c r="KK128" s="4" t="n"/>
     </row>
-    <row r="129" ht="16.95" customHeight="1" s="15" thickBot="1">
+    <row r="129" ht="4" customHeight="1" s="15" thickBot="1">
       <c r="A129" s="3" t="n"/>
       <c r="P129" s="14" t="n"/>
       <c r="T129" s="16" t="n"/>
@@ -11143,7 +11143,7 @@
       <c r="KC129" s="16" t="n"/>
       <c r="KK129" s="4" t="n"/>
     </row>
-    <row r="130" ht="16.95" customHeight="1" s="15">
+    <row r="130" ht="4" customHeight="1" s="15">
       <c r="A130" s="3" t="n"/>
       <c r="P130" s="14" t="n"/>
       <c r="T130" s="16" t="n"/>
@@ -11181,7 +11181,7 @@
       <c r="KC130" s="16" t="n"/>
       <c r="KK130" s="4" t="n"/>
     </row>
-    <row r="131" ht="16.95" customHeight="1" s="15">
+    <row r="131" ht="4" customHeight="1" s="15">
       <c r="A131" s="3" t="n"/>
       <c r="P131" s="14" t="n"/>
       <c r="T131" s="16" t="n"/>
@@ -11219,7 +11219,7 @@
       <c r="KC131" s="16" t="n"/>
       <c r="KK131" s="4" t="n"/>
     </row>
-    <row r="132" ht="16.95" customHeight="1" s="15">
+    <row r="132" ht="4" customHeight="1" s="15">
       <c r="A132" s="3" t="n"/>
       <c r="P132" s="14" t="n"/>
       <c r="T132" s="16" t="n"/>
@@ -11257,7 +11257,7 @@
       <c r="KC132" s="16" t="n"/>
       <c r="KK132" s="4" t="n"/>
     </row>
-    <row r="133" ht="16.95" customHeight="1" s="15">
+    <row r="133" ht="4" customHeight="1" s="15">
       <c r="A133" s="3" t="n"/>
       <c r="P133" s="14" t="n"/>
       <c r="T133" s="16" t="n"/>
@@ -11295,7 +11295,7 @@
       <c r="KC133" s="16" t="n"/>
       <c r="KK133" s="4" t="n"/>
     </row>
-    <row r="134" ht="16.95" customHeight="1" s="15">
+    <row r="134" ht="4" customHeight="1" s="15">
       <c r="A134" s="3" t="n"/>
       <c r="P134" s="14" t="n"/>
       <c r="T134" s="16" t="n"/>
@@ -11324,7 +11324,7 @@
       <c r="KC134" s="16" t="n"/>
       <c r="KK134" s="4" t="n"/>
     </row>
-    <row r="135" ht="16.95" customHeight="1" s="15">
+    <row r="135" ht="4" customHeight="1" s="15">
       <c r="A135" s="3" t="n"/>
       <c r="P135" s="14" t="n"/>
       <c r="T135" s="16" t="n"/>
@@ -11343,7 +11343,7 @@
       <c r="KC135" s="16" t="n"/>
       <c r="KK135" s="4" t="n"/>
     </row>
-    <row r="136" ht="16.95" customHeight="1" s="15">
+    <row r="136" ht="4" customHeight="1" s="15">
       <c r="A136" s="3" t="n"/>
       <c r="P136" s="14" t="n"/>
       <c r="T136" s="16" t="n"/>
@@ -11362,7 +11362,7 @@
       <c r="KC136" s="16" t="n"/>
       <c r="KK136" s="4" t="n"/>
     </row>
-    <row r="137" ht="16.95" customHeight="1" s="15" thickBot="1">
+    <row r="137" ht="4" customHeight="1" s="15" thickBot="1">
       <c r="A137" s="3" t="n"/>
       <c r="P137" s="14" t="n"/>
       <c r="T137" s="16" t="n"/>
@@ -11381,7 +11381,7 @@
       <c r="KC137" s="16" t="n"/>
       <c r="KK137" s="4" t="n"/>
     </row>
-    <row r="138" ht="16.95" customHeight="1" s="15" thickBot="1">
+    <row r="138" ht="4" customHeight="1" s="15" thickBot="1">
       <c r="A138" s="3" t="n"/>
       <c r="P138" s="14" t="n"/>
       <c r="T138" s="16" t="n"/>
@@ -11504,7 +11504,7 @@
       <c r="KC138" s="16" t="n"/>
       <c r="KK138" s="4" t="n"/>
     </row>
-    <row r="139" ht="16.95" customHeight="1" s="15">
+    <row r="139" ht="4" customHeight="1" s="15">
       <c r="A139" s="3" t="n"/>
       <c r="P139" s="14" t="n"/>
       <c r="T139" s="16" t="n"/>
@@ -11535,7 +11535,7 @@
       <c r="KC139" s="16" t="n"/>
       <c r="KK139" s="4" t="n"/>
     </row>
-    <row r="140" ht="16.95" customHeight="1" s="15" thickBot="1">
+    <row r="140" ht="4" customHeight="1" s="15" thickBot="1">
       <c r="A140" s="3" t="n"/>
       <c r="P140" s="14" t="n"/>
       <c r="T140" s="16" t="n"/>
@@ -11634,7 +11634,7 @@
       <c r="KC140" s="16" t="n"/>
       <c r="KK140" s="4" t="n"/>
     </row>
-    <row r="141" ht="16.95" customHeight="1" s="15" thickBot="1">
+    <row r="141" ht="4" customHeight="1" s="15" thickBot="1">
       <c r="A141" s="3" t="n"/>
       <c r="P141" s="14" t="n"/>
       <c r="T141" s="16" t="n"/>
@@ -11757,7 +11757,7 @@
       <c r="KC141" s="16" t="n"/>
       <c r="KK141" s="4" t="n"/>
     </row>
-    <row r="142" ht="16.95" customHeight="1" s="15">
+    <row r="142" ht="4" customHeight="1" s="15">
       <c r="A142" s="3" t="n"/>
       <c r="P142" s="14" t="n"/>
       <c r="T142" s="16" t="n"/>
@@ -11788,7 +11788,7 @@
       <c r="KC142" s="16" t="n"/>
       <c r="KK142" s="4" t="n"/>
     </row>
-    <row r="143" ht="16.95" customHeight="1" s="15" thickBot="1">
+    <row r="143" ht="4" customHeight="1" s="15" thickBot="1">
       <c r="A143" s="3" t="n"/>
       <c r="P143" s="14" t="n"/>
       <c r="T143" s="16" t="n"/>
@@ -11887,7 +11887,7 @@
       <c r="KC143" s="16" t="n"/>
       <c r="KK143" s="4" t="n"/>
     </row>
-    <row r="144" ht="16.95" customHeight="1" s="15" thickBot="1">
+    <row r="144" ht="4" customHeight="1" s="15" thickBot="1">
       <c r="A144" s="3" t="n"/>
       <c r="P144" s="14" t="n"/>
       <c r="T144" s="16" t="n"/>
@@ -12010,7 +12010,7 @@
       <c r="KC144" s="16" t="n"/>
       <c r="KK144" s="4" t="n"/>
     </row>
-    <row r="145" ht="16.95" customHeight="1" s="15">
+    <row r="145" ht="4" customHeight="1" s="15">
       <c r="A145" s="3" t="n"/>
       <c r="P145" s="14" t="n"/>
       <c r="T145" s="16" t="n"/>
@@ -12041,7 +12041,7 @@
       <c r="KC145" s="16" t="n"/>
       <c r="KK145" s="4" t="n"/>
     </row>
-    <row r="146" ht="16.95" customHeight="1" s="15" thickBot="1">
+    <row r="146" ht="4" customHeight="1" s="15" thickBot="1">
       <c r="A146" s="3" t="n"/>
       <c r="P146" s="14" t="n"/>
       <c r="T146" s="16" t="n"/>
@@ -12140,7 +12140,7 @@
       <c r="KC146" s="16" t="n"/>
       <c r="KK146" s="4" t="n"/>
     </row>
-    <row r="147" ht="16.95" customHeight="1" s="15" thickBot="1">
+    <row r="147" ht="4" customHeight="1" s="15" thickBot="1">
       <c r="A147" s="3" t="n"/>
       <c r="P147" s="14" t="n"/>
       <c r="T147" s="16" t="n"/>
@@ -12263,7 +12263,7 @@
       <c r="KC147" s="16" t="n"/>
       <c r="KK147" s="4" t="n"/>
     </row>
-    <row r="148" ht="16.95" customHeight="1" s="15">
+    <row r="148" ht="4" customHeight="1" s="15">
       <c r="A148" s="3" t="n"/>
       <c r="P148" s="14" t="n"/>
       <c r="T148" s="16" t="n"/>
@@ -12294,7 +12294,7 @@
       <c r="KC148" s="16" t="n"/>
       <c r="KK148" s="4" t="n"/>
     </row>
-    <row r="149" ht="16.95" customHeight="1" s="15" thickBot="1">
+    <row r="149" ht="4" customHeight="1" s="15" thickBot="1">
       <c r="A149" s="3" t="n"/>
       <c r="P149" s="14" t="n"/>
       <c r="T149" s="16" t="n"/>
@@ -12393,7 +12393,7 @@
       <c r="KC149" s="16" t="n"/>
       <c r="KK149" s="4" t="n"/>
     </row>
-    <row r="150" ht="16.95" customHeight="1" s="15" thickBot="1">
+    <row r="150" ht="4" customHeight="1" s="15" thickBot="1">
       <c r="A150" s="3" t="n"/>
       <c r="P150" s="14" t="n"/>
       <c r="T150" s="16" t="n"/>
@@ -12535,7 +12535,7 @@
       <c r="KC150" s="16" t="n"/>
       <c r="KK150" s="4" t="n"/>
     </row>
-    <row r="151" ht="16.95" customHeight="1" s="15" thickBot="1">
+    <row r="151" ht="4" customHeight="1" s="15" thickBot="1">
       <c r="A151" s="3" t="n"/>
       <c r="P151" s="17" t="n"/>
       <c r="Q151" s="18" t="n"/>
@@ -12591,7 +12591,7 @@
       <c r="KC151" s="19" t="n"/>
       <c r="KK151" s="4" t="n"/>
     </row>
-    <row r="152" ht="16.95" customHeight="1" s="15" thickBot="1">
+    <row r="152" ht="4" customHeight="1" s="15" thickBot="1">
       <c r="A152" s="3" t="n"/>
       <c r="P152" s="25" t="inlineStr">
         <is>
@@ -12723,7 +12723,7 @@
       <c r="KC152" s="13" t="n"/>
       <c r="KK152" s="4" t="n"/>
     </row>
-    <row r="153" ht="16.95" customHeight="1" s="15" thickBot="1">
+    <row r="153" ht="4" customHeight="1" s="15" thickBot="1">
       <c r="A153" s="3" t="n"/>
       <c r="P153" s="14" t="n"/>
       <c r="T153" s="16" t="n"/>
@@ -12865,7 +12865,7 @@
       <c r="KC153" s="16" t="n"/>
       <c r="KK153" s="4" t="n"/>
     </row>
-    <row r="154" ht="16.95" customHeight="1" s="15">
+    <row r="154" ht="4" customHeight="1" s="15">
       <c r="A154" s="3" t="n"/>
       <c r="P154" s="14" t="n"/>
       <c r="T154" s="16" t="n"/>
@@ -12915,7 +12915,7 @@
       <c r="KC154" s="16" t="n"/>
       <c r="KK154" s="4" t="n"/>
     </row>
-    <row r="155" ht="16.95" customHeight="1" s="15" thickBot="1">
+    <row r="155" ht="4" customHeight="1" s="15" thickBot="1">
       <c r="A155" s="3" t="n"/>
       <c r="P155" s="14" t="n"/>
       <c r="T155" s="16" t="n"/>
@@ -13033,7 +13033,7 @@
       <c r="KC155" s="16" t="n"/>
       <c r="KK155" s="4" t="n"/>
     </row>
-    <row r="156" ht="16.95" customHeight="1" s="15" thickBot="1">
+    <row r="156" ht="4" customHeight="1" s="15" thickBot="1">
       <c r="A156" s="3" t="n"/>
       <c r="P156" s="14" t="n"/>
       <c r="T156" s="16" t="n"/>
@@ -13163,7 +13163,7 @@
       <c r="KC156" s="16" t="n"/>
       <c r="KK156" s="4" t="n"/>
     </row>
-    <row r="157" ht="16.95" customHeight="1" s="15">
+    <row r="157" ht="4" customHeight="1" s="15">
       <c r="A157" s="3" t="n"/>
       <c r="P157" s="14" t="n"/>
       <c r="T157" s="16" t="n"/>
@@ -13207,7 +13207,7 @@
       <c r="KC157" s="16" t="n"/>
       <c r="KK157" s="4" t="n"/>
     </row>
-    <row r="158" ht="16.95" customHeight="1" s="15" thickBot="1">
+    <row r="158" ht="4" customHeight="1" s="15" thickBot="1">
       <c r="A158" s="3" t="n"/>
       <c r="P158" s="14" t="n"/>
       <c r="T158" s="16" t="n"/>
@@ -13325,7 +13325,7 @@
       <c r="KC158" s="16" t="n"/>
       <c r="KK158" s="4" t="n"/>
     </row>
-    <row r="159" ht="16.95" customHeight="1" s="15" thickBot="1">
+    <row r="159" ht="4" customHeight="1" s="15" thickBot="1">
       <c r="A159" s="3" t="n"/>
       <c r="P159" s="14" t="n"/>
       <c r="T159" s="16" t="n"/>
@@ -13412,7 +13412,7 @@
       <c r="KC159" s="16" t="n"/>
       <c r="KK159" s="4" t="n"/>
     </row>
-    <row r="160" ht="16.95" customHeight="1" s="15">
+    <row r="160" ht="4" customHeight="1" s="15">
       <c r="A160" s="3" t="n"/>
       <c r="P160" s="14" t="n"/>
       <c r="T160" s="16" t="n"/>
@@ -13455,7 +13455,7 @@
       <c r="KC160" s="16" t="n"/>
       <c r="KK160" s="4" t="n"/>
     </row>
-    <row r="161" ht="16.95" customHeight="1" s="15">
+    <row r="161" ht="4" customHeight="1" s="15">
       <c r="A161" s="3" t="n"/>
       <c r="P161" s="14" t="n"/>
       <c r="T161" s="16" t="n"/>
@@ -13498,7 +13498,7 @@
       <c r="KC161" s="16" t="n"/>
       <c r="KK161" s="4" t="n"/>
     </row>
-    <row r="162" ht="16.95" customHeight="1" s="15">
+    <row r="162" ht="4" customHeight="1" s="15">
       <c r="A162" s="3" t="n"/>
       <c r="P162" s="14" t="n"/>
       <c r="T162" s="16" t="n"/>
@@ -13541,7 +13541,7 @@
       <c r="KC162" s="16" t="n"/>
       <c r="KK162" s="4" t="n"/>
     </row>
-    <row r="163" ht="16.95" customHeight="1" s="15" thickBot="1">
+    <row r="163" ht="4" customHeight="1" s="15" thickBot="1">
       <c r="A163" s="3" t="n"/>
       <c r="P163" s="14" t="n"/>
       <c r="T163" s="16" t="n"/>
@@ -13659,7 +13659,7 @@
       <c r="KC163" s="16" t="n"/>
       <c r="KK163" s="4" t="n"/>
     </row>
-    <row r="164" ht="16.95" customHeight="1" s="15" thickBot="1">
+    <row r="164" ht="4" customHeight="1" s="15" thickBot="1">
       <c r="A164" s="3" t="n"/>
       <c r="P164" s="14" t="n"/>
       <c r="T164" s="16" t="n"/>
@@ -13785,7 +13785,7 @@
       <c r="KC164" s="16" t="n"/>
       <c r="KK164" s="4" t="n"/>
     </row>
-    <row r="165" ht="16.95" customHeight="1" s="15">
+    <row r="165" ht="4" customHeight="1" s="15">
       <c r="A165" s="3" t="n"/>
       <c r="P165" s="14" t="n"/>
       <c r="T165" s="16" t="n"/>
@@ -13827,7 +13827,7 @@
       <c r="KC165" s="16" t="n"/>
       <c r="KK165" s="4" t="n"/>
     </row>
-    <row r="166" ht="16.95" customHeight="1" s="15">
+    <row r="166" ht="4" customHeight="1" s="15">
       <c r="A166" s="3" t="n"/>
       <c r="P166" s="14" t="n"/>
       <c r="T166" s="16" t="n"/>
@@ -13869,7 +13869,7 @@
       <c r="KC166" s="16" t="n"/>
       <c r="KK166" s="4" t="n"/>
     </row>
-    <row r="167" ht="16.95" customHeight="1" s="15" thickBot="1">
+    <row r="167" ht="4" customHeight="1" s="15" thickBot="1">
       <c r="A167" s="3" t="n"/>
       <c r="P167" s="14" t="n"/>
       <c r="T167" s="16" t="n"/>
@@ -13915,7 +13915,7 @@
       <c r="KC167" s="16" t="n"/>
       <c r="KK167" s="4" t="n"/>
     </row>
-    <row r="168" ht="16.95" customHeight="1" s="15">
+    <row r="168" ht="4" customHeight="1" s="15">
       <c r="A168" s="3" t="n"/>
       <c r="P168" s="14" t="n"/>
       <c r="T168" s="16" t="n"/>
@@ -13957,7 +13957,7 @@
       <c r="KC168" s="16" t="n"/>
       <c r="KK168" s="4" t="n"/>
     </row>
-    <row r="169" ht="16.95" customHeight="1" s="15">
+    <row r="169" ht="4" customHeight="1" s="15">
       <c r="A169" s="3" t="n"/>
       <c r="P169" s="14" t="n"/>
       <c r="T169" s="16" t="n"/>
@@ -13990,7 +13990,7 @@
       <c r="KC169" s="16" t="n"/>
       <c r="KK169" s="4" t="n"/>
     </row>
-    <row r="170" ht="16.95" customHeight="1" s="15">
+    <row r="170" ht="4" customHeight="1" s="15">
       <c r="A170" s="3" t="n"/>
       <c r="P170" s="14" t="n"/>
       <c r="T170" s="16" t="n"/>
@@ -14013,7 +14013,7 @@
       <c r="KC170" s="16" t="n"/>
       <c r="KK170" s="4" t="n"/>
     </row>
-    <row r="171" ht="16.95" customHeight="1" s="15" thickBot="1">
+    <row r="171" ht="4" customHeight="1" s="15" thickBot="1">
       <c r="A171" s="3" t="n"/>
       <c r="P171" s="14" t="n"/>
       <c r="T171" s="16" t="n"/>
@@ -14084,7 +14084,7 @@
       <c r="KC171" s="16" t="n"/>
       <c r="KK171" s="4" t="n"/>
     </row>
-    <row r="172" ht="16.95" customHeight="1" s="15" thickBot="1">
+    <row r="172" ht="4" customHeight="1" s="15" thickBot="1">
       <c r="A172" s="3" t="n"/>
       <c r="P172" s="14" t="n"/>
       <c r="T172" s="16" t="n"/>
@@ -14159,7 +14159,7 @@
       <c r="KC172" s="16" t="n"/>
       <c r="KK172" s="4" t="n"/>
     </row>
-    <row r="173" ht="16.95" customHeight="1" s="15">
+    <row r="173" ht="4" customHeight="1" s="15">
       <c r="A173" s="3" t="n"/>
       <c r="P173" s="14" t="n"/>
       <c r="T173" s="16" t="n"/>
@@ -14182,7 +14182,7 @@
       <c r="KC173" s="16" t="n"/>
       <c r="KK173" s="4" t="n"/>
     </row>
-    <row r="174" ht="16.95" customHeight="1" s="15">
+    <row r="174" ht="4" customHeight="1" s="15">
       <c r="A174" s="3" t="n"/>
       <c r="P174" s="14" t="n"/>
       <c r="T174" s="16" t="n"/>
@@ -14205,7 +14205,7 @@
       <c r="KC174" s="16" t="n"/>
       <c r="KK174" s="4" t="n"/>
     </row>
-    <row r="175" ht="16.95" customHeight="1" s="15">
+    <row r="175" ht="4" customHeight="1" s="15">
       <c r="A175" s="3" t="n"/>
       <c r="P175" s="14" t="n"/>
       <c r="T175" s="16" t="n"/>
@@ -14228,7 +14228,7 @@
       <c r="KC175" s="16" t="n"/>
       <c r="KK175" s="4" t="n"/>
     </row>
-    <row r="176" ht="16.95" customHeight="1" s="15">
+    <row r="176" ht="4" customHeight="1" s="15">
       <c r="A176" s="3" t="n"/>
       <c r="P176" s="14" t="n"/>
       <c r="T176" s="16" t="n"/>
@@ -14251,7 +14251,7 @@
       <c r="KC176" s="16" t="n"/>
       <c r="KK176" s="4" t="n"/>
     </row>
-    <row r="177" ht="16.95" customHeight="1" s="15">
+    <row r="177" ht="4" customHeight="1" s="15">
       <c r="A177" s="3" t="n"/>
       <c r="P177" s="14" t="n"/>
       <c r="T177" s="16" t="n"/>
@@ -14274,7 +14274,7 @@
       <c r="KC177" s="16" t="n"/>
       <c r="KK177" s="4" t="n"/>
     </row>
-    <row r="178" ht="16.95" customHeight="1" s="15" thickBot="1">
+    <row r="178" ht="4" customHeight="1" s="15" thickBot="1">
       <c r="A178" s="3" t="n"/>
       <c r="P178" s="14" t="n"/>
       <c r="T178" s="16" t="n"/>
@@ -14373,7 +14373,7 @@
       <c r="KC178" s="16" t="n"/>
       <c r="KK178" s="4" t="n"/>
     </row>
-    <row r="179" ht="16.95" customHeight="1" s="15" thickBot="1">
+    <row r="179" ht="4" customHeight="1" s="15" thickBot="1">
       <c r="A179" s="3" t="n"/>
       <c r="P179" s="14" t="n"/>
       <c r="T179" s="16" t="n"/>
@@ -14480,7 +14480,7 @@
       <c r="KC179" s="16" t="n"/>
       <c r="KK179" s="4" t="n"/>
     </row>
-    <row r="180" ht="16.95" customHeight="1" s="15">
+    <row r="180" ht="4" customHeight="1" s="15">
       <c r="A180" s="3" t="n"/>
       <c r="P180" s="14" t="n"/>
       <c r="T180" s="16" t="n"/>
@@ -14503,7 +14503,7 @@
       <c r="KC180" s="16" t="n"/>
       <c r="KK180" s="4" t="n"/>
     </row>
-    <row r="181" ht="16.95" customHeight="1" s="15">
+    <row r="181" ht="4" customHeight="1" s="15">
       <c r="A181" s="3" t="n"/>
       <c r="P181" s="14" t="n"/>
       <c r="T181" s="16" t="n"/>
@@ -14526,7 +14526,7 @@
       <c r="KC181" s="16" t="n"/>
       <c r="KK181" s="4" t="n"/>
     </row>
-    <row r="182" ht="16.95" customHeight="1" s="15" thickBot="1">
+    <row r="182" ht="4" customHeight="1" s="15" thickBot="1">
       <c r="A182" s="3" t="n"/>
       <c r="P182" s="14" t="n"/>
       <c r="T182" s="16" t="n"/>
@@ -14553,7 +14553,7 @@
       <c r="KC182" s="16" t="n"/>
       <c r="KK182" s="4" t="n"/>
     </row>
-    <row r="183" ht="16.95" customHeight="1" s="15">
+    <row r="183" ht="4" customHeight="1" s="15">
       <c r="A183" s="3" t="n"/>
       <c r="P183" s="14" t="n"/>
       <c r="T183" s="16" t="n"/>
@@ -14576,7 +14576,7 @@
       <c r="KC183" s="16" t="n"/>
       <c r="KK183" s="4" t="n"/>
     </row>
-    <row r="184" ht="16.95" customHeight="1" s="15">
+    <row r="184" ht="4" customHeight="1" s="15">
       <c r="A184" s="3" t="n"/>
       <c r="P184" s="14" t="n"/>
       <c r="T184" s="16" t="n"/>
@@ -14599,7 +14599,7 @@
       <c r="KC184" s="16" t="n"/>
       <c r="KK184" s="4" t="n"/>
     </row>
-    <row r="185" ht="16.95" customHeight="1" s="15">
+    <row r="185" ht="4" customHeight="1" s="15">
       <c r="A185" s="3" t="n"/>
       <c r="P185" s="14" t="n"/>
       <c r="T185" s="16" t="n"/>
@@ -14641,7 +14641,7 @@
       <c r="KC185" s="16" t="n"/>
       <c r="KK185" s="4" t="n"/>
     </row>
-    <row r="186" ht="16.95" customHeight="1" s="15">
+    <row r="186" ht="4" customHeight="1" s="15">
       <c r="A186" s="3" t="n"/>
       <c r="P186" s="14" t="n"/>
       <c r="T186" s="16" t="n"/>
@@ -14683,7 +14683,7 @@
       <c r="KC186" s="16" t="n"/>
       <c r="KK186" s="4" t="n"/>
     </row>
-    <row r="187" ht="16.95" customHeight="1" s="15">
+    <row r="187" ht="4" customHeight="1" s="15">
       <c r="A187" s="3" t="n"/>
       <c r="P187" s="14" t="n"/>
       <c r="T187" s="16" t="n"/>
@@ -14725,7 +14725,7 @@
       <c r="KC187" s="16" t="n"/>
       <c r="KK187" s="4" t="n"/>
     </row>
-    <row r="188" ht="16.95" customHeight="1" s="15">
+    <row r="188" ht="4" customHeight="1" s="15">
       <c r="A188" s="3" t="n"/>
       <c r="P188" s="14" t="n"/>
       <c r="T188" s="16" t="n"/>
@@ -14767,7 +14767,7 @@
       <c r="KC188" s="16" t="n"/>
       <c r="KK188" s="4" t="n"/>
     </row>
-    <row r="189" ht="16.95" customHeight="1" s="15">
+    <row r="189" ht="4" customHeight="1" s="15">
       <c r="A189" s="3" t="n"/>
       <c r="P189" s="14" t="n"/>
       <c r="T189" s="16" t="n"/>
@@ -14809,7 +14809,7 @@
       <c r="KC189" s="16" t="n"/>
       <c r="KK189" s="4" t="n"/>
     </row>
-    <row r="190" ht="16.95" customHeight="1" s="15">
+    <row r="190" ht="4" customHeight="1" s="15">
       <c r="A190" s="3" t="n"/>
       <c r="P190" s="14" t="n"/>
       <c r="T190" s="16" t="n"/>
@@ -14851,7 +14851,7 @@
       <c r="KC190" s="16" t="n"/>
       <c r="KK190" s="4" t="n"/>
     </row>
-    <row r="191" ht="16.95" customHeight="1" s="15">
+    <row r="191" ht="4" customHeight="1" s="15">
       <c r="A191" s="3" t="n"/>
       <c r="P191" s="14" t="n"/>
       <c r="T191" s="16" t="n"/>
@@ -14893,7 +14893,7 @@
       <c r="KC191" s="16" t="n"/>
       <c r="KK191" s="4" t="n"/>
     </row>
-    <row r="192" ht="16.95" customHeight="1" s="15">
+    <row r="192" ht="4" customHeight="1" s="15">
       <c r="A192" s="3" t="n"/>
       <c r="P192" s="14" t="n"/>
       <c r="T192" s="16" t="n"/>
@@ -14935,7 +14935,7 @@
       <c r="KC192" s="16" t="n"/>
       <c r="KK192" s="4" t="n"/>
     </row>
-    <row r="193" ht="16.95" customHeight="1" s="15" thickBot="1">
+    <row r="193" ht="4" customHeight="1" s="15" thickBot="1">
       <c r="A193" s="3" t="n"/>
       <c r="P193" s="14" t="n"/>
       <c r="T193" s="16" t="n"/>
@@ -15053,7 +15053,7 @@
       <c r="KC193" s="16" t="n"/>
       <c r="KK193" s="4" t="n"/>
     </row>
-    <row r="194" ht="16.95" customHeight="1" s="15" thickBot="1">
+    <row r="194" ht="4" customHeight="1" s="15" thickBot="1">
       <c r="A194" s="3" t="n"/>
       <c r="P194" s="14" t="n"/>
       <c r="T194" s="16" t="n"/>
@@ -15295,7 +15295,7 @@
       <c r="KC194" s="16" t="n"/>
       <c r="KK194" s="4" t="n"/>
     </row>
-    <row r="195" ht="16.95" customHeight="1" s="15">
+    <row r="195" ht="4" customHeight="1" s="15">
       <c r="A195" s="3" t="n"/>
       <c r="P195" s="14" t="n"/>
       <c r="T195" s="16" t="n"/>
@@ -15449,7 +15449,7 @@
       <c r="KC195" s="16" t="n"/>
       <c r="KK195" s="4" t="n"/>
     </row>
-    <row r="196" ht="16.95" customHeight="1" s="15">
+    <row r="196" ht="4" customHeight="1" s="15">
       <c r="A196" s="3" t="n"/>
       <c r="P196" s="14" t="n"/>
       <c r="T196" s="16" t="n"/>
@@ -15603,7 +15603,7 @@
       <c r="KC196" s="16" t="n"/>
       <c r="KK196" s="4" t="n"/>
     </row>
-    <row r="197" ht="16.95" customHeight="1" s="15">
+    <row r="197" ht="4" customHeight="1" s="15">
       <c r="A197" s="3" t="n"/>
       <c r="P197" s="14" t="n"/>
       <c r="T197" s="16" t="n"/>
@@ -15757,7 +15757,7 @@
       <c r="KC197" s="16" t="n"/>
       <c r="KK197" s="4" t="n"/>
     </row>
-    <row r="198" ht="16.95" customHeight="1" s="15" thickBot="1">
+    <row r="198" ht="4" customHeight="1" s="15" thickBot="1">
       <c r="A198" s="3" t="n"/>
       <c r="P198" s="17" t="n"/>
       <c r="Q198" s="18" t="n"/>
@@ -15995,7 +15995,7 @@
       <c r="KC198" s="19" t="n"/>
       <c r="KK198" s="4" t="n"/>
     </row>
-    <row r="199" ht="16.95" customHeight="1" s="15" thickBot="1">
+    <row r="199" ht="4" customHeight="1" s="15" thickBot="1">
       <c r="A199" s="3" t="n"/>
       <c r="U199" s="25" t="n">
         <v>1</v>
@@ -16275,7 +16275,7 @@
       <c r="JX199" s="13" t="n"/>
       <c r="KK199" s="4" t="n"/>
     </row>
-    <row r="200" ht="16.95" customHeight="1" s="15">
+    <row r="200" ht="4" customHeight="1" s="15">
       <c r="A200" s="3" t="n"/>
       <c r="U200" s="14" t="n"/>
       <c r="BL200" s="16" t="n"/>
@@ -16291,7 +16291,7 @@
       <c r="JX200" s="16" t="n"/>
       <c r="KK200" s="4" t="n"/>
     </row>
-    <row r="201" ht="16.95" customHeight="1" s="15">
+    <row r="201" ht="4" customHeight="1" s="15">
       <c r="A201" s="3" t="n"/>
       <c r="U201" s="14" t="n"/>
       <c r="BL201" s="16" t="n"/>
@@ -16307,7 +16307,7 @@
       <c r="JX201" s="16" t="n"/>
       <c r="KK201" s="4" t="n"/>
     </row>
-    <row r="202" ht="16.95" customHeight="1" s="15">
+    <row r="202" ht="4" customHeight="1" s="15">
       <c r="A202" s="3" t="n"/>
       <c r="U202" s="14" t="n"/>
       <c r="BL202" s="16" t="n"/>
@@ -16323,7 +16323,7 @@
       <c r="JX202" s="16" t="n"/>
       <c r="KK202" s="4" t="n"/>
     </row>
-    <row r="203" ht="16.95" customHeight="1" s="15" thickBot="1">
+    <row r="203" ht="4" customHeight="1" s="15" thickBot="1">
       <c r="A203" s="3" t="n"/>
       <c r="U203" s="17" t="n"/>
       <c r="V203" s="18" t="n"/>
@@ -16591,31 +16591,31 @@
       <c r="JX203" s="19" t="n"/>
       <c r="KK203" s="4" t="n"/>
     </row>
-    <row r="204" ht="16.95" customHeight="1" s="15">
+    <row r="204" ht="4" customHeight="1" s="15">
       <c r="A204" s="3" t="n"/>
       <c r="KK204" s="4" t="n"/>
     </row>
-    <row r="205" ht="16.95" customHeight="1" s="15">
+    <row r="205" ht="4" customHeight="1" s="15">
       <c r="A205" s="3" t="n"/>
       <c r="KK205" s="4" t="n"/>
     </row>
-    <row r="206" ht="16.95" customHeight="1" s="15">
+    <row r="206" ht="4" customHeight="1" s="15">
       <c r="A206" s="3" t="n"/>
       <c r="KK206" s="4" t="n"/>
     </row>
-    <row r="207" ht="16.95" customHeight="1" s="15">
+    <row r="207" ht="4" customHeight="1" s="15">
       <c r="A207" s="3" t="n"/>
       <c r="KK207" s="4" t="n"/>
     </row>
-    <row r="208" ht="16.95" customHeight="1" s="15">
+    <row r="208" ht="4" customHeight="1" s="15">
       <c r="A208" s="3" t="n"/>
       <c r="KK208" s="4" t="n"/>
     </row>
-    <row r="209" ht="16.95" customHeight="1" s="15">
+    <row r="209" ht="4" customHeight="1" s="15">
       <c r="A209" s="3" t="n"/>
       <c r="KK209" s="4" t="n"/>
     </row>
-    <row r="210" ht="16.95" customHeight="1" s="15" thickBot="1">
+    <row r="210" ht="4" customHeight="1" s="15" thickBot="1">
       <c r="A210" s="5" t="n"/>
       <c r="B210" s="6" t="n"/>
       <c r="C210" s="6" t="n"/>

--- a/가공도_도면_1.xlsx
+++ b/가공도_도면_1.xlsx
@@ -40,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="24">
+  <borders count="38">
     <border>
       <left/>
       <right/>
@@ -301,11 +301,135 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <right/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -360,6 +484,38 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -891,7 +1047,7 @@
       <c r="N2" s="11" t="n"/>
       <c r="O2" s="11" t="n"/>
       <c r="P2" s="12" t="n"/>
-      <c r="Q2" s="10" t="n">
+      <c r="Q2" s="32" t="n">
         <v>2</v>
       </c>
       <c r="R2" s="11" t="n"/>
@@ -904,7 +1060,7 @@
       <c r="Y2" s="11" t="n"/>
       <c r="Z2" s="11" t="n"/>
       <c r="AA2" s="12" t="n"/>
-      <c r="AB2" s="10" t="n">
+      <c r="AB2" s="32" t="n">
         <v>3</v>
       </c>
       <c r="AC2" s="11" t="n"/>
@@ -916,7 +1072,7 @@
       <c r="AI2" s="11" t="n"/>
       <c r="AJ2" s="11" t="n"/>
       <c r="AK2" s="12" t="n"/>
-      <c r="AL2" s="10" t="n">
+      <c r="AL2" s="32" t="n">
         <v>4</v>
       </c>
       <c r="AM2" s="11" t="n"/>
@@ -929,7 +1085,7 @@
       <c r="AT2" s="11" t="n"/>
       <c r="AU2" s="11" t="n"/>
       <c r="AV2" s="12" t="n"/>
-      <c r="AW2" s="10" t="n">
+      <c r="AW2" s="32" t="n">
         <v>5</v>
       </c>
       <c r="AX2" s="11" t="n"/>
@@ -943,7 +1099,7 @@
       <c r="BF2" s="11" t="n"/>
       <c r="BG2" s="11" t="n"/>
       <c r="BH2" s="12" t="n"/>
-      <c r="BI2" s="10" t="n">
+      <c r="BI2" s="32" t="n">
         <v>6</v>
       </c>
       <c r="BJ2" s="11" t="n"/>
@@ -987,7 +1143,7 @@
         </is>
       </c>
       <c r="BS3" s="23" t="n"/>
-      <c r="BT3" s="10" t="inlineStr">
+      <c r="BT3" s="33" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -1018,66 +1174,66 @@
       <c r="BQ4" s="18" t="n"/>
       <c r="BR4" s="18" t="n"/>
       <c r="BS4" s="20" t="n"/>
-      <c r="BT4" s="25" t="n"/>
+      <c r="BT4" s="34" t="n"/>
       <c r="BV4" s="5" t="n"/>
     </row>
     <row r="5" ht="13.95" customHeight="1" s="16">
       <c r="A5" s="6" t="n"/>
       <c r="E5" s="25" t="n"/>
-      <c r="AY5" s="10" t="inlineStr">
+      <c r="AY5" s="35" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="AZ5" s="19" t="n"/>
-      <c r="BA5" s="13" t="inlineStr">
+      <c r="AZ5" s="36" t="n"/>
+      <c r="BA5" s="37" t="inlineStr">
         <is>
           <t>ITEM</t>
         </is>
       </c>
-      <c r="BB5" s="14" t="n"/>
-      <c r="BC5" s="14" t="n"/>
-      <c r="BD5" s="14" t="n"/>
-      <c r="BE5" s="10" t="inlineStr">
+      <c r="BB5" s="38" t="n"/>
+      <c r="BC5" s="38" t="n"/>
+      <c r="BD5" s="38" t="n"/>
+      <c r="BE5" s="35" t="inlineStr">
         <is>
           <t>MATERIAL</t>
         </is>
       </c>
-      <c r="BF5" s="14" t="n"/>
-      <c r="BG5" s="19" t="n"/>
-      <c r="BH5" s="10" t="inlineStr">
+      <c r="BF5" s="38" t="n"/>
+      <c r="BG5" s="36" t="n"/>
+      <c r="BH5" s="33" t="inlineStr">
         <is>
           <t>SIZE</t>
         </is>
       </c>
-      <c r="BI5" s="14" t="n"/>
-      <c r="BJ5" s="14" t="n"/>
-      <c r="BK5" s="14" t="n"/>
-      <c r="BL5" s="14" t="n"/>
-      <c r="BM5" s="19" t="n"/>
-      <c r="BN5" s="10" t="inlineStr">
+      <c r="BI5" s="38" t="n"/>
+      <c r="BJ5" s="38" t="n"/>
+      <c r="BK5" s="38" t="n"/>
+      <c r="BL5" s="38" t="n"/>
+      <c r="BM5" s="36" t="n"/>
+      <c r="BN5" s="33" t="inlineStr">
         <is>
           <t>Q'TY</t>
         </is>
       </c>
-      <c r="BO5" s="10" t="inlineStr">
+      <c r="BO5" s="33" t="inlineStr">
         <is>
           <t>T/W</t>
         </is>
       </c>
-      <c r="BP5" s="14" t="n"/>
-      <c r="BQ5" s="19" t="n"/>
-      <c r="BR5" s="10" t="inlineStr">
+      <c r="BP5" s="38" t="n"/>
+      <c r="BQ5" s="36" t="n"/>
+      <c r="BR5" s="33" t="inlineStr">
         <is>
           <t>MA</t>
         </is>
       </c>
-      <c r="BS5" s="10" t="inlineStr">
+      <c r="BS5" s="33" t="inlineStr">
         <is>
           <t>FA</t>
         </is>
       </c>
-      <c r="BT5" s="25" t="n"/>
+      <c r="BT5" s="34" t="n"/>
       <c r="BV5" s="5" t="n"/>
     </row>
     <row r="6" ht="13.95" customHeight="1" s="16">
@@ -1085,85 +1241,85 @@
       <c r="E6" s="25" t="n"/>
       <c r="AY6" s="17" t="n"/>
       <c r="AZ6" s="20" t="n"/>
-      <c r="BA6" s="17" t="n"/>
+      <c r="BA6" s="39" t="n"/>
       <c r="BB6" s="18" t="n"/>
       <c r="BC6" s="18" t="n"/>
       <c r="BD6" s="18" t="n"/>
       <c r="BE6" s="17" t="n"/>
       <c r="BF6" s="18" t="n"/>
       <c r="BG6" s="20" t="n"/>
-      <c r="BH6" s="17" t="n"/>
+      <c r="BH6" s="39" t="n"/>
       <c r="BI6" s="18" t="n"/>
       <c r="BJ6" s="18" t="n"/>
       <c r="BK6" s="18" t="n"/>
       <c r="BL6" s="18" t="n"/>
       <c r="BM6" s="20" t="n"/>
-      <c r="BN6" s="21" t="n"/>
-      <c r="BO6" s="17" t="n"/>
+      <c r="BN6" s="40" t="n"/>
+      <c r="BO6" s="39" t="n"/>
       <c r="BP6" s="18" t="n"/>
       <c r="BQ6" s="20" t="n"/>
-      <c r="BR6" s="21" t="n"/>
-      <c r="BS6" s="21" t="n"/>
-      <c r="BT6" s="25" t="n"/>
+      <c r="BR6" s="40" t="n"/>
+      <c r="BS6" s="40" t="n"/>
+      <c r="BT6" s="34" t="n"/>
       <c r="BV6" s="5" t="n"/>
     </row>
     <row r="7" ht="13.95" customHeight="1" s="16">
       <c r="A7" s="6" t="n"/>
       <c r="E7" s="25" t="n"/>
-      <c r="AY7" s="10" t="inlineStr">
+      <c r="AY7" s="35" t="inlineStr">
         <is>
           <t>{Input_4}</t>
         </is>
       </c>
-      <c r="AZ7" s="12" t="n"/>
-      <c r="BA7" s="10" t="inlineStr">
+      <c r="AZ7" s="41" t="n"/>
+      <c r="BA7" s="33" t="inlineStr">
         <is>
           <t>{Input_24}</t>
         </is>
       </c>
-      <c r="BB7" s="11" t="n"/>
-      <c r="BC7" s="11" t="n"/>
-      <c r="BD7" s="12" t="n"/>
-      <c r="BE7" s="10" t="inlineStr">
+      <c r="BB7" s="42" t="n"/>
+      <c r="BC7" s="42" t="n"/>
+      <c r="BD7" s="41" t="n"/>
+      <c r="BE7" s="33" t="inlineStr">
         <is>
           <t>{Input_44}</t>
         </is>
       </c>
-      <c r="BF7" s="11" t="n"/>
-      <c r="BG7" s="12" t="n"/>
-      <c r="BH7" s="10" t="inlineStr">
+      <c r="BF7" s="42" t="n"/>
+      <c r="BG7" s="41" t="n"/>
+      <c r="BH7" s="33" t="inlineStr">
         <is>
           <t>{Input_64}</t>
         </is>
       </c>
-      <c r="BI7" s="11" t="n"/>
-      <c r="BJ7" s="11" t="n"/>
-      <c r="BK7" s="11" t="n"/>
-      <c r="BL7" s="11" t="n"/>
-      <c r="BM7" s="12" t="n"/>
-      <c r="BN7" s="10" t="inlineStr">
+      <c r="BI7" s="42" t="n"/>
+      <c r="BJ7" s="42" t="n"/>
+      <c r="BK7" s="42" t="n"/>
+      <c r="BL7" s="42" t="n"/>
+      <c r="BM7" s="41" t="n"/>
+      <c r="BN7" s="33" t="inlineStr">
         <is>
           <t>{Input_84}</t>
         </is>
       </c>
-      <c r="BO7" s="10" t="inlineStr">
+      <c r="BO7" s="33" t="inlineStr">
         <is>
           <t>{Input_104}</t>
         </is>
       </c>
-      <c r="BP7" s="11" t="n"/>
-      <c r="BQ7" s="12" t="n"/>
-      <c r="BR7" s="10" t="inlineStr">
+      <c r="BP7" s="42" t="n"/>
+      <c r="BQ7" s="41" t="n"/>
+      <c r="BR7" s="33" t="inlineStr">
         <is>
           <t>{Input_124}</t>
         </is>
       </c>
-      <c r="BS7" s="10" t="inlineStr">
+      <c r="BS7" s="33" t="inlineStr">
         <is>
           <t>{Input_144}</t>
         </is>
       </c>
-      <c r="BT7" s="25" t="n"/>
+      <c r="BT7" s="34" t="n"/>
       <c r="BV7" s="5" t="n"/>
     </row>
     <row r="8" ht="13.95" customHeight="1" s="16">
@@ -1179,237 +1335,237 @@
           <t>{View_1}</t>
         </is>
       </c>
-      <c r="AY8" s="10" t="inlineStr">
+      <c r="AY8" s="35" t="inlineStr">
         <is>
           <t>{Input_5}</t>
         </is>
       </c>
-      <c r="AZ8" s="12" t="n"/>
-      <c r="BA8" s="10" t="inlineStr">
+      <c r="AZ8" s="41" t="n"/>
+      <c r="BA8" s="33" t="inlineStr">
         <is>
           <t>{Input_25}</t>
         </is>
       </c>
-      <c r="BB8" s="11" t="n"/>
-      <c r="BC8" s="11" t="n"/>
-      <c r="BD8" s="12" t="n"/>
-      <c r="BE8" s="10" t="inlineStr">
+      <c r="BB8" s="42" t="n"/>
+      <c r="BC8" s="42" t="n"/>
+      <c r="BD8" s="41" t="n"/>
+      <c r="BE8" s="33" t="inlineStr">
         <is>
           <t>{Input_45}</t>
         </is>
       </c>
-      <c r="BF8" s="11" t="n"/>
-      <c r="BG8" s="12" t="n"/>
-      <c r="BH8" s="10" t="inlineStr">
+      <c r="BF8" s="42" t="n"/>
+      <c r="BG8" s="41" t="n"/>
+      <c r="BH8" s="33" t="inlineStr">
         <is>
           <t>{Input_65}</t>
         </is>
       </c>
-      <c r="BI8" s="11" t="n"/>
-      <c r="BJ8" s="11" t="n"/>
-      <c r="BK8" s="11" t="n"/>
-      <c r="BL8" s="11" t="n"/>
-      <c r="BM8" s="12" t="n"/>
-      <c r="BN8" s="10" t="inlineStr">
+      <c r="BI8" s="42" t="n"/>
+      <c r="BJ8" s="42" t="n"/>
+      <c r="BK8" s="42" t="n"/>
+      <c r="BL8" s="42" t="n"/>
+      <c r="BM8" s="41" t="n"/>
+      <c r="BN8" s="33" t="inlineStr">
         <is>
           <t>{Input_85}</t>
         </is>
       </c>
-      <c r="BO8" s="10" t="inlineStr">
+      <c r="BO8" s="33" t="inlineStr">
         <is>
           <t>{Input_105}</t>
         </is>
       </c>
-      <c r="BP8" s="11" t="n"/>
-      <c r="BQ8" s="12" t="n"/>
-      <c r="BR8" s="10" t="inlineStr">
+      <c r="BP8" s="42" t="n"/>
+      <c r="BQ8" s="41" t="n"/>
+      <c r="BR8" s="33" t="inlineStr">
         <is>
           <t>{Input_125}</t>
         </is>
       </c>
-      <c r="BS8" s="10" t="inlineStr">
+      <c r="BS8" s="33" t="inlineStr">
         <is>
           <t>{Input_145}</t>
         </is>
       </c>
-      <c r="BT8" s="25" t="n"/>
+      <c r="BT8" s="34" t="n"/>
       <c r="BV8" s="5" t="n"/>
     </row>
     <row r="9" ht="13.95" customHeight="1" s="16">
       <c r="A9" s="6" t="n"/>
       <c r="E9" s="25" t="n"/>
-      <c r="AY9" s="10" t="inlineStr">
+      <c r="AY9" s="35" t="inlineStr">
         <is>
           <t>{Input_6}</t>
         </is>
       </c>
-      <c r="AZ9" s="12" t="n"/>
-      <c r="BA9" s="10" t="inlineStr">
+      <c r="AZ9" s="41" t="n"/>
+      <c r="BA9" s="33" t="inlineStr">
         <is>
           <t>{Input_26}</t>
         </is>
       </c>
-      <c r="BB9" s="11" t="n"/>
-      <c r="BC9" s="11" t="n"/>
-      <c r="BD9" s="12" t="n"/>
-      <c r="BE9" s="10" t="inlineStr">
+      <c r="BB9" s="42" t="n"/>
+      <c r="BC9" s="42" t="n"/>
+      <c r="BD9" s="41" t="n"/>
+      <c r="BE9" s="33" t="inlineStr">
         <is>
           <t>{Input_46}</t>
         </is>
       </c>
-      <c r="BF9" s="11" t="n"/>
-      <c r="BG9" s="12" t="n"/>
-      <c r="BH9" s="10" t="inlineStr">
+      <c r="BF9" s="42" t="n"/>
+      <c r="BG9" s="41" t="n"/>
+      <c r="BH9" s="33" t="inlineStr">
         <is>
           <t>{Input_66}</t>
         </is>
       </c>
-      <c r="BI9" s="11" t="n"/>
-      <c r="BJ9" s="11" t="n"/>
-      <c r="BK9" s="11" t="n"/>
-      <c r="BL9" s="11" t="n"/>
-      <c r="BM9" s="12" t="n"/>
-      <c r="BN9" s="10" t="inlineStr">
+      <c r="BI9" s="42" t="n"/>
+      <c r="BJ9" s="42" t="n"/>
+      <c r="BK9" s="42" t="n"/>
+      <c r="BL9" s="42" t="n"/>
+      <c r="BM9" s="41" t="n"/>
+      <c r="BN9" s="33" t="inlineStr">
         <is>
           <t>{Input_86}</t>
         </is>
       </c>
-      <c r="BO9" s="10" t="inlineStr">
+      <c r="BO9" s="33" t="inlineStr">
         <is>
           <t>{Input_106}</t>
         </is>
       </c>
-      <c r="BP9" s="11" t="n"/>
-      <c r="BQ9" s="12" t="n"/>
-      <c r="BR9" s="10" t="inlineStr">
+      <c r="BP9" s="42" t="n"/>
+      <c r="BQ9" s="41" t="n"/>
+      <c r="BR9" s="33" t="inlineStr">
         <is>
           <t>{Input_126}</t>
         </is>
       </c>
-      <c r="BS9" s="10" t="inlineStr">
+      <c r="BS9" s="33" t="inlineStr">
         <is>
           <t>{Input_146}</t>
         </is>
       </c>
-      <c r="BT9" s="25" t="n"/>
+      <c r="BT9" s="34" t="n"/>
       <c r="BV9" s="5" t="n"/>
     </row>
     <row r="10" ht="13.95" customHeight="1" s="16">
       <c r="A10" s="6" t="n"/>
       <c r="E10" s="25" t="n"/>
-      <c r="AY10" s="10" t="inlineStr">
+      <c r="AY10" s="35" t="inlineStr">
         <is>
           <t>{Input_7}</t>
         </is>
       </c>
-      <c r="AZ10" s="12" t="n"/>
-      <c r="BA10" s="10" t="inlineStr">
+      <c r="AZ10" s="41" t="n"/>
+      <c r="BA10" s="33" t="inlineStr">
         <is>
           <t>{Input_27}</t>
         </is>
       </c>
-      <c r="BB10" s="11" t="n"/>
-      <c r="BC10" s="11" t="n"/>
-      <c r="BD10" s="12" t="n"/>
-      <c r="BE10" s="10" t="inlineStr">
+      <c r="BB10" s="42" t="n"/>
+      <c r="BC10" s="42" t="n"/>
+      <c r="BD10" s="41" t="n"/>
+      <c r="BE10" s="33" t="inlineStr">
         <is>
           <t>{Input_47}</t>
         </is>
       </c>
-      <c r="BF10" s="11" t="n"/>
-      <c r="BG10" s="12" t="n"/>
-      <c r="BH10" s="10" t="inlineStr">
+      <c r="BF10" s="42" t="n"/>
+      <c r="BG10" s="41" t="n"/>
+      <c r="BH10" s="33" t="inlineStr">
         <is>
           <t>{Input_67}</t>
         </is>
       </c>
-      <c r="BI10" s="11" t="n"/>
-      <c r="BJ10" s="11" t="n"/>
-      <c r="BK10" s="11" t="n"/>
-      <c r="BL10" s="11" t="n"/>
-      <c r="BM10" s="12" t="n"/>
-      <c r="BN10" s="10" t="inlineStr">
+      <c r="BI10" s="42" t="n"/>
+      <c r="BJ10" s="42" t="n"/>
+      <c r="BK10" s="42" t="n"/>
+      <c r="BL10" s="42" t="n"/>
+      <c r="BM10" s="41" t="n"/>
+      <c r="BN10" s="33" t="inlineStr">
         <is>
           <t>{Input_87}</t>
         </is>
       </c>
-      <c r="BO10" s="10" t="inlineStr">
+      <c r="BO10" s="33" t="inlineStr">
         <is>
           <t>{Input_107}</t>
         </is>
       </c>
-      <c r="BP10" s="11" t="n"/>
-      <c r="BQ10" s="12" t="n"/>
-      <c r="BR10" s="10" t="inlineStr">
+      <c r="BP10" s="42" t="n"/>
+      <c r="BQ10" s="41" t="n"/>
+      <c r="BR10" s="33" t="inlineStr">
         <is>
           <t>{Input_127}</t>
         </is>
       </c>
-      <c r="BS10" s="10" t="inlineStr">
+      <c r="BS10" s="33" t="inlineStr">
         <is>
           <t>{Input_147}</t>
         </is>
       </c>
-      <c r="BT10" s="25" t="n"/>
+      <c r="BT10" s="34" t="n"/>
       <c r="BV10" s="5" t="n"/>
     </row>
     <row r="11" ht="13.95" customHeight="1" s="16">
       <c r="A11" s="6" t="n"/>
       <c r="E11" s="25" t="n"/>
-      <c r="AY11" s="10" t="inlineStr">
+      <c r="AY11" s="35" t="inlineStr">
         <is>
           <t>{Input_8}</t>
         </is>
       </c>
-      <c r="AZ11" s="19" t="n"/>
-      <c r="BA11" s="10" t="inlineStr">
+      <c r="AZ11" s="36" t="n"/>
+      <c r="BA11" s="33" t="inlineStr">
         <is>
           <t>{Input_28}</t>
         </is>
       </c>
-      <c r="BB11" s="14" t="n"/>
-      <c r="BC11" s="14" t="n"/>
-      <c r="BD11" s="19" t="n"/>
-      <c r="BE11" s="10" t="inlineStr">
+      <c r="BB11" s="38" t="n"/>
+      <c r="BC11" s="38" t="n"/>
+      <c r="BD11" s="36" t="n"/>
+      <c r="BE11" s="33" t="inlineStr">
         <is>
           <t>{Input_48}</t>
         </is>
       </c>
-      <c r="BF11" s="14" t="n"/>
-      <c r="BG11" s="19" t="n"/>
-      <c r="BH11" s="10" t="inlineStr">
+      <c r="BF11" s="38" t="n"/>
+      <c r="BG11" s="36" t="n"/>
+      <c r="BH11" s="33" t="inlineStr">
         <is>
           <t>{Input_68}</t>
         </is>
       </c>
-      <c r="BI11" s="14" t="n"/>
-      <c r="BJ11" s="14" t="n"/>
-      <c r="BK11" s="14" t="n"/>
-      <c r="BL11" s="14" t="n"/>
-      <c r="BM11" s="19" t="n"/>
-      <c r="BN11" s="10" t="inlineStr">
+      <c r="BI11" s="38" t="n"/>
+      <c r="BJ11" s="38" t="n"/>
+      <c r="BK11" s="38" t="n"/>
+      <c r="BL11" s="38" t="n"/>
+      <c r="BM11" s="36" t="n"/>
+      <c r="BN11" s="33" t="inlineStr">
         <is>
           <t>{Input_88}</t>
         </is>
       </c>
-      <c r="BO11" s="10" t="inlineStr">
+      <c r="BO11" s="33" t="inlineStr">
         <is>
           <t>{Input_108}</t>
         </is>
       </c>
-      <c r="BP11" s="14" t="n"/>
-      <c r="BQ11" s="19" t="n"/>
-      <c r="BR11" s="10" t="inlineStr">
+      <c r="BP11" s="38" t="n"/>
+      <c r="BQ11" s="36" t="n"/>
+      <c r="BR11" s="33" t="inlineStr">
         <is>
           <t>{Input_128}</t>
         </is>
       </c>
-      <c r="BS11" s="10" t="inlineStr">
+      <c r="BS11" s="33" t="inlineStr">
         <is>
           <t>{Input_148}</t>
         </is>
       </c>
-      <c r="BT11" s="25" t="n"/>
+      <c r="BT11" s="34" t="n"/>
       <c r="BV11" s="5" t="n"/>
     </row>
     <row r="12" ht="13.95" customHeight="1" s="16">
@@ -1417,325 +1573,325 @@
       <c r="E12" s="25" t="n"/>
       <c r="AY12" s="17" t="n"/>
       <c r="AZ12" s="20" t="n"/>
-      <c r="BA12" s="17" t="n"/>
+      <c r="BA12" s="39" t="n"/>
       <c r="BB12" s="18" t="n"/>
       <c r="BC12" s="18" t="n"/>
       <c r="BD12" s="20" t="n"/>
-      <c r="BE12" s="17" t="n"/>
+      <c r="BE12" s="39" t="n"/>
       <c r="BF12" s="18" t="n"/>
       <c r="BG12" s="20" t="n"/>
-      <c r="BH12" s="17" t="n"/>
+      <c r="BH12" s="39" t="n"/>
       <c r="BI12" s="18" t="n"/>
       <c r="BJ12" s="18" t="n"/>
       <c r="BK12" s="18" t="n"/>
       <c r="BL12" s="18" t="n"/>
       <c r="BM12" s="20" t="n"/>
-      <c r="BN12" s="21" t="n"/>
-      <c r="BO12" s="17" t="n"/>
+      <c r="BN12" s="40" t="n"/>
+      <c r="BO12" s="39" t="n"/>
       <c r="BP12" s="18" t="n"/>
       <c r="BQ12" s="20" t="n"/>
-      <c r="BR12" s="21" t="n"/>
-      <c r="BS12" s="21" t="n"/>
-      <c r="BT12" s="25" t="n"/>
+      <c r="BR12" s="40" t="n"/>
+      <c r="BS12" s="40" t="n"/>
+      <c r="BT12" s="34" t="n"/>
       <c r="BV12" s="5" t="n"/>
     </row>
     <row r="13" ht="13.95" customHeight="1" s="16">
       <c r="A13" s="6" t="n"/>
       <c r="E13" s="25" t="n"/>
-      <c r="AY13" s="10" t="inlineStr">
+      <c r="AY13" s="35" t="inlineStr">
         <is>
           <t>{Input_9}</t>
         </is>
       </c>
-      <c r="AZ13" s="12" t="n"/>
-      <c r="BA13" s="10" t="inlineStr">
+      <c r="AZ13" s="41" t="n"/>
+      <c r="BA13" s="33" t="inlineStr">
         <is>
           <t>{Input_29}</t>
         </is>
       </c>
-      <c r="BB13" s="11" t="n"/>
-      <c r="BC13" s="11" t="n"/>
-      <c r="BD13" s="12" t="n"/>
-      <c r="BE13" s="10" t="inlineStr">
+      <c r="BB13" s="42" t="n"/>
+      <c r="BC13" s="42" t="n"/>
+      <c r="BD13" s="41" t="n"/>
+      <c r="BE13" s="33" t="inlineStr">
         <is>
           <t>{Input_49}</t>
         </is>
       </c>
-      <c r="BF13" s="11" t="n"/>
-      <c r="BG13" s="12" t="n"/>
-      <c r="BH13" s="10" t="inlineStr">
+      <c r="BF13" s="42" t="n"/>
+      <c r="BG13" s="41" t="n"/>
+      <c r="BH13" s="33" t="inlineStr">
         <is>
           <t>{Input_69}</t>
         </is>
       </c>
-      <c r="BI13" s="11" t="n"/>
-      <c r="BJ13" s="11" t="n"/>
-      <c r="BK13" s="11" t="n"/>
-      <c r="BL13" s="11" t="n"/>
-      <c r="BM13" s="12" t="n"/>
-      <c r="BN13" s="10" t="inlineStr">
+      <c r="BI13" s="42" t="n"/>
+      <c r="BJ13" s="42" t="n"/>
+      <c r="BK13" s="42" t="n"/>
+      <c r="BL13" s="42" t="n"/>
+      <c r="BM13" s="41" t="n"/>
+      <c r="BN13" s="33" t="inlineStr">
         <is>
           <t>{Input_89}</t>
         </is>
       </c>
-      <c r="BO13" s="10" t="inlineStr">
+      <c r="BO13" s="33" t="inlineStr">
         <is>
           <t>{Input_109}</t>
         </is>
       </c>
-      <c r="BP13" s="11" t="n"/>
-      <c r="BQ13" s="12" t="n"/>
-      <c r="BR13" s="10" t="inlineStr">
+      <c r="BP13" s="42" t="n"/>
+      <c r="BQ13" s="41" t="n"/>
+      <c r="BR13" s="33" t="inlineStr">
         <is>
           <t>{Input_129}</t>
         </is>
       </c>
-      <c r="BS13" s="10" t="inlineStr">
+      <c r="BS13" s="33" t="inlineStr">
         <is>
           <t>{Input_149}</t>
         </is>
       </c>
-      <c r="BT13" s="25" t="n"/>
+      <c r="BT13" s="34" t="n"/>
       <c r="BV13" s="5" t="n"/>
     </row>
     <row r="14" ht="13.95" customHeight="1" s="16">
       <c r="A14" s="6" t="n"/>
       <c r="E14" s="25" t="n"/>
-      <c r="AY14" s="10" t="inlineStr">
+      <c r="AY14" s="35" t="inlineStr">
         <is>
           <t>{Input_10}</t>
         </is>
       </c>
-      <c r="AZ14" s="12" t="n"/>
-      <c r="BA14" s="10" t="inlineStr">
+      <c r="AZ14" s="41" t="n"/>
+      <c r="BA14" s="33" t="inlineStr">
         <is>
           <t>{Input_30}</t>
         </is>
       </c>
-      <c r="BB14" s="11" t="n"/>
-      <c r="BC14" s="11" t="n"/>
-      <c r="BD14" s="12" t="n"/>
-      <c r="BE14" s="10" t="inlineStr">
+      <c r="BB14" s="42" t="n"/>
+      <c r="BC14" s="42" t="n"/>
+      <c r="BD14" s="41" t="n"/>
+      <c r="BE14" s="33" t="inlineStr">
         <is>
           <t>{Input_50}</t>
         </is>
       </c>
-      <c r="BF14" s="11" t="n"/>
-      <c r="BG14" s="12" t="n"/>
-      <c r="BH14" s="10" t="inlineStr">
+      <c r="BF14" s="42" t="n"/>
+      <c r="BG14" s="41" t="n"/>
+      <c r="BH14" s="33" t="inlineStr">
         <is>
           <t>{Input_70}</t>
         </is>
       </c>
-      <c r="BI14" s="11" t="n"/>
-      <c r="BJ14" s="11" t="n"/>
-      <c r="BK14" s="11" t="n"/>
-      <c r="BL14" s="11" t="n"/>
-      <c r="BM14" s="12" t="n"/>
-      <c r="BN14" s="10" t="inlineStr">
+      <c r="BI14" s="42" t="n"/>
+      <c r="BJ14" s="42" t="n"/>
+      <c r="BK14" s="42" t="n"/>
+      <c r="BL14" s="42" t="n"/>
+      <c r="BM14" s="41" t="n"/>
+      <c r="BN14" s="33" t="inlineStr">
         <is>
           <t>{Input_90}</t>
         </is>
       </c>
-      <c r="BO14" s="10" t="inlineStr">
+      <c r="BO14" s="33" t="inlineStr">
         <is>
           <t>{Input_110}</t>
         </is>
       </c>
-      <c r="BP14" s="11" t="n"/>
-      <c r="BQ14" s="12" t="n"/>
-      <c r="BR14" s="10" t="inlineStr">
+      <c r="BP14" s="42" t="n"/>
+      <c r="BQ14" s="41" t="n"/>
+      <c r="BR14" s="33" t="inlineStr">
         <is>
           <t>{Input_130}</t>
         </is>
       </c>
-      <c r="BS14" s="10" t="inlineStr">
+      <c r="BS14" s="33" t="inlineStr">
         <is>
           <t>{Input_150}</t>
         </is>
       </c>
-      <c r="BT14" s="25" t="n"/>
+      <c r="BT14" s="34" t="n"/>
       <c r="BV14" s="5" t="n"/>
     </row>
     <row r="15" ht="13.95" customHeight="1" s="16">
       <c r="A15" s="6" t="n"/>
       <c r="E15" s="25" t="n"/>
-      <c r="AY15" s="10" t="inlineStr">
+      <c r="AY15" s="35" t="inlineStr">
         <is>
           <t>{Input_11}</t>
         </is>
       </c>
-      <c r="AZ15" s="12" t="n"/>
-      <c r="BA15" s="10" t="inlineStr">
+      <c r="AZ15" s="41" t="n"/>
+      <c r="BA15" s="33" t="inlineStr">
         <is>
           <t>{Input_31}</t>
         </is>
       </c>
-      <c r="BB15" s="11" t="n"/>
-      <c r="BC15" s="11" t="n"/>
-      <c r="BD15" s="12" t="n"/>
-      <c r="BE15" s="10" t="inlineStr">
+      <c r="BB15" s="42" t="n"/>
+      <c r="BC15" s="42" t="n"/>
+      <c r="BD15" s="41" t="n"/>
+      <c r="BE15" s="33" t="inlineStr">
         <is>
           <t>{Input_51}</t>
         </is>
       </c>
-      <c r="BF15" s="11" t="n"/>
-      <c r="BG15" s="12" t="n"/>
-      <c r="BH15" s="10" t="inlineStr">
+      <c r="BF15" s="42" t="n"/>
+      <c r="BG15" s="41" t="n"/>
+      <c r="BH15" s="33" t="inlineStr">
         <is>
           <t>{Input_71}</t>
         </is>
       </c>
-      <c r="BI15" s="11" t="n"/>
-      <c r="BJ15" s="11" t="n"/>
-      <c r="BK15" s="11" t="n"/>
-      <c r="BL15" s="11" t="n"/>
-      <c r="BM15" s="12" t="n"/>
-      <c r="BN15" s="10" t="inlineStr">
+      <c r="BI15" s="42" t="n"/>
+      <c r="BJ15" s="42" t="n"/>
+      <c r="BK15" s="42" t="n"/>
+      <c r="BL15" s="42" t="n"/>
+      <c r="BM15" s="41" t="n"/>
+      <c r="BN15" s="33" t="inlineStr">
         <is>
           <t>{Input_91}</t>
         </is>
       </c>
-      <c r="BO15" s="10" t="inlineStr">
+      <c r="BO15" s="33" t="inlineStr">
         <is>
           <t>{Input_111}</t>
         </is>
       </c>
-      <c r="BP15" s="11" t="n"/>
-      <c r="BQ15" s="12" t="n"/>
-      <c r="BR15" s="10" t="inlineStr">
+      <c r="BP15" s="42" t="n"/>
+      <c r="BQ15" s="41" t="n"/>
+      <c r="BR15" s="33" t="inlineStr">
         <is>
           <t>{Input_131}</t>
         </is>
       </c>
-      <c r="BS15" s="10" t="inlineStr">
+      <c r="BS15" s="33" t="inlineStr">
         <is>
           <t>{Input_151}</t>
         </is>
       </c>
-      <c r="BT15" s="25" t="n"/>
+      <c r="BT15" s="34" t="n"/>
       <c r="BV15" s="5" t="n"/>
     </row>
     <row r="16" ht="13.95" customHeight="1" s="16">
       <c r="A16" s="6" t="n"/>
       <c r="E16" s="21" t="n"/>
-      <c r="AY16" s="10" t="inlineStr">
+      <c r="AY16" s="35" t="inlineStr">
         <is>
           <t>{Input_12}</t>
         </is>
       </c>
-      <c r="AZ16" s="12" t="n"/>
-      <c r="BA16" s="10" t="inlineStr">
+      <c r="AZ16" s="41" t="n"/>
+      <c r="BA16" s="33" t="inlineStr">
         <is>
           <t>{Input_32}</t>
         </is>
       </c>
-      <c r="BB16" s="11" t="n"/>
-      <c r="BC16" s="11" t="n"/>
-      <c r="BD16" s="12" t="n"/>
-      <c r="BE16" s="10" t="inlineStr">
+      <c r="BB16" s="42" t="n"/>
+      <c r="BC16" s="42" t="n"/>
+      <c r="BD16" s="41" t="n"/>
+      <c r="BE16" s="33" t="inlineStr">
         <is>
           <t>{Input_52}</t>
         </is>
       </c>
-      <c r="BF16" s="11" t="n"/>
-      <c r="BG16" s="12" t="n"/>
-      <c r="BH16" s="10" t="inlineStr">
+      <c r="BF16" s="42" t="n"/>
+      <c r="BG16" s="41" t="n"/>
+      <c r="BH16" s="33" t="inlineStr">
         <is>
           <t>{Input_72}</t>
         </is>
       </c>
-      <c r="BI16" s="11" t="n"/>
-      <c r="BJ16" s="11" t="n"/>
-      <c r="BK16" s="11" t="n"/>
-      <c r="BL16" s="11" t="n"/>
-      <c r="BM16" s="12" t="n"/>
-      <c r="BN16" s="10" t="inlineStr">
+      <c r="BI16" s="42" t="n"/>
+      <c r="BJ16" s="42" t="n"/>
+      <c r="BK16" s="42" t="n"/>
+      <c r="BL16" s="42" t="n"/>
+      <c r="BM16" s="41" t="n"/>
+      <c r="BN16" s="33" t="inlineStr">
         <is>
           <t>{Input_92}</t>
         </is>
       </c>
-      <c r="BO16" s="10" t="inlineStr">
+      <c r="BO16" s="33" t="inlineStr">
         <is>
           <t>{Input_112}</t>
         </is>
       </c>
-      <c r="BP16" s="11" t="n"/>
-      <c r="BQ16" s="12" t="n"/>
-      <c r="BR16" s="10" t="inlineStr">
+      <c r="BP16" s="42" t="n"/>
+      <c r="BQ16" s="41" t="n"/>
+      <c r="BR16" s="33" t="inlineStr">
         <is>
           <t>{Input_132}</t>
         </is>
       </c>
-      <c r="BS16" s="10" t="inlineStr">
+      <c r="BS16" s="33" t="inlineStr">
         <is>
           <t>{Input_152}</t>
         </is>
       </c>
-      <c r="BT16" s="21" t="n"/>
+      <c r="BT16" s="40" t="n"/>
       <c r="BV16" s="5" t="n"/>
     </row>
     <row r="17" ht="13.95" customHeight="1" s="16">
       <c r="A17" s="6" t="n"/>
-      <c r="E17" s="10" t="inlineStr">
+      <c r="E17" s="35" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="AY17" s="10" t="inlineStr">
+      <c r="AY17" s="35" t="inlineStr">
         <is>
           <t>{Input_13}</t>
         </is>
       </c>
-      <c r="AZ17" s="12" t="n"/>
-      <c r="BA17" s="10" t="inlineStr">
+      <c r="AZ17" s="41" t="n"/>
+      <c r="BA17" s="33" t="inlineStr">
         <is>
           <t>{Input_33}</t>
         </is>
       </c>
-      <c r="BB17" s="11" t="n"/>
-      <c r="BC17" s="11" t="n"/>
-      <c r="BD17" s="12" t="n"/>
-      <c r="BE17" s="10" t="inlineStr">
+      <c r="BB17" s="42" t="n"/>
+      <c r="BC17" s="42" t="n"/>
+      <c r="BD17" s="41" t="n"/>
+      <c r="BE17" s="33" t="inlineStr">
         <is>
           <t>{Input_53}</t>
         </is>
       </c>
-      <c r="BF17" s="11" t="n"/>
-      <c r="BG17" s="12" t="n"/>
-      <c r="BH17" s="10" t="inlineStr">
+      <c r="BF17" s="42" t="n"/>
+      <c r="BG17" s="41" t="n"/>
+      <c r="BH17" s="33" t="inlineStr">
         <is>
           <t>{Input_73}</t>
         </is>
       </c>
-      <c r="BI17" s="11" t="n"/>
-      <c r="BJ17" s="11" t="n"/>
-      <c r="BK17" s="11" t="n"/>
-      <c r="BL17" s="11" t="n"/>
-      <c r="BM17" s="12" t="n"/>
-      <c r="BN17" s="10" t="inlineStr">
+      <c r="BI17" s="42" t="n"/>
+      <c r="BJ17" s="42" t="n"/>
+      <c r="BK17" s="42" t="n"/>
+      <c r="BL17" s="42" t="n"/>
+      <c r="BM17" s="41" t="n"/>
+      <c r="BN17" s="33" t="inlineStr">
         <is>
           <t>{Input_93}</t>
         </is>
       </c>
-      <c r="BO17" s="10" t="inlineStr">
+      <c r="BO17" s="33" t="inlineStr">
         <is>
           <t>{Input_113}</t>
         </is>
       </c>
-      <c r="BP17" s="11" t="n"/>
-      <c r="BQ17" s="12" t="n"/>
-      <c r="BR17" s="10" t="inlineStr">
+      <c r="BP17" s="42" t="n"/>
+      <c r="BQ17" s="41" t="n"/>
+      <c r="BR17" s="33" t="inlineStr">
         <is>
           <t>{Input_133}</t>
         </is>
       </c>
-      <c r="BS17" s="10" t="inlineStr">
+      <c r="BS17" s="33" t="inlineStr">
         <is>
           <t>{Input_153}</t>
         </is>
       </c>
-      <c r="BT17" s="10" t="inlineStr">
+      <c r="BT17" s="33" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -1755,532 +1911,532 @@
           <t>{View_2}</t>
         </is>
       </c>
-      <c r="AY18" s="10" t="inlineStr">
+      <c r="AY18" s="35" t="inlineStr">
         <is>
           <t>{Input_14}</t>
         </is>
       </c>
-      <c r="AZ18" s="12" t="n"/>
-      <c r="BA18" s="10" t="inlineStr">
+      <c r="AZ18" s="41" t="n"/>
+      <c r="BA18" s="33" t="inlineStr">
         <is>
           <t>{Input_34}</t>
         </is>
       </c>
-      <c r="BB18" s="11" t="n"/>
-      <c r="BC18" s="11" t="n"/>
-      <c r="BD18" s="12" t="n"/>
-      <c r="BE18" s="10" t="inlineStr">
+      <c r="BB18" s="42" t="n"/>
+      <c r="BC18" s="42" t="n"/>
+      <c r="BD18" s="41" t="n"/>
+      <c r="BE18" s="33" t="inlineStr">
         <is>
           <t>{Input_54}</t>
         </is>
       </c>
-      <c r="BF18" s="11" t="n"/>
-      <c r="BG18" s="12" t="n"/>
-      <c r="BH18" s="10" t="inlineStr">
+      <c r="BF18" s="42" t="n"/>
+      <c r="BG18" s="41" t="n"/>
+      <c r="BH18" s="33" t="inlineStr">
         <is>
           <t>{Input_74}</t>
         </is>
       </c>
-      <c r="BI18" s="11" t="n"/>
-      <c r="BJ18" s="11" t="n"/>
-      <c r="BK18" s="11" t="n"/>
-      <c r="BL18" s="11" t="n"/>
-      <c r="BM18" s="12" t="n"/>
-      <c r="BN18" s="10" t="inlineStr">
+      <c r="BI18" s="42" t="n"/>
+      <c r="BJ18" s="42" t="n"/>
+      <c r="BK18" s="42" t="n"/>
+      <c r="BL18" s="42" t="n"/>
+      <c r="BM18" s="41" t="n"/>
+      <c r="BN18" s="33" t="inlineStr">
         <is>
           <t>{Input_94}</t>
         </is>
       </c>
-      <c r="BO18" s="10" t="inlineStr">
+      <c r="BO18" s="33" t="inlineStr">
         <is>
           <t>{Input_114}</t>
         </is>
       </c>
-      <c r="BP18" s="11" t="n"/>
-      <c r="BQ18" s="12" t="n"/>
-      <c r="BR18" s="10" t="inlineStr">
+      <c r="BP18" s="42" t="n"/>
+      <c r="BQ18" s="41" t="n"/>
+      <c r="BR18" s="33" t="inlineStr">
         <is>
           <t>{Input_134}</t>
         </is>
       </c>
-      <c r="BS18" s="10" t="inlineStr">
+      <c r="BS18" s="33" t="inlineStr">
         <is>
           <t>{Input_154}</t>
         </is>
       </c>
-      <c r="BT18" s="25" t="n"/>
+      <c r="BT18" s="34" t="n"/>
       <c r="BV18" s="5" t="n"/>
     </row>
     <row r="19" ht="13.95" customHeight="1" s="16">
       <c r="A19" s="6" t="n"/>
       <c r="E19" s="25" t="n"/>
-      <c r="AY19" s="10" t="inlineStr">
+      <c r="AY19" s="35" t="inlineStr">
         <is>
           <t>{Input_15}</t>
         </is>
       </c>
-      <c r="AZ19" s="12" t="n"/>
-      <c r="BA19" s="10" t="inlineStr">
+      <c r="AZ19" s="41" t="n"/>
+      <c r="BA19" s="33" t="inlineStr">
         <is>
           <t>{Input_35}</t>
         </is>
       </c>
-      <c r="BB19" s="11" t="n"/>
-      <c r="BC19" s="11" t="n"/>
-      <c r="BD19" s="12" t="n"/>
-      <c r="BE19" s="10" t="inlineStr">
+      <c r="BB19" s="42" t="n"/>
+      <c r="BC19" s="42" t="n"/>
+      <c r="BD19" s="41" t="n"/>
+      <c r="BE19" s="33" t="inlineStr">
         <is>
           <t>{Input_55}</t>
         </is>
       </c>
-      <c r="BF19" s="11" t="n"/>
-      <c r="BG19" s="12" t="n"/>
-      <c r="BH19" s="10" t="inlineStr">
+      <c r="BF19" s="42" t="n"/>
+      <c r="BG19" s="41" t="n"/>
+      <c r="BH19" s="33" t="inlineStr">
         <is>
           <t>{Input_75}</t>
         </is>
       </c>
-      <c r="BI19" s="11" t="n"/>
-      <c r="BJ19" s="11" t="n"/>
-      <c r="BK19" s="11" t="n"/>
-      <c r="BL19" s="11" t="n"/>
-      <c r="BM19" s="12" t="n"/>
-      <c r="BN19" s="10" t="inlineStr">
+      <c r="BI19" s="42" t="n"/>
+      <c r="BJ19" s="42" t="n"/>
+      <c r="BK19" s="42" t="n"/>
+      <c r="BL19" s="42" t="n"/>
+      <c r="BM19" s="41" t="n"/>
+      <c r="BN19" s="33" t="inlineStr">
         <is>
           <t>{Input_95}</t>
         </is>
       </c>
-      <c r="BO19" s="10" t="inlineStr">
+      <c r="BO19" s="33" t="inlineStr">
         <is>
           <t>{Input_115}</t>
         </is>
       </c>
-      <c r="BP19" s="11" t="n"/>
-      <c r="BQ19" s="12" t="n"/>
-      <c r="BR19" s="10" t="inlineStr">
+      <c r="BP19" s="42" t="n"/>
+      <c r="BQ19" s="41" t="n"/>
+      <c r="BR19" s="33" t="inlineStr">
         <is>
           <t>{Input_135}</t>
         </is>
       </c>
-      <c r="BS19" s="10" t="inlineStr">
+      <c r="BS19" s="33" t="inlineStr">
         <is>
           <t>{Input_155}</t>
         </is>
       </c>
-      <c r="BT19" s="25" t="n"/>
+      <c r="BT19" s="34" t="n"/>
       <c r="BV19" s="5" t="n"/>
     </row>
     <row r="20" ht="13.95" customHeight="1" s="16">
       <c r="A20" s="6" t="n"/>
       <c r="E20" s="25" t="n"/>
-      <c r="AY20" s="10" t="inlineStr">
+      <c r="AY20" s="35" t="inlineStr">
         <is>
           <t>{Input_16}</t>
         </is>
       </c>
-      <c r="AZ20" s="12" t="n"/>
-      <c r="BA20" s="10" t="inlineStr">
+      <c r="AZ20" s="41" t="n"/>
+      <c r="BA20" s="33" t="inlineStr">
         <is>
           <t>{Input_36}</t>
         </is>
       </c>
-      <c r="BB20" s="11" t="n"/>
-      <c r="BC20" s="11" t="n"/>
-      <c r="BD20" s="12" t="n"/>
-      <c r="BE20" s="10" t="inlineStr">
+      <c r="BB20" s="42" t="n"/>
+      <c r="BC20" s="42" t="n"/>
+      <c r="BD20" s="41" t="n"/>
+      <c r="BE20" s="33" t="inlineStr">
         <is>
           <t>{Input_56}</t>
         </is>
       </c>
-      <c r="BF20" s="11" t="n"/>
-      <c r="BG20" s="12" t="n"/>
-      <c r="BH20" s="10" t="inlineStr">
+      <c r="BF20" s="42" t="n"/>
+      <c r="BG20" s="41" t="n"/>
+      <c r="BH20" s="33" t="inlineStr">
         <is>
           <t>{Input_76}</t>
         </is>
       </c>
-      <c r="BI20" s="11" t="n"/>
-      <c r="BJ20" s="11" t="n"/>
-      <c r="BK20" s="11" t="n"/>
-      <c r="BL20" s="11" t="n"/>
-      <c r="BM20" s="12" t="n"/>
-      <c r="BN20" s="10" t="inlineStr">
+      <c r="BI20" s="42" t="n"/>
+      <c r="BJ20" s="42" t="n"/>
+      <c r="BK20" s="42" t="n"/>
+      <c r="BL20" s="42" t="n"/>
+      <c r="BM20" s="41" t="n"/>
+      <c r="BN20" s="33" t="inlineStr">
         <is>
           <t>{Input_96}</t>
         </is>
       </c>
-      <c r="BO20" s="10" t="inlineStr">
+      <c r="BO20" s="33" t="inlineStr">
         <is>
           <t>{Input_116}</t>
         </is>
       </c>
-      <c r="BP20" s="11" t="n"/>
-      <c r="BQ20" s="12" t="n"/>
-      <c r="BR20" s="10" t="inlineStr">
+      <c r="BP20" s="42" t="n"/>
+      <c r="BQ20" s="41" t="n"/>
+      <c r="BR20" s="33" t="inlineStr">
         <is>
           <t>{Input_136}</t>
         </is>
       </c>
-      <c r="BS20" s="10" t="inlineStr">
+      <c r="BS20" s="33" t="inlineStr">
         <is>
           <t>{Input_156}</t>
         </is>
       </c>
-      <c r="BT20" s="25" t="n"/>
+      <c r="BT20" s="34" t="n"/>
       <c r="BV20" s="5" t="n"/>
     </row>
     <row r="21" ht="13.95" customHeight="1" s="16">
       <c r="A21" s="6" t="n"/>
       <c r="E21" s="25" t="n"/>
-      <c r="AY21" s="10" t="inlineStr">
+      <c r="AY21" s="35" t="inlineStr">
         <is>
           <t>{Input_17}</t>
         </is>
       </c>
-      <c r="AZ21" s="12" t="n"/>
-      <c r="BA21" s="10" t="inlineStr">
+      <c r="AZ21" s="41" t="n"/>
+      <c r="BA21" s="33" t="inlineStr">
         <is>
           <t>{Input_37}</t>
         </is>
       </c>
-      <c r="BB21" s="11" t="n"/>
-      <c r="BC21" s="11" t="n"/>
-      <c r="BD21" s="12" t="n"/>
-      <c r="BE21" s="10" t="inlineStr">
+      <c r="BB21" s="42" t="n"/>
+      <c r="BC21" s="42" t="n"/>
+      <c r="BD21" s="41" t="n"/>
+      <c r="BE21" s="33" t="inlineStr">
         <is>
           <t>{Input_57}</t>
         </is>
       </c>
-      <c r="BF21" s="11" t="n"/>
-      <c r="BG21" s="12" t="n"/>
-      <c r="BH21" s="10" t="inlineStr">
+      <c r="BF21" s="42" t="n"/>
+      <c r="BG21" s="41" t="n"/>
+      <c r="BH21" s="33" t="inlineStr">
         <is>
           <t>{Input_77}</t>
         </is>
       </c>
-      <c r="BI21" s="11" t="n"/>
-      <c r="BJ21" s="11" t="n"/>
-      <c r="BK21" s="11" t="n"/>
-      <c r="BL21" s="11" t="n"/>
-      <c r="BM21" s="12" t="n"/>
-      <c r="BN21" s="10" t="inlineStr">
+      <c r="BI21" s="42" t="n"/>
+      <c r="BJ21" s="42" t="n"/>
+      <c r="BK21" s="42" t="n"/>
+      <c r="BL21" s="42" t="n"/>
+      <c r="BM21" s="41" t="n"/>
+      <c r="BN21" s="33" t="inlineStr">
         <is>
           <t>{Input_97}</t>
         </is>
       </c>
-      <c r="BO21" s="10" t="inlineStr">
+      <c r="BO21" s="33" t="inlineStr">
         <is>
           <t>{Input_117}</t>
         </is>
       </c>
-      <c r="BP21" s="11" t="n"/>
-      <c r="BQ21" s="12" t="n"/>
-      <c r="BR21" s="10" t="inlineStr">
+      <c r="BP21" s="42" t="n"/>
+      <c r="BQ21" s="41" t="n"/>
+      <c r="BR21" s="33" t="inlineStr">
         <is>
           <t>{Input_137}</t>
         </is>
       </c>
-      <c r="BS21" s="10" t="inlineStr">
+      <c r="BS21" s="33" t="inlineStr">
         <is>
           <t>{Input_157}</t>
         </is>
       </c>
-      <c r="BT21" s="25" t="n"/>
+      <c r="BT21" s="34" t="n"/>
       <c r="BV21" s="5" t="n"/>
     </row>
     <row r="22" ht="13.95" customHeight="1" s="16">
       <c r="A22" s="6" t="n"/>
       <c r="E22" s="25" t="n"/>
-      <c r="AY22" s="10" t="inlineStr">
+      <c r="AY22" s="35" t="inlineStr">
         <is>
           <t>{Input_18}</t>
         </is>
       </c>
-      <c r="AZ22" s="12" t="n"/>
-      <c r="BA22" s="10" t="inlineStr">
+      <c r="AZ22" s="41" t="n"/>
+      <c r="BA22" s="33" t="inlineStr">
         <is>
           <t>{Input_38}</t>
         </is>
       </c>
-      <c r="BB22" s="11" t="n"/>
-      <c r="BC22" s="11" t="n"/>
-      <c r="BD22" s="12" t="n"/>
-      <c r="BE22" s="10" t="inlineStr">
+      <c r="BB22" s="42" t="n"/>
+      <c r="BC22" s="42" t="n"/>
+      <c r="BD22" s="41" t="n"/>
+      <c r="BE22" s="33" t="inlineStr">
         <is>
           <t>{Input_58}</t>
         </is>
       </c>
-      <c r="BF22" s="11" t="n"/>
-      <c r="BG22" s="12" t="n"/>
-      <c r="BH22" s="10" t="inlineStr">
+      <c r="BF22" s="42" t="n"/>
+      <c r="BG22" s="41" t="n"/>
+      <c r="BH22" s="33" t="inlineStr">
         <is>
           <t>{Input_78}</t>
         </is>
       </c>
-      <c r="BI22" s="11" t="n"/>
-      <c r="BJ22" s="11" t="n"/>
-      <c r="BK22" s="11" t="n"/>
-      <c r="BL22" s="11" t="n"/>
-      <c r="BM22" s="12" t="n"/>
-      <c r="BN22" s="10" t="inlineStr">
+      <c r="BI22" s="42" t="n"/>
+      <c r="BJ22" s="42" t="n"/>
+      <c r="BK22" s="42" t="n"/>
+      <c r="BL22" s="42" t="n"/>
+      <c r="BM22" s="41" t="n"/>
+      <c r="BN22" s="33" t="inlineStr">
         <is>
           <t>{Input_98}</t>
         </is>
       </c>
-      <c r="BO22" s="10" t="inlineStr">
+      <c r="BO22" s="33" t="inlineStr">
         <is>
           <t>{Input_118}</t>
         </is>
       </c>
-      <c r="BP22" s="11" t="n"/>
-      <c r="BQ22" s="12" t="n"/>
-      <c r="BR22" s="10" t="inlineStr">
+      <c r="BP22" s="42" t="n"/>
+      <c r="BQ22" s="41" t="n"/>
+      <c r="BR22" s="33" t="inlineStr">
         <is>
           <t>{Input_138}</t>
         </is>
       </c>
-      <c r="BS22" s="10" t="inlineStr">
+      <c r="BS22" s="33" t="inlineStr">
         <is>
           <t>{Input_158}</t>
         </is>
       </c>
-      <c r="BT22" s="25" t="n"/>
+      <c r="BT22" s="34" t="n"/>
       <c r="BV22" s="5" t="n"/>
     </row>
     <row r="23" ht="13.95" customHeight="1" s="16">
       <c r="A23" s="6" t="n"/>
       <c r="E23" s="25" t="n"/>
-      <c r="AY23" s="10" t="inlineStr">
+      <c r="AY23" s="35" t="inlineStr">
         <is>
           <t>{Input_19}</t>
         </is>
       </c>
-      <c r="AZ23" s="12" t="n"/>
-      <c r="BA23" s="10" t="inlineStr">
+      <c r="AZ23" s="41" t="n"/>
+      <c r="BA23" s="33" t="inlineStr">
         <is>
           <t>{Input_39}</t>
         </is>
       </c>
-      <c r="BB23" s="11" t="n"/>
-      <c r="BC23" s="11" t="n"/>
-      <c r="BD23" s="12" t="n"/>
-      <c r="BE23" s="10" t="inlineStr">
+      <c r="BB23" s="42" t="n"/>
+      <c r="BC23" s="42" t="n"/>
+      <c r="BD23" s="41" t="n"/>
+      <c r="BE23" s="33" t="inlineStr">
         <is>
           <t>{Input_59}</t>
         </is>
       </c>
-      <c r="BF23" s="11" t="n"/>
-      <c r="BG23" s="12" t="n"/>
-      <c r="BH23" s="10" t="inlineStr">
+      <c r="BF23" s="42" t="n"/>
+      <c r="BG23" s="41" t="n"/>
+      <c r="BH23" s="33" t="inlineStr">
         <is>
           <t>{Input_79}</t>
         </is>
       </c>
-      <c r="BI23" s="11" t="n"/>
-      <c r="BJ23" s="11" t="n"/>
-      <c r="BK23" s="11" t="n"/>
-      <c r="BL23" s="11" t="n"/>
-      <c r="BM23" s="12" t="n"/>
-      <c r="BN23" s="10" t="inlineStr">
+      <c r="BI23" s="42" t="n"/>
+      <c r="BJ23" s="42" t="n"/>
+      <c r="BK23" s="42" t="n"/>
+      <c r="BL23" s="42" t="n"/>
+      <c r="BM23" s="41" t="n"/>
+      <c r="BN23" s="33" t="inlineStr">
         <is>
           <t>{Input_99}</t>
         </is>
       </c>
-      <c r="BO23" s="10" t="inlineStr">
+      <c r="BO23" s="33" t="inlineStr">
         <is>
           <t>{Input_119}</t>
         </is>
       </c>
-      <c r="BP23" s="11" t="n"/>
-      <c r="BQ23" s="12" t="n"/>
-      <c r="BR23" s="10" t="inlineStr">
+      <c r="BP23" s="42" t="n"/>
+      <c r="BQ23" s="41" t="n"/>
+      <c r="BR23" s="33" t="inlineStr">
         <is>
           <t>{Input_139}</t>
         </is>
       </c>
-      <c r="BS23" s="10" t="inlineStr">
+      <c r="BS23" s="33" t="inlineStr">
         <is>
           <t>{Input_159}</t>
         </is>
       </c>
-      <c r="BT23" s="25" t="n"/>
+      <c r="BT23" s="34" t="n"/>
       <c r="BV23" s="5" t="n"/>
     </row>
     <row r="24" ht="13.95" customHeight="1" s="16">
       <c r="A24" s="6" t="n"/>
       <c r="E24" s="25" t="n"/>
-      <c r="AY24" s="10" t="inlineStr">
+      <c r="AY24" s="35" t="inlineStr">
         <is>
           <t>{Input_20}</t>
         </is>
       </c>
-      <c r="AZ24" s="12" t="n"/>
-      <c r="BA24" s="10" t="inlineStr">
+      <c r="AZ24" s="41" t="n"/>
+      <c r="BA24" s="33" t="inlineStr">
         <is>
           <t>{Input_40}</t>
         </is>
       </c>
-      <c r="BB24" s="11" t="n"/>
-      <c r="BC24" s="11" t="n"/>
-      <c r="BD24" s="12" t="n"/>
-      <c r="BE24" s="10" t="inlineStr">
+      <c r="BB24" s="42" t="n"/>
+      <c r="BC24" s="42" t="n"/>
+      <c r="BD24" s="41" t="n"/>
+      <c r="BE24" s="33" t="inlineStr">
         <is>
           <t>{Input_60}</t>
         </is>
       </c>
-      <c r="BF24" s="11" t="n"/>
-      <c r="BG24" s="12" t="n"/>
-      <c r="BH24" s="10" t="inlineStr">
+      <c r="BF24" s="42" t="n"/>
+      <c r="BG24" s="41" t="n"/>
+      <c r="BH24" s="33" t="inlineStr">
         <is>
           <t>{Input_80}</t>
         </is>
       </c>
-      <c r="BI24" s="11" t="n"/>
-      <c r="BJ24" s="11" t="n"/>
-      <c r="BK24" s="11" t="n"/>
-      <c r="BL24" s="11" t="n"/>
-      <c r="BM24" s="12" t="n"/>
-      <c r="BN24" s="10" t="inlineStr">
+      <c r="BI24" s="42" t="n"/>
+      <c r="BJ24" s="42" t="n"/>
+      <c r="BK24" s="42" t="n"/>
+      <c r="BL24" s="42" t="n"/>
+      <c r="BM24" s="41" t="n"/>
+      <c r="BN24" s="33" t="inlineStr">
         <is>
           <t>{Input_100}</t>
         </is>
       </c>
-      <c r="BO24" s="10" t="inlineStr">
+      <c r="BO24" s="33" t="inlineStr">
         <is>
           <t>{Input_120}</t>
         </is>
       </c>
-      <c r="BP24" s="11" t="n"/>
-      <c r="BQ24" s="12" t="n"/>
-      <c r="BR24" s="10" t="inlineStr">
+      <c r="BP24" s="42" t="n"/>
+      <c r="BQ24" s="41" t="n"/>
+      <c r="BR24" s="33" t="inlineStr">
         <is>
           <t>{Input_140}</t>
         </is>
       </c>
-      <c r="BS24" s="10" t="inlineStr">
+      <c r="BS24" s="33" t="inlineStr">
         <is>
           <t>{Input_160}</t>
         </is>
       </c>
-      <c r="BT24" s="25" t="n"/>
+      <c r="BT24" s="34" t="n"/>
       <c r="BV24" s="5" t="n"/>
     </row>
     <row r="25" ht="13.95" customHeight="1" s="16">
       <c r="A25" s="6" t="n"/>
       <c r="E25" s="25" t="n"/>
-      <c r="AY25" s="10" t="inlineStr">
+      <c r="AY25" s="35" t="inlineStr">
         <is>
           <t>{Input_21}</t>
         </is>
       </c>
-      <c r="AZ25" s="12" t="n"/>
-      <c r="BA25" s="10" t="inlineStr">
+      <c r="AZ25" s="41" t="n"/>
+      <c r="BA25" s="33" t="inlineStr">
         <is>
           <t>{Input_41}</t>
         </is>
       </c>
-      <c r="BB25" s="11" t="n"/>
-      <c r="BC25" s="11" t="n"/>
-      <c r="BD25" s="12" t="n"/>
-      <c r="BE25" s="10" t="inlineStr">
+      <c r="BB25" s="42" t="n"/>
+      <c r="BC25" s="42" t="n"/>
+      <c r="BD25" s="41" t="n"/>
+      <c r="BE25" s="33" t="inlineStr">
         <is>
           <t>{Input_61}</t>
         </is>
       </c>
-      <c r="BF25" s="11" t="n"/>
-      <c r="BG25" s="12" t="n"/>
-      <c r="BH25" s="10" t="inlineStr">
+      <c r="BF25" s="42" t="n"/>
+      <c r="BG25" s="41" t="n"/>
+      <c r="BH25" s="33" t="inlineStr">
         <is>
           <t>{Input_81}</t>
         </is>
       </c>
-      <c r="BI25" s="11" t="n"/>
-      <c r="BJ25" s="11" t="n"/>
-      <c r="BK25" s="11" t="n"/>
-      <c r="BL25" s="11" t="n"/>
-      <c r="BM25" s="12" t="n"/>
-      <c r="BN25" s="10" t="inlineStr">
+      <c r="BI25" s="42" t="n"/>
+      <c r="BJ25" s="42" t="n"/>
+      <c r="BK25" s="42" t="n"/>
+      <c r="BL25" s="42" t="n"/>
+      <c r="BM25" s="41" t="n"/>
+      <c r="BN25" s="33" t="inlineStr">
         <is>
           <t>{Input_101}</t>
         </is>
       </c>
-      <c r="BO25" s="10" t="inlineStr">
+      <c r="BO25" s="33" t="inlineStr">
         <is>
           <t>{Input_121}</t>
         </is>
       </c>
-      <c r="BP25" s="11" t="n"/>
-      <c r="BQ25" s="12" t="n"/>
-      <c r="BR25" s="10" t="inlineStr">
+      <c r="BP25" s="42" t="n"/>
+      <c r="BQ25" s="41" t="n"/>
+      <c r="BR25" s="33" t="inlineStr">
         <is>
           <t>{Input_141}</t>
         </is>
       </c>
-      <c r="BS25" s="10" t="inlineStr">
+      <c r="BS25" s="33" t="inlineStr">
         <is>
           <t>{Input_161}</t>
         </is>
       </c>
-      <c r="BT25" s="25" t="n"/>
+      <c r="BT25" s="34" t="n"/>
       <c r="BV25" s="5" t="n"/>
     </row>
     <row r="26" ht="13.95" customHeight="1" s="16">
       <c r="A26" s="6" t="n"/>
       <c r="E26" s="25" t="n"/>
-      <c r="AY26" s="10" t="inlineStr">
+      <c r="AY26" s="35" t="inlineStr">
         <is>
           <t>{Input_22}</t>
         </is>
       </c>
-      <c r="AZ26" s="12" t="n"/>
-      <c r="BA26" s="10" t="inlineStr">
+      <c r="AZ26" s="41" t="n"/>
+      <c r="BA26" s="33" t="inlineStr">
         <is>
           <t>{Input_42}</t>
         </is>
       </c>
-      <c r="BB26" s="11" t="n"/>
-      <c r="BC26" s="11" t="n"/>
-      <c r="BD26" s="12" t="n"/>
-      <c r="BE26" s="10" t="inlineStr">
+      <c r="BB26" s="42" t="n"/>
+      <c r="BC26" s="42" t="n"/>
+      <c r="BD26" s="41" t="n"/>
+      <c r="BE26" s="33" t="inlineStr">
         <is>
           <t>{Input_62}</t>
         </is>
       </c>
-      <c r="BF26" s="11" t="n"/>
-      <c r="BG26" s="12" t="n"/>
-      <c r="BH26" s="10" t="inlineStr">
+      <c r="BF26" s="42" t="n"/>
+      <c r="BG26" s="41" t="n"/>
+      <c r="BH26" s="33" t="inlineStr">
         <is>
           <t>{Input_82}</t>
         </is>
       </c>
-      <c r="BI26" s="11" t="n"/>
-      <c r="BJ26" s="11" t="n"/>
-      <c r="BK26" s="11" t="n"/>
-      <c r="BL26" s="11" t="n"/>
-      <c r="BM26" s="12" t="n"/>
-      <c r="BN26" s="10" t="inlineStr">
+      <c r="BI26" s="42" t="n"/>
+      <c r="BJ26" s="42" t="n"/>
+      <c r="BK26" s="42" t="n"/>
+      <c r="BL26" s="42" t="n"/>
+      <c r="BM26" s="41" t="n"/>
+      <c r="BN26" s="33" t="inlineStr">
         <is>
           <t>{Input_102}</t>
         </is>
       </c>
-      <c r="BO26" s="10" t="inlineStr">
+      <c r="BO26" s="33" t="inlineStr">
         <is>
           <t>{Input_122}</t>
         </is>
       </c>
-      <c r="BP26" s="11" t="n"/>
-      <c r="BQ26" s="12" t="n"/>
-      <c r="BR26" s="10" t="inlineStr">
+      <c r="BP26" s="42" t="n"/>
+      <c r="BQ26" s="41" t="n"/>
+      <c r="BR26" s="33" t="inlineStr">
         <is>
           <t>{Input_142}</t>
         </is>
       </c>
-      <c r="BS26" s="10" t="inlineStr">
+      <c r="BS26" s="33" t="inlineStr">
         <is>
           <t>{Input_162}</t>
         </is>
       </c>
-      <c r="BT26" s="25" t="n"/>
+      <c r="BT26" s="34" t="n"/>
       <c r="BV26" s="5" t="n"/>
     </row>
     <row r="27" ht="13.95" customHeight="1" s="16">
@@ -2296,60 +2452,60 @@
           <t>{View_3}</t>
         </is>
       </c>
-      <c r="AY27" s="10" t="inlineStr">
+      <c r="AY27" s="35" t="inlineStr">
         <is>
           <t>{Input_23}</t>
         </is>
       </c>
-      <c r="AZ27" s="12" t="n"/>
-      <c r="BA27" s="10" t="inlineStr">
+      <c r="AZ27" s="41" t="n"/>
+      <c r="BA27" s="33" t="inlineStr">
         <is>
           <t>{Input_43}</t>
         </is>
       </c>
-      <c r="BB27" s="11" t="n"/>
-      <c r="BC27" s="11" t="n"/>
-      <c r="BD27" s="12" t="n"/>
-      <c r="BE27" s="10" t="inlineStr">
+      <c r="BB27" s="42" t="n"/>
+      <c r="BC27" s="42" t="n"/>
+      <c r="BD27" s="41" t="n"/>
+      <c r="BE27" s="33" t="inlineStr">
         <is>
           <t>{Input_63}</t>
         </is>
       </c>
-      <c r="BF27" s="11" t="n"/>
-      <c r="BG27" s="12" t="n"/>
-      <c r="BH27" s="10" t="inlineStr">
+      <c r="BF27" s="42" t="n"/>
+      <c r="BG27" s="41" t="n"/>
+      <c r="BH27" s="33" t="inlineStr">
         <is>
           <t>{Input_83}</t>
         </is>
       </c>
-      <c r="BI27" s="11" t="n"/>
-      <c r="BJ27" s="11" t="n"/>
-      <c r="BK27" s="11" t="n"/>
-      <c r="BL27" s="11" t="n"/>
-      <c r="BM27" s="12" t="n"/>
-      <c r="BN27" s="10" t="inlineStr">
+      <c r="BI27" s="42" t="n"/>
+      <c r="BJ27" s="42" t="n"/>
+      <c r="BK27" s="42" t="n"/>
+      <c r="BL27" s="42" t="n"/>
+      <c r="BM27" s="41" t="n"/>
+      <c r="BN27" s="33" t="inlineStr">
         <is>
           <t>{Input_103}</t>
         </is>
       </c>
-      <c r="BO27" s="10" t="inlineStr">
+      <c r="BO27" s="33" t="inlineStr">
         <is>
           <t>{Input_123}</t>
         </is>
       </c>
-      <c r="BP27" s="11" t="n"/>
-      <c r="BQ27" s="12" t="n"/>
-      <c r="BR27" s="10" t="inlineStr">
+      <c r="BP27" s="42" t="n"/>
+      <c r="BQ27" s="41" t="n"/>
+      <c r="BR27" s="33" t="inlineStr">
         <is>
           <t>{Input_143}</t>
         </is>
       </c>
-      <c r="BS27" s="10" t="inlineStr">
+      <c r="BS27" s="33" t="inlineStr">
         <is>
           <t>{Input_163}</t>
         </is>
       </c>
-      <c r="BT27" s="25" t="n"/>
+      <c r="BT27" s="34" t="n"/>
       <c r="BV27" s="5" t="n"/>
     </row>
     <row r="28" ht="13.95" customHeight="1" s="16">
@@ -2360,12 +2516,12 @@
     </row>
     <row r="29" ht="13.95" customHeight="1" s="16">
       <c r="A29" s="6" t="n"/>
-      <c r="E29" s="10" t="inlineStr">
+      <c r="E29" s="35" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="BT29" s="10" t="inlineStr">
+      <c r="BT29" s="35" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -2404,7 +2560,7 @@
       <c r="BQ30" s="14" t="n"/>
       <c r="BR30" s="14" t="n"/>
       <c r="BS30" s="19" t="n"/>
-      <c r="BT30" s="25" t="n"/>
+      <c r="BT30" s="34" t="n"/>
       <c r="BV30" s="5" t="n"/>
     </row>
     <row r="31" ht="13.95" customHeight="1" s="16">
@@ -2412,7 +2568,7 @@
       <c r="E31" s="25" t="n"/>
       <c r="AY31" s="15" t="n"/>
       <c r="BS31" s="23" t="n"/>
-      <c r="BT31" s="25" t="n"/>
+      <c r="BT31" s="34" t="n"/>
       <c r="BV31" s="5" t="n"/>
     </row>
     <row r="32" ht="13.95" customHeight="1" s="16">
@@ -2420,7 +2576,7 @@
       <c r="E32" s="25" t="n"/>
       <c r="AY32" s="15" t="n"/>
       <c r="BS32" s="23" t="n"/>
-      <c r="BT32" s="25" t="n"/>
+      <c r="BT32" s="34" t="n"/>
       <c r="BV32" s="5" t="n"/>
     </row>
     <row r="33" ht="13.95" customHeight="1" s="16">
@@ -2428,7 +2584,7 @@
       <c r="E33" s="25" t="n"/>
       <c r="AY33" s="15" t="n"/>
       <c r="BS33" s="23" t="n"/>
-      <c r="BT33" s="25" t="n"/>
+      <c r="BT33" s="34" t="n"/>
       <c r="BV33" s="5" t="n"/>
     </row>
     <row r="34" ht="13.95" customHeight="1" s="16">
@@ -2455,7 +2611,7 @@
       <c r="BQ34" s="18" t="n"/>
       <c r="BR34" s="18" t="n"/>
       <c r="BS34" s="20" t="n"/>
-      <c r="BT34" s="25" t="n"/>
+      <c r="BT34" s="34" t="n"/>
       <c r="BV34" s="5" t="n"/>
     </row>
     <row r="35" ht="13.95" customHeight="1" s="16">
@@ -2488,14 +2644,14 @@
           <t>{Input_170}</t>
         </is>
       </c>
-      <c r="AZ37" s="10" t="inlineStr">
+      <c r="AZ37" s="32" t="inlineStr">
         <is>
           <t>{Input_171}</t>
         </is>
       </c>
       <c r="BA37" s="11" t="n"/>
       <c r="BB37" s="12" t="n"/>
-      <c r="BC37" s="10" t="inlineStr">
+      <c r="BC37" s="32" t="inlineStr">
         <is>
           <t>{Input_172}</t>
         </is>
@@ -2507,246 +2663,246 @@
       <c r="BH37" s="11" t="n"/>
       <c r="BI37" s="11" t="n"/>
       <c r="BJ37" s="12" t="n"/>
-      <c r="BK37" s="10" t="inlineStr">
+      <c r="BK37" s="32" t="inlineStr">
         <is>
           <t>{Input_173}</t>
         </is>
       </c>
       <c r="BL37" s="11" t="n"/>
       <c r="BM37" s="12" t="n"/>
-      <c r="BN37" s="10" t="inlineStr">
+      <c r="BN37" s="32" t="inlineStr">
         <is>
           <t>{Input_174}</t>
         </is>
       </c>
       <c r="BO37" s="11" t="n"/>
       <c r="BP37" s="12" t="n"/>
-      <c r="BQ37" s="10" t="inlineStr">
+      <c r="BQ37" s="32" t="inlineStr">
         <is>
           <t>{Input_175}</t>
         </is>
       </c>
       <c r="BR37" s="11" t="n"/>
       <c r="BS37" s="12" t="n"/>
-      <c r="BT37" s="25" t="n"/>
+      <c r="BT37" s="34" t="n"/>
       <c r="BV37" s="5" t="n"/>
     </row>
     <row r="38" ht="13.95" customHeight="1" s="16">
       <c r="A38" s="6" t="n"/>
       <c r="E38" s="25" t="n"/>
-      <c r="AY38" s="10" t="inlineStr">
+      <c r="AY38" s="35" t="inlineStr">
         <is>
           <t>{Input_176}</t>
         </is>
       </c>
-      <c r="AZ38" s="10" t="inlineStr">
+      <c r="AZ38" s="33" t="inlineStr">
         <is>
           <t>{Input_177}</t>
         </is>
       </c>
-      <c r="BA38" s="11" t="n"/>
-      <c r="BB38" s="12" t="n"/>
-      <c r="BC38" s="10" t="inlineStr">
+      <c r="BA38" s="42" t="n"/>
+      <c r="BB38" s="41" t="n"/>
+      <c r="BC38" s="33" t="inlineStr">
         <is>
           <t>{Input_178}</t>
         </is>
       </c>
-      <c r="BD38" s="11" t="n"/>
-      <c r="BE38" s="11" t="n"/>
-      <c r="BF38" s="11" t="n"/>
-      <c r="BG38" s="11" t="n"/>
-      <c r="BH38" s="11" t="n"/>
-      <c r="BI38" s="11" t="n"/>
-      <c r="BJ38" s="12" t="n"/>
-      <c r="BK38" s="10" t="inlineStr">
+      <c r="BD38" s="42" t="n"/>
+      <c r="BE38" s="42" t="n"/>
+      <c r="BF38" s="42" t="n"/>
+      <c r="BG38" s="42" t="n"/>
+      <c r="BH38" s="42" t="n"/>
+      <c r="BI38" s="42" t="n"/>
+      <c r="BJ38" s="41" t="n"/>
+      <c r="BK38" s="33" t="inlineStr">
         <is>
           <t>{Input_179}</t>
         </is>
       </c>
-      <c r="BL38" s="11" t="n"/>
-      <c r="BM38" s="12" t="n"/>
-      <c r="BN38" s="10" t="inlineStr">
+      <c r="BL38" s="42" t="n"/>
+      <c r="BM38" s="41" t="n"/>
+      <c r="BN38" s="33" t="inlineStr">
         <is>
           <t>{Input_180}</t>
         </is>
       </c>
-      <c r="BO38" s="11" t="n"/>
-      <c r="BP38" s="12" t="n"/>
-      <c r="BQ38" s="10" t="inlineStr">
+      <c r="BO38" s="42" t="n"/>
+      <c r="BP38" s="41" t="n"/>
+      <c r="BQ38" s="33" t="inlineStr">
         <is>
           <t>{Input_181}</t>
         </is>
       </c>
-      <c r="BR38" s="11" t="n"/>
-      <c r="BS38" s="12" t="n"/>
-      <c r="BT38" s="25" t="n"/>
+      <c r="BR38" s="42" t="n"/>
+      <c r="BS38" s="41" t="n"/>
+      <c r="BT38" s="34" t="n"/>
       <c r="BV38" s="5" t="n"/>
     </row>
     <row r="39" ht="13.95" customHeight="1" s="16">
       <c r="A39" s="6" t="n"/>
       <c r="E39" s="25" t="n"/>
-      <c r="AY39" s="10" t="inlineStr">
+      <c r="AY39" s="35" t="inlineStr">
         <is>
           <t>{Input_182}</t>
         </is>
       </c>
-      <c r="AZ39" s="10" t="inlineStr">
+      <c r="AZ39" s="33" t="inlineStr">
         <is>
           <t>{Input_183}</t>
         </is>
       </c>
-      <c r="BA39" s="11" t="n"/>
-      <c r="BB39" s="12" t="n"/>
-      <c r="BC39" s="10" t="inlineStr">
+      <c r="BA39" s="42" t="n"/>
+      <c r="BB39" s="41" t="n"/>
+      <c r="BC39" s="33" t="inlineStr">
         <is>
           <t>{Input_184}</t>
         </is>
       </c>
-      <c r="BD39" s="11" t="n"/>
-      <c r="BE39" s="11" t="n"/>
-      <c r="BF39" s="11" t="n"/>
-      <c r="BG39" s="11" t="n"/>
-      <c r="BH39" s="11" t="n"/>
-      <c r="BI39" s="11" t="n"/>
-      <c r="BJ39" s="12" t="n"/>
-      <c r="BK39" s="10" t="inlineStr">
+      <c r="BD39" s="42" t="n"/>
+      <c r="BE39" s="42" t="n"/>
+      <c r="BF39" s="42" t="n"/>
+      <c r="BG39" s="42" t="n"/>
+      <c r="BH39" s="42" t="n"/>
+      <c r="BI39" s="42" t="n"/>
+      <c r="BJ39" s="41" t="n"/>
+      <c r="BK39" s="33" t="inlineStr">
         <is>
           <t>{Input_185}</t>
         </is>
       </c>
-      <c r="BL39" s="11" t="n"/>
-      <c r="BM39" s="12" t="n"/>
-      <c r="BN39" s="10" t="inlineStr">
+      <c r="BL39" s="42" t="n"/>
+      <c r="BM39" s="41" t="n"/>
+      <c r="BN39" s="33" t="inlineStr">
         <is>
           <t>{Input_186}</t>
         </is>
       </c>
-      <c r="BO39" s="11" t="n"/>
-      <c r="BP39" s="12" t="n"/>
-      <c r="BQ39" s="10" t="inlineStr">
+      <c r="BO39" s="42" t="n"/>
+      <c r="BP39" s="41" t="n"/>
+      <c r="BQ39" s="33" t="inlineStr">
         <is>
           <t>{Input_187}</t>
         </is>
       </c>
-      <c r="BR39" s="11" t="n"/>
-      <c r="BS39" s="12" t="n"/>
-      <c r="BT39" s="25" t="n"/>
+      <c r="BR39" s="42" t="n"/>
+      <c r="BS39" s="41" t="n"/>
+      <c r="BT39" s="34" t="n"/>
       <c r="BV39" s="5" t="n"/>
     </row>
     <row r="40" ht="13.95" customHeight="1" s="16">
       <c r="A40" s="6" t="n"/>
       <c r="E40" s="25" t="n"/>
-      <c r="AY40" s="10" t="inlineStr">
+      <c r="AY40" s="35" t="inlineStr">
         <is>
           <t>{Input_188}</t>
         </is>
       </c>
-      <c r="AZ40" s="10" t="inlineStr">
+      <c r="AZ40" s="33" t="inlineStr">
         <is>
           <t>{Input_189}</t>
         </is>
       </c>
-      <c r="BA40" s="11" t="n"/>
-      <c r="BB40" s="12" t="n"/>
-      <c r="BC40" s="10" t="inlineStr">
+      <c r="BA40" s="42" t="n"/>
+      <c r="BB40" s="41" t="n"/>
+      <c r="BC40" s="33" t="inlineStr">
         <is>
           <t>{Input_190}</t>
         </is>
       </c>
-      <c r="BD40" s="11" t="n"/>
-      <c r="BE40" s="11" t="n"/>
-      <c r="BF40" s="11" t="n"/>
-      <c r="BG40" s="11" t="n"/>
-      <c r="BH40" s="11" t="n"/>
-      <c r="BI40" s="11" t="n"/>
-      <c r="BJ40" s="12" t="n"/>
-      <c r="BK40" s="10" t="inlineStr">
+      <c r="BD40" s="42" t="n"/>
+      <c r="BE40" s="42" t="n"/>
+      <c r="BF40" s="42" t="n"/>
+      <c r="BG40" s="42" t="n"/>
+      <c r="BH40" s="42" t="n"/>
+      <c r="BI40" s="42" t="n"/>
+      <c r="BJ40" s="41" t="n"/>
+      <c r="BK40" s="33" t="inlineStr">
         <is>
           <t>{Input_191}</t>
         </is>
       </c>
-      <c r="BL40" s="11" t="n"/>
-      <c r="BM40" s="12" t="n"/>
-      <c r="BN40" s="10" t="inlineStr">
+      <c r="BL40" s="42" t="n"/>
+      <c r="BM40" s="41" t="n"/>
+      <c r="BN40" s="33" t="inlineStr">
         <is>
           <t>{Input_192}</t>
         </is>
       </c>
-      <c r="BO40" s="11" t="n"/>
-      <c r="BP40" s="12" t="n"/>
-      <c r="BQ40" s="10" t="inlineStr">
+      <c r="BO40" s="42" t="n"/>
+      <c r="BP40" s="41" t="n"/>
+      <c r="BQ40" s="33" t="inlineStr">
         <is>
           <t>{Input_193}</t>
         </is>
       </c>
-      <c r="BR40" s="11" t="n"/>
-      <c r="BS40" s="12" t="n"/>
-      <c r="BT40" s="25" t="n"/>
+      <c r="BR40" s="42" t="n"/>
+      <c r="BS40" s="41" t="n"/>
+      <c r="BT40" s="34" t="n"/>
       <c r="BV40" s="5" t="n"/>
     </row>
     <row r="41" ht="13.95" customHeight="1" s="16">
       <c r="A41" s="6" t="n"/>
       <c r="E41" s="21" t="n"/>
-      <c r="AY41" s="10" t="inlineStr">
+      <c r="AY41" s="35" t="inlineStr">
         <is>
           <t>{Input_194}</t>
         </is>
       </c>
-      <c r="AZ41" s="10" t="inlineStr">
+      <c r="AZ41" s="33" t="inlineStr">
         <is>
           <t>{Input_195}</t>
         </is>
       </c>
-      <c r="BA41" s="14" t="n"/>
-      <c r="BB41" s="19" t="n"/>
-      <c r="BC41" s="10" t="inlineStr">
+      <c r="BA41" s="38" t="n"/>
+      <c r="BB41" s="36" t="n"/>
+      <c r="BC41" s="33" t="inlineStr">
         <is>
           <t>{Input_196}</t>
         </is>
       </c>
-      <c r="BD41" s="14" t="n"/>
-      <c r="BE41" s="14" t="n"/>
-      <c r="BF41" s="14" t="n"/>
-      <c r="BG41" s="14" t="n"/>
-      <c r="BH41" s="14" t="n"/>
-      <c r="BI41" s="14" t="n"/>
-      <c r="BJ41" s="19" t="n"/>
-      <c r="BK41" s="10" t="inlineStr">
+      <c r="BD41" s="38" t="n"/>
+      <c r="BE41" s="38" t="n"/>
+      <c r="BF41" s="38" t="n"/>
+      <c r="BG41" s="38" t="n"/>
+      <c r="BH41" s="38" t="n"/>
+      <c r="BI41" s="38" t="n"/>
+      <c r="BJ41" s="36" t="n"/>
+      <c r="BK41" s="33" t="inlineStr">
         <is>
           <t>{Input_197}</t>
         </is>
       </c>
-      <c r="BL41" s="14" t="n"/>
-      <c r="BM41" s="19" t="n"/>
-      <c r="BN41" s="10" t="inlineStr">
+      <c r="BL41" s="38" t="n"/>
+      <c r="BM41" s="36" t="n"/>
+      <c r="BN41" s="33" t="inlineStr">
         <is>
           <t>{Input_198}</t>
         </is>
       </c>
-      <c r="BO41" s="14" t="n"/>
-      <c r="BP41" s="19" t="n"/>
-      <c r="BQ41" s="10" t="inlineStr">
+      <c r="BO41" s="38" t="n"/>
+      <c r="BP41" s="36" t="n"/>
+      <c r="BQ41" s="33" t="inlineStr">
         <is>
           <t>{Input_199}</t>
         </is>
       </c>
-      <c r="BR41" s="14" t="n"/>
-      <c r="BS41" s="19" t="n"/>
-      <c r="BT41" s="21" t="n"/>
+      <c r="BR41" s="38" t="n"/>
+      <c r="BS41" s="36" t="n"/>
+      <c r="BT41" s="40" t="n"/>
       <c r="BV41" s="5" t="n"/>
     </row>
     <row r="42" ht="13.95" customHeight="1" s="16">
       <c r="A42" s="6" t="n"/>
-      <c r="E42" s="10" t="inlineStr">
+      <c r="E42" s="35" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
       <c r="AY42" s="21" t="n"/>
-      <c r="AZ42" s="17" t="n"/>
+      <c r="AZ42" s="39" t="n"/>
       <c r="BA42" s="18" t="n"/>
       <c r="BB42" s="20" t="n"/>
-      <c r="BC42" s="17" t="n"/>
+      <c r="BC42" s="39" t="n"/>
       <c r="BD42" s="18" t="n"/>
       <c r="BE42" s="18" t="n"/>
       <c r="BF42" s="18" t="n"/>
@@ -2754,16 +2910,16 @@
       <c r="BH42" s="18" t="n"/>
       <c r="BI42" s="18" t="n"/>
       <c r="BJ42" s="20" t="n"/>
-      <c r="BK42" s="17" t="n"/>
+      <c r="BK42" s="39" t="n"/>
       <c r="BL42" s="18" t="n"/>
       <c r="BM42" s="20" t="n"/>
-      <c r="BN42" s="17" t="n"/>
+      <c r="BN42" s="39" t="n"/>
       <c r="BO42" s="18" t="n"/>
       <c r="BP42" s="20" t="n"/>
-      <c r="BQ42" s="17" t="n"/>
+      <c r="BQ42" s="39" t="n"/>
       <c r="BR42" s="18" t="n"/>
       <c r="BS42" s="20" t="n"/>
-      <c r="BT42" s="10" t="inlineStr">
+      <c r="BT42" s="33" t="inlineStr">
         <is>
           <t>D</t>
         </is>
@@ -2773,91 +2929,91 @@
     <row r="43" ht="13.95" customHeight="1" s="16">
       <c r="A43" s="6" t="n"/>
       <c r="E43" s="25" t="n"/>
-      <c r="AY43" s="10" t="inlineStr">
+      <c r="AY43" s="35" t="inlineStr">
         <is>
           <t>REV.</t>
         </is>
       </c>
-      <c r="AZ43" s="10" t="inlineStr">
+      <c r="AZ43" s="33" t="inlineStr">
         <is>
           <t>DATE</t>
         </is>
       </c>
-      <c r="BA43" s="11" t="n"/>
-      <c r="BB43" s="12" t="n"/>
-      <c r="BC43" s="10" t="inlineStr">
+      <c r="BA43" s="42" t="n"/>
+      <c r="BB43" s="41" t="n"/>
+      <c r="BC43" s="33" t="inlineStr">
         <is>
           <t>DESCRIPTION</t>
         </is>
       </c>
-      <c r="BD43" s="11" t="n"/>
-      <c r="BE43" s="11" t="n"/>
-      <c r="BF43" s="11" t="n"/>
-      <c r="BG43" s="11" t="n"/>
-      <c r="BH43" s="11" t="n"/>
-      <c r="BI43" s="11" t="n"/>
-      <c r="BJ43" s="12" t="n"/>
-      <c r="BK43" s="10" t="inlineStr">
+      <c r="BD43" s="42" t="n"/>
+      <c r="BE43" s="42" t="n"/>
+      <c r="BF43" s="42" t="n"/>
+      <c r="BG43" s="42" t="n"/>
+      <c r="BH43" s="42" t="n"/>
+      <c r="BI43" s="42" t="n"/>
+      <c r="BJ43" s="41" t="n"/>
+      <c r="BK43" s="33" t="inlineStr">
         <is>
           <t>DRAWN</t>
         </is>
       </c>
-      <c r="BL43" s="11" t="n"/>
-      <c r="BM43" s="12" t="n"/>
-      <c r="BN43" s="10" t="inlineStr">
+      <c r="BL43" s="42" t="n"/>
+      <c r="BM43" s="41" t="n"/>
+      <c r="BN43" s="33" t="inlineStr">
         <is>
           <t>CHECKED</t>
         </is>
       </c>
-      <c r="BO43" s="11" t="n"/>
-      <c r="BP43" s="12" t="n"/>
-      <c r="BQ43" s="10" t="inlineStr">
+      <c r="BO43" s="42" t="n"/>
+      <c r="BP43" s="41" t="n"/>
+      <c r="BQ43" s="33" t="inlineStr">
         <is>
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="BR43" s="11" t="n"/>
-      <c r="BS43" s="12" t="n"/>
-      <c r="BT43" s="25" t="n"/>
+      <c r="BR43" s="42" t="n"/>
+      <c r="BS43" s="41" t="n"/>
+      <c r="BT43" s="34" t="n"/>
       <c r="BV43" s="5" t="n"/>
     </row>
     <row r="44" ht="13.95" customHeight="1" s="16">
       <c r="A44" s="6" t="n"/>
       <c r="E44" s="25" t="n"/>
-      <c r="AY44" s="10" t="inlineStr">
+      <c r="AY44" s="35" t="inlineStr">
         <is>
           <t>PAINT CODE</t>
         </is>
       </c>
-      <c r="AZ44" s="11" t="n"/>
-      <c r="BA44" s="11" t="n"/>
-      <c r="BB44" s="12" t="n"/>
-      <c r="BC44" s="10" t="inlineStr">
+      <c r="AZ44" s="42" t="n"/>
+      <c r="BA44" s="42" t="n"/>
+      <c r="BB44" s="41" t="n"/>
+      <c r="BC44" s="33" t="inlineStr">
         <is>
           <t>{Input_165}</t>
         </is>
       </c>
-      <c r="BD44" s="11" t="n"/>
-      <c r="BE44" s="11" t="n"/>
-      <c r="BF44" s="11" t="n"/>
-      <c r="BG44" s="11" t="n"/>
-      <c r="BH44" s="11" t="n"/>
-      <c r="BI44" s="11" t="n"/>
-      <c r="BJ44" s="12" t="n"/>
-      <c r="BK44" s="10" t="inlineStr">
+      <c r="BD44" s="42" t="n"/>
+      <c r="BE44" s="42" t="n"/>
+      <c r="BF44" s="42" t="n"/>
+      <c r="BG44" s="42" t="n"/>
+      <c r="BH44" s="42" t="n"/>
+      <c r="BI44" s="42" t="n"/>
+      <c r="BJ44" s="41" t="n"/>
+      <c r="BK44" s="33" t="inlineStr">
         <is>
           <t>DP No.</t>
         </is>
       </c>
-      <c r="BL44" s="11" t="n"/>
-      <c r="BM44" s="11" t="n"/>
-      <c r="BN44" s="11" t="n"/>
-      <c r="BO44" s="11" t="n"/>
-      <c r="BP44" s="11" t="n"/>
-      <c r="BQ44" s="11" t="n"/>
-      <c r="BR44" s="11" t="n"/>
-      <c r="BS44" s="12" t="n"/>
-      <c r="BT44" s="25" t="n"/>
+      <c r="BL44" s="42" t="n"/>
+      <c r="BM44" s="42" t="n"/>
+      <c r="BN44" s="42" t="n"/>
+      <c r="BO44" s="42" t="n"/>
+      <c r="BP44" s="42" t="n"/>
+      <c r="BQ44" s="42" t="n"/>
+      <c r="BR44" s="42" t="n"/>
+      <c r="BS44" s="41" t="n"/>
+      <c r="BT44" s="34" t="n"/>
       <c r="BV44" s="5" t="n"/>
     </row>
     <row r="45" ht="13.95" customHeight="1" s="16">
@@ -2871,7 +3027,7 @@
       <c r="AZ45" s="18" t="n"/>
       <c r="BA45" s="18" t="n"/>
       <c r="BB45" s="20" t="n"/>
-      <c r="BC45" s="31" t="inlineStr">
+      <c r="BC45" s="43" t="inlineStr">
         <is>
           <t>{Input_167}</t>
         </is>
@@ -2883,55 +3039,55 @@
       <c r="BH45" s="18" t="n"/>
       <c r="BI45" s="18" t="n"/>
       <c r="BJ45" s="18" t="n"/>
-      <c r="BK45" s="10" t="inlineStr">
+      <c r="BK45" s="35" t="inlineStr">
         <is>
           <t>{Input_168}</t>
         </is>
       </c>
-      <c r="BL45" s="11" t="n"/>
-      <c r="BM45" s="11" t="n"/>
-      <c r="BN45" s="11" t="n"/>
-      <c r="BO45" s="11" t="n"/>
-      <c r="BP45" s="11" t="n"/>
-      <c r="BQ45" s="11" t="n"/>
-      <c r="BR45" s="11" t="n"/>
-      <c r="BS45" s="12" t="n"/>
-      <c r="BT45" s="25" t="n"/>
+      <c r="BL45" s="42" t="n"/>
+      <c r="BM45" s="42" t="n"/>
+      <c r="BN45" s="42" t="n"/>
+      <c r="BO45" s="42" t="n"/>
+      <c r="BP45" s="42" t="n"/>
+      <c r="BQ45" s="42" t="n"/>
+      <c r="BR45" s="42" t="n"/>
+      <c r="BS45" s="41" t="n"/>
+      <c r="BT45" s="34" t="n"/>
       <c r="BV45" s="5" t="n"/>
     </row>
     <row r="46" ht="13.95" customHeight="1" s="16">
       <c r="A46" s="6" t="n"/>
       <c r="E46" s="25" t="n"/>
-      <c r="AY46" s="27" t="inlineStr">
+      <c r="AY46" s="44" t="inlineStr">
         <is>
           <t>CLIENT</t>
         </is>
       </c>
-      <c r="AZ46" s="14" t="n"/>
-      <c r="BA46" s="14" t="n"/>
-      <c r="BB46" s="14" t="n"/>
-      <c r="BC46" s="14" t="n"/>
-      <c r="BD46" s="14" t="n"/>
-      <c r="BE46" s="14" t="n"/>
-      <c r="BF46" s="19" t="n"/>
-      <c r="BG46" s="10" t="inlineStr">
+      <c r="AZ46" s="38" t="n"/>
+      <c r="BA46" s="38" t="n"/>
+      <c r="BB46" s="38" t="n"/>
+      <c r="BC46" s="38" t="n"/>
+      <c r="BD46" s="38" t="n"/>
+      <c r="BE46" s="38" t="n"/>
+      <c r="BF46" s="36" t="n"/>
+      <c r="BG46" s="33" t="inlineStr">
         <is>
           <t>{Input_1}</t>
         </is>
       </c>
-      <c r="BH46" s="14" t="n"/>
-      <c r="BI46" s="14" t="n"/>
-      <c r="BJ46" s="14" t="n"/>
-      <c r="BK46" s="14" t="n"/>
-      <c r="BL46" s="14" t="n"/>
-      <c r="BM46" s="14" t="n"/>
-      <c r="BN46" s="14" t="n"/>
-      <c r="BO46" s="14" t="n"/>
-      <c r="BP46" s="14" t="n"/>
-      <c r="BQ46" s="14" t="n"/>
-      <c r="BR46" s="14" t="n"/>
-      <c r="BS46" s="19" t="n"/>
-      <c r="BT46" s="25" t="n"/>
+      <c r="BH46" s="38" t="n"/>
+      <c r="BI46" s="38" t="n"/>
+      <c r="BJ46" s="38" t="n"/>
+      <c r="BK46" s="38" t="n"/>
+      <c r="BL46" s="38" t="n"/>
+      <c r="BM46" s="38" t="n"/>
+      <c r="BN46" s="38" t="n"/>
+      <c r="BO46" s="38" t="n"/>
+      <c r="BP46" s="38" t="n"/>
+      <c r="BQ46" s="38" t="n"/>
+      <c r="BR46" s="38" t="n"/>
+      <c r="BS46" s="36" t="n"/>
+      <c r="BT46" s="34" t="n"/>
       <c r="BV46" s="5" t="n"/>
     </row>
     <row r="47" ht="13.95" customHeight="1" s="16">
@@ -2943,9 +3099,9 @@
         </is>
       </c>
       <c r="BF47" s="23" t="n"/>
-      <c r="BG47" s="15" t="n"/>
+      <c r="BG47" s="45" t="n"/>
       <c r="BS47" s="23" t="n"/>
-      <c r="BT47" s="25" t="n"/>
+      <c r="BT47" s="34" t="n"/>
       <c r="BV47" s="5" t="n"/>
     </row>
     <row r="48" ht="13.95" customHeight="1" s="16">
@@ -2963,7 +3119,7 @@
       </c>
       <c r="AY48" s="15" t="n"/>
       <c r="BF48" s="23" t="n"/>
-      <c r="BG48" s="17" t="n"/>
+      <c r="BG48" s="39" t="n"/>
       <c r="BH48" s="18" t="n"/>
       <c r="BI48" s="18" t="n"/>
       <c r="BJ48" s="18" t="n"/>
@@ -2976,7 +3132,7 @@
       <c r="BQ48" s="18" t="n"/>
       <c r="BR48" s="18" t="n"/>
       <c r="BS48" s="20" t="n"/>
-      <c r="BT48" s="25" t="n"/>
+      <c r="BT48" s="34" t="n"/>
       <c r="BV48" s="5" t="n"/>
     </row>
     <row r="49" ht="13.95" customHeight="1" s="16">
@@ -2984,24 +3140,24 @@
       <c r="E49" s="25" t="n"/>
       <c r="AY49" s="15" t="n"/>
       <c r="BF49" s="23" t="n"/>
-      <c r="BG49" s="10" t="inlineStr">
+      <c r="BG49" s="33" t="inlineStr">
         <is>
           <t>{Input_2}</t>
         </is>
       </c>
-      <c r="BH49" s="14" t="n"/>
-      <c r="BI49" s="14" t="n"/>
-      <c r="BJ49" s="14" t="n"/>
-      <c r="BK49" s="14" t="n"/>
-      <c r="BL49" s="14" t="n"/>
-      <c r="BM49" s="14" t="n"/>
-      <c r="BN49" s="14" t="n"/>
-      <c r="BO49" s="14" t="n"/>
-      <c r="BP49" s="14" t="n"/>
-      <c r="BQ49" s="14" t="n"/>
-      <c r="BR49" s="14" t="n"/>
-      <c r="BS49" s="19" t="n"/>
-      <c r="BT49" s="25" t="n"/>
+      <c r="BH49" s="38" t="n"/>
+      <c r="BI49" s="38" t="n"/>
+      <c r="BJ49" s="38" t="n"/>
+      <c r="BK49" s="38" t="n"/>
+      <c r="BL49" s="38" t="n"/>
+      <c r="BM49" s="38" t="n"/>
+      <c r="BN49" s="38" t="n"/>
+      <c r="BO49" s="38" t="n"/>
+      <c r="BP49" s="38" t="n"/>
+      <c r="BQ49" s="38" t="n"/>
+      <c r="BR49" s="38" t="n"/>
+      <c r="BS49" s="36" t="n"/>
+      <c r="BT49" s="34" t="n"/>
       <c r="BV49" s="5" t="n"/>
     </row>
     <row r="50" ht="13.95" customHeight="1" s="16">
@@ -3015,7 +3171,7 @@
       <c r="BD50" s="18" t="n"/>
       <c r="BE50" s="18" t="n"/>
       <c r="BF50" s="20" t="n"/>
-      <c r="BG50" s="17" t="n"/>
+      <c r="BG50" s="39" t="n"/>
       <c r="BH50" s="18" t="n"/>
       <c r="BI50" s="18" t="n"/>
       <c r="BJ50" s="18" t="n"/>
@@ -3028,42 +3184,42 @@
       <c r="BQ50" s="18" t="n"/>
       <c r="BR50" s="18" t="n"/>
       <c r="BS50" s="20" t="n"/>
-      <c r="BT50" s="25" t="n"/>
+      <c r="BT50" s="34" t="n"/>
       <c r="BV50" s="5" t="n"/>
     </row>
     <row r="51" ht="13.95" customHeight="1" s="16">
       <c r="A51" s="6" t="n"/>
       <c r="E51" s="25" t="n"/>
-      <c r="AY51" s="27" t="inlineStr">
+      <c r="AY51" s="44" t="inlineStr">
         <is>
           <t>CONTRACTOR</t>
         </is>
       </c>
-      <c r="AZ51" s="14" t="n"/>
-      <c r="BA51" s="14" t="n"/>
-      <c r="BB51" s="14" t="n"/>
-      <c r="BC51" s="14" t="n"/>
-      <c r="BD51" s="14" t="n"/>
-      <c r="BE51" s="14" t="n"/>
-      <c r="BF51" s="19" t="n"/>
-      <c r="BG51" s="10" t="inlineStr">
+      <c r="AZ51" s="38" t="n"/>
+      <c r="BA51" s="38" t="n"/>
+      <c r="BB51" s="38" t="n"/>
+      <c r="BC51" s="38" t="n"/>
+      <c r="BD51" s="38" t="n"/>
+      <c r="BE51" s="38" t="n"/>
+      <c r="BF51" s="36" t="n"/>
+      <c r="BG51" s="33" t="inlineStr">
         <is>
           <t>{Input_3}</t>
         </is>
       </c>
-      <c r="BH51" s="14" t="n"/>
-      <c r="BI51" s="14" t="n"/>
-      <c r="BJ51" s="14" t="n"/>
-      <c r="BK51" s="14" t="n"/>
-      <c r="BL51" s="14" t="n"/>
-      <c r="BM51" s="14" t="n"/>
-      <c r="BN51" s="14" t="n"/>
-      <c r="BO51" s="14" t="n"/>
-      <c r="BP51" s="14" t="n"/>
-      <c r="BQ51" s="14" t="n"/>
-      <c r="BR51" s="14" t="n"/>
-      <c r="BS51" s="19" t="n"/>
-      <c r="BT51" s="25" t="n"/>
+      <c r="BH51" s="38" t="n"/>
+      <c r="BI51" s="38" t="n"/>
+      <c r="BJ51" s="38" t="n"/>
+      <c r="BK51" s="38" t="n"/>
+      <c r="BL51" s="38" t="n"/>
+      <c r="BM51" s="38" t="n"/>
+      <c r="BN51" s="38" t="n"/>
+      <c r="BO51" s="38" t="n"/>
+      <c r="BP51" s="38" t="n"/>
+      <c r="BQ51" s="38" t="n"/>
+      <c r="BR51" s="38" t="n"/>
+      <c r="BS51" s="36" t="n"/>
+      <c r="BT51" s="34" t="n"/>
       <c r="BV51" s="5" t="n"/>
     </row>
     <row r="52" ht="13.95" customHeight="1" s="16">
@@ -3075,9 +3231,9 @@
         </is>
       </c>
       <c r="BF52" s="23" t="n"/>
-      <c r="BG52" s="15" t="n"/>
+      <c r="BG52" s="45" t="n"/>
       <c r="BS52" s="23" t="n"/>
-      <c r="BT52" s="25" t="n"/>
+      <c r="BT52" s="34" t="n"/>
       <c r="BV52" s="5" t="n"/>
     </row>
     <row r="53" ht="13.95" customHeight="1" s="16">
@@ -3085,9 +3241,9 @@
       <c r="E53" s="25" t="n"/>
       <c r="AY53" s="15" t="n"/>
       <c r="BF53" s="23" t="n"/>
-      <c r="BG53" s="15" t="n"/>
+      <c r="BG53" s="45" t="n"/>
       <c r="BS53" s="23" t="n"/>
-      <c r="BT53" s="25" t="n"/>
+      <c r="BT53" s="34" t="n"/>
       <c r="BV53" s="5" t="n"/>
     </row>
     <row r="54" ht="13.95" customHeight="1" s="16">
@@ -3101,7 +3257,7 @@
       <c r="BD54" s="18" t="n"/>
       <c r="BE54" s="18" t="n"/>
       <c r="BF54" s="20" t="n"/>
-      <c r="BG54" s="17" t="n"/>
+      <c r="BG54" s="39" t="n"/>
       <c r="BH54" s="18" t="n"/>
       <c r="BI54" s="18" t="n"/>
       <c r="BJ54" s="18" t="n"/>
@@ -3114,42 +3270,42 @@
       <c r="BQ54" s="18" t="n"/>
       <c r="BR54" s="18" t="n"/>
       <c r="BS54" s="20" t="n"/>
-      <c r="BT54" s="25" t="n"/>
+      <c r="BT54" s="34" t="n"/>
       <c r="BV54" s="5" t="n"/>
     </row>
     <row r="55" ht="13.95" customHeight="1" s="16">
       <c r="A55" s="6" t="n"/>
       <c r="E55" s="21" t="n"/>
-      <c r="AY55" s="13" t="inlineStr">
+      <c r="AY55" s="46" t="inlineStr">
         <is>
           <t>TAG NO.</t>
         </is>
       </c>
-      <c r="AZ55" s="11" t="n"/>
-      <c r="BA55" s="30" t="inlineStr">
+      <c r="AZ55" s="42" t="n"/>
+      <c r="BA55" s="47" t="inlineStr">
         <is>
           <t>{Input_169}</t>
         </is>
       </c>
-      <c r="BB55" s="11" t="n"/>
-      <c r="BC55" s="11" t="n"/>
-      <c r="BD55" s="11" t="n"/>
-      <c r="BE55" s="11" t="n"/>
-      <c r="BF55" s="11" t="n"/>
-      <c r="BG55" s="11" t="n"/>
-      <c r="BH55" s="11" t="n"/>
-      <c r="BI55" s="11" t="n"/>
-      <c r="BJ55" s="11" t="n"/>
-      <c r="BK55" s="11" t="n"/>
-      <c r="BL55" s="11" t="n"/>
-      <c r="BM55" s="11" t="n"/>
-      <c r="BN55" s="11" t="n"/>
-      <c r="BO55" s="11" t="n"/>
-      <c r="BP55" s="11" t="n"/>
-      <c r="BQ55" s="11" t="n"/>
-      <c r="BR55" s="11" t="n"/>
-      <c r="BS55" s="12" t="n"/>
-      <c r="BT55" s="21" t="n"/>
+      <c r="BB55" s="42" t="n"/>
+      <c r="BC55" s="42" t="n"/>
+      <c r="BD55" s="42" t="n"/>
+      <c r="BE55" s="42" t="n"/>
+      <c r="BF55" s="42" t="n"/>
+      <c r="BG55" s="42" t="n"/>
+      <c r="BH55" s="42" t="n"/>
+      <c r="BI55" s="42" t="n"/>
+      <c r="BJ55" s="42" t="n"/>
+      <c r="BK55" s="42" t="n"/>
+      <c r="BL55" s="42" t="n"/>
+      <c r="BM55" s="42" t="n"/>
+      <c r="BN55" s="42" t="n"/>
+      <c r="BO55" s="42" t="n"/>
+      <c r="BP55" s="42" t="n"/>
+      <c r="BQ55" s="42" t="n"/>
+      <c r="BR55" s="42" t="n"/>
+      <c r="BS55" s="41" t="n"/>
+      <c r="BT55" s="40" t="n"/>
       <c r="BV55" s="5" t="n"/>
     </row>
     <row r="56" ht="13.95" customHeight="1" s="16">
@@ -3167,7 +3323,7 @@
       <c r="N56" s="11" t="n"/>
       <c r="O56" s="11" t="n"/>
       <c r="P56" s="12" t="n"/>
-      <c r="Q56" s="10" t="n">
+      <c r="Q56" s="32" t="n">
         <v>2</v>
       </c>
       <c r="R56" s="11" t="n"/>
@@ -3180,7 +3336,7 @@
       <c r="Y56" s="11" t="n"/>
       <c r="Z56" s="11" t="n"/>
       <c r="AA56" s="12" t="n"/>
-      <c r="AB56" s="10" t="n">
+      <c r="AB56" s="32" t="n">
         <v>3</v>
       </c>
       <c r="AC56" s="11" t="n"/>
@@ -3192,7 +3348,7 @@
       <c r="AI56" s="11" t="n"/>
       <c r="AJ56" s="11" t="n"/>
       <c r="AK56" s="12" t="n"/>
-      <c r="AL56" s="10" t="n">
+      <c r="AL56" s="32" t="n">
         <v>4</v>
       </c>
       <c r="AM56" s="11" t="n"/>
@@ -3205,33 +3361,33 @@
       <c r="AT56" s="11" t="n"/>
       <c r="AU56" s="11" t="n"/>
       <c r="AV56" s="12" t="n"/>
-      <c r="AW56" s="10" t="n">
+      <c r="AW56" s="32" t="n">
         <v>5</v>
       </c>
       <c r="AX56" s="11" t="n"/>
-      <c r="AY56" s="11" t="n"/>
-      <c r="AZ56" s="11" t="n"/>
-      <c r="BA56" s="11" t="n"/>
-      <c r="BB56" s="11" t="n"/>
-      <c r="BC56" s="11" t="n"/>
-      <c r="BD56" s="11" t="n"/>
-      <c r="BE56" s="11" t="n"/>
-      <c r="BF56" s="11" t="n"/>
-      <c r="BG56" s="11" t="n"/>
-      <c r="BH56" s="12" t="n"/>
-      <c r="BI56" s="10" t="n">
+      <c r="AY56" s="42" t="n"/>
+      <c r="AZ56" s="42" t="n"/>
+      <c r="BA56" s="42" t="n"/>
+      <c r="BB56" s="42" t="n"/>
+      <c r="BC56" s="42" t="n"/>
+      <c r="BD56" s="42" t="n"/>
+      <c r="BE56" s="42" t="n"/>
+      <c r="BF56" s="42" t="n"/>
+      <c r="BG56" s="42" t="n"/>
+      <c r="BH56" s="41" t="n"/>
+      <c r="BI56" s="33" t="n">
         <v>6</v>
       </c>
-      <c r="BJ56" s="11" t="n"/>
-      <c r="BK56" s="11" t="n"/>
-      <c r="BL56" s="11" t="n"/>
-      <c r="BM56" s="11" t="n"/>
-      <c r="BN56" s="11" t="n"/>
-      <c r="BO56" s="11" t="n"/>
-      <c r="BP56" s="11" t="n"/>
-      <c r="BQ56" s="11" t="n"/>
-      <c r="BR56" s="11" t="n"/>
-      <c r="BS56" s="12" t="n"/>
+      <c r="BJ56" s="42" t="n"/>
+      <c r="BK56" s="42" t="n"/>
+      <c r="BL56" s="42" t="n"/>
+      <c r="BM56" s="42" t="n"/>
+      <c r="BN56" s="42" t="n"/>
+      <c r="BO56" s="42" t="n"/>
+      <c r="BP56" s="42" t="n"/>
+      <c r="BQ56" s="42" t="n"/>
+      <c r="BR56" s="42" t="n"/>
+      <c r="BS56" s="41" t="n"/>
       <c r="BV56" s="5" t="n"/>
     </row>
     <row r="57" ht="13.95" customHeight="1" s="16">

--- a/가공도_도면_1.xlsx
+++ b/가공도_도면_1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\duddl\Desktop\Project\a2z\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{725186F8-5E04-451E-9D72-822569AC5CEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B2C5A5C-2569-4B41-9B00-81C6FA9AFB01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="696" yWindow="720" windowWidth="20256" windowHeight="11520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -766,7 +766,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="22">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -843,54 +843,12 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color auto="1"/>
       </left>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1005,7 +963,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1014,42 +972,54 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1058,40 +1028,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1099,13 +1046,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -1495,85 +1444,85 @@
       <c r="BZ1" s="6"/>
     </row>
     <row r="2" spans="1:78" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="C2" s="11">
+      <c r="C2" s="14">
         <v>1</v>
       </c>
-      <c r="D2" s="12"/>
-      <c r="E2" s="12"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="12"/>
-      <c r="H2" s="12"/>
-      <c r="I2" s="12"/>
-      <c r="J2" s="12"/>
-      <c r="K2" s="12"/>
-      <c r="L2" s="13"/>
-      <c r="M2" s="11">
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+      <c r="H2" s="15"/>
+      <c r="I2" s="15"/>
+      <c r="J2" s="15"/>
+      <c r="K2" s="15"/>
+      <c r="L2" s="16"/>
+      <c r="M2" s="14">
         <v>2</v>
       </c>
-      <c r="N2" s="12"/>
-      <c r="O2" s="12"/>
-      <c r="P2" s="12"/>
-      <c r="Q2" s="12"/>
-      <c r="R2" s="12"/>
-      <c r="S2" s="12"/>
-      <c r="T2" s="12"/>
-      <c r="U2" s="12"/>
-      <c r="V2" s="12"/>
-      <c r="W2" s="12"/>
-      <c r="X2" s="13"/>
-      <c r="Y2" s="11">
+      <c r="N2" s="15"/>
+      <c r="O2" s="15"/>
+      <c r="P2" s="15"/>
+      <c r="Q2" s="15"/>
+      <c r="R2" s="15"/>
+      <c r="S2" s="15"/>
+      <c r="T2" s="15"/>
+      <c r="U2" s="15"/>
+      <c r="V2" s="15"/>
+      <c r="W2" s="15"/>
+      <c r="X2" s="16"/>
+      <c r="Y2" s="14">
         <v>3</v>
       </c>
-      <c r="Z2" s="12"/>
-      <c r="AA2" s="12"/>
-      <c r="AB2" s="12"/>
-      <c r="AC2" s="12"/>
-      <c r="AD2" s="12"/>
-      <c r="AE2" s="12"/>
-      <c r="AF2" s="12"/>
-      <c r="AG2" s="12"/>
-      <c r="AH2" s="12"/>
-      <c r="AI2" s="13"/>
-      <c r="AJ2" s="11">
+      <c r="Z2" s="15"/>
+      <c r="AA2" s="15"/>
+      <c r="AB2" s="15"/>
+      <c r="AC2" s="15"/>
+      <c r="AD2" s="15"/>
+      <c r="AE2" s="15"/>
+      <c r="AF2" s="15"/>
+      <c r="AG2" s="15"/>
+      <c r="AH2" s="15"/>
+      <c r="AI2" s="16"/>
+      <c r="AJ2" s="14">
         <v>4</v>
       </c>
-      <c r="AK2" s="12"/>
-      <c r="AL2" s="12"/>
-      <c r="AM2" s="12"/>
-      <c r="AN2" s="12"/>
-      <c r="AO2" s="12"/>
-      <c r="AP2" s="12"/>
-      <c r="AQ2" s="12"/>
-      <c r="AR2" s="12"/>
-      <c r="AS2" s="12"/>
-      <c r="AT2" s="13"/>
-      <c r="AU2" s="11">
+      <c r="AK2" s="15"/>
+      <c r="AL2" s="15"/>
+      <c r="AM2" s="15"/>
+      <c r="AN2" s="15"/>
+      <c r="AO2" s="15"/>
+      <c r="AP2" s="15"/>
+      <c r="AQ2" s="15"/>
+      <c r="AR2" s="15"/>
+      <c r="AS2" s="15"/>
+      <c r="AT2" s="16"/>
+      <c r="AU2" s="14">
         <v>5</v>
       </c>
-      <c r="AV2" s="12"/>
-      <c r="AW2" s="12"/>
-      <c r="AX2" s="12"/>
-      <c r="AY2" s="12"/>
-      <c r="AZ2" s="12"/>
-      <c r="BA2" s="12"/>
-      <c r="BB2" s="12"/>
-      <c r="BC2" s="12"/>
-      <c r="BD2" s="12"/>
-      <c r="BE2" s="12"/>
-      <c r="BF2" s="13"/>
-      <c r="BG2" s="11">
+      <c r="AV2" s="15"/>
+      <c r="AW2" s="15"/>
+      <c r="AX2" s="15"/>
+      <c r="AY2" s="15"/>
+      <c r="AZ2" s="15"/>
+      <c r="BA2" s="15"/>
+      <c r="BB2" s="15"/>
+      <c r="BC2" s="15"/>
+      <c r="BD2" s="15"/>
+      <c r="BE2" s="15"/>
+      <c r="BF2" s="16"/>
+      <c r="BG2" s="14">
         <v>6</v>
       </c>
-      <c r="BH2" s="12"/>
-      <c r="BI2" s="12"/>
-      <c r="BJ2" s="12"/>
-      <c r="BK2" s="12"/>
-      <c r="BL2" s="12"/>
-      <c r="BM2" s="12"/>
-      <c r="BN2" s="12"/>
-      <c r="BO2" s="12"/>
-      <c r="BP2" s="12"/>
-      <c r="BQ2" s="13"/>
+      <c r="BH2" s="15"/>
+      <c r="BI2" s="15"/>
+      <c r="BJ2" s="15"/>
+      <c r="BK2" s="15"/>
+      <c r="BL2" s="15"/>
+      <c r="BM2" s="15"/>
+      <c r="BN2" s="15"/>
+      <c r="BO2" s="15"/>
+      <c r="BP2" s="15"/>
+      <c r="BQ2" s="16"/>
       <c r="BR2" s="2"/>
       <c r="BT2" s="6"/>
       <c r="BU2" s="6"/>
@@ -1584,43 +1533,43 @@
       <c r="BZ2" s="6"/>
     </row>
     <row r="3" spans="1:78" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B3" s="16" t="s">
+      <c r="B3" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="34" t="s">
+      <c r="C3" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="34"/>
+      <c r="D3" s="32"/>
       <c r="Y3" s="3"/>
-      <c r="AT3" s="34" t="s">
+      <c r="AT3" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="AU3" s="34"/>
-      <c r="AV3" s="34"/>
-      <c r="AW3" s="25" t="s">
+      <c r="AU3" s="32"/>
+      <c r="AV3" s="32"/>
+      <c r="AW3" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="AX3" s="26"/>
-      <c r="AY3" s="26"/>
-      <c r="AZ3" s="26"/>
-      <c r="BA3" s="26"/>
-      <c r="BB3" s="26"/>
-      <c r="BC3" s="26"/>
-      <c r="BD3" s="26"/>
-      <c r="BE3" s="26"/>
-      <c r="BF3" s="26"/>
-      <c r="BG3" s="26"/>
-      <c r="BH3" s="26"/>
-      <c r="BI3" s="26"/>
-      <c r="BJ3" s="26"/>
-      <c r="BK3" s="26"/>
-      <c r="BL3" s="26"/>
-      <c r="BM3" s="26"/>
-      <c r="BN3" s="26"/>
-      <c r="BO3" s="26"/>
-      <c r="BP3" s="26"/>
-      <c r="BQ3" s="27"/>
-      <c r="BR3" s="16" t="s">
+      <c r="AX3" s="18"/>
+      <c r="AY3" s="18"/>
+      <c r="AZ3" s="18"/>
+      <c r="BA3" s="18"/>
+      <c r="BB3" s="18"/>
+      <c r="BC3" s="18"/>
+      <c r="BD3" s="18"/>
+      <c r="BE3" s="18"/>
+      <c r="BF3" s="18"/>
+      <c r="BG3" s="18"/>
+      <c r="BH3" s="18"/>
+      <c r="BI3" s="18"/>
+      <c r="BJ3" s="18"/>
+      <c r="BK3" s="18"/>
+      <c r="BL3" s="18"/>
+      <c r="BM3" s="18"/>
+      <c r="BN3" s="18"/>
+      <c r="BO3" s="18"/>
+      <c r="BP3" s="18"/>
+      <c r="BQ3" s="19"/>
+      <c r="BR3" s="26" t="s">
         <v>0</v>
       </c>
       <c r="BT3" s="6"/>
@@ -1632,72 +1581,36 @@
       <c r="BZ3" s="6"/>
     </row>
     <row r="4" spans="1:78" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="17"/>
-      <c r="C4" s="34"/>
-      <c r="D4" s="34"/>
-      <c r="E4" s="38"/>
-      <c r="F4" s="39"/>
-      <c r="G4" s="39"/>
-      <c r="H4" s="39"/>
-      <c r="I4" s="39"/>
-      <c r="J4" s="39"/>
-      <c r="K4" s="39"/>
-      <c r="L4" s="39"/>
-      <c r="M4" s="39"/>
-      <c r="N4" s="39"/>
-      <c r="O4" s="39"/>
-      <c r="P4" s="39"/>
-      <c r="Q4" s="39"/>
-      <c r="R4" s="39"/>
-      <c r="S4" s="39"/>
-      <c r="T4" s="39"/>
-      <c r="U4" s="39"/>
-      <c r="V4" s="39"/>
-      <c r="W4" s="39"/>
-      <c r="AA4" s="38"/>
-      <c r="AB4" s="39"/>
-      <c r="AC4" s="39"/>
-      <c r="AD4" s="39"/>
-      <c r="AE4" s="39"/>
-      <c r="AF4" s="39"/>
-      <c r="AG4" s="39"/>
-      <c r="AH4" s="39"/>
-      <c r="AI4" s="39"/>
-      <c r="AJ4" s="39"/>
-      <c r="AK4" s="39"/>
-      <c r="AL4" s="39"/>
-      <c r="AM4" s="39"/>
-      <c r="AN4" s="39"/>
-      <c r="AO4" s="39"/>
-      <c r="AP4" s="39"/>
-      <c r="AQ4" s="39"/>
-      <c r="AR4" s="39"/>
-      <c r="AS4" s="39"/>
-      <c r="AT4" s="34"/>
-      <c r="AU4" s="34"/>
-      <c r="AV4" s="34"/>
-      <c r="AW4" s="28"/>
-      <c r="AX4" s="29"/>
-      <c r="AY4" s="29"/>
-      <c r="AZ4" s="29"/>
-      <c r="BA4" s="29"/>
-      <c r="BB4" s="29"/>
-      <c r="BC4" s="29"/>
-      <c r="BD4" s="29"/>
-      <c r="BE4" s="29"/>
-      <c r="BF4" s="29"/>
-      <c r="BG4" s="29"/>
-      <c r="BH4" s="29"/>
-      <c r="BI4" s="29"/>
-      <c r="BJ4" s="29"/>
-      <c r="BK4" s="29"/>
-      <c r="BL4" s="29"/>
-      <c r="BM4" s="29"/>
-      <c r="BN4" s="29"/>
-      <c r="BO4" s="29"/>
-      <c r="BP4" s="29"/>
-      <c r="BQ4" s="30"/>
-      <c r="BR4" s="17"/>
+      <c r="B4" s="31"/>
+      <c r="C4" s="32"/>
+      <c r="D4" s="32"/>
+      <c r="E4" s="11"/>
+      <c r="AA4" s="11"/>
+      <c r="AT4" s="32"/>
+      <c r="AU4" s="32"/>
+      <c r="AV4" s="32"/>
+      <c r="AW4" s="20"/>
+      <c r="AX4" s="21"/>
+      <c r="AY4" s="21"/>
+      <c r="AZ4" s="21"/>
+      <c r="BA4" s="21"/>
+      <c r="BB4" s="21"/>
+      <c r="BC4" s="21"/>
+      <c r="BD4" s="21"/>
+      <c r="BE4" s="21"/>
+      <c r="BF4" s="21"/>
+      <c r="BG4" s="21"/>
+      <c r="BH4" s="21"/>
+      <c r="BI4" s="21"/>
+      <c r="BJ4" s="21"/>
+      <c r="BK4" s="21"/>
+      <c r="BL4" s="21"/>
+      <c r="BM4" s="21"/>
+      <c r="BN4" s="21"/>
+      <c r="BO4" s="21"/>
+      <c r="BP4" s="21"/>
+      <c r="BQ4" s="22"/>
+      <c r="BR4" s="31"/>
       <c r="BT4" s="6"/>
       <c r="BU4" s="6"/>
       <c r="BV4" s="6"/>
@@ -1707,88 +1620,50 @@
       <c r="BZ4" s="6"/>
     </row>
     <row r="5" spans="1:78" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B5" s="17"/>
-      <c r="C5" s="34"/>
-      <c r="D5" s="34"/>
-      <c r="E5" s="39"/>
-      <c r="F5" s="39"/>
-      <c r="G5" s="39"/>
-      <c r="H5" s="39"/>
-      <c r="I5" s="39"/>
-      <c r="J5" s="39"/>
-      <c r="K5" s="39"/>
-      <c r="L5" s="39"/>
-      <c r="M5" s="39"/>
-      <c r="N5" s="39"/>
-      <c r="O5" s="39"/>
-      <c r="P5" s="39"/>
-      <c r="Q5" s="39"/>
-      <c r="R5" s="39"/>
-      <c r="S5" s="39"/>
-      <c r="T5" s="39"/>
-      <c r="U5" s="39"/>
-      <c r="V5" s="39"/>
-      <c r="W5" s="39"/>
-      <c r="AA5" s="39"/>
-      <c r="AB5" s="39"/>
-      <c r="AC5" s="39"/>
-      <c r="AD5" s="39"/>
-      <c r="AE5" s="39"/>
-      <c r="AF5" s="39"/>
-      <c r="AG5" s="39"/>
-      <c r="AH5" s="39"/>
-      <c r="AI5" s="39"/>
-      <c r="AJ5" s="39"/>
-      <c r="AK5" s="39"/>
-      <c r="AL5" s="39"/>
-      <c r="AM5" s="39"/>
-      <c r="AN5" s="39"/>
-      <c r="AO5" s="39"/>
-      <c r="AP5" s="39"/>
-      <c r="AQ5" s="39"/>
-      <c r="AR5" s="39"/>
-      <c r="AS5" s="39"/>
-      <c r="AT5" s="34"/>
-      <c r="AU5" s="34"/>
-      <c r="AV5" s="34"/>
-      <c r="AW5" s="25" t="s">
+      <c r="B5" s="31"/>
+      <c r="C5" s="32"/>
+      <c r="D5" s="32"/>
+      <c r="AT5" s="32"/>
+      <c r="AU5" s="32"/>
+      <c r="AV5" s="32"/>
+      <c r="AW5" s="17" t="s">
         <v>227</v>
       </c>
-      <c r="AX5" s="27"/>
-      <c r="AY5" s="25" t="s">
+      <c r="AX5" s="19"/>
+      <c r="AY5" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="AZ5" s="26"/>
-      <c r="BA5" s="26"/>
-      <c r="BB5" s="27"/>
-      <c r="BC5" s="25" t="s">
+      <c r="AZ5" s="18"/>
+      <c r="BA5" s="18"/>
+      <c r="BB5" s="19"/>
+      <c r="BC5" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="BD5" s="26"/>
-      <c r="BE5" s="27"/>
-      <c r="BF5" s="25" t="s">
+      <c r="BD5" s="18"/>
+      <c r="BE5" s="19"/>
+      <c r="BF5" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="BG5" s="26"/>
-      <c r="BH5" s="26"/>
-      <c r="BI5" s="26"/>
-      <c r="BJ5" s="26"/>
-      <c r="BK5" s="27"/>
-      <c r="BL5" s="16" t="s">
+      <c r="BG5" s="18"/>
+      <c r="BH5" s="18"/>
+      <c r="BI5" s="18"/>
+      <c r="BJ5" s="18"/>
+      <c r="BK5" s="19"/>
+      <c r="BL5" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="BM5" s="25" t="s">
+      <c r="BM5" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="BN5" s="26"/>
-      <c r="BO5" s="27"/>
-      <c r="BP5" s="16" t="s">
+      <c r="BN5" s="18"/>
+      <c r="BO5" s="19"/>
+      <c r="BP5" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="BQ5" s="16" t="s">
+      <c r="BQ5" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="BR5" s="17"/>
+      <c r="BR5" s="31"/>
       <c r="BT5" s="6"/>
       <c r="BU5" s="6"/>
       <c r="BV5" s="6"/>
@@ -1798,70 +1673,32 @@
       <c r="BZ5" s="6"/>
     </row>
     <row r="6" spans="1:78" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B6" s="17"/>
-      <c r="E6" s="39"/>
-      <c r="F6" s="39"/>
-      <c r="G6" s="39"/>
-      <c r="H6" s="39"/>
-      <c r="I6" s="39"/>
-      <c r="J6" s="39"/>
-      <c r="K6" s="39"/>
-      <c r="L6" s="39"/>
-      <c r="M6" s="39"/>
-      <c r="N6" s="39"/>
-      <c r="O6" s="39"/>
-      <c r="P6" s="39"/>
-      <c r="Q6" s="39"/>
-      <c r="R6" s="39"/>
-      <c r="S6" s="39"/>
-      <c r="T6" s="39"/>
-      <c r="U6" s="39"/>
-      <c r="V6" s="39"/>
-      <c r="W6" s="39"/>
-      <c r="AA6" s="39"/>
-      <c r="AB6" s="39"/>
-      <c r="AC6" s="39"/>
-      <c r="AD6" s="39"/>
-      <c r="AE6" s="39"/>
-      <c r="AF6" s="39"/>
-      <c r="AG6" s="39"/>
-      <c r="AH6" s="39"/>
-      <c r="AI6" s="39"/>
-      <c r="AJ6" s="39"/>
-      <c r="AK6" s="39"/>
-      <c r="AL6" s="39"/>
-      <c r="AM6" s="39"/>
-      <c r="AN6" s="39"/>
-      <c r="AO6" s="39"/>
-      <c r="AP6" s="39"/>
-      <c r="AQ6" s="39"/>
-      <c r="AR6" s="39"/>
-      <c r="AS6" s="39"/>
-      <c r="AT6" s="34"/>
-      <c r="AU6" s="34"/>
-      <c r="AV6" s="34"/>
-      <c r="AW6" s="28"/>
-      <c r="AX6" s="30"/>
-      <c r="AY6" s="28"/>
-      <c r="AZ6" s="29"/>
-      <c r="BA6" s="29"/>
-      <c r="BB6" s="30"/>
-      <c r="BC6" s="28"/>
-      <c r="BD6" s="29"/>
-      <c r="BE6" s="30"/>
-      <c r="BF6" s="28"/>
-      <c r="BG6" s="29"/>
-      <c r="BH6" s="29"/>
-      <c r="BI6" s="29"/>
-      <c r="BJ6" s="29"/>
-      <c r="BK6" s="30"/>
-      <c r="BL6" s="18"/>
-      <c r="BM6" s="28"/>
-      <c r="BN6" s="29"/>
-      <c r="BO6" s="30"/>
-      <c r="BP6" s="18"/>
-      <c r="BQ6" s="18"/>
-      <c r="BR6" s="17"/>
+      <c r="B6" s="31"/>
+      <c r="AT6" s="32"/>
+      <c r="AU6" s="32"/>
+      <c r="AV6" s="32"/>
+      <c r="AW6" s="20"/>
+      <c r="AX6" s="22"/>
+      <c r="AY6" s="20"/>
+      <c r="AZ6" s="21"/>
+      <c r="BA6" s="21"/>
+      <c r="BB6" s="22"/>
+      <c r="BC6" s="20"/>
+      <c r="BD6" s="21"/>
+      <c r="BE6" s="22"/>
+      <c r="BF6" s="20"/>
+      <c r="BG6" s="21"/>
+      <c r="BH6" s="21"/>
+      <c r="BI6" s="21"/>
+      <c r="BJ6" s="21"/>
+      <c r="BK6" s="22"/>
+      <c r="BL6" s="27"/>
+      <c r="BM6" s="20"/>
+      <c r="BN6" s="21"/>
+      <c r="BO6" s="22"/>
+      <c r="BP6" s="27"/>
+      <c r="BQ6" s="27"/>
+      <c r="BR6" s="31"/>
       <c r="BT6" s="6"/>
       <c r="BU6" s="6"/>
       <c r="BV6" s="6"/>
@@ -1871,92 +1708,80 @@
       <c r="BZ6" s="6"/>
     </row>
     <row r="7" spans="1:78" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B7" s="17"/>
-      <c r="E7" s="14" t="s">
+      <c r="B7" s="31"/>
+      <c r="E7" s="12" t="s">
         <v>232</v>
       </c>
-      <c r="F7" s="15"/>
-      <c r="G7" s="15"/>
-      <c r="H7" s="15"/>
-      <c r="I7" s="15"/>
-      <c r="J7" s="15"/>
-      <c r="K7" s="15"/>
-      <c r="L7" s="15"/>
-      <c r="M7" s="15"/>
-      <c r="N7" s="15"/>
-      <c r="O7" s="15"/>
-      <c r="P7" s="15"/>
-      <c r="Q7" s="15"/>
-      <c r="R7" s="15"/>
-      <c r="T7" s="14" t="s">
+      <c r="F7" s="13"/>
+      <c r="G7" s="13"/>
+      <c r="H7" s="13"/>
+      <c r="I7" s="13"/>
+      <c r="J7" s="13"/>
+      <c r="K7" s="13"/>
+      <c r="L7" s="13"/>
+      <c r="M7" s="13"/>
+      <c r="N7" s="13"/>
+      <c r="O7" s="13"/>
+      <c r="P7" s="13"/>
+      <c r="Q7" s="13"/>
+      <c r="R7" s="13"/>
+      <c r="T7" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="U7" s="15"/>
-      <c r="V7" s="15"/>
-      <c r="W7" s="15"/>
-      <c r="X7" s="15"/>
-      <c r="Y7" s="15"/>
-      <c r="Z7" s="15"/>
-      <c r="AA7" s="15"/>
-      <c r="AB7" s="15"/>
-      <c r="AC7" s="15"/>
-      <c r="AD7" s="15"/>
-      <c r="AE7" s="15"/>
-      <c r="AF7" s="15"/>
-      <c r="AG7" s="15"/>
-      <c r="AH7" s="39"/>
-      <c r="AI7" s="39"/>
-      <c r="AJ7" s="39"/>
-      <c r="AK7" s="39"/>
-      <c r="AL7" s="39"/>
-      <c r="AM7" s="39"/>
-      <c r="AN7" s="39"/>
-      <c r="AO7" s="39"/>
-      <c r="AP7" s="39"/>
-      <c r="AQ7" s="39"/>
-      <c r="AR7" s="39"/>
-      <c r="AS7" s="39"/>
-      <c r="AT7" s="34"/>
-      <c r="AU7" s="34"/>
-      <c r="AV7" s="34"/>
-      <c r="AW7" s="11" t="s">
+      <c r="U7" s="13"/>
+      <c r="V7" s="13"/>
+      <c r="W7" s="13"/>
+      <c r="X7" s="13"/>
+      <c r="Y7" s="13"/>
+      <c r="Z7" s="13"/>
+      <c r="AA7" s="13"/>
+      <c r="AB7" s="13"/>
+      <c r="AC7" s="13"/>
+      <c r="AD7" s="13"/>
+      <c r="AE7" s="13"/>
+      <c r="AF7" s="13"/>
+      <c r="AG7" s="13"/>
+      <c r="AT7" s="32"/>
+      <c r="AU7" s="32"/>
+      <c r="AV7" s="32"/>
+      <c r="AW7" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="AX7" s="13"/>
-      <c r="AY7" s="11" t="s">
+      <c r="AX7" s="16"/>
+      <c r="AY7" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="AZ7" s="12"/>
-      <c r="BA7" s="12"/>
-      <c r="BB7" s="13"/>
-      <c r="BC7" s="11" t="s">
+      <c r="AZ7" s="15"/>
+      <c r="BA7" s="15"/>
+      <c r="BB7" s="16"/>
+      <c r="BC7" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="BD7" s="12"/>
-      <c r="BE7" s="13"/>
-      <c r="BF7" s="11" t="s">
+      <c r="BD7" s="15"/>
+      <c r="BE7" s="16"/>
+      <c r="BF7" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="BG7" s="12"/>
-      <c r="BH7" s="12"/>
-      <c r="BI7" s="12"/>
-      <c r="BJ7" s="12"/>
-      <c r="BK7" s="13"/>
+      <c r="BG7" s="15"/>
+      <c r="BH7" s="15"/>
+      <c r="BI7" s="15"/>
+      <c r="BJ7" s="15"/>
+      <c r="BK7" s="16"/>
       <c r="BL7" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="BM7" s="11" t="s">
+      <c r="BM7" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="BN7" s="12"/>
-      <c r="BO7" s="13"/>
+      <c r="BN7" s="15"/>
+      <c r="BO7" s="16"/>
       <c r="BP7" s="4" t="s">
         <v>19</v>
       </c>
       <c r="BQ7" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="BR7" s="17"/>
+      <c r="BR7" s="31"/>
       <c r="BT7" s="6"/>
       <c r="BU7" s="6"/>
       <c r="BV7" s="6"/>
@@ -1966,88 +1791,76 @@
       <c r="BZ7" s="6"/>
     </row>
     <row r="8" spans="1:78" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B8" s="17"/>
-      <c r="E8" s="15"/>
-      <c r="F8" s="15"/>
-      <c r="G8" s="15"/>
-      <c r="H8" s="15"/>
-      <c r="I8" s="15"/>
-      <c r="J8" s="15"/>
-      <c r="K8" s="15"/>
-      <c r="L8" s="15"/>
-      <c r="M8" s="15"/>
-      <c r="N8" s="15"/>
-      <c r="O8" s="15"/>
-      <c r="P8" s="15"/>
-      <c r="Q8" s="15"/>
-      <c r="R8" s="15"/>
-      <c r="T8" s="15"/>
-      <c r="U8" s="15"/>
-      <c r="V8" s="15"/>
-      <c r="W8" s="15"/>
-      <c r="X8" s="15"/>
-      <c r="Y8" s="15"/>
-      <c r="Z8" s="15"/>
-      <c r="AA8" s="15"/>
-      <c r="AB8" s="15"/>
-      <c r="AC8" s="15"/>
-      <c r="AD8" s="15"/>
-      <c r="AE8" s="15"/>
-      <c r="AF8" s="15"/>
-      <c r="AG8" s="15"/>
-      <c r="AH8" s="39"/>
-      <c r="AI8" s="39"/>
-      <c r="AJ8" s="39"/>
-      <c r="AK8" s="39"/>
-      <c r="AL8" s="39"/>
-      <c r="AM8" s="39"/>
-      <c r="AN8" s="39"/>
-      <c r="AO8" s="39"/>
-      <c r="AP8" s="39"/>
-      <c r="AQ8" s="39"/>
-      <c r="AR8" s="39"/>
-      <c r="AS8" s="39"/>
-      <c r="AT8" s="34"/>
-      <c r="AU8" s="34"/>
-      <c r="AV8" s="34"/>
-      <c r="AW8" s="11" t="s">
+      <c r="B8" s="31"/>
+      <c r="E8" s="13"/>
+      <c r="F8" s="13"/>
+      <c r="G8" s="13"/>
+      <c r="H8" s="13"/>
+      <c r="I8" s="13"/>
+      <c r="J8" s="13"/>
+      <c r="K8" s="13"/>
+      <c r="L8" s="13"/>
+      <c r="M8" s="13"/>
+      <c r="N8" s="13"/>
+      <c r="O8" s="13"/>
+      <c r="P8" s="13"/>
+      <c r="Q8" s="13"/>
+      <c r="R8" s="13"/>
+      <c r="T8" s="13"/>
+      <c r="U8" s="13"/>
+      <c r="V8" s="13"/>
+      <c r="W8" s="13"/>
+      <c r="X8" s="13"/>
+      <c r="Y8" s="13"/>
+      <c r="Z8" s="13"/>
+      <c r="AA8" s="13"/>
+      <c r="AB8" s="13"/>
+      <c r="AC8" s="13"/>
+      <c r="AD8" s="13"/>
+      <c r="AE8" s="13"/>
+      <c r="AF8" s="13"/>
+      <c r="AG8" s="13"/>
+      <c r="AT8" s="32"/>
+      <c r="AU8" s="32"/>
+      <c r="AV8" s="32"/>
+      <c r="AW8" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="AX8" s="13"/>
-      <c r="AY8" s="11" t="s">
+      <c r="AX8" s="16"/>
+      <c r="AY8" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="AZ8" s="12"/>
-      <c r="BA8" s="12"/>
-      <c r="BB8" s="13"/>
-      <c r="BC8" s="11" t="s">
+      <c r="AZ8" s="15"/>
+      <c r="BA8" s="15"/>
+      <c r="BB8" s="16"/>
+      <c r="BC8" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="BD8" s="12"/>
-      <c r="BE8" s="13"/>
-      <c r="BF8" s="11" t="s">
+      <c r="BD8" s="15"/>
+      <c r="BE8" s="16"/>
+      <c r="BF8" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="BG8" s="12"/>
-      <c r="BH8" s="12"/>
-      <c r="BI8" s="12"/>
-      <c r="BJ8" s="12"/>
-      <c r="BK8" s="13"/>
+      <c r="BG8" s="15"/>
+      <c r="BH8" s="15"/>
+      <c r="BI8" s="15"/>
+      <c r="BJ8" s="15"/>
+      <c r="BK8" s="16"/>
       <c r="BL8" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="BM8" s="11" t="s">
+      <c r="BM8" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="BN8" s="12"/>
-      <c r="BO8" s="13"/>
+      <c r="BN8" s="15"/>
+      <c r="BO8" s="16"/>
       <c r="BP8" s="8" t="s">
         <v>27</v>
       </c>
       <c r="BQ8" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="BR8" s="17"/>
+      <c r="BR8" s="31"/>
       <c r="BT8" s="6"/>
       <c r="BU8" s="6"/>
       <c r="BV8" s="6"/>
@@ -2057,88 +1870,76 @@
       <c r="BZ8" s="6"/>
     </row>
     <row r="9" spans="1:78" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B9" s="17"/>
-      <c r="E9" s="15"/>
-      <c r="F9" s="15"/>
-      <c r="G9" s="15"/>
-      <c r="H9" s="15"/>
-      <c r="I9" s="15"/>
-      <c r="J9" s="15"/>
-      <c r="K9" s="15"/>
-      <c r="L9" s="15"/>
-      <c r="M9" s="15"/>
-      <c r="N9" s="15"/>
-      <c r="O9" s="15"/>
-      <c r="P9" s="15"/>
-      <c r="Q9" s="15"/>
-      <c r="R9" s="15"/>
-      <c r="T9" s="15"/>
-      <c r="U9" s="15"/>
-      <c r="V9" s="15"/>
-      <c r="W9" s="15"/>
-      <c r="X9" s="15"/>
-      <c r="Y9" s="15"/>
-      <c r="Z9" s="15"/>
-      <c r="AA9" s="15"/>
-      <c r="AB9" s="15"/>
-      <c r="AC9" s="15"/>
-      <c r="AD9" s="15"/>
-      <c r="AE9" s="15"/>
-      <c r="AF9" s="15"/>
-      <c r="AG9" s="15"/>
-      <c r="AH9" s="39"/>
-      <c r="AI9" s="39"/>
-      <c r="AJ9" s="39"/>
-      <c r="AK9" s="39"/>
-      <c r="AL9" s="39"/>
-      <c r="AM9" s="39"/>
-      <c r="AN9" s="39"/>
-      <c r="AO9" s="39"/>
-      <c r="AP9" s="39"/>
-      <c r="AQ9" s="39"/>
-      <c r="AR9" s="39"/>
-      <c r="AS9" s="39"/>
-      <c r="AT9" s="34"/>
-      <c r="AU9" s="34"/>
-      <c r="AV9" s="34"/>
-      <c r="AW9" s="11" t="s">
+      <c r="B9" s="31"/>
+      <c r="E9" s="13"/>
+      <c r="F9" s="13"/>
+      <c r="G9" s="13"/>
+      <c r="H9" s="13"/>
+      <c r="I9" s="13"/>
+      <c r="J9" s="13"/>
+      <c r="K9" s="13"/>
+      <c r="L9" s="13"/>
+      <c r="M9" s="13"/>
+      <c r="N9" s="13"/>
+      <c r="O9" s="13"/>
+      <c r="P9" s="13"/>
+      <c r="Q9" s="13"/>
+      <c r="R9" s="13"/>
+      <c r="T9" s="13"/>
+      <c r="U9" s="13"/>
+      <c r="V9" s="13"/>
+      <c r="W9" s="13"/>
+      <c r="X9" s="13"/>
+      <c r="Y9" s="13"/>
+      <c r="Z9" s="13"/>
+      <c r="AA9" s="13"/>
+      <c r="AB9" s="13"/>
+      <c r="AC9" s="13"/>
+      <c r="AD9" s="13"/>
+      <c r="AE9" s="13"/>
+      <c r="AF9" s="13"/>
+      <c r="AG9" s="13"/>
+      <c r="AT9" s="32"/>
+      <c r="AU9" s="32"/>
+      <c r="AV9" s="32"/>
+      <c r="AW9" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="AX9" s="13"/>
-      <c r="AY9" s="11" t="s">
+      <c r="AX9" s="16"/>
+      <c r="AY9" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="AZ9" s="12"/>
-      <c r="BA9" s="12"/>
-      <c r="BB9" s="13"/>
-      <c r="BC9" s="11" t="s">
+      <c r="AZ9" s="15"/>
+      <c r="BA9" s="15"/>
+      <c r="BB9" s="16"/>
+      <c r="BC9" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="BD9" s="12"/>
-      <c r="BE9" s="13"/>
-      <c r="BF9" s="11" t="s">
+      <c r="BD9" s="15"/>
+      <c r="BE9" s="16"/>
+      <c r="BF9" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="BG9" s="12"/>
-      <c r="BH9" s="12"/>
-      <c r="BI9" s="12"/>
-      <c r="BJ9" s="12"/>
-      <c r="BK9" s="13"/>
+      <c r="BG9" s="15"/>
+      <c r="BH9" s="15"/>
+      <c r="BI9" s="15"/>
+      <c r="BJ9" s="15"/>
+      <c r="BK9" s="16"/>
       <c r="BL9" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="BM9" s="11" t="s">
+      <c r="BM9" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="BN9" s="12"/>
-      <c r="BO9" s="13"/>
+      <c r="BN9" s="15"/>
+      <c r="BO9" s="16"/>
       <c r="BP9" s="8" t="s">
         <v>35</v>
       </c>
       <c r="BQ9" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="BR9" s="17"/>
+      <c r="BR9" s="31"/>
       <c r="BT9" s="6"/>
       <c r="BU9" s="6"/>
       <c r="BV9" s="6"/>
@@ -2148,88 +1949,76 @@
       <c r="BZ9" s="6"/>
     </row>
     <row r="10" spans="1:78" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B10" s="17"/>
-      <c r="E10" s="15"/>
-      <c r="F10" s="15"/>
-      <c r="G10" s="15"/>
-      <c r="H10" s="15"/>
-      <c r="I10" s="15"/>
-      <c r="J10" s="15"/>
-      <c r="K10" s="15"/>
-      <c r="L10" s="15"/>
-      <c r="M10" s="15"/>
-      <c r="N10" s="15"/>
-      <c r="O10" s="15"/>
-      <c r="P10" s="15"/>
-      <c r="Q10" s="15"/>
-      <c r="R10" s="15"/>
-      <c r="T10" s="15"/>
-      <c r="U10" s="15"/>
-      <c r="V10" s="15"/>
-      <c r="W10" s="15"/>
-      <c r="X10" s="15"/>
-      <c r="Y10" s="15"/>
-      <c r="Z10" s="15"/>
-      <c r="AA10" s="15"/>
-      <c r="AB10" s="15"/>
-      <c r="AC10" s="15"/>
-      <c r="AD10" s="15"/>
-      <c r="AE10" s="15"/>
-      <c r="AF10" s="15"/>
-      <c r="AG10" s="15"/>
-      <c r="AH10" s="39"/>
-      <c r="AI10" s="39"/>
-      <c r="AJ10" s="39"/>
-      <c r="AK10" s="39"/>
-      <c r="AL10" s="39"/>
-      <c r="AM10" s="39"/>
-      <c r="AN10" s="39"/>
-      <c r="AO10" s="39"/>
-      <c r="AP10" s="39"/>
-      <c r="AQ10" s="39"/>
-      <c r="AR10" s="39"/>
-      <c r="AS10" s="39"/>
-      <c r="AT10" s="34"/>
-      <c r="AU10" s="34"/>
-      <c r="AV10" s="34"/>
-      <c r="AW10" s="11" t="s">
+      <c r="B10" s="31"/>
+      <c r="E10" s="13"/>
+      <c r="F10" s="13"/>
+      <c r="G10" s="13"/>
+      <c r="H10" s="13"/>
+      <c r="I10" s="13"/>
+      <c r="J10" s="13"/>
+      <c r="K10" s="13"/>
+      <c r="L10" s="13"/>
+      <c r="M10" s="13"/>
+      <c r="N10" s="13"/>
+      <c r="O10" s="13"/>
+      <c r="P10" s="13"/>
+      <c r="Q10" s="13"/>
+      <c r="R10" s="13"/>
+      <c r="T10" s="13"/>
+      <c r="U10" s="13"/>
+      <c r="V10" s="13"/>
+      <c r="W10" s="13"/>
+      <c r="X10" s="13"/>
+      <c r="Y10" s="13"/>
+      <c r="Z10" s="13"/>
+      <c r="AA10" s="13"/>
+      <c r="AB10" s="13"/>
+      <c r="AC10" s="13"/>
+      <c r="AD10" s="13"/>
+      <c r="AE10" s="13"/>
+      <c r="AF10" s="13"/>
+      <c r="AG10" s="13"/>
+      <c r="AT10" s="32"/>
+      <c r="AU10" s="32"/>
+      <c r="AV10" s="32"/>
+      <c r="AW10" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="AX10" s="13"/>
-      <c r="AY10" s="11" t="s">
+      <c r="AX10" s="16"/>
+      <c r="AY10" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="AZ10" s="12"/>
-      <c r="BA10" s="12"/>
-      <c r="BB10" s="13"/>
-      <c r="BC10" s="11" t="s">
+      <c r="AZ10" s="15"/>
+      <c r="BA10" s="15"/>
+      <c r="BB10" s="16"/>
+      <c r="BC10" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="BD10" s="12"/>
-      <c r="BE10" s="13"/>
-      <c r="BF10" s="11" t="s">
+      <c r="BD10" s="15"/>
+      <c r="BE10" s="16"/>
+      <c r="BF10" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="BG10" s="12"/>
-      <c r="BH10" s="12"/>
-      <c r="BI10" s="12"/>
-      <c r="BJ10" s="12"/>
-      <c r="BK10" s="13"/>
+      <c r="BG10" s="15"/>
+      <c r="BH10" s="15"/>
+      <c r="BI10" s="15"/>
+      <c r="BJ10" s="15"/>
+      <c r="BK10" s="16"/>
       <c r="BL10" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="BM10" s="11" t="s">
+      <c r="BM10" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="BN10" s="12"/>
-      <c r="BO10" s="13"/>
+      <c r="BN10" s="15"/>
+      <c r="BO10" s="16"/>
       <c r="BP10" s="8" t="s">
         <v>43</v>
       </c>
       <c r="BQ10" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="BR10" s="17"/>
+      <c r="BR10" s="31"/>
       <c r="BT10" s="6"/>
       <c r="BU10" s="6"/>
       <c r="BV10" s="6"/>
@@ -2239,88 +2028,76 @@
       <c r="BZ10" s="6"/>
     </row>
     <row r="11" spans="1:78" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B11" s="17"/>
-      <c r="E11" s="15"/>
-      <c r="F11" s="15"/>
-      <c r="G11" s="15"/>
-      <c r="H11" s="15"/>
-      <c r="I11" s="15"/>
-      <c r="J11" s="15"/>
-      <c r="K11" s="15"/>
-      <c r="L11" s="15"/>
-      <c r="M11" s="15"/>
-      <c r="N11" s="15"/>
-      <c r="O11" s="15"/>
-      <c r="P11" s="15"/>
-      <c r="Q11" s="15"/>
-      <c r="R11" s="15"/>
-      <c r="T11" s="15"/>
-      <c r="U11" s="15"/>
-      <c r="V11" s="15"/>
-      <c r="W11" s="15"/>
-      <c r="X11" s="15"/>
-      <c r="Y11" s="15"/>
-      <c r="Z11" s="15"/>
-      <c r="AA11" s="15"/>
-      <c r="AB11" s="15"/>
-      <c r="AC11" s="15"/>
-      <c r="AD11" s="15"/>
-      <c r="AE11" s="15"/>
-      <c r="AF11" s="15"/>
-      <c r="AG11" s="15"/>
-      <c r="AH11" s="39"/>
-      <c r="AI11" s="39"/>
-      <c r="AJ11" s="39"/>
-      <c r="AK11" s="39"/>
-      <c r="AL11" s="39"/>
-      <c r="AM11" s="39"/>
-      <c r="AN11" s="39"/>
-      <c r="AO11" s="39"/>
-      <c r="AP11" s="39"/>
-      <c r="AQ11" s="39"/>
-      <c r="AR11" s="39"/>
-      <c r="AS11" s="39"/>
-      <c r="AT11" s="34"/>
-      <c r="AU11" s="34"/>
-      <c r="AV11" s="34"/>
-      <c r="AW11" s="11" t="s">
+      <c r="B11" s="31"/>
+      <c r="E11" s="13"/>
+      <c r="F11" s="13"/>
+      <c r="G11" s="13"/>
+      <c r="H11" s="13"/>
+      <c r="I11" s="13"/>
+      <c r="J11" s="13"/>
+      <c r="K11" s="13"/>
+      <c r="L11" s="13"/>
+      <c r="M11" s="13"/>
+      <c r="N11" s="13"/>
+      <c r="O11" s="13"/>
+      <c r="P11" s="13"/>
+      <c r="Q11" s="13"/>
+      <c r="R11" s="13"/>
+      <c r="T11" s="13"/>
+      <c r="U11" s="13"/>
+      <c r="V11" s="13"/>
+      <c r="W11" s="13"/>
+      <c r="X11" s="13"/>
+      <c r="Y11" s="13"/>
+      <c r="Z11" s="13"/>
+      <c r="AA11" s="13"/>
+      <c r="AB11" s="13"/>
+      <c r="AC11" s="13"/>
+      <c r="AD11" s="13"/>
+      <c r="AE11" s="13"/>
+      <c r="AF11" s="13"/>
+      <c r="AG11" s="13"/>
+      <c r="AT11" s="32"/>
+      <c r="AU11" s="32"/>
+      <c r="AV11" s="32"/>
+      <c r="AW11" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="AX11" s="13"/>
-      <c r="AY11" s="11" t="s">
+      <c r="AX11" s="16"/>
+      <c r="AY11" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="AZ11" s="12"/>
-      <c r="BA11" s="12"/>
-      <c r="BB11" s="13"/>
-      <c r="BC11" s="11" t="s">
+      <c r="AZ11" s="15"/>
+      <c r="BA11" s="15"/>
+      <c r="BB11" s="16"/>
+      <c r="BC11" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="BD11" s="12"/>
-      <c r="BE11" s="13"/>
-      <c r="BF11" s="11" t="s">
+      <c r="BD11" s="15"/>
+      <c r="BE11" s="16"/>
+      <c r="BF11" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="BG11" s="12"/>
-      <c r="BH11" s="12"/>
-      <c r="BI11" s="12"/>
-      <c r="BJ11" s="12"/>
-      <c r="BK11" s="13"/>
+      <c r="BG11" s="15"/>
+      <c r="BH11" s="15"/>
+      <c r="BI11" s="15"/>
+      <c r="BJ11" s="15"/>
+      <c r="BK11" s="16"/>
       <c r="BL11" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="BM11" s="11" t="s">
+      <c r="BM11" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="BN11" s="12"/>
-      <c r="BO11" s="13"/>
+      <c r="BN11" s="15"/>
+      <c r="BO11" s="16"/>
       <c r="BP11" s="10" t="s">
         <v>51</v>
       </c>
       <c r="BQ11" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="BR11" s="17"/>
+      <c r="BR11" s="31"/>
       <c r="BT11" s="6"/>
       <c r="BU11" s="6"/>
       <c r="BV11" s="6"/>
@@ -2330,57 +2107,45 @@
       <c r="BZ11" s="6"/>
     </row>
     <row r="12" spans="1:78" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B12" s="17"/>
-      <c r="AH12" s="39"/>
-      <c r="AI12" s="39"/>
-      <c r="AJ12" s="39"/>
-      <c r="AK12" s="39"/>
-      <c r="AL12" s="39"/>
-      <c r="AM12" s="39"/>
-      <c r="AN12" s="39"/>
-      <c r="AO12" s="39"/>
-      <c r="AP12" s="39"/>
-      <c r="AQ12" s="39"/>
-      <c r="AR12" s="39"/>
-      <c r="AS12" s="39"/>
-      <c r="AW12" s="11" t="s">
+      <c r="B12" s="31"/>
+      <c r="AW12" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="AX12" s="13"/>
-      <c r="AY12" s="11" t="s">
+      <c r="AX12" s="16"/>
+      <c r="AY12" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="AZ12" s="12"/>
-      <c r="BA12" s="12"/>
-      <c r="BB12" s="13"/>
-      <c r="BC12" s="11" t="s">
+      <c r="AZ12" s="15"/>
+      <c r="BA12" s="15"/>
+      <c r="BB12" s="16"/>
+      <c r="BC12" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="BD12" s="12"/>
-      <c r="BE12" s="13"/>
-      <c r="BF12" s="11" t="s">
+      <c r="BD12" s="15"/>
+      <c r="BE12" s="16"/>
+      <c r="BF12" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="BG12" s="12"/>
-      <c r="BH12" s="12"/>
-      <c r="BI12" s="12"/>
-      <c r="BJ12" s="12"/>
-      <c r="BK12" s="13"/>
+      <c r="BG12" s="15"/>
+      <c r="BH12" s="15"/>
+      <c r="BI12" s="15"/>
+      <c r="BJ12" s="15"/>
+      <c r="BK12" s="16"/>
       <c r="BL12" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="BM12" s="11" t="s">
+      <c r="BM12" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="BN12" s="12"/>
-      <c r="BO12" s="13"/>
+      <c r="BN12" s="15"/>
+      <c r="BO12" s="16"/>
       <c r="BP12" s="8" t="s">
         <v>59</v>
       </c>
       <c r="BQ12" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="BR12" s="17"/>
+      <c r="BR12" s="31"/>
       <c r="BT12" s="6"/>
       <c r="BU12" s="6"/>
       <c r="BV12" s="6"/>
@@ -2390,57 +2155,45 @@
       <c r="BZ12" s="6"/>
     </row>
     <row r="13" spans="1:78" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B13" s="17"/>
-      <c r="AH13" s="39"/>
-      <c r="AI13" s="39"/>
-      <c r="AJ13" s="39"/>
-      <c r="AK13" s="39"/>
-      <c r="AL13" s="39"/>
-      <c r="AM13" s="39"/>
-      <c r="AN13" s="39"/>
-      <c r="AO13" s="39"/>
-      <c r="AP13" s="39"/>
-      <c r="AQ13" s="39"/>
-      <c r="AR13" s="39"/>
-      <c r="AS13" s="39"/>
-      <c r="AW13" s="11" t="s">
+      <c r="B13" s="31"/>
+      <c r="AW13" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="AX13" s="13"/>
-      <c r="AY13" s="11" t="s">
+      <c r="AX13" s="16"/>
+      <c r="AY13" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="AZ13" s="12"/>
-      <c r="BA13" s="12"/>
-      <c r="BB13" s="13"/>
-      <c r="BC13" s="11" t="s">
+      <c r="AZ13" s="15"/>
+      <c r="BA13" s="15"/>
+      <c r="BB13" s="16"/>
+      <c r="BC13" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="BD13" s="12"/>
-      <c r="BE13" s="13"/>
-      <c r="BF13" s="11" t="s">
+      <c r="BD13" s="15"/>
+      <c r="BE13" s="16"/>
+      <c r="BF13" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="BG13" s="12"/>
-      <c r="BH13" s="12"/>
-      <c r="BI13" s="12"/>
-      <c r="BJ13" s="12"/>
-      <c r="BK13" s="13"/>
+      <c r="BG13" s="15"/>
+      <c r="BH13" s="15"/>
+      <c r="BI13" s="15"/>
+      <c r="BJ13" s="15"/>
+      <c r="BK13" s="16"/>
       <c r="BL13" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="BM13" s="11" t="s">
+      <c r="BM13" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="BN13" s="12"/>
-      <c r="BO13" s="13"/>
+      <c r="BN13" s="15"/>
+      <c r="BO13" s="16"/>
       <c r="BP13" s="8" t="s">
         <v>67</v>
       </c>
       <c r="BQ13" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="BR13" s="17"/>
+      <c r="BR13" s="31"/>
       <c r="BT13" s="6"/>
       <c r="BU13" s="6"/>
       <c r="BV13" s="6"/>
@@ -2450,57 +2203,45 @@
       <c r="BZ13" s="6"/>
     </row>
     <row r="14" spans="1:78" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B14" s="17"/>
-      <c r="AH14" s="39"/>
-      <c r="AI14" s="39"/>
-      <c r="AJ14" s="39"/>
-      <c r="AK14" s="39"/>
-      <c r="AL14" s="39"/>
-      <c r="AM14" s="39"/>
-      <c r="AN14" s="39"/>
-      <c r="AO14" s="39"/>
-      <c r="AP14" s="39"/>
-      <c r="AQ14" s="39"/>
-      <c r="AR14" s="39"/>
-      <c r="AS14" s="39"/>
-      <c r="AW14" s="11" t="s">
+      <c r="B14" s="31"/>
+      <c r="AW14" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="AX14" s="13"/>
-      <c r="AY14" s="11" t="s">
+      <c r="AX14" s="16"/>
+      <c r="AY14" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="AZ14" s="12"/>
-      <c r="BA14" s="12"/>
-      <c r="BB14" s="13"/>
-      <c r="BC14" s="11" t="s">
+      <c r="AZ14" s="15"/>
+      <c r="BA14" s="15"/>
+      <c r="BB14" s="16"/>
+      <c r="BC14" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="BD14" s="12"/>
-      <c r="BE14" s="13"/>
-      <c r="BF14" s="11" t="s">
+      <c r="BD14" s="15"/>
+      <c r="BE14" s="16"/>
+      <c r="BF14" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="BG14" s="12"/>
-      <c r="BH14" s="12"/>
-      <c r="BI14" s="12"/>
-      <c r="BJ14" s="12"/>
-      <c r="BK14" s="13"/>
+      <c r="BG14" s="15"/>
+      <c r="BH14" s="15"/>
+      <c r="BI14" s="15"/>
+      <c r="BJ14" s="15"/>
+      <c r="BK14" s="16"/>
       <c r="BL14" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="BM14" s="11" t="s">
+      <c r="BM14" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="BN14" s="12"/>
-      <c r="BO14" s="13"/>
+      <c r="BN14" s="15"/>
+      <c r="BO14" s="16"/>
       <c r="BP14" s="8" t="s">
         <v>75</v>
       </c>
       <c r="BQ14" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="BR14" s="17"/>
+      <c r="BR14" s="31"/>
       <c r="BT14" s="6"/>
       <c r="BU14" s="6"/>
       <c r="BV14" s="6"/>
@@ -2510,57 +2251,45 @@
       <c r="BZ14" s="6"/>
     </row>
     <row r="15" spans="1:78" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B15" s="17"/>
-      <c r="AH15" s="39"/>
-      <c r="AI15" s="39"/>
-      <c r="AJ15" s="39"/>
-      <c r="AK15" s="39"/>
-      <c r="AL15" s="39"/>
-      <c r="AM15" s="39"/>
-      <c r="AN15" s="39"/>
-      <c r="AO15" s="39"/>
-      <c r="AP15" s="39"/>
-      <c r="AQ15" s="39"/>
-      <c r="AR15" s="39"/>
-      <c r="AS15" s="39"/>
-      <c r="AW15" s="11" t="s">
+      <c r="B15" s="31"/>
+      <c r="AW15" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="AX15" s="13"/>
-      <c r="AY15" s="11" t="s">
+      <c r="AX15" s="16"/>
+      <c r="AY15" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="AZ15" s="12"/>
-      <c r="BA15" s="12"/>
-      <c r="BB15" s="13"/>
-      <c r="BC15" s="11" t="s">
+      <c r="AZ15" s="15"/>
+      <c r="BA15" s="15"/>
+      <c r="BB15" s="16"/>
+      <c r="BC15" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="BD15" s="12"/>
-      <c r="BE15" s="13"/>
-      <c r="BF15" s="11" t="s">
+      <c r="BD15" s="15"/>
+      <c r="BE15" s="16"/>
+      <c r="BF15" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="BG15" s="12"/>
-      <c r="BH15" s="12"/>
-      <c r="BI15" s="12"/>
-      <c r="BJ15" s="12"/>
-      <c r="BK15" s="13"/>
+      <c r="BG15" s="15"/>
+      <c r="BH15" s="15"/>
+      <c r="BI15" s="15"/>
+      <c r="BJ15" s="15"/>
+      <c r="BK15" s="16"/>
       <c r="BL15" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="BM15" s="11" t="s">
+      <c r="BM15" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="BN15" s="12"/>
-      <c r="BO15" s="13"/>
+      <c r="BN15" s="15"/>
+      <c r="BO15" s="16"/>
       <c r="BP15" s="8" t="s">
         <v>83</v>
       </c>
       <c r="BQ15" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="BR15" s="17"/>
+      <c r="BR15" s="31"/>
       <c r="BT15" s="6"/>
       <c r="BU15" s="6"/>
       <c r="BV15" s="6"/>
@@ -2570,57 +2299,45 @@
       <c r="BZ15" s="6"/>
     </row>
     <row r="16" spans="1:78" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B16" s="18"/>
-      <c r="AH16" s="39"/>
-      <c r="AI16" s="39"/>
-      <c r="AJ16" s="39"/>
-      <c r="AK16" s="39"/>
-      <c r="AL16" s="39"/>
-      <c r="AM16" s="39"/>
-      <c r="AN16" s="39"/>
-      <c r="AO16" s="39"/>
-      <c r="AP16" s="39"/>
-      <c r="AQ16" s="39"/>
-      <c r="AR16" s="39"/>
-      <c r="AS16" s="39"/>
-      <c r="AW16" s="11" t="s">
+      <c r="B16" s="27"/>
+      <c r="AW16" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="AX16" s="13"/>
-      <c r="AY16" s="11" t="s">
+      <c r="AX16" s="16"/>
+      <c r="AY16" s="14" t="s">
         <v>87</v>
       </c>
-      <c r="AZ16" s="12"/>
-      <c r="BA16" s="12"/>
-      <c r="BB16" s="13"/>
-      <c r="BC16" s="11" t="s">
+      <c r="AZ16" s="15"/>
+      <c r="BA16" s="15"/>
+      <c r="BB16" s="16"/>
+      <c r="BC16" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="BD16" s="12"/>
-      <c r="BE16" s="13"/>
-      <c r="BF16" s="11" t="s">
+      <c r="BD16" s="15"/>
+      <c r="BE16" s="16"/>
+      <c r="BF16" s="14" t="s">
         <v>89</v>
       </c>
-      <c r="BG16" s="12"/>
-      <c r="BH16" s="12"/>
-      <c r="BI16" s="12"/>
-      <c r="BJ16" s="12"/>
-      <c r="BK16" s="13"/>
+      <c r="BG16" s="15"/>
+      <c r="BH16" s="15"/>
+      <c r="BI16" s="15"/>
+      <c r="BJ16" s="15"/>
+      <c r="BK16" s="16"/>
       <c r="BL16" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="BM16" s="11" t="s">
+      <c r="BM16" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="BN16" s="12"/>
-      <c r="BO16" s="13"/>
+      <c r="BN16" s="15"/>
+      <c r="BO16" s="16"/>
       <c r="BP16" s="8" t="s">
         <v>92</v>
       </c>
       <c r="BQ16" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="BR16" s="18"/>
+      <c r="BR16" s="27"/>
       <c r="BT16" s="6"/>
       <c r="BU16" s="6"/>
       <c r="BV16" s="6"/>
@@ -2630,91 +2347,79 @@
       <c r="BZ16" s="6"/>
     </row>
     <row r="17" spans="2:86" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B17" s="16" t="s">
+      <c r="B17" s="26" t="s">
         <v>85</v>
       </c>
-      <c r="E17" s="14" t="s">
+      <c r="E17" s="12" t="s">
         <v>233</v>
       </c>
-      <c r="F17" s="15"/>
-      <c r="G17" s="15"/>
-      <c r="H17" s="15"/>
-      <c r="I17" s="15"/>
-      <c r="J17" s="15"/>
-      <c r="K17" s="15"/>
-      <c r="L17" s="15"/>
-      <c r="M17" s="15"/>
-      <c r="N17" s="15"/>
-      <c r="O17" s="15"/>
-      <c r="P17" s="15"/>
-      <c r="Q17" s="15"/>
-      <c r="R17" s="15"/>
-      <c r="T17" s="14" t="s">
+      <c r="F17" s="13"/>
+      <c r="G17" s="13"/>
+      <c r="H17" s="13"/>
+      <c r="I17" s="13"/>
+      <c r="J17" s="13"/>
+      <c r="K17" s="13"/>
+      <c r="L17" s="13"/>
+      <c r="M17" s="13"/>
+      <c r="N17" s="13"/>
+      <c r="O17" s="13"/>
+      <c r="P17" s="13"/>
+      <c r="Q17" s="13"/>
+      <c r="R17" s="13"/>
+      <c r="T17" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="U17" s="15"/>
-      <c r="V17" s="15"/>
-      <c r="W17" s="15"/>
-      <c r="X17" s="15"/>
-      <c r="Y17" s="15"/>
-      <c r="Z17" s="15"/>
-      <c r="AA17" s="15"/>
-      <c r="AB17" s="15"/>
-      <c r="AC17" s="15"/>
-      <c r="AD17" s="15"/>
-      <c r="AE17" s="15"/>
-      <c r="AF17" s="15"/>
-      <c r="AG17" s="15"/>
-      <c r="AH17" s="39"/>
-      <c r="AI17" s="39"/>
-      <c r="AJ17" s="39"/>
-      <c r="AK17" s="39"/>
-      <c r="AL17" s="39"/>
-      <c r="AM17" s="39"/>
-      <c r="AN17" s="39"/>
-      <c r="AO17" s="39"/>
-      <c r="AP17" s="39"/>
-      <c r="AQ17" s="39"/>
-      <c r="AR17" s="39"/>
-      <c r="AS17" s="39"/>
-      <c r="AW17" s="11" t="s">
+      <c r="U17" s="13"/>
+      <c r="V17" s="13"/>
+      <c r="W17" s="13"/>
+      <c r="X17" s="13"/>
+      <c r="Y17" s="13"/>
+      <c r="Z17" s="13"/>
+      <c r="AA17" s="13"/>
+      <c r="AB17" s="13"/>
+      <c r="AC17" s="13"/>
+      <c r="AD17" s="13"/>
+      <c r="AE17" s="13"/>
+      <c r="AF17" s="13"/>
+      <c r="AG17" s="13"/>
+      <c r="AW17" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="AX17" s="13"/>
-      <c r="AY17" s="11" t="s">
+      <c r="AX17" s="16"/>
+      <c r="AY17" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="AZ17" s="12"/>
-      <c r="BA17" s="12"/>
-      <c r="BB17" s="13"/>
-      <c r="BC17" s="11" t="s">
+      <c r="AZ17" s="15"/>
+      <c r="BA17" s="15"/>
+      <c r="BB17" s="16"/>
+      <c r="BC17" s="14" t="s">
         <v>96</v>
       </c>
-      <c r="BD17" s="12"/>
-      <c r="BE17" s="13"/>
-      <c r="BF17" s="11" t="s">
+      <c r="BD17" s="15"/>
+      <c r="BE17" s="16"/>
+      <c r="BF17" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="BG17" s="12"/>
-      <c r="BH17" s="12"/>
-      <c r="BI17" s="12"/>
-      <c r="BJ17" s="12"/>
-      <c r="BK17" s="13"/>
+      <c r="BG17" s="15"/>
+      <c r="BH17" s="15"/>
+      <c r="BI17" s="15"/>
+      <c r="BJ17" s="15"/>
+      <c r="BK17" s="16"/>
       <c r="BL17" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="BM17" s="11" t="s">
+      <c r="BM17" s="14" t="s">
         <v>99</v>
       </c>
-      <c r="BN17" s="12"/>
-      <c r="BO17" s="13"/>
+      <c r="BN17" s="15"/>
+      <c r="BO17" s="16"/>
       <c r="BP17" s="8" t="s">
         <v>100</v>
       </c>
       <c r="BQ17" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="BR17" s="16" t="s">
+      <c r="BR17" s="26" t="s">
         <v>85</v>
       </c>
       <c r="BT17" s="6"/>
@@ -2726,85 +2431,73 @@
       <c r="BZ17" s="6"/>
     </row>
     <row r="18" spans="2:86" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B18" s="17"/>
-      <c r="E18" s="15"/>
-      <c r="F18" s="15"/>
-      <c r="G18" s="15"/>
-      <c r="H18" s="15"/>
-      <c r="I18" s="15"/>
-      <c r="J18" s="15"/>
-      <c r="K18" s="15"/>
-      <c r="L18" s="15"/>
-      <c r="M18" s="15"/>
-      <c r="N18" s="15"/>
-      <c r="O18" s="15"/>
-      <c r="P18" s="15"/>
-      <c r="Q18" s="15"/>
-      <c r="R18" s="15"/>
-      <c r="T18" s="15"/>
-      <c r="U18" s="15"/>
-      <c r="V18" s="15"/>
-      <c r="W18" s="15"/>
-      <c r="X18" s="15"/>
-      <c r="Y18" s="15"/>
-      <c r="Z18" s="15"/>
-      <c r="AA18" s="15"/>
-      <c r="AB18" s="15"/>
-      <c r="AC18" s="15"/>
-      <c r="AD18" s="15"/>
-      <c r="AE18" s="15"/>
-      <c r="AF18" s="15"/>
-      <c r="AG18" s="15"/>
-      <c r="AH18" s="39"/>
-      <c r="AI18" s="39"/>
-      <c r="AJ18" s="39"/>
-      <c r="AK18" s="39"/>
-      <c r="AL18" s="39"/>
-      <c r="AM18" s="39"/>
-      <c r="AN18" s="39"/>
-      <c r="AO18" s="39"/>
-      <c r="AP18" s="39"/>
-      <c r="AQ18" s="39"/>
-      <c r="AR18" s="39"/>
-      <c r="AS18" s="39"/>
-      <c r="AW18" s="11" t="s">
+      <c r="B18" s="31"/>
+      <c r="E18" s="13"/>
+      <c r="F18" s="13"/>
+      <c r="G18" s="13"/>
+      <c r="H18" s="13"/>
+      <c r="I18" s="13"/>
+      <c r="J18" s="13"/>
+      <c r="K18" s="13"/>
+      <c r="L18" s="13"/>
+      <c r="M18" s="13"/>
+      <c r="N18" s="13"/>
+      <c r="O18" s="13"/>
+      <c r="P18" s="13"/>
+      <c r="Q18" s="13"/>
+      <c r="R18" s="13"/>
+      <c r="T18" s="13"/>
+      <c r="U18" s="13"/>
+      <c r="V18" s="13"/>
+      <c r="W18" s="13"/>
+      <c r="X18" s="13"/>
+      <c r="Y18" s="13"/>
+      <c r="Z18" s="13"/>
+      <c r="AA18" s="13"/>
+      <c r="AB18" s="13"/>
+      <c r="AC18" s="13"/>
+      <c r="AD18" s="13"/>
+      <c r="AE18" s="13"/>
+      <c r="AF18" s="13"/>
+      <c r="AG18" s="13"/>
+      <c r="AW18" s="14" t="s">
         <v>102</v>
       </c>
-      <c r="AX18" s="13"/>
-      <c r="AY18" s="11" t="s">
+      <c r="AX18" s="16"/>
+      <c r="AY18" s="14" t="s">
         <v>103</v>
       </c>
-      <c r="AZ18" s="12"/>
-      <c r="BA18" s="12"/>
-      <c r="BB18" s="13"/>
-      <c r="BC18" s="11" t="s">
+      <c r="AZ18" s="15"/>
+      <c r="BA18" s="15"/>
+      <c r="BB18" s="16"/>
+      <c r="BC18" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="BD18" s="12"/>
-      <c r="BE18" s="13"/>
-      <c r="BF18" s="11" t="s">
+      <c r="BD18" s="15"/>
+      <c r="BE18" s="16"/>
+      <c r="BF18" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="BG18" s="12"/>
-      <c r="BH18" s="12"/>
-      <c r="BI18" s="12"/>
-      <c r="BJ18" s="12"/>
-      <c r="BK18" s="13"/>
+      <c r="BG18" s="15"/>
+      <c r="BH18" s="15"/>
+      <c r="BI18" s="15"/>
+      <c r="BJ18" s="15"/>
+      <c r="BK18" s="16"/>
       <c r="BL18" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="BM18" s="11" t="s">
+      <c r="BM18" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="BN18" s="12"/>
-      <c r="BO18" s="13"/>
+      <c r="BN18" s="15"/>
+      <c r="BO18" s="16"/>
       <c r="BP18" s="8" t="s">
         <v>108</v>
       </c>
       <c r="BQ18" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="BR18" s="17"/>
+      <c r="BR18" s="31"/>
       <c r="BT18" s="6"/>
       <c r="BU18" s="6"/>
       <c r="BV18" s="6"/>
@@ -2814,85 +2507,73 @@
       <c r="BZ18" s="6"/>
     </row>
     <row r="19" spans="2:86" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B19" s="17"/>
-      <c r="E19" s="15"/>
-      <c r="F19" s="15"/>
-      <c r="G19" s="15"/>
-      <c r="H19" s="15"/>
-      <c r="I19" s="15"/>
-      <c r="J19" s="15"/>
-      <c r="K19" s="15"/>
-      <c r="L19" s="15"/>
-      <c r="M19" s="15"/>
-      <c r="N19" s="15"/>
-      <c r="O19" s="15"/>
-      <c r="P19" s="15"/>
-      <c r="Q19" s="15"/>
-      <c r="R19" s="15"/>
-      <c r="T19" s="15"/>
-      <c r="U19" s="15"/>
-      <c r="V19" s="15"/>
-      <c r="W19" s="15"/>
-      <c r="X19" s="15"/>
-      <c r="Y19" s="15"/>
-      <c r="Z19" s="15"/>
-      <c r="AA19" s="15"/>
-      <c r="AB19" s="15"/>
-      <c r="AC19" s="15"/>
-      <c r="AD19" s="15"/>
-      <c r="AE19" s="15"/>
-      <c r="AF19" s="15"/>
-      <c r="AG19" s="15"/>
-      <c r="AH19" s="39"/>
-      <c r="AI19" s="39"/>
-      <c r="AJ19" s="39"/>
-      <c r="AK19" s="39"/>
-      <c r="AL19" s="39"/>
-      <c r="AM19" s="39"/>
-      <c r="AN19" s="39"/>
-      <c r="AO19" s="39"/>
-      <c r="AP19" s="39"/>
-      <c r="AQ19" s="39"/>
-      <c r="AR19" s="39"/>
-      <c r="AS19" s="39"/>
-      <c r="AW19" s="11" t="s">
+      <c r="B19" s="31"/>
+      <c r="E19" s="13"/>
+      <c r="F19" s="13"/>
+      <c r="G19" s="13"/>
+      <c r="H19" s="13"/>
+      <c r="I19" s="13"/>
+      <c r="J19" s="13"/>
+      <c r="K19" s="13"/>
+      <c r="L19" s="13"/>
+      <c r="M19" s="13"/>
+      <c r="N19" s="13"/>
+      <c r="O19" s="13"/>
+      <c r="P19" s="13"/>
+      <c r="Q19" s="13"/>
+      <c r="R19" s="13"/>
+      <c r="T19" s="13"/>
+      <c r="U19" s="13"/>
+      <c r="V19" s="13"/>
+      <c r="W19" s="13"/>
+      <c r="X19" s="13"/>
+      <c r="Y19" s="13"/>
+      <c r="Z19" s="13"/>
+      <c r="AA19" s="13"/>
+      <c r="AB19" s="13"/>
+      <c r="AC19" s="13"/>
+      <c r="AD19" s="13"/>
+      <c r="AE19" s="13"/>
+      <c r="AF19" s="13"/>
+      <c r="AG19" s="13"/>
+      <c r="AW19" s="14" t="s">
         <v>110</v>
       </c>
-      <c r="AX19" s="13"/>
-      <c r="AY19" s="11" t="s">
+      <c r="AX19" s="16"/>
+      <c r="AY19" s="14" t="s">
         <v>111</v>
       </c>
-      <c r="AZ19" s="12"/>
-      <c r="BA19" s="12"/>
-      <c r="BB19" s="13"/>
-      <c r="BC19" s="11" t="s">
+      <c r="AZ19" s="15"/>
+      <c r="BA19" s="15"/>
+      <c r="BB19" s="16"/>
+      <c r="BC19" s="14" t="s">
         <v>112</v>
       </c>
-      <c r="BD19" s="12"/>
-      <c r="BE19" s="13"/>
-      <c r="BF19" s="11" t="s">
+      <c r="BD19" s="15"/>
+      <c r="BE19" s="16"/>
+      <c r="BF19" s="14" t="s">
         <v>113</v>
       </c>
-      <c r="BG19" s="12"/>
-      <c r="BH19" s="12"/>
-      <c r="BI19" s="12"/>
-      <c r="BJ19" s="12"/>
-      <c r="BK19" s="13"/>
+      <c r="BG19" s="15"/>
+      <c r="BH19" s="15"/>
+      <c r="BI19" s="15"/>
+      <c r="BJ19" s="15"/>
+      <c r="BK19" s="16"/>
       <c r="BL19" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="BM19" s="11" t="s">
+      <c r="BM19" s="14" t="s">
         <v>115</v>
       </c>
-      <c r="BN19" s="12"/>
-      <c r="BO19" s="13"/>
+      <c r="BN19" s="15"/>
+      <c r="BO19" s="16"/>
       <c r="BP19" s="8" t="s">
         <v>116</v>
       </c>
       <c r="BQ19" s="8" t="s">
         <v>117</v>
       </c>
-      <c r="BR19" s="17"/>
+      <c r="BR19" s="31"/>
       <c r="BT19" s="6"/>
       <c r="BU19" s="6"/>
       <c r="BV19" s="6"/>
@@ -2902,85 +2583,73 @@
       <c r="BZ19" s="6"/>
     </row>
     <row r="20" spans="2:86" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B20" s="17"/>
-      <c r="E20" s="15"/>
-      <c r="F20" s="15"/>
-      <c r="G20" s="15"/>
-      <c r="H20" s="15"/>
-      <c r="I20" s="15"/>
-      <c r="J20" s="15"/>
-      <c r="K20" s="15"/>
-      <c r="L20" s="15"/>
-      <c r="M20" s="15"/>
-      <c r="N20" s="15"/>
-      <c r="O20" s="15"/>
-      <c r="P20" s="15"/>
-      <c r="Q20" s="15"/>
-      <c r="R20" s="15"/>
-      <c r="T20" s="15"/>
-      <c r="U20" s="15"/>
-      <c r="V20" s="15"/>
-      <c r="W20" s="15"/>
-      <c r="X20" s="15"/>
-      <c r="Y20" s="15"/>
-      <c r="Z20" s="15"/>
-      <c r="AA20" s="15"/>
-      <c r="AB20" s="15"/>
-      <c r="AC20" s="15"/>
-      <c r="AD20" s="15"/>
-      <c r="AE20" s="15"/>
-      <c r="AF20" s="15"/>
-      <c r="AG20" s="15"/>
-      <c r="AH20" s="39"/>
-      <c r="AI20" s="39"/>
-      <c r="AJ20" s="39"/>
-      <c r="AK20" s="39"/>
-      <c r="AL20" s="39"/>
-      <c r="AM20" s="39"/>
-      <c r="AN20" s="39"/>
-      <c r="AO20" s="39"/>
-      <c r="AP20" s="39"/>
-      <c r="AQ20" s="39"/>
-      <c r="AR20" s="39"/>
-      <c r="AS20" s="39"/>
-      <c r="AW20" s="11" t="s">
+      <c r="B20" s="31"/>
+      <c r="E20" s="13"/>
+      <c r="F20" s="13"/>
+      <c r="G20" s="13"/>
+      <c r="H20" s="13"/>
+      <c r="I20" s="13"/>
+      <c r="J20" s="13"/>
+      <c r="K20" s="13"/>
+      <c r="L20" s="13"/>
+      <c r="M20" s="13"/>
+      <c r="N20" s="13"/>
+      <c r="O20" s="13"/>
+      <c r="P20" s="13"/>
+      <c r="Q20" s="13"/>
+      <c r="R20" s="13"/>
+      <c r="T20" s="13"/>
+      <c r="U20" s="13"/>
+      <c r="V20" s="13"/>
+      <c r="W20" s="13"/>
+      <c r="X20" s="13"/>
+      <c r="Y20" s="13"/>
+      <c r="Z20" s="13"/>
+      <c r="AA20" s="13"/>
+      <c r="AB20" s="13"/>
+      <c r="AC20" s="13"/>
+      <c r="AD20" s="13"/>
+      <c r="AE20" s="13"/>
+      <c r="AF20" s="13"/>
+      <c r="AG20" s="13"/>
+      <c r="AW20" s="14" t="s">
         <v>118</v>
       </c>
-      <c r="AX20" s="13"/>
-      <c r="AY20" s="11" t="s">
+      <c r="AX20" s="16"/>
+      <c r="AY20" s="14" t="s">
         <v>119</v>
       </c>
-      <c r="AZ20" s="12"/>
-      <c r="BA20" s="12"/>
-      <c r="BB20" s="13"/>
-      <c r="BC20" s="11" t="s">
+      <c r="AZ20" s="15"/>
+      <c r="BA20" s="15"/>
+      <c r="BB20" s="16"/>
+      <c r="BC20" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="BD20" s="12"/>
-      <c r="BE20" s="13"/>
-      <c r="BF20" s="11" t="s">
+      <c r="BD20" s="15"/>
+      <c r="BE20" s="16"/>
+      <c r="BF20" s="14" t="s">
         <v>121</v>
       </c>
-      <c r="BG20" s="12"/>
-      <c r="BH20" s="12"/>
-      <c r="BI20" s="12"/>
-      <c r="BJ20" s="12"/>
-      <c r="BK20" s="13"/>
+      <c r="BG20" s="15"/>
+      <c r="BH20" s="15"/>
+      <c r="BI20" s="15"/>
+      <c r="BJ20" s="15"/>
+      <c r="BK20" s="16"/>
       <c r="BL20" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="BM20" s="11" t="s">
+      <c r="BM20" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="BN20" s="12"/>
-      <c r="BO20" s="13"/>
+      <c r="BN20" s="15"/>
+      <c r="BO20" s="16"/>
       <c r="BP20" s="8" t="s">
         <v>124</v>
       </c>
       <c r="BQ20" s="8" t="s">
         <v>125</v>
       </c>
-      <c r="BR20" s="17"/>
+      <c r="BR20" s="31"/>
       <c r="BT20" s="6"/>
       <c r="BU20" s="6"/>
       <c r="BV20" s="6"/>
@@ -2990,57 +2659,45 @@
       <c r="BZ20" s="6"/>
     </row>
     <row r="21" spans="2:86" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B21" s="17"/>
-      <c r="AH21" s="39"/>
-      <c r="AI21" s="39"/>
-      <c r="AJ21" s="39"/>
-      <c r="AK21" s="39"/>
-      <c r="AL21" s="39"/>
-      <c r="AM21" s="39"/>
-      <c r="AN21" s="39"/>
-      <c r="AO21" s="39"/>
-      <c r="AP21" s="39"/>
-      <c r="AQ21" s="39"/>
-      <c r="AR21" s="39"/>
-      <c r="AS21" s="39"/>
-      <c r="AW21" s="11" t="s">
+      <c r="B21" s="31"/>
+      <c r="AW21" s="14" t="s">
         <v>126</v>
       </c>
-      <c r="AX21" s="13"/>
-      <c r="AY21" s="11" t="s">
+      <c r="AX21" s="16"/>
+      <c r="AY21" s="14" t="s">
         <v>127</v>
       </c>
-      <c r="AZ21" s="12"/>
-      <c r="BA21" s="12"/>
-      <c r="BB21" s="13"/>
-      <c r="BC21" s="11" t="s">
+      <c r="AZ21" s="15"/>
+      <c r="BA21" s="15"/>
+      <c r="BB21" s="16"/>
+      <c r="BC21" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="BD21" s="12"/>
-      <c r="BE21" s="13"/>
-      <c r="BF21" s="11" t="s">
+      <c r="BD21" s="15"/>
+      <c r="BE21" s="16"/>
+      <c r="BF21" s="14" t="s">
         <v>129</v>
       </c>
-      <c r="BG21" s="12"/>
-      <c r="BH21" s="12"/>
-      <c r="BI21" s="12"/>
-      <c r="BJ21" s="12"/>
-      <c r="BK21" s="13"/>
+      <c r="BG21" s="15"/>
+      <c r="BH21" s="15"/>
+      <c r="BI21" s="15"/>
+      <c r="BJ21" s="15"/>
+      <c r="BK21" s="16"/>
       <c r="BL21" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="BM21" s="11" t="s">
+      <c r="BM21" s="14" t="s">
         <v>131</v>
       </c>
-      <c r="BN21" s="12"/>
-      <c r="BO21" s="13"/>
+      <c r="BN21" s="15"/>
+      <c r="BO21" s="16"/>
       <c r="BP21" s="8" t="s">
         <v>132</v>
       </c>
       <c r="BQ21" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="BR21" s="17"/>
+      <c r="BR21" s="31"/>
       <c r="BT21" s="6"/>
       <c r="BU21" s="6"/>
       <c r="BV21" s="6"/>
@@ -3058,57 +2715,45 @@
       <c r="CH21" s="6"/>
     </row>
     <row r="22" spans="2:86" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B22" s="17"/>
-      <c r="AH22" s="39"/>
-      <c r="AI22" s="39"/>
-      <c r="AJ22" s="39"/>
-      <c r="AK22" s="39"/>
-      <c r="AL22" s="39"/>
-      <c r="AM22" s="39"/>
-      <c r="AN22" s="39"/>
-      <c r="AO22" s="39"/>
-      <c r="AP22" s="39"/>
-      <c r="AQ22" s="39"/>
-      <c r="AR22" s="39"/>
-      <c r="AS22" s="39"/>
-      <c r="AW22" s="11" t="s">
+      <c r="B22" s="31"/>
+      <c r="AW22" s="14" t="s">
         <v>134</v>
       </c>
-      <c r="AX22" s="13"/>
-      <c r="AY22" s="11" t="s">
+      <c r="AX22" s="16"/>
+      <c r="AY22" s="14" t="s">
         <v>135</v>
       </c>
-      <c r="AZ22" s="12"/>
-      <c r="BA22" s="12"/>
-      <c r="BB22" s="13"/>
-      <c r="BC22" s="11" t="s">
+      <c r="AZ22" s="15"/>
+      <c r="BA22" s="15"/>
+      <c r="BB22" s="16"/>
+      <c r="BC22" s="14" t="s">
         <v>136</v>
       </c>
-      <c r="BD22" s="12"/>
-      <c r="BE22" s="13"/>
-      <c r="BF22" s="11" t="s">
+      <c r="BD22" s="15"/>
+      <c r="BE22" s="16"/>
+      <c r="BF22" s="14" t="s">
         <v>137</v>
       </c>
-      <c r="BG22" s="12"/>
-      <c r="BH22" s="12"/>
-      <c r="BI22" s="12"/>
-      <c r="BJ22" s="12"/>
-      <c r="BK22" s="13"/>
+      <c r="BG22" s="15"/>
+      <c r="BH22" s="15"/>
+      <c r="BI22" s="15"/>
+      <c r="BJ22" s="15"/>
+      <c r="BK22" s="16"/>
       <c r="BL22" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="BM22" s="11" t="s">
+      <c r="BM22" s="14" t="s">
         <v>139</v>
       </c>
-      <c r="BN22" s="12"/>
-      <c r="BO22" s="13"/>
+      <c r="BN22" s="15"/>
+      <c r="BO22" s="16"/>
       <c r="BP22" s="8" t="s">
         <v>140</v>
       </c>
       <c r="BQ22" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="BR22" s="17"/>
+      <c r="BR22" s="31"/>
       <c r="BT22" s="6"/>
       <c r="BU22" s="6"/>
       <c r="BV22" s="6"/>
@@ -3126,57 +2771,45 @@
       <c r="CH22" s="6"/>
     </row>
     <row r="23" spans="2:86" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B23" s="17"/>
-      <c r="AH23" s="39"/>
-      <c r="AI23" s="39"/>
-      <c r="AJ23" s="39"/>
-      <c r="AK23" s="39"/>
-      <c r="AL23" s="39"/>
-      <c r="AM23" s="39"/>
-      <c r="AN23" s="39"/>
-      <c r="AO23" s="39"/>
-      <c r="AP23" s="39"/>
-      <c r="AQ23" s="39"/>
-      <c r="AR23" s="39"/>
-      <c r="AS23" s="39"/>
-      <c r="AW23" s="11" t="s">
+      <c r="B23" s="31"/>
+      <c r="AW23" s="14" t="s">
         <v>142</v>
       </c>
-      <c r="AX23" s="13"/>
-      <c r="AY23" s="11" t="s">
+      <c r="AX23" s="16"/>
+      <c r="AY23" s="14" t="s">
         <v>143</v>
       </c>
-      <c r="AZ23" s="12"/>
-      <c r="BA23" s="12"/>
-      <c r="BB23" s="13"/>
-      <c r="BC23" s="11" t="s">
+      <c r="AZ23" s="15"/>
+      <c r="BA23" s="15"/>
+      <c r="BB23" s="16"/>
+      <c r="BC23" s="14" t="s">
         <v>144</v>
       </c>
-      <c r="BD23" s="12"/>
-      <c r="BE23" s="13"/>
-      <c r="BF23" s="11" t="s">
+      <c r="BD23" s="15"/>
+      <c r="BE23" s="16"/>
+      <c r="BF23" s="14" t="s">
         <v>145</v>
       </c>
-      <c r="BG23" s="12"/>
-      <c r="BH23" s="12"/>
-      <c r="BI23" s="12"/>
-      <c r="BJ23" s="12"/>
-      <c r="BK23" s="13"/>
+      <c r="BG23" s="15"/>
+      <c r="BH23" s="15"/>
+      <c r="BI23" s="15"/>
+      <c r="BJ23" s="15"/>
+      <c r="BK23" s="16"/>
       <c r="BL23" s="8" t="s">
         <v>146</v>
       </c>
-      <c r="BM23" s="11" t="s">
+      <c r="BM23" s="14" t="s">
         <v>147</v>
       </c>
-      <c r="BN23" s="12"/>
-      <c r="BO23" s="13"/>
+      <c r="BN23" s="15"/>
+      <c r="BO23" s="16"/>
       <c r="BP23" s="8" t="s">
         <v>148</v>
       </c>
       <c r="BQ23" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="BR23" s="17"/>
+      <c r="BR23" s="31"/>
       <c r="BT23" s="6"/>
       <c r="BU23" s="6"/>
       <c r="BV23" s="6"/>
@@ -3194,57 +2827,45 @@
       <c r="CH23" s="6"/>
     </row>
     <row r="24" spans="2:86" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B24" s="17"/>
-      <c r="AH24" s="39"/>
-      <c r="AI24" s="39"/>
-      <c r="AJ24" s="39"/>
-      <c r="AK24" s="39"/>
-      <c r="AL24" s="39"/>
-      <c r="AM24" s="39"/>
-      <c r="AN24" s="39"/>
-      <c r="AO24" s="39"/>
-      <c r="AP24" s="39"/>
-      <c r="AQ24" s="39"/>
-      <c r="AR24" s="39"/>
-      <c r="AS24" s="39"/>
-      <c r="AW24" s="11" t="s">
+      <c r="B24" s="31"/>
+      <c r="AW24" s="14" t="s">
         <v>150</v>
       </c>
-      <c r="AX24" s="13"/>
-      <c r="AY24" s="11" t="s">
+      <c r="AX24" s="16"/>
+      <c r="AY24" s="14" t="s">
         <v>151</v>
       </c>
-      <c r="AZ24" s="12"/>
-      <c r="BA24" s="12"/>
-      <c r="BB24" s="13"/>
-      <c r="BC24" s="11" t="s">
+      <c r="AZ24" s="15"/>
+      <c r="BA24" s="15"/>
+      <c r="BB24" s="16"/>
+      <c r="BC24" s="14" t="s">
         <v>152</v>
       </c>
-      <c r="BD24" s="12"/>
-      <c r="BE24" s="13"/>
-      <c r="BF24" s="11" t="s">
+      <c r="BD24" s="15"/>
+      <c r="BE24" s="16"/>
+      <c r="BF24" s="14" t="s">
         <v>153</v>
       </c>
-      <c r="BG24" s="12"/>
-      <c r="BH24" s="12"/>
-      <c r="BI24" s="12"/>
-      <c r="BJ24" s="12"/>
-      <c r="BK24" s="13"/>
+      <c r="BG24" s="15"/>
+      <c r="BH24" s="15"/>
+      <c r="BI24" s="15"/>
+      <c r="BJ24" s="15"/>
+      <c r="BK24" s="16"/>
       <c r="BL24" s="8" t="s">
         <v>154</v>
       </c>
-      <c r="BM24" s="11" t="s">
+      <c r="BM24" s="14" t="s">
         <v>155</v>
       </c>
-      <c r="BN24" s="12"/>
-      <c r="BO24" s="13"/>
+      <c r="BN24" s="15"/>
+      <c r="BO24" s="16"/>
       <c r="BP24" s="8" t="s">
         <v>156</v>
       </c>
       <c r="BQ24" s="8" t="s">
         <v>157</v>
       </c>
-      <c r="BR24" s="17"/>
+      <c r="BR24" s="31"/>
       <c r="BT24" s="6"/>
       <c r="BU24" s="6"/>
       <c r="BV24" s="6"/>
@@ -3262,57 +2883,45 @@
       <c r="CH24" s="6"/>
     </row>
     <row r="25" spans="2:86" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B25" s="17"/>
-      <c r="AH25" s="39"/>
-      <c r="AI25" s="39"/>
-      <c r="AJ25" s="39"/>
-      <c r="AK25" s="39"/>
-      <c r="AL25" s="39"/>
-      <c r="AM25" s="39"/>
-      <c r="AN25" s="39"/>
-      <c r="AO25" s="39"/>
-      <c r="AP25" s="39"/>
-      <c r="AQ25" s="39"/>
-      <c r="AR25" s="39"/>
-      <c r="AS25" s="39"/>
-      <c r="AW25" s="11" t="s">
+      <c r="B25" s="31"/>
+      <c r="AW25" s="14" t="s">
         <v>228</v>
       </c>
-      <c r="AX25" s="13"/>
-      <c r="AY25" s="35" t="s">
+      <c r="AX25" s="16"/>
+      <c r="AY25" s="28" t="s">
         <v>158</v>
       </c>
-      <c r="AZ25" s="36"/>
-      <c r="BA25" s="36"/>
-      <c r="BB25" s="37"/>
-      <c r="BC25" s="12" t="s">
+      <c r="AZ25" s="29"/>
+      <c r="BA25" s="29"/>
+      <c r="BB25" s="30"/>
+      <c r="BC25" s="15" t="s">
         <v>229</v>
       </c>
-      <c r="BD25" s="12"/>
-      <c r="BE25" s="13"/>
-      <c r="BF25" s="11" t="s">
+      <c r="BD25" s="15"/>
+      <c r="BE25" s="16"/>
+      <c r="BF25" s="14" t="s">
         <v>230</v>
       </c>
-      <c r="BG25" s="12"/>
-      <c r="BH25" s="12"/>
-      <c r="BI25" s="12"/>
-      <c r="BJ25" s="12"/>
-      <c r="BK25" s="13"/>
+      <c r="BG25" s="15"/>
+      <c r="BH25" s="15"/>
+      <c r="BI25" s="15"/>
+      <c r="BJ25" s="15"/>
+      <c r="BK25" s="16"/>
       <c r="BL25" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="BM25" s="11" t="s">
+      <c r="BM25" s="14" t="s">
         <v>231</v>
       </c>
-      <c r="BN25" s="12"/>
-      <c r="BO25" s="13"/>
+      <c r="BN25" s="15"/>
+      <c r="BO25" s="16"/>
       <c r="BP25" s="8" t="s">
         <v>160</v>
       </c>
       <c r="BQ25" s="8" t="s">
         <v>161</v>
       </c>
-      <c r="BR25" s="17"/>
+      <c r="BR25" s="31"/>
       <c r="BT25" s="6"/>
       <c r="BU25" s="6"/>
       <c r="BV25" s="6"/>
@@ -3330,89 +2939,77 @@
       <c r="CH25" s="6"/>
     </row>
     <row r="26" spans="2:86" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B26" s="17"/>
-      <c r="E26" s="14" t="s">
+      <c r="B26" s="31"/>
+      <c r="E26" s="12" t="s">
         <v>234</v>
       </c>
-      <c r="F26" s="15"/>
-      <c r="G26" s="15"/>
-      <c r="H26" s="15"/>
-      <c r="I26" s="15"/>
-      <c r="J26" s="15"/>
-      <c r="K26" s="15"/>
-      <c r="L26" s="15"/>
-      <c r="M26" s="15"/>
-      <c r="N26" s="15"/>
-      <c r="O26" s="15"/>
-      <c r="P26" s="15"/>
-      <c r="Q26" s="15"/>
-      <c r="R26" s="15"/>
-      <c r="T26" s="14" t="s">
+      <c r="F26" s="13"/>
+      <c r="G26" s="13"/>
+      <c r="H26" s="13"/>
+      <c r="I26" s="13"/>
+      <c r="J26" s="13"/>
+      <c r="K26" s="13"/>
+      <c r="L26" s="13"/>
+      <c r="M26" s="13"/>
+      <c r="N26" s="13"/>
+      <c r="O26" s="13"/>
+      <c r="P26" s="13"/>
+      <c r="Q26" s="13"/>
+      <c r="R26" s="13"/>
+      <c r="T26" s="12" t="s">
         <v>173</v>
       </c>
-      <c r="U26" s="15"/>
-      <c r="V26" s="15"/>
-      <c r="W26" s="15"/>
-      <c r="X26" s="15"/>
-      <c r="Y26" s="15"/>
-      <c r="Z26" s="15"/>
-      <c r="AA26" s="15"/>
-      <c r="AB26" s="15"/>
-      <c r="AC26" s="15"/>
-      <c r="AD26" s="15"/>
-      <c r="AE26" s="15"/>
-      <c r="AF26" s="15"/>
-      <c r="AG26" s="15"/>
-      <c r="AH26" s="39"/>
-      <c r="AI26" s="39"/>
-      <c r="AJ26" s="39"/>
-      <c r="AK26" s="39"/>
-      <c r="AL26" s="39"/>
-      <c r="AM26" s="39"/>
-      <c r="AN26" s="39"/>
-      <c r="AO26" s="39"/>
-      <c r="AP26" s="39"/>
-      <c r="AQ26" s="39"/>
-      <c r="AR26" s="39"/>
-      <c r="AS26" s="39"/>
-      <c r="AW26" s="11" t="s">
+      <c r="U26" s="13"/>
+      <c r="V26" s="13"/>
+      <c r="W26" s="13"/>
+      <c r="X26" s="13"/>
+      <c r="Y26" s="13"/>
+      <c r="Z26" s="13"/>
+      <c r="AA26" s="13"/>
+      <c r="AB26" s="13"/>
+      <c r="AC26" s="13"/>
+      <c r="AD26" s="13"/>
+      <c r="AE26" s="13"/>
+      <c r="AF26" s="13"/>
+      <c r="AG26" s="13"/>
+      <c r="AW26" s="14" t="s">
         <v>162</v>
       </c>
-      <c r="AX26" s="13"/>
-      <c r="AY26" s="11" t="s">
+      <c r="AX26" s="16"/>
+      <c r="AY26" s="14" t="s">
         <v>163</v>
       </c>
-      <c r="AZ26" s="12"/>
-      <c r="BA26" s="12"/>
-      <c r="BB26" s="13"/>
-      <c r="BC26" s="11" t="s">
+      <c r="AZ26" s="15"/>
+      <c r="BA26" s="15"/>
+      <c r="BB26" s="16"/>
+      <c r="BC26" s="14" t="s">
         <v>164</v>
       </c>
-      <c r="BD26" s="12"/>
-      <c r="BE26" s="13"/>
-      <c r="BF26" s="11" t="s">
+      <c r="BD26" s="15"/>
+      <c r="BE26" s="16"/>
+      <c r="BF26" s="14" t="s">
         <v>165</v>
       </c>
-      <c r="BG26" s="12"/>
-      <c r="BH26" s="12"/>
-      <c r="BI26" s="12"/>
-      <c r="BJ26" s="12"/>
-      <c r="BK26" s="13"/>
+      <c r="BG26" s="15"/>
+      <c r="BH26" s="15"/>
+      <c r="BI26" s="15"/>
+      <c r="BJ26" s="15"/>
+      <c r="BK26" s="16"/>
       <c r="BL26" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="BM26" s="11" t="s">
+      <c r="BM26" s="14" t="s">
         <v>167</v>
       </c>
-      <c r="BN26" s="12"/>
-      <c r="BO26" s="13"/>
+      <c r="BN26" s="15"/>
+      <c r="BO26" s="16"/>
       <c r="BP26" s="7" t="s">
         <v>168</v>
       </c>
       <c r="BQ26" s="7" t="s">
         <v>169</v>
       </c>
-      <c r="BR26" s="17"/>
+      <c r="BR26" s="31"/>
       <c r="BT26" s="6"/>
       <c r="BU26" s="6"/>
       <c r="BV26" s="6"/>
@@ -3430,49 +3027,37 @@
       <c r="CH26" s="6"/>
     </row>
     <row r="27" spans="2:86" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B27" s="17"/>
-      <c r="E27" s="15"/>
-      <c r="F27" s="15"/>
-      <c r="G27" s="15"/>
-      <c r="H27" s="15"/>
-      <c r="I27" s="15"/>
-      <c r="J27" s="15"/>
-      <c r="K27" s="15"/>
-      <c r="L27" s="15"/>
-      <c r="M27" s="15"/>
-      <c r="N27" s="15"/>
-      <c r="O27" s="15"/>
-      <c r="P27" s="15"/>
-      <c r="Q27" s="15"/>
-      <c r="R27" s="15"/>
-      <c r="T27" s="15"/>
-      <c r="U27" s="15"/>
-      <c r="V27" s="15"/>
-      <c r="W27" s="15"/>
-      <c r="X27" s="15"/>
-      <c r="Y27" s="15"/>
-      <c r="Z27" s="15"/>
-      <c r="AA27" s="15"/>
-      <c r="AB27" s="15"/>
-      <c r="AC27" s="15"/>
-      <c r="AD27" s="15"/>
-      <c r="AE27" s="15"/>
-      <c r="AF27" s="15"/>
-      <c r="AG27" s="15"/>
-      <c r="AH27" s="39"/>
-      <c r="AI27" s="39"/>
-      <c r="AJ27" s="39"/>
-      <c r="AK27" s="39"/>
-      <c r="AL27" s="39"/>
-      <c r="AM27" s="39"/>
-      <c r="AN27" s="39"/>
-      <c r="AO27" s="39"/>
-      <c r="AP27" s="39"/>
-      <c r="AQ27" s="39"/>
-      <c r="AR27" s="39"/>
-      <c r="AS27" s="39"/>
+      <c r="B27" s="31"/>
+      <c r="E27" s="13"/>
+      <c r="F27" s="13"/>
+      <c r="G27" s="13"/>
+      <c r="H27" s="13"/>
+      <c r="I27" s="13"/>
+      <c r="J27" s="13"/>
+      <c r="K27" s="13"/>
+      <c r="L27" s="13"/>
+      <c r="M27" s="13"/>
+      <c r="N27" s="13"/>
+      <c r="O27" s="13"/>
+      <c r="P27" s="13"/>
+      <c r="Q27" s="13"/>
+      <c r="R27" s="13"/>
+      <c r="T27" s="13"/>
+      <c r="U27" s="13"/>
+      <c r="V27" s="13"/>
+      <c r="W27" s="13"/>
+      <c r="X27" s="13"/>
+      <c r="Y27" s="13"/>
+      <c r="Z27" s="13"/>
+      <c r="AA27" s="13"/>
+      <c r="AB27" s="13"/>
+      <c r="AC27" s="13"/>
+      <c r="AD27" s="13"/>
+      <c r="AE27" s="13"/>
+      <c r="AF27" s="13"/>
+      <c r="AG27" s="13"/>
       <c r="BQ27" s="6"/>
-      <c r="BR27" s="17"/>
+      <c r="BR27" s="31"/>
       <c r="BT27" s="6"/>
       <c r="BU27" s="6"/>
       <c r="BV27" s="6"/>
@@ -3490,40 +3075,40 @@
       <c r="CH27" s="6"/>
     </row>
     <row r="28" spans="2:86" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B28" s="17"/>
-      <c r="E28" s="15"/>
-      <c r="F28" s="15"/>
-      <c r="G28" s="15"/>
-      <c r="H28" s="15"/>
-      <c r="I28" s="15"/>
-      <c r="J28" s="15"/>
-      <c r="K28" s="15"/>
-      <c r="L28" s="15"/>
-      <c r="M28" s="15"/>
-      <c r="N28" s="15"/>
-      <c r="O28" s="15"/>
-      <c r="P28" s="15"/>
-      <c r="Q28" s="15"/>
-      <c r="R28" s="15"/>
-      <c r="T28" s="15"/>
-      <c r="U28" s="15"/>
-      <c r="V28" s="15"/>
-      <c r="W28" s="15"/>
-      <c r="X28" s="15"/>
-      <c r="Y28" s="15"/>
-      <c r="Z28" s="15"/>
-      <c r="AA28" s="15"/>
-      <c r="AB28" s="15"/>
-      <c r="AC28" s="15"/>
-      <c r="AD28" s="15"/>
-      <c r="AE28" s="15"/>
-      <c r="AF28" s="15"/>
-      <c r="AG28" s="15"/>
-      <c r="AI28" s="14"/>
-      <c r="AJ28" s="15"/>
-      <c r="AK28" s="15"/>
-      <c r="AL28" s="15"/>
-      <c r="AM28" s="15"/>
+      <c r="B28" s="31"/>
+      <c r="E28" s="13"/>
+      <c r="F28" s="13"/>
+      <c r="G28" s="13"/>
+      <c r="H28" s="13"/>
+      <c r="I28" s="13"/>
+      <c r="J28" s="13"/>
+      <c r="K28" s="13"/>
+      <c r="L28" s="13"/>
+      <c r="M28" s="13"/>
+      <c r="N28" s="13"/>
+      <c r="O28" s="13"/>
+      <c r="P28" s="13"/>
+      <c r="Q28" s="13"/>
+      <c r="R28" s="13"/>
+      <c r="T28" s="13"/>
+      <c r="U28" s="13"/>
+      <c r="V28" s="13"/>
+      <c r="W28" s="13"/>
+      <c r="X28" s="13"/>
+      <c r="Y28" s="13"/>
+      <c r="Z28" s="13"/>
+      <c r="AA28" s="13"/>
+      <c r="AB28" s="13"/>
+      <c r="AC28" s="13"/>
+      <c r="AD28" s="13"/>
+      <c r="AE28" s="13"/>
+      <c r="AF28" s="13"/>
+      <c r="AG28" s="13"/>
+      <c r="AI28" s="12"/>
+      <c r="AJ28" s="13"/>
+      <c r="AK28" s="13"/>
+      <c r="AL28" s="13"/>
+      <c r="AM28" s="13"/>
       <c r="AV28" s="6"/>
       <c r="AW28" s="9"/>
       <c r="AX28" s="9"/>
@@ -3546,7 +3131,7 @@
       <c r="BO28" s="9"/>
       <c r="BP28" s="9"/>
       <c r="BQ28" s="9"/>
-      <c r="BR28" s="17"/>
+      <c r="BR28" s="31"/>
       <c r="BT28" s="6"/>
       <c r="BU28" s="6"/>
       <c r="BV28" s="6"/>
@@ -3564,42 +3149,42 @@
       <c r="CH28" s="6"/>
     </row>
     <row r="29" spans="2:86" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B29" s="18"/>
-      <c r="E29" s="15"/>
-      <c r="F29" s="15"/>
-      <c r="G29" s="15"/>
-      <c r="H29" s="15"/>
-      <c r="I29" s="15"/>
-      <c r="J29" s="15"/>
-      <c r="K29" s="15"/>
-      <c r="L29" s="15"/>
-      <c r="M29" s="15"/>
-      <c r="N29" s="15"/>
-      <c r="O29" s="15"/>
-      <c r="P29" s="15"/>
-      <c r="Q29" s="15"/>
-      <c r="R29" s="15"/>
-      <c r="T29" s="15"/>
-      <c r="U29" s="15"/>
-      <c r="V29" s="15"/>
-      <c r="W29" s="15"/>
-      <c r="X29" s="15"/>
-      <c r="Y29" s="15"/>
-      <c r="Z29" s="15"/>
-      <c r="AA29" s="15"/>
-      <c r="AB29" s="15"/>
-      <c r="AC29" s="15"/>
-      <c r="AD29" s="15"/>
-      <c r="AE29" s="15"/>
-      <c r="AF29" s="15"/>
-      <c r="AG29" s="15"/>
-      <c r="AI29" s="15"/>
-      <c r="AJ29" s="15"/>
-      <c r="AK29" s="15"/>
-      <c r="AL29" s="15"/>
-      <c r="AM29" s="15"/>
+      <c r="B29" s="27"/>
+      <c r="E29" s="13"/>
+      <c r="F29" s="13"/>
+      <c r="G29" s="13"/>
+      <c r="H29" s="13"/>
+      <c r="I29" s="13"/>
+      <c r="J29" s="13"/>
+      <c r="K29" s="13"/>
+      <c r="L29" s="13"/>
+      <c r="M29" s="13"/>
+      <c r="N29" s="13"/>
+      <c r="O29" s="13"/>
+      <c r="P29" s="13"/>
+      <c r="Q29" s="13"/>
+      <c r="R29" s="13"/>
+      <c r="T29" s="13"/>
+      <c r="U29" s="13"/>
+      <c r="V29" s="13"/>
+      <c r="W29" s="13"/>
+      <c r="X29" s="13"/>
+      <c r="Y29" s="13"/>
+      <c r="Z29" s="13"/>
+      <c r="AA29" s="13"/>
+      <c r="AB29" s="13"/>
+      <c r="AC29" s="13"/>
+      <c r="AD29" s="13"/>
+      <c r="AE29" s="13"/>
+      <c r="AF29" s="13"/>
+      <c r="AG29" s="13"/>
+      <c r="AI29" s="13"/>
+      <c r="AJ29" s="13"/>
+      <c r="AK29" s="13"/>
+      <c r="AL29" s="13"/>
+      <c r="AM29" s="13"/>
       <c r="BQ29" s="6"/>
-      <c r="BR29" s="18"/>
+      <c r="BR29" s="27"/>
       <c r="BT29" s="6"/>
       <c r="BU29" s="6"/>
       <c r="BV29" s="6"/>
@@ -3617,10 +3202,10 @@
       <c r="CH29" s="6"/>
     </row>
     <row r="30" spans="2:86" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B30" s="16" t="s">
+      <c r="B30" s="26" t="s">
         <v>170</v>
       </c>
-      <c r="BR30" s="16" t="s">
+      <c r="BR30" s="26" t="s">
         <v>170</v>
       </c>
       <c r="BT30" s="6"/>
@@ -3632,33 +3217,33 @@
       <c r="BZ30" s="6"/>
     </row>
     <row r="31" spans="2:86" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B31" s="17"/>
-      <c r="AW31" s="25" t="s">
+      <c r="B31" s="31"/>
+      <c r="AW31" s="17" t="s">
         <v>171</v>
       </c>
-      <c r="AX31" s="26"/>
-      <c r="AY31" s="19" t="s">
+      <c r="AX31" s="18"/>
+      <c r="AY31" s="18" t="s">
         <v>172</v>
       </c>
-      <c r="AZ31" s="20"/>
-      <c r="BA31" s="20"/>
-      <c r="BB31" s="20"/>
-      <c r="BC31" s="20"/>
-      <c r="BD31" s="20"/>
-      <c r="BE31" s="20"/>
-      <c r="BF31" s="20"/>
-      <c r="BG31" s="20"/>
-      <c r="BH31" s="20"/>
-      <c r="BI31" s="20"/>
-      <c r="BJ31" s="20"/>
-      <c r="BK31" s="20"/>
-      <c r="BL31" s="20"/>
-      <c r="BM31" s="20"/>
-      <c r="BN31" s="20"/>
-      <c r="BO31" s="20"/>
-      <c r="BP31" s="20"/>
-      <c r="BQ31" s="21"/>
-      <c r="BR31" s="17"/>
+      <c r="AZ31" s="18"/>
+      <c r="BA31" s="18"/>
+      <c r="BB31" s="18"/>
+      <c r="BC31" s="18"/>
+      <c r="BD31" s="18"/>
+      <c r="BE31" s="18"/>
+      <c r="BF31" s="18"/>
+      <c r="BG31" s="18"/>
+      <c r="BH31" s="18"/>
+      <c r="BI31" s="18"/>
+      <c r="BJ31" s="18"/>
+      <c r="BK31" s="18"/>
+      <c r="BL31" s="18"/>
+      <c r="BM31" s="18"/>
+      <c r="BN31" s="18"/>
+      <c r="BO31" s="18"/>
+      <c r="BP31" s="18"/>
+      <c r="BQ31" s="19"/>
+      <c r="BR31" s="31"/>
       <c r="BT31" s="6"/>
       <c r="BU31" s="6"/>
       <c r="BV31" s="6"/>
@@ -3668,41 +3253,29 @@
       <c r="BZ31" s="6"/>
     </row>
     <row r="32" spans="2:86" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B32" s="17"/>
-      <c r="AH32" s="39"/>
-      <c r="AI32" s="39"/>
-      <c r="AJ32" s="39"/>
-      <c r="AK32" s="39"/>
-      <c r="AL32" s="39"/>
-      <c r="AM32" s="39"/>
-      <c r="AN32" s="39"/>
-      <c r="AO32" s="39"/>
-      <c r="AP32" s="39"/>
-      <c r="AQ32" s="39"/>
-      <c r="AR32" s="39"/>
-      <c r="AS32" s="39"/>
-      <c r="AW32" s="31"/>
-      <c r="AX32" s="32"/>
-      <c r="AY32" s="15"/>
-      <c r="AZ32" s="15"/>
-      <c r="BA32" s="15"/>
-      <c r="BB32" s="15"/>
-      <c r="BC32" s="15"/>
-      <c r="BD32" s="15"/>
-      <c r="BE32" s="15"/>
-      <c r="BF32" s="15"/>
-      <c r="BG32" s="15"/>
-      <c r="BH32" s="15"/>
-      <c r="BI32" s="15"/>
-      <c r="BJ32" s="15"/>
-      <c r="BK32" s="15"/>
-      <c r="BL32" s="15"/>
-      <c r="BM32" s="15"/>
-      <c r="BN32" s="15"/>
-      <c r="BO32" s="15"/>
-      <c r="BP32" s="15"/>
-      <c r="BQ32" s="22"/>
-      <c r="BR32" s="17"/>
+      <c r="B32" s="31"/>
+      <c r="AW32" s="23"/>
+      <c r="AX32" s="24"/>
+      <c r="AY32" s="24"/>
+      <c r="AZ32" s="24"/>
+      <c r="BA32" s="24"/>
+      <c r="BB32" s="24"/>
+      <c r="BC32" s="24"/>
+      <c r="BD32" s="24"/>
+      <c r="BE32" s="24"/>
+      <c r="BF32" s="24"/>
+      <c r="BG32" s="24"/>
+      <c r="BH32" s="24"/>
+      <c r="BI32" s="24"/>
+      <c r="BJ32" s="24"/>
+      <c r="BK32" s="24"/>
+      <c r="BL32" s="24"/>
+      <c r="BM32" s="24"/>
+      <c r="BN32" s="24"/>
+      <c r="BO32" s="24"/>
+      <c r="BP32" s="24"/>
+      <c r="BQ32" s="25"/>
+      <c r="BR32" s="31"/>
       <c r="BT32" s="6"/>
       <c r="BU32" s="6"/>
       <c r="BV32" s="6"/>
@@ -3712,41 +3285,29 @@
       <c r="BZ32" s="6"/>
     </row>
     <row r="33" spans="2:78" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B33" s="17"/>
-      <c r="AH33" s="39"/>
-      <c r="AI33" s="39"/>
-      <c r="AJ33" s="39"/>
-      <c r="AK33" s="39"/>
-      <c r="AL33" s="39"/>
-      <c r="AM33" s="39"/>
-      <c r="AN33" s="39"/>
-      <c r="AO33" s="39"/>
-      <c r="AP33" s="39"/>
-      <c r="AQ33" s="39"/>
-      <c r="AR33" s="39"/>
-      <c r="AS33" s="39"/>
-      <c r="AW33" s="31"/>
-      <c r="AX33" s="32"/>
-      <c r="AY33" s="15"/>
-      <c r="AZ33" s="15"/>
-      <c r="BA33" s="15"/>
-      <c r="BB33" s="15"/>
-      <c r="BC33" s="15"/>
-      <c r="BD33" s="15"/>
-      <c r="BE33" s="15"/>
-      <c r="BF33" s="15"/>
-      <c r="BG33" s="15"/>
-      <c r="BH33" s="15"/>
-      <c r="BI33" s="15"/>
-      <c r="BJ33" s="15"/>
-      <c r="BK33" s="15"/>
-      <c r="BL33" s="15"/>
-      <c r="BM33" s="15"/>
-      <c r="BN33" s="15"/>
-      <c r="BO33" s="15"/>
-      <c r="BP33" s="15"/>
-      <c r="BQ33" s="22"/>
-      <c r="BR33" s="17"/>
+      <c r="B33" s="31"/>
+      <c r="AW33" s="23"/>
+      <c r="AX33" s="24"/>
+      <c r="AY33" s="24"/>
+      <c r="AZ33" s="24"/>
+      <c r="BA33" s="24"/>
+      <c r="BB33" s="24"/>
+      <c r="BC33" s="24"/>
+      <c r="BD33" s="24"/>
+      <c r="BE33" s="24"/>
+      <c r="BF33" s="24"/>
+      <c r="BG33" s="24"/>
+      <c r="BH33" s="24"/>
+      <c r="BI33" s="24"/>
+      <c r="BJ33" s="24"/>
+      <c r="BK33" s="24"/>
+      <c r="BL33" s="24"/>
+      <c r="BM33" s="24"/>
+      <c r="BN33" s="24"/>
+      <c r="BO33" s="24"/>
+      <c r="BP33" s="24"/>
+      <c r="BQ33" s="25"/>
+      <c r="BR33" s="31"/>
       <c r="BT33" s="6"/>
       <c r="BU33" s="6"/>
       <c r="BV33" s="6"/>
@@ -3756,41 +3317,29 @@
       <c r="BZ33" s="6"/>
     </row>
     <row r="34" spans="2:78" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B34" s="17"/>
-      <c r="AH34" s="39"/>
-      <c r="AI34" s="39"/>
-      <c r="AJ34" s="39"/>
-      <c r="AK34" s="39"/>
-      <c r="AL34" s="39"/>
-      <c r="AM34" s="39"/>
-      <c r="AN34" s="39"/>
-      <c r="AO34" s="39"/>
-      <c r="AP34" s="39"/>
-      <c r="AQ34" s="39"/>
-      <c r="AR34" s="39"/>
-      <c r="AS34" s="39"/>
-      <c r="AW34" s="31"/>
-      <c r="AX34" s="32"/>
-      <c r="AY34" s="15"/>
-      <c r="AZ34" s="15"/>
-      <c r="BA34" s="15"/>
-      <c r="BB34" s="15"/>
-      <c r="BC34" s="15"/>
-      <c r="BD34" s="15"/>
-      <c r="BE34" s="15"/>
-      <c r="BF34" s="15"/>
-      <c r="BG34" s="15"/>
-      <c r="BH34" s="15"/>
-      <c r="BI34" s="15"/>
-      <c r="BJ34" s="15"/>
-      <c r="BK34" s="15"/>
-      <c r="BL34" s="15"/>
-      <c r="BM34" s="15"/>
-      <c r="BN34" s="15"/>
-      <c r="BO34" s="15"/>
-      <c r="BP34" s="15"/>
-      <c r="BQ34" s="22"/>
-      <c r="BR34" s="17"/>
+      <c r="B34" s="31"/>
+      <c r="AW34" s="23"/>
+      <c r="AX34" s="24"/>
+      <c r="AY34" s="24"/>
+      <c r="AZ34" s="24"/>
+      <c r="BA34" s="24"/>
+      <c r="BB34" s="24"/>
+      <c r="BC34" s="24"/>
+      <c r="BD34" s="24"/>
+      <c r="BE34" s="24"/>
+      <c r="BF34" s="24"/>
+      <c r="BG34" s="24"/>
+      <c r="BH34" s="24"/>
+      <c r="BI34" s="24"/>
+      <c r="BJ34" s="24"/>
+      <c r="BK34" s="24"/>
+      <c r="BL34" s="24"/>
+      <c r="BM34" s="24"/>
+      <c r="BN34" s="24"/>
+      <c r="BO34" s="24"/>
+      <c r="BP34" s="24"/>
+      <c r="BQ34" s="25"/>
+      <c r="BR34" s="31"/>
       <c r="BT34" s="6"/>
       <c r="BU34" s="6"/>
       <c r="BV34" s="6"/>
@@ -3800,73 +3349,61 @@
       <c r="BZ34" s="6"/>
     </row>
     <row r="35" spans="2:78" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B35" s="17"/>
-      <c r="E35" s="14" t="s">
+      <c r="B35" s="31"/>
+      <c r="E35" s="12" t="s">
         <v>235</v>
       </c>
-      <c r="F35" s="15"/>
-      <c r="G35" s="15"/>
-      <c r="H35" s="15"/>
-      <c r="I35" s="15"/>
-      <c r="J35" s="15"/>
-      <c r="K35" s="15"/>
-      <c r="L35" s="15"/>
-      <c r="M35" s="15"/>
-      <c r="N35" s="15"/>
-      <c r="O35" s="15"/>
-      <c r="P35" s="15"/>
-      <c r="Q35" s="15"/>
-      <c r="R35" s="15"/>
-      <c r="T35" s="14" t="s">
+      <c r="F35" s="13"/>
+      <c r="G35" s="13"/>
+      <c r="H35" s="13"/>
+      <c r="I35" s="13"/>
+      <c r="J35" s="13"/>
+      <c r="K35" s="13"/>
+      <c r="L35" s="13"/>
+      <c r="M35" s="13"/>
+      <c r="N35" s="13"/>
+      <c r="O35" s="13"/>
+      <c r="P35" s="13"/>
+      <c r="Q35" s="13"/>
+      <c r="R35" s="13"/>
+      <c r="T35" s="12" t="s">
         <v>174</v>
       </c>
-      <c r="U35" s="15"/>
-      <c r="V35" s="15"/>
-      <c r="W35" s="15"/>
-      <c r="X35" s="15"/>
-      <c r="Y35" s="15"/>
-      <c r="Z35" s="15"/>
-      <c r="AA35" s="15"/>
-      <c r="AB35" s="15"/>
-      <c r="AC35" s="15"/>
-      <c r="AD35" s="15"/>
-      <c r="AE35" s="15"/>
-      <c r="AF35" s="15"/>
-      <c r="AG35" s="15"/>
-      <c r="AH35" s="39"/>
-      <c r="AI35" s="39"/>
-      <c r="AJ35" s="39"/>
-      <c r="AK35" s="39"/>
-      <c r="AL35" s="39"/>
-      <c r="AM35" s="39"/>
-      <c r="AN35" s="39"/>
-      <c r="AO35" s="39"/>
-      <c r="AP35" s="39"/>
-      <c r="AQ35" s="39"/>
-      <c r="AR35" s="39"/>
-      <c r="AS35" s="39"/>
-      <c r="AW35" s="31"/>
-      <c r="AX35" s="32"/>
-      <c r="AY35" s="15"/>
-      <c r="AZ35" s="15"/>
-      <c r="BA35" s="15"/>
-      <c r="BB35" s="15"/>
-      <c r="BC35" s="15"/>
-      <c r="BD35" s="15"/>
-      <c r="BE35" s="15"/>
-      <c r="BF35" s="15"/>
-      <c r="BG35" s="15"/>
-      <c r="BH35" s="15"/>
-      <c r="BI35" s="15"/>
-      <c r="BJ35" s="15"/>
-      <c r="BK35" s="15"/>
-      <c r="BL35" s="15"/>
-      <c r="BM35" s="15"/>
-      <c r="BN35" s="15"/>
-      <c r="BO35" s="15"/>
-      <c r="BP35" s="15"/>
-      <c r="BQ35" s="22"/>
-      <c r="BR35" s="17"/>
+      <c r="U35" s="13"/>
+      <c r="V35" s="13"/>
+      <c r="W35" s="13"/>
+      <c r="X35" s="13"/>
+      <c r="Y35" s="13"/>
+      <c r="Z35" s="13"/>
+      <c r="AA35" s="13"/>
+      <c r="AB35" s="13"/>
+      <c r="AC35" s="13"/>
+      <c r="AD35" s="13"/>
+      <c r="AE35" s="13"/>
+      <c r="AF35" s="13"/>
+      <c r="AG35" s="13"/>
+      <c r="AW35" s="23"/>
+      <c r="AX35" s="24"/>
+      <c r="AY35" s="24"/>
+      <c r="AZ35" s="24"/>
+      <c r="BA35" s="24"/>
+      <c r="BB35" s="24"/>
+      <c r="BC35" s="24"/>
+      <c r="BD35" s="24"/>
+      <c r="BE35" s="24"/>
+      <c r="BF35" s="24"/>
+      <c r="BG35" s="24"/>
+      <c r="BH35" s="24"/>
+      <c r="BI35" s="24"/>
+      <c r="BJ35" s="24"/>
+      <c r="BK35" s="24"/>
+      <c r="BL35" s="24"/>
+      <c r="BM35" s="24"/>
+      <c r="BN35" s="24"/>
+      <c r="BO35" s="24"/>
+      <c r="BP35" s="24"/>
+      <c r="BQ35" s="25"/>
+      <c r="BR35" s="31"/>
       <c r="BT35" s="6"/>
       <c r="BU35" s="6"/>
       <c r="BV35" s="6"/>
@@ -3876,69 +3413,57 @@
       <c r="BZ35" s="6"/>
     </row>
     <row r="36" spans="2:78" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B36" s="17"/>
-      <c r="E36" s="15"/>
-      <c r="F36" s="15"/>
-      <c r="G36" s="15"/>
-      <c r="H36" s="15"/>
-      <c r="I36" s="15"/>
-      <c r="J36" s="15"/>
-      <c r="K36" s="15"/>
-      <c r="L36" s="15"/>
-      <c r="M36" s="15"/>
-      <c r="N36" s="15"/>
-      <c r="O36" s="15"/>
-      <c r="P36" s="15"/>
-      <c r="Q36" s="15"/>
-      <c r="R36" s="15"/>
-      <c r="T36" s="15"/>
-      <c r="U36" s="15"/>
-      <c r="V36" s="15"/>
-      <c r="W36" s="15"/>
-      <c r="X36" s="15"/>
-      <c r="Y36" s="15"/>
-      <c r="Z36" s="15"/>
-      <c r="AA36" s="15"/>
-      <c r="AB36" s="15"/>
-      <c r="AC36" s="15"/>
-      <c r="AD36" s="15"/>
-      <c r="AE36" s="15"/>
-      <c r="AF36" s="15"/>
-      <c r="AG36" s="15"/>
-      <c r="AH36" s="39"/>
-      <c r="AI36" s="39"/>
-      <c r="AJ36" s="39"/>
-      <c r="AK36" s="39"/>
-      <c r="AL36" s="39"/>
-      <c r="AM36" s="39"/>
-      <c r="AN36" s="39"/>
-      <c r="AO36" s="39"/>
-      <c r="AP36" s="39"/>
-      <c r="AQ36" s="39"/>
-      <c r="AR36" s="39"/>
-      <c r="AS36" s="39"/>
-      <c r="AW36" s="28"/>
-      <c r="AX36" s="29"/>
-      <c r="AY36" s="23"/>
-      <c r="AZ36" s="23"/>
-      <c r="BA36" s="23"/>
-      <c r="BB36" s="23"/>
-      <c r="BC36" s="23"/>
-      <c r="BD36" s="23"/>
-      <c r="BE36" s="23"/>
-      <c r="BF36" s="23"/>
-      <c r="BG36" s="23"/>
-      <c r="BH36" s="23"/>
-      <c r="BI36" s="23"/>
-      <c r="BJ36" s="23"/>
-      <c r="BK36" s="23"/>
-      <c r="BL36" s="23"/>
-      <c r="BM36" s="23"/>
-      <c r="BN36" s="23"/>
-      <c r="BO36" s="23"/>
-      <c r="BP36" s="23"/>
-      <c r="BQ36" s="24"/>
-      <c r="BR36" s="17"/>
+      <c r="B36" s="31"/>
+      <c r="E36" s="13"/>
+      <c r="F36" s="13"/>
+      <c r="G36" s="13"/>
+      <c r="H36" s="13"/>
+      <c r="I36" s="13"/>
+      <c r="J36" s="13"/>
+      <c r="K36" s="13"/>
+      <c r="L36" s="13"/>
+      <c r="M36" s="13"/>
+      <c r="N36" s="13"/>
+      <c r="O36" s="13"/>
+      <c r="P36" s="13"/>
+      <c r="Q36" s="13"/>
+      <c r="R36" s="13"/>
+      <c r="T36" s="13"/>
+      <c r="U36" s="13"/>
+      <c r="V36" s="13"/>
+      <c r="W36" s="13"/>
+      <c r="X36" s="13"/>
+      <c r="Y36" s="13"/>
+      <c r="Z36" s="13"/>
+      <c r="AA36" s="13"/>
+      <c r="AB36" s="13"/>
+      <c r="AC36" s="13"/>
+      <c r="AD36" s="13"/>
+      <c r="AE36" s="13"/>
+      <c r="AF36" s="13"/>
+      <c r="AG36" s="13"/>
+      <c r="AW36" s="20"/>
+      <c r="AX36" s="21"/>
+      <c r="AY36" s="21"/>
+      <c r="AZ36" s="21"/>
+      <c r="BA36" s="21"/>
+      <c r="BB36" s="21"/>
+      <c r="BC36" s="21"/>
+      <c r="BD36" s="21"/>
+      <c r="BE36" s="21"/>
+      <c r="BF36" s="21"/>
+      <c r="BG36" s="21"/>
+      <c r="BH36" s="21"/>
+      <c r="BI36" s="21"/>
+      <c r="BJ36" s="21"/>
+      <c r="BK36" s="21"/>
+      <c r="BL36" s="21"/>
+      <c r="BM36" s="21"/>
+      <c r="BN36" s="21"/>
+      <c r="BO36" s="21"/>
+      <c r="BP36" s="21"/>
+      <c r="BQ36" s="22"/>
+      <c r="BR36" s="31"/>
       <c r="BT36" s="6"/>
       <c r="BU36" s="6"/>
       <c r="BV36" s="6"/>
@@ -3948,48 +3473,36 @@
       <c r="BZ36" s="6"/>
     </row>
     <row r="37" spans="2:78" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B37" s="17"/>
-      <c r="E37" s="15"/>
-      <c r="F37" s="15"/>
-      <c r="G37" s="15"/>
-      <c r="H37" s="15"/>
-      <c r="I37" s="15"/>
-      <c r="J37" s="15"/>
-      <c r="K37" s="15"/>
-      <c r="L37" s="15"/>
-      <c r="M37" s="15"/>
-      <c r="N37" s="15"/>
-      <c r="O37" s="15"/>
-      <c r="P37" s="15"/>
-      <c r="Q37" s="15"/>
-      <c r="R37" s="15"/>
-      <c r="T37" s="15"/>
-      <c r="U37" s="15"/>
-      <c r="V37" s="15"/>
-      <c r="W37" s="15"/>
-      <c r="X37" s="15"/>
-      <c r="Y37" s="15"/>
-      <c r="Z37" s="15"/>
-      <c r="AA37" s="15"/>
-      <c r="AB37" s="15"/>
-      <c r="AC37" s="15"/>
-      <c r="AD37" s="15"/>
-      <c r="AE37" s="15"/>
-      <c r="AF37" s="15"/>
-      <c r="AG37" s="15"/>
-      <c r="AH37" s="39"/>
-      <c r="AI37" s="39"/>
-      <c r="AJ37" s="39"/>
-      <c r="AK37" s="39"/>
-      <c r="AL37" s="39"/>
-      <c r="AM37" s="39"/>
-      <c r="AN37" s="39"/>
-      <c r="AO37" s="39"/>
-      <c r="AP37" s="39"/>
-      <c r="AQ37" s="39"/>
-      <c r="AR37" s="39"/>
-      <c r="AS37" s="39"/>
-      <c r="BR37" s="17"/>
+      <c r="B37" s="31"/>
+      <c r="E37" s="13"/>
+      <c r="F37" s="13"/>
+      <c r="G37" s="13"/>
+      <c r="H37" s="13"/>
+      <c r="I37" s="13"/>
+      <c r="J37" s="13"/>
+      <c r="K37" s="13"/>
+      <c r="L37" s="13"/>
+      <c r="M37" s="13"/>
+      <c r="N37" s="13"/>
+      <c r="O37" s="13"/>
+      <c r="P37" s="13"/>
+      <c r="Q37" s="13"/>
+      <c r="R37" s="13"/>
+      <c r="T37" s="13"/>
+      <c r="U37" s="13"/>
+      <c r="V37" s="13"/>
+      <c r="W37" s="13"/>
+      <c r="X37" s="13"/>
+      <c r="Y37" s="13"/>
+      <c r="Z37" s="13"/>
+      <c r="AA37" s="13"/>
+      <c r="AB37" s="13"/>
+      <c r="AC37" s="13"/>
+      <c r="AD37" s="13"/>
+      <c r="AE37" s="13"/>
+      <c r="AF37" s="13"/>
+      <c r="AG37" s="13"/>
+      <c r="BR37" s="31"/>
       <c r="BT37" s="6"/>
       <c r="BU37" s="6"/>
       <c r="BV37" s="6"/>
@@ -3999,48 +3512,36 @@
       <c r="BZ37" s="6"/>
     </row>
     <row r="38" spans="2:78" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B38" s="17"/>
-      <c r="E38" s="15"/>
-      <c r="F38" s="15"/>
-      <c r="G38" s="15"/>
-      <c r="H38" s="15"/>
-      <c r="I38" s="15"/>
-      <c r="J38" s="15"/>
-      <c r="K38" s="15"/>
-      <c r="L38" s="15"/>
-      <c r="M38" s="15"/>
-      <c r="N38" s="15"/>
-      <c r="O38" s="15"/>
-      <c r="P38" s="15"/>
-      <c r="Q38" s="15"/>
-      <c r="R38" s="15"/>
-      <c r="T38" s="15"/>
-      <c r="U38" s="15"/>
-      <c r="V38" s="15"/>
-      <c r="W38" s="15"/>
-      <c r="X38" s="15"/>
-      <c r="Y38" s="15"/>
-      <c r="Z38" s="15"/>
-      <c r="AA38" s="15"/>
-      <c r="AB38" s="15"/>
-      <c r="AC38" s="15"/>
-      <c r="AD38" s="15"/>
-      <c r="AE38" s="15"/>
-      <c r="AF38" s="15"/>
-      <c r="AG38" s="15"/>
-      <c r="AH38" s="39"/>
-      <c r="AI38" s="39"/>
-      <c r="AJ38" s="39"/>
-      <c r="AK38" s="39"/>
-      <c r="AL38" s="39"/>
-      <c r="AM38" s="39"/>
-      <c r="AN38" s="39"/>
-      <c r="AO38" s="39"/>
-      <c r="AP38" s="39"/>
-      <c r="AQ38" s="39"/>
-      <c r="AR38" s="39"/>
-      <c r="AS38" s="39"/>
-      <c r="BR38" s="17"/>
+      <c r="B38" s="31"/>
+      <c r="E38" s="13"/>
+      <c r="F38" s="13"/>
+      <c r="G38" s="13"/>
+      <c r="H38" s="13"/>
+      <c r="I38" s="13"/>
+      <c r="J38" s="13"/>
+      <c r="K38" s="13"/>
+      <c r="L38" s="13"/>
+      <c r="M38" s="13"/>
+      <c r="N38" s="13"/>
+      <c r="O38" s="13"/>
+      <c r="P38" s="13"/>
+      <c r="Q38" s="13"/>
+      <c r="R38" s="13"/>
+      <c r="T38" s="13"/>
+      <c r="U38" s="13"/>
+      <c r="V38" s="13"/>
+      <c r="W38" s="13"/>
+      <c r="X38" s="13"/>
+      <c r="Y38" s="13"/>
+      <c r="Z38" s="13"/>
+      <c r="AA38" s="13"/>
+      <c r="AB38" s="13"/>
+      <c r="AC38" s="13"/>
+      <c r="AD38" s="13"/>
+      <c r="AE38" s="13"/>
+      <c r="AF38" s="13"/>
+      <c r="AG38" s="13"/>
+      <c r="BR38" s="31"/>
       <c r="BT38" s="6"/>
       <c r="BU38" s="6"/>
       <c r="BV38" s="6"/>
@@ -4050,81 +3551,69 @@
       <c r="BZ38" s="6"/>
     </row>
     <row r="39" spans="2:78" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B39" s="17"/>
-      <c r="E39" s="15"/>
-      <c r="F39" s="15"/>
-      <c r="G39" s="15"/>
-      <c r="H39" s="15"/>
-      <c r="I39" s="15"/>
-      <c r="J39" s="15"/>
-      <c r="K39" s="15"/>
-      <c r="L39" s="15"/>
-      <c r="M39" s="15"/>
-      <c r="N39" s="15"/>
-      <c r="O39" s="15"/>
-      <c r="P39" s="15"/>
-      <c r="Q39" s="15"/>
-      <c r="R39" s="15"/>
-      <c r="T39" s="15"/>
-      <c r="U39" s="15"/>
-      <c r="V39" s="15"/>
-      <c r="W39" s="15"/>
-      <c r="X39" s="15"/>
-      <c r="Y39" s="15"/>
-      <c r="Z39" s="15"/>
-      <c r="AA39" s="15"/>
-      <c r="AB39" s="15"/>
-      <c r="AC39" s="15"/>
-      <c r="AD39" s="15"/>
-      <c r="AE39" s="15"/>
-      <c r="AF39" s="15"/>
-      <c r="AG39" s="15"/>
-      <c r="AH39" s="39"/>
-      <c r="AI39" s="39"/>
-      <c r="AJ39" s="39"/>
-      <c r="AK39" s="39"/>
-      <c r="AL39" s="39"/>
-      <c r="AM39" s="39"/>
-      <c r="AN39" s="39"/>
-      <c r="AO39" s="39"/>
-      <c r="AP39" s="39"/>
-      <c r="AQ39" s="39"/>
-      <c r="AR39" s="39"/>
-      <c r="AS39" s="39"/>
+      <c r="B39" s="31"/>
+      <c r="E39" s="13"/>
+      <c r="F39" s="13"/>
+      <c r="G39" s="13"/>
+      <c r="H39" s="13"/>
+      <c r="I39" s="13"/>
+      <c r="J39" s="13"/>
+      <c r="K39" s="13"/>
+      <c r="L39" s="13"/>
+      <c r="M39" s="13"/>
+      <c r="N39" s="13"/>
+      <c r="O39" s="13"/>
+      <c r="P39" s="13"/>
+      <c r="Q39" s="13"/>
+      <c r="R39" s="13"/>
+      <c r="T39" s="13"/>
+      <c r="U39" s="13"/>
+      <c r="V39" s="13"/>
+      <c r="W39" s="13"/>
+      <c r="X39" s="13"/>
+      <c r="Y39" s="13"/>
+      <c r="Z39" s="13"/>
+      <c r="AA39" s="13"/>
+      <c r="AB39" s="13"/>
+      <c r="AC39" s="13"/>
+      <c r="AD39" s="13"/>
+      <c r="AE39" s="13"/>
+      <c r="AF39" s="13"/>
+      <c r="AG39" s="13"/>
       <c r="AW39" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="AX39" s="11" t="s">
+      <c r="AX39" s="14" t="s">
         <v>176</v>
       </c>
-      <c r="AY39" s="12"/>
-      <c r="AZ39" s="13"/>
-      <c r="BA39" s="11" t="s">
+      <c r="AY39" s="15"/>
+      <c r="AZ39" s="16"/>
+      <c r="BA39" s="14" t="s">
         <v>177</v>
       </c>
-      <c r="BB39" s="12"/>
-      <c r="BC39" s="12"/>
-      <c r="BD39" s="12"/>
-      <c r="BE39" s="12"/>
-      <c r="BF39" s="12"/>
-      <c r="BG39" s="12"/>
-      <c r="BH39" s="13"/>
-      <c r="BI39" s="11" t="s">
+      <c r="BB39" s="15"/>
+      <c r="BC39" s="15"/>
+      <c r="BD39" s="15"/>
+      <c r="BE39" s="15"/>
+      <c r="BF39" s="15"/>
+      <c r="BG39" s="15"/>
+      <c r="BH39" s="16"/>
+      <c r="BI39" s="14" t="s">
         <v>178</v>
       </c>
-      <c r="BJ39" s="12"/>
-      <c r="BK39" s="13"/>
-      <c r="BL39" s="11" t="s">
+      <c r="BJ39" s="15"/>
+      <c r="BK39" s="16"/>
+      <c r="BL39" s="14" t="s">
         <v>179</v>
       </c>
-      <c r="BM39" s="12"/>
-      <c r="BN39" s="13"/>
-      <c r="BO39" s="11" t="s">
+      <c r="BM39" s="15"/>
+      <c r="BN39" s="16"/>
+      <c r="BO39" s="14" t="s">
         <v>180</v>
       </c>
-      <c r="BP39" s="12"/>
-      <c r="BQ39" s="13"/>
-      <c r="BR39" s="17"/>
+      <c r="BP39" s="15"/>
+      <c r="BQ39" s="16"/>
+      <c r="BR39" s="31"/>
       <c r="BT39" s="6"/>
       <c r="BU39" s="6"/>
       <c r="BV39" s="6"/>
@@ -4134,53 +3623,41 @@
       <c r="BZ39" s="6"/>
     </row>
     <row r="40" spans="2:78" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B40" s="17"/>
-      <c r="AH40" s="39"/>
-      <c r="AI40" s="39"/>
-      <c r="AJ40" s="39"/>
-      <c r="AK40" s="39"/>
-      <c r="AL40" s="39"/>
-      <c r="AM40" s="39"/>
-      <c r="AN40" s="39"/>
-      <c r="AO40" s="39"/>
-      <c r="AP40" s="39"/>
-      <c r="AQ40" s="39"/>
-      <c r="AR40" s="39"/>
-      <c r="AS40" s="39"/>
+      <c r="B40" s="31"/>
       <c r="AW40" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="AX40" s="11" t="s">
+      <c r="AX40" s="14" t="s">
         <v>182</v>
       </c>
-      <c r="AY40" s="12"/>
-      <c r="AZ40" s="13"/>
-      <c r="BA40" s="11" t="s">
+      <c r="AY40" s="15"/>
+      <c r="AZ40" s="16"/>
+      <c r="BA40" s="14" t="s">
         <v>183</v>
       </c>
-      <c r="BB40" s="12"/>
-      <c r="BC40" s="12"/>
-      <c r="BD40" s="12"/>
-      <c r="BE40" s="12"/>
-      <c r="BF40" s="12"/>
-      <c r="BG40" s="12"/>
-      <c r="BH40" s="13"/>
-      <c r="BI40" s="11" t="s">
+      <c r="BB40" s="15"/>
+      <c r="BC40" s="15"/>
+      <c r="BD40" s="15"/>
+      <c r="BE40" s="15"/>
+      <c r="BF40" s="15"/>
+      <c r="BG40" s="15"/>
+      <c r="BH40" s="16"/>
+      <c r="BI40" s="14" t="s">
         <v>184</v>
       </c>
-      <c r="BJ40" s="12"/>
-      <c r="BK40" s="13"/>
-      <c r="BL40" s="11" t="s">
+      <c r="BJ40" s="15"/>
+      <c r="BK40" s="16"/>
+      <c r="BL40" s="14" t="s">
         <v>185</v>
       </c>
-      <c r="BM40" s="12"/>
-      <c r="BN40" s="13"/>
-      <c r="BO40" s="11" t="s">
+      <c r="BM40" s="15"/>
+      <c r="BN40" s="16"/>
+      <c r="BO40" s="14" t="s">
         <v>186</v>
       </c>
-      <c r="BP40" s="12"/>
-      <c r="BQ40" s="13"/>
-      <c r="BR40" s="17"/>
+      <c r="BP40" s="15"/>
+      <c r="BQ40" s="16"/>
+      <c r="BR40" s="31"/>
       <c r="BT40" s="6"/>
       <c r="BU40" s="6"/>
       <c r="BV40" s="6"/>
@@ -4190,53 +3667,41 @@
       <c r="BZ40" s="6"/>
     </row>
     <row r="41" spans="2:78" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B41" s="17"/>
-      <c r="AH41" s="39"/>
-      <c r="AI41" s="39"/>
-      <c r="AJ41" s="39"/>
-      <c r="AK41" s="39"/>
-      <c r="AL41" s="39"/>
-      <c r="AM41" s="39"/>
-      <c r="AN41" s="39"/>
-      <c r="AO41" s="39"/>
-      <c r="AP41" s="39"/>
-      <c r="AQ41" s="39"/>
-      <c r="AR41" s="39"/>
-      <c r="AS41" s="39"/>
+      <c r="B41" s="31"/>
       <c r="AW41" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="AX41" s="11" t="s">
+      <c r="AX41" s="14" t="s">
         <v>188</v>
       </c>
-      <c r="AY41" s="12"/>
-      <c r="AZ41" s="13"/>
-      <c r="BA41" s="11" t="s">
+      <c r="AY41" s="15"/>
+      <c r="AZ41" s="16"/>
+      <c r="BA41" s="14" t="s">
         <v>189</v>
       </c>
-      <c r="BB41" s="12"/>
-      <c r="BC41" s="12"/>
-      <c r="BD41" s="12"/>
-      <c r="BE41" s="12"/>
-      <c r="BF41" s="12"/>
-      <c r="BG41" s="12"/>
-      <c r="BH41" s="13"/>
-      <c r="BI41" s="11" t="s">
+      <c r="BB41" s="15"/>
+      <c r="BC41" s="15"/>
+      <c r="BD41" s="15"/>
+      <c r="BE41" s="15"/>
+      <c r="BF41" s="15"/>
+      <c r="BG41" s="15"/>
+      <c r="BH41" s="16"/>
+      <c r="BI41" s="14" t="s">
         <v>190</v>
       </c>
-      <c r="BJ41" s="12"/>
-      <c r="BK41" s="13"/>
-      <c r="BL41" s="11" t="s">
+      <c r="BJ41" s="15"/>
+      <c r="BK41" s="16"/>
+      <c r="BL41" s="14" t="s">
         <v>191</v>
       </c>
-      <c r="BM41" s="12"/>
-      <c r="BN41" s="13"/>
-      <c r="BO41" s="11" t="s">
+      <c r="BM41" s="15"/>
+      <c r="BN41" s="16"/>
+      <c r="BO41" s="14" t="s">
         <v>192</v>
       </c>
-      <c r="BP41" s="12"/>
-      <c r="BQ41" s="13"/>
-      <c r="BR41" s="17"/>
+      <c r="BP41" s="15"/>
+      <c r="BQ41" s="16"/>
+      <c r="BR41" s="31"/>
       <c r="BT41" s="6"/>
       <c r="BU41" s="6"/>
       <c r="BV41" s="6"/>
@@ -4246,53 +3711,41 @@
       <c r="BZ41" s="6"/>
     </row>
     <row r="42" spans="2:78" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B42" s="17"/>
-      <c r="AH42" s="39"/>
-      <c r="AI42" s="39"/>
-      <c r="AJ42" s="39"/>
-      <c r="AK42" s="39"/>
-      <c r="AL42" s="39"/>
-      <c r="AM42" s="39"/>
-      <c r="AN42" s="39"/>
-      <c r="AO42" s="39"/>
-      <c r="AP42" s="39"/>
-      <c r="AQ42" s="39"/>
-      <c r="AR42" s="39"/>
-      <c r="AS42" s="39"/>
+      <c r="B42" s="31"/>
       <c r="AW42" s="5" t="s">
         <v>193</v>
       </c>
-      <c r="AX42" s="11" t="s">
+      <c r="AX42" s="14" t="s">
         <v>194</v>
       </c>
-      <c r="AY42" s="12"/>
-      <c r="AZ42" s="13"/>
-      <c r="BA42" s="11" t="s">
+      <c r="AY42" s="15"/>
+      <c r="AZ42" s="16"/>
+      <c r="BA42" s="14" t="s">
         <v>195</v>
       </c>
-      <c r="BB42" s="12"/>
-      <c r="BC42" s="12"/>
-      <c r="BD42" s="12"/>
-      <c r="BE42" s="12"/>
-      <c r="BF42" s="12"/>
-      <c r="BG42" s="12"/>
-      <c r="BH42" s="13"/>
-      <c r="BI42" s="11" t="s">
+      <c r="BB42" s="15"/>
+      <c r="BC42" s="15"/>
+      <c r="BD42" s="15"/>
+      <c r="BE42" s="15"/>
+      <c r="BF42" s="15"/>
+      <c r="BG42" s="15"/>
+      <c r="BH42" s="16"/>
+      <c r="BI42" s="14" t="s">
         <v>196</v>
       </c>
-      <c r="BJ42" s="12"/>
-      <c r="BK42" s="13"/>
-      <c r="BL42" s="11" t="s">
+      <c r="BJ42" s="15"/>
+      <c r="BK42" s="16"/>
+      <c r="BL42" s="14" t="s">
         <v>197</v>
       </c>
-      <c r="BM42" s="12"/>
-      <c r="BN42" s="13"/>
-      <c r="BO42" s="11" t="s">
+      <c r="BM42" s="15"/>
+      <c r="BN42" s="16"/>
+      <c r="BO42" s="14" t="s">
         <v>198</v>
       </c>
-      <c r="BP42" s="12"/>
-      <c r="BQ42" s="13"/>
-      <c r="BR42" s="17"/>
+      <c r="BP42" s="15"/>
+      <c r="BQ42" s="16"/>
+      <c r="BR42" s="31"/>
       <c r="BT42" s="6"/>
       <c r="BU42" s="6"/>
       <c r="BV42" s="6"/>
@@ -4302,53 +3755,41 @@
       <c r="BZ42" s="6"/>
     </row>
     <row r="43" spans="2:78" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B43" s="18"/>
-      <c r="AH43" s="39"/>
-      <c r="AI43" s="39"/>
-      <c r="AJ43" s="39"/>
-      <c r="AK43" s="39"/>
-      <c r="AL43" s="39"/>
-      <c r="AM43" s="39"/>
-      <c r="AN43" s="39"/>
-      <c r="AO43" s="39"/>
-      <c r="AP43" s="39"/>
-      <c r="AQ43" s="39"/>
-      <c r="AR43" s="39"/>
-      <c r="AS43" s="39"/>
-      <c r="AW43" s="16" t="s">
+      <c r="B43" s="27"/>
+      <c r="AW43" s="26" t="s">
         <v>199</v>
       </c>
-      <c r="AX43" s="25" t="s">
+      <c r="AX43" s="17" t="s">
         <v>200</v>
       </c>
-      <c r="AY43" s="26"/>
-      <c r="AZ43" s="27"/>
-      <c r="BA43" s="25" t="s">
+      <c r="AY43" s="18"/>
+      <c r="AZ43" s="19"/>
+      <c r="BA43" s="17" t="s">
         <v>201</v>
       </c>
-      <c r="BB43" s="26"/>
-      <c r="BC43" s="26"/>
-      <c r="BD43" s="26"/>
-      <c r="BE43" s="26"/>
-      <c r="BF43" s="26"/>
-      <c r="BG43" s="26"/>
-      <c r="BH43" s="27"/>
-      <c r="BI43" s="25" t="s">
+      <c r="BB43" s="18"/>
+      <c r="BC43" s="18"/>
+      <c r="BD43" s="18"/>
+      <c r="BE43" s="18"/>
+      <c r="BF43" s="18"/>
+      <c r="BG43" s="18"/>
+      <c r="BH43" s="19"/>
+      <c r="BI43" s="17" t="s">
         <v>202</v>
       </c>
-      <c r="BJ43" s="26"/>
-      <c r="BK43" s="27"/>
-      <c r="BL43" s="25" t="s">
+      <c r="BJ43" s="18"/>
+      <c r="BK43" s="19"/>
+      <c r="BL43" s="17" t="s">
         <v>203</v>
       </c>
-      <c r="BM43" s="26"/>
-      <c r="BN43" s="27"/>
-      <c r="BO43" s="25" t="s">
+      <c r="BM43" s="18"/>
+      <c r="BN43" s="19"/>
+      <c r="BO43" s="17" t="s">
         <v>204</v>
       </c>
-      <c r="BP43" s="26"/>
-      <c r="BQ43" s="27"/>
-      <c r="BR43" s="18"/>
+      <c r="BP43" s="18"/>
+      <c r="BQ43" s="19"/>
+      <c r="BR43" s="27"/>
       <c r="BT43" s="6"/>
       <c r="BU43" s="6"/>
       <c r="BV43" s="6"/>
@@ -4358,43 +3799,31 @@
       <c r="BZ43" s="6"/>
     </row>
     <row r="44" spans="2:78" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B44" s="16" t="s">
+      <c r="B44" s="26" t="s">
         <v>205</v>
       </c>
-      <c r="AH44" s="39"/>
-      <c r="AI44" s="39"/>
-      <c r="AJ44" s="39"/>
-      <c r="AK44" s="39"/>
-      <c r="AL44" s="39"/>
-      <c r="AM44" s="39"/>
-      <c r="AN44" s="39"/>
-      <c r="AO44" s="39"/>
-      <c r="AP44" s="39"/>
-      <c r="AQ44" s="39"/>
-      <c r="AR44" s="39"/>
-      <c r="AS44" s="39"/>
-      <c r="AW44" s="18"/>
-      <c r="AX44" s="28"/>
-      <c r="AY44" s="29"/>
-      <c r="AZ44" s="30"/>
-      <c r="BA44" s="28"/>
-      <c r="BB44" s="29"/>
-      <c r="BC44" s="29"/>
-      <c r="BD44" s="29"/>
-      <c r="BE44" s="29"/>
-      <c r="BF44" s="29"/>
-      <c r="BG44" s="29"/>
-      <c r="BH44" s="30"/>
-      <c r="BI44" s="28"/>
-      <c r="BJ44" s="29"/>
-      <c r="BK44" s="30"/>
-      <c r="BL44" s="28"/>
-      <c r="BM44" s="29"/>
-      <c r="BN44" s="30"/>
-      <c r="BO44" s="28"/>
-      <c r="BP44" s="29"/>
-      <c r="BQ44" s="30"/>
-      <c r="BR44" s="16" t="s">
+      <c r="AW44" s="27"/>
+      <c r="AX44" s="20"/>
+      <c r="AY44" s="21"/>
+      <c r="AZ44" s="22"/>
+      <c r="BA44" s="20"/>
+      <c r="BB44" s="21"/>
+      <c r="BC44" s="21"/>
+      <c r="BD44" s="21"/>
+      <c r="BE44" s="21"/>
+      <c r="BF44" s="21"/>
+      <c r="BG44" s="21"/>
+      <c r="BH44" s="22"/>
+      <c r="BI44" s="20"/>
+      <c r="BJ44" s="21"/>
+      <c r="BK44" s="22"/>
+      <c r="BL44" s="20"/>
+      <c r="BM44" s="21"/>
+      <c r="BN44" s="22"/>
+      <c r="BO44" s="20"/>
+      <c r="BP44" s="21"/>
+      <c r="BQ44" s="22"/>
+      <c r="BR44" s="26" t="s">
         <v>205</v>
       </c>
       <c r="BT44" s="6"/>
@@ -4406,53 +3835,41 @@
       <c r="BZ44" s="6"/>
     </row>
     <row r="45" spans="2:78" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B45" s="17"/>
-      <c r="AH45" s="39"/>
-      <c r="AI45" s="39"/>
-      <c r="AJ45" s="39"/>
-      <c r="AK45" s="39"/>
-      <c r="AL45" s="39"/>
-      <c r="AM45" s="39"/>
-      <c r="AN45" s="39"/>
-      <c r="AO45" s="39"/>
-      <c r="AP45" s="39"/>
-      <c r="AQ45" s="39"/>
-      <c r="AR45" s="39"/>
-      <c r="AS45" s="39"/>
+      <c r="B45" s="31"/>
       <c r="AW45" s="5" t="s">
         <v>206</v>
       </c>
-      <c r="AX45" s="11" t="s">
+      <c r="AX45" s="14" t="s">
         <v>207</v>
       </c>
-      <c r="AY45" s="12"/>
-      <c r="AZ45" s="13"/>
-      <c r="BA45" s="11" t="s">
+      <c r="AY45" s="15"/>
+      <c r="AZ45" s="16"/>
+      <c r="BA45" s="14" t="s">
         <v>208</v>
       </c>
-      <c r="BB45" s="12"/>
-      <c r="BC45" s="12"/>
-      <c r="BD45" s="12"/>
-      <c r="BE45" s="12"/>
-      <c r="BF45" s="12"/>
-      <c r="BG45" s="12"/>
-      <c r="BH45" s="13"/>
-      <c r="BI45" s="11" t="s">
+      <c r="BB45" s="15"/>
+      <c r="BC45" s="15"/>
+      <c r="BD45" s="15"/>
+      <c r="BE45" s="15"/>
+      <c r="BF45" s="15"/>
+      <c r="BG45" s="15"/>
+      <c r="BH45" s="16"/>
+      <c r="BI45" s="14" t="s">
         <v>209</v>
       </c>
-      <c r="BJ45" s="12"/>
-      <c r="BK45" s="13"/>
-      <c r="BL45" s="11" t="s">
+      <c r="BJ45" s="15"/>
+      <c r="BK45" s="16"/>
+      <c r="BL45" s="14" t="s">
         <v>210</v>
       </c>
-      <c r="BM45" s="12"/>
-      <c r="BN45" s="13"/>
-      <c r="BO45" s="11" t="s">
+      <c r="BM45" s="15"/>
+      <c r="BN45" s="16"/>
+      <c r="BO45" s="14" t="s">
         <v>211</v>
       </c>
-      <c r="BP45" s="12"/>
-      <c r="BQ45" s="13"/>
-      <c r="BR45" s="17"/>
+      <c r="BP45" s="15"/>
+      <c r="BQ45" s="16"/>
+      <c r="BR45" s="31"/>
       <c r="BT45" s="6"/>
       <c r="BU45" s="6"/>
       <c r="BV45" s="6"/>
@@ -4462,47 +3879,35 @@
       <c r="BZ45" s="6"/>
     </row>
     <row r="46" spans="2:78" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B46" s="17"/>
-      <c r="AH46" s="39"/>
-      <c r="AI46" s="39"/>
-      <c r="AJ46" s="39"/>
-      <c r="AK46" s="39"/>
-      <c r="AL46" s="39"/>
-      <c r="AM46" s="39"/>
-      <c r="AN46" s="39"/>
-      <c r="AO46" s="39"/>
-      <c r="AP46" s="39"/>
-      <c r="AQ46" s="39"/>
-      <c r="AR46" s="39"/>
-      <c r="AS46" s="39"/>
-      <c r="AW46" s="11" t="s">
+      <c r="B46" s="31"/>
+      <c r="AW46" s="14" t="s">
         <v>212</v>
       </c>
-      <c r="AX46" s="12"/>
-      <c r="AY46" s="12"/>
-      <c r="AZ46" s="13"/>
-      <c r="BA46" s="11" t="s">
+      <c r="AX46" s="15"/>
+      <c r="AY46" s="15"/>
+      <c r="AZ46" s="16"/>
+      <c r="BA46" s="14" t="s">
         <v>213</v>
       </c>
-      <c r="BB46" s="12"/>
-      <c r="BC46" s="12"/>
-      <c r="BD46" s="12"/>
-      <c r="BE46" s="12"/>
-      <c r="BF46" s="12"/>
-      <c r="BG46" s="12"/>
-      <c r="BH46" s="13"/>
-      <c r="BI46" s="11" t="s">
+      <c r="BB46" s="15"/>
+      <c r="BC46" s="15"/>
+      <c r="BD46" s="15"/>
+      <c r="BE46" s="15"/>
+      <c r="BF46" s="15"/>
+      <c r="BG46" s="15"/>
+      <c r="BH46" s="16"/>
+      <c r="BI46" s="14" t="s">
         <v>214</v>
       </c>
-      <c r="BJ46" s="12"/>
-      <c r="BK46" s="12"/>
-      <c r="BL46" s="12"/>
-      <c r="BM46" s="12"/>
-      <c r="BN46" s="12"/>
-      <c r="BO46" s="12"/>
-      <c r="BP46" s="12"/>
-      <c r="BQ46" s="13"/>
-      <c r="BR46" s="17"/>
+      <c r="BJ46" s="15"/>
+      <c r="BK46" s="15"/>
+      <c r="BL46" s="15"/>
+      <c r="BM46" s="15"/>
+      <c r="BN46" s="15"/>
+      <c r="BO46" s="15"/>
+      <c r="BP46" s="15"/>
+      <c r="BQ46" s="16"/>
+      <c r="BR46" s="31"/>
       <c r="BT46" s="6"/>
       <c r="BU46" s="6"/>
       <c r="BV46" s="6"/>
@@ -4512,79 +3917,67 @@
       <c r="BZ46" s="6"/>
     </row>
     <row r="47" spans="2:78" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B47" s="17"/>
-      <c r="E47" s="14" t="s">
+      <c r="B47" s="31"/>
+      <c r="E47" s="12" t="s">
         <v>236</v>
       </c>
-      <c r="F47" s="15"/>
-      <c r="G47" s="15"/>
-      <c r="H47" s="15"/>
-      <c r="I47" s="15"/>
-      <c r="J47" s="15"/>
-      <c r="K47" s="15"/>
-      <c r="L47" s="15"/>
-      <c r="M47" s="15"/>
-      <c r="N47" s="15"/>
-      <c r="O47" s="15"/>
-      <c r="P47" s="15"/>
-      <c r="Q47" s="15"/>
-      <c r="R47" s="15"/>
-      <c r="T47" s="14" t="s">
+      <c r="F47" s="13"/>
+      <c r="G47" s="13"/>
+      <c r="H47" s="13"/>
+      <c r="I47" s="13"/>
+      <c r="J47" s="13"/>
+      <c r="K47" s="13"/>
+      <c r="L47" s="13"/>
+      <c r="M47" s="13"/>
+      <c r="N47" s="13"/>
+      <c r="O47" s="13"/>
+      <c r="P47" s="13"/>
+      <c r="Q47" s="13"/>
+      <c r="R47" s="13"/>
+      <c r="T47" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="U47" s="15"/>
-      <c r="V47" s="15"/>
-      <c r="W47" s="15"/>
-      <c r="X47" s="15"/>
-      <c r="Y47" s="15"/>
-      <c r="Z47" s="15"/>
-      <c r="AA47" s="15"/>
-      <c r="AB47" s="15"/>
-      <c r="AC47" s="15"/>
-      <c r="AD47" s="15"/>
-      <c r="AE47" s="15"/>
-      <c r="AF47" s="15"/>
-      <c r="AG47" s="15"/>
-      <c r="AH47" s="39"/>
-      <c r="AI47" s="39"/>
-      <c r="AJ47" s="39"/>
-      <c r="AK47" s="39"/>
-      <c r="AL47" s="39"/>
-      <c r="AM47" s="39"/>
-      <c r="AN47" s="39"/>
-      <c r="AO47" s="39"/>
-      <c r="AP47" s="39"/>
-      <c r="AQ47" s="39"/>
-      <c r="AR47" s="39"/>
-      <c r="AS47" s="39"/>
-      <c r="AW47" s="11" t="s">
+      <c r="U47" s="13"/>
+      <c r="V47" s="13"/>
+      <c r="W47" s="13"/>
+      <c r="X47" s="13"/>
+      <c r="Y47" s="13"/>
+      <c r="Z47" s="13"/>
+      <c r="AA47" s="13"/>
+      <c r="AB47" s="13"/>
+      <c r="AC47" s="13"/>
+      <c r="AD47" s="13"/>
+      <c r="AE47" s="13"/>
+      <c r="AF47" s="13"/>
+      <c r="AG47" s="13"/>
+      <c r="AW47" s="14" t="s">
         <v>215</v>
       </c>
-      <c r="AX47" s="12"/>
-      <c r="AY47" s="12"/>
-      <c r="AZ47" s="13"/>
-      <c r="BA47" s="11" t="s">
+      <c r="AX47" s="15"/>
+      <c r="AY47" s="15"/>
+      <c r="AZ47" s="16"/>
+      <c r="BA47" s="14" t="s">
         <v>216</v>
       </c>
-      <c r="BB47" s="12"/>
-      <c r="BC47" s="12"/>
-      <c r="BD47" s="12"/>
-      <c r="BE47" s="12"/>
-      <c r="BF47" s="12"/>
-      <c r="BG47" s="12"/>
-      <c r="BH47" s="13"/>
-      <c r="BI47" s="11" t="s">
+      <c r="BB47" s="15"/>
+      <c r="BC47" s="15"/>
+      <c r="BD47" s="15"/>
+      <c r="BE47" s="15"/>
+      <c r="BF47" s="15"/>
+      <c r="BG47" s="15"/>
+      <c r="BH47" s="16"/>
+      <c r="BI47" s="14" t="s">
         <v>217</v>
       </c>
-      <c r="BJ47" s="12"/>
-      <c r="BK47" s="12"/>
-      <c r="BL47" s="12"/>
-      <c r="BM47" s="12"/>
-      <c r="BN47" s="12"/>
-      <c r="BO47" s="12"/>
-      <c r="BP47" s="12"/>
-      <c r="BQ47" s="13"/>
-      <c r="BR47" s="17"/>
+      <c r="BJ47" s="15"/>
+      <c r="BK47" s="15"/>
+      <c r="BL47" s="15"/>
+      <c r="BM47" s="15"/>
+      <c r="BN47" s="15"/>
+      <c r="BO47" s="15"/>
+      <c r="BP47" s="15"/>
+      <c r="BQ47" s="16"/>
+      <c r="BR47" s="31"/>
       <c r="BT47" s="6"/>
       <c r="BU47" s="6"/>
       <c r="BV47" s="6"/>
@@ -4594,73 +3987,61 @@
       <c r="BZ47" s="6"/>
     </row>
     <row r="48" spans="2:78" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B48" s="17"/>
-      <c r="E48" s="15"/>
-      <c r="F48" s="15"/>
-      <c r="G48" s="15"/>
-      <c r="H48" s="15"/>
-      <c r="I48" s="15"/>
-      <c r="J48" s="15"/>
-      <c r="K48" s="15"/>
-      <c r="L48" s="15"/>
-      <c r="M48" s="15"/>
-      <c r="N48" s="15"/>
-      <c r="O48" s="15"/>
-      <c r="P48" s="15"/>
-      <c r="Q48" s="15"/>
-      <c r="R48" s="15"/>
-      <c r="T48" s="15"/>
-      <c r="U48" s="15"/>
-      <c r="V48" s="15"/>
-      <c r="W48" s="15"/>
-      <c r="X48" s="15"/>
-      <c r="Y48" s="15"/>
-      <c r="Z48" s="15"/>
-      <c r="AA48" s="15"/>
-      <c r="AB48" s="15"/>
-      <c r="AC48" s="15"/>
-      <c r="AD48" s="15"/>
-      <c r="AE48" s="15"/>
-      <c r="AF48" s="15"/>
-      <c r="AG48" s="15"/>
-      <c r="AH48" s="39"/>
-      <c r="AI48" s="39"/>
-      <c r="AJ48" s="39"/>
-      <c r="AK48" s="39"/>
-      <c r="AL48" s="39"/>
-      <c r="AM48" s="39"/>
-      <c r="AN48" s="39"/>
-      <c r="AO48" s="39"/>
-      <c r="AP48" s="39"/>
-      <c r="AQ48" s="39"/>
-      <c r="AR48" s="39"/>
-      <c r="AS48" s="39"/>
-      <c r="AW48" s="25" t="s">
+      <c r="B48" s="31"/>
+      <c r="E48" s="13"/>
+      <c r="F48" s="13"/>
+      <c r="G48" s="13"/>
+      <c r="H48" s="13"/>
+      <c r="I48" s="13"/>
+      <c r="J48" s="13"/>
+      <c r="K48" s="13"/>
+      <c r="L48" s="13"/>
+      <c r="M48" s="13"/>
+      <c r="N48" s="13"/>
+      <c r="O48" s="13"/>
+      <c r="P48" s="13"/>
+      <c r="Q48" s="13"/>
+      <c r="R48" s="13"/>
+      <c r="T48" s="13"/>
+      <c r="U48" s="13"/>
+      <c r="V48" s="13"/>
+      <c r="W48" s="13"/>
+      <c r="X48" s="13"/>
+      <c r="Y48" s="13"/>
+      <c r="Z48" s="13"/>
+      <c r="AA48" s="13"/>
+      <c r="AB48" s="13"/>
+      <c r="AC48" s="13"/>
+      <c r="AD48" s="13"/>
+      <c r="AE48" s="13"/>
+      <c r="AF48" s="13"/>
+      <c r="AG48" s="13"/>
+      <c r="AW48" s="17" t="s">
         <v>218</v>
       </c>
-      <c r="AX48" s="26"/>
-      <c r="AY48" s="26"/>
-      <c r="AZ48" s="26"/>
-      <c r="BA48" s="26"/>
-      <c r="BB48" s="26"/>
-      <c r="BC48" s="26"/>
-      <c r="BD48" s="27"/>
-      <c r="BE48" s="25" t="s">
+      <c r="AX48" s="18"/>
+      <c r="AY48" s="18"/>
+      <c r="AZ48" s="18"/>
+      <c r="BA48" s="18"/>
+      <c r="BB48" s="18"/>
+      <c r="BC48" s="18"/>
+      <c r="BD48" s="19"/>
+      <c r="BE48" s="17" t="s">
         <v>219</v>
       </c>
-      <c r="BF48" s="26"/>
-      <c r="BG48" s="26"/>
-      <c r="BH48" s="26"/>
-      <c r="BI48" s="26"/>
-      <c r="BJ48" s="26"/>
-      <c r="BK48" s="26"/>
-      <c r="BL48" s="26"/>
-      <c r="BM48" s="26"/>
-      <c r="BN48" s="26"/>
-      <c r="BO48" s="26"/>
-      <c r="BP48" s="26"/>
-      <c r="BQ48" s="27"/>
-      <c r="BR48" s="17"/>
+      <c r="BF48" s="18"/>
+      <c r="BG48" s="18"/>
+      <c r="BH48" s="18"/>
+      <c r="BI48" s="18"/>
+      <c r="BJ48" s="18"/>
+      <c r="BK48" s="18"/>
+      <c r="BL48" s="18"/>
+      <c r="BM48" s="18"/>
+      <c r="BN48" s="18"/>
+      <c r="BO48" s="18"/>
+      <c r="BP48" s="18"/>
+      <c r="BQ48" s="19"/>
+      <c r="BR48" s="31"/>
       <c r="BT48" s="6"/>
       <c r="BU48" s="6"/>
       <c r="BV48" s="6"/>
@@ -4670,71 +4051,59 @@
       <c r="BZ48" s="6"/>
     </row>
     <row r="49" spans="1:78" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B49" s="17"/>
-      <c r="E49" s="15"/>
-      <c r="F49" s="15"/>
-      <c r="G49" s="15"/>
-      <c r="H49" s="15"/>
-      <c r="I49" s="15"/>
-      <c r="J49" s="15"/>
-      <c r="K49" s="15"/>
-      <c r="L49" s="15"/>
-      <c r="M49" s="15"/>
-      <c r="N49" s="15"/>
-      <c r="O49" s="15"/>
-      <c r="P49" s="15"/>
-      <c r="Q49" s="15"/>
-      <c r="R49" s="15"/>
-      <c r="T49" s="15"/>
-      <c r="U49" s="15"/>
-      <c r="V49" s="15"/>
-      <c r="W49" s="15"/>
-      <c r="X49" s="15"/>
-      <c r="Y49" s="15"/>
-      <c r="Z49" s="15"/>
-      <c r="AA49" s="15"/>
-      <c r="AB49" s="15"/>
-      <c r="AC49" s="15"/>
-      <c r="AD49" s="15"/>
-      <c r="AE49" s="15"/>
-      <c r="AF49" s="15"/>
-      <c r="AG49" s="15"/>
-      <c r="AH49" s="39"/>
-      <c r="AI49" s="39"/>
-      <c r="AJ49" s="39"/>
-      <c r="AK49" s="39"/>
-      <c r="AL49" s="39"/>
-      <c r="AM49" s="39"/>
-      <c r="AN49" s="39"/>
-      <c r="AO49" s="39"/>
-      <c r="AP49" s="39"/>
-      <c r="AQ49" s="39"/>
-      <c r="AR49" s="39"/>
-      <c r="AS49" s="39"/>
-      <c r="AW49" s="31" t="s">
+      <c r="B49" s="31"/>
+      <c r="E49" s="13"/>
+      <c r="F49" s="13"/>
+      <c r="G49" s="13"/>
+      <c r="H49" s="13"/>
+      <c r="I49" s="13"/>
+      <c r="J49" s="13"/>
+      <c r="K49" s="13"/>
+      <c r="L49" s="13"/>
+      <c r="M49" s="13"/>
+      <c r="N49" s="13"/>
+      <c r="O49" s="13"/>
+      <c r="P49" s="13"/>
+      <c r="Q49" s="13"/>
+      <c r="R49" s="13"/>
+      <c r="T49" s="13"/>
+      <c r="U49" s="13"/>
+      <c r="V49" s="13"/>
+      <c r="W49" s="13"/>
+      <c r="X49" s="13"/>
+      <c r="Y49" s="13"/>
+      <c r="Z49" s="13"/>
+      <c r="AA49" s="13"/>
+      <c r="AB49" s="13"/>
+      <c r="AC49" s="13"/>
+      <c r="AD49" s="13"/>
+      <c r="AE49" s="13"/>
+      <c r="AF49" s="13"/>
+      <c r="AG49" s="13"/>
+      <c r="AW49" s="23" t="s">
         <v>220</v>
       </c>
-      <c r="AX49" s="32"/>
-      <c r="AY49" s="32"/>
-      <c r="AZ49" s="32"/>
-      <c r="BA49" s="32"/>
-      <c r="BB49" s="32"/>
-      <c r="BC49" s="32"/>
-      <c r="BD49" s="33"/>
-      <c r="BE49" s="28"/>
-      <c r="BF49" s="29"/>
-      <c r="BG49" s="29"/>
-      <c r="BH49" s="29"/>
-      <c r="BI49" s="29"/>
-      <c r="BJ49" s="29"/>
-      <c r="BK49" s="29"/>
-      <c r="BL49" s="29"/>
-      <c r="BM49" s="29"/>
-      <c r="BN49" s="29"/>
-      <c r="BO49" s="29"/>
-      <c r="BP49" s="29"/>
-      <c r="BQ49" s="30"/>
-      <c r="BR49" s="17"/>
+      <c r="AX49" s="24"/>
+      <c r="AY49" s="24"/>
+      <c r="AZ49" s="24"/>
+      <c r="BA49" s="24"/>
+      <c r="BB49" s="24"/>
+      <c r="BC49" s="24"/>
+      <c r="BD49" s="25"/>
+      <c r="BE49" s="20"/>
+      <c r="BF49" s="21"/>
+      <c r="BG49" s="21"/>
+      <c r="BH49" s="21"/>
+      <c r="BI49" s="21"/>
+      <c r="BJ49" s="21"/>
+      <c r="BK49" s="21"/>
+      <c r="BL49" s="21"/>
+      <c r="BM49" s="21"/>
+      <c r="BN49" s="21"/>
+      <c r="BO49" s="21"/>
+      <c r="BP49" s="21"/>
+      <c r="BQ49" s="22"/>
+      <c r="BR49" s="31"/>
       <c r="BT49" s="6"/>
       <c r="BU49" s="6"/>
       <c r="BV49" s="6"/>
@@ -4744,71 +4113,59 @@
       <c r="BZ49" s="6"/>
     </row>
     <row r="50" spans="1:78" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B50" s="17"/>
-      <c r="E50" s="15"/>
-      <c r="F50" s="15"/>
-      <c r="G50" s="15"/>
-      <c r="H50" s="15"/>
-      <c r="I50" s="15"/>
-      <c r="J50" s="15"/>
-      <c r="K50" s="15"/>
-      <c r="L50" s="15"/>
-      <c r="M50" s="15"/>
-      <c r="N50" s="15"/>
-      <c r="O50" s="15"/>
-      <c r="P50" s="15"/>
-      <c r="Q50" s="15"/>
-      <c r="R50" s="15"/>
-      <c r="T50" s="15"/>
-      <c r="U50" s="15"/>
-      <c r="V50" s="15"/>
-      <c r="W50" s="15"/>
-      <c r="X50" s="15"/>
-      <c r="Y50" s="15"/>
-      <c r="Z50" s="15"/>
-      <c r="AA50" s="15"/>
-      <c r="AB50" s="15"/>
-      <c r="AC50" s="15"/>
-      <c r="AD50" s="15"/>
-      <c r="AE50" s="15"/>
-      <c r="AF50" s="15"/>
-      <c r="AG50" s="15"/>
-      <c r="AH50" s="39"/>
-      <c r="AI50" s="39"/>
-      <c r="AJ50" s="39"/>
-      <c r="AK50" s="39"/>
-      <c r="AL50" s="39"/>
-      <c r="AM50" s="39"/>
-      <c r="AN50" s="39"/>
-      <c r="AO50" s="39"/>
-      <c r="AP50" s="39"/>
-      <c r="AQ50" s="39"/>
-      <c r="AR50" s="39"/>
-      <c r="AS50" s="39"/>
-      <c r="AW50" s="31"/>
-      <c r="AX50" s="32"/>
-      <c r="AY50" s="32"/>
-      <c r="AZ50" s="32"/>
-      <c r="BA50" s="32"/>
-      <c r="BB50" s="32"/>
-      <c r="BC50" s="32"/>
-      <c r="BD50" s="33"/>
-      <c r="BE50" s="25" t="s">
+      <c r="B50" s="31"/>
+      <c r="E50" s="13"/>
+      <c r="F50" s="13"/>
+      <c r="G50" s="13"/>
+      <c r="H50" s="13"/>
+      <c r="I50" s="13"/>
+      <c r="J50" s="13"/>
+      <c r="K50" s="13"/>
+      <c r="L50" s="13"/>
+      <c r="M50" s="13"/>
+      <c r="N50" s="13"/>
+      <c r="O50" s="13"/>
+      <c r="P50" s="13"/>
+      <c r="Q50" s="13"/>
+      <c r="R50" s="13"/>
+      <c r="T50" s="13"/>
+      <c r="U50" s="13"/>
+      <c r="V50" s="13"/>
+      <c r="W50" s="13"/>
+      <c r="X50" s="13"/>
+      <c r="Y50" s="13"/>
+      <c r="Z50" s="13"/>
+      <c r="AA50" s="13"/>
+      <c r="AB50" s="13"/>
+      <c r="AC50" s="13"/>
+      <c r="AD50" s="13"/>
+      <c r="AE50" s="13"/>
+      <c r="AF50" s="13"/>
+      <c r="AG50" s="13"/>
+      <c r="AW50" s="23"/>
+      <c r="AX50" s="24"/>
+      <c r="AY50" s="24"/>
+      <c r="AZ50" s="24"/>
+      <c r="BA50" s="24"/>
+      <c r="BB50" s="24"/>
+      <c r="BC50" s="24"/>
+      <c r="BD50" s="25"/>
+      <c r="BE50" s="17" t="s">
         <v>221</v>
       </c>
-      <c r="BF50" s="26"/>
-      <c r="BG50" s="26"/>
-      <c r="BH50" s="26"/>
-      <c r="BI50" s="26"/>
-      <c r="BJ50" s="26"/>
-      <c r="BK50" s="26"/>
-      <c r="BL50" s="26"/>
-      <c r="BM50" s="26"/>
-      <c r="BN50" s="26"/>
-      <c r="BO50" s="26"/>
-      <c r="BP50" s="26"/>
-      <c r="BQ50" s="27"/>
-      <c r="BR50" s="17"/>
+      <c r="BF50" s="18"/>
+      <c r="BG50" s="18"/>
+      <c r="BH50" s="18"/>
+      <c r="BI50" s="18"/>
+      <c r="BJ50" s="18"/>
+      <c r="BK50" s="18"/>
+      <c r="BL50" s="18"/>
+      <c r="BM50" s="18"/>
+      <c r="BN50" s="18"/>
+      <c r="BO50" s="18"/>
+      <c r="BP50" s="18"/>
+      <c r="BQ50" s="19"/>
+      <c r="BR50" s="31"/>
       <c r="BT50" s="6"/>
       <c r="BU50" s="6"/>
       <c r="BV50" s="6"/>
@@ -4818,69 +4175,57 @@
       <c r="BZ50" s="6"/>
     </row>
     <row r="51" spans="1:78" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B51" s="17"/>
-      <c r="E51" s="15"/>
-      <c r="F51" s="15"/>
-      <c r="G51" s="15"/>
-      <c r="H51" s="15"/>
-      <c r="I51" s="15"/>
-      <c r="J51" s="15"/>
-      <c r="K51" s="15"/>
-      <c r="L51" s="15"/>
-      <c r="M51" s="15"/>
-      <c r="N51" s="15"/>
-      <c r="O51" s="15"/>
-      <c r="P51" s="15"/>
-      <c r="Q51" s="15"/>
-      <c r="R51" s="15"/>
-      <c r="T51" s="15"/>
-      <c r="U51" s="15"/>
-      <c r="V51" s="15"/>
-      <c r="W51" s="15"/>
-      <c r="X51" s="15"/>
-      <c r="Y51" s="15"/>
-      <c r="Z51" s="15"/>
-      <c r="AA51" s="15"/>
-      <c r="AB51" s="15"/>
-      <c r="AC51" s="15"/>
-      <c r="AD51" s="15"/>
-      <c r="AE51" s="15"/>
-      <c r="AF51" s="15"/>
-      <c r="AG51" s="15"/>
-      <c r="AH51" s="39"/>
-      <c r="AI51" s="39"/>
-      <c r="AJ51" s="39"/>
-      <c r="AK51" s="39"/>
-      <c r="AL51" s="39"/>
-      <c r="AM51" s="39"/>
-      <c r="AN51" s="39"/>
-      <c r="AO51" s="39"/>
-      <c r="AP51" s="39"/>
-      <c r="AQ51" s="39"/>
-      <c r="AR51" s="39"/>
-      <c r="AS51" s="39"/>
-      <c r="AW51" s="28"/>
-      <c r="AX51" s="29"/>
-      <c r="AY51" s="29"/>
-      <c r="AZ51" s="29"/>
-      <c r="BA51" s="29"/>
-      <c r="BB51" s="29"/>
-      <c r="BC51" s="29"/>
-      <c r="BD51" s="30"/>
-      <c r="BE51" s="28"/>
-      <c r="BF51" s="29"/>
-      <c r="BG51" s="29"/>
-      <c r="BH51" s="29"/>
-      <c r="BI51" s="29"/>
-      <c r="BJ51" s="29"/>
-      <c r="BK51" s="29"/>
-      <c r="BL51" s="29"/>
-      <c r="BM51" s="29"/>
-      <c r="BN51" s="29"/>
-      <c r="BO51" s="29"/>
-      <c r="BP51" s="29"/>
-      <c r="BQ51" s="30"/>
-      <c r="BR51" s="17"/>
+      <c r="B51" s="31"/>
+      <c r="E51" s="13"/>
+      <c r="F51" s="13"/>
+      <c r="G51" s="13"/>
+      <c r="H51" s="13"/>
+      <c r="I51" s="13"/>
+      <c r="J51" s="13"/>
+      <c r="K51" s="13"/>
+      <c r="L51" s="13"/>
+      <c r="M51" s="13"/>
+      <c r="N51" s="13"/>
+      <c r="O51" s="13"/>
+      <c r="P51" s="13"/>
+      <c r="Q51" s="13"/>
+      <c r="R51" s="13"/>
+      <c r="T51" s="13"/>
+      <c r="U51" s="13"/>
+      <c r="V51" s="13"/>
+      <c r="W51" s="13"/>
+      <c r="X51" s="13"/>
+      <c r="Y51" s="13"/>
+      <c r="Z51" s="13"/>
+      <c r="AA51" s="13"/>
+      <c r="AB51" s="13"/>
+      <c r="AC51" s="13"/>
+      <c r="AD51" s="13"/>
+      <c r="AE51" s="13"/>
+      <c r="AF51" s="13"/>
+      <c r="AG51" s="13"/>
+      <c r="AW51" s="20"/>
+      <c r="AX51" s="21"/>
+      <c r="AY51" s="21"/>
+      <c r="AZ51" s="21"/>
+      <c r="BA51" s="21"/>
+      <c r="BB51" s="21"/>
+      <c r="BC51" s="21"/>
+      <c r="BD51" s="22"/>
+      <c r="BE51" s="20"/>
+      <c r="BF51" s="21"/>
+      <c r="BG51" s="21"/>
+      <c r="BH51" s="21"/>
+      <c r="BI51" s="21"/>
+      <c r="BJ51" s="21"/>
+      <c r="BK51" s="21"/>
+      <c r="BL51" s="21"/>
+      <c r="BM51" s="21"/>
+      <c r="BN51" s="21"/>
+      <c r="BO51" s="21"/>
+      <c r="BP51" s="21"/>
+      <c r="BQ51" s="22"/>
+      <c r="BR51" s="31"/>
       <c r="BT51" s="6"/>
       <c r="BU51" s="6"/>
       <c r="BV51" s="6"/>
@@ -4890,71 +4235,33 @@
       <c r="BZ51" s="6"/>
     </row>
     <row r="52" spans="1:78" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B52" s="17"/>
-      <c r="E52" s="39"/>
-      <c r="F52" s="39"/>
-      <c r="G52" s="39"/>
-      <c r="H52" s="39"/>
-      <c r="I52" s="39"/>
-      <c r="J52" s="39"/>
-      <c r="K52" s="39"/>
-      <c r="L52" s="39"/>
-      <c r="M52" s="39"/>
-      <c r="N52" s="39"/>
-      <c r="O52" s="39"/>
-      <c r="P52" s="39"/>
-      <c r="Q52" s="39"/>
-      <c r="R52" s="39"/>
-      <c r="S52" s="39"/>
-      <c r="T52" s="39"/>
-      <c r="U52" s="39"/>
-      <c r="V52" s="39"/>
-      <c r="W52" s="39"/>
-      <c r="AA52" s="39"/>
-      <c r="AB52" s="39"/>
-      <c r="AC52" s="39"/>
-      <c r="AD52" s="39"/>
-      <c r="AE52" s="39"/>
-      <c r="AF52" s="39"/>
-      <c r="AG52" s="39"/>
-      <c r="AH52" s="39"/>
-      <c r="AI52" s="39"/>
-      <c r="AJ52" s="39"/>
-      <c r="AK52" s="39"/>
-      <c r="AL52" s="39"/>
-      <c r="AM52" s="39"/>
-      <c r="AN52" s="39"/>
-      <c r="AO52" s="39"/>
-      <c r="AP52" s="39"/>
-      <c r="AQ52" s="39"/>
-      <c r="AR52" s="39"/>
-      <c r="AS52" s="39"/>
-      <c r="AW52" s="25" t="s">
+      <c r="B52" s="31"/>
+      <c r="AW52" s="17" t="s">
         <v>222</v>
       </c>
-      <c r="AX52" s="26"/>
-      <c r="AY52" s="26"/>
-      <c r="AZ52" s="26"/>
-      <c r="BA52" s="26"/>
-      <c r="BB52" s="26"/>
-      <c r="BC52" s="26"/>
-      <c r="BD52" s="27"/>
-      <c r="BE52" s="25" t="s">
+      <c r="AX52" s="18"/>
+      <c r="AY52" s="18"/>
+      <c r="AZ52" s="18"/>
+      <c r="BA52" s="18"/>
+      <c r="BB52" s="18"/>
+      <c r="BC52" s="18"/>
+      <c r="BD52" s="19"/>
+      <c r="BE52" s="17" t="s">
         <v>223</v>
       </c>
-      <c r="BF52" s="26"/>
-      <c r="BG52" s="26"/>
-      <c r="BH52" s="26"/>
-      <c r="BI52" s="26"/>
-      <c r="BJ52" s="26"/>
-      <c r="BK52" s="26"/>
-      <c r="BL52" s="26"/>
-      <c r="BM52" s="26"/>
-      <c r="BN52" s="26"/>
-      <c r="BO52" s="26"/>
-      <c r="BP52" s="26"/>
-      <c r="BQ52" s="27"/>
-      <c r="BR52" s="17"/>
+      <c r="BF52" s="18"/>
+      <c r="BG52" s="18"/>
+      <c r="BH52" s="18"/>
+      <c r="BI52" s="18"/>
+      <c r="BJ52" s="18"/>
+      <c r="BK52" s="18"/>
+      <c r="BL52" s="18"/>
+      <c r="BM52" s="18"/>
+      <c r="BN52" s="18"/>
+      <c r="BO52" s="18"/>
+      <c r="BP52" s="18"/>
+      <c r="BQ52" s="19"/>
+      <c r="BR52" s="31"/>
       <c r="BT52" s="6"/>
       <c r="BU52" s="6"/>
       <c r="BV52" s="6"/>
@@ -4964,69 +4271,31 @@
       <c r="BZ52" s="6"/>
     </row>
     <row r="53" spans="1:78" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B53" s="17"/>
-      <c r="E53" s="39"/>
-      <c r="F53" s="39"/>
-      <c r="G53" s="39"/>
-      <c r="H53" s="39"/>
-      <c r="I53" s="39"/>
-      <c r="J53" s="39"/>
-      <c r="K53" s="39"/>
-      <c r="L53" s="39"/>
-      <c r="M53" s="39"/>
-      <c r="N53" s="39"/>
-      <c r="O53" s="39"/>
-      <c r="P53" s="39"/>
-      <c r="Q53" s="39"/>
-      <c r="R53" s="39"/>
-      <c r="S53" s="39"/>
-      <c r="T53" s="39"/>
-      <c r="U53" s="39"/>
-      <c r="V53" s="39"/>
-      <c r="W53" s="39"/>
-      <c r="AA53" s="39"/>
-      <c r="AB53" s="39"/>
-      <c r="AC53" s="39"/>
-      <c r="AD53" s="39"/>
-      <c r="AE53" s="39"/>
-      <c r="AF53" s="39"/>
-      <c r="AG53" s="39"/>
-      <c r="AH53" s="39"/>
-      <c r="AI53" s="39"/>
-      <c r="AJ53" s="39"/>
-      <c r="AK53" s="39"/>
-      <c r="AL53" s="39"/>
-      <c r="AM53" s="39"/>
-      <c r="AN53" s="39"/>
-      <c r="AO53" s="39"/>
-      <c r="AP53" s="39"/>
-      <c r="AQ53" s="39"/>
-      <c r="AR53" s="39"/>
-      <c r="AS53" s="39"/>
-      <c r="AW53" s="31" t="s">
+      <c r="B53" s="31"/>
+      <c r="AW53" s="23" t="s">
         <v>224</v>
       </c>
-      <c r="AX53" s="32"/>
-      <c r="AY53" s="32"/>
-      <c r="AZ53" s="32"/>
-      <c r="BA53" s="32"/>
-      <c r="BB53" s="32"/>
-      <c r="BC53" s="32"/>
-      <c r="BD53" s="33"/>
-      <c r="BE53" s="31"/>
-      <c r="BF53" s="32"/>
-      <c r="BG53" s="32"/>
-      <c r="BH53" s="32"/>
-      <c r="BI53" s="32"/>
-      <c r="BJ53" s="32"/>
-      <c r="BK53" s="32"/>
-      <c r="BL53" s="32"/>
-      <c r="BM53" s="32"/>
-      <c r="BN53" s="32"/>
-      <c r="BO53" s="32"/>
-      <c r="BP53" s="32"/>
-      <c r="BQ53" s="33"/>
-      <c r="BR53" s="17"/>
+      <c r="AX53" s="24"/>
+      <c r="AY53" s="24"/>
+      <c r="AZ53" s="24"/>
+      <c r="BA53" s="24"/>
+      <c r="BB53" s="24"/>
+      <c r="BC53" s="24"/>
+      <c r="BD53" s="25"/>
+      <c r="BE53" s="23"/>
+      <c r="BF53" s="24"/>
+      <c r="BG53" s="24"/>
+      <c r="BH53" s="24"/>
+      <c r="BI53" s="24"/>
+      <c r="BJ53" s="24"/>
+      <c r="BK53" s="24"/>
+      <c r="BL53" s="24"/>
+      <c r="BM53" s="24"/>
+      <c r="BN53" s="24"/>
+      <c r="BO53" s="24"/>
+      <c r="BP53" s="24"/>
+      <c r="BQ53" s="25"/>
+      <c r="BR53" s="31"/>
       <c r="BT53" s="6"/>
       <c r="BU53" s="6"/>
       <c r="BV53" s="6"/>
@@ -5036,67 +4305,29 @@
       <c r="BZ53" s="6"/>
     </row>
     <row r="54" spans="1:78" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B54" s="17"/>
-      <c r="E54" s="39"/>
-      <c r="F54" s="39"/>
-      <c r="G54" s="39"/>
-      <c r="H54" s="39"/>
-      <c r="I54" s="39"/>
-      <c r="J54" s="39"/>
-      <c r="K54" s="39"/>
-      <c r="L54" s="39"/>
-      <c r="M54" s="39"/>
-      <c r="N54" s="39"/>
-      <c r="O54" s="39"/>
-      <c r="P54" s="39"/>
-      <c r="Q54" s="39"/>
-      <c r="R54" s="39"/>
-      <c r="S54" s="39"/>
-      <c r="T54" s="39"/>
-      <c r="U54" s="39"/>
-      <c r="V54" s="39"/>
-      <c r="W54" s="39"/>
-      <c r="AA54" s="39"/>
-      <c r="AB54" s="39"/>
-      <c r="AC54" s="39"/>
-      <c r="AD54" s="39"/>
-      <c r="AE54" s="39"/>
-      <c r="AF54" s="39"/>
-      <c r="AG54" s="39"/>
-      <c r="AH54" s="39"/>
-      <c r="AI54" s="39"/>
-      <c r="AJ54" s="39"/>
-      <c r="AK54" s="39"/>
-      <c r="AL54" s="39"/>
-      <c r="AM54" s="39"/>
-      <c r="AN54" s="39"/>
-      <c r="AO54" s="39"/>
-      <c r="AP54" s="39"/>
-      <c r="AQ54" s="39"/>
-      <c r="AR54" s="39"/>
-      <c r="AS54" s="39"/>
-      <c r="AW54" s="31"/>
-      <c r="AX54" s="32"/>
-      <c r="AY54" s="32"/>
-      <c r="AZ54" s="32"/>
-      <c r="BA54" s="32"/>
-      <c r="BB54" s="32"/>
-      <c r="BC54" s="32"/>
-      <c r="BD54" s="33"/>
-      <c r="BE54" s="31"/>
-      <c r="BF54" s="32"/>
-      <c r="BG54" s="32"/>
-      <c r="BH54" s="32"/>
-      <c r="BI54" s="32"/>
-      <c r="BJ54" s="32"/>
-      <c r="BK54" s="32"/>
-      <c r="BL54" s="32"/>
-      <c r="BM54" s="32"/>
-      <c r="BN54" s="32"/>
-      <c r="BO54" s="32"/>
-      <c r="BP54" s="32"/>
-      <c r="BQ54" s="33"/>
-      <c r="BR54" s="17"/>
+      <c r="B54" s="31"/>
+      <c r="AW54" s="23"/>
+      <c r="AX54" s="24"/>
+      <c r="AY54" s="24"/>
+      <c r="AZ54" s="24"/>
+      <c r="BA54" s="24"/>
+      <c r="BB54" s="24"/>
+      <c r="BC54" s="24"/>
+      <c r="BD54" s="25"/>
+      <c r="BE54" s="23"/>
+      <c r="BF54" s="24"/>
+      <c r="BG54" s="24"/>
+      <c r="BH54" s="24"/>
+      <c r="BI54" s="24"/>
+      <c r="BJ54" s="24"/>
+      <c r="BK54" s="24"/>
+      <c r="BL54" s="24"/>
+      <c r="BM54" s="24"/>
+      <c r="BN54" s="24"/>
+      <c r="BO54" s="24"/>
+      <c r="BP54" s="24"/>
+      <c r="BQ54" s="25"/>
+      <c r="BR54" s="31"/>
       <c r="BT54" s="6"/>
       <c r="BU54" s="6"/>
       <c r="BV54" s="6"/>
@@ -5106,67 +4337,29 @@
       <c r="BZ54" s="6"/>
     </row>
     <row r="55" spans="1:78" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B55" s="17"/>
-      <c r="E55" s="39"/>
-      <c r="F55" s="39"/>
-      <c r="G55" s="39"/>
-      <c r="H55" s="39"/>
-      <c r="I55" s="39"/>
-      <c r="J55" s="39"/>
-      <c r="K55" s="39"/>
-      <c r="L55" s="39"/>
-      <c r="M55" s="39"/>
-      <c r="N55" s="39"/>
-      <c r="O55" s="39"/>
-      <c r="P55" s="39"/>
-      <c r="Q55" s="39"/>
-      <c r="R55" s="39"/>
-      <c r="S55" s="39"/>
-      <c r="T55" s="39"/>
-      <c r="U55" s="39"/>
-      <c r="V55" s="39"/>
-      <c r="W55" s="39"/>
-      <c r="AA55" s="39"/>
-      <c r="AB55" s="39"/>
-      <c r="AC55" s="39"/>
-      <c r="AD55" s="39"/>
-      <c r="AE55" s="39"/>
-      <c r="AF55" s="39"/>
-      <c r="AG55" s="39"/>
-      <c r="AH55" s="39"/>
-      <c r="AI55" s="39"/>
-      <c r="AJ55" s="39"/>
-      <c r="AK55" s="39"/>
-      <c r="AL55" s="39"/>
-      <c r="AM55" s="39"/>
-      <c r="AN55" s="39"/>
-      <c r="AO55" s="39"/>
-      <c r="AP55" s="39"/>
-      <c r="AQ55" s="39"/>
-      <c r="AR55" s="39"/>
-      <c r="AS55" s="39"/>
-      <c r="AW55" s="28"/>
-      <c r="AX55" s="29"/>
-      <c r="AY55" s="29"/>
-      <c r="AZ55" s="29"/>
-      <c r="BA55" s="29"/>
-      <c r="BB55" s="29"/>
-      <c r="BC55" s="29"/>
-      <c r="BD55" s="30"/>
-      <c r="BE55" s="28"/>
-      <c r="BF55" s="29"/>
-      <c r="BG55" s="29"/>
-      <c r="BH55" s="29"/>
-      <c r="BI55" s="29"/>
-      <c r="BJ55" s="29"/>
-      <c r="BK55" s="29"/>
-      <c r="BL55" s="29"/>
-      <c r="BM55" s="29"/>
-      <c r="BN55" s="29"/>
-      <c r="BO55" s="29"/>
-      <c r="BP55" s="29"/>
-      <c r="BQ55" s="30"/>
-      <c r="BR55" s="17"/>
+      <c r="B55" s="31"/>
+      <c r="AW55" s="20"/>
+      <c r="AX55" s="21"/>
+      <c r="AY55" s="21"/>
+      <c r="AZ55" s="21"/>
+      <c r="BA55" s="21"/>
+      <c r="BB55" s="21"/>
+      <c r="BC55" s="21"/>
+      <c r="BD55" s="22"/>
+      <c r="BE55" s="20"/>
+      <c r="BF55" s="21"/>
+      <c r="BG55" s="21"/>
+      <c r="BH55" s="21"/>
+      <c r="BI55" s="21"/>
+      <c r="BJ55" s="21"/>
+      <c r="BK55" s="21"/>
+      <c r="BL55" s="21"/>
+      <c r="BM55" s="21"/>
+      <c r="BN55" s="21"/>
+      <c r="BO55" s="21"/>
+      <c r="BP55" s="21"/>
+      <c r="BQ55" s="22"/>
+      <c r="BR55" s="31"/>
       <c r="BT55" s="6"/>
       <c r="BU55" s="6"/>
       <c r="BV55" s="6"/>
@@ -5176,43 +4369,43 @@
       <c r="BZ55" s="6"/>
     </row>
     <row r="56" spans="1:78" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B56" s="18"/>
-      <c r="K56" s="14"/>
-      <c r="L56" s="15"/>
-      <c r="M56" s="15"/>
-      <c r="N56" s="15"/>
-      <c r="O56" s="15"/>
-      <c r="AI56" s="14"/>
-      <c r="AJ56" s="15"/>
-      <c r="AK56" s="15"/>
-      <c r="AL56" s="15"/>
-      <c r="AM56" s="15"/>
-      <c r="AW56" s="11" t="s">
+      <c r="B56" s="27"/>
+      <c r="K56" s="12"/>
+      <c r="L56" s="13"/>
+      <c r="M56" s="13"/>
+      <c r="N56" s="13"/>
+      <c r="O56" s="13"/>
+      <c r="AI56" s="12"/>
+      <c r="AJ56" s="13"/>
+      <c r="AK56" s="13"/>
+      <c r="AL56" s="13"/>
+      <c r="AM56" s="13"/>
+      <c r="AW56" s="14" t="s">
         <v>225</v>
       </c>
-      <c r="AX56" s="12"/>
-      <c r="AY56" s="12" t="s">
+      <c r="AX56" s="15"/>
+      <c r="AY56" s="15" t="s">
         <v>226</v>
       </c>
-      <c r="AZ56" s="12"/>
-      <c r="BA56" s="12"/>
-      <c r="BB56" s="12"/>
-      <c r="BC56" s="12"/>
-      <c r="BD56" s="12"/>
-      <c r="BE56" s="12"/>
-      <c r="BF56" s="12"/>
-      <c r="BG56" s="12"/>
-      <c r="BH56" s="12"/>
-      <c r="BI56" s="12"/>
-      <c r="BJ56" s="12"/>
-      <c r="BK56" s="12"/>
-      <c r="BL56" s="12"/>
-      <c r="BM56" s="12"/>
-      <c r="BN56" s="12"/>
-      <c r="BO56" s="12"/>
-      <c r="BP56" s="12"/>
-      <c r="BQ56" s="13"/>
-      <c r="BR56" s="18"/>
+      <c r="AZ56" s="15"/>
+      <c r="BA56" s="15"/>
+      <c r="BB56" s="15"/>
+      <c r="BC56" s="15"/>
+      <c r="BD56" s="15"/>
+      <c r="BE56" s="15"/>
+      <c r="BF56" s="15"/>
+      <c r="BG56" s="15"/>
+      <c r="BH56" s="15"/>
+      <c r="BI56" s="15"/>
+      <c r="BJ56" s="15"/>
+      <c r="BK56" s="15"/>
+      <c r="BL56" s="15"/>
+      <c r="BM56" s="15"/>
+      <c r="BN56" s="15"/>
+      <c r="BO56" s="15"/>
+      <c r="BP56" s="15"/>
+      <c r="BQ56" s="16"/>
+      <c r="BR56" s="27"/>
       <c r="BT56" s="6"/>
       <c r="BU56" s="6"/>
       <c r="BV56" s="6"/>
@@ -5222,85 +4415,85 @@
       <c r="BZ56" s="6"/>
     </row>
     <row r="57" spans="1:78" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="C57" s="11">
+      <c r="C57" s="14">
         <v>1</v>
       </c>
-      <c r="D57" s="12"/>
-      <c r="E57" s="12"/>
-      <c r="F57" s="12"/>
-      <c r="G57" s="12"/>
-      <c r="H57" s="12"/>
-      <c r="I57" s="12"/>
-      <c r="J57" s="12"/>
-      <c r="K57" s="12"/>
-      <c r="L57" s="13"/>
-      <c r="M57" s="11">
+      <c r="D57" s="15"/>
+      <c r="E57" s="15"/>
+      <c r="F57" s="15"/>
+      <c r="G57" s="15"/>
+      <c r="H57" s="15"/>
+      <c r="I57" s="15"/>
+      <c r="J57" s="15"/>
+      <c r="K57" s="15"/>
+      <c r="L57" s="16"/>
+      <c r="M57" s="14">
         <v>2</v>
       </c>
-      <c r="N57" s="12"/>
-      <c r="O57" s="12"/>
-      <c r="P57" s="12"/>
-      <c r="Q57" s="12"/>
-      <c r="R57" s="12"/>
-      <c r="S57" s="12"/>
-      <c r="T57" s="12"/>
-      <c r="U57" s="12"/>
-      <c r="V57" s="12"/>
-      <c r="W57" s="12"/>
-      <c r="X57" s="13"/>
-      <c r="Y57" s="11">
+      <c r="N57" s="15"/>
+      <c r="O57" s="15"/>
+      <c r="P57" s="15"/>
+      <c r="Q57" s="15"/>
+      <c r="R57" s="15"/>
+      <c r="S57" s="15"/>
+      <c r="T57" s="15"/>
+      <c r="U57" s="15"/>
+      <c r="V57" s="15"/>
+      <c r="W57" s="15"/>
+      <c r="X57" s="16"/>
+      <c r="Y57" s="14">
         <v>3</v>
       </c>
-      <c r="Z57" s="12"/>
-      <c r="AA57" s="12"/>
-      <c r="AB57" s="12"/>
-      <c r="AC57" s="12"/>
-      <c r="AD57" s="12"/>
-      <c r="AE57" s="12"/>
-      <c r="AF57" s="12"/>
-      <c r="AG57" s="12"/>
-      <c r="AH57" s="12"/>
-      <c r="AI57" s="13"/>
-      <c r="AJ57" s="11">
+      <c r="Z57" s="15"/>
+      <c r="AA57" s="15"/>
+      <c r="AB57" s="15"/>
+      <c r="AC57" s="15"/>
+      <c r="AD57" s="15"/>
+      <c r="AE57" s="15"/>
+      <c r="AF57" s="15"/>
+      <c r="AG57" s="15"/>
+      <c r="AH57" s="15"/>
+      <c r="AI57" s="16"/>
+      <c r="AJ57" s="14">
         <v>4</v>
       </c>
-      <c r="AK57" s="12"/>
-      <c r="AL57" s="12"/>
-      <c r="AM57" s="12"/>
-      <c r="AN57" s="12"/>
-      <c r="AO57" s="12"/>
-      <c r="AP57" s="12"/>
-      <c r="AQ57" s="12"/>
-      <c r="AR57" s="12"/>
-      <c r="AS57" s="12"/>
-      <c r="AT57" s="13"/>
-      <c r="AU57" s="11">
+      <c r="AK57" s="15"/>
+      <c r="AL57" s="15"/>
+      <c r="AM57" s="15"/>
+      <c r="AN57" s="15"/>
+      <c r="AO57" s="15"/>
+      <c r="AP57" s="15"/>
+      <c r="AQ57" s="15"/>
+      <c r="AR57" s="15"/>
+      <c r="AS57" s="15"/>
+      <c r="AT57" s="16"/>
+      <c r="AU57" s="14">
         <v>5</v>
       </c>
-      <c r="AV57" s="12"/>
-      <c r="AW57" s="12"/>
-      <c r="AX57" s="12"/>
-      <c r="AY57" s="12"/>
-      <c r="AZ57" s="12"/>
-      <c r="BA57" s="12"/>
-      <c r="BB57" s="12"/>
-      <c r="BC57" s="12"/>
-      <c r="BD57" s="12"/>
-      <c r="BE57" s="12"/>
-      <c r="BF57" s="13"/>
-      <c r="BG57" s="11">
+      <c r="AV57" s="15"/>
+      <c r="AW57" s="15"/>
+      <c r="AX57" s="15"/>
+      <c r="AY57" s="15"/>
+      <c r="AZ57" s="15"/>
+      <c r="BA57" s="15"/>
+      <c r="BB57" s="15"/>
+      <c r="BC57" s="15"/>
+      <c r="BD57" s="15"/>
+      <c r="BE57" s="15"/>
+      <c r="BF57" s="16"/>
+      <c r="BG57" s="14">
         <v>6</v>
       </c>
-      <c r="BH57" s="12"/>
-      <c r="BI57" s="12"/>
-      <c r="BJ57" s="12"/>
-      <c r="BK57" s="12"/>
-      <c r="BL57" s="12"/>
-      <c r="BM57" s="12"/>
-      <c r="BN57" s="12"/>
-      <c r="BO57" s="12"/>
-      <c r="BP57" s="12"/>
-      <c r="BQ57" s="13"/>
+      <c r="BH57" s="15"/>
+      <c r="BI57" s="15"/>
+      <c r="BJ57" s="15"/>
+      <c r="BK57" s="15"/>
+      <c r="BL57" s="15"/>
+      <c r="BM57" s="15"/>
+      <c r="BN57" s="15"/>
+      <c r="BO57" s="15"/>
+      <c r="BP57" s="15"/>
+      <c r="BQ57" s="16"/>
       <c r="BT57" s="6"/>
       <c r="BU57" s="6"/>
       <c r="BV57" s="6"/>
@@ -6012,15 +5205,165 @@
     </row>
   </sheetData>
   <mergeCells count="192">
-    <mergeCell ref="T7:AG11"/>
-    <mergeCell ref="E17:R20"/>
-    <mergeCell ref="T17:AG20"/>
-    <mergeCell ref="E26:R29"/>
-    <mergeCell ref="T26:AG29"/>
-    <mergeCell ref="E35:R39"/>
-    <mergeCell ref="T35:AG39"/>
-    <mergeCell ref="E47:R51"/>
-    <mergeCell ref="T47:AG51"/>
+    <mergeCell ref="AW56:AX56"/>
+    <mergeCell ref="BM25:BO25"/>
+    <mergeCell ref="Y57:AI57"/>
+    <mergeCell ref="BL39:BN39"/>
+    <mergeCell ref="C2:L2"/>
+    <mergeCell ref="BO41:BQ41"/>
+    <mergeCell ref="BF16:BK16"/>
+    <mergeCell ref="AY10:BB10"/>
+    <mergeCell ref="AW11:AX11"/>
+    <mergeCell ref="AY11:BB11"/>
+    <mergeCell ref="BC11:BE11"/>
+    <mergeCell ref="BF11:BK11"/>
+    <mergeCell ref="BM11:BO11"/>
+    <mergeCell ref="AY17:BB17"/>
+    <mergeCell ref="AW24:AX24"/>
+    <mergeCell ref="BF24:BK24"/>
+    <mergeCell ref="BC20:BE20"/>
+    <mergeCell ref="AY15:BB15"/>
+    <mergeCell ref="AW22:AX22"/>
+    <mergeCell ref="BA41:BH41"/>
+    <mergeCell ref="AW26:AX26"/>
+    <mergeCell ref="AY26:BB26"/>
+    <mergeCell ref="BR17:BR29"/>
+    <mergeCell ref="BM9:BO9"/>
+    <mergeCell ref="AY16:BB16"/>
+    <mergeCell ref="BO39:BQ39"/>
+    <mergeCell ref="BM19:BO19"/>
+    <mergeCell ref="BF14:BK14"/>
+    <mergeCell ref="BF23:BK23"/>
+    <mergeCell ref="BM12:BO12"/>
+    <mergeCell ref="BR3:BR16"/>
+    <mergeCell ref="BF25:BK25"/>
+    <mergeCell ref="BF22:BK22"/>
+    <mergeCell ref="BF12:BK12"/>
+    <mergeCell ref="BM20:BO20"/>
+    <mergeCell ref="BF7:BK7"/>
+    <mergeCell ref="AY21:BB21"/>
+    <mergeCell ref="BM18:BO18"/>
+    <mergeCell ref="BF19:BK19"/>
+    <mergeCell ref="BC24:BE24"/>
+    <mergeCell ref="BM7:BO7"/>
+    <mergeCell ref="BM15:BO15"/>
+    <mergeCell ref="BC25:BE25"/>
+    <mergeCell ref="AW13:AX13"/>
+    <mergeCell ref="BA45:BH45"/>
+    <mergeCell ref="AW8:AX8"/>
+    <mergeCell ref="BL45:BN45"/>
+    <mergeCell ref="BF8:BK8"/>
+    <mergeCell ref="BI40:BK40"/>
+    <mergeCell ref="AW46:AZ46"/>
+    <mergeCell ref="BC26:BE26"/>
+    <mergeCell ref="BF26:BK26"/>
+    <mergeCell ref="BM26:BO26"/>
+    <mergeCell ref="BF5:BK6"/>
+    <mergeCell ref="BC17:BE17"/>
+    <mergeCell ref="AY24:BB24"/>
+    <mergeCell ref="BC5:BE6"/>
+    <mergeCell ref="BO42:BQ42"/>
+    <mergeCell ref="BP5:BP6"/>
+    <mergeCell ref="BO40:BQ40"/>
+    <mergeCell ref="BQ5:BQ6"/>
+    <mergeCell ref="BM21:BO21"/>
+    <mergeCell ref="BF13:BK13"/>
+    <mergeCell ref="B17:B29"/>
+    <mergeCell ref="AY9:BB9"/>
+    <mergeCell ref="AW25:AX25"/>
+    <mergeCell ref="AW7:AX7"/>
+    <mergeCell ref="AW15:AX15"/>
+    <mergeCell ref="B44:B56"/>
+    <mergeCell ref="BL41:BN41"/>
+    <mergeCell ref="BA42:BH42"/>
+    <mergeCell ref="AW49:BD51"/>
+    <mergeCell ref="BI45:BK45"/>
+    <mergeCell ref="BC16:BE16"/>
+    <mergeCell ref="BF20:BK20"/>
+    <mergeCell ref="AW20:AX20"/>
+    <mergeCell ref="B30:B43"/>
+    <mergeCell ref="AW47:AZ47"/>
+    <mergeCell ref="BF10:BK10"/>
+    <mergeCell ref="AI28:AM29"/>
+    <mergeCell ref="AW10:AX10"/>
+    <mergeCell ref="BF17:BK17"/>
+    <mergeCell ref="AW23:AX23"/>
+    <mergeCell ref="BC18:BE18"/>
+    <mergeCell ref="AY31:BQ36"/>
+    <mergeCell ref="AY12:BB12"/>
+    <mergeCell ref="BC14:BE14"/>
+    <mergeCell ref="BE52:BQ55"/>
+    <mergeCell ref="M57:X57"/>
+    <mergeCell ref="AX42:AZ42"/>
+    <mergeCell ref="AW43:AW44"/>
+    <mergeCell ref="BR30:BR43"/>
+    <mergeCell ref="BM8:BO8"/>
+    <mergeCell ref="AX39:AZ39"/>
+    <mergeCell ref="BM16:BO16"/>
+    <mergeCell ref="BA46:BH46"/>
+    <mergeCell ref="K56:O56"/>
+    <mergeCell ref="BA39:BH39"/>
+    <mergeCell ref="BM10:BO10"/>
+    <mergeCell ref="AW31:AX36"/>
+    <mergeCell ref="BE48:BQ49"/>
+    <mergeCell ref="BL42:BN42"/>
+    <mergeCell ref="AI56:AM56"/>
+    <mergeCell ref="AY23:BB23"/>
+    <mergeCell ref="AX45:AZ45"/>
+    <mergeCell ref="BI42:BK42"/>
+    <mergeCell ref="BF21:BK21"/>
+    <mergeCell ref="BO45:BQ45"/>
+    <mergeCell ref="BR44:BR56"/>
+    <mergeCell ref="AW52:BD52"/>
+    <mergeCell ref="AW16:AX16"/>
+    <mergeCell ref="B3:B16"/>
+    <mergeCell ref="BC9:BE9"/>
+    <mergeCell ref="AY18:BB18"/>
+    <mergeCell ref="BI47:BQ47"/>
+    <mergeCell ref="AW21:AX21"/>
+    <mergeCell ref="AJ57:AT57"/>
+    <mergeCell ref="BC19:BE19"/>
+    <mergeCell ref="AX41:AZ41"/>
+    <mergeCell ref="BM24:BO24"/>
+    <mergeCell ref="BI39:BK39"/>
+    <mergeCell ref="BC21:BE21"/>
+    <mergeCell ref="AX43:AZ44"/>
+    <mergeCell ref="AY19:BB19"/>
+    <mergeCell ref="AY13:BB13"/>
+    <mergeCell ref="AX40:AZ40"/>
+    <mergeCell ref="AY22:BB22"/>
+    <mergeCell ref="BA43:BH44"/>
+    <mergeCell ref="BL40:BN40"/>
+    <mergeCell ref="BC12:BE12"/>
+    <mergeCell ref="BL43:BN44"/>
+    <mergeCell ref="C3:D5"/>
+    <mergeCell ref="AT3:AV11"/>
+    <mergeCell ref="C57:L57"/>
+    <mergeCell ref="BI41:BK41"/>
+    <mergeCell ref="AW3:BQ4"/>
+    <mergeCell ref="AW48:BD48"/>
+    <mergeCell ref="BE50:BQ51"/>
+    <mergeCell ref="AY5:BB6"/>
+    <mergeCell ref="BC13:BE13"/>
+    <mergeCell ref="BM13:BO13"/>
+    <mergeCell ref="AY20:BB20"/>
+    <mergeCell ref="BM22:BO22"/>
+    <mergeCell ref="AW14:AX14"/>
+    <mergeCell ref="AY7:BB7"/>
+    <mergeCell ref="BC10:BE10"/>
+    <mergeCell ref="BM17:BO17"/>
+    <mergeCell ref="BC23:BE23"/>
+    <mergeCell ref="BF18:BK18"/>
+    <mergeCell ref="AW12:AX12"/>
+    <mergeCell ref="BM14:BO14"/>
+    <mergeCell ref="BI46:BQ46"/>
+    <mergeCell ref="BM23:BO23"/>
+    <mergeCell ref="BF15:BK15"/>
+    <mergeCell ref="BL5:BL6"/>
+    <mergeCell ref="AY14:BB14"/>
+    <mergeCell ref="AY25:BB25"/>
+    <mergeCell ref="BM5:BO6"/>
+    <mergeCell ref="AW5:AX6"/>
     <mergeCell ref="M2:X2"/>
     <mergeCell ref="AU2:BF2"/>
     <mergeCell ref="AW18:AX18"/>
@@ -6045,165 +5388,15 @@
     <mergeCell ref="AW19:AX19"/>
     <mergeCell ref="AW53:BD55"/>
     <mergeCell ref="E7:R11"/>
-    <mergeCell ref="AW3:BQ4"/>
-    <mergeCell ref="AW48:BD48"/>
-    <mergeCell ref="BE50:BQ51"/>
-    <mergeCell ref="AY5:BB6"/>
-    <mergeCell ref="BC13:BE13"/>
-    <mergeCell ref="BM13:BO13"/>
-    <mergeCell ref="AY20:BB20"/>
-    <mergeCell ref="BM22:BO22"/>
-    <mergeCell ref="AW14:AX14"/>
-    <mergeCell ref="AY7:BB7"/>
-    <mergeCell ref="BC10:BE10"/>
-    <mergeCell ref="BM17:BO17"/>
-    <mergeCell ref="BC23:BE23"/>
-    <mergeCell ref="BF18:BK18"/>
-    <mergeCell ref="AW12:AX12"/>
-    <mergeCell ref="BM14:BO14"/>
-    <mergeCell ref="BI46:BQ46"/>
-    <mergeCell ref="BM23:BO23"/>
-    <mergeCell ref="BF15:BK15"/>
-    <mergeCell ref="BL5:BL6"/>
-    <mergeCell ref="AY14:BB14"/>
-    <mergeCell ref="AY25:BB25"/>
-    <mergeCell ref="B3:B16"/>
-    <mergeCell ref="BC9:BE9"/>
-    <mergeCell ref="AY18:BB18"/>
-    <mergeCell ref="BI47:BQ47"/>
-    <mergeCell ref="AW21:AX21"/>
-    <mergeCell ref="AJ57:AT57"/>
-    <mergeCell ref="BC19:BE19"/>
-    <mergeCell ref="AX41:AZ41"/>
-    <mergeCell ref="BM24:BO24"/>
-    <mergeCell ref="BI39:BK39"/>
-    <mergeCell ref="BC21:BE21"/>
-    <mergeCell ref="AX43:AZ44"/>
-    <mergeCell ref="AY19:BB19"/>
-    <mergeCell ref="AY13:BB13"/>
-    <mergeCell ref="AX40:AZ40"/>
-    <mergeCell ref="AY22:BB22"/>
-    <mergeCell ref="BA43:BH44"/>
-    <mergeCell ref="BL40:BN40"/>
-    <mergeCell ref="BC12:BE12"/>
-    <mergeCell ref="BL43:BN44"/>
-    <mergeCell ref="C3:D5"/>
-    <mergeCell ref="AT3:AV11"/>
-    <mergeCell ref="C57:L57"/>
-    <mergeCell ref="BI41:BK41"/>
-    <mergeCell ref="BE52:BQ55"/>
-    <mergeCell ref="M57:X57"/>
-    <mergeCell ref="AX42:AZ42"/>
-    <mergeCell ref="AW43:AW44"/>
-    <mergeCell ref="BR30:BR43"/>
-    <mergeCell ref="BM8:BO8"/>
-    <mergeCell ref="AX39:AZ39"/>
-    <mergeCell ref="BM16:BO16"/>
-    <mergeCell ref="BA46:BH46"/>
-    <mergeCell ref="K56:O56"/>
-    <mergeCell ref="BA39:BH39"/>
-    <mergeCell ref="BM10:BO10"/>
-    <mergeCell ref="AW31:AX36"/>
-    <mergeCell ref="BE48:BQ49"/>
-    <mergeCell ref="BL42:BN42"/>
-    <mergeCell ref="AI56:AM56"/>
-    <mergeCell ref="AY23:BB23"/>
-    <mergeCell ref="AX45:AZ45"/>
-    <mergeCell ref="BI42:BK42"/>
-    <mergeCell ref="BF21:BK21"/>
-    <mergeCell ref="BO45:BQ45"/>
-    <mergeCell ref="BR44:BR56"/>
-    <mergeCell ref="B17:B29"/>
-    <mergeCell ref="AY9:BB9"/>
-    <mergeCell ref="AW25:AX25"/>
-    <mergeCell ref="AW7:AX7"/>
-    <mergeCell ref="AW15:AX15"/>
-    <mergeCell ref="B44:B56"/>
-    <mergeCell ref="BL41:BN41"/>
-    <mergeCell ref="BA42:BH42"/>
-    <mergeCell ref="AW49:BD51"/>
-    <mergeCell ref="BI45:BK45"/>
-    <mergeCell ref="BC16:BE16"/>
-    <mergeCell ref="BF20:BK20"/>
-    <mergeCell ref="AW20:AX20"/>
-    <mergeCell ref="B30:B43"/>
-    <mergeCell ref="AW47:AZ47"/>
-    <mergeCell ref="BF10:BK10"/>
-    <mergeCell ref="AI28:AM29"/>
-    <mergeCell ref="AW10:AX10"/>
-    <mergeCell ref="BF17:BK17"/>
-    <mergeCell ref="AW23:AX23"/>
-    <mergeCell ref="BM5:BO6"/>
-    <mergeCell ref="AW5:AX6"/>
-    <mergeCell ref="BC18:BE18"/>
-    <mergeCell ref="AY31:BQ36"/>
-    <mergeCell ref="AY12:BB12"/>
-    <mergeCell ref="BC14:BE14"/>
-    <mergeCell ref="AW52:BD52"/>
-    <mergeCell ref="AW16:AX16"/>
-    <mergeCell ref="BF5:BK6"/>
-    <mergeCell ref="BC17:BE17"/>
-    <mergeCell ref="AY24:BB24"/>
-    <mergeCell ref="BC5:BE6"/>
-    <mergeCell ref="BO42:BQ42"/>
-    <mergeCell ref="BP5:BP6"/>
-    <mergeCell ref="BO40:BQ40"/>
-    <mergeCell ref="BQ5:BQ6"/>
-    <mergeCell ref="BM21:BO21"/>
-    <mergeCell ref="BF13:BK13"/>
-    <mergeCell ref="AW13:AX13"/>
-    <mergeCell ref="BA45:BH45"/>
-    <mergeCell ref="AW8:AX8"/>
-    <mergeCell ref="BL45:BN45"/>
-    <mergeCell ref="BF8:BK8"/>
-    <mergeCell ref="BI40:BK40"/>
-    <mergeCell ref="AW46:AZ46"/>
-    <mergeCell ref="BC26:BE26"/>
-    <mergeCell ref="BF26:BK26"/>
-    <mergeCell ref="BM26:BO26"/>
-    <mergeCell ref="BR17:BR29"/>
-    <mergeCell ref="BM9:BO9"/>
-    <mergeCell ref="AY16:BB16"/>
-    <mergeCell ref="BO39:BQ39"/>
-    <mergeCell ref="BM19:BO19"/>
-    <mergeCell ref="BF14:BK14"/>
-    <mergeCell ref="BF23:BK23"/>
-    <mergeCell ref="BM12:BO12"/>
-    <mergeCell ref="BR3:BR16"/>
-    <mergeCell ref="BF25:BK25"/>
-    <mergeCell ref="BF22:BK22"/>
-    <mergeCell ref="BF12:BK12"/>
-    <mergeCell ref="BM20:BO20"/>
-    <mergeCell ref="BF7:BK7"/>
-    <mergeCell ref="AY21:BB21"/>
-    <mergeCell ref="BM18:BO18"/>
-    <mergeCell ref="BF19:BK19"/>
-    <mergeCell ref="BC24:BE24"/>
-    <mergeCell ref="BM7:BO7"/>
-    <mergeCell ref="BM15:BO15"/>
-    <mergeCell ref="BC25:BE25"/>
-    <mergeCell ref="AW56:AX56"/>
-    <mergeCell ref="BM25:BO25"/>
-    <mergeCell ref="Y57:AI57"/>
-    <mergeCell ref="BL39:BN39"/>
-    <mergeCell ref="C2:L2"/>
-    <mergeCell ref="BO41:BQ41"/>
-    <mergeCell ref="BF16:BK16"/>
-    <mergeCell ref="AY10:BB10"/>
-    <mergeCell ref="AW11:AX11"/>
-    <mergeCell ref="AY11:BB11"/>
-    <mergeCell ref="BC11:BE11"/>
-    <mergeCell ref="BF11:BK11"/>
-    <mergeCell ref="BM11:BO11"/>
-    <mergeCell ref="AY17:BB17"/>
-    <mergeCell ref="AW24:AX24"/>
-    <mergeCell ref="BF24:BK24"/>
-    <mergeCell ref="BC20:BE20"/>
-    <mergeCell ref="AY15:BB15"/>
-    <mergeCell ref="AW22:AX22"/>
-    <mergeCell ref="BA41:BH41"/>
-    <mergeCell ref="AW26:AX26"/>
-    <mergeCell ref="AY26:BB26"/>
+    <mergeCell ref="T7:AG11"/>
+    <mergeCell ref="E17:R20"/>
+    <mergeCell ref="T17:AG20"/>
+    <mergeCell ref="E26:R29"/>
+    <mergeCell ref="T26:AG29"/>
+    <mergeCell ref="E35:R39"/>
+    <mergeCell ref="T35:AG39"/>
+    <mergeCell ref="E47:R51"/>
+    <mergeCell ref="T47:AG51"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/가공도_도면_1.xlsx
+++ b/가공도_도면_1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\duddl\Desktop\Project\a2z\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B2C5A5C-2569-4B41-9B00-81C6FA9AFB01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C255A571-DDB1-4FDE-BFE8-F4B87DC5E7EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="696" yWindow="720" windowWidth="20256" windowHeight="11520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="238">
   <si>
     <t>A</t>
   </si>
@@ -736,6 +736,10 @@
   </si>
   <si>
     <t>{Input_204}</t>
+  </si>
+  <si>
+    <t>{View_8}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -994,10 +998,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1005,6 +1005,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1034,11 +1043,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1048,12 +1058,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1444,85 +1448,85 @@
       <c r="BZ1" s="6"/>
     </row>
     <row r="2" spans="1:78" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="C2" s="14">
+      <c r="C2" s="12">
         <v>1</v>
       </c>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
-      <c r="H2" s="15"/>
-      <c r="I2" s="15"/>
-      <c r="J2" s="15"/>
-      <c r="K2" s="15"/>
-      <c r="L2" s="16"/>
-      <c r="M2" s="14">
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="13"/>
+      <c r="J2" s="13"/>
+      <c r="K2" s="13"/>
+      <c r="L2" s="14"/>
+      <c r="M2" s="12">
         <v>2</v>
       </c>
-      <c r="N2" s="15"/>
-      <c r="O2" s="15"/>
-      <c r="P2" s="15"/>
-      <c r="Q2" s="15"/>
-      <c r="R2" s="15"/>
-      <c r="S2" s="15"/>
-      <c r="T2" s="15"/>
-      <c r="U2" s="15"/>
-      <c r="V2" s="15"/>
-      <c r="W2" s="15"/>
-      <c r="X2" s="16"/>
-      <c r="Y2" s="14">
+      <c r="N2" s="13"/>
+      <c r="O2" s="13"/>
+      <c r="P2" s="13"/>
+      <c r="Q2" s="13"/>
+      <c r="R2" s="13"/>
+      <c r="S2" s="13"/>
+      <c r="T2" s="13"/>
+      <c r="U2" s="13"/>
+      <c r="V2" s="13"/>
+      <c r="W2" s="13"/>
+      <c r="X2" s="14"/>
+      <c r="Y2" s="12">
         <v>3</v>
       </c>
-      <c r="Z2" s="15"/>
-      <c r="AA2" s="15"/>
-      <c r="AB2" s="15"/>
-      <c r="AC2" s="15"/>
-      <c r="AD2" s="15"/>
-      <c r="AE2" s="15"/>
-      <c r="AF2" s="15"/>
-      <c r="AG2" s="15"/>
-      <c r="AH2" s="15"/>
-      <c r="AI2" s="16"/>
-      <c r="AJ2" s="14">
+      <c r="Z2" s="13"/>
+      <c r="AA2" s="13"/>
+      <c r="AB2" s="13"/>
+      <c r="AC2" s="13"/>
+      <c r="AD2" s="13"/>
+      <c r="AE2" s="13"/>
+      <c r="AF2" s="13"/>
+      <c r="AG2" s="13"/>
+      <c r="AH2" s="13"/>
+      <c r="AI2" s="14"/>
+      <c r="AJ2" s="12">
         <v>4</v>
       </c>
-      <c r="AK2" s="15"/>
-      <c r="AL2" s="15"/>
-      <c r="AM2" s="15"/>
-      <c r="AN2" s="15"/>
-      <c r="AO2" s="15"/>
-      <c r="AP2" s="15"/>
-      <c r="AQ2" s="15"/>
-      <c r="AR2" s="15"/>
-      <c r="AS2" s="15"/>
-      <c r="AT2" s="16"/>
-      <c r="AU2" s="14">
+      <c r="AK2" s="13"/>
+      <c r="AL2" s="13"/>
+      <c r="AM2" s="13"/>
+      <c r="AN2" s="13"/>
+      <c r="AO2" s="13"/>
+      <c r="AP2" s="13"/>
+      <c r="AQ2" s="13"/>
+      <c r="AR2" s="13"/>
+      <c r="AS2" s="13"/>
+      <c r="AT2" s="14"/>
+      <c r="AU2" s="12">
         <v>5</v>
       </c>
-      <c r="AV2" s="15"/>
-      <c r="AW2" s="15"/>
-      <c r="AX2" s="15"/>
-      <c r="AY2" s="15"/>
-      <c r="AZ2" s="15"/>
-      <c r="BA2" s="15"/>
-      <c r="BB2" s="15"/>
-      <c r="BC2" s="15"/>
-      <c r="BD2" s="15"/>
-      <c r="BE2" s="15"/>
-      <c r="BF2" s="16"/>
-      <c r="BG2" s="14">
+      <c r="AV2" s="13"/>
+      <c r="AW2" s="13"/>
+      <c r="AX2" s="13"/>
+      <c r="AY2" s="13"/>
+      <c r="AZ2" s="13"/>
+      <c r="BA2" s="13"/>
+      <c r="BB2" s="13"/>
+      <c r="BC2" s="13"/>
+      <c r="BD2" s="13"/>
+      <c r="BE2" s="13"/>
+      <c r="BF2" s="14"/>
+      <c r="BG2" s="12">
         <v>6</v>
       </c>
-      <c r="BH2" s="15"/>
-      <c r="BI2" s="15"/>
-      <c r="BJ2" s="15"/>
-      <c r="BK2" s="15"/>
-      <c r="BL2" s="15"/>
-      <c r="BM2" s="15"/>
-      <c r="BN2" s="15"/>
-      <c r="BO2" s="15"/>
-      <c r="BP2" s="15"/>
-      <c r="BQ2" s="16"/>
+      <c r="BH2" s="13"/>
+      <c r="BI2" s="13"/>
+      <c r="BJ2" s="13"/>
+      <c r="BK2" s="13"/>
+      <c r="BL2" s="13"/>
+      <c r="BM2" s="13"/>
+      <c r="BN2" s="13"/>
+      <c r="BO2" s="13"/>
+      <c r="BP2" s="13"/>
+      <c r="BQ2" s="14"/>
       <c r="BR2" s="2"/>
       <c r="BT2" s="6"/>
       <c r="BU2" s="6"/>
@@ -1533,43 +1537,43 @@
       <c r="BZ2" s="6"/>
     </row>
     <row r="3" spans="1:78" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B3" s="26" t="s">
+      <c r="B3" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="32" t="s">
+      <c r="C3" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="32"/>
+      <c r="D3" s="29"/>
       <c r="Y3" s="3"/>
-      <c r="AT3" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="AU3" s="32"/>
-      <c r="AV3" s="32"/>
-      <c r="AW3" s="17" t="s">
+      <c r="AT3" s="29" t="s">
+        <v>237</v>
+      </c>
+      <c r="AU3" s="29"/>
+      <c r="AV3" s="29"/>
+      <c r="AW3" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="AX3" s="18"/>
-      <c r="AY3" s="18"/>
-      <c r="AZ3" s="18"/>
-      <c r="BA3" s="18"/>
-      <c r="BB3" s="18"/>
-      <c r="BC3" s="18"/>
-      <c r="BD3" s="18"/>
-      <c r="BE3" s="18"/>
-      <c r="BF3" s="18"/>
-      <c r="BG3" s="18"/>
-      <c r="BH3" s="18"/>
-      <c r="BI3" s="18"/>
-      <c r="BJ3" s="18"/>
-      <c r="BK3" s="18"/>
-      <c r="BL3" s="18"/>
-      <c r="BM3" s="18"/>
-      <c r="BN3" s="18"/>
-      <c r="BO3" s="18"/>
-      <c r="BP3" s="18"/>
-      <c r="BQ3" s="19"/>
-      <c r="BR3" s="26" t="s">
+      <c r="AX3" s="19"/>
+      <c r="AY3" s="19"/>
+      <c r="AZ3" s="19"/>
+      <c r="BA3" s="19"/>
+      <c r="BB3" s="19"/>
+      <c r="BC3" s="19"/>
+      <c r="BD3" s="19"/>
+      <c r="BE3" s="19"/>
+      <c r="BF3" s="19"/>
+      <c r="BG3" s="19"/>
+      <c r="BH3" s="19"/>
+      <c r="BI3" s="19"/>
+      <c r="BJ3" s="19"/>
+      <c r="BK3" s="19"/>
+      <c r="BL3" s="19"/>
+      <c r="BM3" s="19"/>
+      <c r="BN3" s="19"/>
+      <c r="BO3" s="19"/>
+      <c r="BP3" s="19"/>
+      <c r="BQ3" s="20"/>
+      <c r="BR3" s="15" t="s">
         <v>0</v>
       </c>
       <c r="BT3" s="6"/>
@@ -1581,36 +1585,36 @@
       <c r="BZ3" s="6"/>
     </row>
     <row r="4" spans="1:78" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="31"/>
-      <c r="C4" s="32"/>
-      <c r="D4" s="32"/>
+      <c r="B4" s="16"/>
+      <c r="C4" s="29"/>
+      <c r="D4" s="29"/>
       <c r="E4" s="11"/>
       <c r="AA4" s="11"/>
-      <c r="AT4" s="32"/>
-      <c r="AU4" s="32"/>
-      <c r="AV4" s="32"/>
-      <c r="AW4" s="20"/>
-      <c r="AX4" s="21"/>
-      <c r="AY4" s="21"/>
-      <c r="AZ4" s="21"/>
-      <c r="BA4" s="21"/>
-      <c r="BB4" s="21"/>
-      <c r="BC4" s="21"/>
-      <c r="BD4" s="21"/>
-      <c r="BE4" s="21"/>
-      <c r="BF4" s="21"/>
-      <c r="BG4" s="21"/>
-      <c r="BH4" s="21"/>
-      <c r="BI4" s="21"/>
-      <c r="BJ4" s="21"/>
-      <c r="BK4" s="21"/>
-      <c r="BL4" s="21"/>
-      <c r="BM4" s="21"/>
-      <c r="BN4" s="21"/>
-      <c r="BO4" s="21"/>
-      <c r="BP4" s="21"/>
-      <c r="BQ4" s="22"/>
-      <c r="BR4" s="31"/>
+      <c r="AT4" s="29"/>
+      <c r="AU4" s="29"/>
+      <c r="AV4" s="29"/>
+      <c r="AW4" s="21"/>
+      <c r="AX4" s="22"/>
+      <c r="AY4" s="22"/>
+      <c r="AZ4" s="22"/>
+      <c r="BA4" s="22"/>
+      <c r="BB4" s="22"/>
+      <c r="BC4" s="22"/>
+      <c r="BD4" s="22"/>
+      <c r="BE4" s="22"/>
+      <c r="BF4" s="22"/>
+      <c r="BG4" s="22"/>
+      <c r="BH4" s="22"/>
+      <c r="BI4" s="22"/>
+      <c r="BJ4" s="22"/>
+      <c r="BK4" s="22"/>
+      <c r="BL4" s="22"/>
+      <c r="BM4" s="22"/>
+      <c r="BN4" s="22"/>
+      <c r="BO4" s="22"/>
+      <c r="BP4" s="22"/>
+      <c r="BQ4" s="23"/>
+      <c r="BR4" s="16"/>
       <c r="BT4" s="6"/>
       <c r="BU4" s="6"/>
       <c r="BV4" s="6"/>
@@ -1620,50 +1624,50 @@
       <c r="BZ4" s="6"/>
     </row>
     <row r="5" spans="1:78" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B5" s="31"/>
-      <c r="C5" s="32"/>
-      <c r="D5" s="32"/>
-      <c r="AT5" s="32"/>
-      <c r="AU5" s="32"/>
-      <c r="AV5" s="32"/>
-      <c r="AW5" s="17" t="s">
+      <c r="B5" s="16"/>
+      <c r="C5" s="29"/>
+      <c r="D5" s="29"/>
+      <c r="AT5" s="29"/>
+      <c r="AU5" s="29"/>
+      <c r="AV5" s="29"/>
+      <c r="AW5" s="18" t="s">
         <v>227</v>
       </c>
-      <c r="AX5" s="19"/>
-      <c r="AY5" s="17" t="s">
+      <c r="AX5" s="20"/>
+      <c r="AY5" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="AZ5" s="18"/>
-      <c r="BA5" s="18"/>
-      <c r="BB5" s="19"/>
-      <c r="BC5" s="17" t="s">
+      <c r="AZ5" s="19"/>
+      <c r="BA5" s="19"/>
+      <c r="BB5" s="20"/>
+      <c r="BC5" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="BD5" s="18"/>
-      <c r="BE5" s="19"/>
-      <c r="BF5" s="17" t="s">
+      <c r="BD5" s="19"/>
+      <c r="BE5" s="20"/>
+      <c r="BF5" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="BG5" s="18"/>
-      <c r="BH5" s="18"/>
-      <c r="BI5" s="18"/>
-      <c r="BJ5" s="18"/>
-      <c r="BK5" s="19"/>
-      <c r="BL5" s="26" t="s">
+      <c r="BG5" s="19"/>
+      <c r="BH5" s="19"/>
+      <c r="BI5" s="19"/>
+      <c r="BJ5" s="19"/>
+      <c r="BK5" s="20"/>
+      <c r="BL5" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="BM5" s="17" t="s">
+      <c r="BM5" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="BN5" s="18"/>
-      <c r="BO5" s="19"/>
-      <c r="BP5" s="26" t="s">
+      <c r="BN5" s="19"/>
+      <c r="BO5" s="20"/>
+      <c r="BP5" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="BQ5" s="26" t="s">
+      <c r="BQ5" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="BR5" s="31"/>
+      <c r="BR5" s="16"/>
       <c r="BT5" s="6"/>
       <c r="BU5" s="6"/>
       <c r="BV5" s="6"/>
@@ -1673,32 +1677,32 @@
       <c r="BZ5" s="6"/>
     </row>
     <row r="6" spans="1:78" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B6" s="31"/>
-      <c r="AT6" s="32"/>
-      <c r="AU6" s="32"/>
-      <c r="AV6" s="32"/>
-      <c r="AW6" s="20"/>
-      <c r="AX6" s="22"/>
-      <c r="AY6" s="20"/>
-      <c r="AZ6" s="21"/>
-      <c r="BA6" s="21"/>
-      <c r="BB6" s="22"/>
-      <c r="BC6" s="20"/>
-      <c r="BD6" s="21"/>
-      <c r="BE6" s="22"/>
-      <c r="BF6" s="20"/>
-      <c r="BG6" s="21"/>
-      <c r="BH6" s="21"/>
-      <c r="BI6" s="21"/>
-      <c r="BJ6" s="21"/>
-      <c r="BK6" s="22"/>
-      <c r="BL6" s="27"/>
-      <c r="BM6" s="20"/>
-      <c r="BN6" s="21"/>
-      <c r="BO6" s="22"/>
-      <c r="BP6" s="27"/>
-      <c r="BQ6" s="27"/>
-      <c r="BR6" s="31"/>
+      <c r="B6" s="16"/>
+      <c r="AT6" s="29"/>
+      <c r="AU6" s="29"/>
+      <c r="AV6" s="29"/>
+      <c r="AW6" s="21"/>
+      <c r="AX6" s="23"/>
+      <c r="AY6" s="21"/>
+      <c r="AZ6" s="22"/>
+      <c r="BA6" s="22"/>
+      <c r="BB6" s="23"/>
+      <c r="BC6" s="21"/>
+      <c r="BD6" s="22"/>
+      <c r="BE6" s="23"/>
+      <c r="BF6" s="21"/>
+      <c r="BG6" s="22"/>
+      <c r="BH6" s="22"/>
+      <c r="BI6" s="22"/>
+      <c r="BJ6" s="22"/>
+      <c r="BK6" s="23"/>
+      <c r="BL6" s="17"/>
+      <c r="BM6" s="21"/>
+      <c r="BN6" s="22"/>
+      <c r="BO6" s="23"/>
+      <c r="BP6" s="17"/>
+      <c r="BQ6" s="17"/>
+      <c r="BR6" s="16"/>
       <c r="BT6" s="6"/>
       <c r="BU6" s="6"/>
       <c r="BV6" s="6"/>
@@ -1708,80 +1712,80 @@
       <c r="BZ6" s="6"/>
     </row>
     <row r="7" spans="1:78" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B7" s="31"/>
-      <c r="E7" s="12" t="s">
+      <c r="B7" s="16"/>
+      <c r="E7" s="27" t="s">
         <v>232</v>
       </c>
-      <c r="F7" s="13"/>
-      <c r="G7" s="13"/>
-      <c r="H7" s="13"/>
-      <c r="I7" s="13"/>
-      <c r="J7" s="13"/>
-      <c r="K7" s="13"/>
-      <c r="L7" s="13"/>
-      <c r="M7" s="13"/>
-      <c r="N7" s="13"/>
-      <c r="O7" s="13"/>
-      <c r="P7" s="13"/>
-      <c r="Q7" s="13"/>
-      <c r="R7" s="13"/>
-      <c r="T7" s="12" t="s">
+      <c r="F7" s="28"/>
+      <c r="G7" s="28"/>
+      <c r="H7" s="28"/>
+      <c r="I7" s="28"/>
+      <c r="J7" s="28"/>
+      <c r="K7" s="28"/>
+      <c r="L7" s="28"/>
+      <c r="M7" s="28"/>
+      <c r="N7" s="28"/>
+      <c r="O7" s="28"/>
+      <c r="P7" s="28"/>
+      <c r="Q7" s="28"/>
+      <c r="R7" s="28"/>
+      <c r="T7" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="U7" s="13"/>
-      <c r="V7" s="13"/>
-      <c r="W7" s="13"/>
-      <c r="X7" s="13"/>
-      <c r="Y7" s="13"/>
-      <c r="Z7" s="13"/>
-      <c r="AA7" s="13"/>
-      <c r="AB7" s="13"/>
-      <c r="AC7" s="13"/>
-      <c r="AD7" s="13"/>
-      <c r="AE7" s="13"/>
-      <c r="AF7" s="13"/>
-      <c r="AG7" s="13"/>
-      <c r="AT7" s="32"/>
-      <c r="AU7" s="32"/>
-      <c r="AV7" s="32"/>
-      <c r="AW7" s="14" t="s">
+      <c r="U7" s="28"/>
+      <c r="V7" s="28"/>
+      <c r="W7" s="28"/>
+      <c r="X7" s="28"/>
+      <c r="Y7" s="28"/>
+      <c r="Z7" s="28"/>
+      <c r="AA7" s="28"/>
+      <c r="AB7" s="28"/>
+      <c r="AC7" s="28"/>
+      <c r="AD7" s="28"/>
+      <c r="AE7" s="28"/>
+      <c r="AF7" s="28"/>
+      <c r="AG7" s="28"/>
+      <c r="AT7" s="29"/>
+      <c r="AU7" s="29"/>
+      <c r="AV7" s="29"/>
+      <c r="AW7" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="AX7" s="16"/>
-      <c r="AY7" s="14" t="s">
+      <c r="AX7" s="14"/>
+      <c r="AY7" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="AZ7" s="15"/>
-      <c r="BA7" s="15"/>
-      <c r="BB7" s="16"/>
-      <c r="BC7" s="14" t="s">
+      <c r="AZ7" s="13"/>
+      <c r="BA7" s="13"/>
+      <c r="BB7" s="14"/>
+      <c r="BC7" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="BD7" s="15"/>
-      <c r="BE7" s="16"/>
-      <c r="BF7" s="14" t="s">
+      <c r="BD7" s="13"/>
+      <c r="BE7" s="14"/>
+      <c r="BF7" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="BG7" s="15"/>
-      <c r="BH7" s="15"/>
-      <c r="BI7" s="15"/>
-      <c r="BJ7" s="15"/>
-      <c r="BK7" s="16"/>
+      <c r="BG7" s="13"/>
+      <c r="BH7" s="13"/>
+      <c r="BI7" s="13"/>
+      <c r="BJ7" s="13"/>
+      <c r="BK7" s="14"/>
       <c r="BL7" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="BM7" s="14" t="s">
+      <c r="BM7" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="BN7" s="15"/>
-      <c r="BO7" s="16"/>
+      <c r="BN7" s="13"/>
+      <c r="BO7" s="14"/>
       <c r="BP7" s="4" t="s">
         <v>19</v>
       </c>
       <c r="BQ7" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="BR7" s="31"/>
+      <c r="BR7" s="16"/>
       <c r="BT7" s="6"/>
       <c r="BU7" s="6"/>
       <c r="BV7" s="6"/>
@@ -1791,76 +1795,76 @@
       <c r="BZ7" s="6"/>
     </row>
     <row r="8" spans="1:78" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B8" s="31"/>
-      <c r="E8" s="13"/>
-      <c r="F8" s="13"/>
-      <c r="G8" s="13"/>
-      <c r="H8" s="13"/>
-      <c r="I8" s="13"/>
-      <c r="J8" s="13"/>
-      <c r="K8" s="13"/>
-      <c r="L8" s="13"/>
-      <c r="M8" s="13"/>
-      <c r="N8" s="13"/>
-      <c r="O8" s="13"/>
-      <c r="P8" s="13"/>
-      <c r="Q8" s="13"/>
-      <c r="R8" s="13"/>
-      <c r="T8" s="13"/>
-      <c r="U8" s="13"/>
-      <c r="V8" s="13"/>
-      <c r="W8" s="13"/>
-      <c r="X8" s="13"/>
-      <c r="Y8" s="13"/>
-      <c r="Z8" s="13"/>
-      <c r="AA8" s="13"/>
-      <c r="AB8" s="13"/>
-      <c r="AC8" s="13"/>
-      <c r="AD8" s="13"/>
-      <c r="AE8" s="13"/>
-      <c r="AF8" s="13"/>
-      <c r="AG8" s="13"/>
-      <c r="AT8" s="32"/>
-      <c r="AU8" s="32"/>
-      <c r="AV8" s="32"/>
-      <c r="AW8" s="14" t="s">
+      <c r="B8" s="16"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="28"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="28"/>
+      <c r="I8" s="28"/>
+      <c r="J8" s="28"/>
+      <c r="K8" s="28"/>
+      <c r="L8" s="28"/>
+      <c r="M8" s="28"/>
+      <c r="N8" s="28"/>
+      <c r="O8" s="28"/>
+      <c r="P8" s="28"/>
+      <c r="Q8" s="28"/>
+      <c r="R8" s="28"/>
+      <c r="T8" s="28"/>
+      <c r="U8" s="28"/>
+      <c r="V8" s="28"/>
+      <c r="W8" s="28"/>
+      <c r="X8" s="28"/>
+      <c r="Y8" s="28"/>
+      <c r="Z8" s="28"/>
+      <c r="AA8" s="28"/>
+      <c r="AB8" s="28"/>
+      <c r="AC8" s="28"/>
+      <c r="AD8" s="28"/>
+      <c r="AE8" s="28"/>
+      <c r="AF8" s="28"/>
+      <c r="AG8" s="28"/>
+      <c r="AT8" s="29"/>
+      <c r="AU8" s="29"/>
+      <c r="AV8" s="29"/>
+      <c r="AW8" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="AX8" s="16"/>
-      <c r="AY8" s="14" t="s">
+      <c r="AX8" s="14"/>
+      <c r="AY8" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="AZ8" s="15"/>
-      <c r="BA8" s="15"/>
-      <c r="BB8" s="16"/>
-      <c r="BC8" s="14" t="s">
+      <c r="AZ8" s="13"/>
+      <c r="BA8" s="13"/>
+      <c r="BB8" s="14"/>
+      <c r="BC8" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="BD8" s="15"/>
-      <c r="BE8" s="16"/>
-      <c r="BF8" s="14" t="s">
+      <c r="BD8" s="13"/>
+      <c r="BE8" s="14"/>
+      <c r="BF8" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="BG8" s="15"/>
-      <c r="BH8" s="15"/>
-      <c r="BI8" s="15"/>
-      <c r="BJ8" s="15"/>
-      <c r="BK8" s="16"/>
+      <c r="BG8" s="13"/>
+      <c r="BH8" s="13"/>
+      <c r="BI8" s="13"/>
+      <c r="BJ8" s="13"/>
+      <c r="BK8" s="14"/>
       <c r="BL8" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="BM8" s="14" t="s">
+      <c r="BM8" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="BN8" s="15"/>
-      <c r="BO8" s="16"/>
+      <c r="BN8" s="13"/>
+      <c r="BO8" s="14"/>
       <c r="BP8" s="8" t="s">
         <v>27</v>
       </c>
       <c r="BQ8" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="BR8" s="31"/>
+      <c r="BR8" s="16"/>
       <c r="BT8" s="6"/>
       <c r="BU8" s="6"/>
       <c r="BV8" s="6"/>
@@ -1870,76 +1874,76 @@
       <c r="BZ8" s="6"/>
     </row>
     <row r="9" spans="1:78" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B9" s="31"/>
-      <c r="E9" s="13"/>
-      <c r="F9" s="13"/>
-      <c r="G9" s="13"/>
-      <c r="H9" s="13"/>
-      <c r="I9" s="13"/>
-      <c r="J9" s="13"/>
-      <c r="K9" s="13"/>
-      <c r="L9" s="13"/>
-      <c r="M9" s="13"/>
-      <c r="N9" s="13"/>
-      <c r="O9" s="13"/>
-      <c r="P9" s="13"/>
-      <c r="Q9" s="13"/>
-      <c r="R9" s="13"/>
-      <c r="T9" s="13"/>
-      <c r="U9" s="13"/>
-      <c r="V9" s="13"/>
-      <c r="W9" s="13"/>
-      <c r="X9" s="13"/>
-      <c r="Y9" s="13"/>
-      <c r="Z9" s="13"/>
-      <c r="AA9" s="13"/>
-      <c r="AB9" s="13"/>
-      <c r="AC9" s="13"/>
-      <c r="AD9" s="13"/>
-      <c r="AE9" s="13"/>
-      <c r="AF9" s="13"/>
-      <c r="AG9" s="13"/>
-      <c r="AT9" s="32"/>
-      <c r="AU9" s="32"/>
-      <c r="AV9" s="32"/>
-      <c r="AW9" s="14" t="s">
+      <c r="B9" s="16"/>
+      <c r="E9" s="28"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="28"/>
+      <c r="H9" s="28"/>
+      <c r="I9" s="28"/>
+      <c r="J9" s="28"/>
+      <c r="K9" s="28"/>
+      <c r="L9" s="28"/>
+      <c r="M9" s="28"/>
+      <c r="N9" s="28"/>
+      <c r="O9" s="28"/>
+      <c r="P9" s="28"/>
+      <c r="Q9" s="28"/>
+      <c r="R9" s="28"/>
+      <c r="T9" s="28"/>
+      <c r="U9" s="28"/>
+      <c r="V9" s="28"/>
+      <c r="W9" s="28"/>
+      <c r="X9" s="28"/>
+      <c r="Y9" s="28"/>
+      <c r="Z9" s="28"/>
+      <c r="AA9" s="28"/>
+      <c r="AB9" s="28"/>
+      <c r="AC9" s="28"/>
+      <c r="AD9" s="28"/>
+      <c r="AE9" s="28"/>
+      <c r="AF9" s="28"/>
+      <c r="AG9" s="28"/>
+      <c r="AT9" s="29"/>
+      <c r="AU9" s="29"/>
+      <c r="AV9" s="29"/>
+      <c r="AW9" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="AX9" s="16"/>
-      <c r="AY9" s="14" t="s">
+      <c r="AX9" s="14"/>
+      <c r="AY9" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="AZ9" s="15"/>
-      <c r="BA9" s="15"/>
-      <c r="BB9" s="16"/>
-      <c r="BC9" s="14" t="s">
+      <c r="AZ9" s="13"/>
+      <c r="BA9" s="13"/>
+      <c r="BB9" s="14"/>
+      <c r="BC9" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="BD9" s="15"/>
-      <c r="BE9" s="16"/>
-      <c r="BF9" s="14" t="s">
+      <c r="BD9" s="13"/>
+      <c r="BE9" s="14"/>
+      <c r="BF9" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="BG9" s="15"/>
-      <c r="BH9" s="15"/>
-      <c r="BI9" s="15"/>
-      <c r="BJ9" s="15"/>
-      <c r="BK9" s="16"/>
+      <c r="BG9" s="13"/>
+      <c r="BH9" s="13"/>
+      <c r="BI9" s="13"/>
+      <c r="BJ9" s="13"/>
+      <c r="BK9" s="14"/>
       <c r="BL9" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="BM9" s="14" t="s">
+      <c r="BM9" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="BN9" s="15"/>
-      <c r="BO9" s="16"/>
+      <c r="BN9" s="13"/>
+      <c r="BO9" s="14"/>
       <c r="BP9" s="8" t="s">
         <v>35</v>
       </c>
       <c r="BQ9" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="BR9" s="31"/>
+      <c r="BR9" s="16"/>
       <c r="BT9" s="6"/>
       <c r="BU9" s="6"/>
       <c r="BV9" s="6"/>
@@ -1949,76 +1953,76 @@
       <c r="BZ9" s="6"/>
     </row>
     <row r="10" spans="1:78" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B10" s="31"/>
-      <c r="E10" s="13"/>
-      <c r="F10" s="13"/>
-      <c r="G10" s="13"/>
-      <c r="H10" s="13"/>
-      <c r="I10" s="13"/>
-      <c r="J10" s="13"/>
-      <c r="K10" s="13"/>
-      <c r="L10" s="13"/>
-      <c r="M10" s="13"/>
-      <c r="N10" s="13"/>
-      <c r="O10" s="13"/>
-      <c r="P10" s="13"/>
-      <c r="Q10" s="13"/>
-      <c r="R10" s="13"/>
-      <c r="T10" s="13"/>
-      <c r="U10" s="13"/>
-      <c r="V10" s="13"/>
-      <c r="W10" s="13"/>
-      <c r="X10" s="13"/>
-      <c r="Y10" s="13"/>
-      <c r="Z10" s="13"/>
-      <c r="AA10" s="13"/>
-      <c r="AB10" s="13"/>
-      <c r="AC10" s="13"/>
-      <c r="AD10" s="13"/>
-      <c r="AE10" s="13"/>
-      <c r="AF10" s="13"/>
-      <c r="AG10" s="13"/>
-      <c r="AT10" s="32"/>
-      <c r="AU10" s="32"/>
-      <c r="AV10" s="32"/>
-      <c r="AW10" s="14" t="s">
+      <c r="B10" s="16"/>
+      <c r="E10" s="28"/>
+      <c r="F10" s="28"/>
+      <c r="G10" s="28"/>
+      <c r="H10" s="28"/>
+      <c r="I10" s="28"/>
+      <c r="J10" s="28"/>
+      <c r="K10" s="28"/>
+      <c r="L10" s="28"/>
+      <c r="M10" s="28"/>
+      <c r="N10" s="28"/>
+      <c r="O10" s="28"/>
+      <c r="P10" s="28"/>
+      <c r="Q10" s="28"/>
+      <c r="R10" s="28"/>
+      <c r="T10" s="28"/>
+      <c r="U10" s="28"/>
+      <c r="V10" s="28"/>
+      <c r="W10" s="28"/>
+      <c r="X10" s="28"/>
+      <c r="Y10" s="28"/>
+      <c r="Z10" s="28"/>
+      <c r="AA10" s="28"/>
+      <c r="AB10" s="28"/>
+      <c r="AC10" s="28"/>
+      <c r="AD10" s="28"/>
+      <c r="AE10" s="28"/>
+      <c r="AF10" s="28"/>
+      <c r="AG10" s="28"/>
+      <c r="AT10" s="29"/>
+      <c r="AU10" s="29"/>
+      <c r="AV10" s="29"/>
+      <c r="AW10" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="AX10" s="16"/>
-      <c r="AY10" s="14" t="s">
+      <c r="AX10" s="14"/>
+      <c r="AY10" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="AZ10" s="15"/>
-      <c r="BA10" s="15"/>
-      <c r="BB10" s="16"/>
-      <c r="BC10" s="14" t="s">
+      <c r="AZ10" s="13"/>
+      <c r="BA10" s="13"/>
+      <c r="BB10" s="14"/>
+      <c r="BC10" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="BD10" s="15"/>
-      <c r="BE10" s="16"/>
-      <c r="BF10" s="14" t="s">
+      <c r="BD10" s="13"/>
+      <c r="BE10" s="14"/>
+      <c r="BF10" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="BG10" s="15"/>
-      <c r="BH10" s="15"/>
-      <c r="BI10" s="15"/>
-      <c r="BJ10" s="15"/>
-      <c r="BK10" s="16"/>
+      <c r="BG10" s="13"/>
+      <c r="BH10" s="13"/>
+      <c r="BI10" s="13"/>
+      <c r="BJ10" s="13"/>
+      <c r="BK10" s="14"/>
       <c r="BL10" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="BM10" s="14" t="s">
+      <c r="BM10" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="BN10" s="15"/>
-      <c r="BO10" s="16"/>
+      <c r="BN10" s="13"/>
+      <c r="BO10" s="14"/>
       <c r="BP10" s="8" t="s">
         <v>43</v>
       </c>
       <c r="BQ10" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="BR10" s="31"/>
+      <c r="BR10" s="16"/>
       <c r="BT10" s="6"/>
       <c r="BU10" s="6"/>
       <c r="BV10" s="6"/>
@@ -2028,76 +2032,76 @@
       <c r="BZ10" s="6"/>
     </row>
     <row r="11" spans="1:78" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B11" s="31"/>
-      <c r="E11" s="13"/>
-      <c r="F11" s="13"/>
-      <c r="G11" s="13"/>
-      <c r="H11" s="13"/>
-      <c r="I11" s="13"/>
-      <c r="J11" s="13"/>
-      <c r="K11" s="13"/>
-      <c r="L11" s="13"/>
-      <c r="M11" s="13"/>
-      <c r="N11" s="13"/>
-      <c r="O11" s="13"/>
-      <c r="P11" s="13"/>
-      <c r="Q11" s="13"/>
-      <c r="R11" s="13"/>
-      <c r="T11" s="13"/>
-      <c r="U11" s="13"/>
-      <c r="V11" s="13"/>
-      <c r="W11" s="13"/>
-      <c r="X11" s="13"/>
-      <c r="Y11" s="13"/>
-      <c r="Z11" s="13"/>
-      <c r="AA11" s="13"/>
-      <c r="AB11" s="13"/>
-      <c r="AC11" s="13"/>
-      <c r="AD11" s="13"/>
-      <c r="AE11" s="13"/>
-      <c r="AF11" s="13"/>
-      <c r="AG11" s="13"/>
-      <c r="AT11" s="32"/>
-      <c r="AU11" s="32"/>
-      <c r="AV11" s="32"/>
-      <c r="AW11" s="14" t="s">
+      <c r="B11" s="16"/>
+      <c r="E11" s="28"/>
+      <c r="F11" s="28"/>
+      <c r="G11" s="28"/>
+      <c r="H11" s="28"/>
+      <c r="I11" s="28"/>
+      <c r="J11" s="28"/>
+      <c r="K11" s="28"/>
+      <c r="L11" s="28"/>
+      <c r="M11" s="28"/>
+      <c r="N11" s="28"/>
+      <c r="O11" s="28"/>
+      <c r="P11" s="28"/>
+      <c r="Q11" s="28"/>
+      <c r="R11" s="28"/>
+      <c r="T11" s="28"/>
+      <c r="U11" s="28"/>
+      <c r="V11" s="28"/>
+      <c r="W11" s="28"/>
+      <c r="X11" s="28"/>
+      <c r="Y11" s="28"/>
+      <c r="Z11" s="28"/>
+      <c r="AA11" s="28"/>
+      <c r="AB11" s="28"/>
+      <c r="AC11" s="28"/>
+      <c r="AD11" s="28"/>
+      <c r="AE11" s="28"/>
+      <c r="AF11" s="28"/>
+      <c r="AG11" s="28"/>
+      <c r="AT11" s="29"/>
+      <c r="AU11" s="29"/>
+      <c r="AV11" s="29"/>
+      <c r="AW11" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="AX11" s="16"/>
-      <c r="AY11" s="14" t="s">
+      <c r="AX11" s="14"/>
+      <c r="AY11" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="AZ11" s="15"/>
-      <c r="BA11" s="15"/>
-      <c r="BB11" s="16"/>
-      <c r="BC11" s="14" t="s">
+      <c r="AZ11" s="13"/>
+      <c r="BA11" s="13"/>
+      <c r="BB11" s="14"/>
+      <c r="BC11" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="BD11" s="15"/>
-      <c r="BE11" s="16"/>
-      <c r="BF11" s="14" t="s">
+      <c r="BD11" s="13"/>
+      <c r="BE11" s="14"/>
+      <c r="BF11" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="BG11" s="15"/>
-      <c r="BH11" s="15"/>
-      <c r="BI11" s="15"/>
-      <c r="BJ11" s="15"/>
-      <c r="BK11" s="16"/>
+      <c r="BG11" s="13"/>
+      <c r="BH11" s="13"/>
+      <c r="BI11" s="13"/>
+      <c r="BJ11" s="13"/>
+      <c r="BK11" s="14"/>
       <c r="BL11" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="BM11" s="14" t="s">
+      <c r="BM11" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="BN11" s="15"/>
-      <c r="BO11" s="16"/>
+      <c r="BN11" s="13"/>
+      <c r="BO11" s="14"/>
       <c r="BP11" s="10" t="s">
         <v>51</v>
       </c>
       <c r="BQ11" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="BR11" s="31"/>
+      <c r="BR11" s="16"/>
       <c r="BT11" s="6"/>
       <c r="BU11" s="6"/>
       <c r="BV11" s="6"/>
@@ -2107,45 +2111,45 @@
       <c r="BZ11" s="6"/>
     </row>
     <row r="12" spans="1:78" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B12" s="31"/>
-      <c r="AW12" s="14" t="s">
+      <c r="B12" s="16"/>
+      <c r="AW12" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="AX12" s="16"/>
-      <c r="AY12" s="14" t="s">
+      <c r="AX12" s="14"/>
+      <c r="AY12" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="AZ12" s="15"/>
-      <c r="BA12" s="15"/>
-      <c r="BB12" s="16"/>
-      <c r="BC12" s="14" t="s">
+      <c r="AZ12" s="13"/>
+      <c r="BA12" s="13"/>
+      <c r="BB12" s="14"/>
+      <c r="BC12" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="BD12" s="15"/>
-      <c r="BE12" s="16"/>
-      <c r="BF12" s="14" t="s">
+      <c r="BD12" s="13"/>
+      <c r="BE12" s="14"/>
+      <c r="BF12" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="BG12" s="15"/>
-      <c r="BH12" s="15"/>
-      <c r="BI12" s="15"/>
-      <c r="BJ12" s="15"/>
-      <c r="BK12" s="16"/>
+      <c r="BG12" s="13"/>
+      <c r="BH12" s="13"/>
+      <c r="BI12" s="13"/>
+      <c r="BJ12" s="13"/>
+      <c r="BK12" s="14"/>
       <c r="BL12" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="BM12" s="14" t="s">
+      <c r="BM12" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="BN12" s="15"/>
-      <c r="BO12" s="16"/>
+      <c r="BN12" s="13"/>
+      <c r="BO12" s="14"/>
       <c r="BP12" s="8" t="s">
         <v>59</v>
       </c>
       <c r="BQ12" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="BR12" s="31"/>
+      <c r="BR12" s="16"/>
       <c r="BT12" s="6"/>
       <c r="BU12" s="6"/>
       <c r="BV12" s="6"/>
@@ -2155,45 +2159,45 @@
       <c r="BZ12" s="6"/>
     </row>
     <row r="13" spans="1:78" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B13" s="31"/>
-      <c r="AW13" s="14" t="s">
+      <c r="B13" s="16"/>
+      <c r="AW13" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="AX13" s="16"/>
-      <c r="AY13" s="14" t="s">
+      <c r="AX13" s="14"/>
+      <c r="AY13" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="AZ13" s="15"/>
-      <c r="BA13" s="15"/>
-      <c r="BB13" s="16"/>
-      <c r="BC13" s="14" t="s">
+      <c r="AZ13" s="13"/>
+      <c r="BA13" s="13"/>
+      <c r="BB13" s="14"/>
+      <c r="BC13" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="BD13" s="15"/>
-      <c r="BE13" s="16"/>
-      <c r="BF13" s="14" t="s">
+      <c r="BD13" s="13"/>
+      <c r="BE13" s="14"/>
+      <c r="BF13" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="BG13" s="15"/>
-      <c r="BH13" s="15"/>
-      <c r="BI13" s="15"/>
-      <c r="BJ13" s="15"/>
-      <c r="BK13" s="16"/>
+      <c r="BG13" s="13"/>
+      <c r="BH13" s="13"/>
+      <c r="BI13" s="13"/>
+      <c r="BJ13" s="13"/>
+      <c r="BK13" s="14"/>
       <c r="BL13" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="BM13" s="14" t="s">
+      <c r="BM13" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="BN13" s="15"/>
-      <c r="BO13" s="16"/>
+      <c r="BN13" s="13"/>
+      <c r="BO13" s="14"/>
       <c r="BP13" s="8" t="s">
         <v>67</v>
       </c>
       <c r="BQ13" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="BR13" s="31"/>
+      <c r="BR13" s="16"/>
       <c r="BT13" s="6"/>
       <c r="BU13" s="6"/>
       <c r="BV13" s="6"/>
@@ -2203,45 +2207,45 @@
       <c r="BZ13" s="6"/>
     </row>
     <row r="14" spans="1:78" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B14" s="31"/>
-      <c r="AW14" s="14" t="s">
+      <c r="B14" s="16"/>
+      <c r="AW14" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="AX14" s="16"/>
-      <c r="AY14" s="14" t="s">
+      <c r="AX14" s="14"/>
+      <c r="AY14" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="AZ14" s="15"/>
-      <c r="BA14" s="15"/>
-      <c r="BB14" s="16"/>
-      <c r="BC14" s="14" t="s">
+      <c r="AZ14" s="13"/>
+      <c r="BA14" s="13"/>
+      <c r="BB14" s="14"/>
+      <c r="BC14" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="BD14" s="15"/>
-      <c r="BE14" s="16"/>
-      <c r="BF14" s="14" t="s">
+      <c r="BD14" s="13"/>
+      <c r="BE14" s="14"/>
+      <c r="BF14" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="BG14" s="15"/>
-      <c r="BH14" s="15"/>
-      <c r="BI14" s="15"/>
-      <c r="BJ14" s="15"/>
-      <c r="BK14" s="16"/>
+      <c r="BG14" s="13"/>
+      <c r="BH14" s="13"/>
+      <c r="BI14" s="13"/>
+      <c r="BJ14" s="13"/>
+      <c r="BK14" s="14"/>
       <c r="BL14" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="BM14" s="14" t="s">
+      <c r="BM14" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="BN14" s="15"/>
-      <c r="BO14" s="16"/>
+      <c r="BN14" s="13"/>
+      <c r="BO14" s="14"/>
       <c r="BP14" s="8" t="s">
         <v>75</v>
       </c>
       <c r="BQ14" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="BR14" s="31"/>
+      <c r="BR14" s="16"/>
       <c r="BT14" s="6"/>
       <c r="BU14" s="6"/>
       <c r="BV14" s="6"/>
@@ -2251,45 +2255,45 @@
       <c r="BZ14" s="6"/>
     </row>
     <row r="15" spans="1:78" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B15" s="31"/>
-      <c r="AW15" s="14" t="s">
+      <c r="B15" s="16"/>
+      <c r="AW15" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="AX15" s="16"/>
-      <c r="AY15" s="14" t="s">
+      <c r="AX15" s="14"/>
+      <c r="AY15" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="AZ15" s="15"/>
-      <c r="BA15" s="15"/>
-      <c r="BB15" s="16"/>
-      <c r="BC15" s="14" t="s">
+      <c r="AZ15" s="13"/>
+      <c r="BA15" s="13"/>
+      <c r="BB15" s="14"/>
+      <c r="BC15" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="BD15" s="15"/>
-      <c r="BE15" s="16"/>
-      <c r="BF15" s="14" t="s">
+      <c r="BD15" s="13"/>
+      <c r="BE15" s="14"/>
+      <c r="BF15" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="BG15" s="15"/>
-      <c r="BH15" s="15"/>
-      <c r="BI15" s="15"/>
-      <c r="BJ15" s="15"/>
-      <c r="BK15" s="16"/>
+      <c r="BG15" s="13"/>
+      <c r="BH15" s="13"/>
+      <c r="BI15" s="13"/>
+      <c r="BJ15" s="13"/>
+      <c r="BK15" s="14"/>
       <c r="BL15" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="BM15" s="14" t="s">
+      <c r="BM15" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="BN15" s="15"/>
-      <c r="BO15" s="16"/>
+      <c r="BN15" s="13"/>
+      <c r="BO15" s="14"/>
       <c r="BP15" s="8" t="s">
         <v>83</v>
       </c>
       <c r="BQ15" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="BR15" s="31"/>
+      <c r="BR15" s="16"/>
       <c r="BT15" s="6"/>
       <c r="BU15" s="6"/>
       <c r="BV15" s="6"/>
@@ -2299,45 +2303,45 @@
       <c r="BZ15" s="6"/>
     </row>
     <row r="16" spans="1:78" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B16" s="27"/>
-      <c r="AW16" s="14" t="s">
+      <c r="B16" s="17"/>
+      <c r="AW16" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="AX16" s="16"/>
-      <c r="AY16" s="14" t="s">
+      <c r="AX16" s="14"/>
+      <c r="AY16" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="AZ16" s="15"/>
-      <c r="BA16" s="15"/>
-      <c r="BB16" s="16"/>
-      <c r="BC16" s="14" t="s">
+      <c r="AZ16" s="13"/>
+      <c r="BA16" s="13"/>
+      <c r="BB16" s="14"/>
+      <c r="BC16" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="BD16" s="15"/>
-      <c r="BE16" s="16"/>
-      <c r="BF16" s="14" t="s">
+      <c r="BD16" s="13"/>
+      <c r="BE16" s="14"/>
+      <c r="BF16" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="BG16" s="15"/>
-      <c r="BH16" s="15"/>
-      <c r="BI16" s="15"/>
-      <c r="BJ16" s="15"/>
-      <c r="BK16" s="16"/>
+      <c r="BG16" s="13"/>
+      <c r="BH16" s="13"/>
+      <c r="BI16" s="13"/>
+      <c r="BJ16" s="13"/>
+      <c r="BK16" s="14"/>
       <c r="BL16" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="BM16" s="14" t="s">
+      <c r="BM16" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="BN16" s="15"/>
-      <c r="BO16" s="16"/>
+      <c r="BN16" s="13"/>
+      <c r="BO16" s="14"/>
       <c r="BP16" s="8" t="s">
         <v>92</v>
       </c>
       <c r="BQ16" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="BR16" s="27"/>
+      <c r="BR16" s="17"/>
       <c r="BT16" s="6"/>
       <c r="BU16" s="6"/>
       <c r="BV16" s="6"/>
@@ -2347,79 +2351,79 @@
       <c r="BZ16" s="6"/>
     </row>
     <row r="17" spans="2:86" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B17" s="26" t="s">
+      <c r="B17" s="15" t="s">
         <v>85</v>
       </c>
-      <c r="E17" s="12" t="s">
+      <c r="E17" s="27" t="s">
         <v>233</v>
       </c>
-      <c r="F17" s="13"/>
-      <c r="G17" s="13"/>
-      <c r="H17" s="13"/>
-      <c r="I17" s="13"/>
-      <c r="J17" s="13"/>
-      <c r="K17" s="13"/>
-      <c r="L17" s="13"/>
-      <c r="M17" s="13"/>
-      <c r="N17" s="13"/>
-      <c r="O17" s="13"/>
-      <c r="P17" s="13"/>
-      <c r="Q17" s="13"/>
-      <c r="R17" s="13"/>
-      <c r="T17" s="12" t="s">
+      <c r="F17" s="28"/>
+      <c r="G17" s="28"/>
+      <c r="H17" s="28"/>
+      <c r="I17" s="28"/>
+      <c r="J17" s="28"/>
+      <c r="K17" s="28"/>
+      <c r="L17" s="28"/>
+      <c r="M17" s="28"/>
+      <c r="N17" s="28"/>
+      <c r="O17" s="28"/>
+      <c r="P17" s="28"/>
+      <c r="Q17" s="28"/>
+      <c r="R17" s="28"/>
+      <c r="T17" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="U17" s="13"/>
-      <c r="V17" s="13"/>
-      <c r="W17" s="13"/>
-      <c r="X17" s="13"/>
-      <c r="Y17" s="13"/>
-      <c r="Z17" s="13"/>
-      <c r="AA17" s="13"/>
-      <c r="AB17" s="13"/>
-      <c r="AC17" s="13"/>
-      <c r="AD17" s="13"/>
-      <c r="AE17" s="13"/>
-      <c r="AF17" s="13"/>
-      <c r="AG17" s="13"/>
-      <c r="AW17" s="14" t="s">
+      <c r="U17" s="28"/>
+      <c r="V17" s="28"/>
+      <c r="W17" s="28"/>
+      <c r="X17" s="28"/>
+      <c r="Y17" s="28"/>
+      <c r="Z17" s="28"/>
+      <c r="AA17" s="28"/>
+      <c r="AB17" s="28"/>
+      <c r="AC17" s="28"/>
+      <c r="AD17" s="28"/>
+      <c r="AE17" s="28"/>
+      <c r="AF17" s="28"/>
+      <c r="AG17" s="28"/>
+      <c r="AW17" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="AX17" s="16"/>
-      <c r="AY17" s="14" t="s">
+      <c r="AX17" s="14"/>
+      <c r="AY17" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="AZ17" s="15"/>
-      <c r="BA17" s="15"/>
-      <c r="BB17" s="16"/>
-      <c r="BC17" s="14" t="s">
+      <c r="AZ17" s="13"/>
+      <c r="BA17" s="13"/>
+      <c r="BB17" s="14"/>
+      <c r="BC17" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="BD17" s="15"/>
-      <c r="BE17" s="16"/>
-      <c r="BF17" s="14" t="s">
+      <c r="BD17" s="13"/>
+      <c r="BE17" s="14"/>
+      <c r="BF17" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="BG17" s="15"/>
-      <c r="BH17" s="15"/>
-      <c r="BI17" s="15"/>
-      <c r="BJ17" s="15"/>
-      <c r="BK17" s="16"/>
+      <c r="BG17" s="13"/>
+      <c r="BH17" s="13"/>
+      <c r="BI17" s="13"/>
+      <c r="BJ17" s="13"/>
+      <c r="BK17" s="14"/>
       <c r="BL17" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="BM17" s="14" t="s">
+      <c r="BM17" s="12" t="s">
         <v>99</v>
       </c>
-      <c r="BN17" s="15"/>
-      <c r="BO17" s="16"/>
+      <c r="BN17" s="13"/>
+      <c r="BO17" s="14"/>
       <c r="BP17" s="8" t="s">
         <v>100</v>
       </c>
       <c r="BQ17" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="BR17" s="26" t="s">
+      <c r="BR17" s="15" t="s">
         <v>85</v>
       </c>
       <c r="BT17" s="6"/>
@@ -2431,73 +2435,73 @@
       <c r="BZ17" s="6"/>
     </row>
     <row r="18" spans="2:86" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B18" s="31"/>
-      <c r="E18" s="13"/>
-      <c r="F18" s="13"/>
-      <c r="G18" s="13"/>
-      <c r="H18" s="13"/>
-      <c r="I18" s="13"/>
-      <c r="J18" s="13"/>
-      <c r="K18" s="13"/>
-      <c r="L18" s="13"/>
-      <c r="M18" s="13"/>
-      <c r="N18" s="13"/>
-      <c r="O18" s="13"/>
-      <c r="P18" s="13"/>
-      <c r="Q18" s="13"/>
-      <c r="R18" s="13"/>
-      <c r="T18" s="13"/>
-      <c r="U18" s="13"/>
-      <c r="V18" s="13"/>
-      <c r="W18" s="13"/>
-      <c r="X18" s="13"/>
-      <c r="Y18" s="13"/>
-      <c r="Z18" s="13"/>
-      <c r="AA18" s="13"/>
-      <c r="AB18" s="13"/>
-      <c r="AC18" s="13"/>
-      <c r="AD18" s="13"/>
-      <c r="AE18" s="13"/>
-      <c r="AF18" s="13"/>
-      <c r="AG18" s="13"/>
-      <c r="AW18" s="14" t="s">
+      <c r="B18" s="16"/>
+      <c r="E18" s="28"/>
+      <c r="F18" s="28"/>
+      <c r="G18" s="28"/>
+      <c r="H18" s="28"/>
+      <c r="I18" s="28"/>
+      <c r="J18" s="28"/>
+      <c r="K18" s="28"/>
+      <c r="L18" s="28"/>
+      <c r="M18" s="28"/>
+      <c r="N18" s="28"/>
+      <c r="O18" s="28"/>
+      <c r="P18" s="28"/>
+      <c r="Q18" s="28"/>
+      <c r="R18" s="28"/>
+      <c r="T18" s="28"/>
+      <c r="U18" s="28"/>
+      <c r="V18" s="28"/>
+      <c r="W18" s="28"/>
+      <c r="X18" s="28"/>
+      <c r="Y18" s="28"/>
+      <c r="Z18" s="28"/>
+      <c r="AA18" s="28"/>
+      <c r="AB18" s="28"/>
+      <c r="AC18" s="28"/>
+      <c r="AD18" s="28"/>
+      <c r="AE18" s="28"/>
+      <c r="AF18" s="28"/>
+      <c r="AG18" s="28"/>
+      <c r="AW18" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="AX18" s="16"/>
-      <c r="AY18" s="14" t="s">
+      <c r="AX18" s="14"/>
+      <c r="AY18" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="AZ18" s="15"/>
-      <c r="BA18" s="15"/>
-      <c r="BB18" s="16"/>
-      <c r="BC18" s="14" t="s">
+      <c r="AZ18" s="13"/>
+      <c r="BA18" s="13"/>
+      <c r="BB18" s="14"/>
+      <c r="BC18" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="BD18" s="15"/>
-      <c r="BE18" s="16"/>
-      <c r="BF18" s="14" t="s">
+      <c r="BD18" s="13"/>
+      <c r="BE18" s="14"/>
+      <c r="BF18" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="BG18" s="15"/>
-      <c r="BH18" s="15"/>
-      <c r="BI18" s="15"/>
-      <c r="BJ18" s="15"/>
-      <c r="BK18" s="16"/>
+      <c r="BG18" s="13"/>
+      <c r="BH18" s="13"/>
+      <c r="BI18" s="13"/>
+      <c r="BJ18" s="13"/>
+      <c r="BK18" s="14"/>
       <c r="BL18" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="BM18" s="14" t="s">
+      <c r="BM18" s="12" t="s">
         <v>107</v>
       </c>
-      <c r="BN18" s="15"/>
-      <c r="BO18" s="16"/>
+      <c r="BN18" s="13"/>
+      <c r="BO18" s="14"/>
       <c r="BP18" s="8" t="s">
         <v>108</v>
       </c>
       <c r="BQ18" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="BR18" s="31"/>
+      <c r="BR18" s="16"/>
       <c r="BT18" s="6"/>
       <c r="BU18" s="6"/>
       <c r="BV18" s="6"/>
@@ -2507,73 +2511,73 @@
       <c r="BZ18" s="6"/>
     </row>
     <row r="19" spans="2:86" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B19" s="31"/>
-      <c r="E19" s="13"/>
-      <c r="F19" s="13"/>
-      <c r="G19" s="13"/>
-      <c r="H19" s="13"/>
-      <c r="I19" s="13"/>
-      <c r="J19" s="13"/>
-      <c r="K19" s="13"/>
-      <c r="L19" s="13"/>
-      <c r="M19" s="13"/>
-      <c r="N19" s="13"/>
-      <c r="O19" s="13"/>
-      <c r="P19" s="13"/>
-      <c r="Q19" s="13"/>
-      <c r="R19" s="13"/>
-      <c r="T19" s="13"/>
-      <c r="U19" s="13"/>
-      <c r="V19" s="13"/>
-      <c r="W19" s="13"/>
-      <c r="X19" s="13"/>
-      <c r="Y19" s="13"/>
-      <c r="Z19" s="13"/>
-      <c r="AA19" s="13"/>
-      <c r="AB19" s="13"/>
-      <c r="AC19" s="13"/>
-      <c r="AD19" s="13"/>
-      <c r="AE19" s="13"/>
-      <c r="AF19" s="13"/>
-      <c r="AG19" s="13"/>
-      <c r="AW19" s="14" t="s">
+      <c r="B19" s="16"/>
+      <c r="E19" s="28"/>
+      <c r="F19" s="28"/>
+      <c r="G19" s="28"/>
+      <c r="H19" s="28"/>
+      <c r="I19" s="28"/>
+      <c r="J19" s="28"/>
+      <c r="K19" s="28"/>
+      <c r="L19" s="28"/>
+      <c r="M19" s="28"/>
+      <c r="N19" s="28"/>
+      <c r="O19" s="28"/>
+      <c r="P19" s="28"/>
+      <c r="Q19" s="28"/>
+      <c r="R19" s="28"/>
+      <c r="T19" s="28"/>
+      <c r="U19" s="28"/>
+      <c r="V19" s="28"/>
+      <c r="W19" s="28"/>
+      <c r="X19" s="28"/>
+      <c r="Y19" s="28"/>
+      <c r="Z19" s="28"/>
+      <c r="AA19" s="28"/>
+      <c r="AB19" s="28"/>
+      <c r="AC19" s="28"/>
+      <c r="AD19" s="28"/>
+      <c r="AE19" s="28"/>
+      <c r="AF19" s="28"/>
+      <c r="AG19" s="28"/>
+      <c r="AW19" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="AX19" s="16"/>
-      <c r="AY19" s="14" t="s">
+      <c r="AX19" s="14"/>
+      <c r="AY19" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="AZ19" s="15"/>
-      <c r="BA19" s="15"/>
-      <c r="BB19" s="16"/>
-      <c r="BC19" s="14" t="s">
+      <c r="AZ19" s="13"/>
+      <c r="BA19" s="13"/>
+      <c r="BB19" s="14"/>
+      <c r="BC19" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="BD19" s="15"/>
-      <c r="BE19" s="16"/>
-      <c r="BF19" s="14" t="s">
+      <c r="BD19" s="13"/>
+      <c r="BE19" s="14"/>
+      <c r="BF19" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="BG19" s="15"/>
-      <c r="BH19" s="15"/>
-      <c r="BI19" s="15"/>
-      <c r="BJ19" s="15"/>
-      <c r="BK19" s="16"/>
+      <c r="BG19" s="13"/>
+      <c r="BH19" s="13"/>
+      <c r="BI19" s="13"/>
+      <c r="BJ19" s="13"/>
+      <c r="BK19" s="14"/>
       <c r="BL19" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="BM19" s="14" t="s">
+      <c r="BM19" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="BN19" s="15"/>
-      <c r="BO19" s="16"/>
+      <c r="BN19" s="13"/>
+      <c r="BO19" s="14"/>
       <c r="BP19" s="8" t="s">
         <v>116</v>
       </c>
       <c r="BQ19" s="8" t="s">
         <v>117</v>
       </c>
-      <c r="BR19" s="31"/>
+      <c r="BR19" s="16"/>
       <c r="BT19" s="6"/>
       <c r="BU19" s="6"/>
       <c r="BV19" s="6"/>
@@ -2583,73 +2587,73 @@
       <c r="BZ19" s="6"/>
     </row>
     <row r="20" spans="2:86" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B20" s="31"/>
-      <c r="E20" s="13"/>
-      <c r="F20" s="13"/>
-      <c r="G20" s="13"/>
-      <c r="H20" s="13"/>
-      <c r="I20" s="13"/>
-      <c r="J20" s="13"/>
-      <c r="K20" s="13"/>
-      <c r="L20" s="13"/>
-      <c r="M20" s="13"/>
-      <c r="N20" s="13"/>
-      <c r="O20" s="13"/>
-      <c r="P20" s="13"/>
-      <c r="Q20" s="13"/>
-      <c r="R20" s="13"/>
-      <c r="T20" s="13"/>
-      <c r="U20" s="13"/>
-      <c r="V20" s="13"/>
-      <c r="W20" s="13"/>
-      <c r="X20" s="13"/>
-      <c r="Y20" s="13"/>
-      <c r="Z20" s="13"/>
-      <c r="AA20" s="13"/>
-      <c r="AB20" s="13"/>
-      <c r="AC20" s="13"/>
-      <c r="AD20" s="13"/>
-      <c r="AE20" s="13"/>
-      <c r="AF20" s="13"/>
-      <c r="AG20" s="13"/>
-      <c r="AW20" s="14" t="s">
+      <c r="B20" s="16"/>
+      <c r="E20" s="28"/>
+      <c r="F20" s="28"/>
+      <c r="G20" s="28"/>
+      <c r="H20" s="28"/>
+      <c r="I20" s="28"/>
+      <c r="J20" s="28"/>
+      <c r="K20" s="28"/>
+      <c r="L20" s="28"/>
+      <c r="M20" s="28"/>
+      <c r="N20" s="28"/>
+      <c r="O20" s="28"/>
+      <c r="P20" s="28"/>
+      <c r="Q20" s="28"/>
+      <c r="R20" s="28"/>
+      <c r="T20" s="28"/>
+      <c r="U20" s="28"/>
+      <c r="V20" s="28"/>
+      <c r="W20" s="28"/>
+      <c r="X20" s="28"/>
+      <c r="Y20" s="28"/>
+      <c r="Z20" s="28"/>
+      <c r="AA20" s="28"/>
+      <c r="AB20" s="28"/>
+      <c r="AC20" s="28"/>
+      <c r="AD20" s="28"/>
+      <c r="AE20" s="28"/>
+      <c r="AF20" s="28"/>
+      <c r="AG20" s="28"/>
+      <c r="AW20" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="AX20" s="16"/>
-      <c r="AY20" s="14" t="s">
+      <c r="AX20" s="14"/>
+      <c r="AY20" s="12" t="s">
         <v>119</v>
       </c>
-      <c r="AZ20" s="15"/>
-      <c r="BA20" s="15"/>
-      <c r="BB20" s="16"/>
-      <c r="BC20" s="14" t="s">
+      <c r="AZ20" s="13"/>
+      <c r="BA20" s="13"/>
+      <c r="BB20" s="14"/>
+      <c r="BC20" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="BD20" s="15"/>
-      <c r="BE20" s="16"/>
-      <c r="BF20" s="14" t="s">
+      <c r="BD20" s="13"/>
+      <c r="BE20" s="14"/>
+      <c r="BF20" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="BG20" s="15"/>
-      <c r="BH20" s="15"/>
-      <c r="BI20" s="15"/>
-      <c r="BJ20" s="15"/>
-      <c r="BK20" s="16"/>
+      <c r="BG20" s="13"/>
+      <c r="BH20" s="13"/>
+      <c r="BI20" s="13"/>
+      <c r="BJ20" s="13"/>
+      <c r="BK20" s="14"/>
       <c r="BL20" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="BM20" s="14" t="s">
+      <c r="BM20" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="BN20" s="15"/>
-      <c r="BO20" s="16"/>
+      <c r="BN20" s="13"/>
+      <c r="BO20" s="14"/>
       <c r="BP20" s="8" t="s">
         <v>124</v>
       </c>
       <c r="BQ20" s="8" t="s">
         <v>125</v>
       </c>
-      <c r="BR20" s="31"/>
+      <c r="BR20" s="16"/>
       <c r="BT20" s="6"/>
       <c r="BU20" s="6"/>
       <c r="BV20" s="6"/>
@@ -2659,45 +2663,45 @@
       <c r="BZ20" s="6"/>
     </row>
     <row r="21" spans="2:86" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B21" s="31"/>
-      <c r="AW21" s="14" t="s">
+      <c r="B21" s="16"/>
+      <c r="AW21" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="AX21" s="16"/>
-      <c r="AY21" s="14" t="s">
+      <c r="AX21" s="14"/>
+      <c r="AY21" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="AZ21" s="15"/>
-      <c r="BA21" s="15"/>
-      <c r="BB21" s="16"/>
-      <c r="BC21" s="14" t="s">
+      <c r="AZ21" s="13"/>
+      <c r="BA21" s="13"/>
+      <c r="BB21" s="14"/>
+      <c r="BC21" s="12" t="s">
         <v>128</v>
       </c>
-      <c r="BD21" s="15"/>
-      <c r="BE21" s="16"/>
-      <c r="BF21" s="14" t="s">
+      <c r="BD21" s="13"/>
+      <c r="BE21" s="14"/>
+      <c r="BF21" s="12" t="s">
         <v>129</v>
       </c>
-      <c r="BG21" s="15"/>
-      <c r="BH21" s="15"/>
-      <c r="BI21" s="15"/>
-      <c r="BJ21" s="15"/>
-      <c r="BK21" s="16"/>
+      <c r="BG21" s="13"/>
+      <c r="BH21" s="13"/>
+      <c r="BI21" s="13"/>
+      <c r="BJ21" s="13"/>
+      <c r="BK21" s="14"/>
       <c r="BL21" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="BM21" s="14" t="s">
+      <c r="BM21" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="BN21" s="15"/>
-      <c r="BO21" s="16"/>
+      <c r="BN21" s="13"/>
+      <c r="BO21" s="14"/>
       <c r="BP21" s="8" t="s">
         <v>132</v>
       </c>
       <c r="BQ21" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="BR21" s="31"/>
+      <c r="BR21" s="16"/>
       <c r="BT21" s="6"/>
       <c r="BU21" s="6"/>
       <c r="BV21" s="6"/>
@@ -2715,45 +2719,45 @@
       <c r="CH21" s="6"/>
     </row>
     <row r="22" spans="2:86" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B22" s="31"/>
-      <c r="AW22" s="14" t="s">
+      <c r="B22" s="16"/>
+      <c r="AW22" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="AX22" s="16"/>
-      <c r="AY22" s="14" t="s">
+      <c r="AX22" s="14"/>
+      <c r="AY22" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="AZ22" s="15"/>
-      <c r="BA22" s="15"/>
-      <c r="BB22" s="16"/>
-      <c r="BC22" s="14" t="s">
+      <c r="AZ22" s="13"/>
+      <c r="BA22" s="13"/>
+      <c r="BB22" s="14"/>
+      <c r="BC22" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="BD22" s="15"/>
-      <c r="BE22" s="16"/>
-      <c r="BF22" s="14" t="s">
+      <c r="BD22" s="13"/>
+      <c r="BE22" s="14"/>
+      <c r="BF22" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="BG22" s="15"/>
-      <c r="BH22" s="15"/>
-      <c r="BI22" s="15"/>
-      <c r="BJ22" s="15"/>
-      <c r="BK22" s="16"/>
+      <c r="BG22" s="13"/>
+      <c r="BH22" s="13"/>
+      <c r="BI22" s="13"/>
+      <c r="BJ22" s="13"/>
+      <c r="BK22" s="14"/>
       <c r="BL22" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="BM22" s="14" t="s">
+      <c r="BM22" s="12" t="s">
         <v>139</v>
       </c>
-      <c r="BN22" s="15"/>
-      <c r="BO22" s="16"/>
+      <c r="BN22" s="13"/>
+      <c r="BO22" s="14"/>
       <c r="BP22" s="8" t="s">
         <v>140</v>
       </c>
       <c r="BQ22" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="BR22" s="31"/>
+      <c r="BR22" s="16"/>
       <c r="BT22" s="6"/>
       <c r="BU22" s="6"/>
       <c r="BV22" s="6"/>
@@ -2771,45 +2775,45 @@
       <c r="CH22" s="6"/>
     </row>
     <row r="23" spans="2:86" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B23" s="31"/>
-      <c r="AW23" s="14" t="s">
+      <c r="B23" s="16"/>
+      <c r="AW23" s="12" t="s">
         <v>142</v>
       </c>
-      <c r="AX23" s="16"/>
-      <c r="AY23" s="14" t="s">
+      <c r="AX23" s="14"/>
+      <c r="AY23" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="AZ23" s="15"/>
-      <c r="BA23" s="15"/>
-      <c r="BB23" s="16"/>
-      <c r="BC23" s="14" t="s">
+      <c r="AZ23" s="13"/>
+      <c r="BA23" s="13"/>
+      <c r="BB23" s="14"/>
+      <c r="BC23" s="12" t="s">
         <v>144</v>
       </c>
-      <c r="BD23" s="15"/>
-      <c r="BE23" s="16"/>
-      <c r="BF23" s="14" t="s">
+      <c r="BD23" s="13"/>
+      <c r="BE23" s="14"/>
+      <c r="BF23" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="BG23" s="15"/>
-      <c r="BH23" s="15"/>
-      <c r="BI23" s="15"/>
-      <c r="BJ23" s="15"/>
-      <c r="BK23" s="16"/>
+      <c r="BG23" s="13"/>
+      <c r="BH23" s="13"/>
+      <c r="BI23" s="13"/>
+      <c r="BJ23" s="13"/>
+      <c r="BK23" s="14"/>
       <c r="BL23" s="8" t="s">
         <v>146</v>
       </c>
-      <c r="BM23" s="14" t="s">
+      <c r="BM23" s="12" t="s">
         <v>147</v>
       </c>
-      <c r="BN23" s="15"/>
-      <c r="BO23" s="16"/>
+      <c r="BN23" s="13"/>
+      <c r="BO23" s="14"/>
       <c r="BP23" s="8" t="s">
         <v>148</v>
       </c>
       <c r="BQ23" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="BR23" s="31"/>
+      <c r="BR23" s="16"/>
       <c r="BT23" s="6"/>
       <c r="BU23" s="6"/>
       <c r="BV23" s="6"/>
@@ -2827,45 +2831,45 @@
       <c r="CH23" s="6"/>
     </row>
     <row r="24" spans="2:86" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B24" s="31"/>
-      <c r="AW24" s="14" t="s">
+      <c r="B24" s="16"/>
+      <c r="AW24" s="12" t="s">
         <v>150</v>
       </c>
-      <c r="AX24" s="16"/>
-      <c r="AY24" s="14" t="s">
+      <c r="AX24" s="14"/>
+      <c r="AY24" s="12" t="s">
         <v>151</v>
       </c>
-      <c r="AZ24" s="15"/>
-      <c r="BA24" s="15"/>
-      <c r="BB24" s="16"/>
-      <c r="BC24" s="14" t="s">
+      <c r="AZ24" s="13"/>
+      <c r="BA24" s="13"/>
+      <c r="BB24" s="14"/>
+      <c r="BC24" s="12" t="s">
         <v>152</v>
       </c>
-      <c r="BD24" s="15"/>
-      <c r="BE24" s="16"/>
-      <c r="BF24" s="14" t="s">
+      <c r="BD24" s="13"/>
+      <c r="BE24" s="14"/>
+      <c r="BF24" s="12" t="s">
         <v>153</v>
       </c>
-      <c r="BG24" s="15"/>
-      <c r="BH24" s="15"/>
-      <c r="BI24" s="15"/>
-      <c r="BJ24" s="15"/>
-      <c r="BK24" s="16"/>
+      <c r="BG24" s="13"/>
+      <c r="BH24" s="13"/>
+      <c r="BI24" s="13"/>
+      <c r="BJ24" s="13"/>
+      <c r="BK24" s="14"/>
       <c r="BL24" s="8" t="s">
         <v>154</v>
       </c>
-      <c r="BM24" s="14" t="s">
+      <c r="BM24" s="12" t="s">
         <v>155</v>
       </c>
-      <c r="BN24" s="15"/>
-      <c r="BO24" s="16"/>
+      <c r="BN24" s="13"/>
+      <c r="BO24" s="14"/>
       <c r="BP24" s="8" t="s">
         <v>156</v>
       </c>
       <c r="BQ24" s="8" t="s">
         <v>157</v>
       </c>
-      <c r="BR24" s="31"/>
+      <c r="BR24" s="16"/>
       <c r="BT24" s="6"/>
       <c r="BU24" s="6"/>
       <c r="BV24" s="6"/>
@@ -2883,45 +2887,45 @@
       <c r="CH24" s="6"/>
     </row>
     <row r="25" spans="2:86" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B25" s="31"/>
-      <c r="AW25" s="14" t="s">
+      <c r="B25" s="16"/>
+      <c r="AW25" s="12" t="s">
         <v>228</v>
       </c>
-      <c r="AX25" s="16"/>
-      <c r="AY25" s="28" t="s">
+      <c r="AX25" s="14"/>
+      <c r="AY25" s="30" t="s">
         <v>158</v>
       </c>
-      <c r="AZ25" s="29"/>
-      <c r="BA25" s="29"/>
-      <c r="BB25" s="30"/>
-      <c r="BC25" s="15" t="s">
+      <c r="AZ25" s="31"/>
+      <c r="BA25" s="31"/>
+      <c r="BB25" s="32"/>
+      <c r="BC25" s="13" t="s">
         <v>229</v>
       </c>
-      <c r="BD25" s="15"/>
-      <c r="BE25" s="16"/>
-      <c r="BF25" s="14" t="s">
+      <c r="BD25" s="13"/>
+      <c r="BE25" s="14"/>
+      <c r="BF25" s="12" t="s">
         <v>230</v>
       </c>
-      <c r="BG25" s="15"/>
-      <c r="BH25" s="15"/>
-      <c r="BI25" s="15"/>
-      <c r="BJ25" s="15"/>
-      <c r="BK25" s="16"/>
+      <c r="BG25" s="13"/>
+      <c r="BH25" s="13"/>
+      <c r="BI25" s="13"/>
+      <c r="BJ25" s="13"/>
+      <c r="BK25" s="14"/>
       <c r="BL25" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="BM25" s="14" t="s">
+      <c r="BM25" s="12" t="s">
         <v>231</v>
       </c>
-      <c r="BN25" s="15"/>
-      <c r="BO25" s="16"/>
+      <c r="BN25" s="13"/>
+      <c r="BO25" s="14"/>
       <c r="BP25" s="8" t="s">
         <v>160</v>
       </c>
       <c r="BQ25" s="8" t="s">
         <v>161</v>
       </c>
-      <c r="BR25" s="31"/>
+      <c r="BR25" s="16"/>
       <c r="BT25" s="6"/>
       <c r="BU25" s="6"/>
       <c r="BV25" s="6"/>
@@ -2939,77 +2943,77 @@
       <c r="CH25" s="6"/>
     </row>
     <row r="26" spans="2:86" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B26" s="31"/>
-      <c r="E26" s="12" t="s">
+      <c r="B26" s="16"/>
+      <c r="E26" s="27" t="s">
         <v>234</v>
       </c>
-      <c r="F26" s="13"/>
-      <c r="G26" s="13"/>
-      <c r="H26" s="13"/>
-      <c r="I26" s="13"/>
-      <c r="J26" s="13"/>
-      <c r="K26" s="13"/>
-      <c r="L26" s="13"/>
-      <c r="M26" s="13"/>
-      <c r="N26" s="13"/>
-      <c r="O26" s="13"/>
-      <c r="P26" s="13"/>
-      <c r="Q26" s="13"/>
-      <c r="R26" s="13"/>
-      <c r="T26" s="12" t="s">
+      <c r="F26" s="28"/>
+      <c r="G26" s="28"/>
+      <c r="H26" s="28"/>
+      <c r="I26" s="28"/>
+      <c r="J26" s="28"/>
+      <c r="K26" s="28"/>
+      <c r="L26" s="28"/>
+      <c r="M26" s="28"/>
+      <c r="N26" s="28"/>
+      <c r="O26" s="28"/>
+      <c r="P26" s="28"/>
+      <c r="Q26" s="28"/>
+      <c r="R26" s="28"/>
+      <c r="T26" s="27" t="s">
         <v>173</v>
       </c>
-      <c r="U26" s="13"/>
-      <c r="V26" s="13"/>
-      <c r="W26" s="13"/>
-      <c r="X26" s="13"/>
-      <c r="Y26" s="13"/>
-      <c r="Z26" s="13"/>
-      <c r="AA26" s="13"/>
-      <c r="AB26" s="13"/>
-      <c r="AC26" s="13"/>
-      <c r="AD26" s="13"/>
-      <c r="AE26" s="13"/>
-      <c r="AF26" s="13"/>
-      <c r="AG26" s="13"/>
-      <c r="AW26" s="14" t="s">
+      <c r="U26" s="28"/>
+      <c r="V26" s="28"/>
+      <c r="W26" s="28"/>
+      <c r="X26" s="28"/>
+      <c r="Y26" s="28"/>
+      <c r="Z26" s="28"/>
+      <c r="AA26" s="28"/>
+      <c r="AB26" s="28"/>
+      <c r="AC26" s="28"/>
+      <c r="AD26" s="28"/>
+      <c r="AE26" s="28"/>
+      <c r="AF26" s="28"/>
+      <c r="AG26" s="28"/>
+      <c r="AW26" s="12" t="s">
         <v>162</v>
       </c>
-      <c r="AX26" s="16"/>
-      <c r="AY26" s="14" t="s">
+      <c r="AX26" s="14"/>
+      <c r="AY26" s="12" t="s">
         <v>163</v>
       </c>
-      <c r="AZ26" s="15"/>
-      <c r="BA26" s="15"/>
-      <c r="BB26" s="16"/>
-      <c r="BC26" s="14" t="s">
+      <c r="AZ26" s="13"/>
+      <c r="BA26" s="13"/>
+      <c r="BB26" s="14"/>
+      <c r="BC26" s="12" t="s">
         <v>164</v>
       </c>
-      <c r="BD26" s="15"/>
-      <c r="BE26" s="16"/>
-      <c r="BF26" s="14" t="s">
+      <c r="BD26" s="13"/>
+      <c r="BE26" s="14"/>
+      <c r="BF26" s="12" t="s">
         <v>165</v>
       </c>
-      <c r="BG26" s="15"/>
-      <c r="BH26" s="15"/>
-      <c r="BI26" s="15"/>
-      <c r="BJ26" s="15"/>
-      <c r="BK26" s="16"/>
+      <c r="BG26" s="13"/>
+      <c r="BH26" s="13"/>
+      <c r="BI26" s="13"/>
+      <c r="BJ26" s="13"/>
+      <c r="BK26" s="14"/>
       <c r="BL26" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="BM26" s="14" t="s">
+      <c r="BM26" s="12" t="s">
         <v>167</v>
       </c>
-      <c r="BN26" s="15"/>
-      <c r="BO26" s="16"/>
+      <c r="BN26" s="13"/>
+      <c r="BO26" s="14"/>
       <c r="BP26" s="7" t="s">
         <v>168</v>
       </c>
       <c r="BQ26" s="7" t="s">
         <v>169</v>
       </c>
-      <c r="BR26" s="31"/>
+      <c r="BR26" s="16"/>
       <c r="BT26" s="6"/>
       <c r="BU26" s="6"/>
       <c r="BV26" s="6"/>
@@ -3027,37 +3031,37 @@
       <c r="CH26" s="6"/>
     </row>
     <row r="27" spans="2:86" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B27" s="31"/>
-      <c r="E27" s="13"/>
-      <c r="F27" s="13"/>
-      <c r="G27" s="13"/>
-      <c r="H27" s="13"/>
-      <c r="I27" s="13"/>
-      <c r="J27" s="13"/>
-      <c r="K27" s="13"/>
-      <c r="L27" s="13"/>
-      <c r="M27" s="13"/>
-      <c r="N27" s="13"/>
-      <c r="O27" s="13"/>
-      <c r="P27" s="13"/>
-      <c r="Q27" s="13"/>
-      <c r="R27" s="13"/>
-      <c r="T27" s="13"/>
-      <c r="U27" s="13"/>
-      <c r="V27" s="13"/>
-      <c r="W27" s="13"/>
-      <c r="X27" s="13"/>
-      <c r="Y27" s="13"/>
-      <c r="Z27" s="13"/>
-      <c r="AA27" s="13"/>
-      <c r="AB27" s="13"/>
-      <c r="AC27" s="13"/>
-      <c r="AD27" s="13"/>
-      <c r="AE27" s="13"/>
-      <c r="AF27" s="13"/>
-      <c r="AG27" s="13"/>
+      <c r="B27" s="16"/>
+      <c r="E27" s="28"/>
+      <c r="F27" s="28"/>
+      <c r="G27" s="28"/>
+      <c r="H27" s="28"/>
+      <c r="I27" s="28"/>
+      <c r="J27" s="28"/>
+      <c r="K27" s="28"/>
+      <c r="L27" s="28"/>
+      <c r="M27" s="28"/>
+      <c r="N27" s="28"/>
+      <c r="O27" s="28"/>
+      <c r="P27" s="28"/>
+      <c r="Q27" s="28"/>
+      <c r="R27" s="28"/>
+      <c r="T27" s="28"/>
+      <c r="U27" s="28"/>
+      <c r="V27" s="28"/>
+      <c r="W27" s="28"/>
+      <c r="X27" s="28"/>
+      <c r="Y27" s="28"/>
+      <c r="Z27" s="28"/>
+      <c r="AA27" s="28"/>
+      <c r="AB27" s="28"/>
+      <c r="AC27" s="28"/>
+      <c r="AD27" s="28"/>
+      <c r="AE27" s="28"/>
+      <c r="AF27" s="28"/>
+      <c r="AG27" s="28"/>
       <c r="BQ27" s="6"/>
-      <c r="BR27" s="31"/>
+      <c r="BR27" s="16"/>
       <c r="BT27" s="6"/>
       <c r="BU27" s="6"/>
       <c r="BV27" s="6"/>
@@ -3075,40 +3079,40 @@
       <c r="CH27" s="6"/>
     </row>
     <row r="28" spans="2:86" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B28" s="31"/>
-      <c r="E28" s="13"/>
-      <c r="F28" s="13"/>
-      <c r="G28" s="13"/>
-      <c r="H28" s="13"/>
-      <c r="I28" s="13"/>
-      <c r="J28" s="13"/>
-      <c r="K28" s="13"/>
-      <c r="L28" s="13"/>
-      <c r="M28" s="13"/>
-      <c r="N28" s="13"/>
-      <c r="O28" s="13"/>
-      <c r="P28" s="13"/>
-      <c r="Q28" s="13"/>
-      <c r="R28" s="13"/>
-      <c r="T28" s="13"/>
-      <c r="U28" s="13"/>
-      <c r="V28" s="13"/>
-      <c r="W28" s="13"/>
-      <c r="X28" s="13"/>
-      <c r="Y28" s="13"/>
-      <c r="Z28" s="13"/>
-      <c r="AA28" s="13"/>
-      <c r="AB28" s="13"/>
-      <c r="AC28" s="13"/>
-      <c r="AD28" s="13"/>
-      <c r="AE28" s="13"/>
-      <c r="AF28" s="13"/>
-      <c r="AG28" s="13"/>
-      <c r="AI28" s="12"/>
-      <c r="AJ28" s="13"/>
-      <c r="AK28" s="13"/>
-      <c r="AL28" s="13"/>
-      <c r="AM28" s="13"/>
+      <c r="B28" s="16"/>
+      <c r="E28" s="28"/>
+      <c r="F28" s="28"/>
+      <c r="G28" s="28"/>
+      <c r="H28" s="28"/>
+      <c r="I28" s="28"/>
+      <c r="J28" s="28"/>
+      <c r="K28" s="28"/>
+      <c r="L28" s="28"/>
+      <c r="M28" s="28"/>
+      <c r="N28" s="28"/>
+      <c r="O28" s="28"/>
+      <c r="P28" s="28"/>
+      <c r="Q28" s="28"/>
+      <c r="R28" s="28"/>
+      <c r="T28" s="28"/>
+      <c r="U28" s="28"/>
+      <c r="V28" s="28"/>
+      <c r="W28" s="28"/>
+      <c r="X28" s="28"/>
+      <c r="Y28" s="28"/>
+      <c r="Z28" s="28"/>
+      <c r="AA28" s="28"/>
+      <c r="AB28" s="28"/>
+      <c r="AC28" s="28"/>
+      <c r="AD28" s="28"/>
+      <c r="AE28" s="28"/>
+      <c r="AF28" s="28"/>
+      <c r="AG28" s="28"/>
+      <c r="AI28" s="27"/>
+      <c r="AJ28" s="28"/>
+      <c r="AK28" s="28"/>
+      <c r="AL28" s="28"/>
+      <c r="AM28" s="28"/>
       <c r="AV28" s="6"/>
       <c r="AW28" s="9"/>
       <c r="AX28" s="9"/>
@@ -3131,7 +3135,7 @@
       <c r="BO28" s="9"/>
       <c r="BP28" s="9"/>
       <c r="BQ28" s="9"/>
-      <c r="BR28" s="31"/>
+      <c r="BR28" s="16"/>
       <c r="BT28" s="6"/>
       <c r="BU28" s="6"/>
       <c r="BV28" s="6"/>
@@ -3149,42 +3153,42 @@
       <c r="CH28" s="6"/>
     </row>
     <row r="29" spans="2:86" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B29" s="27"/>
-      <c r="E29" s="13"/>
-      <c r="F29" s="13"/>
-      <c r="G29" s="13"/>
-      <c r="H29" s="13"/>
-      <c r="I29" s="13"/>
-      <c r="J29" s="13"/>
-      <c r="K29" s="13"/>
-      <c r="L29" s="13"/>
-      <c r="M29" s="13"/>
-      <c r="N29" s="13"/>
-      <c r="O29" s="13"/>
-      <c r="P29" s="13"/>
-      <c r="Q29" s="13"/>
-      <c r="R29" s="13"/>
-      <c r="T29" s="13"/>
-      <c r="U29" s="13"/>
-      <c r="V29" s="13"/>
-      <c r="W29" s="13"/>
-      <c r="X29" s="13"/>
-      <c r="Y29" s="13"/>
-      <c r="Z29" s="13"/>
-      <c r="AA29" s="13"/>
-      <c r="AB29" s="13"/>
-      <c r="AC29" s="13"/>
-      <c r="AD29" s="13"/>
-      <c r="AE29" s="13"/>
-      <c r="AF29" s="13"/>
-      <c r="AG29" s="13"/>
-      <c r="AI29" s="13"/>
-      <c r="AJ29" s="13"/>
-      <c r="AK29" s="13"/>
-      <c r="AL29" s="13"/>
-      <c r="AM29" s="13"/>
+      <c r="B29" s="17"/>
+      <c r="E29" s="28"/>
+      <c r="F29" s="28"/>
+      <c r="G29" s="28"/>
+      <c r="H29" s="28"/>
+      <c r="I29" s="28"/>
+      <c r="J29" s="28"/>
+      <c r="K29" s="28"/>
+      <c r="L29" s="28"/>
+      <c r="M29" s="28"/>
+      <c r="N29" s="28"/>
+      <c r="O29" s="28"/>
+      <c r="P29" s="28"/>
+      <c r="Q29" s="28"/>
+      <c r="R29" s="28"/>
+      <c r="T29" s="28"/>
+      <c r="U29" s="28"/>
+      <c r="V29" s="28"/>
+      <c r="W29" s="28"/>
+      <c r="X29" s="28"/>
+      <c r="Y29" s="28"/>
+      <c r="Z29" s="28"/>
+      <c r="AA29" s="28"/>
+      <c r="AB29" s="28"/>
+      <c r="AC29" s="28"/>
+      <c r="AD29" s="28"/>
+      <c r="AE29" s="28"/>
+      <c r="AF29" s="28"/>
+      <c r="AG29" s="28"/>
+      <c r="AI29" s="28"/>
+      <c r="AJ29" s="28"/>
+      <c r="AK29" s="28"/>
+      <c r="AL29" s="28"/>
+      <c r="AM29" s="28"/>
       <c r="BQ29" s="6"/>
-      <c r="BR29" s="27"/>
+      <c r="BR29" s="17"/>
       <c r="BT29" s="6"/>
       <c r="BU29" s="6"/>
       <c r="BV29" s="6"/>
@@ -3202,10 +3206,10 @@
       <c r="CH29" s="6"/>
     </row>
     <row r="30" spans="2:86" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B30" s="26" t="s">
+      <c r="B30" s="15" t="s">
         <v>170</v>
       </c>
-      <c r="BR30" s="26" t="s">
+      <c r="BR30" s="15" t="s">
         <v>170</v>
       </c>
       <c r="BT30" s="6"/>
@@ -3217,33 +3221,33 @@
       <c r="BZ30" s="6"/>
     </row>
     <row r="31" spans="2:86" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B31" s="31"/>
-      <c r="AW31" s="17" t="s">
+      <c r="B31" s="16"/>
+      <c r="AW31" s="18" t="s">
         <v>171</v>
       </c>
-      <c r="AX31" s="18"/>
-      <c r="AY31" s="18" t="s">
+      <c r="AX31" s="19"/>
+      <c r="AY31" s="19" t="s">
         <v>172</v>
       </c>
-      <c r="AZ31" s="18"/>
-      <c r="BA31" s="18"/>
-      <c r="BB31" s="18"/>
-      <c r="BC31" s="18"/>
-      <c r="BD31" s="18"/>
-      <c r="BE31" s="18"/>
-      <c r="BF31" s="18"/>
-      <c r="BG31" s="18"/>
-      <c r="BH31" s="18"/>
-      <c r="BI31" s="18"/>
-      <c r="BJ31" s="18"/>
-      <c r="BK31" s="18"/>
-      <c r="BL31" s="18"/>
-      <c r="BM31" s="18"/>
-      <c r="BN31" s="18"/>
-      <c r="BO31" s="18"/>
-      <c r="BP31" s="18"/>
-      <c r="BQ31" s="19"/>
-      <c r="BR31" s="31"/>
+      <c r="AZ31" s="19"/>
+      <c r="BA31" s="19"/>
+      <c r="BB31" s="19"/>
+      <c r="BC31" s="19"/>
+      <c r="BD31" s="19"/>
+      <c r="BE31" s="19"/>
+      <c r="BF31" s="19"/>
+      <c r="BG31" s="19"/>
+      <c r="BH31" s="19"/>
+      <c r="BI31" s="19"/>
+      <c r="BJ31" s="19"/>
+      <c r="BK31" s="19"/>
+      <c r="BL31" s="19"/>
+      <c r="BM31" s="19"/>
+      <c r="BN31" s="19"/>
+      <c r="BO31" s="19"/>
+      <c r="BP31" s="19"/>
+      <c r="BQ31" s="20"/>
+      <c r="BR31" s="16"/>
       <c r="BT31" s="6"/>
       <c r="BU31" s="6"/>
       <c r="BV31" s="6"/>
@@ -3253,29 +3257,29 @@
       <c r="BZ31" s="6"/>
     </row>
     <row r="32" spans="2:86" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B32" s="31"/>
-      <c r="AW32" s="23"/>
-      <c r="AX32" s="24"/>
-      <c r="AY32" s="24"/>
-      <c r="AZ32" s="24"/>
-      <c r="BA32" s="24"/>
-      <c r="BB32" s="24"/>
-      <c r="BC32" s="24"/>
-      <c r="BD32" s="24"/>
-      <c r="BE32" s="24"/>
-      <c r="BF32" s="24"/>
-      <c r="BG32" s="24"/>
-      <c r="BH32" s="24"/>
-      <c r="BI32" s="24"/>
-      <c r="BJ32" s="24"/>
-      <c r="BK32" s="24"/>
-      <c r="BL32" s="24"/>
-      <c r="BM32" s="24"/>
-      <c r="BN32" s="24"/>
-      <c r="BO32" s="24"/>
-      <c r="BP32" s="24"/>
-      <c r="BQ32" s="25"/>
-      <c r="BR32" s="31"/>
+      <c r="B32" s="16"/>
+      <c r="AW32" s="24"/>
+      <c r="AX32" s="25"/>
+      <c r="AY32" s="25"/>
+      <c r="AZ32" s="25"/>
+      <c r="BA32" s="25"/>
+      <c r="BB32" s="25"/>
+      <c r="BC32" s="25"/>
+      <c r="BD32" s="25"/>
+      <c r="BE32" s="25"/>
+      <c r="BF32" s="25"/>
+      <c r="BG32" s="25"/>
+      <c r="BH32" s="25"/>
+      <c r="BI32" s="25"/>
+      <c r="BJ32" s="25"/>
+      <c r="BK32" s="25"/>
+      <c r="BL32" s="25"/>
+      <c r="BM32" s="25"/>
+      <c r="BN32" s="25"/>
+      <c r="BO32" s="25"/>
+      <c r="BP32" s="25"/>
+      <c r="BQ32" s="26"/>
+      <c r="BR32" s="16"/>
       <c r="BT32" s="6"/>
       <c r="BU32" s="6"/>
       <c r="BV32" s="6"/>
@@ -3285,29 +3289,29 @@
       <c r="BZ32" s="6"/>
     </row>
     <row r="33" spans="2:78" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B33" s="31"/>
-      <c r="AW33" s="23"/>
-      <c r="AX33" s="24"/>
-      <c r="AY33" s="24"/>
-      <c r="AZ33" s="24"/>
-      <c r="BA33" s="24"/>
-      <c r="BB33" s="24"/>
-      <c r="BC33" s="24"/>
-      <c r="BD33" s="24"/>
-      <c r="BE33" s="24"/>
-      <c r="BF33" s="24"/>
-      <c r="BG33" s="24"/>
-      <c r="BH33" s="24"/>
-      <c r="BI33" s="24"/>
-      <c r="BJ33" s="24"/>
-      <c r="BK33" s="24"/>
-      <c r="BL33" s="24"/>
-      <c r="BM33" s="24"/>
-      <c r="BN33" s="24"/>
-      <c r="BO33" s="24"/>
-      <c r="BP33" s="24"/>
-      <c r="BQ33" s="25"/>
-      <c r="BR33" s="31"/>
+      <c r="B33" s="16"/>
+      <c r="AW33" s="24"/>
+      <c r="AX33" s="25"/>
+      <c r="AY33" s="25"/>
+      <c r="AZ33" s="25"/>
+      <c r="BA33" s="25"/>
+      <c r="BB33" s="25"/>
+      <c r="BC33" s="25"/>
+      <c r="BD33" s="25"/>
+      <c r="BE33" s="25"/>
+      <c r="BF33" s="25"/>
+      <c r="BG33" s="25"/>
+      <c r="BH33" s="25"/>
+      <c r="BI33" s="25"/>
+      <c r="BJ33" s="25"/>
+      <c r="BK33" s="25"/>
+      <c r="BL33" s="25"/>
+      <c r="BM33" s="25"/>
+      <c r="BN33" s="25"/>
+      <c r="BO33" s="25"/>
+      <c r="BP33" s="25"/>
+      <c r="BQ33" s="26"/>
+      <c r="BR33" s="16"/>
       <c r="BT33" s="6"/>
       <c r="BU33" s="6"/>
       <c r="BV33" s="6"/>
@@ -3317,29 +3321,29 @@
       <c r="BZ33" s="6"/>
     </row>
     <row r="34" spans="2:78" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B34" s="31"/>
-      <c r="AW34" s="23"/>
-      <c r="AX34" s="24"/>
-      <c r="AY34" s="24"/>
-      <c r="AZ34" s="24"/>
-      <c r="BA34" s="24"/>
-      <c r="BB34" s="24"/>
-      <c r="BC34" s="24"/>
-      <c r="BD34" s="24"/>
-      <c r="BE34" s="24"/>
-      <c r="BF34" s="24"/>
-      <c r="BG34" s="24"/>
-      <c r="BH34" s="24"/>
-      <c r="BI34" s="24"/>
-      <c r="BJ34" s="24"/>
-      <c r="BK34" s="24"/>
-      <c r="BL34" s="24"/>
-      <c r="BM34" s="24"/>
-      <c r="BN34" s="24"/>
-      <c r="BO34" s="24"/>
-      <c r="BP34" s="24"/>
-      <c r="BQ34" s="25"/>
-      <c r="BR34" s="31"/>
+      <c r="B34" s="16"/>
+      <c r="AW34" s="24"/>
+      <c r="AX34" s="25"/>
+      <c r="AY34" s="25"/>
+      <c r="AZ34" s="25"/>
+      <c r="BA34" s="25"/>
+      <c r="BB34" s="25"/>
+      <c r="BC34" s="25"/>
+      <c r="BD34" s="25"/>
+      <c r="BE34" s="25"/>
+      <c r="BF34" s="25"/>
+      <c r="BG34" s="25"/>
+      <c r="BH34" s="25"/>
+      <c r="BI34" s="25"/>
+      <c r="BJ34" s="25"/>
+      <c r="BK34" s="25"/>
+      <c r="BL34" s="25"/>
+      <c r="BM34" s="25"/>
+      <c r="BN34" s="25"/>
+      <c r="BO34" s="25"/>
+      <c r="BP34" s="25"/>
+      <c r="BQ34" s="26"/>
+      <c r="BR34" s="16"/>
       <c r="BT34" s="6"/>
       <c r="BU34" s="6"/>
       <c r="BV34" s="6"/>
@@ -3349,61 +3353,61 @@
       <c r="BZ34" s="6"/>
     </row>
     <row r="35" spans="2:78" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B35" s="31"/>
-      <c r="E35" s="12" t="s">
+      <c r="B35" s="16"/>
+      <c r="E35" s="27" t="s">
         <v>235</v>
       </c>
-      <c r="F35" s="13"/>
-      <c r="G35" s="13"/>
-      <c r="H35" s="13"/>
-      <c r="I35" s="13"/>
-      <c r="J35" s="13"/>
-      <c r="K35" s="13"/>
-      <c r="L35" s="13"/>
-      <c r="M35" s="13"/>
-      <c r="N35" s="13"/>
-      <c r="O35" s="13"/>
-      <c r="P35" s="13"/>
-      <c r="Q35" s="13"/>
-      <c r="R35" s="13"/>
-      <c r="T35" s="12" t="s">
+      <c r="F35" s="28"/>
+      <c r="G35" s="28"/>
+      <c r="H35" s="28"/>
+      <c r="I35" s="28"/>
+      <c r="J35" s="28"/>
+      <c r="K35" s="28"/>
+      <c r="L35" s="28"/>
+      <c r="M35" s="28"/>
+      <c r="N35" s="28"/>
+      <c r="O35" s="28"/>
+      <c r="P35" s="28"/>
+      <c r="Q35" s="28"/>
+      <c r="R35" s="28"/>
+      <c r="T35" s="27" t="s">
         <v>174</v>
       </c>
-      <c r="U35" s="13"/>
-      <c r="V35" s="13"/>
-      <c r="W35" s="13"/>
-      <c r="X35" s="13"/>
-      <c r="Y35" s="13"/>
-      <c r="Z35" s="13"/>
-      <c r="AA35" s="13"/>
-      <c r="AB35" s="13"/>
-      <c r="AC35" s="13"/>
-      <c r="AD35" s="13"/>
-      <c r="AE35" s="13"/>
-      <c r="AF35" s="13"/>
-      <c r="AG35" s="13"/>
-      <c r="AW35" s="23"/>
-      <c r="AX35" s="24"/>
-      <c r="AY35" s="24"/>
-      <c r="AZ35" s="24"/>
-      <c r="BA35" s="24"/>
-      <c r="BB35" s="24"/>
-      <c r="BC35" s="24"/>
-      <c r="BD35" s="24"/>
-      <c r="BE35" s="24"/>
-      <c r="BF35" s="24"/>
-      <c r="BG35" s="24"/>
-      <c r="BH35" s="24"/>
-      <c r="BI35" s="24"/>
-      <c r="BJ35" s="24"/>
-      <c r="BK35" s="24"/>
-      <c r="BL35" s="24"/>
-      <c r="BM35" s="24"/>
-      <c r="BN35" s="24"/>
-      <c r="BO35" s="24"/>
-      <c r="BP35" s="24"/>
-      <c r="BQ35" s="25"/>
-      <c r="BR35" s="31"/>
+      <c r="U35" s="28"/>
+      <c r="V35" s="28"/>
+      <c r="W35" s="28"/>
+      <c r="X35" s="28"/>
+      <c r="Y35" s="28"/>
+      <c r="Z35" s="28"/>
+      <c r="AA35" s="28"/>
+      <c r="AB35" s="28"/>
+      <c r="AC35" s="28"/>
+      <c r="AD35" s="28"/>
+      <c r="AE35" s="28"/>
+      <c r="AF35" s="28"/>
+      <c r="AG35" s="28"/>
+      <c r="AW35" s="24"/>
+      <c r="AX35" s="25"/>
+      <c r="AY35" s="25"/>
+      <c r="AZ35" s="25"/>
+      <c r="BA35" s="25"/>
+      <c r="BB35" s="25"/>
+      <c r="BC35" s="25"/>
+      <c r="BD35" s="25"/>
+      <c r="BE35" s="25"/>
+      <c r="BF35" s="25"/>
+      <c r="BG35" s="25"/>
+      <c r="BH35" s="25"/>
+      <c r="BI35" s="25"/>
+      <c r="BJ35" s="25"/>
+      <c r="BK35" s="25"/>
+      <c r="BL35" s="25"/>
+      <c r="BM35" s="25"/>
+      <c r="BN35" s="25"/>
+      <c r="BO35" s="25"/>
+      <c r="BP35" s="25"/>
+      <c r="BQ35" s="26"/>
+      <c r="BR35" s="16"/>
       <c r="BT35" s="6"/>
       <c r="BU35" s="6"/>
       <c r="BV35" s="6"/>
@@ -3413,57 +3417,57 @@
       <c r="BZ35" s="6"/>
     </row>
     <row r="36" spans="2:78" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B36" s="31"/>
-      <c r="E36" s="13"/>
-      <c r="F36" s="13"/>
-      <c r="G36" s="13"/>
-      <c r="H36" s="13"/>
-      <c r="I36" s="13"/>
-      <c r="J36" s="13"/>
-      <c r="K36" s="13"/>
-      <c r="L36" s="13"/>
-      <c r="M36" s="13"/>
-      <c r="N36" s="13"/>
-      <c r="O36" s="13"/>
-      <c r="P36" s="13"/>
-      <c r="Q36" s="13"/>
-      <c r="R36" s="13"/>
-      <c r="T36" s="13"/>
-      <c r="U36" s="13"/>
-      <c r="V36" s="13"/>
-      <c r="W36" s="13"/>
-      <c r="X36" s="13"/>
-      <c r="Y36" s="13"/>
-      <c r="Z36" s="13"/>
-      <c r="AA36" s="13"/>
-      <c r="AB36" s="13"/>
-      <c r="AC36" s="13"/>
-      <c r="AD36" s="13"/>
-      <c r="AE36" s="13"/>
-      <c r="AF36" s="13"/>
-      <c r="AG36" s="13"/>
-      <c r="AW36" s="20"/>
-      <c r="AX36" s="21"/>
-      <c r="AY36" s="21"/>
-      <c r="AZ36" s="21"/>
-      <c r="BA36" s="21"/>
-      <c r="BB36" s="21"/>
-      <c r="BC36" s="21"/>
-      <c r="BD36" s="21"/>
-      <c r="BE36" s="21"/>
-      <c r="BF36" s="21"/>
-      <c r="BG36" s="21"/>
-      <c r="BH36" s="21"/>
-      <c r="BI36" s="21"/>
-      <c r="BJ36" s="21"/>
-      <c r="BK36" s="21"/>
-      <c r="BL36" s="21"/>
-      <c r="BM36" s="21"/>
-      <c r="BN36" s="21"/>
-      <c r="BO36" s="21"/>
-      <c r="BP36" s="21"/>
-      <c r="BQ36" s="22"/>
-      <c r="BR36" s="31"/>
+      <c r="B36" s="16"/>
+      <c r="E36" s="28"/>
+      <c r="F36" s="28"/>
+      <c r="G36" s="28"/>
+      <c r="H36" s="28"/>
+      <c r="I36" s="28"/>
+      <c r="J36" s="28"/>
+      <c r="K36" s="28"/>
+      <c r="L36" s="28"/>
+      <c r="M36" s="28"/>
+      <c r="N36" s="28"/>
+      <c r="O36" s="28"/>
+      <c r="P36" s="28"/>
+      <c r="Q36" s="28"/>
+      <c r="R36" s="28"/>
+      <c r="T36" s="28"/>
+      <c r="U36" s="28"/>
+      <c r="V36" s="28"/>
+      <c r="W36" s="28"/>
+      <c r="X36" s="28"/>
+      <c r="Y36" s="28"/>
+      <c r="Z36" s="28"/>
+      <c r="AA36" s="28"/>
+      <c r="AB36" s="28"/>
+      <c r="AC36" s="28"/>
+      <c r="AD36" s="28"/>
+      <c r="AE36" s="28"/>
+      <c r="AF36" s="28"/>
+      <c r="AG36" s="28"/>
+      <c r="AW36" s="21"/>
+      <c r="AX36" s="22"/>
+      <c r="AY36" s="22"/>
+      <c r="AZ36" s="22"/>
+      <c r="BA36" s="22"/>
+      <c r="BB36" s="22"/>
+      <c r="BC36" s="22"/>
+      <c r="BD36" s="22"/>
+      <c r="BE36" s="22"/>
+      <c r="BF36" s="22"/>
+      <c r="BG36" s="22"/>
+      <c r="BH36" s="22"/>
+      <c r="BI36" s="22"/>
+      <c r="BJ36" s="22"/>
+      <c r="BK36" s="22"/>
+      <c r="BL36" s="22"/>
+      <c r="BM36" s="22"/>
+      <c r="BN36" s="22"/>
+      <c r="BO36" s="22"/>
+      <c r="BP36" s="22"/>
+      <c r="BQ36" s="23"/>
+      <c r="BR36" s="16"/>
       <c r="BT36" s="6"/>
       <c r="BU36" s="6"/>
       <c r="BV36" s="6"/>
@@ -3473,36 +3477,36 @@
       <c r="BZ36" s="6"/>
     </row>
     <row r="37" spans="2:78" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B37" s="31"/>
-      <c r="E37" s="13"/>
-      <c r="F37" s="13"/>
-      <c r="G37" s="13"/>
-      <c r="H37" s="13"/>
-      <c r="I37" s="13"/>
-      <c r="J37" s="13"/>
-      <c r="K37" s="13"/>
-      <c r="L37" s="13"/>
-      <c r="M37" s="13"/>
-      <c r="N37" s="13"/>
-      <c r="O37" s="13"/>
-      <c r="P37" s="13"/>
-      <c r="Q37" s="13"/>
-      <c r="R37" s="13"/>
-      <c r="T37" s="13"/>
-      <c r="U37" s="13"/>
-      <c r="V37" s="13"/>
-      <c r="W37" s="13"/>
-      <c r="X37" s="13"/>
-      <c r="Y37" s="13"/>
-      <c r="Z37" s="13"/>
-      <c r="AA37" s="13"/>
-      <c r="AB37" s="13"/>
-      <c r="AC37" s="13"/>
-      <c r="AD37" s="13"/>
-      <c r="AE37" s="13"/>
-      <c r="AF37" s="13"/>
-      <c r="AG37" s="13"/>
-      <c r="BR37" s="31"/>
+      <c r="B37" s="16"/>
+      <c r="E37" s="28"/>
+      <c r="F37" s="28"/>
+      <c r="G37" s="28"/>
+      <c r="H37" s="28"/>
+      <c r="I37" s="28"/>
+      <c r="J37" s="28"/>
+      <c r="K37" s="28"/>
+      <c r="L37" s="28"/>
+      <c r="M37" s="28"/>
+      <c r="N37" s="28"/>
+      <c r="O37" s="28"/>
+      <c r="P37" s="28"/>
+      <c r="Q37" s="28"/>
+      <c r="R37" s="28"/>
+      <c r="T37" s="28"/>
+      <c r="U37" s="28"/>
+      <c r="V37" s="28"/>
+      <c r="W37" s="28"/>
+      <c r="X37" s="28"/>
+      <c r="Y37" s="28"/>
+      <c r="Z37" s="28"/>
+      <c r="AA37" s="28"/>
+      <c r="AB37" s="28"/>
+      <c r="AC37" s="28"/>
+      <c r="AD37" s="28"/>
+      <c r="AE37" s="28"/>
+      <c r="AF37" s="28"/>
+      <c r="AG37" s="28"/>
+      <c r="BR37" s="16"/>
       <c r="BT37" s="6"/>
       <c r="BU37" s="6"/>
       <c r="BV37" s="6"/>
@@ -3512,36 +3516,36 @@
       <c r="BZ37" s="6"/>
     </row>
     <row r="38" spans="2:78" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B38" s="31"/>
-      <c r="E38" s="13"/>
-      <c r="F38" s="13"/>
-      <c r="G38" s="13"/>
-      <c r="H38" s="13"/>
-      <c r="I38" s="13"/>
-      <c r="J38" s="13"/>
-      <c r="K38" s="13"/>
-      <c r="L38" s="13"/>
-      <c r="M38" s="13"/>
-      <c r="N38" s="13"/>
-      <c r="O38" s="13"/>
-      <c r="P38" s="13"/>
-      <c r="Q38" s="13"/>
-      <c r="R38" s="13"/>
-      <c r="T38" s="13"/>
-      <c r="U38" s="13"/>
-      <c r="V38" s="13"/>
-      <c r="W38" s="13"/>
-      <c r="X38" s="13"/>
-      <c r="Y38" s="13"/>
-      <c r="Z38" s="13"/>
-      <c r="AA38" s="13"/>
-      <c r="AB38" s="13"/>
-      <c r="AC38" s="13"/>
-      <c r="AD38" s="13"/>
-      <c r="AE38" s="13"/>
-      <c r="AF38" s="13"/>
-      <c r="AG38" s="13"/>
-      <c r="BR38" s="31"/>
+      <c r="B38" s="16"/>
+      <c r="E38" s="28"/>
+      <c r="F38" s="28"/>
+      <c r="G38" s="28"/>
+      <c r="H38" s="28"/>
+      <c r="I38" s="28"/>
+      <c r="J38" s="28"/>
+      <c r="K38" s="28"/>
+      <c r="L38" s="28"/>
+      <c r="M38" s="28"/>
+      <c r="N38" s="28"/>
+      <c r="O38" s="28"/>
+      <c r="P38" s="28"/>
+      <c r="Q38" s="28"/>
+      <c r="R38" s="28"/>
+      <c r="T38" s="28"/>
+      <c r="U38" s="28"/>
+      <c r="V38" s="28"/>
+      <c r="W38" s="28"/>
+      <c r="X38" s="28"/>
+      <c r="Y38" s="28"/>
+      <c r="Z38" s="28"/>
+      <c r="AA38" s="28"/>
+      <c r="AB38" s="28"/>
+      <c r="AC38" s="28"/>
+      <c r="AD38" s="28"/>
+      <c r="AE38" s="28"/>
+      <c r="AF38" s="28"/>
+      <c r="AG38" s="28"/>
+      <c r="BR38" s="16"/>
       <c r="BT38" s="6"/>
       <c r="BU38" s="6"/>
       <c r="BV38" s="6"/>
@@ -3551,69 +3555,69 @@
       <c r="BZ38" s="6"/>
     </row>
     <row r="39" spans="2:78" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B39" s="31"/>
-      <c r="E39" s="13"/>
-      <c r="F39" s="13"/>
-      <c r="G39" s="13"/>
-      <c r="H39" s="13"/>
-      <c r="I39" s="13"/>
-      <c r="J39" s="13"/>
-      <c r="K39" s="13"/>
-      <c r="L39" s="13"/>
-      <c r="M39" s="13"/>
-      <c r="N39" s="13"/>
-      <c r="O39" s="13"/>
-      <c r="P39" s="13"/>
-      <c r="Q39" s="13"/>
-      <c r="R39" s="13"/>
-      <c r="T39" s="13"/>
-      <c r="U39" s="13"/>
-      <c r="V39" s="13"/>
-      <c r="W39" s="13"/>
-      <c r="X39" s="13"/>
-      <c r="Y39" s="13"/>
-      <c r="Z39" s="13"/>
-      <c r="AA39" s="13"/>
-      <c r="AB39" s="13"/>
-      <c r="AC39" s="13"/>
-      <c r="AD39" s="13"/>
-      <c r="AE39" s="13"/>
-      <c r="AF39" s="13"/>
-      <c r="AG39" s="13"/>
+      <c r="B39" s="16"/>
+      <c r="E39" s="28"/>
+      <c r="F39" s="28"/>
+      <c r="G39" s="28"/>
+      <c r="H39" s="28"/>
+      <c r="I39" s="28"/>
+      <c r="J39" s="28"/>
+      <c r="K39" s="28"/>
+      <c r="L39" s="28"/>
+      <c r="M39" s="28"/>
+      <c r="N39" s="28"/>
+      <c r="O39" s="28"/>
+      <c r="P39" s="28"/>
+      <c r="Q39" s="28"/>
+      <c r="R39" s="28"/>
+      <c r="T39" s="28"/>
+      <c r="U39" s="28"/>
+      <c r="V39" s="28"/>
+      <c r="W39" s="28"/>
+      <c r="X39" s="28"/>
+      <c r="Y39" s="28"/>
+      <c r="Z39" s="28"/>
+      <c r="AA39" s="28"/>
+      <c r="AB39" s="28"/>
+      <c r="AC39" s="28"/>
+      <c r="AD39" s="28"/>
+      <c r="AE39" s="28"/>
+      <c r="AF39" s="28"/>
+      <c r="AG39" s="28"/>
       <c r="AW39" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="AX39" s="14" t="s">
+      <c r="AX39" s="12" t="s">
         <v>176</v>
       </c>
-      <c r="AY39" s="15"/>
-      <c r="AZ39" s="16"/>
-      <c r="BA39" s="14" t="s">
+      <c r="AY39" s="13"/>
+      <c r="AZ39" s="14"/>
+      <c r="BA39" s="12" t="s">
         <v>177</v>
       </c>
-      <c r="BB39" s="15"/>
-      <c r="BC39" s="15"/>
-      <c r="BD39" s="15"/>
-      <c r="BE39" s="15"/>
-      <c r="BF39" s="15"/>
-      <c r="BG39" s="15"/>
-      <c r="BH39" s="16"/>
-      <c r="BI39" s="14" t="s">
+      <c r="BB39" s="13"/>
+      <c r="BC39" s="13"/>
+      <c r="BD39" s="13"/>
+      <c r="BE39" s="13"/>
+      <c r="BF39" s="13"/>
+      <c r="BG39" s="13"/>
+      <c r="BH39" s="14"/>
+      <c r="BI39" s="12" t="s">
         <v>178</v>
       </c>
-      <c r="BJ39" s="15"/>
-      <c r="BK39" s="16"/>
-      <c r="BL39" s="14" t="s">
+      <c r="BJ39" s="13"/>
+      <c r="BK39" s="14"/>
+      <c r="BL39" s="12" t="s">
         <v>179</v>
       </c>
-      <c r="BM39" s="15"/>
-      <c r="BN39" s="16"/>
-      <c r="BO39" s="14" t="s">
+      <c r="BM39" s="13"/>
+      <c r="BN39" s="14"/>
+      <c r="BO39" s="12" t="s">
         <v>180</v>
       </c>
-      <c r="BP39" s="15"/>
-      <c r="BQ39" s="16"/>
-      <c r="BR39" s="31"/>
+      <c r="BP39" s="13"/>
+      <c r="BQ39" s="14"/>
+      <c r="BR39" s="16"/>
       <c r="BT39" s="6"/>
       <c r="BU39" s="6"/>
       <c r="BV39" s="6"/>
@@ -3623,41 +3627,41 @@
       <c r="BZ39" s="6"/>
     </row>
     <row r="40" spans="2:78" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B40" s="31"/>
+      <c r="B40" s="16"/>
       <c r="AW40" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="AX40" s="14" t="s">
+      <c r="AX40" s="12" t="s">
         <v>182</v>
       </c>
-      <c r="AY40" s="15"/>
-      <c r="AZ40" s="16"/>
-      <c r="BA40" s="14" t="s">
+      <c r="AY40" s="13"/>
+      <c r="AZ40" s="14"/>
+      <c r="BA40" s="12" t="s">
         <v>183</v>
       </c>
-      <c r="BB40" s="15"/>
-      <c r="BC40" s="15"/>
-      <c r="BD40" s="15"/>
-      <c r="BE40" s="15"/>
-      <c r="BF40" s="15"/>
-      <c r="BG40" s="15"/>
-      <c r="BH40" s="16"/>
-      <c r="BI40" s="14" t="s">
+      <c r="BB40" s="13"/>
+      <c r="BC40" s="13"/>
+      <c r="BD40" s="13"/>
+      <c r="BE40" s="13"/>
+      <c r="BF40" s="13"/>
+      <c r="BG40" s="13"/>
+      <c r="BH40" s="14"/>
+      <c r="BI40" s="12" t="s">
         <v>184</v>
       </c>
-      <c r="BJ40" s="15"/>
-      <c r="BK40" s="16"/>
-      <c r="BL40" s="14" t="s">
+      <c r="BJ40" s="13"/>
+      <c r="BK40" s="14"/>
+      <c r="BL40" s="12" t="s">
         <v>185</v>
       </c>
-      <c r="BM40" s="15"/>
-      <c r="BN40" s="16"/>
-      <c r="BO40" s="14" t="s">
+      <c r="BM40" s="13"/>
+      <c r="BN40" s="14"/>
+      <c r="BO40" s="12" t="s">
         <v>186</v>
       </c>
-      <c r="BP40" s="15"/>
-      <c r="BQ40" s="16"/>
-      <c r="BR40" s="31"/>
+      <c r="BP40" s="13"/>
+      <c r="BQ40" s="14"/>
+      <c r="BR40" s="16"/>
       <c r="BT40" s="6"/>
       <c r="BU40" s="6"/>
       <c r="BV40" s="6"/>
@@ -3667,41 +3671,41 @@
       <c r="BZ40" s="6"/>
     </row>
     <row r="41" spans="2:78" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B41" s="31"/>
+      <c r="B41" s="16"/>
       <c r="AW41" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="AX41" s="14" t="s">
+      <c r="AX41" s="12" t="s">
         <v>188</v>
       </c>
-      <c r="AY41" s="15"/>
-      <c r="AZ41" s="16"/>
-      <c r="BA41" s="14" t="s">
+      <c r="AY41" s="13"/>
+      <c r="AZ41" s="14"/>
+      <c r="BA41" s="12" t="s">
         <v>189</v>
       </c>
-      <c r="BB41" s="15"/>
-      <c r="BC41" s="15"/>
-      <c r="BD41" s="15"/>
-      <c r="BE41" s="15"/>
-      <c r="BF41" s="15"/>
-      <c r="BG41" s="15"/>
-      <c r="BH41" s="16"/>
-      <c r="BI41" s="14" t="s">
+      <c r="BB41" s="13"/>
+      <c r="BC41" s="13"/>
+      <c r="BD41" s="13"/>
+      <c r="BE41" s="13"/>
+      <c r="BF41" s="13"/>
+      <c r="BG41" s="13"/>
+      <c r="BH41" s="14"/>
+      <c r="BI41" s="12" t="s">
         <v>190</v>
       </c>
-      <c r="BJ41" s="15"/>
-      <c r="BK41" s="16"/>
-      <c r="BL41" s="14" t="s">
+      <c r="BJ41" s="13"/>
+      <c r="BK41" s="14"/>
+      <c r="BL41" s="12" t="s">
         <v>191</v>
       </c>
-      <c r="BM41" s="15"/>
-      <c r="BN41" s="16"/>
-      <c r="BO41" s="14" t="s">
+      <c r="BM41" s="13"/>
+      <c r="BN41" s="14"/>
+      <c r="BO41" s="12" t="s">
         <v>192</v>
       </c>
-      <c r="BP41" s="15"/>
-      <c r="BQ41" s="16"/>
-      <c r="BR41" s="31"/>
+      <c r="BP41" s="13"/>
+      <c r="BQ41" s="14"/>
+      <c r="BR41" s="16"/>
       <c r="BT41" s="6"/>
       <c r="BU41" s="6"/>
       <c r="BV41" s="6"/>
@@ -3711,41 +3715,41 @@
       <c r="BZ41" s="6"/>
     </row>
     <row r="42" spans="2:78" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B42" s="31"/>
+      <c r="B42" s="16"/>
       <c r="AW42" s="5" t="s">
         <v>193</v>
       </c>
-      <c r="AX42" s="14" t="s">
+      <c r="AX42" s="12" t="s">
         <v>194</v>
       </c>
-      <c r="AY42" s="15"/>
-      <c r="AZ42" s="16"/>
-      <c r="BA42" s="14" t="s">
+      <c r="AY42" s="13"/>
+      <c r="AZ42" s="14"/>
+      <c r="BA42" s="12" t="s">
         <v>195</v>
       </c>
-      <c r="BB42" s="15"/>
-      <c r="BC42" s="15"/>
-      <c r="BD42" s="15"/>
-      <c r="BE42" s="15"/>
-      <c r="BF42" s="15"/>
-      <c r="BG42" s="15"/>
-      <c r="BH42" s="16"/>
-      <c r="BI42" s="14" t="s">
+      <c r="BB42" s="13"/>
+      <c r="BC42" s="13"/>
+      <c r="BD42" s="13"/>
+      <c r="BE42" s="13"/>
+      <c r="BF42" s="13"/>
+      <c r="BG42" s="13"/>
+      <c r="BH42" s="14"/>
+      <c r="BI42" s="12" t="s">
         <v>196</v>
       </c>
-      <c r="BJ42" s="15"/>
-      <c r="BK42" s="16"/>
-      <c r="BL42" s="14" t="s">
+      <c r="BJ42" s="13"/>
+      <c r="BK42" s="14"/>
+      <c r="BL42" s="12" t="s">
         <v>197</v>
       </c>
-      <c r="BM42" s="15"/>
-      <c r="BN42" s="16"/>
-      <c r="BO42" s="14" t="s">
+      <c r="BM42" s="13"/>
+      <c r="BN42" s="14"/>
+      <c r="BO42" s="12" t="s">
         <v>198</v>
       </c>
-      <c r="BP42" s="15"/>
-      <c r="BQ42" s="16"/>
-      <c r="BR42" s="31"/>
+      <c r="BP42" s="13"/>
+      <c r="BQ42" s="14"/>
+      <c r="BR42" s="16"/>
       <c r="BT42" s="6"/>
       <c r="BU42" s="6"/>
       <c r="BV42" s="6"/>
@@ -3755,41 +3759,41 @@
       <c r="BZ42" s="6"/>
     </row>
     <row r="43" spans="2:78" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B43" s="27"/>
-      <c r="AW43" s="26" t="s">
+      <c r="B43" s="17"/>
+      <c r="AW43" s="15" t="s">
         <v>199</v>
       </c>
-      <c r="AX43" s="17" t="s">
+      <c r="AX43" s="18" t="s">
         <v>200</v>
       </c>
-      <c r="AY43" s="18"/>
-      <c r="AZ43" s="19"/>
-      <c r="BA43" s="17" t="s">
+      <c r="AY43" s="19"/>
+      <c r="AZ43" s="20"/>
+      <c r="BA43" s="18" t="s">
         <v>201</v>
       </c>
-      <c r="BB43" s="18"/>
-      <c r="BC43" s="18"/>
-      <c r="BD43" s="18"/>
-      <c r="BE43" s="18"/>
-      <c r="BF43" s="18"/>
-      <c r="BG43" s="18"/>
-      <c r="BH43" s="19"/>
-      <c r="BI43" s="17" t="s">
+      <c r="BB43" s="19"/>
+      <c r="BC43" s="19"/>
+      <c r="BD43" s="19"/>
+      <c r="BE43" s="19"/>
+      <c r="BF43" s="19"/>
+      <c r="BG43" s="19"/>
+      <c r="BH43" s="20"/>
+      <c r="BI43" s="18" t="s">
         <v>202</v>
       </c>
-      <c r="BJ43" s="18"/>
-      <c r="BK43" s="19"/>
-      <c r="BL43" s="17" t="s">
+      <c r="BJ43" s="19"/>
+      <c r="BK43" s="20"/>
+      <c r="BL43" s="18" t="s">
         <v>203</v>
       </c>
-      <c r="BM43" s="18"/>
-      <c r="BN43" s="19"/>
-      <c r="BO43" s="17" t="s">
+      <c r="BM43" s="19"/>
+      <c r="BN43" s="20"/>
+      <c r="BO43" s="18" t="s">
         <v>204</v>
       </c>
-      <c r="BP43" s="18"/>
-      <c r="BQ43" s="19"/>
-      <c r="BR43" s="27"/>
+      <c r="BP43" s="19"/>
+      <c r="BQ43" s="20"/>
+      <c r="BR43" s="17"/>
       <c r="BT43" s="6"/>
       <c r="BU43" s="6"/>
       <c r="BV43" s="6"/>
@@ -3799,31 +3803,31 @@
       <c r="BZ43" s="6"/>
     </row>
     <row r="44" spans="2:78" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B44" s="26" t="s">
+      <c r="B44" s="15" t="s">
         <v>205</v>
       </c>
-      <c r="AW44" s="27"/>
-      <c r="AX44" s="20"/>
-      <c r="AY44" s="21"/>
-      <c r="AZ44" s="22"/>
-      <c r="BA44" s="20"/>
-      <c r="BB44" s="21"/>
-      <c r="BC44" s="21"/>
-      <c r="BD44" s="21"/>
-      <c r="BE44" s="21"/>
-      <c r="BF44" s="21"/>
-      <c r="BG44" s="21"/>
-      <c r="BH44" s="22"/>
-      <c r="BI44" s="20"/>
-      <c r="BJ44" s="21"/>
-      <c r="BK44" s="22"/>
-      <c r="BL44" s="20"/>
-      <c r="BM44" s="21"/>
-      <c r="BN44" s="22"/>
-      <c r="BO44" s="20"/>
-      <c r="BP44" s="21"/>
-      <c r="BQ44" s="22"/>
-      <c r="BR44" s="26" t="s">
+      <c r="AW44" s="17"/>
+      <c r="AX44" s="21"/>
+      <c r="AY44" s="22"/>
+      <c r="AZ44" s="23"/>
+      <c r="BA44" s="21"/>
+      <c r="BB44" s="22"/>
+      <c r="BC44" s="22"/>
+      <c r="BD44" s="22"/>
+      <c r="BE44" s="22"/>
+      <c r="BF44" s="22"/>
+      <c r="BG44" s="22"/>
+      <c r="BH44" s="23"/>
+      <c r="BI44" s="21"/>
+      <c r="BJ44" s="22"/>
+      <c r="BK44" s="23"/>
+      <c r="BL44" s="21"/>
+      <c r="BM44" s="22"/>
+      <c r="BN44" s="23"/>
+      <c r="BO44" s="21"/>
+      <c r="BP44" s="22"/>
+      <c r="BQ44" s="23"/>
+      <c r="BR44" s="15" t="s">
         <v>205</v>
       </c>
       <c r="BT44" s="6"/>
@@ -3835,41 +3839,41 @@
       <c r="BZ44" s="6"/>
     </row>
     <row r="45" spans="2:78" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B45" s="31"/>
+      <c r="B45" s="16"/>
       <c r="AW45" s="5" t="s">
         <v>206</v>
       </c>
-      <c r="AX45" s="14" t="s">
+      <c r="AX45" s="12" t="s">
         <v>207</v>
       </c>
-      <c r="AY45" s="15"/>
-      <c r="AZ45" s="16"/>
-      <c r="BA45" s="14" t="s">
+      <c r="AY45" s="13"/>
+      <c r="AZ45" s="14"/>
+      <c r="BA45" s="12" t="s">
         <v>208</v>
       </c>
-      <c r="BB45" s="15"/>
-      <c r="BC45" s="15"/>
-      <c r="BD45" s="15"/>
-      <c r="BE45" s="15"/>
-      <c r="BF45" s="15"/>
-      <c r="BG45" s="15"/>
-      <c r="BH45" s="16"/>
-      <c r="BI45" s="14" t="s">
+      <c r="BB45" s="13"/>
+      <c r="BC45" s="13"/>
+      <c r="BD45" s="13"/>
+      <c r="BE45" s="13"/>
+      <c r="BF45" s="13"/>
+      <c r="BG45" s="13"/>
+      <c r="BH45" s="14"/>
+      <c r="BI45" s="12" t="s">
         <v>209</v>
       </c>
-      <c r="BJ45" s="15"/>
-      <c r="BK45" s="16"/>
-      <c r="BL45" s="14" t="s">
+      <c r="BJ45" s="13"/>
+      <c r="BK45" s="14"/>
+      <c r="BL45" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="BM45" s="15"/>
-      <c r="BN45" s="16"/>
-      <c r="BO45" s="14" t="s">
+      <c r="BM45" s="13"/>
+      <c r="BN45" s="14"/>
+      <c r="BO45" s="12" t="s">
         <v>211</v>
       </c>
-      <c r="BP45" s="15"/>
-      <c r="BQ45" s="16"/>
-      <c r="BR45" s="31"/>
+      <c r="BP45" s="13"/>
+      <c r="BQ45" s="14"/>
+      <c r="BR45" s="16"/>
       <c r="BT45" s="6"/>
       <c r="BU45" s="6"/>
       <c r="BV45" s="6"/>
@@ -3879,35 +3883,35 @@
       <c r="BZ45" s="6"/>
     </row>
     <row r="46" spans="2:78" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B46" s="31"/>
-      <c r="AW46" s="14" t="s">
+      <c r="B46" s="16"/>
+      <c r="AW46" s="12" t="s">
         <v>212</v>
       </c>
-      <c r="AX46" s="15"/>
-      <c r="AY46" s="15"/>
-      <c r="AZ46" s="16"/>
-      <c r="BA46" s="14" t="s">
+      <c r="AX46" s="13"/>
+      <c r="AY46" s="13"/>
+      <c r="AZ46" s="14"/>
+      <c r="BA46" s="12" t="s">
         <v>213</v>
       </c>
-      <c r="BB46" s="15"/>
-      <c r="BC46" s="15"/>
-      <c r="BD46" s="15"/>
-      <c r="BE46" s="15"/>
-      <c r="BF46" s="15"/>
-      <c r="BG46" s="15"/>
-      <c r="BH46" s="16"/>
-      <c r="BI46" s="14" t="s">
+      <c r="BB46" s="13"/>
+      <c r="BC46" s="13"/>
+      <c r="BD46" s="13"/>
+      <c r="BE46" s="13"/>
+      <c r="BF46" s="13"/>
+      <c r="BG46" s="13"/>
+      <c r="BH46" s="14"/>
+      <c r="BI46" s="12" t="s">
         <v>214</v>
       </c>
-      <c r="BJ46" s="15"/>
-      <c r="BK46" s="15"/>
-      <c r="BL46" s="15"/>
-      <c r="BM46" s="15"/>
-      <c r="BN46" s="15"/>
-      <c r="BO46" s="15"/>
-      <c r="BP46" s="15"/>
-      <c r="BQ46" s="16"/>
-      <c r="BR46" s="31"/>
+      <c r="BJ46" s="13"/>
+      <c r="BK46" s="13"/>
+      <c r="BL46" s="13"/>
+      <c r="BM46" s="13"/>
+      <c r="BN46" s="13"/>
+      <c r="BO46" s="13"/>
+      <c r="BP46" s="13"/>
+      <c r="BQ46" s="14"/>
+      <c r="BR46" s="16"/>
       <c r="BT46" s="6"/>
       <c r="BU46" s="6"/>
       <c r="BV46" s="6"/>
@@ -3917,67 +3921,67 @@
       <c r="BZ46" s="6"/>
     </row>
     <row r="47" spans="2:78" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B47" s="31"/>
-      <c r="E47" s="12" t="s">
+      <c r="B47" s="16"/>
+      <c r="E47" s="27" t="s">
         <v>236</v>
       </c>
-      <c r="F47" s="13"/>
-      <c r="G47" s="13"/>
-      <c r="H47" s="13"/>
-      <c r="I47" s="13"/>
-      <c r="J47" s="13"/>
-      <c r="K47" s="13"/>
-      <c r="L47" s="13"/>
-      <c r="M47" s="13"/>
-      <c r="N47" s="13"/>
-      <c r="O47" s="13"/>
-      <c r="P47" s="13"/>
-      <c r="Q47" s="13"/>
-      <c r="R47" s="13"/>
-      <c r="T47" s="12" t="s">
+      <c r="F47" s="28"/>
+      <c r="G47" s="28"/>
+      <c r="H47" s="28"/>
+      <c r="I47" s="28"/>
+      <c r="J47" s="28"/>
+      <c r="K47" s="28"/>
+      <c r="L47" s="28"/>
+      <c r="M47" s="28"/>
+      <c r="N47" s="28"/>
+      <c r="O47" s="28"/>
+      <c r="P47" s="28"/>
+      <c r="Q47" s="28"/>
+      <c r="R47" s="28"/>
+      <c r="T47" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="U47" s="13"/>
-      <c r="V47" s="13"/>
-      <c r="W47" s="13"/>
-      <c r="X47" s="13"/>
-      <c r="Y47" s="13"/>
-      <c r="Z47" s="13"/>
-      <c r="AA47" s="13"/>
-      <c r="AB47" s="13"/>
-      <c r="AC47" s="13"/>
-      <c r="AD47" s="13"/>
-      <c r="AE47" s="13"/>
-      <c r="AF47" s="13"/>
-      <c r="AG47" s="13"/>
-      <c r="AW47" s="14" t="s">
+      <c r="U47" s="28"/>
+      <c r="V47" s="28"/>
+      <c r="W47" s="28"/>
+      <c r="X47" s="28"/>
+      <c r="Y47" s="28"/>
+      <c r="Z47" s="28"/>
+      <c r="AA47" s="28"/>
+      <c r="AB47" s="28"/>
+      <c r="AC47" s="28"/>
+      <c r="AD47" s="28"/>
+      <c r="AE47" s="28"/>
+      <c r="AF47" s="28"/>
+      <c r="AG47" s="28"/>
+      <c r="AW47" s="12" t="s">
         <v>215</v>
       </c>
-      <c r="AX47" s="15"/>
-      <c r="AY47" s="15"/>
-      <c r="AZ47" s="16"/>
-      <c r="BA47" s="14" t="s">
+      <c r="AX47" s="13"/>
+      <c r="AY47" s="13"/>
+      <c r="AZ47" s="14"/>
+      <c r="BA47" s="12" t="s">
         <v>216</v>
       </c>
-      <c r="BB47" s="15"/>
-      <c r="BC47" s="15"/>
-      <c r="BD47" s="15"/>
-      <c r="BE47" s="15"/>
-      <c r="BF47" s="15"/>
-      <c r="BG47" s="15"/>
-      <c r="BH47" s="16"/>
-      <c r="BI47" s="14" t="s">
+      <c r="BB47" s="13"/>
+      <c r="BC47" s="13"/>
+      <c r="BD47" s="13"/>
+      <c r="BE47" s="13"/>
+      <c r="BF47" s="13"/>
+      <c r="BG47" s="13"/>
+      <c r="BH47" s="14"/>
+      <c r="BI47" s="12" t="s">
         <v>217</v>
       </c>
-      <c r="BJ47" s="15"/>
-      <c r="BK47" s="15"/>
-      <c r="BL47" s="15"/>
-      <c r="BM47" s="15"/>
-      <c r="BN47" s="15"/>
-      <c r="BO47" s="15"/>
-      <c r="BP47" s="15"/>
-      <c r="BQ47" s="16"/>
-      <c r="BR47" s="31"/>
+      <c r="BJ47" s="13"/>
+      <c r="BK47" s="13"/>
+      <c r="BL47" s="13"/>
+      <c r="BM47" s="13"/>
+      <c r="BN47" s="13"/>
+      <c r="BO47" s="13"/>
+      <c r="BP47" s="13"/>
+      <c r="BQ47" s="14"/>
+      <c r="BR47" s="16"/>
       <c r="BT47" s="6"/>
       <c r="BU47" s="6"/>
       <c r="BV47" s="6"/>
@@ -3987,61 +3991,61 @@
       <c r="BZ47" s="6"/>
     </row>
     <row r="48" spans="2:78" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B48" s="31"/>
-      <c r="E48" s="13"/>
-      <c r="F48" s="13"/>
-      <c r="G48" s="13"/>
-      <c r="H48" s="13"/>
-      <c r="I48" s="13"/>
-      <c r="J48" s="13"/>
-      <c r="K48" s="13"/>
-      <c r="L48" s="13"/>
-      <c r="M48" s="13"/>
-      <c r="N48" s="13"/>
-      <c r="O48" s="13"/>
-      <c r="P48" s="13"/>
-      <c r="Q48" s="13"/>
-      <c r="R48" s="13"/>
-      <c r="T48" s="13"/>
-      <c r="U48" s="13"/>
-      <c r="V48" s="13"/>
-      <c r="W48" s="13"/>
-      <c r="X48" s="13"/>
-      <c r="Y48" s="13"/>
-      <c r="Z48" s="13"/>
-      <c r="AA48" s="13"/>
-      <c r="AB48" s="13"/>
-      <c r="AC48" s="13"/>
-      <c r="AD48" s="13"/>
-      <c r="AE48" s="13"/>
-      <c r="AF48" s="13"/>
-      <c r="AG48" s="13"/>
-      <c r="AW48" s="17" t="s">
+      <c r="B48" s="16"/>
+      <c r="E48" s="28"/>
+      <c r="F48" s="28"/>
+      <c r="G48" s="28"/>
+      <c r="H48" s="28"/>
+      <c r="I48" s="28"/>
+      <c r="J48" s="28"/>
+      <c r="K48" s="28"/>
+      <c r="L48" s="28"/>
+      <c r="M48" s="28"/>
+      <c r="N48" s="28"/>
+      <c r="O48" s="28"/>
+      <c r="P48" s="28"/>
+      <c r="Q48" s="28"/>
+      <c r="R48" s="28"/>
+      <c r="T48" s="28"/>
+      <c r="U48" s="28"/>
+      <c r="V48" s="28"/>
+      <c r="W48" s="28"/>
+      <c r="X48" s="28"/>
+      <c r="Y48" s="28"/>
+      <c r="Z48" s="28"/>
+      <c r="AA48" s="28"/>
+      <c r="AB48" s="28"/>
+      <c r="AC48" s="28"/>
+      <c r="AD48" s="28"/>
+      <c r="AE48" s="28"/>
+      <c r="AF48" s="28"/>
+      <c r="AG48" s="28"/>
+      <c r="AW48" s="18" t="s">
         <v>218</v>
       </c>
-      <c r="AX48" s="18"/>
-      <c r="AY48" s="18"/>
-      <c r="AZ48" s="18"/>
-      <c r="BA48" s="18"/>
-      <c r="BB48" s="18"/>
-      <c r="BC48" s="18"/>
-      <c r="BD48" s="19"/>
-      <c r="BE48" s="17" t="s">
+      <c r="AX48" s="19"/>
+      <c r="AY48" s="19"/>
+      <c r="AZ48" s="19"/>
+      <c r="BA48" s="19"/>
+      <c r="BB48" s="19"/>
+      <c r="BC48" s="19"/>
+      <c r="BD48" s="20"/>
+      <c r="BE48" s="18" t="s">
         <v>219</v>
       </c>
-      <c r="BF48" s="18"/>
-      <c r="BG48" s="18"/>
-      <c r="BH48" s="18"/>
-      <c r="BI48" s="18"/>
-      <c r="BJ48" s="18"/>
-      <c r="BK48" s="18"/>
-      <c r="BL48" s="18"/>
-      <c r="BM48" s="18"/>
-      <c r="BN48" s="18"/>
-      <c r="BO48" s="18"/>
-      <c r="BP48" s="18"/>
-      <c r="BQ48" s="19"/>
-      <c r="BR48" s="31"/>
+      <c r="BF48" s="19"/>
+      <c r="BG48" s="19"/>
+      <c r="BH48" s="19"/>
+      <c r="BI48" s="19"/>
+      <c r="BJ48" s="19"/>
+      <c r="BK48" s="19"/>
+      <c r="BL48" s="19"/>
+      <c r="BM48" s="19"/>
+      <c r="BN48" s="19"/>
+      <c r="BO48" s="19"/>
+      <c r="BP48" s="19"/>
+      <c r="BQ48" s="20"/>
+      <c r="BR48" s="16"/>
       <c r="BT48" s="6"/>
       <c r="BU48" s="6"/>
       <c r="BV48" s="6"/>
@@ -4051,59 +4055,59 @@
       <c r="BZ48" s="6"/>
     </row>
     <row r="49" spans="1:78" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B49" s="31"/>
-      <c r="E49" s="13"/>
-      <c r="F49" s="13"/>
-      <c r="G49" s="13"/>
-      <c r="H49" s="13"/>
-      <c r="I49" s="13"/>
-      <c r="J49" s="13"/>
-      <c r="K49" s="13"/>
-      <c r="L49" s="13"/>
-      <c r="M49" s="13"/>
-      <c r="N49" s="13"/>
-      <c r="O49" s="13"/>
-      <c r="P49" s="13"/>
-      <c r="Q49" s="13"/>
-      <c r="R49" s="13"/>
-      <c r="T49" s="13"/>
-      <c r="U49" s="13"/>
-      <c r="V49" s="13"/>
-      <c r="W49" s="13"/>
-      <c r="X49" s="13"/>
-      <c r="Y49" s="13"/>
-      <c r="Z49" s="13"/>
-      <c r="AA49" s="13"/>
-      <c r="AB49" s="13"/>
-      <c r="AC49" s="13"/>
-      <c r="AD49" s="13"/>
-      <c r="AE49" s="13"/>
-      <c r="AF49" s="13"/>
-      <c r="AG49" s="13"/>
-      <c r="AW49" s="23" t="s">
+      <c r="B49" s="16"/>
+      <c r="E49" s="28"/>
+      <c r="F49" s="28"/>
+      <c r="G49" s="28"/>
+      <c r="H49" s="28"/>
+      <c r="I49" s="28"/>
+      <c r="J49" s="28"/>
+      <c r="K49" s="28"/>
+      <c r="L49" s="28"/>
+      <c r="M49" s="28"/>
+      <c r="N49" s="28"/>
+      <c r="O49" s="28"/>
+      <c r="P49" s="28"/>
+      <c r="Q49" s="28"/>
+      <c r="R49" s="28"/>
+      <c r="T49" s="28"/>
+      <c r="U49" s="28"/>
+      <c r="V49" s="28"/>
+      <c r="W49" s="28"/>
+      <c r="X49" s="28"/>
+      <c r="Y49" s="28"/>
+      <c r="Z49" s="28"/>
+      <c r="AA49" s="28"/>
+      <c r="AB49" s="28"/>
+      <c r="AC49" s="28"/>
+      <c r="AD49" s="28"/>
+      <c r="AE49" s="28"/>
+      <c r="AF49" s="28"/>
+      <c r="AG49" s="28"/>
+      <c r="AW49" s="24" t="s">
         <v>220</v>
       </c>
-      <c r="AX49" s="24"/>
-      <c r="AY49" s="24"/>
-      <c r="AZ49" s="24"/>
-      <c r="BA49" s="24"/>
-      <c r="BB49" s="24"/>
-      <c r="BC49" s="24"/>
-      <c r="BD49" s="25"/>
-      <c r="BE49" s="20"/>
-      <c r="BF49" s="21"/>
-      <c r="BG49" s="21"/>
-      <c r="BH49" s="21"/>
-      <c r="BI49" s="21"/>
-      <c r="BJ49" s="21"/>
-      <c r="BK49" s="21"/>
-      <c r="BL49" s="21"/>
-      <c r="BM49" s="21"/>
-      <c r="BN49" s="21"/>
-      <c r="BO49" s="21"/>
-      <c r="BP49" s="21"/>
-      <c r="BQ49" s="22"/>
-      <c r="BR49" s="31"/>
+      <c r="AX49" s="25"/>
+      <c r="AY49" s="25"/>
+      <c r="AZ49" s="25"/>
+      <c r="BA49" s="25"/>
+      <c r="BB49" s="25"/>
+      <c r="BC49" s="25"/>
+      <c r="BD49" s="26"/>
+      <c r="BE49" s="21"/>
+      <c r="BF49" s="22"/>
+      <c r="BG49" s="22"/>
+      <c r="BH49" s="22"/>
+      <c r="BI49" s="22"/>
+      <c r="BJ49" s="22"/>
+      <c r="BK49" s="22"/>
+      <c r="BL49" s="22"/>
+      <c r="BM49" s="22"/>
+      <c r="BN49" s="22"/>
+      <c r="BO49" s="22"/>
+      <c r="BP49" s="22"/>
+      <c r="BQ49" s="23"/>
+      <c r="BR49" s="16"/>
       <c r="BT49" s="6"/>
       <c r="BU49" s="6"/>
       <c r="BV49" s="6"/>
@@ -4113,59 +4117,59 @@
       <c r="BZ49" s="6"/>
     </row>
     <row r="50" spans="1:78" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B50" s="31"/>
-      <c r="E50" s="13"/>
-      <c r="F50" s="13"/>
-      <c r="G50" s="13"/>
-      <c r="H50" s="13"/>
-      <c r="I50" s="13"/>
-      <c r="J50" s="13"/>
-      <c r="K50" s="13"/>
-      <c r="L50" s="13"/>
-      <c r="M50" s="13"/>
-      <c r="N50" s="13"/>
-      <c r="O50" s="13"/>
-      <c r="P50" s="13"/>
-      <c r="Q50" s="13"/>
-      <c r="R50" s="13"/>
-      <c r="T50" s="13"/>
-      <c r="U50" s="13"/>
-      <c r="V50" s="13"/>
-      <c r="W50" s="13"/>
-      <c r="X50" s="13"/>
-      <c r="Y50" s="13"/>
-      <c r="Z50" s="13"/>
-      <c r="AA50" s="13"/>
-      <c r="AB50" s="13"/>
-      <c r="AC50" s="13"/>
-      <c r="AD50" s="13"/>
-      <c r="AE50" s="13"/>
-      <c r="AF50" s="13"/>
-      <c r="AG50" s="13"/>
-      <c r="AW50" s="23"/>
-      <c r="AX50" s="24"/>
-      <c r="AY50" s="24"/>
-      <c r="AZ50" s="24"/>
-      <c r="BA50" s="24"/>
-      <c r="BB50" s="24"/>
-      <c r="BC50" s="24"/>
-      <c r="BD50" s="25"/>
-      <c r="BE50" s="17" t="s">
+      <c r="B50" s="16"/>
+      <c r="E50" s="28"/>
+      <c r="F50" s="28"/>
+      <c r="G50" s="28"/>
+      <c r="H50" s="28"/>
+      <c r="I50" s="28"/>
+      <c r="J50" s="28"/>
+      <c r="K50" s="28"/>
+      <c r="L50" s="28"/>
+      <c r="M50" s="28"/>
+      <c r="N50" s="28"/>
+      <c r="O50" s="28"/>
+      <c r="P50" s="28"/>
+      <c r="Q50" s="28"/>
+      <c r="R50" s="28"/>
+      <c r="T50" s="28"/>
+      <c r="U50" s="28"/>
+      <c r="V50" s="28"/>
+      <c r="W50" s="28"/>
+      <c r="X50" s="28"/>
+      <c r="Y50" s="28"/>
+      <c r="Z50" s="28"/>
+      <c r="AA50" s="28"/>
+      <c r="AB50" s="28"/>
+      <c r="AC50" s="28"/>
+      <c r="AD50" s="28"/>
+      <c r="AE50" s="28"/>
+      <c r="AF50" s="28"/>
+      <c r="AG50" s="28"/>
+      <c r="AW50" s="24"/>
+      <c r="AX50" s="25"/>
+      <c r="AY50" s="25"/>
+      <c r="AZ50" s="25"/>
+      <c r="BA50" s="25"/>
+      <c r="BB50" s="25"/>
+      <c r="BC50" s="25"/>
+      <c r="BD50" s="26"/>
+      <c r="BE50" s="18" t="s">
         <v>221</v>
       </c>
-      <c r="BF50" s="18"/>
-      <c r="BG50" s="18"/>
-      <c r="BH50" s="18"/>
-      <c r="BI50" s="18"/>
-      <c r="BJ50" s="18"/>
-      <c r="BK50" s="18"/>
-      <c r="BL50" s="18"/>
-      <c r="BM50" s="18"/>
-      <c r="BN50" s="18"/>
-      <c r="BO50" s="18"/>
-      <c r="BP50" s="18"/>
-      <c r="BQ50" s="19"/>
-      <c r="BR50" s="31"/>
+      <c r="BF50" s="19"/>
+      <c r="BG50" s="19"/>
+      <c r="BH50" s="19"/>
+      <c r="BI50" s="19"/>
+      <c r="BJ50" s="19"/>
+      <c r="BK50" s="19"/>
+      <c r="BL50" s="19"/>
+      <c r="BM50" s="19"/>
+      <c r="BN50" s="19"/>
+      <c r="BO50" s="19"/>
+      <c r="BP50" s="19"/>
+      <c r="BQ50" s="20"/>
+      <c r="BR50" s="16"/>
       <c r="BT50" s="6"/>
       <c r="BU50" s="6"/>
       <c r="BV50" s="6"/>
@@ -4175,57 +4179,57 @@
       <c r="BZ50" s="6"/>
     </row>
     <row r="51" spans="1:78" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B51" s="31"/>
-      <c r="E51" s="13"/>
-      <c r="F51" s="13"/>
-      <c r="G51" s="13"/>
-      <c r="H51" s="13"/>
-      <c r="I51" s="13"/>
-      <c r="J51" s="13"/>
-      <c r="K51" s="13"/>
-      <c r="L51" s="13"/>
-      <c r="M51" s="13"/>
-      <c r="N51" s="13"/>
-      <c r="O51" s="13"/>
-      <c r="P51" s="13"/>
-      <c r="Q51" s="13"/>
-      <c r="R51" s="13"/>
-      <c r="T51" s="13"/>
-      <c r="U51" s="13"/>
-      <c r="V51" s="13"/>
-      <c r="W51" s="13"/>
-      <c r="X51" s="13"/>
-      <c r="Y51" s="13"/>
-      <c r="Z51" s="13"/>
-      <c r="AA51" s="13"/>
-      <c r="AB51" s="13"/>
-      <c r="AC51" s="13"/>
-      <c r="AD51" s="13"/>
-      <c r="AE51" s="13"/>
-      <c r="AF51" s="13"/>
-      <c r="AG51" s="13"/>
-      <c r="AW51" s="20"/>
-      <c r="AX51" s="21"/>
-      <c r="AY51" s="21"/>
-      <c r="AZ51" s="21"/>
-      <c r="BA51" s="21"/>
-      <c r="BB51" s="21"/>
-      <c r="BC51" s="21"/>
-      <c r="BD51" s="22"/>
-      <c r="BE51" s="20"/>
-      <c r="BF51" s="21"/>
-      <c r="BG51" s="21"/>
-      <c r="BH51" s="21"/>
-      <c r="BI51" s="21"/>
-      <c r="BJ51" s="21"/>
-      <c r="BK51" s="21"/>
-      <c r="BL51" s="21"/>
-      <c r="BM51" s="21"/>
-      <c r="BN51" s="21"/>
-      <c r="BO51" s="21"/>
-      <c r="BP51" s="21"/>
-      <c r="BQ51" s="22"/>
-      <c r="BR51" s="31"/>
+      <c r="B51" s="16"/>
+      <c r="E51" s="28"/>
+      <c r="F51" s="28"/>
+      <c r="G51" s="28"/>
+      <c r="H51" s="28"/>
+      <c r="I51" s="28"/>
+      <c r="J51" s="28"/>
+      <c r="K51" s="28"/>
+      <c r="L51" s="28"/>
+      <c r="M51" s="28"/>
+      <c r="N51" s="28"/>
+      <c r="O51" s="28"/>
+      <c r="P51" s="28"/>
+      <c r="Q51" s="28"/>
+      <c r="R51" s="28"/>
+      <c r="T51" s="28"/>
+      <c r="U51" s="28"/>
+      <c r="V51" s="28"/>
+      <c r="W51" s="28"/>
+      <c r="X51" s="28"/>
+      <c r="Y51" s="28"/>
+      <c r="Z51" s="28"/>
+      <c r="AA51" s="28"/>
+      <c r="AB51" s="28"/>
+      <c r="AC51" s="28"/>
+      <c r="AD51" s="28"/>
+      <c r="AE51" s="28"/>
+      <c r="AF51" s="28"/>
+      <c r="AG51" s="28"/>
+      <c r="AW51" s="21"/>
+      <c r="AX51" s="22"/>
+      <c r="AY51" s="22"/>
+      <c r="AZ51" s="22"/>
+      <c r="BA51" s="22"/>
+      <c r="BB51" s="22"/>
+      <c r="BC51" s="22"/>
+      <c r="BD51" s="23"/>
+      <c r="BE51" s="21"/>
+      <c r="BF51" s="22"/>
+      <c r="BG51" s="22"/>
+      <c r="BH51" s="22"/>
+      <c r="BI51" s="22"/>
+      <c r="BJ51" s="22"/>
+      <c r="BK51" s="22"/>
+      <c r="BL51" s="22"/>
+      <c r="BM51" s="22"/>
+      <c r="BN51" s="22"/>
+      <c r="BO51" s="22"/>
+      <c r="BP51" s="22"/>
+      <c r="BQ51" s="23"/>
+      <c r="BR51" s="16"/>
       <c r="BT51" s="6"/>
       <c r="BU51" s="6"/>
       <c r="BV51" s="6"/>
@@ -4235,33 +4239,33 @@
       <c r="BZ51" s="6"/>
     </row>
     <row r="52" spans="1:78" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B52" s="31"/>
-      <c r="AW52" s="17" t="s">
+      <c r="B52" s="16"/>
+      <c r="AW52" s="18" t="s">
         <v>222</v>
       </c>
-      <c r="AX52" s="18"/>
-      <c r="AY52" s="18"/>
-      <c r="AZ52" s="18"/>
-      <c r="BA52" s="18"/>
-      <c r="BB52" s="18"/>
-      <c r="BC52" s="18"/>
-      <c r="BD52" s="19"/>
-      <c r="BE52" s="17" t="s">
+      <c r="AX52" s="19"/>
+      <c r="AY52" s="19"/>
+      <c r="AZ52" s="19"/>
+      <c r="BA52" s="19"/>
+      <c r="BB52" s="19"/>
+      <c r="BC52" s="19"/>
+      <c r="BD52" s="20"/>
+      <c r="BE52" s="18" t="s">
         <v>223</v>
       </c>
-      <c r="BF52" s="18"/>
-      <c r="BG52" s="18"/>
-      <c r="BH52" s="18"/>
-      <c r="BI52" s="18"/>
-      <c r="BJ52" s="18"/>
-      <c r="BK52" s="18"/>
-      <c r="BL52" s="18"/>
-      <c r="BM52" s="18"/>
-      <c r="BN52" s="18"/>
-      <c r="BO52" s="18"/>
-      <c r="BP52" s="18"/>
-      <c r="BQ52" s="19"/>
-      <c r="BR52" s="31"/>
+      <c r="BF52" s="19"/>
+      <c r="BG52" s="19"/>
+      <c r="BH52" s="19"/>
+      <c r="BI52" s="19"/>
+      <c r="BJ52" s="19"/>
+      <c r="BK52" s="19"/>
+      <c r="BL52" s="19"/>
+      <c r="BM52" s="19"/>
+      <c r="BN52" s="19"/>
+      <c r="BO52" s="19"/>
+      <c r="BP52" s="19"/>
+      <c r="BQ52" s="20"/>
+      <c r="BR52" s="16"/>
       <c r="BT52" s="6"/>
       <c r="BU52" s="6"/>
       <c r="BV52" s="6"/>
@@ -4271,31 +4275,31 @@
       <c r="BZ52" s="6"/>
     </row>
     <row r="53" spans="1:78" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B53" s="31"/>
-      <c r="AW53" s="23" t="s">
+      <c r="B53" s="16"/>
+      <c r="AW53" s="24" t="s">
         <v>224</v>
       </c>
-      <c r="AX53" s="24"/>
-      <c r="AY53" s="24"/>
-      <c r="AZ53" s="24"/>
-      <c r="BA53" s="24"/>
-      <c r="BB53" s="24"/>
-      <c r="BC53" s="24"/>
-      <c r="BD53" s="25"/>
-      <c r="BE53" s="23"/>
-      <c r="BF53" s="24"/>
-      <c r="BG53" s="24"/>
-      <c r="BH53" s="24"/>
-      <c r="BI53" s="24"/>
-      <c r="BJ53" s="24"/>
-      <c r="BK53" s="24"/>
-      <c r="BL53" s="24"/>
-      <c r="BM53" s="24"/>
-      <c r="BN53" s="24"/>
-      <c r="BO53" s="24"/>
-      <c r="BP53" s="24"/>
-      <c r="BQ53" s="25"/>
-      <c r="BR53" s="31"/>
+      <c r="AX53" s="25"/>
+      <c r="AY53" s="25"/>
+      <c r="AZ53" s="25"/>
+      <c r="BA53" s="25"/>
+      <c r="BB53" s="25"/>
+      <c r="BC53" s="25"/>
+      <c r="BD53" s="26"/>
+      <c r="BE53" s="24"/>
+      <c r="BF53" s="25"/>
+      <c r="BG53" s="25"/>
+      <c r="BH53" s="25"/>
+      <c r="BI53" s="25"/>
+      <c r="BJ53" s="25"/>
+      <c r="BK53" s="25"/>
+      <c r="BL53" s="25"/>
+      <c r="BM53" s="25"/>
+      <c r="BN53" s="25"/>
+      <c r="BO53" s="25"/>
+      <c r="BP53" s="25"/>
+      <c r="BQ53" s="26"/>
+      <c r="BR53" s="16"/>
       <c r="BT53" s="6"/>
       <c r="BU53" s="6"/>
       <c r="BV53" s="6"/>
@@ -4305,29 +4309,29 @@
       <c r="BZ53" s="6"/>
     </row>
     <row r="54" spans="1:78" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B54" s="31"/>
-      <c r="AW54" s="23"/>
-      <c r="AX54" s="24"/>
-      <c r="AY54" s="24"/>
-      <c r="AZ54" s="24"/>
-      <c r="BA54" s="24"/>
-      <c r="BB54" s="24"/>
-      <c r="BC54" s="24"/>
-      <c r="BD54" s="25"/>
-      <c r="BE54" s="23"/>
-      <c r="BF54" s="24"/>
-      <c r="BG54" s="24"/>
-      <c r="BH54" s="24"/>
-      <c r="BI54" s="24"/>
-      <c r="BJ54" s="24"/>
-      <c r="BK54" s="24"/>
-      <c r="BL54" s="24"/>
-      <c r="BM54" s="24"/>
-      <c r="BN54" s="24"/>
-      <c r="BO54" s="24"/>
-      <c r="BP54" s="24"/>
-      <c r="BQ54" s="25"/>
-      <c r="BR54" s="31"/>
+      <c r="B54" s="16"/>
+      <c r="AW54" s="24"/>
+      <c r="AX54" s="25"/>
+      <c r="AY54" s="25"/>
+      <c r="AZ54" s="25"/>
+      <c r="BA54" s="25"/>
+      <c r="BB54" s="25"/>
+      <c r="BC54" s="25"/>
+      <c r="BD54" s="26"/>
+      <c r="BE54" s="24"/>
+      <c r="BF54" s="25"/>
+      <c r="BG54" s="25"/>
+      <c r="BH54" s="25"/>
+      <c r="BI54" s="25"/>
+      <c r="BJ54" s="25"/>
+      <c r="BK54" s="25"/>
+      <c r="BL54" s="25"/>
+      <c r="BM54" s="25"/>
+      <c r="BN54" s="25"/>
+      <c r="BO54" s="25"/>
+      <c r="BP54" s="25"/>
+      <c r="BQ54" s="26"/>
+      <c r="BR54" s="16"/>
       <c r="BT54" s="6"/>
       <c r="BU54" s="6"/>
       <c r="BV54" s="6"/>
@@ -4337,29 +4341,29 @@
       <c r="BZ54" s="6"/>
     </row>
     <row r="55" spans="1:78" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B55" s="31"/>
-      <c r="AW55" s="20"/>
-      <c r="AX55" s="21"/>
-      <c r="AY55" s="21"/>
-      <c r="AZ55" s="21"/>
-      <c r="BA55" s="21"/>
-      <c r="BB55" s="21"/>
-      <c r="BC55" s="21"/>
-      <c r="BD55" s="22"/>
-      <c r="BE55" s="20"/>
-      <c r="BF55" s="21"/>
-      <c r="BG55" s="21"/>
-      <c r="BH55" s="21"/>
-      <c r="BI55" s="21"/>
-      <c r="BJ55" s="21"/>
-      <c r="BK55" s="21"/>
-      <c r="BL55" s="21"/>
-      <c r="BM55" s="21"/>
-      <c r="BN55" s="21"/>
-      <c r="BO55" s="21"/>
-      <c r="BP55" s="21"/>
-      <c r="BQ55" s="22"/>
-      <c r="BR55" s="31"/>
+      <c r="B55" s="16"/>
+      <c r="AW55" s="21"/>
+      <c r="AX55" s="22"/>
+      <c r="AY55" s="22"/>
+      <c r="AZ55" s="22"/>
+      <c r="BA55" s="22"/>
+      <c r="BB55" s="22"/>
+      <c r="BC55" s="22"/>
+      <c r="BD55" s="23"/>
+      <c r="BE55" s="21"/>
+      <c r="BF55" s="22"/>
+      <c r="BG55" s="22"/>
+      <c r="BH55" s="22"/>
+      <c r="BI55" s="22"/>
+      <c r="BJ55" s="22"/>
+      <c r="BK55" s="22"/>
+      <c r="BL55" s="22"/>
+      <c r="BM55" s="22"/>
+      <c r="BN55" s="22"/>
+      <c r="BO55" s="22"/>
+      <c r="BP55" s="22"/>
+      <c r="BQ55" s="23"/>
+      <c r="BR55" s="16"/>
       <c r="BT55" s="6"/>
       <c r="BU55" s="6"/>
       <c r="BV55" s="6"/>
@@ -4369,43 +4373,43 @@
       <c r="BZ55" s="6"/>
     </row>
     <row r="56" spans="1:78" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B56" s="27"/>
-      <c r="K56" s="12"/>
-      <c r="L56" s="13"/>
-      <c r="M56" s="13"/>
-      <c r="N56" s="13"/>
-      <c r="O56" s="13"/>
-      <c r="AI56" s="12"/>
-      <c r="AJ56" s="13"/>
-      <c r="AK56" s="13"/>
-      <c r="AL56" s="13"/>
-      <c r="AM56" s="13"/>
-      <c r="AW56" s="14" t="s">
+      <c r="B56" s="17"/>
+      <c r="K56" s="27"/>
+      <c r="L56" s="28"/>
+      <c r="M56" s="28"/>
+      <c r="N56" s="28"/>
+      <c r="O56" s="28"/>
+      <c r="AI56" s="27"/>
+      <c r="AJ56" s="28"/>
+      <c r="AK56" s="28"/>
+      <c r="AL56" s="28"/>
+      <c r="AM56" s="28"/>
+      <c r="AW56" s="12" t="s">
         <v>225</v>
       </c>
-      <c r="AX56" s="15"/>
-      <c r="AY56" s="15" t="s">
+      <c r="AX56" s="13"/>
+      <c r="AY56" s="13" t="s">
         <v>226</v>
       </c>
-      <c r="AZ56" s="15"/>
-      <c r="BA56" s="15"/>
-      <c r="BB56" s="15"/>
-      <c r="BC56" s="15"/>
-      <c r="BD56" s="15"/>
-      <c r="BE56" s="15"/>
-      <c r="BF56" s="15"/>
-      <c r="BG56" s="15"/>
-      <c r="BH56" s="15"/>
-      <c r="BI56" s="15"/>
-      <c r="BJ56" s="15"/>
-      <c r="BK56" s="15"/>
-      <c r="BL56" s="15"/>
-      <c r="BM56" s="15"/>
-      <c r="BN56" s="15"/>
-      <c r="BO56" s="15"/>
-      <c r="BP56" s="15"/>
-      <c r="BQ56" s="16"/>
-      <c r="BR56" s="27"/>
+      <c r="AZ56" s="13"/>
+      <c r="BA56" s="13"/>
+      <c r="BB56" s="13"/>
+      <c r="BC56" s="13"/>
+      <c r="BD56" s="13"/>
+      <c r="BE56" s="13"/>
+      <c r="BF56" s="13"/>
+      <c r="BG56" s="13"/>
+      <c r="BH56" s="13"/>
+      <c r="BI56" s="13"/>
+      <c r="BJ56" s="13"/>
+      <c r="BK56" s="13"/>
+      <c r="BL56" s="13"/>
+      <c r="BM56" s="13"/>
+      <c r="BN56" s="13"/>
+      <c r="BO56" s="13"/>
+      <c r="BP56" s="13"/>
+      <c r="BQ56" s="14"/>
+      <c r="BR56" s="17"/>
       <c r="BT56" s="6"/>
       <c r="BU56" s="6"/>
       <c r="BV56" s="6"/>
@@ -4415,85 +4419,85 @@
       <c r="BZ56" s="6"/>
     </row>
     <row r="57" spans="1:78" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="C57" s="14">
+      <c r="C57" s="12">
         <v>1</v>
       </c>
-      <c r="D57" s="15"/>
-      <c r="E57" s="15"/>
-      <c r="F57" s="15"/>
-      <c r="G57" s="15"/>
-      <c r="H57" s="15"/>
-      <c r="I57" s="15"/>
-      <c r="J57" s="15"/>
-      <c r="K57" s="15"/>
-      <c r="L57" s="16"/>
-      <c r="M57" s="14">
+      <c r="D57" s="13"/>
+      <c r="E57" s="13"/>
+      <c r="F57" s="13"/>
+      <c r="G57" s="13"/>
+      <c r="H57" s="13"/>
+      <c r="I57" s="13"/>
+      <c r="J57" s="13"/>
+      <c r="K57" s="13"/>
+      <c r="L57" s="14"/>
+      <c r="M57" s="12">
         <v>2</v>
       </c>
-      <c r="N57" s="15"/>
-      <c r="O57" s="15"/>
-      <c r="P57" s="15"/>
-      <c r="Q57" s="15"/>
-      <c r="R57" s="15"/>
-      <c r="S57" s="15"/>
-      <c r="T57" s="15"/>
-      <c r="U57" s="15"/>
-      <c r="V57" s="15"/>
-      <c r="W57" s="15"/>
-      <c r="X57" s="16"/>
-      <c r="Y57" s="14">
+      <c r="N57" s="13"/>
+      <c r="O57" s="13"/>
+      <c r="P57" s="13"/>
+      <c r="Q57" s="13"/>
+      <c r="R57" s="13"/>
+      <c r="S57" s="13"/>
+      <c r="T57" s="13"/>
+      <c r="U57" s="13"/>
+      <c r="V57" s="13"/>
+      <c r="W57" s="13"/>
+      <c r="X57" s="14"/>
+      <c r="Y57" s="12">
         <v>3</v>
       </c>
-      <c r="Z57" s="15"/>
-      <c r="AA57" s="15"/>
-      <c r="AB57" s="15"/>
-      <c r="AC57" s="15"/>
-      <c r="AD57" s="15"/>
-      <c r="AE57" s="15"/>
-      <c r="AF57" s="15"/>
-      <c r="AG57" s="15"/>
-      <c r="AH57" s="15"/>
-      <c r="AI57" s="16"/>
-      <c r="AJ57" s="14">
+      <c r="Z57" s="13"/>
+      <c r="AA57" s="13"/>
+      <c r="AB57" s="13"/>
+      <c r="AC57" s="13"/>
+      <c r="AD57" s="13"/>
+      <c r="AE57" s="13"/>
+      <c r="AF57" s="13"/>
+      <c r="AG57" s="13"/>
+      <c r="AH57" s="13"/>
+      <c r="AI57" s="14"/>
+      <c r="AJ57" s="12">
         <v>4</v>
       </c>
-      <c r="AK57" s="15"/>
-      <c r="AL57" s="15"/>
-      <c r="AM57" s="15"/>
-      <c r="AN57" s="15"/>
-      <c r="AO57" s="15"/>
-      <c r="AP57" s="15"/>
-      <c r="AQ57" s="15"/>
-      <c r="AR57" s="15"/>
-      <c r="AS57" s="15"/>
-      <c r="AT57" s="16"/>
-      <c r="AU57" s="14">
+      <c r="AK57" s="13"/>
+      <c r="AL57" s="13"/>
+      <c r="AM57" s="13"/>
+      <c r="AN57" s="13"/>
+      <c r="AO57" s="13"/>
+      <c r="AP57" s="13"/>
+      <c r="AQ57" s="13"/>
+      <c r="AR57" s="13"/>
+      <c r="AS57" s="13"/>
+      <c r="AT57" s="14"/>
+      <c r="AU57" s="12">
         <v>5</v>
       </c>
-      <c r="AV57" s="15"/>
-      <c r="AW57" s="15"/>
-      <c r="AX57" s="15"/>
-      <c r="AY57" s="15"/>
-      <c r="AZ57" s="15"/>
-      <c r="BA57" s="15"/>
-      <c r="BB57" s="15"/>
-      <c r="BC57" s="15"/>
-      <c r="BD57" s="15"/>
-      <c r="BE57" s="15"/>
-      <c r="BF57" s="16"/>
-      <c r="BG57" s="14">
+      <c r="AV57" s="13"/>
+      <c r="AW57" s="13"/>
+      <c r="AX57" s="13"/>
+      <c r="AY57" s="13"/>
+      <c r="AZ57" s="13"/>
+      <c r="BA57" s="13"/>
+      <c r="BB57" s="13"/>
+      <c r="BC57" s="13"/>
+      <c r="BD57" s="13"/>
+      <c r="BE57" s="13"/>
+      <c r="BF57" s="14"/>
+      <c r="BG57" s="12">
         <v>6</v>
       </c>
-      <c r="BH57" s="15"/>
-      <c r="BI57" s="15"/>
-      <c r="BJ57" s="15"/>
-      <c r="BK57" s="15"/>
-      <c r="BL57" s="15"/>
-      <c r="BM57" s="15"/>
-      <c r="BN57" s="15"/>
-      <c r="BO57" s="15"/>
-      <c r="BP57" s="15"/>
-      <c r="BQ57" s="16"/>
+      <c r="BH57" s="13"/>
+      <c r="BI57" s="13"/>
+      <c r="BJ57" s="13"/>
+      <c r="BK57" s="13"/>
+      <c r="BL57" s="13"/>
+      <c r="BM57" s="13"/>
+      <c r="BN57" s="13"/>
+      <c r="BO57" s="13"/>
+      <c r="BP57" s="13"/>
+      <c r="BQ57" s="14"/>
       <c r="BT57" s="6"/>
       <c r="BU57" s="6"/>
       <c r="BV57" s="6"/>
@@ -5205,69 +5209,110 @@
     </row>
   </sheetData>
   <mergeCells count="192">
-    <mergeCell ref="AW56:AX56"/>
-    <mergeCell ref="BM25:BO25"/>
-    <mergeCell ref="Y57:AI57"/>
-    <mergeCell ref="BL39:BN39"/>
-    <mergeCell ref="C2:L2"/>
-    <mergeCell ref="BO41:BQ41"/>
-    <mergeCell ref="BF16:BK16"/>
-    <mergeCell ref="AY10:BB10"/>
-    <mergeCell ref="AW11:AX11"/>
-    <mergeCell ref="AY11:BB11"/>
-    <mergeCell ref="BC11:BE11"/>
-    <mergeCell ref="BF11:BK11"/>
-    <mergeCell ref="BM11:BO11"/>
-    <mergeCell ref="AY17:BB17"/>
-    <mergeCell ref="AW24:AX24"/>
-    <mergeCell ref="BF24:BK24"/>
-    <mergeCell ref="BC20:BE20"/>
-    <mergeCell ref="AY15:BB15"/>
-    <mergeCell ref="AW22:AX22"/>
-    <mergeCell ref="BA41:BH41"/>
-    <mergeCell ref="AW26:AX26"/>
-    <mergeCell ref="AY26:BB26"/>
-    <mergeCell ref="BR17:BR29"/>
-    <mergeCell ref="BM9:BO9"/>
-    <mergeCell ref="AY16:BB16"/>
-    <mergeCell ref="BO39:BQ39"/>
-    <mergeCell ref="BM19:BO19"/>
-    <mergeCell ref="BF14:BK14"/>
-    <mergeCell ref="BF23:BK23"/>
-    <mergeCell ref="BM12:BO12"/>
-    <mergeCell ref="BR3:BR16"/>
-    <mergeCell ref="BF25:BK25"/>
-    <mergeCell ref="BF22:BK22"/>
-    <mergeCell ref="BF12:BK12"/>
-    <mergeCell ref="BM20:BO20"/>
-    <mergeCell ref="BF7:BK7"/>
-    <mergeCell ref="AY21:BB21"/>
-    <mergeCell ref="BM18:BO18"/>
-    <mergeCell ref="BF19:BK19"/>
-    <mergeCell ref="BC24:BE24"/>
-    <mergeCell ref="BM7:BO7"/>
-    <mergeCell ref="BM15:BO15"/>
-    <mergeCell ref="BC25:BE25"/>
-    <mergeCell ref="AW13:AX13"/>
-    <mergeCell ref="BA45:BH45"/>
-    <mergeCell ref="AW8:AX8"/>
-    <mergeCell ref="BL45:BN45"/>
-    <mergeCell ref="BF8:BK8"/>
-    <mergeCell ref="BI40:BK40"/>
-    <mergeCell ref="AW46:AZ46"/>
-    <mergeCell ref="BC26:BE26"/>
-    <mergeCell ref="BF26:BK26"/>
-    <mergeCell ref="BM26:BO26"/>
-    <mergeCell ref="BF5:BK6"/>
-    <mergeCell ref="BC17:BE17"/>
-    <mergeCell ref="AY24:BB24"/>
-    <mergeCell ref="BC5:BE6"/>
-    <mergeCell ref="BO42:BQ42"/>
-    <mergeCell ref="BP5:BP6"/>
-    <mergeCell ref="BO40:BQ40"/>
-    <mergeCell ref="BQ5:BQ6"/>
-    <mergeCell ref="BM21:BO21"/>
-    <mergeCell ref="BF13:BK13"/>
+    <mergeCell ref="T7:AG11"/>
+    <mergeCell ref="E17:R20"/>
+    <mergeCell ref="T17:AG20"/>
+    <mergeCell ref="E26:R29"/>
+    <mergeCell ref="T26:AG29"/>
+    <mergeCell ref="E35:R39"/>
+    <mergeCell ref="T35:AG39"/>
+    <mergeCell ref="E47:R51"/>
+    <mergeCell ref="T47:AG51"/>
+    <mergeCell ref="M2:X2"/>
+    <mergeCell ref="AU2:BF2"/>
+    <mergeCell ref="AW18:AX18"/>
+    <mergeCell ref="BC8:BE8"/>
+    <mergeCell ref="BI43:BK44"/>
+    <mergeCell ref="AU57:BF57"/>
+    <mergeCell ref="AW9:AX9"/>
+    <mergeCell ref="BC22:BE22"/>
+    <mergeCell ref="BA47:BH47"/>
+    <mergeCell ref="BG2:BQ2"/>
+    <mergeCell ref="AJ2:AT2"/>
+    <mergeCell ref="AY56:BQ56"/>
+    <mergeCell ref="Y2:AI2"/>
+    <mergeCell ref="BF9:BK9"/>
+    <mergeCell ref="AY8:BB8"/>
+    <mergeCell ref="AW17:AX17"/>
+    <mergeCell ref="BO43:BQ44"/>
+    <mergeCell ref="BG57:BQ57"/>
+    <mergeCell ref="BC7:BE7"/>
+    <mergeCell ref="BC15:BE15"/>
+    <mergeCell ref="BA40:BH40"/>
+    <mergeCell ref="AW19:AX19"/>
+    <mergeCell ref="AW53:BD55"/>
+    <mergeCell ref="E7:R11"/>
+    <mergeCell ref="AW48:BD48"/>
+    <mergeCell ref="BE50:BQ51"/>
+    <mergeCell ref="AY5:BB6"/>
+    <mergeCell ref="BC13:BE13"/>
+    <mergeCell ref="BM13:BO13"/>
+    <mergeCell ref="AY20:BB20"/>
+    <mergeCell ref="BM22:BO22"/>
+    <mergeCell ref="AW14:AX14"/>
+    <mergeCell ref="AY7:BB7"/>
+    <mergeCell ref="BC10:BE10"/>
+    <mergeCell ref="BM17:BO17"/>
+    <mergeCell ref="BC23:BE23"/>
+    <mergeCell ref="BF18:BK18"/>
+    <mergeCell ref="AW12:AX12"/>
+    <mergeCell ref="BM14:BO14"/>
+    <mergeCell ref="BI46:BQ46"/>
+    <mergeCell ref="BM23:BO23"/>
+    <mergeCell ref="BF15:BK15"/>
+    <mergeCell ref="BL5:BL6"/>
+    <mergeCell ref="AY14:BB14"/>
+    <mergeCell ref="AY25:BB25"/>
+    <mergeCell ref="BM5:BO6"/>
+    <mergeCell ref="AW5:AX6"/>
+    <mergeCell ref="B3:B16"/>
+    <mergeCell ref="BC9:BE9"/>
+    <mergeCell ref="AY18:BB18"/>
+    <mergeCell ref="BI47:BQ47"/>
+    <mergeCell ref="AW21:AX21"/>
+    <mergeCell ref="AJ57:AT57"/>
+    <mergeCell ref="BC19:BE19"/>
+    <mergeCell ref="AX41:AZ41"/>
+    <mergeCell ref="BM24:BO24"/>
+    <mergeCell ref="BI39:BK39"/>
+    <mergeCell ref="BC21:BE21"/>
+    <mergeCell ref="AX43:AZ44"/>
+    <mergeCell ref="AY19:BB19"/>
+    <mergeCell ref="AY13:BB13"/>
+    <mergeCell ref="AX40:AZ40"/>
+    <mergeCell ref="AY22:BB22"/>
+    <mergeCell ref="BA43:BH44"/>
+    <mergeCell ref="BL40:BN40"/>
+    <mergeCell ref="BC12:BE12"/>
+    <mergeCell ref="BL43:BN44"/>
+    <mergeCell ref="C3:D5"/>
+    <mergeCell ref="AT3:AV11"/>
+    <mergeCell ref="C57:L57"/>
+    <mergeCell ref="BI41:BK41"/>
+    <mergeCell ref="BE52:BQ55"/>
+    <mergeCell ref="M57:X57"/>
+    <mergeCell ref="AX42:AZ42"/>
+    <mergeCell ref="AW43:AW44"/>
+    <mergeCell ref="BR30:BR43"/>
+    <mergeCell ref="BM8:BO8"/>
+    <mergeCell ref="AX39:AZ39"/>
+    <mergeCell ref="BM16:BO16"/>
+    <mergeCell ref="BA46:BH46"/>
+    <mergeCell ref="K56:O56"/>
+    <mergeCell ref="BA39:BH39"/>
+    <mergeCell ref="BM10:BO10"/>
+    <mergeCell ref="AW31:AX36"/>
+    <mergeCell ref="BE48:BQ49"/>
+    <mergeCell ref="BL42:BN42"/>
+    <mergeCell ref="AI56:AM56"/>
+    <mergeCell ref="AY23:BB23"/>
+    <mergeCell ref="AX45:AZ45"/>
+    <mergeCell ref="BI42:BK42"/>
+    <mergeCell ref="BF21:BK21"/>
+    <mergeCell ref="BO45:BQ45"/>
+    <mergeCell ref="BR44:BR56"/>
+    <mergeCell ref="AW52:BD52"/>
+    <mergeCell ref="AW16:AX16"/>
     <mergeCell ref="B17:B29"/>
     <mergeCell ref="AY9:BB9"/>
     <mergeCell ref="AW25:AX25"/>
@@ -5292,111 +5337,70 @@
     <mergeCell ref="AY31:BQ36"/>
     <mergeCell ref="AY12:BB12"/>
     <mergeCell ref="BC14:BE14"/>
-    <mergeCell ref="BE52:BQ55"/>
-    <mergeCell ref="M57:X57"/>
-    <mergeCell ref="AX42:AZ42"/>
-    <mergeCell ref="AW43:AW44"/>
-    <mergeCell ref="BR30:BR43"/>
-    <mergeCell ref="BM8:BO8"/>
-    <mergeCell ref="AX39:AZ39"/>
-    <mergeCell ref="BM16:BO16"/>
-    <mergeCell ref="BA46:BH46"/>
-    <mergeCell ref="K56:O56"/>
-    <mergeCell ref="BA39:BH39"/>
-    <mergeCell ref="BM10:BO10"/>
-    <mergeCell ref="AW31:AX36"/>
-    <mergeCell ref="BE48:BQ49"/>
-    <mergeCell ref="BL42:BN42"/>
-    <mergeCell ref="AI56:AM56"/>
-    <mergeCell ref="AY23:BB23"/>
-    <mergeCell ref="AX45:AZ45"/>
-    <mergeCell ref="BI42:BK42"/>
-    <mergeCell ref="BF21:BK21"/>
-    <mergeCell ref="BO45:BQ45"/>
-    <mergeCell ref="BR44:BR56"/>
-    <mergeCell ref="AW52:BD52"/>
-    <mergeCell ref="AW16:AX16"/>
-    <mergeCell ref="B3:B16"/>
-    <mergeCell ref="BC9:BE9"/>
-    <mergeCell ref="AY18:BB18"/>
-    <mergeCell ref="BI47:BQ47"/>
-    <mergeCell ref="AW21:AX21"/>
-    <mergeCell ref="AJ57:AT57"/>
-    <mergeCell ref="BC19:BE19"/>
-    <mergeCell ref="AX41:AZ41"/>
-    <mergeCell ref="BM24:BO24"/>
-    <mergeCell ref="BI39:BK39"/>
-    <mergeCell ref="BC21:BE21"/>
-    <mergeCell ref="AX43:AZ44"/>
-    <mergeCell ref="AY19:BB19"/>
-    <mergeCell ref="AY13:BB13"/>
-    <mergeCell ref="AX40:AZ40"/>
-    <mergeCell ref="AY22:BB22"/>
-    <mergeCell ref="BA43:BH44"/>
-    <mergeCell ref="BL40:BN40"/>
-    <mergeCell ref="BC12:BE12"/>
-    <mergeCell ref="BL43:BN44"/>
-    <mergeCell ref="C3:D5"/>
-    <mergeCell ref="AT3:AV11"/>
-    <mergeCell ref="C57:L57"/>
-    <mergeCell ref="BI41:BK41"/>
+    <mergeCell ref="AW8:AX8"/>
+    <mergeCell ref="BL45:BN45"/>
+    <mergeCell ref="BF8:BK8"/>
+    <mergeCell ref="BI40:BK40"/>
+    <mergeCell ref="AW46:AZ46"/>
+    <mergeCell ref="BC26:BE26"/>
+    <mergeCell ref="BF26:BK26"/>
+    <mergeCell ref="BM26:BO26"/>
+    <mergeCell ref="BF5:BK6"/>
+    <mergeCell ref="BC17:BE17"/>
+    <mergeCell ref="AY24:BB24"/>
+    <mergeCell ref="BC5:BE6"/>
+    <mergeCell ref="BO42:BQ42"/>
+    <mergeCell ref="BP5:BP6"/>
+    <mergeCell ref="BO40:BQ40"/>
+    <mergeCell ref="BQ5:BQ6"/>
+    <mergeCell ref="BM21:BO21"/>
+    <mergeCell ref="BF13:BK13"/>
+    <mergeCell ref="BR17:BR29"/>
+    <mergeCell ref="BM9:BO9"/>
+    <mergeCell ref="AY16:BB16"/>
+    <mergeCell ref="BO39:BQ39"/>
+    <mergeCell ref="BM19:BO19"/>
+    <mergeCell ref="BF14:BK14"/>
+    <mergeCell ref="BF23:BK23"/>
+    <mergeCell ref="BM12:BO12"/>
+    <mergeCell ref="BR3:BR16"/>
+    <mergeCell ref="BF25:BK25"/>
+    <mergeCell ref="BF22:BK22"/>
+    <mergeCell ref="BF12:BK12"/>
+    <mergeCell ref="BM20:BO20"/>
+    <mergeCell ref="BF7:BK7"/>
+    <mergeCell ref="AY21:BB21"/>
+    <mergeCell ref="BM18:BO18"/>
+    <mergeCell ref="BF19:BK19"/>
+    <mergeCell ref="BC24:BE24"/>
+    <mergeCell ref="BM7:BO7"/>
+    <mergeCell ref="BM15:BO15"/>
+    <mergeCell ref="BC25:BE25"/>
     <mergeCell ref="AW3:BQ4"/>
-    <mergeCell ref="AW48:BD48"/>
-    <mergeCell ref="BE50:BQ51"/>
-    <mergeCell ref="AY5:BB6"/>
-    <mergeCell ref="BC13:BE13"/>
-    <mergeCell ref="BM13:BO13"/>
-    <mergeCell ref="AY20:BB20"/>
-    <mergeCell ref="BM22:BO22"/>
-    <mergeCell ref="AW14:AX14"/>
-    <mergeCell ref="AY7:BB7"/>
-    <mergeCell ref="BC10:BE10"/>
-    <mergeCell ref="BM17:BO17"/>
-    <mergeCell ref="BC23:BE23"/>
-    <mergeCell ref="BF18:BK18"/>
-    <mergeCell ref="AW12:AX12"/>
-    <mergeCell ref="BM14:BO14"/>
-    <mergeCell ref="BI46:BQ46"/>
-    <mergeCell ref="BM23:BO23"/>
-    <mergeCell ref="BF15:BK15"/>
-    <mergeCell ref="BL5:BL6"/>
-    <mergeCell ref="AY14:BB14"/>
-    <mergeCell ref="AY25:BB25"/>
-    <mergeCell ref="BM5:BO6"/>
-    <mergeCell ref="AW5:AX6"/>
-    <mergeCell ref="M2:X2"/>
-    <mergeCell ref="AU2:BF2"/>
-    <mergeCell ref="AW18:AX18"/>
-    <mergeCell ref="BC8:BE8"/>
-    <mergeCell ref="BI43:BK44"/>
-    <mergeCell ref="AU57:BF57"/>
-    <mergeCell ref="AW9:AX9"/>
-    <mergeCell ref="BC22:BE22"/>
-    <mergeCell ref="BA47:BH47"/>
-    <mergeCell ref="BG2:BQ2"/>
-    <mergeCell ref="AJ2:AT2"/>
-    <mergeCell ref="AY56:BQ56"/>
-    <mergeCell ref="Y2:AI2"/>
-    <mergeCell ref="BF9:BK9"/>
-    <mergeCell ref="AY8:BB8"/>
-    <mergeCell ref="AW17:AX17"/>
-    <mergeCell ref="BO43:BQ44"/>
-    <mergeCell ref="BG57:BQ57"/>
-    <mergeCell ref="BC7:BE7"/>
-    <mergeCell ref="BC15:BE15"/>
-    <mergeCell ref="BA40:BH40"/>
-    <mergeCell ref="AW19:AX19"/>
-    <mergeCell ref="AW53:BD55"/>
-    <mergeCell ref="E7:R11"/>
-    <mergeCell ref="T7:AG11"/>
-    <mergeCell ref="E17:R20"/>
-    <mergeCell ref="T17:AG20"/>
-    <mergeCell ref="E26:R29"/>
-    <mergeCell ref="T26:AG29"/>
-    <mergeCell ref="E35:R39"/>
-    <mergeCell ref="T35:AG39"/>
-    <mergeCell ref="E47:R51"/>
-    <mergeCell ref="T47:AG51"/>
+    <mergeCell ref="AW56:AX56"/>
+    <mergeCell ref="BM25:BO25"/>
+    <mergeCell ref="Y57:AI57"/>
+    <mergeCell ref="BL39:BN39"/>
+    <mergeCell ref="C2:L2"/>
+    <mergeCell ref="BO41:BQ41"/>
+    <mergeCell ref="BF16:BK16"/>
+    <mergeCell ref="AY10:BB10"/>
+    <mergeCell ref="AW11:AX11"/>
+    <mergeCell ref="AY11:BB11"/>
+    <mergeCell ref="BC11:BE11"/>
+    <mergeCell ref="BF11:BK11"/>
+    <mergeCell ref="BM11:BO11"/>
+    <mergeCell ref="AY17:BB17"/>
+    <mergeCell ref="AW24:AX24"/>
+    <mergeCell ref="BF24:BK24"/>
+    <mergeCell ref="BC20:BE20"/>
+    <mergeCell ref="AY15:BB15"/>
+    <mergeCell ref="AW22:AX22"/>
+    <mergeCell ref="BA41:BH41"/>
+    <mergeCell ref="AW26:AX26"/>
+    <mergeCell ref="AY26:BB26"/>
+    <mergeCell ref="AW13:AX13"/>
+    <mergeCell ref="BA45:BH45"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/가공도_도면_1.xlsx
+++ b/가공도_도면_1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\duddl\Desktop\Project\a2z\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63D8859C-E3C6-4E7C-A1C0-616F0DF53E31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F61223F-06A7-4095-8945-B8EEA7011485}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2304" yWindow="1440" windowWidth="20256" windowHeight="11520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="696" yWindow="720" windowWidth="20256" windowHeight="11520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="237">
   <si>
     <t>A</t>
   </si>
@@ -674,9 +674,6 @@
   </si>
   <si>
     <t>{Input_1}</t>
-  </si>
-  <si>
-    <t>{View_6}</t>
   </si>
   <si>
     <t>{Input_2}</t>
@@ -720,26 +717,26 @@
     <t>{View_7}</t>
   </si>
   <si>
-    <t>{View_8}</t>
+    <t>{Input_200}</t>
+  </si>
+  <si>
+    <t>{Input_201}</t>
+  </si>
+  <si>
+    <t>{Input_202}</t>
+  </si>
+  <si>
+    <t>{Input_203}</t>
+  </si>
+  <si>
+    <t>{Input_204}</t>
+  </si>
+  <si>
+    <t>{View_5}</t>
+  </si>
+  <si>
+    <t>{View_6}</t>
     <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{Input_200}</t>
-  </si>
-  <si>
-    <t>{Input_201}</t>
-  </si>
-  <si>
-    <t>{Input_202}</t>
-  </si>
-  <si>
-    <t>{Input_203}</t>
-  </si>
-  <si>
-    <t>{Input_204}</t>
-  </si>
-  <si>
-    <t>{View_5}</t>
   </si>
 </sst>
 </file>
@@ -967,7 +964,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -995,17 +992,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1016,7 +1011,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1031,10 +1041,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1046,20 +1056,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -1524,189 +1520,189 @@
       <c r="BR2" s="2"/>
     </row>
     <row r="3" spans="1:71" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B3" s="23" t="s">
+      <c r="B3" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="31" t="s">
+      <c r="C3" s="14" t="s">
+        <v>229</v>
+      </c>
+      <c r="D3" s="14"/>
+      <c r="Y3" s="3"/>
+      <c r="AT3" s="14" t="s">
+        <v>236</v>
+      </c>
+      <c r="AU3" s="14"/>
+      <c r="AV3" s="14"/>
+      <c r="AW3" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="AX3" s="22"/>
+      <c r="AY3" s="22"/>
+      <c r="AZ3" s="22"/>
+      <c r="BA3" s="22"/>
+      <c r="BB3" s="22"/>
+      <c r="BC3" s="22"/>
+      <c r="BD3" s="22"/>
+      <c r="BE3" s="22"/>
+      <c r="BF3" s="22"/>
+      <c r="BG3" s="22"/>
+      <c r="BH3" s="22"/>
+      <c r="BI3" s="22"/>
+      <c r="BJ3" s="22"/>
+      <c r="BK3" s="22"/>
+      <c r="BL3" s="22"/>
+      <c r="BM3" s="22"/>
+      <c r="BN3" s="22"/>
+      <c r="BO3" s="22"/>
+      <c r="BP3" s="22"/>
+      <c r="BQ3" s="23"/>
+      <c r="BR3" s="18" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:71" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B4" s="19"/>
+      <c r="C4" s="14"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="11"/>
+      <c r="AA4" s="11"/>
+      <c r="AT4" s="14"/>
+      <c r="AU4" s="14"/>
+      <c r="AV4" s="14"/>
+      <c r="AW4" s="24"/>
+      <c r="AX4" s="25"/>
+      <c r="AY4" s="25"/>
+      <c r="AZ4" s="25"/>
+      <c r="BA4" s="25"/>
+      <c r="BB4" s="25"/>
+      <c r="BC4" s="25"/>
+      <c r="BD4" s="25"/>
+      <c r="BE4" s="25"/>
+      <c r="BF4" s="25"/>
+      <c r="BG4" s="25"/>
+      <c r="BH4" s="25"/>
+      <c r="BI4" s="25"/>
+      <c r="BJ4" s="25"/>
+      <c r="BK4" s="25"/>
+      <c r="BL4" s="25"/>
+      <c r="BM4" s="25"/>
+      <c r="BN4" s="25"/>
+      <c r="BO4" s="25"/>
+      <c r="BP4" s="25"/>
+      <c r="BQ4" s="26"/>
+      <c r="BR4" s="19"/>
+    </row>
+    <row r="5" spans="1:71" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B5" s="19"/>
+      <c r="C5" s="14"/>
+      <c r="D5" s="14"/>
+      <c r="AT5" s="14"/>
+      <c r="AU5" s="14"/>
+      <c r="AV5" s="14"/>
+      <c r="AW5" s="21" t="s">
+        <v>224</v>
+      </c>
+      <c r="AX5" s="23"/>
+      <c r="AY5" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="AZ5" s="22"/>
+      <c r="BA5" s="22"/>
+      <c r="BB5" s="23"/>
+      <c r="BC5" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="BD5" s="22"/>
+      <c r="BE5" s="23"/>
+      <c r="BF5" s="21" t="s">
+        <v>6</v>
+      </c>
+      <c r="BG5" s="22"/>
+      <c r="BH5" s="22"/>
+      <c r="BI5" s="22"/>
+      <c r="BJ5" s="22"/>
+      <c r="BK5" s="23"/>
+      <c r="BL5" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="BM5" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="BN5" s="22"/>
+      <c r="BO5" s="23"/>
+      <c r="BP5" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="BQ5" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="BR5" s="19"/>
+    </row>
+    <row r="6" spans="1:71" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B6" s="19"/>
+      <c r="AT6" s="14"/>
+      <c r="AU6" s="14"/>
+      <c r="AV6" s="14"/>
+      <c r="AW6" s="24"/>
+      <c r="AX6" s="26"/>
+      <c r="AY6" s="24"/>
+      <c r="AZ6" s="25"/>
+      <c r="BA6" s="25"/>
+      <c r="BB6" s="26"/>
+      <c r="BC6" s="24"/>
+      <c r="BD6" s="25"/>
+      <c r="BE6" s="26"/>
+      <c r="BF6" s="24"/>
+      <c r="BG6" s="25"/>
+      <c r="BH6" s="25"/>
+      <c r="BI6" s="25"/>
+      <c r="BJ6" s="25"/>
+      <c r="BK6" s="26"/>
+      <c r="BL6" s="20"/>
+      <c r="BM6" s="24"/>
+      <c r="BN6" s="25"/>
+      <c r="BO6" s="26"/>
+      <c r="BP6" s="20"/>
+      <c r="BQ6" s="20"/>
+      <c r="BR6" s="19"/>
+    </row>
+    <row r="7" spans="1:71" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B7" s="19"/>
+      <c r="E7" s="12" t="s">
         <v>230</v>
       </c>
-      <c r="D3" s="31"/>
-      <c r="Y3" s="3"/>
-      <c r="AT3" s="31" t="s">
-        <v>231</v>
-      </c>
-      <c r="AU3" s="31"/>
-      <c r="AV3" s="31"/>
-      <c r="AW3" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="AX3" s="11"/>
-      <c r="AY3" s="11"/>
-      <c r="AZ3" s="11"/>
-      <c r="BA3" s="11"/>
-      <c r="BB3" s="11"/>
-      <c r="BC3" s="11"/>
-      <c r="BD3" s="11"/>
-      <c r="BE3" s="11"/>
-      <c r="BF3" s="11"/>
-      <c r="BG3" s="11"/>
-      <c r="BH3" s="11"/>
-      <c r="BI3" s="11"/>
-      <c r="BJ3" s="11"/>
-      <c r="BK3" s="11"/>
-      <c r="BL3" s="11"/>
-      <c r="BM3" s="11"/>
-      <c r="BN3" s="11"/>
-      <c r="BO3" s="11"/>
-      <c r="BP3" s="11"/>
-      <c r="BQ3" s="12"/>
-      <c r="BR3" s="23" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:71" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="28"/>
-      <c r="C4" s="31"/>
-      <c r="D4" s="31"/>
-      <c r="E4" s="32"/>
-      <c r="AA4" s="32"/>
-      <c r="AT4" s="31"/>
-      <c r="AU4" s="31"/>
-      <c r="AV4" s="31"/>
-      <c r="AW4" s="19"/>
-      <c r="AX4" s="20"/>
-      <c r="AY4" s="20"/>
-      <c r="AZ4" s="20"/>
-      <c r="BA4" s="20"/>
-      <c r="BB4" s="20"/>
-      <c r="BC4" s="20"/>
-      <c r="BD4" s="20"/>
-      <c r="BE4" s="20"/>
-      <c r="BF4" s="20"/>
-      <c r="BG4" s="20"/>
-      <c r="BH4" s="20"/>
-      <c r="BI4" s="20"/>
-      <c r="BJ4" s="20"/>
-      <c r="BK4" s="20"/>
-      <c r="BL4" s="20"/>
-      <c r="BM4" s="20"/>
-      <c r="BN4" s="20"/>
-      <c r="BO4" s="20"/>
-      <c r="BP4" s="20"/>
-      <c r="BQ4" s="21"/>
-      <c r="BR4" s="28"/>
-    </row>
-    <row r="5" spans="1:71" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B5" s="28"/>
-      <c r="C5" s="31"/>
-      <c r="D5" s="31"/>
-      <c r="AT5" s="31"/>
-      <c r="AU5" s="31"/>
-      <c r="AV5" s="31"/>
-      <c r="AW5" s="18" t="s">
-        <v>225</v>
-      </c>
-      <c r="AX5" s="12"/>
-      <c r="AY5" s="18" t="s">
-        <v>4</v>
-      </c>
-      <c r="AZ5" s="11"/>
-      <c r="BA5" s="11"/>
-      <c r="BB5" s="12"/>
-      <c r="BC5" s="18" t="s">
-        <v>5</v>
-      </c>
-      <c r="BD5" s="11"/>
-      <c r="BE5" s="12"/>
-      <c r="BF5" s="18" t="s">
-        <v>6</v>
-      </c>
-      <c r="BG5" s="11"/>
-      <c r="BH5" s="11"/>
-      <c r="BI5" s="11"/>
-      <c r="BJ5" s="11"/>
-      <c r="BK5" s="12"/>
-      <c r="BL5" s="23" t="s">
-        <v>7</v>
-      </c>
-      <c r="BM5" s="18" t="s">
-        <v>8</v>
-      </c>
-      <c r="BN5" s="11"/>
-      <c r="BO5" s="12"/>
-      <c r="BP5" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="BQ5" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="BR5" s="28"/>
-    </row>
-    <row r="6" spans="1:71" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B6" s="28"/>
-      <c r="AT6" s="31"/>
-      <c r="AU6" s="31"/>
-      <c r="AV6" s="31"/>
-      <c r="AW6" s="19"/>
-      <c r="AX6" s="21"/>
-      <c r="AY6" s="19"/>
-      <c r="AZ6" s="20"/>
-      <c r="BA6" s="20"/>
-      <c r="BB6" s="21"/>
-      <c r="BC6" s="19"/>
-      <c r="BD6" s="20"/>
-      <c r="BE6" s="21"/>
-      <c r="BF6" s="19"/>
-      <c r="BG6" s="20"/>
-      <c r="BH6" s="20"/>
-      <c r="BI6" s="20"/>
-      <c r="BJ6" s="20"/>
-      <c r="BK6" s="21"/>
-      <c r="BL6" s="24"/>
-      <c r="BM6" s="19"/>
-      <c r="BN6" s="20"/>
-      <c r="BO6" s="21"/>
-      <c r="BP6" s="24"/>
-      <c r="BQ6" s="24"/>
-      <c r="BR6" s="28"/>
-    </row>
-    <row r="7" spans="1:71" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B7" s="28"/>
-      <c r="E7" s="29" t="s">
-        <v>232</v>
-      </c>
-      <c r="F7" s="30"/>
-      <c r="G7" s="30"/>
-      <c r="H7" s="30"/>
-      <c r="I7" s="30"/>
-      <c r="J7" s="30"/>
-      <c r="K7" s="30"/>
-      <c r="L7" s="30"/>
-      <c r="M7" s="30"/>
-      <c r="N7" s="30"/>
-      <c r="O7" s="30"/>
-      <c r="P7" s="30"/>
-      <c r="Q7" s="30"/>
-      <c r="R7" s="30"/>
-      <c r="T7" s="29" t="s">
+      <c r="F7" s="13"/>
+      <c r="G7" s="13"/>
+      <c r="H7" s="13"/>
+      <c r="I7" s="13"/>
+      <c r="J7" s="13"/>
+      <c r="K7" s="13"/>
+      <c r="L7" s="13"/>
+      <c r="M7" s="13"/>
+      <c r="N7" s="13"/>
+      <c r="O7" s="13"/>
+      <c r="P7" s="13"/>
+      <c r="Q7" s="13"/>
+      <c r="R7" s="13"/>
+      <c r="T7" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="U7" s="30"/>
-      <c r="V7" s="30"/>
-      <c r="W7" s="30"/>
-      <c r="X7" s="30"/>
-      <c r="Y7" s="30"/>
-      <c r="Z7" s="30"/>
-      <c r="AA7" s="30"/>
-      <c r="AB7" s="30"/>
-      <c r="AC7" s="30"/>
-      <c r="AD7" s="30"/>
-      <c r="AE7" s="30"/>
-      <c r="AF7" s="30"/>
-      <c r="AG7" s="30"/>
-      <c r="AT7" s="31"/>
-      <c r="AU7" s="31"/>
-      <c r="AV7" s="31"/>
+      <c r="U7" s="13"/>
+      <c r="V7" s="13"/>
+      <c r="W7" s="13"/>
+      <c r="X7" s="13"/>
+      <c r="Y7" s="13"/>
+      <c r="Z7" s="13"/>
+      <c r="AA7" s="13"/>
+      <c r="AB7" s="13"/>
+      <c r="AC7" s="13"/>
+      <c r="AD7" s="13"/>
+      <c r="AE7" s="13"/>
+      <c r="AF7" s="13"/>
+      <c r="AG7" s="13"/>
+      <c r="AT7" s="14"/>
+      <c r="AU7" s="14"/>
+      <c r="AV7" s="14"/>
       <c r="AW7" s="15" t="s">
         <v>11</v>
       </c>
@@ -1744,41 +1740,41 @@
       <c r="BQ7" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="BR7" s="28"/>
+      <c r="BR7" s="19"/>
     </row>
     <row r="8" spans="1:71" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B8" s="28"/>
-      <c r="E8" s="30"/>
-      <c r="F8" s="30"/>
-      <c r="G8" s="30"/>
-      <c r="H8" s="30"/>
-      <c r="I8" s="30"/>
-      <c r="J8" s="30"/>
-      <c r="K8" s="30"/>
-      <c r="L8" s="30"/>
-      <c r="M8" s="30"/>
-      <c r="N8" s="30"/>
-      <c r="O8" s="30"/>
-      <c r="P8" s="30"/>
-      <c r="Q8" s="30"/>
-      <c r="R8" s="30"/>
-      <c r="T8" s="30"/>
-      <c r="U8" s="30"/>
-      <c r="V8" s="30"/>
-      <c r="W8" s="30"/>
-      <c r="X8" s="30"/>
-      <c r="Y8" s="30"/>
-      <c r="Z8" s="30"/>
-      <c r="AA8" s="30"/>
-      <c r="AB8" s="30"/>
-      <c r="AC8" s="30"/>
-      <c r="AD8" s="30"/>
-      <c r="AE8" s="30"/>
-      <c r="AF8" s="30"/>
-      <c r="AG8" s="30"/>
-      <c r="AT8" s="31"/>
-      <c r="AU8" s="31"/>
-      <c r="AV8" s="31"/>
+      <c r="B8" s="19"/>
+      <c r="E8" s="13"/>
+      <c r="F8" s="13"/>
+      <c r="G8" s="13"/>
+      <c r="H8" s="13"/>
+      <c r="I8" s="13"/>
+      <c r="J8" s="13"/>
+      <c r="K8" s="13"/>
+      <c r="L8" s="13"/>
+      <c r="M8" s="13"/>
+      <c r="N8" s="13"/>
+      <c r="O8" s="13"/>
+      <c r="P8" s="13"/>
+      <c r="Q8" s="13"/>
+      <c r="R8" s="13"/>
+      <c r="T8" s="13"/>
+      <c r="U8" s="13"/>
+      <c r="V8" s="13"/>
+      <c r="W8" s="13"/>
+      <c r="X8" s="13"/>
+      <c r="Y8" s="13"/>
+      <c r="Z8" s="13"/>
+      <c r="AA8" s="13"/>
+      <c r="AB8" s="13"/>
+      <c r="AC8" s="13"/>
+      <c r="AD8" s="13"/>
+      <c r="AE8" s="13"/>
+      <c r="AF8" s="13"/>
+      <c r="AG8" s="13"/>
+      <c r="AT8" s="14"/>
+      <c r="AU8" s="14"/>
+      <c r="AV8" s="14"/>
       <c r="AW8" s="15" t="s">
         <v>19</v>
       </c>
@@ -1816,41 +1812,41 @@
       <c r="BQ8" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="BR8" s="28"/>
+      <c r="BR8" s="19"/>
     </row>
     <row r="9" spans="1:71" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B9" s="28"/>
-      <c r="E9" s="30"/>
-      <c r="F9" s="30"/>
-      <c r="G9" s="30"/>
-      <c r="H9" s="30"/>
-      <c r="I9" s="30"/>
-      <c r="J9" s="30"/>
-      <c r="K9" s="30"/>
-      <c r="L9" s="30"/>
-      <c r="M9" s="30"/>
-      <c r="N9" s="30"/>
-      <c r="O9" s="30"/>
-      <c r="P9" s="30"/>
-      <c r="Q9" s="30"/>
-      <c r="R9" s="30"/>
-      <c r="T9" s="30"/>
-      <c r="U9" s="30"/>
-      <c r="V9" s="30"/>
-      <c r="W9" s="30"/>
-      <c r="X9" s="30"/>
-      <c r="Y9" s="30"/>
-      <c r="Z9" s="30"/>
-      <c r="AA9" s="30"/>
-      <c r="AB9" s="30"/>
-      <c r="AC9" s="30"/>
-      <c r="AD9" s="30"/>
-      <c r="AE9" s="30"/>
-      <c r="AF9" s="30"/>
-      <c r="AG9" s="30"/>
-      <c r="AT9" s="31"/>
-      <c r="AU9" s="31"/>
-      <c r="AV9" s="31"/>
+      <c r="B9" s="19"/>
+      <c r="E9" s="13"/>
+      <c r="F9" s="13"/>
+      <c r="G9" s="13"/>
+      <c r="H9" s="13"/>
+      <c r="I9" s="13"/>
+      <c r="J9" s="13"/>
+      <c r="K9" s="13"/>
+      <c r="L9" s="13"/>
+      <c r="M9" s="13"/>
+      <c r="N9" s="13"/>
+      <c r="O9" s="13"/>
+      <c r="P9" s="13"/>
+      <c r="Q9" s="13"/>
+      <c r="R9" s="13"/>
+      <c r="T9" s="13"/>
+      <c r="U9" s="13"/>
+      <c r="V9" s="13"/>
+      <c r="W9" s="13"/>
+      <c r="X9" s="13"/>
+      <c r="Y9" s="13"/>
+      <c r="Z9" s="13"/>
+      <c r="AA9" s="13"/>
+      <c r="AB9" s="13"/>
+      <c r="AC9" s="13"/>
+      <c r="AD9" s="13"/>
+      <c r="AE9" s="13"/>
+      <c r="AF9" s="13"/>
+      <c r="AG9" s="13"/>
+      <c r="AT9" s="14"/>
+      <c r="AU9" s="14"/>
+      <c r="AV9" s="14"/>
       <c r="AW9" s="15" t="s">
         <v>27</v>
       </c>
@@ -1888,41 +1884,41 @@
       <c r="BQ9" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="BR9" s="28"/>
+      <c r="BR9" s="19"/>
     </row>
     <row r="10" spans="1:71" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B10" s="28"/>
-      <c r="E10" s="30"/>
-      <c r="F10" s="30"/>
-      <c r="G10" s="30"/>
-      <c r="H10" s="30"/>
-      <c r="I10" s="30"/>
-      <c r="J10" s="30"/>
-      <c r="K10" s="30"/>
-      <c r="L10" s="30"/>
-      <c r="M10" s="30"/>
-      <c r="N10" s="30"/>
-      <c r="O10" s="30"/>
-      <c r="P10" s="30"/>
-      <c r="Q10" s="30"/>
-      <c r="R10" s="30"/>
-      <c r="T10" s="30"/>
-      <c r="U10" s="30"/>
-      <c r="V10" s="30"/>
-      <c r="W10" s="30"/>
-      <c r="X10" s="30"/>
-      <c r="Y10" s="30"/>
-      <c r="Z10" s="30"/>
-      <c r="AA10" s="30"/>
-      <c r="AB10" s="30"/>
-      <c r="AC10" s="30"/>
-      <c r="AD10" s="30"/>
-      <c r="AE10" s="30"/>
-      <c r="AF10" s="30"/>
-      <c r="AG10" s="30"/>
-      <c r="AT10" s="31"/>
-      <c r="AU10" s="31"/>
-      <c r="AV10" s="31"/>
+      <c r="B10" s="19"/>
+      <c r="E10" s="13"/>
+      <c r="F10" s="13"/>
+      <c r="G10" s="13"/>
+      <c r="H10" s="13"/>
+      <c r="I10" s="13"/>
+      <c r="J10" s="13"/>
+      <c r="K10" s="13"/>
+      <c r="L10" s="13"/>
+      <c r="M10" s="13"/>
+      <c r="N10" s="13"/>
+      <c r="O10" s="13"/>
+      <c r="P10" s="13"/>
+      <c r="Q10" s="13"/>
+      <c r="R10" s="13"/>
+      <c r="T10" s="13"/>
+      <c r="U10" s="13"/>
+      <c r="V10" s="13"/>
+      <c r="W10" s="13"/>
+      <c r="X10" s="13"/>
+      <c r="Y10" s="13"/>
+      <c r="Z10" s="13"/>
+      <c r="AA10" s="13"/>
+      <c r="AB10" s="13"/>
+      <c r="AC10" s="13"/>
+      <c r="AD10" s="13"/>
+      <c r="AE10" s="13"/>
+      <c r="AF10" s="13"/>
+      <c r="AG10" s="13"/>
+      <c r="AT10" s="14"/>
+      <c r="AU10" s="14"/>
+      <c r="AV10" s="14"/>
       <c r="AW10" s="15" t="s">
         <v>35</v>
       </c>
@@ -1960,41 +1956,41 @@
       <c r="BQ10" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="BR10" s="28"/>
+      <c r="BR10" s="19"/>
     </row>
     <row r="11" spans="1:71" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B11" s="28"/>
-      <c r="E11" s="30"/>
-      <c r="F11" s="30"/>
-      <c r="G11" s="30"/>
-      <c r="H11" s="30"/>
-      <c r="I11" s="30"/>
-      <c r="J11" s="30"/>
-      <c r="K11" s="30"/>
-      <c r="L11" s="30"/>
-      <c r="M11" s="30"/>
-      <c r="N11" s="30"/>
-      <c r="O11" s="30"/>
-      <c r="P11" s="30"/>
-      <c r="Q11" s="30"/>
-      <c r="R11" s="30"/>
-      <c r="T11" s="30"/>
-      <c r="U11" s="30"/>
-      <c r="V11" s="30"/>
-      <c r="W11" s="30"/>
-      <c r="X11" s="30"/>
-      <c r="Y11" s="30"/>
-      <c r="Z11" s="30"/>
-      <c r="AA11" s="30"/>
-      <c r="AB11" s="30"/>
-      <c r="AC11" s="30"/>
-      <c r="AD11" s="30"/>
-      <c r="AE11" s="30"/>
-      <c r="AF11" s="30"/>
-      <c r="AG11" s="30"/>
-      <c r="AT11" s="31"/>
-      <c r="AU11" s="31"/>
-      <c r="AV11" s="31"/>
+      <c r="B11" s="19"/>
+      <c r="E11" s="13"/>
+      <c r="F11" s="13"/>
+      <c r="G11" s="13"/>
+      <c r="H11" s="13"/>
+      <c r="I11" s="13"/>
+      <c r="J11" s="13"/>
+      <c r="K11" s="13"/>
+      <c r="L11" s="13"/>
+      <c r="M11" s="13"/>
+      <c r="N11" s="13"/>
+      <c r="O11" s="13"/>
+      <c r="P11" s="13"/>
+      <c r="Q11" s="13"/>
+      <c r="R11" s="13"/>
+      <c r="T11" s="13"/>
+      <c r="U11" s="13"/>
+      <c r="V11" s="13"/>
+      <c r="W11" s="13"/>
+      <c r="X11" s="13"/>
+      <c r="Y11" s="13"/>
+      <c r="Z11" s="13"/>
+      <c r="AA11" s="13"/>
+      <c r="AB11" s="13"/>
+      <c r="AC11" s="13"/>
+      <c r="AD11" s="13"/>
+      <c r="AE11" s="13"/>
+      <c r="AF11" s="13"/>
+      <c r="AG11" s="13"/>
+      <c r="AT11" s="14"/>
+      <c r="AU11" s="14"/>
+      <c r="AV11" s="14"/>
       <c r="AW11" s="15" t="s">
         <v>43</v>
       </c>
@@ -2032,10 +2028,10 @@
       <c r="BQ11" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="BR11" s="28"/>
+      <c r="BR11" s="19"/>
     </row>
     <row r="12" spans="1:71" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B12" s="28"/>
+      <c r="B12" s="19"/>
       <c r="AW12" s="15" t="s">
         <v>51</v>
       </c>
@@ -2073,10 +2069,10 @@
       <c r="BQ12" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="BR12" s="28"/>
+      <c r="BR12" s="19"/>
     </row>
     <row r="13" spans="1:71" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B13" s="28"/>
+      <c r="B13" s="19"/>
       <c r="AW13" s="15" t="s">
         <v>59</v>
       </c>
@@ -2114,10 +2110,10 @@
       <c r="BQ13" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="BR13" s="28"/>
+      <c r="BR13" s="19"/>
     </row>
     <row r="14" spans="1:71" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B14" s="28"/>
+      <c r="B14" s="19"/>
       <c r="AW14" s="15" t="s">
         <v>67</v>
       </c>
@@ -2155,10 +2151,10 @@
       <c r="BQ14" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="BR14" s="28"/>
+      <c r="BR14" s="19"/>
     </row>
     <row r="15" spans="1:71" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B15" s="28"/>
+      <c r="B15" s="19"/>
       <c r="AW15" s="15" t="s">
         <v>75</v>
       </c>
@@ -2196,10 +2192,10 @@
       <c r="BQ15" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="BR15" s="28"/>
+      <c r="BR15" s="19"/>
     </row>
     <row r="16" spans="1:71" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B16" s="24"/>
+      <c r="B16" s="20"/>
       <c r="AW16" s="15" t="s">
         <v>84</v>
       </c>
@@ -2237,44 +2233,44 @@
       <c r="BQ16" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="BR16" s="24"/>
+      <c r="BR16" s="20"/>
     </row>
     <row r="17" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B17" s="23" t="s">
+      <c r="B17" s="18" t="s">
         <v>83</v>
       </c>
-      <c r="E17" s="29" t="s">
-        <v>233</v>
-      </c>
-      <c r="F17" s="30"/>
-      <c r="G17" s="30"/>
-      <c r="H17" s="30"/>
-      <c r="I17" s="30"/>
-      <c r="J17" s="30"/>
-      <c r="K17" s="30"/>
-      <c r="L17" s="30"/>
-      <c r="M17" s="30"/>
-      <c r="N17" s="30"/>
-      <c r="O17" s="30"/>
-      <c r="P17" s="30"/>
-      <c r="Q17" s="30"/>
-      <c r="R17" s="30"/>
-      <c r="T17" s="29" t="s">
+      <c r="E17" s="12" t="s">
+        <v>231</v>
+      </c>
+      <c r="F17" s="13"/>
+      <c r="G17" s="13"/>
+      <c r="H17" s="13"/>
+      <c r="I17" s="13"/>
+      <c r="J17" s="13"/>
+      <c r="K17" s="13"/>
+      <c r="L17" s="13"/>
+      <c r="M17" s="13"/>
+      <c r="N17" s="13"/>
+      <c r="O17" s="13"/>
+      <c r="P17" s="13"/>
+      <c r="Q17" s="13"/>
+      <c r="R17" s="13"/>
+      <c r="T17" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="U17" s="30"/>
-      <c r="V17" s="30"/>
-      <c r="W17" s="30"/>
-      <c r="X17" s="30"/>
-      <c r="Y17" s="30"/>
-      <c r="Z17" s="30"/>
-      <c r="AA17" s="30"/>
-      <c r="AB17" s="30"/>
-      <c r="AC17" s="30"/>
-      <c r="AD17" s="30"/>
-      <c r="AE17" s="30"/>
-      <c r="AF17" s="30"/>
-      <c r="AG17" s="30"/>
+      <c r="U17" s="13"/>
+      <c r="V17" s="13"/>
+      <c r="W17" s="13"/>
+      <c r="X17" s="13"/>
+      <c r="Y17" s="13"/>
+      <c r="Z17" s="13"/>
+      <c r="AA17" s="13"/>
+      <c r="AB17" s="13"/>
+      <c r="AC17" s="13"/>
+      <c r="AD17" s="13"/>
+      <c r="AE17" s="13"/>
+      <c r="AF17" s="13"/>
+      <c r="AG17" s="13"/>
       <c r="AW17" s="15" t="s">
         <v>92</v>
       </c>
@@ -2312,40 +2308,40 @@
       <c r="BQ17" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="BR17" s="23" t="s">
+      <c r="BR17" s="18" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="18" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B18" s="28"/>
-      <c r="E18" s="30"/>
-      <c r="F18" s="30"/>
-      <c r="G18" s="30"/>
-      <c r="H18" s="30"/>
-      <c r="I18" s="30"/>
-      <c r="J18" s="30"/>
-      <c r="K18" s="30"/>
-      <c r="L18" s="30"/>
-      <c r="M18" s="30"/>
-      <c r="N18" s="30"/>
-      <c r="O18" s="30"/>
-      <c r="P18" s="30"/>
-      <c r="Q18" s="30"/>
-      <c r="R18" s="30"/>
-      <c r="T18" s="30"/>
-      <c r="U18" s="30"/>
-      <c r="V18" s="30"/>
-      <c r="W18" s="30"/>
-      <c r="X18" s="30"/>
-      <c r="Y18" s="30"/>
-      <c r="Z18" s="30"/>
-      <c r="AA18" s="30"/>
-      <c r="AB18" s="30"/>
-      <c r="AC18" s="30"/>
-      <c r="AD18" s="30"/>
-      <c r="AE18" s="30"/>
-      <c r="AF18" s="30"/>
-      <c r="AG18" s="30"/>
+      <c r="B18" s="19"/>
+      <c r="E18" s="13"/>
+      <c r="F18" s="13"/>
+      <c r="G18" s="13"/>
+      <c r="H18" s="13"/>
+      <c r="I18" s="13"/>
+      <c r="J18" s="13"/>
+      <c r="K18" s="13"/>
+      <c r="L18" s="13"/>
+      <c r="M18" s="13"/>
+      <c r="N18" s="13"/>
+      <c r="O18" s="13"/>
+      <c r="P18" s="13"/>
+      <c r="Q18" s="13"/>
+      <c r="R18" s="13"/>
+      <c r="T18" s="13"/>
+      <c r="U18" s="13"/>
+      <c r="V18" s="13"/>
+      <c r="W18" s="13"/>
+      <c r="X18" s="13"/>
+      <c r="Y18" s="13"/>
+      <c r="Z18" s="13"/>
+      <c r="AA18" s="13"/>
+      <c r="AB18" s="13"/>
+      <c r="AC18" s="13"/>
+      <c r="AD18" s="13"/>
+      <c r="AE18" s="13"/>
+      <c r="AF18" s="13"/>
+      <c r="AG18" s="13"/>
       <c r="AW18" s="15" t="s">
         <v>100</v>
       </c>
@@ -2383,38 +2379,38 @@
       <c r="BQ18" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="BR18" s="28"/>
+      <c r="BR18" s="19"/>
     </row>
     <row r="19" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B19" s="28"/>
-      <c r="E19" s="30"/>
-      <c r="F19" s="30"/>
-      <c r="G19" s="30"/>
-      <c r="H19" s="30"/>
-      <c r="I19" s="30"/>
-      <c r="J19" s="30"/>
-      <c r="K19" s="30"/>
-      <c r="L19" s="30"/>
-      <c r="M19" s="30"/>
-      <c r="N19" s="30"/>
-      <c r="O19" s="30"/>
-      <c r="P19" s="30"/>
-      <c r="Q19" s="30"/>
-      <c r="R19" s="30"/>
-      <c r="T19" s="30"/>
-      <c r="U19" s="30"/>
-      <c r="V19" s="30"/>
-      <c r="W19" s="30"/>
-      <c r="X19" s="30"/>
-      <c r="Y19" s="30"/>
-      <c r="Z19" s="30"/>
-      <c r="AA19" s="30"/>
-      <c r="AB19" s="30"/>
-      <c r="AC19" s="30"/>
-      <c r="AD19" s="30"/>
-      <c r="AE19" s="30"/>
-      <c r="AF19" s="30"/>
-      <c r="AG19" s="30"/>
+      <c r="B19" s="19"/>
+      <c r="E19" s="13"/>
+      <c r="F19" s="13"/>
+      <c r="G19" s="13"/>
+      <c r="H19" s="13"/>
+      <c r="I19" s="13"/>
+      <c r="J19" s="13"/>
+      <c r="K19" s="13"/>
+      <c r="L19" s="13"/>
+      <c r="M19" s="13"/>
+      <c r="N19" s="13"/>
+      <c r="O19" s="13"/>
+      <c r="P19" s="13"/>
+      <c r="Q19" s="13"/>
+      <c r="R19" s="13"/>
+      <c r="T19" s="13"/>
+      <c r="U19" s="13"/>
+      <c r="V19" s="13"/>
+      <c r="W19" s="13"/>
+      <c r="X19" s="13"/>
+      <c r="Y19" s="13"/>
+      <c r="Z19" s="13"/>
+      <c r="AA19" s="13"/>
+      <c r="AB19" s="13"/>
+      <c r="AC19" s="13"/>
+      <c r="AD19" s="13"/>
+      <c r="AE19" s="13"/>
+      <c r="AF19" s="13"/>
+      <c r="AG19" s="13"/>
       <c r="AW19" s="15" t="s">
         <v>108</v>
       </c>
@@ -2452,38 +2448,38 @@
       <c r="BQ19" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="BR19" s="28"/>
+      <c r="BR19" s="19"/>
     </row>
     <row r="20" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B20" s="28"/>
-      <c r="E20" s="30"/>
-      <c r="F20" s="30"/>
-      <c r="G20" s="30"/>
-      <c r="H20" s="30"/>
-      <c r="I20" s="30"/>
-      <c r="J20" s="30"/>
-      <c r="K20" s="30"/>
-      <c r="L20" s="30"/>
-      <c r="M20" s="30"/>
-      <c r="N20" s="30"/>
-      <c r="O20" s="30"/>
-      <c r="P20" s="30"/>
-      <c r="Q20" s="30"/>
-      <c r="R20" s="30"/>
-      <c r="T20" s="30"/>
-      <c r="U20" s="30"/>
-      <c r="V20" s="30"/>
-      <c r="W20" s="30"/>
-      <c r="X20" s="30"/>
-      <c r="Y20" s="30"/>
-      <c r="Z20" s="30"/>
-      <c r="AA20" s="30"/>
-      <c r="AB20" s="30"/>
-      <c r="AC20" s="30"/>
-      <c r="AD20" s="30"/>
-      <c r="AE20" s="30"/>
-      <c r="AF20" s="30"/>
-      <c r="AG20" s="30"/>
+      <c r="B20" s="19"/>
+      <c r="E20" s="13"/>
+      <c r="F20" s="13"/>
+      <c r="G20" s="13"/>
+      <c r="H20" s="13"/>
+      <c r="I20" s="13"/>
+      <c r="J20" s="13"/>
+      <c r="K20" s="13"/>
+      <c r="L20" s="13"/>
+      <c r="M20" s="13"/>
+      <c r="N20" s="13"/>
+      <c r="O20" s="13"/>
+      <c r="P20" s="13"/>
+      <c r="Q20" s="13"/>
+      <c r="R20" s="13"/>
+      <c r="T20" s="13"/>
+      <c r="U20" s="13"/>
+      <c r="V20" s="13"/>
+      <c r="W20" s="13"/>
+      <c r="X20" s="13"/>
+      <c r="Y20" s="13"/>
+      <c r="Z20" s="13"/>
+      <c r="AA20" s="13"/>
+      <c r="AB20" s="13"/>
+      <c r="AC20" s="13"/>
+      <c r="AD20" s="13"/>
+      <c r="AE20" s="13"/>
+      <c r="AF20" s="13"/>
+      <c r="AG20" s="13"/>
       <c r="AW20" s="15" t="s">
         <v>116</v>
       </c>
@@ -2521,10 +2517,10 @@
       <c r="BQ20" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="BR20" s="28"/>
+      <c r="BR20" s="19"/>
     </row>
     <row r="21" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B21" s="28"/>
+      <c r="B21" s="19"/>
       <c r="AW21" s="15" t="s">
         <v>124</v>
       </c>
@@ -2562,10 +2558,10 @@
       <c r="BQ21" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="BR21" s="28"/>
+      <c r="BR21" s="19"/>
     </row>
     <row r="22" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B22" s="28"/>
+      <c r="B22" s="19"/>
       <c r="AW22" s="15" t="s">
         <v>132</v>
       </c>
@@ -2603,10 +2599,10 @@
       <c r="BQ22" s="8" t="s">
         <v>139</v>
       </c>
-      <c r="BR22" s="28"/>
+      <c r="BR22" s="19"/>
     </row>
     <row r="23" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B23" s="28"/>
+      <c r="B23" s="19"/>
       <c r="AW23" s="15" t="s">
         <v>140</v>
       </c>
@@ -2644,10 +2640,10 @@
       <c r="BQ23" s="8" t="s">
         <v>147</v>
       </c>
-      <c r="BR23" s="28"/>
+      <c r="BR23" s="19"/>
     </row>
     <row r="24" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B24" s="28"/>
+      <c r="B24" s="19"/>
       <c r="AW24" s="15" t="s">
         <v>148</v>
       </c>
@@ -2685,27 +2681,27 @@
       <c r="BQ24" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="BR24" s="28"/>
+      <c r="BR24" s="19"/>
     </row>
     <row r="25" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B25" s="28"/>
+      <c r="B25" s="19"/>
       <c r="AW25" s="15" t="s">
+        <v>225</v>
+      </c>
+      <c r="AX25" s="17"/>
+      <c r="AY25" s="30" t="s">
+        <v>156</v>
+      </c>
+      <c r="AZ25" s="31"/>
+      <c r="BA25" s="31"/>
+      <c r="BB25" s="32"/>
+      <c r="BC25" s="16" t="s">
         <v>226</v>
-      </c>
-      <c r="AX25" s="17"/>
-      <c r="AY25" s="25" t="s">
-        <v>156</v>
-      </c>
-      <c r="AZ25" s="26"/>
-      <c r="BA25" s="26"/>
-      <c r="BB25" s="27"/>
-      <c r="BC25" s="16" t="s">
-        <v>227</v>
       </c>
       <c r="BD25" s="16"/>
       <c r="BE25" s="17"/>
       <c r="BF25" s="15" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="BG25" s="16"/>
       <c r="BH25" s="16"/>
@@ -2716,7 +2712,7 @@
         <v>157</v>
       </c>
       <c r="BM25" s="15" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="BN25" s="16"/>
       <c r="BO25" s="17"/>
@@ -2726,42 +2722,42 @@
       <c r="BQ25" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="BR25" s="28"/>
+      <c r="BR25" s="19"/>
     </row>
     <row r="26" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B26" s="28"/>
-      <c r="E26" s="29" t="s">
-        <v>234</v>
-      </c>
-      <c r="F26" s="30"/>
-      <c r="G26" s="30"/>
-      <c r="H26" s="30"/>
-      <c r="I26" s="30"/>
-      <c r="J26" s="30"/>
-      <c r="K26" s="30"/>
-      <c r="L26" s="30"/>
-      <c r="M26" s="30"/>
-      <c r="N26" s="30"/>
-      <c r="O26" s="30"/>
-      <c r="P26" s="30"/>
-      <c r="Q26" s="30"/>
-      <c r="R26" s="30"/>
-      <c r="T26" s="29" t="s">
+      <c r="B26" s="19"/>
+      <c r="E26" s="12" t="s">
+        <v>232</v>
+      </c>
+      <c r="F26" s="13"/>
+      <c r="G26" s="13"/>
+      <c r="H26" s="13"/>
+      <c r="I26" s="13"/>
+      <c r="J26" s="13"/>
+      <c r="K26" s="13"/>
+      <c r="L26" s="13"/>
+      <c r="M26" s="13"/>
+      <c r="N26" s="13"/>
+      <c r="O26" s="13"/>
+      <c r="P26" s="13"/>
+      <c r="Q26" s="13"/>
+      <c r="R26" s="13"/>
+      <c r="T26" s="12" t="s">
         <v>171</v>
       </c>
-      <c r="U26" s="30"/>
-      <c r="V26" s="30"/>
-      <c r="W26" s="30"/>
-      <c r="X26" s="30"/>
-      <c r="Y26" s="30"/>
-      <c r="Z26" s="30"/>
-      <c r="AA26" s="30"/>
-      <c r="AB26" s="30"/>
-      <c r="AC26" s="30"/>
-      <c r="AD26" s="30"/>
-      <c r="AE26" s="30"/>
-      <c r="AF26" s="30"/>
-      <c r="AG26" s="30"/>
+      <c r="U26" s="13"/>
+      <c r="V26" s="13"/>
+      <c r="W26" s="13"/>
+      <c r="X26" s="13"/>
+      <c r="Y26" s="13"/>
+      <c r="Z26" s="13"/>
+      <c r="AA26" s="13"/>
+      <c r="AB26" s="13"/>
+      <c r="AC26" s="13"/>
+      <c r="AD26" s="13"/>
+      <c r="AE26" s="13"/>
+      <c r="AF26" s="13"/>
+      <c r="AG26" s="13"/>
       <c r="AW26" s="15" t="s">
         <v>160</v>
       </c>
@@ -2799,76 +2795,72 @@
       <c r="BQ26" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="BR26" s="28"/>
+      <c r="BR26" s="19"/>
     </row>
     <row r="27" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B27" s="28"/>
-      <c r="E27" s="30"/>
-      <c r="F27" s="30"/>
-      <c r="G27" s="30"/>
-      <c r="H27" s="30"/>
-      <c r="I27" s="30"/>
-      <c r="J27" s="30"/>
-      <c r="K27" s="30"/>
-      <c r="L27" s="30"/>
-      <c r="M27" s="30"/>
-      <c r="N27" s="30"/>
-      <c r="O27" s="30"/>
-      <c r="P27" s="30"/>
-      <c r="Q27" s="30"/>
-      <c r="R27" s="30"/>
-      <c r="T27" s="30"/>
-      <c r="U27" s="30"/>
-      <c r="V27" s="30"/>
-      <c r="W27" s="30"/>
-      <c r="X27" s="30"/>
-      <c r="Y27" s="30"/>
-      <c r="Z27" s="30"/>
-      <c r="AA27" s="30"/>
-      <c r="AB27" s="30"/>
-      <c r="AC27" s="30"/>
-      <c r="AD27" s="30"/>
-      <c r="AE27" s="30"/>
-      <c r="AF27" s="30"/>
-      <c r="AG27" s="30"/>
+      <c r="B27" s="19"/>
+      <c r="E27" s="13"/>
+      <c r="F27" s="13"/>
+      <c r="G27" s="13"/>
+      <c r="H27" s="13"/>
+      <c r="I27" s="13"/>
+      <c r="J27" s="13"/>
+      <c r="K27" s="13"/>
+      <c r="L27" s="13"/>
+      <c r="M27" s="13"/>
+      <c r="N27" s="13"/>
+      <c r="O27" s="13"/>
+      <c r="P27" s="13"/>
+      <c r="Q27" s="13"/>
+      <c r="R27" s="13"/>
+      <c r="T27" s="13"/>
+      <c r="U27" s="13"/>
+      <c r="V27" s="13"/>
+      <c r="W27" s="13"/>
+      <c r="X27" s="13"/>
+      <c r="Y27" s="13"/>
+      <c r="Z27" s="13"/>
+      <c r="AA27" s="13"/>
+      <c r="AB27" s="13"/>
+      <c r="AC27" s="13"/>
+      <c r="AD27" s="13"/>
+      <c r="AE27" s="13"/>
+      <c r="AF27" s="13"/>
+      <c r="AG27" s="13"/>
       <c r="BQ27" s="6"/>
-      <c r="BR27" s="28"/>
+      <c r="BR27" s="19"/>
     </row>
     <row r="28" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B28" s="28"/>
-      <c r="E28" s="30"/>
-      <c r="F28" s="30"/>
-      <c r="G28" s="30"/>
-      <c r="H28" s="30"/>
-      <c r="I28" s="30"/>
-      <c r="J28" s="30"/>
-      <c r="K28" s="30"/>
-      <c r="L28" s="30"/>
-      <c r="M28" s="30"/>
-      <c r="N28" s="30"/>
-      <c r="O28" s="30"/>
-      <c r="P28" s="30"/>
-      <c r="Q28" s="30"/>
-      <c r="R28" s="30"/>
-      <c r="T28" s="30"/>
-      <c r="U28" s="30"/>
-      <c r="V28" s="30"/>
-      <c r="W28" s="30"/>
-      <c r="X28" s="30"/>
-      <c r="Y28" s="30"/>
-      <c r="Z28" s="30"/>
-      <c r="AA28" s="30"/>
-      <c r="AB28" s="30"/>
-      <c r="AC28" s="30"/>
-      <c r="AD28" s="30"/>
-      <c r="AE28" s="30"/>
-      <c r="AF28" s="30"/>
-      <c r="AG28" s="30"/>
-      <c r="AI28" s="32"/>
-      <c r="AJ28" s="33"/>
-      <c r="AK28" s="33"/>
-      <c r="AL28" s="33"/>
-      <c r="AM28" s="33"/>
+      <c r="B28" s="19"/>
+      <c r="E28" s="13"/>
+      <c r="F28" s="13"/>
+      <c r="G28" s="13"/>
+      <c r="H28" s="13"/>
+      <c r="I28" s="13"/>
+      <c r="J28" s="13"/>
+      <c r="K28" s="13"/>
+      <c r="L28" s="13"/>
+      <c r="M28" s="13"/>
+      <c r="N28" s="13"/>
+      <c r="O28" s="13"/>
+      <c r="P28" s="13"/>
+      <c r="Q28" s="13"/>
+      <c r="R28" s="13"/>
+      <c r="T28" s="13"/>
+      <c r="U28" s="13"/>
+      <c r="V28" s="13"/>
+      <c r="W28" s="13"/>
+      <c r="X28" s="13"/>
+      <c r="Y28" s="13"/>
+      <c r="Z28" s="13"/>
+      <c r="AA28" s="13"/>
+      <c r="AB28" s="13"/>
+      <c r="AC28" s="13"/>
+      <c r="AD28" s="13"/>
+      <c r="AE28" s="13"/>
+      <c r="AF28" s="13"/>
+      <c r="AG28" s="13"/>
+      <c r="AI28" s="11"/>
       <c r="AV28" s="6"/>
       <c r="AW28" s="9"/>
       <c r="AX28" s="9"/>
@@ -2891,362 +2883,357 @@
       <c r="BO28" s="9"/>
       <c r="BP28" s="9"/>
       <c r="BQ28" s="9"/>
-      <c r="BR28" s="28"/>
+      <c r="BR28" s="19"/>
     </row>
     <row r="29" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B29" s="24"/>
-      <c r="E29" s="30"/>
-      <c r="F29" s="30"/>
-      <c r="G29" s="30"/>
-      <c r="H29" s="30"/>
-      <c r="I29" s="30"/>
-      <c r="J29" s="30"/>
-      <c r="K29" s="30"/>
-      <c r="L29" s="30"/>
-      <c r="M29" s="30"/>
-      <c r="N29" s="30"/>
-      <c r="O29" s="30"/>
-      <c r="P29" s="30"/>
-      <c r="Q29" s="30"/>
-      <c r="R29" s="30"/>
-      <c r="T29" s="30"/>
-      <c r="U29" s="30"/>
-      <c r="V29" s="30"/>
-      <c r="W29" s="30"/>
-      <c r="X29" s="30"/>
-      <c r="Y29" s="30"/>
-      <c r="Z29" s="30"/>
-      <c r="AA29" s="30"/>
-      <c r="AB29" s="30"/>
-      <c r="AC29" s="30"/>
-      <c r="AD29" s="30"/>
-      <c r="AE29" s="30"/>
-      <c r="AF29" s="30"/>
-      <c r="AG29" s="30"/>
-      <c r="AI29" s="33"/>
-      <c r="AJ29" s="33"/>
-      <c r="AK29" s="33"/>
-      <c r="AL29" s="33"/>
-      <c r="AM29" s="33"/>
+      <c r="B29" s="20"/>
+      <c r="E29" s="13"/>
+      <c r="F29" s="13"/>
+      <c r="G29" s="13"/>
+      <c r="H29" s="13"/>
+      <c r="I29" s="13"/>
+      <c r="J29" s="13"/>
+      <c r="K29" s="13"/>
+      <c r="L29" s="13"/>
+      <c r="M29" s="13"/>
+      <c r="N29" s="13"/>
+      <c r="O29" s="13"/>
+      <c r="P29" s="13"/>
+      <c r="Q29" s="13"/>
+      <c r="R29" s="13"/>
+      <c r="T29" s="13"/>
+      <c r="U29" s="13"/>
+      <c r="V29" s="13"/>
+      <c r="W29" s="13"/>
+      <c r="X29" s="13"/>
+      <c r="Y29" s="13"/>
+      <c r="Z29" s="13"/>
+      <c r="AA29" s="13"/>
+      <c r="AB29" s="13"/>
+      <c r="AC29" s="13"/>
+      <c r="AD29" s="13"/>
+      <c r="AE29" s="13"/>
+      <c r="AF29" s="13"/>
+      <c r="AG29" s="13"/>
       <c r="BQ29" s="6"/>
-      <c r="BR29" s="24"/>
+      <c r="BR29" s="20"/>
     </row>
     <row r="30" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B30" s="23" t="s">
+      <c r="B30" s="18" t="s">
         <v>168</v>
       </c>
-      <c r="BR30" s="23" t="s">
+      <c r="BR30" s="18" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="31" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B31" s="28"/>
-      <c r="AW31" s="18" t="s">
+      <c r="B31" s="19"/>
+      <c r="AW31" s="21" t="s">
         <v>169</v>
       </c>
-      <c r="AX31" s="11"/>
-      <c r="AY31" s="11" t="s">
+      <c r="AX31" s="22"/>
+      <c r="AY31" s="22" t="s">
         <v>170</v>
       </c>
-      <c r="AZ31" s="11"/>
-      <c r="BA31" s="11"/>
-      <c r="BB31" s="11"/>
-      <c r="BC31" s="11"/>
-      <c r="BD31" s="11"/>
-      <c r="BE31" s="11"/>
-      <c r="BF31" s="11"/>
-      <c r="BG31" s="11"/>
-      <c r="BH31" s="11"/>
-      <c r="BI31" s="11"/>
-      <c r="BJ31" s="11"/>
-      <c r="BK31" s="11"/>
-      <c r="BL31" s="11"/>
-      <c r="BM31" s="11"/>
-      <c r="BN31" s="11"/>
-      <c r="BO31" s="11"/>
-      <c r="BP31" s="11"/>
-      <c r="BQ31" s="12"/>
-      <c r="BR31" s="28"/>
+      <c r="AZ31" s="22"/>
+      <c r="BA31" s="22"/>
+      <c r="BB31" s="22"/>
+      <c r="BC31" s="22"/>
+      <c r="BD31" s="22"/>
+      <c r="BE31" s="22"/>
+      <c r="BF31" s="22"/>
+      <c r="BG31" s="22"/>
+      <c r="BH31" s="22"/>
+      <c r="BI31" s="22"/>
+      <c r="BJ31" s="22"/>
+      <c r="BK31" s="22"/>
+      <c r="BL31" s="22"/>
+      <c r="BM31" s="22"/>
+      <c r="BN31" s="22"/>
+      <c r="BO31" s="22"/>
+      <c r="BP31" s="22"/>
+      <c r="BQ31" s="23"/>
+      <c r="BR31" s="19"/>
     </row>
     <row r="32" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B32" s="28"/>
-      <c r="AW32" s="22"/>
-      <c r="AX32" s="13"/>
-      <c r="AY32" s="13"/>
-      <c r="AZ32" s="13"/>
-      <c r="BA32" s="13"/>
-      <c r="BB32" s="13"/>
-      <c r="BC32" s="13"/>
-      <c r="BD32" s="13"/>
-      <c r="BE32" s="13"/>
-      <c r="BF32" s="13"/>
-      <c r="BG32" s="13"/>
-      <c r="BH32" s="13"/>
-      <c r="BI32" s="13"/>
-      <c r="BJ32" s="13"/>
-      <c r="BK32" s="13"/>
-      <c r="BL32" s="13"/>
-      <c r="BM32" s="13"/>
-      <c r="BN32" s="13"/>
-      <c r="BO32" s="13"/>
-      <c r="BP32" s="13"/>
-      <c r="BQ32" s="14"/>
-      <c r="BR32" s="28"/>
+      <c r="B32" s="19"/>
+      <c r="AW32" s="27"/>
+      <c r="AX32" s="28"/>
+      <c r="AY32" s="28"/>
+      <c r="AZ32" s="28"/>
+      <c r="BA32" s="28"/>
+      <c r="BB32" s="28"/>
+      <c r="BC32" s="28"/>
+      <c r="BD32" s="28"/>
+      <c r="BE32" s="28"/>
+      <c r="BF32" s="28"/>
+      <c r="BG32" s="28"/>
+      <c r="BH32" s="28"/>
+      <c r="BI32" s="28"/>
+      <c r="BJ32" s="28"/>
+      <c r="BK32" s="28"/>
+      <c r="BL32" s="28"/>
+      <c r="BM32" s="28"/>
+      <c r="BN32" s="28"/>
+      <c r="BO32" s="28"/>
+      <c r="BP32" s="28"/>
+      <c r="BQ32" s="29"/>
+      <c r="BR32" s="19"/>
     </row>
     <row r="33" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B33" s="28"/>
-      <c r="AW33" s="22"/>
-      <c r="AX33" s="13"/>
-      <c r="AY33" s="13"/>
-      <c r="AZ33" s="13"/>
-      <c r="BA33" s="13"/>
-      <c r="BB33" s="13"/>
-      <c r="BC33" s="13"/>
-      <c r="BD33" s="13"/>
-      <c r="BE33" s="13"/>
-      <c r="BF33" s="13"/>
-      <c r="BG33" s="13"/>
-      <c r="BH33" s="13"/>
-      <c r="BI33" s="13"/>
-      <c r="BJ33" s="13"/>
-      <c r="BK33" s="13"/>
-      <c r="BL33" s="13"/>
-      <c r="BM33" s="13"/>
-      <c r="BN33" s="13"/>
-      <c r="BO33" s="13"/>
-      <c r="BP33" s="13"/>
-      <c r="BQ33" s="14"/>
-      <c r="BR33" s="28"/>
+      <c r="B33" s="19"/>
+      <c r="AW33" s="27"/>
+      <c r="AX33" s="28"/>
+      <c r="AY33" s="28"/>
+      <c r="AZ33" s="28"/>
+      <c r="BA33" s="28"/>
+      <c r="BB33" s="28"/>
+      <c r="BC33" s="28"/>
+      <c r="BD33" s="28"/>
+      <c r="BE33" s="28"/>
+      <c r="BF33" s="28"/>
+      <c r="BG33" s="28"/>
+      <c r="BH33" s="28"/>
+      <c r="BI33" s="28"/>
+      <c r="BJ33" s="28"/>
+      <c r="BK33" s="28"/>
+      <c r="BL33" s="28"/>
+      <c r="BM33" s="28"/>
+      <c r="BN33" s="28"/>
+      <c r="BO33" s="28"/>
+      <c r="BP33" s="28"/>
+      <c r="BQ33" s="29"/>
+      <c r="BR33" s="19"/>
     </row>
     <row r="34" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B34" s="28"/>
-      <c r="AW34" s="22"/>
-      <c r="AX34" s="13"/>
-      <c r="AY34" s="13"/>
-      <c r="AZ34" s="13"/>
-      <c r="BA34" s="13"/>
-      <c r="BB34" s="13"/>
-      <c r="BC34" s="13"/>
-      <c r="BD34" s="13"/>
-      <c r="BE34" s="13"/>
-      <c r="BF34" s="13"/>
-      <c r="BG34" s="13"/>
-      <c r="BH34" s="13"/>
-      <c r="BI34" s="13"/>
-      <c r="BJ34" s="13"/>
-      <c r="BK34" s="13"/>
-      <c r="BL34" s="13"/>
-      <c r="BM34" s="13"/>
-      <c r="BN34" s="13"/>
-      <c r="BO34" s="13"/>
-      <c r="BP34" s="13"/>
-      <c r="BQ34" s="14"/>
-      <c r="BR34" s="28"/>
+      <c r="B34" s="19"/>
+      <c r="AW34" s="27"/>
+      <c r="AX34" s="28"/>
+      <c r="AY34" s="28"/>
+      <c r="AZ34" s="28"/>
+      <c r="BA34" s="28"/>
+      <c r="BB34" s="28"/>
+      <c r="BC34" s="28"/>
+      <c r="BD34" s="28"/>
+      <c r="BE34" s="28"/>
+      <c r="BF34" s="28"/>
+      <c r="BG34" s="28"/>
+      <c r="BH34" s="28"/>
+      <c r="BI34" s="28"/>
+      <c r="BJ34" s="28"/>
+      <c r="BK34" s="28"/>
+      <c r="BL34" s="28"/>
+      <c r="BM34" s="28"/>
+      <c r="BN34" s="28"/>
+      <c r="BO34" s="28"/>
+      <c r="BP34" s="28"/>
+      <c r="BQ34" s="29"/>
+      <c r="BR34" s="19"/>
     </row>
     <row r="35" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B35" s="28"/>
-      <c r="E35" s="29" t="s">
-        <v>235</v>
-      </c>
-      <c r="F35" s="30"/>
-      <c r="G35" s="30"/>
-      <c r="H35" s="30"/>
-      <c r="I35" s="30"/>
-      <c r="J35" s="30"/>
-      <c r="K35" s="30"/>
-      <c r="L35" s="30"/>
-      <c r="M35" s="30"/>
-      <c r="N35" s="30"/>
-      <c r="O35" s="30"/>
-      <c r="P35" s="30"/>
-      <c r="Q35" s="30"/>
-      <c r="R35" s="30"/>
-      <c r="T35" s="29" t="s">
+      <c r="B35" s="19"/>
+      <c r="E35" s="12" t="s">
+        <v>233</v>
+      </c>
+      <c r="F35" s="13"/>
+      <c r="G35" s="13"/>
+      <c r="H35" s="13"/>
+      <c r="I35" s="13"/>
+      <c r="J35" s="13"/>
+      <c r="K35" s="13"/>
+      <c r="L35" s="13"/>
+      <c r="M35" s="13"/>
+      <c r="N35" s="13"/>
+      <c r="O35" s="13"/>
+      <c r="P35" s="13"/>
+      <c r="Q35" s="13"/>
+      <c r="R35" s="13"/>
+      <c r="T35" s="12" t="s">
         <v>172</v>
       </c>
-      <c r="U35" s="30"/>
-      <c r="V35" s="30"/>
-      <c r="W35" s="30"/>
-      <c r="X35" s="30"/>
-      <c r="Y35" s="30"/>
-      <c r="Z35" s="30"/>
-      <c r="AA35" s="30"/>
-      <c r="AB35" s="30"/>
-      <c r="AC35" s="30"/>
-      <c r="AD35" s="30"/>
-      <c r="AE35" s="30"/>
-      <c r="AF35" s="30"/>
-      <c r="AG35" s="30"/>
-      <c r="AW35" s="22"/>
-      <c r="AX35" s="13"/>
-      <c r="AY35" s="13"/>
-      <c r="AZ35" s="13"/>
-      <c r="BA35" s="13"/>
-      <c r="BB35" s="13"/>
-      <c r="BC35" s="13"/>
-      <c r="BD35" s="13"/>
-      <c r="BE35" s="13"/>
-      <c r="BF35" s="13"/>
-      <c r="BG35" s="13"/>
-      <c r="BH35" s="13"/>
-      <c r="BI35" s="13"/>
-      <c r="BJ35" s="13"/>
-      <c r="BK35" s="13"/>
-      <c r="BL35" s="13"/>
-      <c r="BM35" s="13"/>
-      <c r="BN35" s="13"/>
-      <c r="BO35" s="13"/>
-      <c r="BP35" s="13"/>
-      <c r="BQ35" s="14"/>
-      <c r="BR35" s="28"/>
+      <c r="U35" s="13"/>
+      <c r="V35" s="13"/>
+      <c r="W35" s="13"/>
+      <c r="X35" s="13"/>
+      <c r="Y35" s="13"/>
+      <c r="Z35" s="13"/>
+      <c r="AA35" s="13"/>
+      <c r="AB35" s="13"/>
+      <c r="AC35" s="13"/>
+      <c r="AD35" s="13"/>
+      <c r="AE35" s="13"/>
+      <c r="AF35" s="13"/>
+      <c r="AG35" s="13"/>
+      <c r="AW35" s="27"/>
+      <c r="AX35" s="28"/>
+      <c r="AY35" s="28"/>
+      <c r="AZ35" s="28"/>
+      <c r="BA35" s="28"/>
+      <c r="BB35" s="28"/>
+      <c r="BC35" s="28"/>
+      <c r="BD35" s="28"/>
+      <c r="BE35" s="28"/>
+      <c r="BF35" s="28"/>
+      <c r="BG35" s="28"/>
+      <c r="BH35" s="28"/>
+      <c r="BI35" s="28"/>
+      <c r="BJ35" s="28"/>
+      <c r="BK35" s="28"/>
+      <c r="BL35" s="28"/>
+      <c r="BM35" s="28"/>
+      <c r="BN35" s="28"/>
+      <c r="BO35" s="28"/>
+      <c r="BP35" s="28"/>
+      <c r="BQ35" s="29"/>
+      <c r="BR35" s="19"/>
     </row>
     <row r="36" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B36" s="28"/>
-      <c r="E36" s="30"/>
-      <c r="F36" s="30"/>
-      <c r="G36" s="30"/>
-      <c r="H36" s="30"/>
-      <c r="I36" s="30"/>
-      <c r="J36" s="30"/>
-      <c r="K36" s="30"/>
-      <c r="L36" s="30"/>
-      <c r="M36" s="30"/>
-      <c r="N36" s="30"/>
-      <c r="O36" s="30"/>
-      <c r="P36" s="30"/>
-      <c r="Q36" s="30"/>
-      <c r="R36" s="30"/>
-      <c r="T36" s="30"/>
-      <c r="U36" s="30"/>
-      <c r="V36" s="30"/>
-      <c r="W36" s="30"/>
-      <c r="X36" s="30"/>
-      <c r="Y36" s="30"/>
-      <c r="Z36" s="30"/>
-      <c r="AA36" s="30"/>
-      <c r="AB36" s="30"/>
-      <c r="AC36" s="30"/>
-      <c r="AD36" s="30"/>
-      <c r="AE36" s="30"/>
-      <c r="AF36" s="30"/>
-      <c r="AG36" s="30"/>
-      <c r="AW36" s="19"/>
-      <c r="AX36" s="20"/>
-      <c r="AY36" s="20"/>
-      <c r="AZ36" s="20"/>
-      <c r="BA36" s="20"/>
-      <c r="BB36" s="20"/>
-      <c r="BC36" s="20"/>
-      <c r="BD36" s="20"/>
-      <c r="BE36" s="20"/>
-      <c r="BF36" s="20"/>
-      <c r="BG36" s="20"/>
-      <c r="BH36" s="20"/>
-      <c r="BI36" s="20"/>
-      <c r="BJ36" s="20"/>
-      <c r="BK36" s="20"/>
-      <c r="BL36" s="20"/>
-      <c r="BM36" s="20"/>
-      <c r="BN36" s="20"/>
-      <c r="BO36" s="20"/>
-      <c r="BP36" s="20"/>
-      <c r="BQ36" s="21"/>
-      <c r="BR36" s="28"/>
+      <c r="B36" s="19"/>
+      <c r="E36" s="13"/>
+      <c r="F36" s="13"/>
+      <c r="G36" s="13"/>
+      <c r="H36" s="13"/>
+      <c r="I36" s="13"/>
+      <c r="J36" s="13"/>
+      <c r="K36" s="13"/>
+      <c r="L36" s="13"/>
+      <c r="M36" s="13"/>
+      <c r="N36" s="13"/>
+      <c r="O36" s="13"/>
+      <c r="P36" s="13"/>
+      <c r="Q36" s="13"/>
+      <c r="R36" s="13"/>
+      <c r="T36" s="13"/>
+      <c r="U36" s="13"/>
+      <c r="V36" s="13"/>
+      <c r="W36" s="13"/>
+      <c r="X36" s="13"/>
+      <c r="Y36" s="13"/>
+      <c r="Z36" s="13"/>
+      <c r="AA36" s="13"/>
+      <c r="AB36" s="13"/>
+      <c r="AC36" s="13"/>
+      <c r="AD36" s="13"/>
+      <c r="AE36" s="13"/>
+      <c r="AF36" s="13"/>
+      <c r="AG36" s="13"/>
+      <c r="AW36" s="24"/>
+      <c r="AX36" s="25"/>
+      <c r="AY36" s="25"/>
+      <c r="AZ36" s="25"/>
+      <c r="BA36" s="25"/>
+      <c r="BB36" s="25"/>
+      <c r="BC36" s="25"/>
+      <c r="BD36" s="25"/>
+      <c r="BE36" s="25"/>
+      <c r="BF36" s="25"/>
+      <c r="BG36" s="25"/>
+      <c r="BH36" s="25"/>
+      <c r="BI36" s="25"/>
+      <c r="BJ36" s="25"/>
+      <c r="BK36" s="25"/>
+      <c r="BL36" s="25"/>
+      <c r="BM36" s="25"/>
+      <c r="BN36" s="25"/>
+      <c r="BO36" s="25"/>
+      <c r="BP36" s="25"/>
+      <c r="BQ36" s="26"/>
+      <c r="BR36" s="19"/>
     </row>
     <row r="37" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B37" s="28"/>
-      <c r="E37" s="30"/>
-      <c r="F37" s="30"/>
-      <c r="G37" s="30"/>
-      <c r="H37" s="30"/>
-      <c r="I37" s="30"/>
-      <c r="J37" s="30"/>
-      <c r="K37" s="30"/>
-      <c r="L37" s="30"/>
-      <c r="M37" s="30"/>
-      <c r="N37" s="30"/>
-      <c r="O37" s="30"/>
-      <c r="P37" s="30"/>
-      <c r="Q37" s="30"/>
-      <c r="R37" s="30"/>
-      <c r="T37" s="30"/>
-      <c r="U37" s="30"/>
-      <c r="V37" s="30"/>
-      <c r="W37" s="30"/>
-      <c r="X37" s="30"/>
-      <c r="Y37" s="30"/>
-      <c r="Z37" s="30"/>
-      <c r="AA37" s="30"/>
-      <c r="AB37" s="30"/>
-      <c r="AC37" s="30"/>
-      <c r="AD37" s="30"/>
-      <c r="AE37" s="30"/>
-      <c r="AF37" s="30"/>
-      <c r="AG37" s="30"/>
-      <c r="BR37" s="28"/>
+      <c r="B37" s="19"/>
+      <c r="E37" s="13"/>
+      <c r="F37" s="13"/>
+      <c r="G37" s="13"/>
+      <c r="H37" s="13"/>
+      <c r="I37" s="13"/>
+      <c r="J37" s="13"/>
+      <c r="K37" s="13"/>
+      <c r="L37" s="13"/>
+      <c r="M37" s="13"/>
+      <c r="N37" s="13"/>
+      <c r="O37" s="13"/>
+      <c r="P37" s="13"/>
+      <c r="Q37" s="13"/>
+      <c r="R37" s="13"/>
+      <c r="T37" s="13"/>
+      <c r="U37" s="13"/>
+      <c r="V37" s="13"/>
+      <c r="W37" s="13"/>
+      <c r="X37" s="13"/>
+      <c r="Y37" s="13"/>
+      <c r="Z37" s="13"/>
+      <c r="AA37" s="13"/>
+      <c r="AB37" s="13"/>
+      <c r="AC37" s="13"/>
+      <c r="AD37" s="13"/>
+      <c r="AE37" s="13"/>
+      <c r="AF37" s="13"/>
+      <c r="AG37" s="13"/>
+      <c r="BR37" s="19"/>
     </row>
     <row r="38" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B38" s="28"/>
-      <c r="E38" s="30"/>
-      <c r="F38" s="30"/>
-      <c r="G38" s="30"/>
-      <c r="H38" s="30"/>
-      <c r="I38" s="30"/>
-      <c r="J38" s="30"/>
-      <c r="K38" s="30"/>
-      <c r="L38" s="30"/>
-      <c r="M38" s="30"/>
-      <c r="N38" s="30"/>
-      <c r="O38" s="30"/>
-      <c r="P38" s="30"/>
-      <c r="Q38" s="30"/>
-      <c r="R38" s="30"/>
-      <c r="T38" s="30"/>
-      <c r="U38" s="30"/>
-      <c r="V38" s="30"/>
-      <c r="W38" s="30"/>
-      <c r="X38" s="30"/>
-      <c r="Y38" s="30"/>
-      <c r="Z38" s="30"/>
-      <c r="AA38" s="30"/>
-      <c r="AB38" s="30"/>
-      <c r="AC38" s="30"/>
-      <c r="AD38" s="30"/>
-      <c r="AE38" s="30"/>
-      <c r="AF38" s="30"/>
-      <c r="AG38" s="30"/>
-      <c r="BR38" s="28"/>
+      <c r="B38" s="19"/>
+      <c r="E38" s="13"/>
+      <c r="F38" s="13"/>
+      <c r="G38" s="13"/>
+      <c r="H38" s="13"/>
+      <c r="I38" s="13"/>
+      <c r="J38" s="13"/>
+      <c r="K38" s="13"/>
+      <c r="L38" s="13"/>
+      <c r="M38" s="13"/>
+      <c r="N38" s="13"/>
+      <c r="O38" s="13"/>
+      <c r="P38" s="13"/>
+      <c r="Q38" s="13"/>
+      <c r="R38" s="13"/>
+      <c r="T38" s="13"/>
+      <c r="U38" s="13"/>
+      <c r="V38" s="13"/>
+      <c r="W38" s="13"/>
+      <c r="X38" s="13"/>
+      <c r="Y38" s="13"/>
+      <c r="Z38" s="13"/>
+      <c r="AA38" s="13"/>
+      <c r="AB38" s="13"/>
+      <c r="AC38" s="13"/>
+      <c r="AD38" s="13"/>
+      <c r="AE38" s="13"/>
+      <c r="AF38" s="13"/>
+      <c r="AG38" s="13"/>
+      <c r="BR38" s="19"/>
     </row>
     <row r="39" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B39" s="28"/>
-      <c r="E39" s="30"/>
-      <c r="F39" s="30"/>
-      <c r="G39" s="30"/>
-      <c r="H39" s="30"/>
-      <c r="I39" s="30"/>
-      <c r="J39" s="30"/>
-      <c r="K39" s="30"/>
-      <c r="L39" s="30"/>
-      <c r="M39" s="30"/>
-      <c r="N39" s="30"/>
-      <c r="O39" s="30"/>
-      <c r="P39" s="30"/>
-      <c r="Q39" s="30"/>
-      <c r="R39" s="30"/>
-      <c r="T39" s="30"/>
-      <c r="U39" s="30"/>
-      <c r="V39" s="30"/>
-      <c r="W39" s="30"/>
-      <c r="X39" s="30"/>
-      <c r="Y39" s="30"/>
-      <c r="Z39" s="30"/>
-      <c r="AA39" s="30"/>
-      <c r="AB39" s="30"/>
-      <c r="AC39" s="30"/>
-      <c r="AD39" s="30"/>
-      <c r="AE39" s="30"/>
-      <c r="AF39" s="30"/>
-      <c r="AG39" s="30"/>
+      <c r="B39" s="19"/>
+      <c r="E39" s="13"/>
+      <c r="F39" s="13"/>
+      <c r="G39" s="13"/>
+      <c r="H39" s="13"/>
+      <c r="I39" s="13"/>
+      <c r="J39" s="13"/>
+      <c r="K39" s="13"/>
+      <c r="L39" s="13"/>
+      <c r="M39" s="13"/>
+      <c r="N39" s="13"/>
+      <c r="O39" s="13"/>
+      <c r="P39" s="13"/>
+      <c r="Q39" s="13"/>
+      <c r="R39" s="13"/>
+      <c r="T39" s="13"/>
+      <c r="U39" s="13"/>
+      <c r="V39" s="13"/>
+      <c r="W39" s="13"/>
+      <c r="X39" s="13"/>
+      <c r="Y39" s="13"/>
+      <c r="Z39" s="13"/>
+      <c r="AA39" s="13"/>
+      <c r="AB39" s="13"/>
+      <c r="AC39" s="13"/>
+      <c r="AD39" s="13"/>
+      <c r="AE39" s="13"/>
+      <c r="AF39" s="13"/>
+      <c r="AG39" s="13"/>
       <c r="AW39" s="1" t="s">
         <v>173</v>
       </c>
@@ -3280,10 +3267,10 @@
       </c>
       <c r="BP39" s="16"/>
       <c r="BQ39" s="17"/>
-      <c r="BR39" s="28"/>
+      <c r="BR39" s="19"/>
     </row>
     <row r="40" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B40" s="28"/>
+      <c r="B40" s="19"/>
       <c r="AW40" s="5" t="s">
         <v>179</v>
       </c>
@@ -3317,10 +3304,10 @@
       </c>
       <c r="BP40" s="16"/>
       <c r="BQ40" s="17"/>
-      <c r="BR40" s="28"/>
+      <c r="BR40" s="19"/>
     </row>
     <row r="41" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B41" s="28"/>
+      <c r="B41" s="19"/>
       <c r="AW41" s="5" t="s">
         <v>185</v>
       </c>
@@ -3354,10 +3341,10 @@
       </c>
       <c r="BP41" s="16"/>
       <c r="BQ41" s="17"/>
-      <c r="BR41" s="28"/>
+      <c r="BR41" s="19"/>
     </row>
     <row r="42" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B42" s="28"/>
+      <c r="B42" s="19"/>
       <c r="AW42" s="5" t="s">
         <v>191</v>
       </c>
@@ -3391,76 +3378,76 @@
       </c>
       <c r="BP42" s="16"/>
       <c r="BQ42" s="17"/>
-      <c r="BR42" s="28"/>
+      <c r="BR42" s="19"/>
     </row>
     <row r="43" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B43" s="24"/>
-      <c r="AW43" s="23" t="s">
+      <c r="B43" s="20"/>
+      <c r="AW43" s="18" t="s">
         <v>197</v>
       </c>
-      <c r="AX43" s="18" t="s">
+      <c r="AX43" s="21" t="s">
         <v>198</v>
       </c>
-      <c r="AY43" s="11"/>
-      <c r="AZ43" s="12"/>
-      <c r="BA43" s="18" t="s">
+      <c r="AY43" s="22"/>
+      <c r="AZ43" s="23"/>
+      <c r="BA43" s="21" t="s">
         <v>199</v>
       </c>
-      <c r="BB43" s="11"/>
-      <c r="BC43" s="11"/>
-      <c r="BD43" s="11"/>
-      <c r="BE43" s="11"/>
-      <c r="BF43" s="11"/>
-      <c r="BG43" s="11"/>
-      <c r="BH43" s="12"/>
-      <c r="BI43" s="18" t="s">
+      <c r="BB43" s="22"/>
+      <c r="BC43" s="22"/>
+      <c r="BD43" s="22"/>
+      <c r="BE43" s="22"/>
+      <c r="BF43" s="22"/>
+      <c r="BG43" s="22"/>
+      <c r="BH43" s="23"/>
+      <c r="BI43" s="21" t="s">
         <v>200</v>
       </c>
-      <c r="BJ43" s="11"/>
-      <c r="BK43" s="12"/>
-      <c r="BL43" s="18" t="s">
+      <c r="BJ43" s="22"/>
+      <c r="BK43" s="23"/>
+      <c r="BL43" s="21" t="s">
         <v>201</v>
       </c>
-      <c r="BM43" s="11"/>
-      <c r="BN43" s="12"/>
-      <c r="BO43" s="18" t="s">
+      <c r="BM43" s="22"/>
+      <c r="BN43" s="23"/>
+      <c r="BO43" s="21" t="s">
         <v>202</v>
       </c>
-      <c r="BP43" s="11"/>
-      <c r="BQ43" s="12"/>
-      <c r="BR43" s="24"/>
+      <c r="BP43" s="22"/>
+      <c r="BQ43" s="23"/>
+      <c r="BR43" s="20"/>
     </row>
     <row r="44" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B44" s="23" t="s">
+      <c r="B44" s="18" t="s">
         <v>203</v>
       </c>
-      <c r="AW44" s="24"/>
-      <c r="AX44" s="19"/>
-      <c r="AY44" s="20"/>
-      <c r="AZ44" s="21"/>
-      <c r="BA44" s="19"/>
-      <c r="BB44" s="20"/>
-      <c r="BC44" s="20"/>
-      <c r="BD44" s="20"/>
-      <c r="BE44" s="20"/>
-      <c r="BF44" s="20"/>
-      <c r="BG44" s="20"/>
-      <c r="BH44" s="21"/>
-      <c r="BI44" s="19"/>
-      <c r="BJ44" s="20"/>
-      <c r="BK44" s="21"/>
-      <c r="BL44" s="19"/>
-      <c r="BM44" s="20"/>
-      <c r="BN44" s="21"/>
-      <c r="BO44" s="19"/>
-      <c r="BP44" s="20"/>
-      <c r="BQ44" s="21"/>
-      <c r="BR44" s="23" t="s">
+      <c r="AW44" s="20"/>
+      <c r="AX44" s="24"/>
+      <c r="AY44" s="25"/>
+      <c r="AZ44" s="26"/>
+      <c r="BA44" s="24"/>
+      <c r="BB44" s="25"/>
+      <c r="BC44" s="25"/>
+      <c r="BD44" s="25"/>
+      <c r="BE44" s="25"/>
+      <c r="BF44" s="25"/>
+      <c r="BG44" s="25"/>
+      <c r="BH44" s="26"/>
+      <c r="BI44" s="24"/>
+      <c r="BJ44" s="25"/>
+      <c r="BK44" s="26"/>
+      <c r="BL44" s="24"/>
+      <c r="BM44" s="25"/>
+      <c r="BN44" s="26"/>
+      <c r="BO44" s="24"/>
+      <c r="BP44" s="25"/>
+      <c r="BQ44" s="26"/>
+      <c r="BR44" s="18" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="45" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B45" s="28"/>
+      <c r="B45" s="19"/>
       <c r="AW45" s="5" t="s">
         <v>204</v>
       </c>
@@ -3494,10 +3481,10 @@
       </c>
       <c r="BP45" s="16"/>
       <c r="BQ45" s="17"/>
-      <c r="BR45" s="28"/>
+      <c r="BR45" s="19"/>
     </row>
     <row r="46" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B46" s="28"/>
+      <c r="B46" s="19"/>
       <c r="AW46" s="15" t="s">
         <v>210</v>
       </c>
@@ -3525,42 +3512,42 @@
       <c r="BO46" s="16"/>
       <c r="BP46" s="16"/>
       <c r="BQ46" s="17"/>
-      <c r="BR46" s="28"/>
+      <c r="BR46" s="19"/>
     </row>
     <row r="47" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B47" s="28"/>
-      <c r="E47" s="29" t="s">
-        <v>236</v>
-      </c>
-      <c r="F47" s="30"/>
-      <c r="G47" s="30"/>
-      <c r="H47" s="30"/>
-      <c r="I47" s="30"/>
-      <c r="J47" s="30"/>
-      <c r="K47" s="30"/>
-      <c r="L47" s="30"/>
-      <c r="M47" s="30"/>
-      <c r="N47" s="30"/>
-      <c r="O47" s="30"/>
-      <c r="P47" s="30"/>
-      <c r="Q47" s="30"/>
-      <c r="R47" s="30"/>
-      <c r="T47" s="29" t="s">
-        <v>237</v>
-      </c>
-      <c r="U47" s="30"/>
-      <c r="V47" s="30"/>
-      <c r="W47" s="30"/>
-      <c r="X47" s="30"/>
-      <c r="Y47" s="30"/>
-      <c r="Z47" s="30"/>
-      <c r="AA47" s="30"/>
-      <c r="AB47" s="30"/>
-      <c r="AC47" s="30"/>
-      <c r="AD47" s="30"/>
-      <c r="AE47" s="30"/>
-      <c r="AF47" s="30"/>
-      <c r="AG47" s="30"/>
+      <c r="B47" s="19"/>
+      <c r="E47" s="12" t="s">
+        <v>234</v>
+      </c>
+      <c r="F47" s="13"/>
+      <c r="G47" s="13"/>
+      <c r="H47" s="13"/>
+      <c r="I47" s="13"/>
+      <c r="J47" s="13"/>
+      <c r="K47" s="13"/>
+      <c r="L47" s="13"/>
+      <c r="M47" s="13"/>
+      <c r="N47" s="13"/>
+      <c r="O47" s="13"/>
+      <c r="P47" s="13"/>
+      <c r="Q47" s="13"/>
+      <c r="R47" s="13"/>
+      <c r="T47" s="12" t="s">
+        <v>235</v>
+      </c>
+      <c r="U47" s="13"/>
+      <c r="V47" s="13"/>
+      <c r="W47" s="13"/>
+      <c r="X47" s="13"/>
+      <c r="Y47" s="13"/>
+      <c r="Z47" s="13"/>
+      <c r="AA47" s="13"/>
+      <c r="AB47" s="13"/>
+      <c r="AC47" s="13"/>
+      <c r="AD47" s="13"/>
+      <c r="AE47" s="13"/>
+      <c r="AF47" s="13"/>
+      <c r="AG47" s="13"/>
       <c r="AW47" s="15" t="s">
         <v>213</v>
       </c>
@@ -3588,352 +3575,350 @@
       <c r="BO47" s="16"/>
       <c r="BP47" s="16"/>
       <c r="BQ47" s="17"/>
-      <c r="BR47" s="28"/>
+      <c r="BR47" s="19"/>
     </row>
     <row r="48" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B48" s="28"/>
-      <c r="E48" s="30"/>
-      <c r="F48" s="30"/>
-      <c r="G48" s="30"/>
-      <c r="H48" s="30"/>
-      <c r="I48" s="30"/>
-      <c r="J48" s="30"/>
-      <c r="K48" s="30"/>
-      <c r="L48" s="30"/>
-      <c r="M48" s="30"/>
-      <c r="N48" s="30"/>
-      <c r="O48" s="30"/>
-      <c r="P48" s="30"/>
-      <c r="Q48" s="30"/>
-      <c r="R48" s="30"/>
-      <c r="T48" s="30"/>
-      <c r="U48" s="30"/>
-      <c r="V48" s="30"/>
-      <c r="W48" s="30"/>
-      <c r="X48" s="30"/>
-      <c r="Y48" s="30"/>
-      <c r="Z48" s="30"/>
-      <c r="AA48" s="30"/>
-      <c r="AB48" s="30"/>
-      <c r="AC48" s="30"/>
-      <c r="AD48" s="30"/>
-      <c r="AE48" s="30"/>
-      <c r="AF48" s="30"/>
-      <c r="AG48" s="30"/>
-      <c r="AW48" s="18" t="s">
+      <c r="B48" s="19"/>
+      <c r="E48" s="13"/>
+      <c r="F48" s="13"/>
+      <c r="G48" s="13"/>
+      <c r="H48" s="13"/>
+      <c r="I48" s="13"/>
+      <c r="J48" s="13"/>
+      <c r="K48" s="13"/>
+      <c r="L48" s="13"/>
+      <c r="M48" s="13"/>
+      <c r="N48" s="13"/>
+      <c r="O48" s="13"/>
+      <c r="P48" s="13"/>
+      <c r="Q48" s="13"/>
+      <c r="R48" s="13"/>
+      <c r="T48" s="13"/>
+      <c r="U48" s="13"/>
+      <c r="V48" s="13"/>
+      <c r="W48" s="13"/>
+      <c r="X48" s="13"/>
+      <c r="Y48" s="13"/>
+      <c r="Z48" s="13"/>
+      <c r="AA48" s="13"/>
+      <c r="AB48" s="13"/>
+      <c r="AC48" s="13"/>
+      <c r="AD48" s="13"/>
+      <c r="AE48" s="13"/>
+      <c r="AF48" s="13"/>
+      <c r="AG48" s="13"/>
+      <c r="AW48" s="21" t="s">
         <v>216</v>
       </c>
-      <c r="AX48" s="11"/>
-      <c r="AY48" s="11"/>
-      <c r="AZ48" s="11"/>
-      <c r="BA48" s="11"/>
-      <c r="BB48" s="11"/>
-      <c r="BC48" s="11"/>
-      <c r="BD48" s="12"/>
-      <c r="BE48" s="18" t="s">
+      <c r="AX48" s="22"/>
+      <c r="AY48" s="22"/>
+      <c r="AZ48" s="22"/>
+      <c r="BA48" s="22"/>
+      <c r="BB48" s="22"/>
+      <c r="BC48" s="22"/>
+      <c r="BD48" s="23"/>
+      <c r="BE48" s="21" t="s">
         <v>217</v>
       </c>
-      <c r="BF48" s="11"/>
-      <c r="BG48" s="11"/>
-      <c r="BH48" s="11"/>
-      <c r="BI48" s="11"/>
-      <c r="BJ48" s="11"/>
-      <c r="BK48" s="11"/>
-      <c r="BL48" s="11"/>
-      <c r="BM48" s="11"/>
-      <c r="BN48" s="11"/>
-      <c r="BO48" s="11"/>
-      <c r="BP48" s="11"/>
-      <c r="BQ48" s="12"/>
-      <c r="BR48" s="28"/>
+      <c r="BF48" s="22"/>
+      <c r="BG48" s="22"/>
+      <c r="BH48" s="22"/>
+      <c r="BI48" s="22"/>
+      <c r="BJ48" s="22"/>
+      <c r="BK48" s="22"/>
+      <c r="BL48" s="22"/>
+      <c r="BM48" s="22"/>
+      <c r="BN48" s="22"/>
+      <c r="BO48" s="22"/>
+      <c r="BP48" s="22"/>
+      <c r="BQ48" s="23"/>
+      <c r="BR48" s="19"/>
     </row>
     <row r="49" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B49" s="28"/>
-      <c r="E49" s="30"/>
-      <c r="F49" s="30"/>
-      <c r="G49" s="30"/>
-      <c r="H49" s="30"/>
-      <c r="I49" s="30"/>
-      <c r="J49" s="30"/>
-      <c r="K49" s="30"/>
-      <c r="L49" s="30"/>
-      <c r="M49" s="30"/>
-      <c r="N49" s="30"/>
-      <c r="O49" s="30"/>
-      <c r="P49" s="30"/>
-      <c r="Q49" s="30"/>
-      <c r="R49" s="30"/>
-      <c r="T49" s="30"/>
-      <c r="U49" s="30"/>
-      <c r="V49" s="30"/>
-      <c r="W49" s="30"/>
-      <c r="X49" s="30"/>
-      <c r="Y49" s="30"/>
-      <c r="Z49" s="30"/>
-      <c r="AA49" s="30"/>
-      <c r="AB49" s="30"/>
-      <c r="AC49" s="30"/>
-      <c r="AD49" s="30"/>
-      <c r="AE49" s="30"/>
-      <c r="AF49" s="30"/>
-      <c r="AG49" s="30"/>
-      <c r="AW49" s="22" t="s">
+      <c r="B49" s="19"/>
+      <c r="E49" s="13"/>
+      <c r="F49" s="13"/>
+      <c r="G49" s="13"/>
+      <c r="H49" s="13"/>
+      <c r="I49" s="13"/>
+      <c r="J49" s="13"/>
+      <c r="K49" s="13"/>
+      <c r="L49" s="13"/>
+      <c r="M49" s="13"/>
+      <c r="N49" s="13"/>
+      <c r="O49" s="13"/>
+      <c r="P49" s="13"/>
+      <c r="Q49" s="13"/>
+      <c r="R49" s="13"/>
+      <c r="T49" s="13"/>
+      <c r="U49" s="13"/>
+      <c r="V49" s="13"/>
+      <c r="W49" s="13"/>
+      <c r="X49" s="13"/>
+      <c r="Y49" s="13"/>
+      <c r="Z49" s="13"/>
+      <c r="AA49" s="13"/>
+      <c r="AB49" s="13"/>
+      <c r="AC49" s="13"/>
+      <c r="AD49" s="13"/>
+      <c r="AE49" s="13"/>
+      <c r="AF49" s="13"/>
+      <c r="AG49" s="13"/>
+      <c r="AW49" s="27"/>
+      <c r="AX49" s="28"/>
+      <c r="AY49" s="28"/>
+      <c r="AZ49" s="28"/>
+      <c r="BA49" s="28"/>
+      <c r="BB49" s="28"/>
+      <c r="BC49" s="28"/>
+      <c r="BD49" s="29"/>
+      <c r="BE49" s="24"/>
+      <c r="BF49" s="25"/>
+      <c r="BG49" s="25"/>
+      <c r="BH49" s="25"/>
+      <c r="BI49" s="25"/>
+      <c r="BJ49" s="25"/>
+      <c r="BK49" s="25"/>
+      <c r="BL49" s="25"/>
+      <c r="BM49" s="25"/>
+      <c r="BN49" s="25"/>
+      <c r="BO49" s="25"/>
+      <c r="BP49" s="25"/>
+      <c r="BQ49" s="26"/>
+      <c r="BR49" s="19"/>
+    </row>
+    <row r="50" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B50" s="19"/>
+      <c r="E50" s="13"/>
+      <c r="F50" s="13"/>
+      <c r="G50" s="13"/>
+      <c r="H50" s="13"/>
+      <c r="I50" s="13"/>
+      <c r="J50" s="13"/>
+      <c r="K50" s="13"/>
+      <c r="L50" s="13"/>
+      <c r="M50" s="13"/>
+      <c r="N50" s="13"/>
+      <c r="O50" s="13"/>
+      <c r="P50" s="13"/>
+      <c r="Q50" s="13"/>
+      <c r="R50" s="13"/>
+      <c r="T50" s="13"/>
+      <c r="U50" s="13"/>
+      <c r="V50" s="13"/>
+      <c r="W50" s="13"/>
+      <c r="X50" s="13"/>
+      <c r="Y50" s="13"/>
+      <c r="Z50" s="13"/>
+      <c r="AA50" s="13"/>
+      <c r="AB50" s="13"/>
+      <c r="AC50" s="13"/>
+      <c r="AD50" s="13"/>
+      <c r="AE50" s="13"/>
+      <c r="AF50" s="13"/>
+      <c r="AG50" s="13"/>
+      <c r="AW50" s="27"/>
+      <c r="AX50" s="28"/>
+      <c r="AY50" s="28"/>
+      <c r="AZ50" s="28"/>
+      <c r="BA50" s="28"/>
+      <c r="BB50" s="28"/>
+      <c r="BC50" s="28"/>
+      <c r="BD50" s="29"/>
+      <c r="BE50" s="21" t="s">
         <v>218</v>
       </c>
-      <c r="AX49" s="13"/>
-      <c r="AY49" s="13"/>
-      <c r="AZ49" s="13"/>
-      <c r="BA49" s="13"/>
-      <c r="BB49" s="13"/>
-      <c r="BC49" s="13"/>
-      <c r="BD49" s="14"/>
-      <c r="BE49" s="19"/>
-      <c r="BF49" s="20"/>
-      <c r="BG49" s="20"/>
-      <c r="BH49" s="20"/>
-      <c r="BI49" s="20"/>
-      <c r="BJ49" s="20"/>
-      <c r="BK49" s="20"/>
-      <c r="BL49" s="20"/>
-      <c r="BM49" s="20"/>
-      <c r="BN49" s="20"/>
-      <c r="BO49" s="20"/>
-      <c r="BP49" s="20"/>
-      <c r="BQ49" s="21"/>
-      <c r="BR49" s="28"/>
-    </row>
-    <row r="50" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B50" s="28"/>
-      <c r="E50" s="30"/>
-      <c r="F50" s="30"/>
-      <c r="G50" s="30"/>
-      <c r="H50" s="30"/>
-      <c r="I50" s="30"/>
-      <c r="J50" s="30"/>
-      <c r="K50" s="30"/>
-      <c r="L50" s="30"/>
-      <c r="M50" s="30"/>
-      <c r="N50" s="30"/>
-      <c r="O50" s="30"/>
-      <c r="P50" s="30"/>
-      <c r="Q50" s="30"/>
-      <c r="R50" s="30"/>
-      <c r="T50" s="30"/>
-      <c r="U50" s="30"/>
-      <c r="V50" s="30"/>
-      <c r="W50" s="30"/>
-      <c r="X50" s="30"/>
-      <c r="Y50" s="30"/>
-      <c r="Z50" s="30"/>
-      <c r="AA50" s="30"/>
-      <c r="AB50" s="30"/>
-      <c r="AC50" s="30"/>
-      <c r="AD50" s="30"/>
-      <c r="AE50" s="30"/>
-      <c r="AF50" s="30"/>
-      <c r="AG50" s="30"/>
-      <c r="AW50" s="22"/>
-      <c r="AX50" s="13"/>
-      <c r="AY50" s="13"/>
-      <c r="AZ50" s="13"/>
-      <c r="BA50" s="13"/>
-      <c r="BB50" s="13"/>
-      <c r="BC50" s="13"/>
-      <c r="BD50" s="14"/>
-      <c r="BE50" s="18" t="s">
+      <c r="BF50" s="22"/>
+      <c r="BG50" s="22"/>
+      <c r="BH50" s="22"/>
+      <c r="BI50" s="22"/>
+      <c r="BJ50" s="22"/>
+      <c r="BK50" s="22"/>
+      <c r="BL50" s="22"/>
+      <c r="BM50" s="22"/>
+      <c r="BN50" s="22"/>
+      <c r="BO50" s="22"/>
+      <c r="BP50" s="22"/>
+      <c r="BQ50" s="23"/>
+      <c r="BR50" s="19"/>
+    </row>
+    <row r="51" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B51" s="19"/>
+      <c r="E51" s="13"/>
+      <c r="F51" s="13"/>
+      <c r="G51" s="13"/>
+      <c r="H51" s="13"/>
+      <c r="I51" s="13"/>
+      <c r="J51" s="13"/>
+      <c r="K51" s="13"/>
+      <c r="L51" s="13"/>
+      <c r="M51" s="13"/>
+      <c r="N51" s="13"/>
+      <c r="O51" s="13"/>
+      <c r="P51" s="13"/>
+      <c r="Q51" s="13"/>
+      <c r="R51" s="13"/>
+      <c r="T51" s="13"/>
+      <c r="U51" s="13"/>
+      <c r="V51" s="13"/>
+      <c r="W51" s="13"/>
+      <c r="X51" s="13"/>
+      <c r="Y51" s="13"/>
+      <c r="Z51" s="13"/>
+      <c r="AA51" s="13"/>
+      <c r="AB51" s="13"/>
+      <c r="AC51" s="13"/>
+      <c r="AD51" s="13"/>
+      <c r="AE51" s="13"/>
+      <c r="AF51" s="13"/>
+      <c r="AG51" s="13"/>
+      <c r="AW51" s="24"/>
+      <c r="AX51" s="25"/>
+      <c r="AY51" s="25"/>
+      <c r="AZ51" s="25"/>
+      <c r="BA51" s="25"/>
+      <c r="BB51" s="25"/>
+      <c r="BC51" s="25"/>
+      <c r="BD51" s="26"/>
+      <c r="BE51" s="24"/>
+      <c r="BF51" s="25"/>
+      <c r="BG51" s="25"/>
+      <c r="BH51" s="25"/>
+      <c r="BI51" s="25"/>
+      <c r="BJ51" s="25"/>
+      <c r="BK51" s="25"/>
+      <c r="BL51" s="25"/>
+      <c r="BM51" s="25"/>
+      <c r="BN51" s="25"/>
+      <c r="BO51" s="25"/>
+      <c r="BP51" s="25"/>
+      <c r="BQ51" s="26"/>
+      <c r="BR51" s="19"/>
+    </row>
+    <row r="52" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B52" s="19"/>
+      <c r="AW52" s="21" t="s">
         <v>219</v>
       </c>
-      <c r="BF50" s="11"/>
-      <c r="BG50" s="11"/>
-      <c r="BH50" s="11"/>
-      <c r="BI50" s="11"/>
-      <c r="BJ50" s="11"/>
-      <c r="BK50" s="11"/>
-      <c r="BL50" s="11"/>
-      <c r="BM50" s="11"/>
-      <c r="BN50" s="11"/>
-      <c r="BO50" s="11"/>
-      <c r="BP50" s="11"/>
-      <c r="BQ50" s="12"/>
-      <c r="BR50" s="28"/>
-    </row>
-    <row r="51" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B51" s="28"/>
-      <c r="E51" s="30"/>
-      <c r="F51" s="30"/>
-      <c r="G51" s="30"/>
-      <c r="H51" s="30"/>
-      <c r="I51" s="30"/>
-      <c r="J51" s="30"/>
-      <c r="K51" s="30"/>
-      <c r="L51" s="30"/>
-      <c r="M51" s="30"/>
-      <c r="N51" s="30"/>
-      <c r="O51" s="30"/>
-      <c r="P51" s="30"/>
-      <c r="Q51" s="30"/>
-      <c r="R51" s="30"/>
-      <c r="T51" s="30"/>
-      <c r="U51" s="30"/>
-      <c r="V51" s="30"/>
-      <c r="W51" s="30"/>
-      <c r="X51" s="30"/>
-      <c r="Y51" s="30"/>
-      <c r="Z51" s="30"/>
-      <c r="AA51" s="30"/>
-      <c r="AB51" s="30"/>
-      <c r="AC51" s="30"/>
-      <c r="AD51" s="30"/>
-      <c r="AE51" s="30"/>
-      <c r="AF51" s="30"/>
-      <c r="AG51" s="30"/>
-      <c r="AW51" s="19"/>
-      <c r="AX51" s="20"/>
-      <c r="AY51" s="20"/>
-      <c r="AZ51" s="20"/>
-      <c r="BA51" s="20"/>
-      <c r="BB51" s="20"/>
-      <c r="BC51" s="20"/>
-      <c r="BD51" s="21"/>
-      <c r="BE51" s="19"/>
-      <c r="BF51" s="20"/>
-      <c r="BG51" s="20"/>
-      <c r="BH51" s="20"/>
-      <c r="BI51" s="20"/>
-      <c r="BJ51" s="20"/>
-      <c r="BK51" s="20"/>
-      <c r="BL51" s="20"/>
-      <c r="BM51" s="20"/>
-      <c r="BN51" s="20"/>
-      <c r="BO51" s="20"/>
-      <c r="BP51" s="20"/>
-      <c r="BQ51" s="21"/>
-      <c r="BR51" s="28"/>
-    </row>
-    <row r="52" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B52" s="28"/>
-      <c r="AW52" s="18" t="s">
+      <c r="AX52" s="22"/>
+      <c r="AY52" s="22"/>
+      <c r="AZ52" s="22"/>
+      <c r="BA52" s="22"/>
+      <c r="BB52" s="22"/>
+      <c r="BC52" s="22"/>
+      <c r="BD52" s="23"/>
+      <c r="BE52" s="21" t="s">
         <v>220</v>
       </c>
-      <c r="AX52" s="11"/>
-      <c r="AY52" s="11"/>
-      <c r="AZ52" s="11"/>
-      <c r="BA52" s="11"/>
-      <c r="BB52" s="11"/>
-      <c r="BC52" s="11"/>
-      <c r="BD52" s="12"/>
-      <c r="BE52" s="18" t="s">
+      <c r="BF52" s="22"/>
+      <c r="BG52" s="22"/>
+      <c r="BH52" s="22"/>
+      <c r="BI52" s="22"/>
+      <c r="BJ52" s="22"/>
+      <c r="BK52" s="22"/>
+      <c r="BL52" s="22"/>
+      <c r="BM52" s="22"/>
+      <c r="BN52" s="22"/>
+      <c r="BO52" s="22"/>
+      <c r="BP52" s="22"/>
+      <c r="BQ52" s="23"/>
+      <c r="BR52" s="19"/>
+    </row>
+    <row r="53" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B53" s="19"/>
+      <c r="AW53" s="27" t="s">
         <v>221</v>
       </c>
-      <c r="BF52" s="11"/>
-      <c r="BG52" s="11"/>
-      <c r="BH52" s="11"/>
-      <c r="BI52" s="11"/>
-      <c r="BJ52" s="11"/>
-      <c r="BK52" s="11"/>
-      <c r="BL52" s="11"/>
-      <c r="BM52" s="11"/>
-      <c r="BN52" s="11"/>
-      <c r="BO52" s="11"/>
-      <c r="BP52" s="11"/>
-      <c r="BQ52" s="12"/>
-      <c r="BR52" s="28"/>
-    </row>
-    <row r="53" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B53" s="28"/>
-      <c r="AW53" s="22" t="s">
+      <c r="AX53" s="28"/>
+      <c r="AY53" s="28"/>
+      <c r="AZ53" s="28"/>
+      <c r="BA53" s="28"/>
+      <c r="BB53" s="28"/>
+      <c r="BC53" s="28"/>
+      <c r="BD53" s="29"/>
+      <c r="BE53" s="27"/>
+      <c r="BF53" s="28"/>
+      <c r="BG53" s="28"/>
+      <c r="BH53" s="28"/>
+      <c r="BI53" s="28"/>
+      <c r="BJ53" s="28"/>
+      <c r="BK53" s="28"/>
+      <c r="BL53" s="28"/>
+      <c r="BM53" s="28"/>
+      <c r="BN53" s="28"/>
+      <c r="BO53" s="28"/>
+      <c r="BP53" s="28"/>
+      <c r="BQ53" s="29"/>
+      <c r="BR53" s="19"/>
+    </row>
+    <row r="54" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B54" s="19"/>
+      <c r="AW54" s="27"/>
+      <c r="AX54" s="28"/>
+      <c r="AY54" s="28"/>
+      <c r="AZ54" s="28"/>
+      <c r="BA54" s="28"/>
+      <c r="BB54" s="28"/>
+      <c r="BC54" s="28"/>
+      <c r="BD54" s="29"/>
+      <c r="BE54" s="27"/>
+      <c r="BF54" s="28"/>
+      <c r="BG54" s="28"/>
+      <c r="BH54" s="28"/>
+      <c r="BI54" s="28"/>
+      <c r="BJ54" s="28"/>
+      <c r="BK54" s="28"/>
+      <c r="BL54" s="28"/>
+      <c r="BM54" s="28"/>
+      <c r="BN54" s="28"/>
+      <c r="BO54" s="28"/>
+      <c r="BP54" s="28"/>
+      <c r="BQ54" s="29"/>
+      <c r="BR54" s="19"/>
+    </row>
+    <row r="55" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B55" s="19"/>
+      <c r="AW55" s="24"/>
+      <c r="AX55" s="25"/>
+      <c r="AY55" s="25"/>
+      <c r="AZ55" s="25"/>
+      <c r="BA55" s="25"/>
+      <c r="BB55" s="25"/>
+      <c r="BC55" s="25"/>
+      <c r="BD55" s="26"/>
+      <c r="BE55" s="24"/>
+      <c r="BF55" s="25"/>
+      <c r="BG55" s="25"/>
+      <c r="BH55" s="25"/>
+      <c r="BI55" s="25"/>
+      <c r="BJ55" s="25"/>
+      <c r="BK55" s="25"/>
+      <c r="BL55" s="25"/>
+      <c r="BM55" s="25"/>
+      <c r="BN55" s="25"/>
+      <c r="BO55" s="25"/>
+      <c r="BP55" s="25"/>
+      <c r="BQ55" s="26"/>
+      <c r="BR55" s="19"/>
+    </row>
+    <row r="56" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B56" s="20"/>
+      <c r="K56" s="12"/>
+      <c r="L56" s="13"/>
+      <c r="M56" s="13"/>
+      <c r="N56" s="13"/>
+      <c r="O56" s="13"/>
+      <c r="AI56" s="12"/>
+      <c r="AJ56" s="13"/>
+      <c r="AK56" s="13"/>
+      <c r="AL56" s="13"/>
+      <c r="AM56" s="13"/>
+      <c r="AW56" s="15" t="s">
         <v>222</v>
-      </c>
-      <c r="AX53" s="13"/>
-      <c r="AY53" s="13"/>
-      <c r="AZ53" s="13"/>
-      <c r="BA53" s="13"/>
-      <c r="BB53" s="13"/>
-      <c r="BC53" s="13"/>
-      <c r="BD53" s="14"/>
-      <c r="BE53" s="22"/>
-      <c r="BF53" s="13"/>
-      <c r="BG53" s="13"/>
-      <c r="BH53" s="13"/>
-      <c r="BI53" s="13"/>
-      <c r="BJ53" s="13"/>
-      <c r="BK53" s="13"/>
-      <c r="BL53" s="13"/>
-      <c r="BM53" s="13"/>
-      <c r="BN53" s="13"/>
-      <c r="BO53" s="13"/>
-      <c r="BP53" s="13"/>
-      <c r="BQ53" s="14"/>
-      <c r="BR53" s="28"/>
-    </row>
-    <row r="54" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B54" s="28"/>
-      <c r="AW54" s="22"/>
-      <c r="AX54" s="13"/>
-      <c r="AY54" s="13"/>
-      <c r="AZ54" s="13"/>
-      <c r="BA54" s="13"/>
-      <c r="BB54" s="13"/>
-      <c r="BC54" s="13"/>
-      <c r="BD54" s="14"/>
-      <c r="BE54" s="22"/>
-      <c r="BF54" s="13"/>
-      <c r="BG54" s="13"/>
-      <c r="BH54" s="13"/>
-      <c r="BI54" s="13"/>
-      <c r="BJ54" s="13"/>
-      <c r="BK54" s="13"/>
-      <c r="BL54" s="13"/>
-      <c r="BM54" s="13"/>
-      <c r="BN54" s="13"/>
-      <c r="BO54" s="13"/>
-      <c r="BP54" s="13"/>
-      <c r="BQ54" s="14"/>
-      <c r="BR54" s="28"/>
-    </row>
-    <row r="55" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B55" s="28"/>
-      <c r="AW55" s="19"/>
-      <c r="AX55" s="20"/>
-      <c r="AY55" s="20"/>
-      <c r="AZ55" s="20"/>
-      <c r="BA55" s="20"/>
-      <c r="BB55" s="20"/>
-      <c r="BC55" s="20"/>
-      <c r="BD55" s="21"/>
-      <c r="BE55" s="19"/>
-      <c r="BF55" s="20"/>
-      <c r="BG55" s="20"/>
-      <c r="BH55" s="20"/>
-      <c r="BI55" s="20"/>
-      <c r="BJ55" s="20"/>
-      <c r="BK55" s="20"/>
-      <c r="BL55" s="20"/>
-      <c r="BM55" s="20"/>
-      <c r="BN55" s="20"/>
-      <c r="BO55" s="20"/>
-      <c r="BP55" s="20"/>
-      <c r="BQ55" s="21"/>
-      <c r="BR55" s="28"/>
-    </row>
-    <row r="56" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B56" s="24"/>
-      <c r="K56" s="29"/>
-      <c r="L56" s="30"/>
-      <c r="M56" s="30"/>
-      <c r="N56" s="30"/>
-      <c r="O56" s="30"/>
-      <c r="AI56" s="29"/>
-      <c r="AJ56" s="30"/>
-      <c r="AK56" s="30"/>
-      <c r="AL56" s="30"/>
-      <c r="AM56" s="30"/>
-      <c r="AW56" s="15" t="s">
-        <v>223</v>
       </c>
       <c r="AX56" s="16"/>
       <c r="AY56" s="16" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="AZ56" s="16"/>
       <c r="BA56" s="16"/>
@@ -3953,7 +3938,7 @@
       <c r="BO56" s="16"/>
       <c r="BP56" s="16"/>
       <c r="BQ56" s="17"/>
-      <c r="BR56" s="24"/>
+      <c r="BR56" s="20"/>
     </row>
     <row r="57" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C57" s="15">
@@ -4039,39 +4024,138 @@
     <row r="58" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4"/>
   </sheetData>
   <mergeCells count="191">
-    <mergeCell ref="E47:R51"/>
-    <mergeCell ref="T47:AG51"/>
-    <mergeCell ref="AT3:AV11"/>
-    <mergeCell ref="E7:R11"/>
-    <mergeCell ref="T7:AG11"/>
-    <mergeCell ref="E17:R20"/>
-    <mergeCell ref="T17:AG20"/>
-    <mergeCell ref="E26:R29"/>
-    <mergeCell ref="T26:AG29"/>
-    <mergeCell ref="E35:R39"/>
-    <mergeCell ref="T35:AG39"/>
-    <mergeCell ref="AW56:AX56"/>
-    <mergeCell ref="BM25:BO25"/>
-    <mergeCell ref="Y57:AI57"/>
-    <mergeCell ref="BL39:BN39"/>
-    <mergeCell ref="C2:L2"/>
-    <mergeCell ref="BO41:BQ41"/>
-    <mergeCell ref="BF16:BK16"/>
-    <mergeCell ref="AY10:BB10"/>
-    <mergeCell ref="AW11:AX11"/>
-    <mergeCell ref="AY11:BB11"/>
-    <mergeCell ref="BC11:BE11"/>
-    <mergeCell ref="BF11:BK11"/>
-    <mergeCell ref="BM11:BO11"/>
-    <mergeCell ref="AY17:BB17"/>
-    <mergeCell ref="AW24:AX24"/>
-    <mergeCell ref="BF24:BK24"/>
-    <mergeCell ref="BC20:BE20"/>
-    <mergeCell ref="AY15:BB15"/>
-    <mergeCell ref="AW22:AX22"/>
-    <mergeCell ref="BA41:BH41"/>
-    <mergeCell ref="AW26:AX26"/>
-    <mergeCell ref="AY26:BB26"/>
+    <mergeCell ref="M2:X2"/>
+    <mergeCell ref="AU2:BF2"/>
+    <mergeCell ref="AW18:AX18"/>
+    <mergeCell ref="BC8:BE8"/>
+    <mergeCell ref="BI43:BK44"/>
+    <mergeCell ref="AU57:BF57"/>
+    <mergeCell ref="AW9:AX9"/>
+    <mergeCell ref="BC22:BE22"/>
+    <mergeCell ref="BA47:BH47"/>
+    <mergeCell ref="BG2:BQ2"/>
+    <mergeCell ref="AJ2:AT2"/>
+    <mergeCell ref="AY56:BQ56"/>
+    <mergeCell ref="Y2:AI2"/>
+    <mergeCell ref="BF9:BK9"/>
+    <mergeCell ref="AY8:BB8"/>
+    <mergeCell ref="AW17:AX17"/>
+    <mergeCell ref="BO43:BQ44"/>
+    <mergeCell ref="BG57:BQ57"/>
+    <mergeCell ref="BC7:BE7"/>
+    <mergeCell ref="BC15:BE15"/>
+    <mergeCell ref="BA40:BH40"/>
+    <mergeCell ref="AW19:AX19"/>
+    <mergeCell ref="AW53:BD55"/>
+    <mergeCell ref="B3:B16"/>
+    <mergeCell ref="BC9:BE9"/>
+    <mergeCell ref="AY18:BB18"/>
+    <mergeCell ref="BI47:BQ47"/>
+    <mergeCell ref="AW21:AX21"/>
+    <mergeCell ref="AJ57:AT57"/>
+    <mergeCell ref="BC19:BE19"/>
+    <mergeCell ref="AX41:AZ41"/>
+    <mergeCell ref="BM24:BO24"/>
+    <mergeCell ref="BI39:BK39"/>
+    <mergeCell ref="BC21:BE21"/>
+    <mergeCell ref="AX43:AZ44"/>
+    <mergeCell ref="AY19:BB19"/>
+    <mergeCell ref="AY13:BB13"/>
+    <mergeCell ref="AX40:AZ40"/>
+    <mergeCell ref="AY22:BB22"/>
+    <mergeCell ref="BA43:BH44"/>
+    <mergeCell ref="BL40:BN40"/>
+    <mergeCell ref="BC12:BE12"/>
+    <mergeCell ref="BL43:BN44"/>
+    <mergeCell ref="C3:D5"/>
+    <mergeCell ref="C57:L57"/>
+    <mergeCell ref="AW48:BD48"/>
+    <mergeCell ref="AW3:BQ4"/>
+    <mergeCell ref="BE52:BQ55"/>
+    <mergeCell ref="M57:X57"/>
+    <mergeCell ref="AX42:AZ42"/>
+    <mergeCell ref="AW43:AW44"/>
+    <mergeCell ref="BR30:BR43"/>
+    <mergeCell ref="BM8:BO8"/>
+    <mergeCell ref="AX39:AZ39"/>
+    <mergeCell ref="BM16:BO16"/>
+    <mergeCell ref="BA46:BH46"/>
+    <mergeCell ref="K56:O56"/>
+    <mergeCell ref="BA39:BH39"/>
+    <mergeCell ref="BM10:BO10"/>
+    <mergeCell ref="AW31:AX36"/>
+    <mergeCell ref="BE48:BQ49"/>
+    <mergeCell ref="BL42:BN42"/>
+    <mergeCell ref="AI56:AM56"/>
+    <mergeCell ref="AY23:BB23"/>
+    <mergeCell ref="AX45:AZ45"/>
+    <mergeCell ref="BI42:BK42"/>
+    <mergeCell ref="BF21:BK21"/>
+    <mergeCell ref="BO45:BQ45"/>
+    <mergeCell ref="BR44:BR56"/>
+    <mergeCell ref="BI46:BQ46"/>
+    <mergeCell ref="BM23:BO23"/>
+    <mergeCell ref="BE50:BQ51"/>
+    <mergeCell ref="AY5:BB6"/>
+    <mergeCell ref="B17:B29"/>
+    <mergeCell ref="AY9:BB9"/>
+    <mergeCell ref="AW25:AX25"/>
+    <mergeCell ref="AW7:AX7"/>
+    <mergeCell ref="AW15:AX15"/>
+    <mergeCell ref="B44:B56"/>
+    <mergeCell ref="BL41:BN41"/>
+    <mergeCell ref="BA42:BH42"/>
+    <mergeCell ref="AW49:BD51"/>
+    <mergeCell ref="BI45:BK45"/>
+    <mergeCell ref="BC16:BE16"/>
+    <mergeCell ref="BF20:BK20"/>
+    <mergeCell ref="AW20:AX20"/>
+    <mergeCell ref="B30:B43"/>
+    <mergeCell ref="AW47:AZ47"/>
+    <mergeCell ref="BF10:BK10"/>
+    <mergeCell ref="AW10:AX10"/>
+    <mergeCell ref="BF17:BK17"/>
+    <mergeCell ref="AW23:AX23"/>
+    <mergeCell ref="BM5:BO6"/>
+    <mergeCell ref="AW5:AX6"/>
+    <mergeCell ref="BC18:BE18"/>
+    <mergeCell ref="AW13:AX13"/>
+    <mergeCell ref="BA45:BH45"/>
+    <mergeCell ref="AW8:AX8"/>
+    <mergeCell ref="BL45:BN45"/>
+    <mergeCell ref="BF8:BK8"/>
+    <mergeCell ref="BI40:BK40"/>
+    <mergeCell ref="AW46:AZ46"/>
+    <mergeCell ref="BC26:BE26"/>
+    <mergeCell ref="BF26:BK26"/>
+    <mergeCell ref="BM26:BO26"/>
+    <mergeCell ref="BI41:BK41"/>
+    <mergeCell ref="BF15:BK15"/>
+    <mergeCell ref="AY14:BB14"/>
+    <mergeCell ref="AY25:BB25"/>
+    <mergeCell ref="AY31:BQ36"/>
+    <mergeCell ref="AY12:BB12"/>
+    <mergeCell ref="BC14:BE14"/>
+    <mergeCell ref="BM22:BO22"/>
+    <mergeCell ref="AW14:AX14"/>
+    <mergeCell ref="BC10:BE10"/>
+    <mergeCell ref="BM17:BO17"/>
+    <mergeCell ref="BC23:BE23"/>
+    <mergeCell ref="BF18:BK18"/>
+    <mergeCell ref="AW12:AX12"/>
+    <mergeCell ref="BF5:BK6"/>
+    <mergeCell ref="BC17:BE17"/>
+    <mergeCell ref="AY24:BB24"/>
+    <mergeCell ref="BC5:BE6"/>
+    <mergeCell ref="BO42:BQ42"/>
+    <mergeCell ref="BP5:BP6"/>
+    <mergeCell ref="BO40:BQ40"/>
+    <mergeCell ref="BQ5:BQ6"/>
+    <mergeCell ref="BM21:BO21"/>
+    <mergeCell ref="BF13:BK13"/>
+    <mergeCell ref="BL5:BL6"/>
+    <mergeCell ref="AY7:BB7"/>
+    <mergeCell ref="BM14:BO14"/>
     <mergeCell ref="BR17:BR29"/>
     <mergeCell ref="BM9:BO9"/>
     <mergeCell ref="AY16:BB16"/>
@@ -4096,140 +4180,41 @@
     <mergeCell ref="BC13:BE13"/>
     <mergeCell ref="BM13:BO13"/>
     <mergeCell ref="AY20:BB20"/>
+    <mergeCell ref="AW56:AX56"/>
+    <mergeCell ref="BM25:BO25"/>
+    <mergeCell ref="Y57:AI57"/>
+    <mergeCell ref="BL39:BN39"/>
+    <mergeCell ref="C2:L2"/>
+    <mergeCell ref="BO41:BQ41"/>
+    <mergeCell ref="BF16:BK16"/>
+    <mergeCell ref="AY10:BB10"/>
+    <mergeCell ref="AW11:AX11"/>
+    <mergeCell ref="AY11:BB11"/>
+    <mergeCell ref="BC11:BE11"/>
+    <mergeCell ref="BF11:BK11"/>
+    <mergeCell ref="BM11:BO11"/>
+    <mergeCell ref="AY17:BB17"/>
+    <mergeCell ref="AW24:AX24"/>
+    <mergeCell ref="BF24:BK24"/>
+    <mergeCell ref="BC20:BE20"/>
+    <mergeCell ref="AY15:BB15"/>
+    <mergeCell ref="AW22:AX22"/>
+    <mergeCell ref="BA41:BH41"/>
+    <mergeCell ref="AW26:AX26"/>
+    <mergeCell ref="AY26:BB26"/>
     <mergeCell ref="AW52:BD52"/>
     <mergeCell ref="AW16:AX16"/>
-    <mergeCell ref="BF5:BK6"/>
-    <mergeCell ref="BC17:BE17"/>
-    <mergeCell ref="AY24:BB24"/>
-    <mergeCell ref="BC5:BE6"/>
-    <mergeCell ref="BO42:BQ42"/>
-    <mergeCell ref="BP5:BP6"/>
-    <mergeCell ref="BO40:BQ40"/>
-    <mergeCell ref="BQ5:BQ6"/>
-    <mergeCell ref="BM21:BO21"/>
-    <mergeCell ref="BF13:BK13"/>
-    <mergeCell ref="AW13:AX13"/>
-    <mergeCell ref="BA45:BH45"/>
-    <mergeCell ref="AW8:AX8"/>
-    <mergeCell ref="BL45:BN45"/>
-    <mergeCell ref="BF8:BK8"/>
-    <mergeCell ref="BI40:BK40"/>
-    <mergeCell ref="AW46:AZ46"/>
-    <mergeCell ref="BC26:BE26"/>
-    <mergeCell ref="BF26:BK26"/>
-    <mergeCell ref="BM26:BO26"/>
-    <mergeCell ref="BE50:BQ51"/>
-    <mergeCell ref="AY5:BB6"/>
-    <mergeCell ref="B17:B29"/>
-    <mergeCell ref="AY9:BB9"/>
-    <mergeCell ref="AW25:AX25"/>
-    <mergeCell ref="AW7:AX7"/>
-    <mergeCell ref="AW15:AX15"/>
-    <mergeCell ref="B44:B56"/>
-    <mergeCell ref="BL41:BN41"/>
-    <mergeCell ref="BA42:BH42"/>
-    <mergeCell ref="AW49:BD51"/>
-    <mergeCell ref="BI45:BK45"/>
-    <mergeCell ref="BC16:BE16"/>
-    <mergeCell ref="BF20:BK20"/>
-    <mergeCell ref="AW20:AX20"/>
-    <mergeCell ref="B30:B43"/>
-    <mergeCell ref="AW47:AZ47"/>
-    <mergeCell ref="BF10:BK10"/>
-    <mergeCell ref="AW10:AX10"/>
-    <mergeCell ref="BF17:BK17"/>
-    <mergeCell ref="AW23:AX23"/>
-    <mergeCell ref="BM5:BO6"/>
-    <mergeCell ref="AW5:AX6"/>
-    <mergeCell ref="BC18:BE18"/>
-    <mergeCell ref="BI41:BK41"/>
-    <mergeCell ref="BE52:BQ55"/>
-    <mergeCell ref="M57:X57"/>
-    <mergeCell ref="AX42:AZ42"/>
-    <mergeCell ref="AW43:AW44"/>
-    <mergeCell ref="BR30:BR43"/>
-    <mergeCell ref="BM8:BO8"/>
-    <mergeCell ref="AX39:AZ39"/>
-    <mergeCell ref="BM16:BO16"/>
-    <mergeCell ref="BA46:BH46"/>
-    <mergeCell ref="K56:O56"/>
-    <mergeCell ref="BA39:BH39"/>
-    <mergeCell ref="BM10:BO10"/>
-    <mergeCell ref="AW31:AX36"/>
-    <mergeCell ref="BE48:BQ49"/>
-    <mergeCell ref="BL42:BN42"/>
-    <mergeCell ref="AI56:AM56"/>
-    <mergeCell ref="AY23:BB23"/>
-    <mergeCell ref="AX45:AZ45"/>
-    <mergeCell ref="BI42:BK42"/>
-    <mergeCell ref="BF21:BK21"/>
-    <mergeCell ref="BO45:BQ45"/>
-    <mergeCell ref="BR44:BR56"/>
-    <mergeCell ref="B3:B16"/>
-    <mergeCell ref="BC9:BE9"/>
-    <mergeCell ref="AY18:BB18"/>
-    <mergeCell ref="BI47:BQ47"/>
-    <mergeCell ref="AW21:AX21"/>
-    <mergeCell ref="AJ57:AT57"/>
-    <mergeCell ref="BC19:BE19"/>
-    <mergeCell ref="AX41:AZ41"/>
-    <mergeCell ref="BM24:BO24"/>
-    <mergeCell ref="BI39:BK39"/>
-    <mergeCell ref="BC21:BE21"/>
-    <mergeCell ref="AX43:AZ44"/>
-    <mergeCell ref="AY19:BB19"/>
-    <mergeCell ref="AY13:BB13"/>
-    <mergeCell ref="AX40:AZ40"/>
-    <mergeCell ref="AY22:BB22"/>
-    <mergeCell ref="BA43:BH44"/>
-    <mergeCell ref="BL40:BN40"/>
-    <mergeCell ref="BC12:BE12"/>
-    <mergeCell ref="BL43:BN44"/>
-    <mergeCell ref="C3:D5"/>
-    <mergeCell ref="C57:L57"/>
-    <mergeCell ref="AW48:BD48"/>
-    <mergeCell ref="AW3:BQ4"/>
-    <mergeCell ref="BI46:BQ46"/>
-    <mergeCell ref="BM23:BO23"/>
-    <mergeCell ref="BF15:BK15"/>
-    <mergeCell ref="BL5:BL6"/>
-    <mergeCell ref="AY14:BB14"/>
-    <mergeCell ref="AY25:BB25"/>
-    <mergeCell ref="AY31:BQ36"/>
-    <mergeCell ref="AY12:BB12"/>
-    <mergeCell ref="BC14:BE14"/>
-    <mergeCell ref="BM22:BO22"/>
-    <mergeCell ref="AW14:AX14"/>
-    <mergeCell ref="AY7:BB7"/>
-    <mergeCell ref="BC10:BE10"/>
-    <mergeCell ref="BM17:BO17"/>
-    <mergeCell ref="BC23:BE23"/>
-    <mergeCell ref="BF18:BK18"/>
-    <mergeCell ref="AW12:AX12"/>
-    <mergeCell ref="BM14:BO14"/>
-    <mergeCell ref="M2:X2"/>
-    <mergeCell ref="AU2:BF2"/>
-    <mergeCell ref="AW18:AX18"/>
-    <mergeCell ref="BC8:BE8"/>
-    <mergeCell ref="BI43:BK44"/>
-    <mergeCell ref="AU57:BF57"/>
-    <mergeCell ref="AW9:AX9"/>
-    <mergeCell ref="BC22:BE22"/>
-    <mergeCell ref="BA47:BH47"/>
-    <mergeCell ref="BG2:BQ2"/>
-    <mergeCell ref="AJ2:AT2"/>
-    <mergeCell ref="AY56:BQ56"/>
-    <mergeCell ref="Y2:AI2"/>
-    <mergeCell ref="BF9:BK9"/>
-    <mergeCell ref="AY8:BB8"/>
-    <mergeCell ref="AW17:AX17"/>
-    <mergeCell ref="BO43:BQ44"/>
-    <mergeCell ref="BG57:BQ57"/>
-    <mergeCell ref="BC7:BE7"/>
-    <mergeCell ref="BC15:BE15"/>
-    <mergeCell ref="BA40:BH40"/>
-    <mergeCell ref="AW19:AX19"/>
-    <mergeCell ref="AW53:BD55"/>
+    <mergeCell ref="E47:R51"/>
+    <mergeCell ref="T47:AG51"/>
+    <mergeCell ref="AT3:AV11"/>
+    <mergeCell ref="E7:R11"/>
+    <mergeCell ref="T7:AG11"/>
+    <mergeCell ref="E17:R20"/>
+    <mergeCell ref="T17:AG20"/>
+    <mergeCell ref="E26:R29"/>
+    <mergeCell ref="T26:AG29"/>
+    <mergeCell ref="E35:R39"/>
+    <mergeCell ref="T35:AG39"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/가공도_도면_1.xlsx
+++ b/가공도_도면_1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\duddl\Desktop\Project\a2z\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D11C61F-4B05-4749-BBE4-DFFE85540C75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56E747DC-6A03-4992-A4EB-6169B53A3E49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1920" yWindow="720" windowWidth="20256" windowHeight="11520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -616,6 +616,21 @@
     <t>{Input_194}</t>
   </si>
   <si>
+    <t>{Input_195}</t>
+  </si>
+  <si>
+    <t>{Input_196}</t>
+  </si>
+  <si>
+    <t>{Input_197}</t>
+  </si>
+  <si>
+    <t>{Input_198}</t>
+  </si>
+  <si>
+    <t>{Input_199}</t>
+  </si>
+  <si>
     <t>D</t>
   </si>
   <si>
@@ -699,35 +714,15 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>{Input_195}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{Input_196}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{Input_197}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{Input_198}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{Input_199}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{View_5}</t>
-  </si>
-  <si>
     <t>{Image_1}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>{Image_2}</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{View_5}</t>
   </si>
 </sst>
 </file>
@@ -955,7 +950,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -990,7 +985,7 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1031,10 +1026,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1048,19 +1052,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1529,13 +1520,13 @@
       <c r="B3" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="29" t="s">
-        <v>231</v>
-      </c>
-      <c r="D3" s="30"/>
+      <c r="C3" s="32" t="s">
+        <v>230</v>
+      </c>
+      <c r="D3" s="33"/>
       <c r="Y3" s="3"/>
       <c r="AT3" s="14" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AU3" s="14"/>
       <c r="AV3" s="15"/>
@@ -1567,11 +1558,11 @@
       </c>
     </row>
     <row r="4" spans="1:71" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="27"/>
-      <c r="C4" s="31"/>
-      <c r="D4" s="32"/>
-      <c r="E4" s="13"/>
-      <c r="AA4" s="13"/>
+      <c r="B4" s="31"/>
+      <c r="C4" s="34"/>
+      <c r="D4" s="35"/>
+      <c r="E4" s="3"/>
+      <c r="AA4" s="3"/>
       <c r="AT4" s="16"/>
       <c r="AU4" s="16"/>
       <c r="AV4" s="17"/>
@@ -1596,17 +1587,17 @@
       <c r="BO4" s="23"/>
       <c r="BP4" s="23"/>
       <c r="BQ4" s="24"/>
-      <c r="BR4" s="27"/>
+      <c r="BR4" s="31"/>
     </row>
     <row r="5" spans="1:71" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B5" s="27"/>
-      <c r="C5" s="31"/>
-      <c r="D5" s="32"/>
+      <c r="B5" s="31"/>
+      <c r="C5" s="34"/>
+      <c r="D5" s="35"/>
       <c r="AT5" s="16"/>
       <c r="AU5" s="16"/>
       <c r="AV5" s="17"/>
       <c r="AW5" s="21" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="AX5" s="15"/>
       <c r="AY5" s="21" t="s">
@@ -1642,10 +1633,10 @@
       <c r="BQ5" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="BR5" s="27"/>
+      <c r="BR5" s="31"/>
     </row>
     <row r="6" spans="1:71" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B6" s="27"/>
+      <c r="B6" s="31"/>
       <c r="AT6" s="16"/>
       <c r="AU6" s="16"/>
       <c r="AV6" s="17"/>
@@ -1664,48 +1655,48 @@
       <c r="BI6" s="23"/>
       <c r="BJ6" s="23"/>
       <c r="BK6" s="24"/>
-      <c r="BL6" s="28"/>
+      <c r="BL6" s="27"/>
       <c r="BM6" s="22"/>
       <c r="BN6" s="23"/>
       <c r="BO6" s="24"/>
-      <c r="BP6" s="28"/>
-      <c r="BQ6" s="28"/>
-      <c r="BR6" s="27"/>
+      <c r="BP6" s="27"/>
+      <c r="BQ6" s="27"/>
+      <c r="BR6" s="31"/>
     </row>
     <row r="7" spans="1:71" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B7" s="27"/>
-      <c r="E7" s="33" t="s">
-        <v>224</v>
-      </c>
-      <c r="F7" s="34"/>
-      <c r="G7" s="34"/>
-      <c r="H7" s="34"/>
-      <c r="I7" s="34"/>
-      <c r="J7" s="34"/>
-      <c r="K7" s="34"/>
-      <c r="L7" s="34"/>
-      <c r="M7" s="34"/>
-      <c r="N7" s="34"/>
-      <c r="O7" s="34"/>
-      <c r="P7" s="34"/>
-      <c r="Q7" s="34"/>
-      <c r="R7" s="34"/>
-      <c r="T7" s="33" t="s">
+      <c r="B7" s="31"/>
+      <c r="E7" s="13" t="s">
+        <v>198</v>
+      </c>
+      <c r="F7" s="13"/>
+      <c r="G7" s="13"/>
+      <c r="H7" s="13"/>
+      <c r="I7" s="13"/>
+      <c r="J7" s="13"/>
+      <c r="K7" s="13"/>
+      <c r="L7" s="13"/>
+      <c r="M7" s="13"/>
+      <c r="N7" s="13"/>
+      <c r="O7" s="13"/>
+      <c r="P7" s="13"/>
+      <c r="Q7" s="13"/>
+      <c r="R7" s="13"/>
+      <c r="T7" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="U7" s="34"/>
-      <c r="V7" s="34"/>
-      <c r="W7" s="34"/>
-      <c r="X7" s="34"/>
-      <c r="Y7" s="34"/>
-      <c r="Z7" s="34"/>
-      <c r="AA7" s="34"/>
-      <c r="AB7" s="34"/>
-      <c r="AC7" s="34"/>
-      <c r="AD7" s="34"/>
-      <c r="AE7" s="34"/>
-      <c r="AF7" s="34"/>
-      <c r="AG7" s="34"/>
+      <c r="U7" s="13"/>
+      <c r="V7" s="13"/>
+      <c r="W7" s="13"/>
+      <c r="X7" s="13"/>
+      <c r="Y7" s="13"/>
+      <c r="Z7" s="13"/>
+      <c r="AA7" s="13"/>
+      <c r="AB7" s="13"/>
+      <c r="AC7" s="13"/>
+      <c r="AD7" s="13"/>
+      <c r="AE7" s="13"/>
+      <c r="AF7" s="13"/>
+      <c r="AG7" s="13"/>
       <c r="AT7" s="16"/>
       <c r="AU7" s="16"/>
       <c r="AV7" s="17"/>
@@ -1746,38 +1737,38 @@
       <c r="BQ7" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="BR7" s="27"/>
+      <c r="BR7" s="31"/>
     </row>
     <row r="8" spans="1:71" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B8" s="27"/>
-      <c r="E8" s="34"/>
-      <c r="F8" s="34"/>
-      <c r="G8" s="34"/>
-      <c r="H8" s="34"/>
-      <c r="I8" s="34"/>
-      <c r="J8" s="34"/>
-      <c r="K8" s="34"/>
-      <c r="L8" s="34"/>
-      <c r="M8" s="34"/>
-      <c r="N8" s="34"/>
-      <c r="O8" s="34"/>
-      <c r="P8" s="34"/>
-      <c r="Q8" s="34"/>
-      <c r="R8" s="34"/>
-      <c r="T8" s="34"/>
-      <c r="U8" s="34"/>
-      <c r="V8" s="34"/>
-      <c r="W8" s="34"/>
-      <c r="X8" s="34"/>
-      <c r="Y8" s="34"/>
-      <c r="Z8" s="34"/>
-      <c r="AA8" s="34"/>
-      <c r="AB8" s="34"/>
-      <c r="AC8" s="34"/>
-      <c r="AD8" s="34"/>
-      <c r="AE8" s="34"/>
-      <c r="AF8" s="34"/>
-      <c r="AG8" s="34"/>
+      <c r="B8" s="31"/>
+      <c r="E8" s="13"/>
+      <c r="F8" s="13"/>
+      <c r="G8" s="13"/>
+      <c r="H8" s="13"/>
+      <c r="I8" s="13"/>
+      <c r="J8" s="13"/>
+      <c r="K8" s="13"/>
+      <c r="L8" s="13"/>
+      <c r="M8" s="13"/>
+      <c r="N8" s="13"/>
+      <c r="O8" s="13"/>
+      <c r="P8" s="13"/>
+      <c r="Q8" s="13"/>
+      <c r="R8" s="13"/>
+      <c r="T8" s="13"/>
+      <c r="U8" s="13"/>
+      <c r="V8" s="13"/>
+      <c r="W8" s="13"/>
+      <c r="X8" s="13"/>
+      <c r="Y8" s="13"/>
+      <c r="Z8" s="13"/>
+      <c r="AA8" s="13"/>
+      <c r="AB8" s="13"/>
+      <c r="AC8" s="13"/>
+      <c r="AD8" s="13"/>
+      <c r="AE8" s="13"/>
+      <c r="AF8" s="13"/>
+      <c r="AG8" s="13"/>
       <c r="AT8" s="16"/>
       <c r="AU8" s="16"/>
       <c r="AV8" s="17"/>
@@ -1818,38 +1809,38 @@
       <c r="BQ8" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="BR8" s="27"/>
+      <c r="BR8" s="31"/>
     </row>
     <row r="9" spans="1:71" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B9" s="27"/>
-      <c r="E9" s="34"/>
-      <c r="F9" s="34"/>
-      <c r="G9" s="34"/>
-      <c r="H9" s="34"/>
-      <c r="I9" s="34"/>
-      <c r="J9" s="34"/>
-      <c r="K9" s="34"/>
-      <c r="L9" s="34"/>
-      <c r="M9" s="34"/>
-      <c r="N9" s="34"/>
-      <c r="O9" s="34"/>
-      <c r="P9" s="34"/>
-      <c r="Q9" s="34"/>
-      <c r="R9" s="34"/>
-      <c r="T9" s="34"/>
-      <c r="U9" s="34"/>
-      <c r="V9" s="34"/>
-      <c r="W9" s="34"/>
-      <c r="X9" s="34"/>
-      <c r="Y9" s="34"/>
-      <c r="Z9" s="34"/>
-      <c r="AA9" s="34"/>
-      <c r="AB9" s="34"/>
-      <c r="AC9" s="34"/>
-      <c r="AD9" s="34"/>
-      <c r="AE9" s="34"/>
-      <c r="AF9" s="34"/>
-      <c r="AG9" s="34"/>
+      <c r="B9" s="31"/>
+      <c r="E9" s="13"/>
+      <c r="F9" s="13"/>
+      <c r="G9" s="13"/>
+      <c r="H9" s="13"/>
+      <c r="I9" s="13"/>
+      <c r="J9" s="13"/>
+      <c r="K9" s="13"/>
+      <c r="L9" s="13"/>
+      <c r="M9" s="13"/>
+      <c r="N9" s="13"/>
+      <c r="O9" s="13"/>
+      <c r="P9" s="13"/>
+      <c r="Q9" s="13"/>
+      <c r="R9" s="13"/>
+      <c r="T9" s="13"/>
+      <c r="U9" s="13"/>
+      <c r="V9" s="13"/>
+      <c r="W9" s="13"/>
+      <c r="X9" s="13"/>
+      <c r="Y9" s="13"/>
+      <c r="Z9" s="13"/>
+      <c r="AA9" s="13"/>
+      <c r="AB9" s="13"/>
+      <c r="AC9" s="13"/>
+      <c r="AD9" s="13"/>
+      <c r="AE9" s="13"/>
+      <c r="AF9" s="13"/>
+      <c r="AG9" s="13"/>
       <c r="AT9" s="11"/>
       <c r="AU9" s="11"/>
       <c r="AV9" s="12"/>
@@ -1890,38 +1881,38 @@
       <c r="BQ9" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="BR9" s="27"/>
+      <c r="BR9" s="31"/>
     </row>
     <row r="10" spans="1:71" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B10" s="27"/>
-      <c r="E10" s="34"/>
-      <c r="F10" s="34"/>
-      <c r="G10" s="34"/>
-      <c r="H10" s="34"/>
-      <c r="I10" s="34"/>
-      <c r="J10" s="34"/>
-      <c r="K10" s="34"/>
-      <c r="L10" s="34"/>
-      <c r="M10" s="34"/>
-      <c r="N10" s="34"/>
-      <c r="O10" s="34"/>
-      <c r="P10" s="34"/>
-      <c r="Q10" s="34"/>
-      <c r="R10" s="34"/>
-      <c r="T10" s="34"/>
-      <c r="U10" s="34"/>
-      <c r="V10" s="34"/>
-      <c r="W10" s="34"/>
-      <c r="X10" s="34"/>
-      <c r="Y10" s="34"/>
-      <c r="Z10" s="34"/>
-      <c r="AA10" s="34"/>
-      <c r="AB10" s="34"/>
-      <c r="AC10" s="34"/>
-      <c r="AD10" s="34"/>
-      <c r="AE10" s="34"/>
-      <c r="AF10" s="34"/>
-      <c r="AG10" s="34"/>
+      <c r="B10" s="31"/>
+      <c r="E10" s="13"/>
+      <c r="F10" s="13"/>
+      <c r="G10" s="13"/>
+      <c r="H10" s="13"/>
+      <c r="I10" s="13"/>
+      <c r="J10" s="13"/>
+      <c r="K10" s="13"/>
+      <c r="L10" s="13"/>
+      <c r="M10" s="13"/>
+      <c r="N10" s="13"/>
+      <c r="O10" s="13"/>
+      <c r="P10" s="13"/>
+      <c r="Q10" s="13"/>
+      <c r="R10" s="13"/>
+      <c r="T10" s="13"/>
+      <c r="U10" s="13"/>
+      <c r="V10" s="13"/>
+      <c r="W10" s="13"/>
+      <c r="X10" s="13"/>
+      <c r="Y10" s="13"/>
+      <c r="Z10" s="13"/>
+      <c r="AA10" s="13"/>
+      <c r="AB10" s="13"/>
+      <c r="AC10" s="13"/>
+      <c r="AD10" s="13"/>
+      <c r="AE10" s="13"/>
+      <c r="AF10" s="13"/>
+      <c r="AG10" s="13"/>
       <c r="AT10" s="11"/>
       <c r="AU10" s="11"/>
       <c r="AV10" s="12"/>
@@ -1962,38 +1953,38 @@
       <c r="BQ10" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="BR10" s="27"/>
+      <c r="BR10" s="31"/>
     </row>
     <row r="11" spans="1:71" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B11" s="27"/>
-      <c r="E11" s="34"/>
-      <c r="F11" s="34"/>
-      <c r="G11" s="34"/>
-      <c r="H11" s="34"/>
-      <c r="I11" s="34"/>
-      <c r="J11" s="34"/>
-      <c r="K11" s="34"/>
-      <c r="L11" s="34"/>
-      <c r="M11" s="34"/>
-      <c r="N11" s="34"/>
-      <c r="O11" s="34"/>
-      <c r="P11" s="34"/>
-      <c r="Q11" s="34"/>
-      <c r="R11" s="34"/>
-      <c r="T11" s="34"/>
-      <c r="U11" s="34"/>
-      <c r="V11" s="34"/>
-      <c r="W11" s="34"/>
-      <c r="X11" s="34"/>
-      <c r="Y11" s="34"/>
-      <c r="Z11" s="34"/>
-      <c r="AA11" s="34"/>
-      <c r="AB11" s="34"/>
-      <c r="AC11" s="34"/>
-      <c r="AD11" s="34"/>
-      <c r="AE11" s="34"/>
-      <c r="AF11" s="34"/>
-      <c r="AG11" s="34"/>
+      <c r="B11" s="31"/>
+      <c r="E11" s="13"/>
+      <c r="F11" s="13"/>
+      <c r="G11" s="13"/>
+      <c r="H11" s="13"/>
+      <c r="I11" s="13"/>
+      <c r="J11" s="13"/>
+      <c r="K11" s="13"/>
+      <c r="L11" s="13"/>
+      <c r="M11" s="13"/>
+      <c r="N11" s="13"/>
+      <c r="O11" s="13"/>
+      <c r="P11" s="13"/>
+      <c r="Q11" s="13"/>
+      <c r="R11" s="13"/>
+      <c r="T11" s="13"/>
+      <c r="U11" s="13"/>
+      <c r="V11" s="13"/>
+      <c r="W11" s="13"/>
+      <c r="X11" s="13"/>
+      <c r="Y11" s="13"/>
+      <c r="Z11" s="13"/>
+      <c r="AA11" s="13"/>
+      <c r="AB11" s="13"/>
+      <c r="AC11" s="13"/>
+      <c r="AD11" s="13"/>
+      <c r="AE11" s="13"/>
+      <c r="AF11" s="13"/>
+      <c r="AG11" s="13"/>
       <c r="AT11" s="11"/>
       <c r="AU11" s="11"/>
       <c r="AV11" s="12"/>
@@ -2034,10 +2025,10 @@
       <c r="BQ11" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="BR11" s="27"/>
+      <c r="BR11" s="31"/>
     </row>
     <row r="12" spans="1:71" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B12" s="27"/>
+      <c r="B12" s="31"/>
       <c r="AW12" s="18" t="s">
         <v>51</v>
       </c>
@@ -2075,10 +2066,10 @@
       <c r="BQ12" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="BR12" s="27"/>
+      <c r="BR12" s="31"/>
     </row>
     <row r="13" spans="1:71" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B13" s="27"/>
+      <c r="B13" s="31"/>
       <c r="AW13" s="18" t="s">
         <v>59</v>
       </c>
@@ -2116,10 +2107,10 @@
       <c r="BQ13" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="BR13" s="27"/>
+      <c r="BR13" s="31"/>
     </row>
     <row r="14" spans="1:71" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B14" s="27"/>
+      <c r="B14" s="31"/>
       <c r="AW14" s="18" t="s">
         <v>67</v>
       </c>
@@ -2157,10 +2148,10 @@
       <c r="BQ14" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="BR14" s="27"/>
+      <c r="BR14" s="31"/>
     </row>
     <row r="15" spans="1:71" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B15" s="27"/>
+      <c r="B15" s="31"/>
       <c r="AW15" s="18" t="s">
         <v>75</v>
       </c>
@@ -2198,10 +2189,10 @@
       <c r="BQ15" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="BR15" s="27"/>
+      <c r="BR15" s="31"/>
     </row>
     <row r="16" spans="1:71" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B16" s="28"/>
+      <c r="B16" s="27"/>
       <c r="AW16" s="18" t="s">
         <v>84</v>
       </c>
@@ -2239,44 +2230,44 @@
       <c r="BQ16" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="BR16" s="28"/>
+      <c r="BR16" s="27"/>
     </row>
     <row r="17" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B17" s="26" t="s">
         <v>83</v>
       </c>
-      <c r="E17" s="33" t="s">
-        <v>225</v>
-      </c>
-      <c r="F17" s="34"/>
-      <c r="G17" s="34"/>
-      <c r="H17" s="34"/>
-      <c r="I17" s="34"/>
-      <c r="J17" s="34"/>
-      <c r="K17" s="34"/>
-      <c r="L17" s="34"/>
-      <c r="M17" s="34"/>
-      <c r="N17" s="34"/>
-      <c r="O17" s="34"/>
-      <c r="P17" s="34"/>
-      <c r="Q17" s="34"/>
-      <c r="R17" s="34"/>
-      <c r="T17" s="33" t="s">
+      <c r="E17" s="13" t="s">
+        <v>199</v>
+      </c>
+      <c r="F17" s="13"/>
+      <c r="G17" s="13"/>
+      <c r="H17" s="13"/>
+      <c r="I17" s="13"/>
+      <c r="J17" s="13"/>
+      <c r="K17" s="13"/>
+      <c r="L17" s="13"/>
+      <c r="M17" s="13"/>
+      <c r="N17" s="13"/>
+      <c r="O17" s="13"/>
+      <c r="P17" s="13"/>
+      <c r="Q17" s="13"/>
+      <c r="R17" s="13"/>
+      <c r="T17" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="U17" s="34"/>
-      <c r="V17" s="34"/>
-      <c r="W17" s="34"/>
-      <c r="X17" s="34"/>
-      <c r="Y17" s="34"/>
-      <c r="Z17" s="34"/>
-      <c r="AA17" s="34"/>
-      <c r="AB17" s="34"/>
-      <c r="AC17" s="34"/>
-      <c r="AD17" s="34"/>
-      <c r="AE17" s="34"/>
-      <c r="AF17" s="34"/>
-      <c r="AG17" s="34"/>
+      <c r="U17" s="13"/>
+      <c r="V17" s="13"/>
+      <c r="W17" s="13"/>
+      <c r="X17" s="13"/>
+      <c r="Y17" s="13"/>
+      <c r="Z17" s="13"/>
+      <c r="AA17" s="13"/>
+      <c r="AB17" s="13"/>
+      <c r="AC17" s="13"/>
+      <c r="AD17" s="13"/>
+      <c r="AE17" s="13"/>
+      <c r="AF17" s="13"/>
+      <c r="AG17" s="13"/>
       <c r="AW17" s="18" t="s">
         <v>92</v>
       </c>
@@ -2319,35 +2310,35 @@
       </c>
     </row>
     <row r="18" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B18" s="27"/>
-      <c r="E18" s="34"/>
-      <c r="F18" s="34"/>
-      <c r="G18" s="34"/>
-      <c r="H18" s="34"/>
-      <c r="I18" s="34"/>
-      <c r="J18" s="34"/>
-      <c r="K18" s="34"/>
-      <c r="L18" s="34"/>
-      <c r="M18" s="34"/>
-      <c r="N18" s="34"/>
-      <c r="O18" s="34"/>
-      <c r="P18" s="34"/>
-      <c r="Q18" s="34"/>
-      <c r="R18" s="34"/>
-      <c r="T18" s="34"/>
-      <c r="U18" s="34"/>
-      <c r="V18" s="34"/>
-      <c r="W18" s="34"/>
-      <c r="X18" s="34"/>
-      <c r="Y18" s="34"/>
-      <c r="Z18" s="34"/>
-      <c r="AA18" s="34"/>
-      <c r="AB18" s="34"/>
-      <c r="AC18" s="34"/>
-      <c r="AD18" s="34"/>
-      <c r="AE18" s="34"/>
-      <c r="AF18" s="34"/>
-      <c r="AG18" s="34"/>
+      <c r="B18" s="31"/>
+      <c r="E18" s="13"/>
+      <c r="F18" s="13"/>
+      <c r="G18" s="13"/>
+      <c r="H18" s="13"/>
+      <c r="I18" s="13"/>
+      <c r="J18" s="13"/>
+      <c r="K18" s="13"/>
+      <c r="L18" s="13"/>
+      <c r="M18" s="13"/>
+      <c r="N18" s="13"/>
+      <c r="O18" s="13"/>
+      <c r="P18" s="13"/>
+      <c r="Q18" s="13"/>
+      <c r="R18" s="13"/>
+      <c r="T18" s="13"/>
+      <c r="U18" s="13"/>
+      <c r="V18" s="13"/>
+      <c r="W18" s="13"/>
+      <c r="X18" s="13"/>
+      <c r="Y18" s="13"/>
+      <c r="Z18" s="13"/>
+      <c r="AA18" s="13"/>
+      <c r="AB18" s="13"/>
+      <c r="AC18" s="13"/>
+      <c r="AD18" s="13"/>
+      <c r="AE18" s="13"/>
+      <c r="AF18" s="13"/>
+      <c r="AG18" s="13"/>
       <c r="AW18" s="18" t="s">
         <v>100</v>
       </c>
@@ -2385,38 +2376,38 @@
       <c r="BQ18" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="BR18" s="27"/>
+      <c r="BR18" s="31"/>
     </row>
     <row r="19" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B19" s="27"/>
-      <c r="E19" s="34"/>
-      <c r="F19" s="34"/>
-      <c r="G19" s="34"/>
-      <c r="H19" s="34"/>
-      <c r="I19" s="34"/>
-      <c r="J19" s="34"/>
-      <c r="K19" s="34"/>
-      <c r="L19" s="34"/>
-      <c r="M19" s="34"/>
-      <c r="N19" s="34"/>
-      <c r="O19" s="34"/>
-      <c r="P19" s="34"/>
-      <c r="Q19" s="34"/>
-      <c r="R19" s="34"/>
-      <c r="T19" s="34"/>
-      <c r="U19" s="34"/>
-      <c r="V19" s="34"/>
-      <c r="W19" s="34"/>
-      <c r="X19" s="34"/>
-      <c r="Y19" s="34"/>
-      <c r="Z19" s="34"/>
-      <c r="AA19" s="34"/>
-      <c r="AB19" s="34"/>
-      <c r="AC19" s="34"/>
-      <c r="AD19" s="34"/>
-      <c r="AE19" s="34"/>
-      <c r="AF19" s="34"/>
-      <c r="AG19" s="34"/>
+      <c r="B19" s="31"/>
+      <c r="E19" s="13"/>
+      <c r="F19" s="13"/>
+      <c r="G19" s="13"/>
+      <c r="H19" s="13"/>
+      <c r="I19" s="13"/>
+      <c r="J19" s="13"/>
+      <c r="K19" s="13"/>
+      <c r="L19" s="13"/>
+      <c r="M19" s="13"/>
+      <c r="N19" s="13"/>
+      <c r="O19" s="13"/>
+      <c r="P19" s="13"/>
+      <c r="Q19" s="13"/>
+      <c r="R19" s="13"/>
+      <c r="T19" s="13"/>
+      <c r="U19" s="13"/>
+      <c r="V19" s="13"/>
+      <c r="W19" s="13"/>
+      <c r="X19" s="13"/>
+      <c r="Y19" s="13"/>
+      <c r="Z19" s="13"/>
+      <c r="AA19" s="13"/>
+      <c r="AB19" s="13"/>
+      <c r="AC19" s="13"/>
+      <c r="AD19" s="13"/>
+      <c r="AE19" s="13"/>
+      <c r="AF19" s="13"/>
+      <c r="AG19" s="13"/>
       <c r="AW19" s="18" t="s">
         <v>108</v>
       </c>
@@ -2454,38 +2445,38 @@
       <c r="BQ19" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="BR19" s="27"/>
+      <c r="BR19" s="31"/>
     </row>
     <row r="20" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B20" s="27"/>
-      <c r="E20" s="34"/>
-      <c r="F20" s="34"/>
-      <c r="G20" s="34"/>
-      <c r="H20" s="34"/>
-      <c r="I20" s="34"/>
-      <c r="J20" s="34"/>
-      <c r="K20" s="34"/>
-      <c r="L20" s="34"/>
-      <c r="M20" s="34"/>
-      <c r="N20" s="34"/>
-      <c r="O20" s="34"/>
-      <c r="P20" s="34"/>
-      <c r="Q20" s="34"/>
-      <c r="R20" s="34"/>
-      <c r="T20" s="34"/>
-      <c r="U20" s="34"/>
-      <c r="V20" s="34"/>
-      <c r="W20" s="34"/>
-      <c r="X20" s="34"/>
-      <c r="Y20" s="34"/>
-      <c r="Z20" s="34"/>
-      <c r="AA20" s="34"/>
-      <c r="AB20" s="34"/>
-      <c r="AC20" s="34"/>
-      <c r="AD20" s="34"/>
-      <c r="AE20" s="34"/>
-      <c r="AF20" s="34"/>
-      <c r="AG20" s="34"/>
+      <c r="B20" s="31"/>
+      <c r="E20" s="13"/>
+      <c r="F20" s="13"/>
+      <c r="G20" s="13"/>
+      <c r="H20" s="13"/>
+      <c r="I20" s="13"/>
+      <c r="J20" s="13"/>
+      <c r="K20" s="13"/>
+      <c r="L20" s="13"/>
+      <c r="M20" s="13"/>
+      <c r="N20" s="13"/>
+      <c r="O20" s="13"/>
+      <c r="P20" s="13"/>
+      <c r="Q20" s="13"/>
+      <c r="R20" s="13"/>
+      <c r="T20" s="13"/>
+      <c r="U20" s="13"/>
+      <c r="V20" s="13"/>
+      <c r="W20" s="13"/>
+      <c r="X20" s="13"/>
+      <c r="Y20" s="13"/>
+      <c r="Z20" s="13"/>
+      <c r="AA20" s="13"/>
+      <c r="AB20" s="13"/>
+      <c r="AC20" s="13"/>
+      <c r="AD20" s="13"/>
+      <c r="AE20" s="13"/>
+      <c r="AF20" s="13"/>
+      <c r="AG20" s="13"/>
       <c r="AW20" s="18" t="s">
         <v>116</v>
       </c>
@@ -2523,10 +2514,10 @@
       <c r="BQ20" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="BR20" s="27"/>
+      <c r="BR20" s="31"/>
     </row>
     <row r="21" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B21" s="27"/>
+      <c r="B21" s="31"/>
       <c r="AW21" s="18" t="s">
         <v>124</v>
       </c>
@@ -2564,10 +2555,10 @@
       <c r="BQ21" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="BR21" s="27"/>
+      <c r="BR21" s="31"/>
     </row>
     <row r="22" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B22" s="27"/>
+      <c r="B22" s="31"/>
       <c r="AW22" s="18" t="s">
         <v>132</v>
       </c>
@@ -2605,10 +2596,10 @@
       <c r="BQ22" s="8" t="s">
         <v>139</v>
       </c>
-      <c r="BR22" s="27"/>
+      <c r="BR22" s="31"/>
     </row>
     <row r="23" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B23" s="27"/>
+      <c r="B23" s="31"/>
       <c r="AW23" s="18" t="s">
         <v>140</v>
       </c>
@@ -2646,10 +2637,10 @@
       <c r="BQ23" s="8" t="s">
         <v>147</v>
       </c>
-      <c r="BR23" s="27"/>
+      <c r="BR23" s="31"/>
     </row>
     <row r="24" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B24" s="27"/>
+      <c r="B24" s="31"/>
       <c r="AW24" s="18" t="s">
         <v>148</v>
       </c>
@@ -2687,27 +2678,27 @@
       <c r="BQ24" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="BR24" s="27"/>
+      <c r="BR24" s="31"/>
     </row>
     <row r="25" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B25" s="27"/>
+      <c r="B25" s="31"/>
       <c r="AW25" s="18" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="AX25" s="20"/>
-      <c r="AY25" s="35" t="s">
+      <c r="AY25" s="28" t="s">
         <v>156</v>
       </c>
-      <c r="AZ25" s="36"/>
-      <c r="BA25" s="36"/>
-      <c r="BB25" s="37"/>
+      <c r="AZ25" s="29"/>
+      <c r="BA25" s="29"/>
+      <c r="BB25" s="30"/>
       <c r="BC25" s="19" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="BD25" s="19"/>
       <c r="BE25" s="20"/>
       <c r="BF25" s="18" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="BG25" s="19"/>
       <c r="BH25" s="19"/>
@@ -2718,7 +2709,7 @@
         <v>157</v>
       </c>
       <c r="BM25" s="18" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="BN25" s="19"/>
       <c r="BO25" s="20"/>
@@ -2728,42 +2719,42 @@
       <c r="BQ25" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="BR25" s="27"/>
+      <c r="BR25" s="31"/>
     </row>
     <row r="26" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B26" s="27"/>
-      <c r="E26" s="33" t="s">
-        <v>226</v>
-      </c>
-      <c r="F26" s="34"/>
-      <c r="G26" s="34"/>
-      <c r="H26" s="34"/>
-      <c r="I26" s="34"/>
-      <c r="J26" s="34"/>
-      <c r="K26" s="34"/>
-      <c r="L26" s="34"/>
-      <c r="M26" s="34"/>
-      <c r="N26" s="34"/>
-      <c r="O26" s="34"/>
-      <c r="P26" s="34"/>
-      <c r="Q26" s="34"/>
-      <c r="R26" s="34"/>
-      <c r="T26" s="33" t="s">
+      <c r="B26" s="31"/>
+      <c r="E26" s="13" t="s">
+        <v>200</v>
+      </c>
+      <c r="F26" s="13"/>
+      <c r="G26" s="13"/>
+      <c r="H26" s="13"/>
+      <c r="I26" s="13"/>
+      <c r="J26" s="13"/>
+      <c r="K26" s="13"/>
+      <c r="L26" s="13"/>
+      <c r="M26" s="13"/>
+      <c r="N26" s="13"/>
+      <c r="O26" s="13"/>
+      <c r="P26" s="13"/>
+      <c r="Q26" s="13"/>
+      <c r="R26" s="13"/>
+      <c r="T26" s="13" t="s">
         <v>171</v>
       </c>
-      <c r="U26" s="34"/>
-      <c r="V26" s="34"/>
-      <c r="W26" s="34"/>
-      <c r="X26" s="34"/>
-      <c r="Y26" s="34"/>
-      <c r="Z26" s="34"/>
-      <c r="AA26" s="34"/>
-      <c r="AB26" s="34"/>
-      <c r="AC26" s="34"/>
-      <c r="AD26" s="34"/>
-      <c r="AE26" s="34"/>
-      <c r="AF26" s="34"/>
-      <c r="AG26" s="34"/>
+      <c r="U26" s="13"/>
+      <c r="V26" s="13"/>
+      <c r="W26" s="13"/>
+      <c r="X26" s="13"/>
+      <c r="Y26" s="13"/>
+      <c r="Z26" s="13"/>
+      <c r="AA26" s="13"/>
+      <c r="AB26" s="13"/>
+      <c r="AC26" s="13"/>
+      <c r="AD26" s="13"/>
+      <c r="AE26" s="13"/>
+      <c r="AF26" s="13"/>
+      <c r="AG26" s="13"/>
       <c r="AW26" s="18" t="s">
         <v>160</v>
       </c>
@@ -2801,72 +2792,72 @@
       <c r="BQ26" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="BR26" s="27"/>
+      <c r="BR26" s="31"/>
     </row>
     <row r="27" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B27" s="27"/>
-      <c r="E27" s="34"/>
-      <c r="F27" s="34"/>
-      <c r="G27" s="34"/>
-      <c r="H27" s="34"/>
-      <c r="I27" s="34"/>
-      <c r="J27" s="34"/>
-      <c r="K27" s="34"/>
-      <c r="L27" s="34"/>
-      <c r="M27" s="34"/>
-      <c r="N27" s="34"/>
-      <c r="O27" s="34"/>
-      <c r="P27" s="34"/>
-      <c r="Q27" s="34"/>
-      <c r="R27" s="34"/>
-      <c r="T27" s="34"/>
-      <c r="U27" s="34"/>
-      <c r="V27" s="34"/>
-      <c r="W27" s="34"/>
-      <c r="X27" s="34"/>
-      <c r="Y27" s="34"/>
-      <c r="Z27" s="34"/>
-      <c r="AA27" s="34"/>
-      <c r="AB27" s="34"/>
-      <c r="AC27" s="34"/>
-      <c r="AD27" s="34"/>
-      <c r="AE27" s="34"/>
-      <c r="AF27" s="34"/>
-      <c r="AG27" s="34"/>
+      <c r="B27" s="31"/>
+      <c r="E27" s="13"/>
+      <c r="F27" s="13"/>
+      <c r="G27" s="13"/>
+      <c r="H27" s="13"/>
+      <c r="I27" s="13"/>
+      <c r="J27" s="13"/>
+      <c r="K27" s="13"/>
+      <c r="L27" s="13"/>
+      <c r="M27" s="13"/>
+      <c r="N27" s="13"/>
+      <c r="O27" s="13"/>
+      <c r="P27" s="13"/>
+      <c r="Q27" s="13"/>
+      <c r="R27" s="13"/>
+      <c r="T27" s="13"/>
+      <c r="U27" s="13"/>
+      <c r="V27" s="13"/>
+      <c r="W27" s="13"/>
+      <c r="X27" s="13"/>
+      <c r="Y27" s="13"/>
+      <c r="Z27" s="13"/>
+      <c r="AA27" s="13"/>
+      <c r="AB27" s="13"/>
+      <c r="AC27" s="13"/>
+      <c r="AD27" s="13"/>
+      <c r="AE27" s="13"/>
+      <c r="AF27" s="13"/>
+      <c r="AG27" s="13"/>
       <c r="BQ27" s="6"/>
-      <c r="BR27" s="27"/>
+      <c r="BR27" s="31"/>
     </row>
     <row r="28" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B28" s="27"/>
-      <c r="E28" s="34"/>
-      <c r="F28" s="34"/>
-      <c r="G28" s="34"/>
-      <c r="H28" s="34"/>
-      <c r="I28" s="34"/>
-      <c r="J28" s="34"/>
-      <c r="K28" s="34"/>
-      <c r="L28" s="34"/>
-      <c r="M28" s="34"/>
-      <c r="N28" s="34"/>
-      <c r="O28" s="34"/>
-      <c r="P28" s="34"/>
-      <c r="Q28" s="34"/>
-      <c r="R28" s="34"/>
-      <c r="T28" s="34"/>
-      <c r="U28" s="34"/>
-      <c r="V28" s="34"/>
-      <c r="W28" s="34"/>
-      <c r="X28" s="34"/>
-      <c r="Y28" s="34"/>
-      <c r="Z28" s="34"/>
-      <c r="AA28" s="34"/>
-      <c r="AB28" s="34"/>
-      <c r="AC28" s="34"/>
-      <c r="AD28" s="34"/>
-      <c r="AE28" s="34"/>
-      <c r="AF28" s="34"/>
-      <c r="AG28" s="34"/>
-      <c r="AI28" s="13"/>
+      <c r="B28" s="31"/>
+      <c r="E28" s="13"/>
+      <c r="F28" s="13"/>
+      <c r="G28" s="13"/>
+      <c r="H28" s="13"/>
+      <c r="I28" s="13"/>
+      <c r="J28" s="13"/>
+      <c r="K28" s="13"/>
+      <c r="L28" s="13"/>
+      <c r="M28" s="13"/>
+      <c r="N28" s="13"/>
+      <c r="O28" s="13"/>
+      <c r="P28" s="13"/>
+      <c r="Q28" s="13"/>
+      <c r="R28" s="13"/>
+      <c r="T28" s="13"/>
+      <c r="U28" s="13"/>
+      <c r="V28" s="13"/>
+      <c r="W28" s="13"/>
+      <c r="X28" s="13"/>
+      <c r="Y28" s="13"/>
+      <c r="Z28" s="13"/>
+      <c r="AA28" s="13"/>
+      <c r="AB28" s="13"/>
+      <c r="AC28" s="13"/>
+      <c r="AD28" s="13"/>
+      <c r="AE28" s="13"/>
+      <c r="AF28" s="13"/>
+      <c r="AG28" s="13"/>
+      <c r="AI28" s="3"/>
       <c r="AV28" s="6"/>
       <c r="AW28" s="9"/>
       <c r="AX28" s="9"/>
@@ -2889,40 +2880,40 @@
       <c r="BO28" s="9"/>
       <c r="BP28" s="9"/>
       <c r="BQ28" s="9"/>
-      <c r="BR28" s="27"/>
+      <c r="BR28" s="31"/>
     </row>
     <row r="29" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B29" s="28"/>
-      <c r="E29" s="34"/>
-      <c r="F29" s="34"/>
-      <c r="G29" s="34"/>
-      <c r="H29" s="34"/>
-      <c r="I29" s="34"/>
-      <c r="J29" s="34"/>
-      <c r="K29" s="34"/>
-      <c r="L29" s="34"/>
-      <c r="M29" s="34"/>
-      <c r="N29" s="34"/>
-      <c r="O29" s="34"/>
-      <c r="P29" s="34"/>
-      <c r="Q29" s="34"/>
-      <c r="R29" s="34"/>
-      <c r="T29" s="34"/>
-      <c r="U29" s="34"/>
-      <c r="V29" s="34"/>
-      <c r="W29" s="34"/>
-      <c r="X29" s="34"/>
-      <c r="Y29" s="34"/>
-      <c r="Z29" s="34"/>
-      <c r="AA29" s="34"/>
-      <c r="AB29" s="34"/>
-      <c r="AC29" s="34"/>
-      <c r="AD29" s="34"/>
-      <c r="AE29" s="34"/>
-      <c r="AF29" s="34"/>
-      <c r="AG29" s="34"/>
+      <c r="B29" s="27"/>
+      <c r="E29" s="13"/>
+      <c r="F29" s="13"/>
+      <c r="G29" s="13"/>
+      <c r="H29" s="13"/>
+      <c r="I29" s="13"/>
+      <c r="J29" s="13"/>
+      <c r="K29" s="13"/>
+      <c r="L29" s="13"/>
+      <c r="M29" s="13"/>
+      <c r="N29" s="13"/>
+      <c r="O29" s="13"/>
+      <c r="P29" s="13"/>
+      <c r="Q29" s="13"/>
+      <c r="R29" s="13"/>
+      <c r="T29" s="13"/>
+      <c r="U29" s="13"/>
+      <c r="V29" s="13"/>
+      <c r="W29" s="13"/>
+      <c r="X29" s="13"/>
+      <c r="Y29" s="13"/>
+      <c r="Z29" s="13"/>
+      <c r="AA29" s="13"/>
+      <c r="AB29" s="13"/>
+      <c r="AC29" s="13"/>
+      <c r="AD29" s="13"/>
+      <c r="AE29" s="13"/>
+      <c r="AF29" s="13"/>
+      <c r="AG29" s="13"/>
       <c r="BQ29" s="6"/>
-      <c r="BR29" s="28"/>
+      <c r="BR29" s="27"/>
     </row>
     <row r="30" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B30" s="26" t="s">
@@ -2933,7 +2924,7 @@
       </c>
     </row>
     <row r="31" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B31" s="27"/>
+      <c r="B31" s="31"/>
       <c r="AW31" s="21" t="s">
         <v>169</v>
       </c>
@@ -2959,10 +2950,12 @@
       <c r="BO31" s="14"/>
       <c r="BP31" s="14"/>
       <c r="BQ31" s="15"/>
-      <c r="BR31" s="27"/>
+      <c r="BR31" s="31"/>
     </row>
     <row r="32" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B32" s="27"/>
+      <c r="B32" s="31"/>
+      <c r="E32" s="3"/>
+      <c r="AA32" s="3"/>
       <c r="AW32" s="25"/>
       <c r="AX32" s="16"/>
       <c r="AY32" s="16"/>
@@ -2984,10 +2977,10 @@
       <c r="BO32" s="16"/>
       <c r="BP32" s="16"/>
       <c r="BQ32" s="17"/>
-      <c r="BR32" s="27"/>
+      <c r="BR32" s="31"/>
     </row>
     <row r="33" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B33" s="27"/>
+      <c r="B33" s="31"/>
       <c r="AW33" s="25"/>
       <c r="AX33" s="16"/>
       <c r="AY33" s="16"/>
@@ -3009,10 +3002,10 @@
       <c r="BO33" s="16"/>
       <c r="BP33" s="16"/>
       <c r="BQ33" s="17"/>
-      <c r="BR33" s="27"/>
+      <c r="BR33" s="31"/>
     </row>
     <row r="34" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B34" s="27"/>
+      <c r="B34" s="31"/>
       <c r="AW34" s="25"/>
       <c r="AX34" s="16"/>
       <c r="AY34" s="16"/>
@@ -3034,42 +3027,42 @@
       <c r="BO34" s="16"/>
       <c r="BP34" s="16"/>
       <c r="BQ34" s="17"/>
-      <c r="BR34" s="27"/>
+      <c r="BR34" s="31"/>
     </row>
     <row r="35" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B35" s="27"/>
-      <c r="E35" s="33" t="s">
-        <v>227</v>
-      </c>
-      <c r="F35" s="34"/>
-      <c r="G35" s="34"/>
-      <c r="H35" s="34"/>
-      <c r="I35" s="34"/>
-      <c r="J35" s="34"/>
-      <c r="K35" s="34"/>
-      <c r="L35" s="34"/>
-      <c r="M35" s="34"/>
-      <c r="N35" s="34"/>
-      <c r="O35" s="34"/>
-      <c r="P35" s="34"/>
-      <c r="Q35" s="34"/>
-      <c r="R35" s="34"/>
-      <c r="T35" s="33" t="s">
+      <c r="B35" s="31"/>
+      <c r="E35" s="13" t="s">
+        <v>201</v>
+      </c>
+      <c r="F35" s="13"/>
+      <c r="G35" s="13"/>
+      <c r="H35" s="13"/>
+      <c r="I35" s="13"/>
+      <c r="J35" s="13"/>
+      <c r="K35" s="13"/>
+      <c r="L35" s="13"/>
+      <c r="M35" s="13"/>
+      <c r="N35" s="13"/>
+      <c r="O35" s="13"/>
+      <c r="P35" s="13"/>
+      <c r="Q35" s="13"/>
+      <c r="R35" s="13"/>
+      <c r="T35" s="13" t="s">
         <v>172</v>
       </c>
-      <c r="U35" s="34"/>
-      <c r="V35" s="34"/>
-      <c r="W35" s="34"/>
-      <c r="X35" s="34"/>
-      <c r="Y35" s="34"/>
-      <c r="Z35" s="34"/>
-      <c r="AA35" s="34"/>
-      <c r="AB35" s="34"/>
-      <c r="AC35" s="34"/>
-      <c r="AD35" s="34"/>
-      <c r="AE35" s="34"/>
-      <c r="AF35" s="34"/>
-      <c r="AG35" s="34"/>
+      <c r="U35" s="13"/>
+      <c r="V35" s="13"/>
+      <c r="W35" s="13"/>
+      <c r="X35" s="13"/>
+      <c r="Y35" s="13"/>
+      <c r="Z35" s="13"/>
+      <c r="AA35" s="13"/>
+      <c r="AB35" s="13"/>
+      <c r="AC35" s="13"/>
+      <c r="AD35" s="13"/>
+      <c r="AE35" s="13"/>
+      <c r="AF35" s="13"/>
+      <c r="AG35" s="13"/>
       <c r="AW35" s="25"/>
       <c r="AX35" s="16"/>
       <c r="AY35" s="16"/>
@@ -3091,38 +3084,38 @@
       <c r="BO35" s="16"/>
       <c r="BP35" s="16"/>
       <c r="BQ35" s="17"/>
-      <c r="BR35" s="27"/>
+      <c r="BR35" s="31"/>
     </row>
     <row r="36" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B36" s="27"/>
-      <c r="E36" s="34"/>
-      <c r="F36" s="34"/>
-      <c r="G36" s="34"/>
-      <c r="H36" s="34"/>
-      <c r="I36" s="34"/>
-      <c r="J36" s="34"/>
-      <c r="K36" s="34"/>
-      <c r="L36" s="34"/>
-      <c r="M36" s="34"/>
-      <c r="N36" s="34"/>
-      <c r="O36" s="34"/>
-      <c r="P36" s="34"/>
-      <c r="Q36" s="34"/>
-      <c r="R36" s="34"/>
-      <c r="T36" s="34"/>
-      <c r="U36" s="34"/>
-      <c r="V36" s="34"/>
-      <c r="W36" s="34"/>
-      <c r="X36" s="34"/>
-      <c r="Y36" s="34"/>
-      <c r="Z36" s="34"/>
-      <c r="AA36" s="34"/>
-      <c r="AB36" s="34"/>
-      <c r="AC36" s="34"/>
-      <c r="AD36" s="34"/>
-      <c r="AE36" s="34"/>
-      <c r="AF36" s="34"/>
-      <c r="AG36" s="34"/>
+      <c r="B36" s="31"/>
+      <c r="E36" s="13"/>
+      <c r="F36" s="13"/>
+      <c r="G36" s="13"/>
+      <c r="H36" s="13"/>
+      <c r="I36" s="13"/>
+      <c r="J36" s="13"/>
+      <c r="K36" s="13"/>
+      <c r="L36" s="13"/>
+      <c r="M36" s="13"/>
+      <c r="N36" s="13"/>
+      <c r="O36" s="13"/>
+      <c r="P36" s="13"/>
+      <c r="Q36" s="13"/>
+      <c r="R36" s="13"/>
+      <c r="T36" s="13"/>
+      <c r="U36" s="13"/>
+      <c r="V36" s="13"/>
+      <c r="W36" s="13"/>
+      <c r="X36" s="13"/>
+      <c r="Y36" s="13"/>
+      <c r="Z36" s="13"/>
+      <c r="AA36" s="13"/>
+      <c r="AB36" s="13"/>
+      <c r="AC36" s="13"/>
+      <c r="AD36" s="13"/>
+      <c r="AE36" s="13"/>
+      <c r="AF36" s="13"/>
+      <c r="AG36" s="13"/>
       <c r="AW36" s="22"/>
       <c r="AX36" s="23"/>
       <c r="AY36" s="23"/>
@@ -3144,102 +3137,102 @@
       <c r="BO36" s="23"/>
       <c r="BP36" s="23"/>
       <c r="BQ36" s="24"/>
-      <c r="BR36" s="27"/>
+      <c r="BR36" s="31"/>
     </row>
     <row r="37" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B37" s="27"/>
-      <c r="E37" s="34"/>
-      <c r="F37" s="34"/>
-      <c r="G37" s="34"/>
-      <c r="H37" s="34"/>
-      <c r="I37" s="34"/>
-      <c r="J37" s="34"/>
-      <c r="K37" s="34"/>
-      <c r="L37" s="34"/>
-      <c r="M37" s="34"/>
-      <c r="N37" s="34"/>
-      <c r="O37" s="34"/>
-      <c r="P37" s="34"/>
-      <c r="Q37" s="34"/>
-      <c r="R37" s="34"/>
-      <c r="T37" s="34"/>
-      <c r="U37" s="34"/>
-      <c r="V37" s="34"/>
-      <c r="W37" s="34"/>
-      <c r="X37" s="34"/>
-      <c r="Y37" s="34"/>
-      <c r="Z37" s="34"/>
-      <c r="AA37" s="34"/>
-      <c r="AB37" s="34"/>
-      <c r="AC37" s="34"/>
-      <c r="AD37" s="34"/>
-      <c r="AE37" s="34"/>
-      <c r="AF37" s="34"/>
-      <c r="AG37" s="34"/>
-      <c r="BR37" s="27"/>
+      <c r="B37" s="31"/>
+      <c r="E37" s="13"/>
+      <c r="F37" s="13"/>
+      <c r="G37" s="13"/>
+      <c r="H37" s="13"/>
+      <c r="I37" s="13"/>
+      <c r="J37" s="13"/>
+      <c r="K37" s="13"/>
+      <c r="L37" s="13"/>
+      <c r="M37" s="13"/>
+      <c r="N37" s="13"/>
+      <c r="O37" s="13"/>
+      <c r="P37" s="13"/>
+      <c r="Q37" s="13"/>
+      <c r="R37" s="13"/>
+      <c r="T37" s="13"/>
+      <c r="U37" s="13"/>
+      <c r="V37" s="13"/>
+      <c r="W37" s="13"/>
+      <c r="X37" s="13"/>
+      <c r="Y37" s="13"/>
+      <c r="Z37" s="13"/>
+      <c r="AA37" s="13"/>
+      <c r="AB37" s="13"/>
+      <c r="AC37" s="13"/>
+      <c r="AD37" s="13"/>
+      <c r="AE37" s="13"/>
+      <c r="AF37" s="13"/>
+      <c r="AG37" s="13"/>
+      <c r="BR37" s="31"/>
     </row>
     <row r="38" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B38" s="27"/>
-      <c r="E38" s="34"/>
-      <c r="F38" s="34"/>
-      <c r="G38" s="34"/>
-      <c r="H38" s="34"/>
-      <c r="I38" s="34"/>
-      <c r="J38" s="34"/>
-      <c r="K38" s="34"/>
-      <c r="L38" s="34"/>
-      <c r="M38" s="34"/>
-      <c r="N38" s="34"/>
-      <c r="O38" s="34"/>
-      <c r="P38" s="34"/>
-      <c r="Q38" s="34"/>
-      <c r="R38" s="34"/>
-      <c r="T38" s="34"/>
-      <c r="U38" s="34"/>
-      <c r="V38" s="34"/>
-      <c r="W38" s="34"/>
-      <c r="X38" s="34"/>
-      <c r="Y38" s="34"/>
-      <c r="Z38" s="34"/>
-      <c r="AA38" s="34"/>
-      <c r="AB38" s="34"/>
-      <c r="AC38" s="34"/>
-      <c r="AD38" s="34"/>
-      <c r="AE38" s="34"/>
-      <c r="AF38" s="34"/>
-      <c r="AG38" s="34"/>
-      <c r="BR38" s="27"/>
+      <c r="B38" s="31"/>
+      <c r="E38" s="13"/>
+      <c r="F38" s="13"/>
+      <c r="G38" s="13"/>
+      <c r="H38" s="13"/>
+      <c r="I38" s="13"/>
+      <c r="J38" s="13"/>
+      <c r="K38" s="13"/>
+      <c r="L38" s="13"/>
+      <c r="M38" s="13"/>
+      <c r="N38" s="13"/>
+      <c r="O38" s="13"/>
+      <c r="P38" s="13"/>
+      <c r="Q38" s="13"/>
+      <c r="R38" s="13"/>
+      <c r="T38" s="13"/>
+      <c r="U38" s="13"/>
+      <c r="V38" s="13"/>
+      <c r="W38" s="13"/>
+      <c r="X38" s="13"/>
+      <c r="Y38" s="13"/>
+      <c r="Z38" s="13"/>
+      <c r="AA38" s="13"/>
+      <c r="AB38" s="13"/>
+      <c r="AC38" s="13"/>
+      <c r="AD38" s="13"/>
+      <c r="AE38" s="13"/>
+      <c r="AF38" s="13"/>
+      <c r="AG38" s="13"/>
+      <c r="BR38" s="31"/>
     </row>
     <row r="39" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B39" s="27"/>
-      <c r="E39" s="34"/>
-      <c r="F39" s="34"/>
-      <c r="G39" s="34"/>
-      <c r="H39" s="34"/>
-      <c r="I39" s="34"/>
-      <c r="J39" s="34"/>
-      <c r="K39" s="34"/>
-      <c r="L39" s="34"/>
-      <c r="M39" s="34"/>
-      <c r="N39" s="34"/>
-      <c r="O39" s="34"/>
-      <c r="P39" s="34"/>
-      <c r="Q39" s="34"/>
-      <c r="R39" s="34"/>
-      <c r="T39" s="34"/>
-      <c r="U39" s="34"/>
-      <c r="V39" s="34"/>
-      <c r="W39" s="34"/>
-      <c r="X39" s="34"/>
-      <c r="Y39" s="34"/>
-      <c r="Z39" s="34"/>
-      <c r="AA39" s="34"/>
-      <c r="AB39" s="34"/>
-      <c r="AC39" s="34"/>
-      <c r="AD39" s="34"/>
-      <c r="AE39" s="34"/>
-      <c r="AF39" s="34"/>
-      <c r="AG39" s="34"/>
+      <c r="B39" s="31"/>
+      <c r="E39" s="13"/>
+      <c r="F39" s="13"/>
+      <c r="G39" s="13"/>
+      <c r="H39" s="13"/>
+      <c r="I39" s="13"/>
+      <c r="J39" s="13"/>
+      <c r="K39" s="13"/>
+      <c r="L39" s="13"/>
+      <c r="M39" s="13"/>
+      <c r="N39" s="13"/>
+      <c r="O39" s="13"/>
+      <c r="P39" s="13"/>
+      <c r="Q39" s="13"/>
+      <c r="R39" s="13"/>
+      <c r="T39" s="13"/>
+      <c r="U39" s="13"/>
+      <c r="V39" s="13"/>
+      <c r="W39" s="13"/>
+      <c r="X39" s="13"/>
+      <c r="Y39" s="13"/>
+      <c r="Z39" s="13"/>
+      <c r="AA39" s="13"/>
+      <c r="AB39" s="13"/>
+      <c r="AC39" s="13"/>
+      <c r="AD39" s="13"/>
+      <c r="AE39" s="13"/>
+      <c r="AF39" s="13"/>
+      <c r="AG39" s="13"/>
       <c r="AW39" s="1" t="s">
         <v>173</v>
       </c>
@@ -3273,10 +3266,10 @@
       </c>
       <c r="BP39" s="19"/>
       <c r="BQ39" s="20"/>
-      <c r="BR39" s="27"/>
+      <c r="BR39" s="31"/>
     </row>
     <row r="40" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B40" s="27"/>
+      <c r="B40" s="31"/>
       <c r="AW40" s="5" t="s">
         <v>179</v>
       </c>
@@ -3310,10 +3303,10 @@
       </c>
       <c r="BP40" s="19"/>
       <c r="BQ40" s="20"/>
-      <c r="BR40" s="27"/>
+      <c r="BR40" s="31"/>
     </row>
     <row r="41" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B41" s="27"/>
+      <c r="B41" s="31"/>
       <c r="AW41" s="5" t="s">
         <v>185</v>
       </c>
@@ -3347,10 +3340,10 @@
       </c>
       <c r="BP41" s="19"/>
       <c r="BQ41" s="20"/>
-      <c r="BR41" s="27"/>
+      <c r="BR41" s="31"/>
     </row>
     <row r="42" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B42" s="27"/>
+      <c r="B42" s="31"/>
       <c r="AW42" s="5" t="s">
         <v>191</v>
       </c>
@@ -3384,10 +3377,10 @@
       </c>
       <c r="BP42" s="19"/>
       <c r="BQ42" s="20"/>
-      <c r="BR42" s="27"/>
+      <c r="BR42" s="31"/>
     </row>
     <row r="43" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B43" s="28"/>
+      <c r="B43" s="27"/>
       <c r="AW43" s="26" t="s">
         <v>197</v>
       </c>
@@ -3411,13 +3404,13 @@
       <c r="BO43" s="21"/>
       <c r="BP43" s="14"/>
       <c r="BQ43" s="15"/>
-      <c r="BR43" s="28"/>
+      <c r="BR43" s="27"/>
     </row>
     <row r="44" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B44" s="26" t="s">
-        <v>198</v>
-      </c>
-      <c r="AW44" s="28"/>
+        <v>203</v>
+      </c>
+      <c r="AW44" s="27"/>
       <c r="AX44" s="22"/>
       <c r="AY44" s="23"/>
       <c r="AZ44" s="24"/>
@@ -3439,21 +3432,21 @@
       <c r="BP44" s="23"/>
       <c r="BQ44" s="24"/>
       <c r="BR44" s="26" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
     </row>
     <row r="45" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B45" s="27"/>
+      <c r="B45" s="31"/>
       <c r="AW45" s="5" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="AX45" s="18" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="AY45" s="19"/>
       <c r="AZ45" s="20"/>
       <c r="BA45" s="18" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="BB45" s="19"/>
       <c r="BC45" s="19"/>
@@ -3463,32 +3456,32 @@
       <c r="BG45" s="19"/>
       <c r="BH45" s="20"/>
       <c r="BI45" s="18" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="BJ45" s="19"/>
       <c r="BK45" s="20"/>
       <c r="BL45" s="18" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="BM45" s="19"/>
       <c r="BN45" s="20"/>
       <c r="BO45" s="18" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="BP45" s="19"/>
       <c r="BQ45" s="20"/>
-      <c r="BR45" s="27"/>
+      <c r="BR45" s="31"/>
     </row>
     <row r="46" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B46" s="27"/>
+      <c r="B46" s="31"/>
       <c r="AW46" s="18" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="AX46" s="19"/>
       <c r="AY46" s="19"/>
       <c r="AZ46" s="20"/>
       <c r="BA46" s="18" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="BB46" s="19"/>
       <c r="BC46" s="19"/>
@@ -3498,7 +3491,7 @@
       <c r="BG46" s="19"/>
       <c r="BH46" s="20"/>
       <c r="BI46" s="18" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="BJ46" s="19"/>
       <c r="BK46" s="19"/>
@@ -3508,50 +3501,50 @@
       <c r="BO46" s="19"/>
       <c r="BP46" s="19"/>
       <c r="BQ46" s="20"/>
-      <c r="BR46" s="27"/>
+      <c r="BR46" s="31"/>
     </row>
     <row r="47" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B47" s="27"/>
-      <c r="E47" s="33" t="s">
-        <v>228</v>
-      </c>
-      <c r="F47" s="34"/>
-      <c r="G47" s="34"/>
-      <c r="H47" s="34"/>
-      <c r="I47" s="34"/>
-      <c r="J47" s="34"/>
-      <c r="K47" s="34"/>
-      <c r="L47" s="34"/>
-      <c r="M47" s="34"/>
-      <c r="N47" s="34"/>
-      <c r="O47" s="34"/>
-      <c r="P47" s="34"/>
-      <c r="Q47" s="34"/>
-      <c r="R47" s="34"/>
-      <c r="T47" s="33" t="s">
-        <v>229</v>
-      </c>
-      <c r="U47" s="34"/>
-      <c r="V47" s="34"/>
-      <c r="W47" s="34"/>
-      <c r="X47" s="34"/>
-      <c r="Y47" s="34"/>
-      <c r="Z47" s="34"/>
-      <c r="AA47" s="34"/>
-      <c r="AB47" s="34"/>
-      <c r="AC47" s="34"/>
-      <c r="AD47" s="34"/>
-      <c r="AE47" s="34"/>
-      <c r="AF47" s="34"/>
-      <c r="AG47" s="34"/>
+      <c r="B47" s="31"/>
+      <c r="E47" s="13" t="s">
+        <v>202</v>
+      </c>
+      <c r="F47" s="13"/>
+      <c r="G47" s="13"/>
+      <c r="H47" s="13"/>
+      <c r="I47" s="13"/>
+      <c r="J47" s="13"/>
+      <c r="K47" s="13"/>
+      <c r="L47" s="13"/>
+      <c r="M47" s="13"/>
+      <c r="N47" s="13"/>
+      <c r="O47" s="13"/>
+      <c r="P47" s="13"/>
+      <c r="Q47" s="13"/>
+      <c r="R47" s="13"/>
+      <c r="T47" s="13" t="s">
+        <v>231</v>
+      </c>
+      <c r="U47" s="13"/>
+      <c r="V47" s="13"/>
+      <c r="W47" s="13"/>
+      <c r="X47" s="13"/>
+      <c r="Y47" s="13"/>
+      <c r="Z47" s="13"/>
+      <c r="AA47" s="13"/>
+      <c r="AB47" s="13"/>
+      <c r="AC47" s="13"/>
+      <c r="AD47" s="13"/>
+      <c r="AE47" s="13"/>
+      <c r="AF47" s="13"/>
+      <c r="AG47" s="13"/>
       <c r="AW47" s="18" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="AX47" s="19"/>
       <c r="AY47" s="19"/>
       <c r="AZ47" s="20"/>
       <c r="BA47" s="18" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="BB47" s="19"/>
       <c r="BC47" s="19"/>
@@ -3561,7 +3554,7 @@
       <c r="BG47" s="19"/>
       <c r="BH47" s="20"/>
       <c r="BI47" s="18" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="BJ47" s="19"/>
       <c r="BK47" s="19"/>
@@ -3571,40 +3564,40 @@
       <c r="BO47" s="19"/>
       <c r="BP47" s="19"/>
       <c r="BQ47" s="20"/>
-      <c r="BR47" s="27"/>
+      <c r="BR47" s="31"/>
     </row>
     <row r="48" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B48" s="27"/>
-      <c r="E48" s="34"/>
-      <c r="F48" s="34"/>
-      <c r="G48" s="34"/>
-      <c r="H48" s="34"/>
-      <c r="I48" s="34"/>
-      <c r="J48" s="34"/>
-      <c r="K48" s="34"/>
-      <c r="L48" s="34"/>
-      <c r="M48" s="34"/>
-      <c r="N48" s="34"/>
-      <c r="O48" s="34"/>
-      <c r="P48" s="34"/>
-      <c r="Q48" s="34"/>
-      <c r="R48" s="34"/>
-      <c r="T48" s="34"/>
-      <c r="U48" s="34"/>
-      <c r="V48" s="34"/>
-      <c r="W48" s="34"/>
-      <c r="X48" s="34"/>
-      <c r="Y48" s="34"/>
-      <c r="Z48" s="34"/>
-      <c r="AA48" s="34"/>
-      <c r="AB48" s="34"/>
-      <c r="AC48" s="34"/>
-      <c r="AD48" s="34"/>
-      <c r="AE48" s="34"/>
-      <c r="AF48" s="34"/>
-      <c r="AG48" s="34"/>
+      <c r="B48" s="31"/>
+      <c r="E48" s="13"/>
+      <c r="F48" s="13"/>
+      <c r="G48" s="13"/>
+      <c r="H48" s="13"/>
+      <c r="I48" s="13"/>
+      <c r="J48" s="13"/>
+      <c r="K48" s="13"/>
+      <c r="L48" s="13"/>
+      <c r="M48" s="13"/>
+      <c r="N48" s="13"/>
+      <c r="O48" s="13"/>
+      <c r="P48" s="13"/>
+      <c r="Q48" s="13"/>
+      <c r="R48" s="13"/>
+      <c r="T48" s="13"/>
+      <c r="U48" s="13"/>
+      <c r="V48" s="13"/>
+      <c r="W48" s="13"/>
+      <c r="X48" s="13"/>
+      <c r="Y48" s="13"/>
+      <c r="Z48" s="13"/>
+      <c r="AA48" s="13"/>
+      <c r="AB48" s="13"/>
+      <c r="AC48" s="13"/>
+      <c r="AD48" s="13"/>
+      <c r="AE48" s="13"/>
+      <c r="AF48" s="13"/>
+      <c r="AG48" s="13"/>
       <c r="AW48" s="21" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="AX48" s="14"/>
       <c r="AY48" s="14"/>
@@ -3614,7 +3607,7 @@
       <c r="BC48" s="14"/>
       <c r="BD48" s="15"/>
       <c r="BE48" s="21" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="BF48" s="14"/>
       <c r="BG48" s="14"/>
@@ -3628,38 +3621,38 @@
       <c r="BO48" s="14"/>
       <c r="BP48" s="14"/>
       <c r="BQ48" s="15"/>
-      <c r="BR48" s="27"/>
+      <c r="BR48" s="31"/>
     </row>
     <row r="49" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B49" s="27"/>
-      <c r="E49" s="34"/>
-      <c r="F49" s="34"/>
-      <c r="G49" s="34"/>
-      <c r="H49" s="34"/>
-      <c r="I49" s="34"/>
-      <c r="J49" s="34"/>
-      <c r="K49" s="34"/>
-      <c r="L49" s="34"/>
-      <c r="M49" s="34"/>
-      <c r="N49" s="34"/>
-      <c r="O49" s="34"/>
-      <c r="P49" s="34"/>
-      <c r="Q49" s="34"/>
-      <c r="R49" s="34"/>
-      <c r="T49" s="34"/>
-      <c r="U49" s="34"/>
-      <c r="V49" s="34"/>
-      <c r="W49" s="34"/>
-      <c r="X49" s="34"/>
-      <c r="Y49" s="34"/>
-      <c r="Z49" s="34"/>
-      <c r="AA49" s="34"/>
-      <c r="AB49" s="34"/>
-      <c r="AC49" s="34"/>
-      <c r="AD49" s="34"/>
-      <c r="AE49" s="34"/>
-      <c r="AF49" s="34"/>
-      <c r="AG49" s="34"/>
+      <c r="B49" s="31"/>
+      <c r="E49" s="13"/>
+      <c r="F49" s="13"/>
+      <c r="G49" s="13"/>
+      <c r="H49" s="13"/>
+      <c r="I49" s="13"/>
+      <c r="J49" s="13"/>
+      <c r="K49" s="13"/>
+      <c r="L49" s="13"/>
+      <c r="M49" s="13"/>
+      <c r="N49" s="13"/>
+      <c r="O49" s="13"/>
+      <c r="P49" s="13"/>
+      <c r="Q49" s="13"/>
+      <c r="R49" s="13"/>
+      <c r="T49" s="13"/>
+      <c r="U49" s="13"/>
+      <c r="V49" s="13"/>
+      <c r="W49" s="13"/>
+      <c r="X49" s="13"/>
+      <c r="Y49" s="13"/>
+      <c r="Z49" s="13"/>
+      <c r="AA49" s="13"/>
+      <c r="AB49" s="13"/>
+      <c r="AC49" s="13"/>
+      <c r="AD49" s="13"/>
+      <c r="AE49" s="13"/>
+      <c r="AF49" s="13"/>
+      <c r="AG49" s="13"/>
       <c r="AW49" s="25"/>
       <c r="AX49" s="16"/>
       <c r="AY49" s="16"/>
@@ -3681,38 +3674,38 @@
       <c r="BO49" s="23"/>
       <c r="BP49" s="23"/>
       <c r="BQ49" s="24"/>
-      <c r="BR49" s="27"/>
+      <c r="BR49" s="31"/>
     </row>
     <row r="50" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B50" s="27"/>
-      <c r="E50" s="34"/>
-      <c r="F50" s="34"/>
-      <c r="G50" s="34"/>
-      <c r="H50" s="34"/>
-      <c r="I50" s="34"/>
-      <c r="J50" s="34"/>
-      <c r="K50" s="34"/>
-      <c r="L50" s="34"/>
-      <c r="M50" s="34"/>
-      <c r="N50" s="34"/>
-      <c r="O50" s="34"/>
-      <c r="P50" s="34"/>
-      <c r="Q50" s="34"/>
-      <c r="R50" s="34"/>
-      <c r="T50" s="34"/>
-      <c r="U50" s="34"/>
-      <c r="V50" s="34"/>
-      <c r="W50" s="34"/>
-      <c r="X50" s="34"/>
-      <c r="Y50" s="34"/>
-      <c r="Z50" s="34"/>
-      <c r="AA50" s="34"/>
-      <c r="AB50" s="34"/>
-      <c r="AC50" s="34"/>
-      <c r="AD50" s="34"/>
-      <c r="AE50" s="34"/>
-      <c r="AF50" s="34"/>
-      <c r="AG50" s="34"/>
+      <c r="B50" s="31"/>
+      <c r="E50" s="13"/>
+      <c r="F50" s="13"/>
+      <c r="G50" s="13"/>
+      <c r="H50" s="13"/>
+      <c r="I50" s="13"/>
+      <c r="J50" s="13"/>
+      <c r="K50" s="13"/>
+      <c r="L50" s="13"/>
+      <c r="M50" s="13"/>
+      <c r="N50" s="13"/>
+      <c r="O50" s="13"/>
+      <c r="P50" s="13"/>
+      <c r="Q50" s="13"/>
+      <c r="R50" s="13"/>
+      <c r="T50" s="13"/>
+      <c r="U50" s="13"/>
+      <c r="V50" s="13"/>
+      <c r="W50" s="13"/>
+      <c r="X50" s="13"/>
+      <c r="Y50" s="13"/>
+      <c r="Z50" s="13"/>
+      <c r="AA50" s="13"/>
+      <c r="AB50" s="13"/>
+      <c r="AC50" s="13"/>
+      <c r="AD50" s="13"/>
+      <c r="AE50" s="13"/>
+      <c r="AF50" s="13"/>
+      <c r="AG50" s="13"/>
       <c r="AW50" s="25"/>
       <c r="AX50" s="16"/>
       <c r="AY50" s="16"/>
@@ -3722,7 +3715,7 @@
       <c r="BC50" s="16"/>
       <c r="BD50" s="17"/>
       <c r="BE50" s="21" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="BF50" s="14"/>
       <c r="BG50" s="14"/>
@@ -3736,38 +3729,38 @@
       <c r="BO50" s="14"/>
       <c r="BP50" s="14"/>
       <c r="BQ50" s="15"/>
-      <c r="BR50" s="27"/>
+      <c r="BR50" s="31"/>
     </row>
     <row r="51" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B51" s="27"/>
-      <c r="E51" s="34"/>
-      <c r="F51" s="34"/>
-      <c r="G51" s="34"/>
-      <c r="H51" s="34"/>
-      <c r="I51" s="34"/>
-      <c r="J51" s="34"/>
-      <c r="K51" s="34"/>
-      <c r="L51" s="34"/>
-      <c r="M51" s="34"/>
-      <c r="N51" s="34"/>
-      <c r="O51" s="34"/>
-      <c r="P51" s="34"/>
-      <c r="Q51" s="34"/>
-      <c r="R51" s="34"/>
-      <c r="T51" s="34"/>
-      <c r="U51" s="34"/>
-      <c r="V51" s="34"/>
-      <c r="W51" s="34"/>
-      <c r="X51" s="34"/>
-      <c r="Y51" s="34"/>
-      <c r="Z51" s="34"/>
-      <c r="AA51" s="34"/>
-      <c r="AB51" s="34"/>
-      <c r="AC51" s="34"/>
-      <c r="AD51" s="34"/>
-      <c r="AE51" s="34"/>
-      <c r="AF51" s="34"/>
-      <c r="AG51" s="34"/>
+      <c r="B51" s="31"/>
+      <c r="E51" s="13"/>
+      <c r="F51" s="13"/>
+      <c r="G51" s="13"/>
+      <c r="H51" s="13"/>
+      <c r="I51" s="13"/>
+      <c r="J51" s="13"/>
+      <c r="K51" s="13"/>
+      <c r="L51" s="13"/>
+      <c r="M51" s="13"/>
+      <c r="N51" s="13"/>
+      <c r="O51" s="13"/>
+      <c r="P51" s="13"/>
+      <c r="Q51" s="13"/>
+      <c r="R51" s="13"/>
+      <c r="T51" s="13"/>
+      <c r="U51" s="13"/>
+      <c r="V51" s="13"/>
+      <c r="W51" s="13"/>
+      <c r="X51" s="13"/>
+      <c r="Y51" s="13"/>
+      <c r="Z51" s="13"/>
+      <c r="AA51" s="13"/>
+      <c r="AB51" s="13"/>
+      <c r="AC51" s="13"/>
+      <c r="AD51" s="13"/>
+      <c r="AE51" s="13"/>
+      <c r="AF51" s="13"/>
+      <c r="AG51" s="13"/>
       <c r="AW51" s="22"/>
       <c r="AX51" s="23"/>
       <c r="AY51" s="23"/>
@@ -3789,12 +3782,12 @@
       <c r="BO51" s="23"/>
       <c r="BP51" s="23"/>
       <c r="BQ51" s="24"/>
-      <c r="BR51" s="27"/>
+      <c r="BR51" s="31"/>
     </row>
     <row r="52" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B52" s="27"/>
+      <c r="B52" s="31"/>
       <c r="AW52" s="21" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="AX52" s="14"/>
       <c r="AY52" s="14"/>
@@ -3804,7 +3797,7 @@
       <c r="BC52" s="14"/>
       <c r="BD52" s="15"/>
       <c r="BE52" s="21" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="BF52" s="14"/>
       <c r="BG52" s="14"/>
@@ -3818,12 +3811,12 @@
       <c r="BO52" s="14"/>
       <c r="BP52" s="14"/>
       <c r="BQ52" s="15"/>
-      <c r="BR52" s="27"/>
+      <c r="BR52" s="31"/>
     </row>
     <row r="53" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B53" s="27"/>
+      <c r="B53" s="31"/>
       <c r="AW53" s="25" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="AX53" s="16"/>
       <c r="AY53" s="16"/>
@@ -3845,10 +3838,10 @@
       <c r="BO53" s="16"/>
       <c r="BP53" s="16"/>
       <c r="BQ53" s="17"/>
-      <c r="BR53" s="27"/>
+      <c r="BR53" s="31"/>
     </row>
     <row r="54" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B54" s="27"/>
+      <c r="B54" s="31"/>
       <c r="AW54" s="25"/>
       <c r="AX54" s="16"/>
       <c r="AY54" s="16"/>
@@ -3870,10 +3863,10 @@
       <c r="BO54" s="16"/>
       <c r="BP54" s="16"/>
       <c r="BQ54" s="17"/>
-      <c r="BR54" s="27"/>
+      <c r="BR54" s="31"/>
     </row>
     <row r="55" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B55" s="27"/>
+      <c r="B55" s="31"/>
       <c r="AW55" s="22"/>
       <c r="AX55" s="23"/>
       <c r="AY55" s="23"/>
@@ -3895,26 +3888,18 @@
       <c r="BO55" s="23"/>
       <c r="BP55" s="23"/>
       <c r="BQ55" s="24"/>
-      <c r="BR55" s="27"/>
+      <c r="BR55" s="31"/>
     </row>
     <row r="56" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B56" s="28"/>
-      <c r="K56" s="33"/>
-      <c r="L56" s="34"/>
-      <c r="M56" s="34"/>
-      <c r="N56" s="34"/>
-      <c r="O56" s="34"/>
-      <c r="AI56" s="33"/>
-      <c r="AJ56" s="34"/>
-      <c r="AK56" s="34"/>
-      <c r="AL56" s="34"/>
-      <c r="AM56" s="34"/>
+      <c r="B56" s="27"/>
+      <c r="K56" s="3"/>
+      <c r="AI56" s="3"/>
       <c r="AW56" s="18" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="AX56" s="19"/>
       <c r="AY56" s="19" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="AZ56" s="19"/>
       <c r="BA56" s="19"/>
@@ -3934,7 +3919,7 @@
       <c r="BO56" s="19"/>
       <c r="BP56" s="19"/>
       <c r="BQ56" s="20"/>
-      <c r="BR56" s="28"/>
+      <c r="BR56" s="27"/>
     </row>
     <row r="57" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C57" s="18">
@@ -4019,20 +4004,13 @@
     </row>
     <row r="58" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4"/>
   </sheetData>
-  <mergeCells count="191">
-    <mergeCell ref="E7:R11"/>
-    <mergeCell ref="T7:AG11"/>
-    <mergeCell ref="E17:R20"/>
-    <mergeCell ref="T17:AG20"/>
-    <mergeCell ref="E26:R29"/>
-    <mergeCell ref="T26:AG29"/>
-    <mergeCell ref="E35:R39"/>
-    <mergeCell ref="T35:AG39"/>
-    <mergeCell ref="E47:R51"/>
-    <mergeCell ref="T47:AG51"/>
+  <mergeCells count="189">
+    <mergeCell ref="C57:L57"/>
+    <mergeCell ref="M57:X57"/>
+    <mergeCell ref="Y57:AI57"/>
+    <mergeCell ref="AJ57:AT57"/>
     <mergeCell ref="AW56:AX56"/>
     <mergeCell ref="BM25:BO25"/>
-    <mergeCell ref="Y57:AI57"/>
     <mergeCell ref="BL39:BN39"/>
     <mergeCell ref="C2:L2"/>
     <mergeCell ref="BO41:BQ41"/>
@@ -4052,8 +4030,6 @@
     <mergeCell ref="BA41:BH41"/>
     <mergeCell ref="AW26:AX26"/>
     <mergeCell ref="AY26:BB26"/>
-    <mergeCell ref="AW52:BD52"/>
-    <mergeCell ref="AW16:AX16"/>
     <mergeCell ref="BR17:BR29"/>
     <mergeCell ref="BM9:BO9"/>
     <mergeCell ref="AY16:BB16"/>
@@ -4078,6 +4054,8 @@
     <mergeCell ref="BC13:BE13"/>
     <mergeCell ref="BM13:BO13"/>
     <mergeCell ref="AY20:BB20"/>
+    <mergeCell ref="AW52:BD52"/>
+    <mergeCell ref="AW16:AX16"/>
     <mergeCell ref="BF5:BK6"/>
     <mergeCell ref="BC17:BE17"/>
     <mergeCell ref="AY24:BB24"/>
@@ -4088,9 +4066,6 @@
     <mergeCell ref="BQ5:BQ6"/>
     <mergeCell ref="BM21:BO21"/>
     <mergeCell ref="BF13:BK13"/>
-    <mergeCell ref="BL5:BL6"/>
-    <mergeCell ref="AY7:BB7"/>
-    <mergeCell ref="BM14:BO14"/>
     <mergeCell ref="AW13:AX13"/>
     <mergeCell ref="BA45:BH45"/>
     <mergeCell ref="AW8:AX8"/>
@@ -4101,30 +4076,8 @@
     <mergeCell ref="BC26:BE26"/>
     <mergeCell ref="BF26:BK26"/>
     <mergeCell ref="BM26:BO26"/>
-    <mergeCell ref="BI41:BK41"/>
-    <mergeCell ref="BF15:BK15"/>
-    <mergeCell ref="AY14:BB14"/>
-    <mergeCell ref="AY25:BB25"/>
-    <mergeCell ref="AY31:BQ36"/>
-    <mergeCell ref="AY12:BB12"/>
-    <mergeCell ref="BC14:BE14"/>
-    <mergeCell ref="BM22:BO22"/>
-    <mergeCell ref="AW14:AX14"/>
-    <mergeCell ref="BC10:BE10"/>
-    <mergeCell ref="BM17:BO17"/>
-    <mergeCell ref="BC23:BE23"/>
-    <mergeCell ref="BF18:BK18"/>
-    <mergeCell ref="AW12:AX12"/>
     <mergeCell ref="BE50:BQ51"/>
     <mergeCell ref="AY5:BB6"/>
-    <mergeCell ref="B17:B29"/>
-    <mergeCell ref="AY9:BB9"/>
-    <mergeCell ref="AW25:AX25"/>
-    <mergeCell ref="AW7:AX7"/>
-    <mergeCell ref="AW15:AX15"/>
-    <mergeCell ref="B44:B56"/>
-    <mergeCell ref="BL41:BN41"/>
-    <mergeCell ref="BA42:BH42"/>
     <mergeCell ref="AW49:BD51"/>
     <mergeCell ref="BI45:BK45"/>
     <mergeCell ref="BC16:BE16"/>
@@ -4136,11 +4089,10 @@
     <mergeCell ref="AW10:AX10"/>
     <mergeCell ref="BF17:BK17"/>
     <mergeCell ref="AW23:AX23"/>
-    <mergeCell ref="BM5:BO6"/>
-    <mergeCell ref="AW5:AX6"/>
     <mergeCell ref="BC18:BE18"/>
+    <mergeCell ref="AW48:BD48"/>
+    <mergeCell ref="BI41:BK41"/>
     <mergeCell ref="BE52:BQ55"/>
-    <mergeCell ref="M57:X57"/>
     <mergeCell ref="AX42:AZ42"/>
     <mergeCell ref="AW43:AW44"/>
     <mergeCell ref="BR30:BR43"/>
@@ -4148,27 +4100,25 @@
     <mergeCell ref="AX39:AZ39"/>
     <mergeCell ref="BM16:BO16"/>
     <mergeCell ref="BA46:BH46"/>
-    <mergeCell ref="K56:O56"/>
     <mergeCell ref="BA39:BH39"/>
     <mergeCell ref="BM10:BO10"/>
     <mergeCell ref="AW31:AX36"/>
     <mergeCell ref="BE48:BQ49"/>
     <mergeCell ref="BL42:BN42"/>
-    <mergeCell ref="AI56:AM56"/>
     <mergeCell ref="AY23:BB23"/>
     <mergeCell ref="AX45:AZ45"/>
     <mergeCell ref="BI42:BK42"/>
     <mergeCell ref="BF21:BK21"/>
     <mergeCell ref="BO45:BQ45"/>
     <mergeCell ref="BR44:BR56"/>
-    <mergeCell ref="BI46:BQ46"/>
-    <mergeCell ref="BM23:BO23"/>
+    <mergeCell ref="AY9:BB9"/>
+    <mergeCell ref="AW25:AX25"/>
+    <mergeCell ref="AW15:AX15"/>
     <mergeCell ref="B3:B16"/>
     <mergeCell ref="BC9:BE9"/>
     <mergeCell ref="AY18:BB18"/>
     <mergeCell ref="BI47:BQ47"/>
     <mergeCell ref="AW21:AX21"/>
-    <mergeCell ref="AJ57:AT57"/>
     <mergeCell ref="BC19:BE19"/>
     <mergeCell ref="AX41:AZ41"/>
     <mergeCell ref="BM24:BO24"/>
@@ -4184,9 +4134,32 @@
     <mergeCell ref="BC12:BE12"/>
     <mergeCell ref="BL43:BN44"/>
     <mergeCell ref="C3:D5"/>
-    <mergeCell ref="C57:L57"/>
-    <mergeCell ref="AW48:BD48"/>
+    <mergeCell ref="B17:B29"/>
+    <mergeCell ref="AW7:AX7"/>
+    <mergeCell ref="B44:B56"/>
+    <mergeCell ref="BL41:BN41"/>
     <mergeCell ref="AW3:BQ4"/>
+    <mergeCell ref="BI46:BQ46"/>
+    <mergeCell ref="BM23:BO23"/>
+    <mergeCell ref="BF15:BK15"/>
+    <mergeCell ref="BL5:BL6"/>
+    <mergeCell ref="AY14:BB14"/>
+    <mergeCell ref="AY25:BB25"/>
+    <mergeCell ref="AY31:BQ36"/>
+    <mergeCell ref="AY12:BB12"/>
+    <mergeCell ref="BC14:BE14"/>
+    <mergeCell ref="BM22:BO22"/>
+    <mergeCell ref="AW14:AX14"/>
+    <mergeCell ref="AY7:BB7"/>
+    <mergeCell ref="BC10:BE10"/>
+    <mergeCell ref="BM17:BO17"/>
+    <mergeCell ref="BC23:BE23"/>
+    <mergeCell ref="BF18:BK18"/>
+    <mergeCell ref="AW12:AX12"/>
+    <mergeCell ref="BM14:BO14"/>
+    <mergeCell ref="BA42:BH42"/>
+    <mergeCell ref="BM5:BO6"/>
+    <mergeCell ref="AW5:AX6"/>
     <mergeCell ref="AT3:AV8"/>
     <mergeCell ref="M2:X2"/>
     <mergeCell ref="AU2:BF2"/>
@@ -4211,6 +4184,16 @@
     <mergeCell ref="BA40:BH40"/>
     <mergeCell ref="AW19:AX19"/>
     <mergeCell ref="AW53:BD55"/>
+    <mergeCell ref="T7:AG11"/>
+    <mergeCell ref="T17:AG20"/>
+    <mergeCell ref="T26:AG29"/>
+    <mergeCell ref="T35:AG39"/>
+    <mergeCell ref="T47:AG51"/>
+    <mergeCell ref="E7:R11"/>
+    <mergeCell ref="E17:R20"/>
+    <mergeCell ref="E26:R29"/>
+    <mergeCell ref="E35:R39"/>
+    <mergeCell ref="E47:R51"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/가공도_도면_1.xlsx
+++ b/가공도_도면_1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\duddl\Desktop\Project\a2z\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56E747DC-6A03-4992-A4EB-6169B53A3E49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A74EE7FB-CA7A-44BC-A3B3-A687B929A022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1920" yWindow="720" windowWidth="20256" windowHeight="11520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="227">
   <si>
     <t>A</t>
   </si>
@@ -614,21 +614,6 @@
   </si>
   <si>
     <t>{Input_194}</t>
-  </si>
-  <si>
-    <t>{Input_195}</t>
-  </si>
-  <si>
-    <t>{Input_196}</t>
-  </si>
-  <si>
-    <t>{Input_197}</t>
-  </si>
-  <si>
-    <t>{Input_198}</t>
-  </si>
-  <si>
-    <t>{Input_199}</t>
   </si>
   <si>
     <t>D</t>
@@ -984,21 +969,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1008,7 +978,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1023,22 +1008,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1052,6 +1025,18 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1435,137 +1420,137 @@
       <c r="BS1" s="6"/>
     </row>
     <row r="2" spans="1:71" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="C2" s="18">
+      <c r="C2" s="13">
         <v>1</v>
       </c>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
-      <c r="H2" s="19"/>
-      <c r="I2" s="19"/>
-      <c r="J2" s="19"/>
-      <c r="K2" s="19"/>
-      <c r="L2" s="20"/>
-      <c r="M2" s="18">
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="14"/>
+      <c r="J2" s="14"/>
+      <c r="K2" s="14"/>
+      <c r="L2" s="15"/>
+      <c r="M2" s="13">
         <v>2</v>
       </c>
-      <c r="N2" s="19"/>
-      <c r="O2" s="19"/>
-      <c r="P2" s="19"/>
-      <c r="Q2" s="19"/>
-      <c r="R2" s="19"/>
-      <c r="S2" s="19"/>
-      <c r="T2" s="19"/>
-      <c r="U2" s="19"/>
-      <c r="V2" s="19"/>
-      <c r="W2" s="19"/>
-      <c r="X2" s="20"/>
-      <c r="Y2" s="18">
+      <c r="N2" s="14"/>
+      <c r="O2" s="14"/>
+      <c r="P2" s="14"/>
+      <c r="Q2" s="14"/>
+      <c r="R2" s="14"/>
+      <c r="S2" s="14"/>
+      <c r="T2" s="14"/>
+      <c r="U2" s="14"/>
+      <c r="V2" s="14"/>
+      <c r="W2" s="14"/>
+      <c r="X2" s="15"/>
+      <c r="Y2" s="13">
         <v>3</v>
       </c>
-      <c r="Z2" s="19"/>
-      <c r="AA2" s="19"/>
-      <c r="AB2" s="19"/>
-      <c r="AC2" s="19"/>
-      <c r="AD2" s="19"/>
-      <c r="AE2" s="19"/>
-      <c r="AF2" s="19"/>
-      <c r="AG2" s="19"/>
-      <c r="AH2" s="19"/>
-      <c r="AI2" s="20"/>
-      <c r="AJ2" s="18">
+      <c r="Z2" s="14"/>
+      <c r="AA2" s="14"/>
+      <c r="AB2" s="14"/>
+      <c r="AC2" s="14"/>
+      <c r="AD2" s="14"/>
+      <c r="AE2" s="14"/>
+      <c r="AF2" s="14"/>
+      <c r="AG2" s="14"/>
+      <c r="AH2" s="14"/>
+      <c r="AI2" s="15"/>
+      <c r="AJ2" s="13">
         <v>4</v>
       </c>
-      <c r="AK2" s="19"/>
-      <c r="AL2" s="19"/>
-      <c r="AM2" s="19"/>
-      <c r="AN2" s="19"/>
-      <c r="AO2" s="19"/>
-      <c r="AP2" s="19"/>
-      <c r="AQ2" s="19"/>
-      <c r="AR2" s="19"/>
-      <c r="AS2" s="19"/>
-      <c r="AT2" s="20"/>
-      <c r="AU2" s="18">
+      <c r="AK2" s="14"/>
+      <c r="AL2" s="14"/>
+      <c r="AM2" s="14"/>
+      <c r="AN2" s="14"/>
+      <c r="AO2" s="14"/>
+      <c r="AP2" s="14"/>
+      <c r="AQ2" s="14"/>
+      <c r="AR2" s="14"/>
+      <c r="AS2" s="14"/>
+      <c r="AT2" s="15"/>
+      <c r="AU2" s="13">
         <v>5</v>
       </c>
-      <c r="AV2" s="19"/>
-      <c r="AW2" s="19"/>
-      <c r="AX2" s="19"/>
-      <c r="AY2" s="19"/>
-      <c r="AZ2" s="19"/>
-      <c r="BA2" s="19"/>
-      <c r="BB2" s="19"/>
-      <c r="BC2" s="19"/>
-      <c r="BD2" s="19"/>
-      <c r="BE2" s="19"/>
-      <c r="BF2" s="20"/>
-      <c r="BG2" s="18">
+      <c r="AV2" s="14"/>
+      <c r="AW2" s="14"/>
+      <c r="AX2" s="14"/>
+      <c r="AY2" s="14"/>
+      <c r="AZ2" s="14"/>
+      <c r="BA2" s="14"/>
+      <c r="BB2" s="14"/>
+      <c r="BC2" s="14"/>
+      <c r="BD2" s="14"/>
+      <c r="BE2" s="14"/>
+      <c r="BF2" s="15"/>
+      <c r="BG2" s="13">
         <v>6</v>
       </c>
-      <c r="BH2" s="19"/>
-      <c r="BI2" s="19"/>
-      <c r="BJ2" s="19"/>
-      <c r="BK2" s="19"/>
-      <c r="BL2" s="19"/>
-      <c r="BM2" s="19"/>
-      <c r="BN2" s="19"/>
-      <c r="BO2" s="19"/>
-      <c r="BP2" s="19"/>
-      <c r="BQ2" s="20"/>
+      <c r="BH2" s="14"/>
+      <c r="BI2" s="14"/>
+      <c r="BJ2" s="14"/>
+      <c r="BK2" s="14"/>
+      <c r="BL2" s="14"/>
+      <c r="BM2" s="14"/>
+      <c r="BN2" s="14"/>
+      <c r="BO2" s="14"/>
+      <c r="BP2" s="14"/>
+      <c r="BQ2" s="15"/>
       <c r="BR2" s="2"/>
     </row>
     <row r="3" spans="1:71" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B3" s="26" t="s">
+      <c r="B3" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="32" t="s">
-        <v>230</v>
-      </c>
-      <c r="D3" s="33"/>
+      <c r="C3" s="28" t="s">
+        <v>225</v>
+      </c>
+      <c r="D3" s="29"/>
       <c r="Y3" s="3"/>
-      <c r="AT3" s="14" t="s">
-        <v>229</v>
-      </c>
-      <c r="AU3" s="14"/>
-      <c r="AV3" s="15"/>
-      <c r="AW3" s="21" t="s">
+      <c r="AT3" s="20" t="s">
+        <v>224</v>
+      </c>
+      <c r="AU3" s="20"/>
+      <c r="AV3" s="21"/>
+      <c r="AW3" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="AX3" s="14"/>
-      <c r="AY3" s="14"/>
-      <c r="AZ3" s="14"/>
-      <c r="BA3" s="14"/>
-      <c r="BB3" s="14"/>
-      <c r="BC3" s="14"/>
-      <c r="BD3" s="14"/>
-      <c r="BE3" s="14"/>
-      <c r="BF3" s="14"/>
-      <c r="BG3" s="14"/>
-      <c r="BH3" s="14"/>
-      <c r="BI3" s="14"/>
-      <c r="BJ3" s="14"/>
-      <c r="BK3" s="14"/>
-      <c r="BL3" s="14"/>
-      <c r="BM3" s="14"/>
-      <c r="BN3" s="14"/>
-      <c r="BO3" s="14"/>
-      <c r="BP3" s="14"/>
-      <c r="BQ3" s="15"/>
-      <c r="BR3" s="26" t="s">
+      <c r="AX3" s="20"/>
+      <c r="AY3" s="20"/>
+      <c r="AZ3" s="20"/>
+      <c r="BA3" s="20"/>
+      <c r="BB3" s="20"/>
+      <c r="BC3" s="20"/>
+      <c r="BD3" s="20"/>
+      <c r="BE3" s="20"/>
+      <c r="BF3" s="20"/>
+      <c r="BG3" s="20"/>
+      <c r="BH3" s="20"/>
+      <c r="BI3" s="20"/>
+      <c r="BJ3" s="20"/>
+      <c r="BK3" s="20"/>
+      <c r="BL3" s="20"/>
+      <c r="BM3" s="20"/>
+      <c r="BN3" s="20"/>
+      <c r="BO3" s="20"/>
+      <c r="BP3" s="20"/>
+      <c r="BQ3" s="21"/>
+      <c r="BR3" s="16" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:71" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="31"/>
-      <c r="C4" s="34"/>
-      <c r="D4" s="35"/>
+      <c r="B4" s="17"/>
+      <c r="C4" s="30"/>
+      <c r="D4" s="31"/>
       <c r="E4" s="3"/>
       <c r="AA4" s="3"/>
-      <c r="AT4" s="16"/>
-      <c r="AU4" s="16"/>
-      <c r="AV4" s="17"/>
+      <c r="AT4" s="26"/>
+      <c r="AU4" s="26"/>
+      <c r="AV4" s="27"/>
       <c r="AW4" s="22"/>
       <c r="AX4" s="23"/>
       <c r="AY4" s="23"/>
@@ -1587,59 +1572,59 @@
       <c r="BO4" s="23"/>
       <c r="BP4" s="23"/>
       <c r="BQ4" s="24"/>
-      <c r="BR4" s="31"/>
+      <c r="BR4" s="17"/>
     </row>
     <row r="5" spans="1:71" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B5" s="31"/>
-      <c r="C5" s="34"/>
-      <c r="D5" s="35"/>
-      <c r="AT5" s="16"/>
-      <c r="AU5" s="16"/>
-      <c r="AV5" s="17"/>
-      <c r="AW5" s="21" t="s">
-        <v>224</v>
-      </c>
-      <c r="AX5" s="15"/>
-      <c r="AY5" s="21" t="s">
+      <c r="B5" s="17"/>
+      <c r="C5" s="30"/>
+      <c r="D5" s="31"/>
+      <c r="AT5" s="26"/>
+      <c r="AU5" s="26"/>
+      <c r="AV5" s="27"/>
+      <c r="AW5" s="19" t="s">
+        <v>219</v>
+      </c>
+      <c r="AX5" s="21"/>
+      <c r="AY5" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="AZ5" s="14"/>
-      <c r="BA5" s="14"/>
-      <c r="BB5" s="15"/>
-      <c r="BC5" s="21" t="s">
+      <c r="AZ5" s="20"/>
+      <c r="BA5" s="20"/>
+      <c r="BB5" s="21"/>
+      <c r="BC5" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="BD5" s="14"/>
-      <c r="BE5" s="15"/>
-      <c r="BF5" s="21" t="s">
+      <c r="BD5" s="20"/>
+      <c r="BE5" s="21"/>
+      <c r="BF5" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="BG5" s="14"/>
-      <c r="BH5" s="14"/>
-      <c r="BI5" s="14"/>
-      <c r="BJ5" s="14"/>
-      <c r="BK5" s="15"/>
-      <c r="BL5" s="26" t="s">
+      <c r="BG5" s="20"/>
+      <c r="BH5" s="20"/>
+      <c r="BI5" s="20"/>
+      <c r="BJ5" s="20"/>
+      <c r="BK5" s="21"/>
+      <c r="BL5" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="BM5" s="21" t="s">
+      <c r="BM5" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="BN5" s="14"/>
-      <c r="BO5" s="15"/>
-      <c r="BP5" s="26" t="s">
+      <c r="BN5" s="20"/>
+      <c r="BO5" s="21"/>
+      <c r="BP5" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="BQ5" s="26" t="s">
+      <c r="BQ5" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="BR5" s="31"/>
+      <c r="BR5" s="17"/>
     </row>
     <row r="6" spans="1:71" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B6" s="31"/>
-      <c r="AT6" s="16"/>
-      <c r="AU6" s="16"/>
-      <c r="AV6" s="17"/>
+      <c r="B6" s="17"/>
+      <c r="AT6" s="26"/>
+      <c r="AU6" s="26"/>
+      <c r="AV6" s="27"/>
       <c r="AW6" s="22"/>
       <c r="AX6" s="24"/>
       <c r="AY6" s="22"/>
@@ -1655,1208 +1640,1202 @@
       <c r="BI6" s="23"/>
       <c r="BJ6" s="23"/>
       <c r="BK6" s="24"/>
-      <c r="BL6" s="27"/>
+      <c r="BL6" s="18"/>
       <c r="BM6" s="22"/>
       <c r="BN6" s="23"/>
       <c r="BO6" s="24"/>
-      <c r="BP6" s="27"/>
-      <c r="BQ6" s="27"/>
-      <c r="BR6" s="31"/>
+      <c r="BP6" s="18"/>
+      <c r="BQ6" s="18"/>
+      <c r="BR6" s="17"/>
     </row>
     <row r="7" spans="1:71" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B7" s="31"/>
-      <c r="E7" s="13" t="s">
-        <v>198</v>
-      </c>
-      <c r="F7" s="13"/>
-      <c r="G7" s="13"/>
-      <c r="H7" s="13"/>
-      <c r="I7" s="13"/>
-      <c r="J7" s="13"/>
-      <c r="K7" s="13"/>
-      <c r="L7" s="13"/>
-      <c r="M7" s="13"/>
-      <c r="N7" s="13"/>
-      <c r="O7" s="13"/>
-      <c r="P7" s="13"/>
-      <c r="Q7" s="13"/>
-      <c r="R7" s="13"/>
-      <c r="T7" s="13" t="s">
+      <c r="B7" s="17"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="3"/>
+      <c r="N7" s="3"/>
+      <c r="O7" s="3"/>
+      <c r="P7" s="3"/>
+      <c r="Q7" s="3"/>
+      <c r="R7" s="3"/>
+      <c r="T7" s="35" t="s">
         <v>2</v>
       </c>
-      <c r="U7" s="13"/>
-      <c r="V7" s="13"/>
-      <c r="W7" s="13"/>
-      <c r="X7" s="13"/>
-      <c r="Y7" s="13"/>
-      <c r="Z7" s="13"/>
-      <c r="AA7" s="13"/>
-      <c r="AB7" s="13"/>
-      <c r="AC7" s="13"/>
-      <c r="AD7" s="13"/>
-      <c r="AE7" s="13"/>
-      <c r="AF7" s="13"/>
-      <c r="AG7" s="13"/>
-      <c r="AT7" s="16"/>
-      <c r="AU7" s="16"/>
-      <c r="AV7" s="17"/>
-      <c r="AW7" s="18" t="s">
+      <c r="U7" s="35"/>
+      <c r="V7" s="35"/>
+      <c r="W7" s="35"/>
+      <c r="X7" s="35"/>
+      <c r="Y7" s="35"/>
+      <c r="Z7" s="35"/>
+      <c r="AA7" s="35"/>
+      <c r="AB7" s="35"/>
+      <c r="AC7" s="35"/>
+      <c r="AD7" s="35"/>
+      <c r="AE7" s="35"/>
+      <c r="AF7" s="35"/>
+      <c r="AG7" s="35"/>
+      <c r="AT7" s="26"/>
+      <c r="AU7" s="26"/>
+      <c r="AV7" s="27"/>
+      <c r="AW7" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="AX7" s="20"/>
-      <c r="AY7" s="18" t="s">
+      <c r="AX7" s="15"/>
+      <c r="AY7" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="AZ7" s="19"/>
-      <c r="BA7" s="19"/>
-      <c r="BB7" s="20"/>
-      <c r="BC7" s="18" t="s">
+      <c r="AZ7" s="14"/>
+      <c r="BA7" s="14"/>
+      <c r="BB7" s="15"/>
+      <c r="BC7" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="BD7" s="19"/>
-      <c r="BE7" s="20"/>
-      <c r="BF7" s="18" t="s">
+      <c r="BD7" s="14"/>
+      <c r="BE7" s="15"/>
+      <c r="BF7" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="BG7" s="19"/>
-      <c r="BH7" s="19"/>
-      <c r="BI7" s="19"/>
-      <c r="BJ7" s="19"/>
-      <c r="BK7" s="20"/>
+      <c r="BG7" s="14"/>
+      <c r="BH7" s="14"/>
+      <c r="BI7" s="14"/>
+      <c r="BJ7" s="14"/>
+      <c r="BK7" s="15"/>
       <c r="BL7" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="BM7" s="18" t="s">
+      <c r="BM7" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="BN7" s="19"/>
-      <c r="BO7" s="20"/>
+      <c r="BN7" s="14"/>
+      <c r="BO7" s="15"/>
       <c r="BP7" s="4" t="s">
         <v>17</v>
       </c>
       <c r="BQ7" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="BR7" s="31"/>
+      <c r="BR7" s="17"/>
     </row>
     <row r="8" spans="1:71" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B8" s="31"/>
-      <c r="E8" s="13"/>
-      <c r="F8" s="13"/>
-      <c r="G8" s="13"/>
-      <c r="H8" s="13"/>
-      <c r="I8" s="13"/>
-      <c r="J8" s="13"/>
-      <c r="K8" s="13"/>
-      <c r="L8" s="13"/>
-      <c r="M8" s="13"/>
-      <c r="N8" s="13"/>
-      <c r="O8" s="13"/>
-      <c r="P8" s="13"/>
-      <c r="Q8" s="13"/>
-      <c r="R8" s="13"/>
-      <c r="T8" s="13"/>
-      <c r="U8" s="13"/>
-      <c r="V8" s="13"/>
-      <c r="W8" s="13"/>
-      <c r="X8" s="13"/>
-      <c r="Y8" s="13"/>
-      <c r="Z8" s="13"/>
-      <c r="AA8" s="13"/>
-      <c r="AB8" s="13"/>
-      <c r="AC8" s="13"/>
-      <c r="AD8" s="13"/>
-      <c r="AE8" s="13"/>
-      <c r="AF8" s="13"/>
-      <c r="AG8" s="13"/>
-      <c r="AT8" s="16"/>
-      <c r="AU8" s="16"/>
-      <c r="AV8" s="17"/>
-      <c r="AW8" s="18" t="s">
+      <c r="B8" s="17"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="3"/>
+      <c r="J8" s="3"/>
+      <c r="K8" s="3"/>
+      <c r="L8" s="3"/>
+      <c r="M8" s="3"/>
+      <c r="N8" s="3"/>
+      <c r="O8" s="3"/>
+      <c r="P8" s="3"/>
+      <c r="Q8" s="3"/>
+      <c r="R8" s="3"/>
+      <c r="T8" s="35"/>
+      <c r="U8" s="35"/>
+      <c r="V8" s="35"/>
+      <c r="W8" s="35"/>
+      <c r="X8" s="35"/>
+      <c r="Y8" s="35"/>
+      <c r="Z8" s="35"/>
+      <c r="AA8" s="35"/>
+      <c r="AB8" s="35"/>
+      <c r="AC8" s="35"/>
+      <c r="AD8" s="35"/>
+      <c r="AE8" s="35"/>
+      <c r="AF8" s="35"/>
+      <c r="AG8" s="35"/>
+      <c r="AT8" s="26"/>
+      <c r="AU8" s="26"/>
+      <c r="AV8" s="27"/>
+      <c r="AW8" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="AX8" s="20"/>
-      <c r="AY8" s="18" t="s">
+      <c r="AX8" s="15"/>
+      <c r="AY8" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="AZ8" s="19"/>
-      <c r="BA8" s="19"/>
-      <c r="BB8" s="20"/>
-      <c r="BC8" s="18" t="s">
+      <c r="AZ8" s="14"/>
+      <c r="BA8" s="14"/>
+      <c r="BB8" s="15"/>
+      <c r="BC8" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="BD8" s="19"/>
-      <c r="BE8" s="20"/>
-      <c r="BF8" s="18" t="s">
+      <c r="BD8" s="14"/>
+      <c r="BE8" s="15"/>
+      <c r="BF8" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="BG8" s="19"/>
-      <c r="BH8" s="19"/>
-      <c r="BI8" s="19"/>
-      <c r="BJ8" s="19"/>
-      <c r="BK8" s="20"/>
+      <c r="BG8" s="14"/>
+      <c r="BH8" s="14"/>
+      <c r="BI8" s="14"/>
+      <c r="BJ8" s="14"/>
+      <c r="BK8" s="15"/>
       <c r="BL8" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="BM8" s="18" t="s">
+      <c r="BM8" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="BN8" s="19"/>
-      <c r="BO8" s="20"/>
+      <c r="BN8" s="14"/>
+      <c r="BO8" s="15"/>
       <c r="BP8" s="8" t="s">
         <v>25</v>
       </c>
       <c r="BQ8" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="BR8" s="31"/>
+      <c r="BR8" s="17"/>
     </row>
     <row r="9" spans="1:71" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B9" s="31"/>
-      <c r="E9" s="13"/>
-      <c r="F9" s="13"/>
-      <c r="G9" s="13"/>
-      <c r="H9" s="13"/>
-      <c r="I9" s="13"/>
-      <c r="J9" s="13"/>
-      <c r="K9" s="13"/>
-      <c r="L9" s="13"/>
-      <c r="M9" s="13"/>
-      <c r="N9" s="13"/>
-      <c r="O9" s="13"/>
-      <c r="P9" s="13"/>
-      <c r="Q9" s="13"/>
-      <c r="R9" s="13"/>
-      <c r="T9" s="13"/>
-      <c r="U9" s="13"/>
-      <c r="V9" s="13"/>
-      <c r="W9" s="13"/>
-      <c r="X9" s="13"/>
-      <c r="Y9" s="13"/>
-      <c r="Z9" s="13"/>
-      <c r="AA9" s="13"/>
-      <c r="AB9" s="13"/>
-      <c r="AC9" s="13"/>
-      <c r="AD9" s="13"/>
-      <c r="AE9" s="13"/>
-      <c r="AF9" s="13"/>
-      <c r="AG9" s="13"/>
+      <c r="B9" s="17"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
+      <c r="J9" s="3"/>
+      <c r="K9" s="3"/>
+      <c r="L9" s="3"/>
+      <c r="M9" s="3"/>
+      <c r="N9" s="3"/>
+      <c r="O9" s="3"/>
+      <c r="P9" s="3"/>
+      <c r="Q9" s="3"/>
+      <c r="R9" s="3"/>
+      <c r="T9" s="35"/>
+      <c r="U9" s="35"/>
+      <c r="V9" s="35"/>
+      <c r="W9" s="35"/>
+      <c r="X9" s="35"/>
+      <c r="Y9" s="35"/>
+      <c r="Z9" s="35"/>
+      <c r="AA9" s="35"/>
+      <c r="AB9" s="35"/>
+      <c r="AC9" s="35"/>
+      <c r="AD9" s="35"/>
+      <c r="AE9" s="35"/>
+      <c r="AF9" s="35"/>
+      <c r="AG9" s="35"/>
       <c r="AT9" s="11"/>
       <c r="AU9" s="11"/>
       <c r="AV9" s="12"/>
-      <c r="AW9" s="18" t="s">
+      <c r="AW9" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="AX9" s="20"/>
-      <c r="AY9" s="18" t="s">
+      <c r="AX9" s="15"/>
+      <c r="AY9" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="AZ9" s="19"/>
-      <c r="BA9" s="19"/>
-      <c r="BB9" s="20"/>
-      <c r="BC9" s="18" t="s">
+      <c r="AZ9" s="14"/>
+      <c r="BA9" s="14"/>
+      <c r="BB9" s="15"/>
+      <c r="BC9" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="BD9" s="19"/>
-      <c r="BE9" s="20"/>
-      <c r="BF9" s="18" t="s">
+      <c r="BD9" s="14"/>
+      <c r="BE9" s="15"/>
+      <c r="BF9" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="BG9" s="19"/>
-      <c r="BH9" s="19"/>
-      <c r="BI9" s="19"/>
-      <c r="BJ9" s="19"/>
-      <c r="BK9" s="20"/>
+      <c r="BG9" s="14"/>
+      <c r="BH9" s="14"/>
+      <c r="BI9" s="14"/>
+      <c r="BJ9" s="14"/>
+      <c r="BK9" s="15"/>
       <c r="BL9" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="BM9" s="18" t="s">
+      <c r="BM9" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="BN9" s="19"/>
-      <c r="BO9" s="20"/>
+      <c r="BN9" s="14"/>
+      <c r="BO9" s="15"/>
       <c r="BP9" s="8" t="s">
         <v>33</v>
       </c>
       <c r="BQ9" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="BR9" s="31"/>
+      <c r="BR9" s="17"/>
     </row>
     <row r="10" spans="1:71" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B10" s="31"/>
-      <c r="E10" s="13"/>
-      <c r="F10" s="13"/>
-      <c r="G10" s="13"/>
-      <c r="H10" s="13"/>
-      <c r="I10" s="13"/>
-      <c r="J10" s="13"/>
-      <c r="K10" s="13"/>
-      <c r="L10" s="13"/>
-      <c r="M10" s="13"/>
-      <c r="N10" s="13"/>
-      <c r="O10" s="13"/>
-      <c r="P10" s="13"/>
-      <c r="Q10" s="13"/>
-      <c r="R10" s="13"/>
-      <c r="T10" s="13"/>
-      <c r="U10" s="13"/>
-      <c r="V10" s="13"/>
-      <c r="W10" s="13"/>
-      <c r="X10" s="13"/>
-      <c r="Y10" s="13"/>
-      <c r="Z10" s="13"/>
-      <c r="AA10" s="13"/>
-      <c r="AB10" s="13"/>
-      <c r="AC10" s="13"/>
-      <c r="AD10" s="13"/>
-      <c r="AE10" s="13"/>
-      <c r="AF10" s="13"/>
-      <c r="AG10" s="13"/>
+      <c r="B10" s="17"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="3"/>
+      <c r="J10" s="3"/>
+      <c r="K10" s="3"/>
+      <c r="L10" s="3"/>
+      <c r="M10" s="3"/>
+      <c r="N10" s="3"/>
+      <c r="O10" s="3"/>
+      <c r="P10" s="3"/>
+      <c r="Q10" s="3"/>
+      <c r="R10" s="3"/>
+      <c r="T10" s="35"/>
+      <c r="U10" s="35"/>
+      <c r="V10" s="35"/>
+      <c r="W10" s="35"/>
+      <c r="X10" s="35"/>
+      <c r="Y10" s="35"/>
+      <c r="Z10" s="35"/>
+      <c r="AA10" s="35"/>
+      <c r="AB10" s="35"/>
+      <c r="AC10" s="35"/>
+      <c r="AD10" s="35"/>
+      <c r="AE10" s="35"/>
+      <c r="AF10" s="35"/>
+      <c r="AG10" s="35"/>
       <c r="AT10" s="11"/>
       <c r="AU10" s="11"/>
       <c r="AV10" s="12"/>
-      <c r="AW10" s="18" t="s">
+      <c r="AW10" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="AX10" s="20"/>
-      <c r="AY10" s="18" t="s">
+      <c r="AX10" s="15"/>
+      <c r="AY10" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="AZ10" s="19"/>
-      <c r="BA10" s="19"/>
-      <c r="BB10" s="20"/>
-      <c r="BC10" s="18" t="s">
+      <c r="AZ10" s="14"/>
+      <c r="BA10" s="14"/>
+      <c r="BB10" s="15"/>
+      <c r="BC10" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="BD10" s="19"/>
-      <c r="BE10" s="20"/>
-      <c r="BF10" s="18" t="s">
+      <c r="BD10" s="14"/>
+      <c r="BE10" s="15"/>
+      <c r="BF10" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="BG10" s="19"/>
-      <c r="BH10" s="19"/>
-      <c r="BI10" s="19"/>
-      <c r="BJ10" s="19"/>
-      <c r="BK10" s="20"/>
+      <c r="BG10" s="14"/>
+      <c r="BH10" s="14"/>
+      <c r="BI10" s="14"/>
+      <c r="BJ10" s="14"/>
+      <c r="BK10" s="15"/>
       <c r="BL10" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="BM10" s="18" t="s">
+      <c r="BM10" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="BN10" s="19"/>
-      <c r="BO10" s="20"/>
+      <c r="BN10" s="14"/>
+      <c r="BO10" s="15"/>
       <c r="BP10" s="8" t="s">
         <v>41</v>
       </c>
       <c r="BQ10" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="BR10" s="31"/>
+      <c r="BR10" s="17"/>
     </row>
     <row r="11" spans="1:71" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B11" s="31"/>
-      <c r="E11" s="13"/>
-      <c r="F11" s="13"/>
-      <c r="G11" s="13"/>
-      <c r="H11" s="13"/>
-      <c r="I11" s="13"/>
-      <c r="J11" s="13"/>
-      <c r="K11" s="13"/>
-      <c r="L11" s="13"/>
-      <c r="M11" s="13"/>
-      <c r="N11" s="13"/>
-      <c r="O11" s="13"/>
-      <c r="P11" s="13"/>
-      <c r="Q11" s="13"/>
-      <c r="R11" s="13"/>
-      <c r="T11" s="13"/>
-      <c r="U11" s="13"/>
-      <c r="V11" s="13"/>
-      <c r="W11" s="13"/>
-      <c r="X11" s="13"/>
-      <c r="Y11" s="13"/>
-      <c r="Z11" s="13"/>
-      <c r="AA11" s="13"/>
-      <c r="AB11" s="13"/>
-      <c r="AC11" s="13"/>
-      <c r="AD11" s="13"/>
-      <c r="AE11" s="13"/>
-      <c r="AF11" s="13"/>
-      <c r="AG11" s="13"/>
+      <c r="B11" s="17"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
+      <c r="H11" s="3"/>
+      <c r="I11" s="3"/>
+      <c r="J11" s="3"/>
+      <c r="K11" s="3"/>
+      <c r="L11" s="3"/>
+      <c r="M11" s="3"/>
+      <c r="N11" s="3"/>
+      <c r="O11" s="3"/>
+      <c r="P11" s="3"/>
+      <c r="Q11" s="3"/>
+      <c r="R11" s="3"/>
+      <c r="T11" s="35"/>
+      <c r="U11" s="35"/>
+      <c r="V11" s="35"/>
+      <c r="W11" s="35"/>
+      <c r="X11" s="35"/>
+      <c r="Y11" s="35"/>
+      <c r="Z11" s="35"/>
+      <c r="AA11" s="35"/>
+      <c r="AB11" s="35"/>
+      <c r="AC11" s="35"/>
+      <c r="AD11" s="35"/>
+      <c r="AE11" s="35"/>
+      <c r="AF11" s="35"/>
+      <c r="AG11" s="35"/>
       <c r="AT11" s="11"/>
       <c r="AU11" s="11"/>
       <c r="AV11" s="12"/>
-      <c r="AW11" s="18" t="s">
+      <c r="AW11" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="AX11" s="20"/>
-      <c r="AY11" s="18" t="s">
+      <c r="AX11" s="15"/>
+      <c r="AY11" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="AZ11" s="19"/>
-      <c r="BA11" s="19"/>
-      <c r="BB11" s="20"/>
-      <c r="BC11" s="18" t="s">
+      <c r="AZ11" s="14"/>
+      <c r="BA11" s="14"/>
+      <c r="BB11" s="15"/>
+      <c r="BC11" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="BD11" s="19"/>
-      <c r="BE11" s="20"/>
-      <c r="BF11" s="18" t="s">
+      <c r="BD11" s="14"/>
+      <c r="BE11" s="15"/>
+      <c r="BF11" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="BG11" s="19"/>
-      <c r="BH11" s="19"/>
-      <c r="BI11" s="19"/>
-      <c r="BJ11" s="19"/>
-      <c r="BK11" s="20"/>
+      <c r="BG11" s="14"/>
+      <c r="BH11" s="14"/>
+      <c r="BI11" s="14"/>
+      <c r="BJ11" s="14"/>
+      <c r="BK11" s="15"/>
       <c r="BL11" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="BM11" s="18" t="s">
+      <c r="BM11" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="BN11" s="19"/>
-      <c r="BO11" s="20"/>
+      <c r="BN11" s="14"/>
+      <c r="BO11" s="15"/>
       <c r="BP11" s="10" t="s">
         <v>49</v>
       </c>
       <c r="BQ11" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="BR11" s="31"/>
+      <c r="BR11" s="17"/>
     </row>
     <row r="12" spans="1:71" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B12" s="31"/>
-      <c r="AW12" s="18" t="s">
+      <c r="B12" s="17"/>
+      <c r="AW12" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="AX12" s="20"/>
-      <c r="AY12" s="18" t="s">
+      <c r="AX12" s="15"/>
+      <c r="AY12" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="AZ12" s="19"/>
-      <c r="BA12" s="19"/>
-      <c r="BB12" s="20"/>
-      <c r="BC12" s="18" t="s">
+      <c r="AZ12" s="14"/>
+      <c r="BA12" s="14"/>
+      <c r="BB12" s="15"/>
+      <c r="BC12" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="BD12" s="19"/>
-      <c r="BE12" s="20"/>
-      <c r="BF12" s="18" t="s">
+      <c r="BD12" s="14"/>
+      <c r="BE12" s="15"/>
+      <c r="BF12" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="BG12" s="19"/>
-      <c r="BH12" s="19"/>
-      <c r="BI12" s="19"/>
-      <c r="BJ12" s="19"/>
-      <c r="BK12" s="20"/>
+      <c r="BG12" s="14"/>
+      <c r="BH12" s="14"/>
+      <c r="BI12" s="14"/>
+      <c r="BJ12" s="14"/>
+      <c r="BK12" s="15"/>
       <c r="BL12" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="BM12" s="18" t="s">
+      <c r="BM12" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="BN12" s="19"/>
-      <c r="BO12" s="20"/>
+      <c r="BN12" s="14"/>
+      <c r="BO12" s="15"/>
       <c r="BP12" s="8" t="s">
         <v>57</v>
       </c>
       <c r="BQ12" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="BR12" s="31"/>
+      <c r="BR12" s="17"/>
     </row>
     <row r="13" spans="1:71" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B13" s="31"/>
-      <c r="AW13" s="18" t="s">
+      <c r="B13" s="17"/>
+      <c r="AW13" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="AX13" s="20"/>
-      <c r="AY13" s="18" t="s">
+      <c r="AX13" s="15"/>
+      <c r="AY13" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="AZ13" s="19"/>
-      <c r="BA13" s="19"/>
-      <c r="BB13" s="20"/>
-      <c r="BC13" s="18" t="s">
+      <c r="AZ13" s="14"/>
+      <c r="BA13" s="14"/>
+      <c r="BB13" s="15"/>
+      <c r="BC13" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="BD13" s="19"/>
-      <c r="BE13" s="20"/>
-      <c r="BF13" s="18" t="s">
+      <c r="BD13" s="14"/>
+      <c r="BE13" s="15"/>
+      <c r="BF13" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="BG13" s="19"/>
-      <c r="BH13" s="19"/>
-      <c r="BI13" s="19"/>
-      <c r="BJ13" s="19"/>
-      <c r="BK13" s="20"/>
+      <c r="BG13" s="14"/>
+      <c r="BH13" s="14"/>
+      <c r="BI13" s="14"/>
+      <c r="BJ13" s="14"/>
+      <c r="BK13" s="15"/>
       <c r="BL13" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="BM13" s="18" t="s">
+      <c r="BM13" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="BN13" s="19"/>
-      <c r="BO13" s="20"/>
+      <c r="BN13" s="14"/>
+      <c r="BO13" s="15"/>
       <c r="BP13" s="8" t="s">
         <v>65</v>
       </c>
       <c r="BQ13" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="BR13" s="31"/>
+      <c r="BR13" s="17"/>
     </row>
     <row r="14" spans="1:71" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B14" s="31"/>
-      <c r="AW14" s="18" t="s">
+      <c r="B14" s="17"/>
+      <c r="AW14" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="AX14" s="20"/>
-      <c r="AY14" s="18" t="s">
+      <c r="AX14" s="15"/>
+      <c r="AY14" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="AZ14" s="19"/>
-      <c r="BA14" s="19"/>
-      <c r="BB14" s="20"/>
-      <c r="BC14" s="18" t="s">
+      <c r="AZ14" s="14"/>
+      <c r="BA14" s="14"/>
+      <c r="BB14" s="15"/>
+      <c r="BC14" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="BD14" s="19"/>
-      <c r="BE14" s="20"/>
-      <c r="BF14" s="18" t="s">
+      <c r="BD14" s="14"/>
+      <c r="BE14" s="15"/>
+      <c r="BF14" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="BG14" s="19"/>
-      <c r="BH14" s="19"/>
-      <c r="BI14" s="19"/>
-      <c r="BJ14" s="19"/>
-      <c r="BK14" s="20"/>
+      <c r="BG14" s="14"/>
+      <c r="BH14" s="14"/>
+      <c r="BI14" s="14"/>
+      <c r="BJ14" s="14"/>
+      <c r="BK14" s="15"/>
       <c r="BL14" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="BM14" s="18" t="s">
+      <c r="BM14" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="BN14" s="19"/>
-      <c r="BO14" s="20"/>
+      <c r="BN14" s="14"/>
+      <c r="BO14" s="15"/>
       <c r="BP14" s="8" t="s">
         <v>73</v>
       </c>
       <c r="BQ14" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="BR14" s="31"/>
+      <c r="BR14" s="17"/>
     </row>
     <row r="15" spans="1:71" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B15" s="31"/>
-      <c r="AW15" s="18" t="s">
+      <c r="B15" s="17"/>
+      <c r="AW15" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="AX15" s="20"/>
-      <c r="AY15" s="18" t="s">
+      <c r="AX15" s="15"/>
+      <c r="AY15" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="AZ15" s="19"/>
-      <c r="BA15" s="19"/>
-      <c r="BB15" s="20"/>
-      <c r="BC15" s="18" t="s">
+      <c r="AZ15" s="14"/>
+      <c r="BA15" s="14"/>
+      <c r="BB15" s="15"/>
+      <c r="BC15" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="BD15" s="19"/>
-      <c r="BE15" s="20"/>
-      <c r="BF15" s="18" t="s">
+      <c r="BD15" s="14"/>
+      <c r="BE15" s="15"/>
+      <c r="BF15" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="BG15" s="19"/>
-      <c r="BH15" s="19"/>
-      <c r="BI15" s="19"/>
-      <c r="BJ15" s="19"/>
-      <c r="BK15" s="20"/>
+      <c r="BG15" s="14"/>
+      <c r="BH15" s="14"/>
+      <c r="BI15" s="14"/>
+      <c r="BJ15" s="14"/>
+      <c r="BK15" s="15"/>
       <c r="BL15" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="BM15" s="18" t="s">
+      <c r="BM15" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="BN15" s="19"/>
-      <c r="BO15" s="20"/>
+      <c r="BN15" s="14"/>
+      <c r="BO15" s="15"/>
       <c r="BP15" s="8" t="s">
         <v>81</v>
       </c>
       <c r="BQ15" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="BR15" s="31"/>
+      <c r="BR15" s="17"/>
     </row>
     <row r="16" spans="1:71" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B16" s="27"/>
-      <c r="AW16" s="18" t="s">
+      <c r="B16" s="18"/>
+      <c r="AW16" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="AX16" s="20"/>
-      <c r="AY16" s="18" t="s">
+      <c r="AX16" s="15"/>
+      <c r="AY16" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="AZ16" s="19"/>
-      <c r="BA16" s="19"/>
-      <c r="BB16" s="20"/>
-      <c r="BC16" s="18" t="s">
+      <c r="AZ16" s="14"/>
+      <c r="BA16" s="14"/>
+      <c r="BB16" s="15"/>
+      <c r="BC16" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="BD16" s="19"/>
-      <c r="BE16" s="20"/>
-      <c r="BF16" s="18" t="s">
+      <c r="BD16" s="14"/>
+      <c r="BE16" s="15"/>
+      <c r="BF16" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="BG16" s="19"/>
-      <c r="BH16" s="19"/>
-      <c r="BI16" s="19"/>
-      <c r="BJ16" s="19"/>
-      <c r="BK16" s="20"/>
+      <c r="BG16" s="14"/>
+      <c r="BH16" s="14"/>
+      <c r="BI16" s="14"/>
+      <c r="BJ16" s="14"/>
+      <c r="BK16" s="15"/>
       <c r="BL16" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="BM16" s="18" t="s">
+      <c r="BM16" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="BN16" s="19"/>
-      <c r="BO16" s="20"/>
+      <c r="BN16" s="14"/>
+      <c r="BO16" s="15"/>
       <c r="BP16" s="8" t="s">
         <v>90</v>
       </c>
       <c r="BQ16" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="BR16" s="27"/>
+      <c r="BR16" s="18"/>
     </row>
     <row r="17" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B17" s="26" t="s">
+      <c r="B17" s="16" t="s">
         <v>83</v>
       </c>
-      <c r="E17" s="13" t="s">
-        <v>199</v>
-      </c>
-      <c r="F17" s="13"/>
-      <c r="G17" s="13"/>
-      <c r="H17" s="13"/>
-      <c r="I17" s="13"/>
-      <c r="J17" s="13"/>
-      <c r="K17" s="13"/>
-      <c r="L17" s="13"/>
-      <c r="M17" s="13"/>
-      <c r="N17" s="13"/>
-      <c r="O17" s="13"/>
-      <c r="P17" s="13"/>
-      <c r="Q17" s="13"/>
-      <c r="R17" s="13"/>
-      <c r="T17" s="13" t="s">
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="3"/>
+      <c r="H17" s="3"/>
+      <c r="I17" s="3"/>
+      <c r="J17" s="3"/>
+      <c r="K17" s="3"/>
+      <c r="L17" s="3"/>
+      <c r="M17" s="3"/>
+      <c r="N17" s="3"/>
+      <c r="O17" s="3"/>
+      <c r="P17" s="3"/>
+      <c r="Q17" s="3"/>
+      <c r="R17" s="3"/>
+      <c r="T17" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="U17" s="13"/>
-      <c r="V17" s="13"/>
-      <c r="W17" s="13"/>
-      <c r="X17" s="13"/>
-      <c r="Y17" s="13"/>
-      <c r="Z17" s="13"/>
-      <c r="AA17" s="13"/>
-      <c r="AB17" s="13"/>
-      <c r="AC17" s="13"/>
-      <c r="AD17" s="13"/>
-      <c r="AE17" s="13"/>
-      <c r="AF17" s="13"/>
-      <c r="AG17" s="13"/>
-      <c r="AW17" s="18" t="s">
+      <c r="U17" s="35"/>
+      <c r="V17" s="35"/>
+      <c r="W17" s="35"/>
+      <c r="X17" s="35"/>
+      <c r="Y17" s="35"/>
+      <c r="Z17" s="35"/>
+      <c r="AA17" s="35"/>
+      <c r="AB17" s="35"/>
+      <c r="AC17" s="35"/>
+      <c r="AD17" s="35"/>
+      <c r="AE17" s="35"/>
+      <c r="AF17" s="35"/>
+      <c r="AG17" s="35"/>
+      <c r="AW17" s="13" t="s">
         <v>92</v>
       </c>
-      <c r="AX17" s="20"/>
-      <c r="AY17" s="18" t="s">
+      <c r="AX17" s="15"/>
+      <c r="AY17" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AZ17" s="19"/>
-      <c r="BA17" s="19"/>
-      <c r="BB17" s="20"/>
-      <c r="BC17" s="18" t="s">
+      <c r="AZ17" s="14"/>
+      <c r="BA17" s="14"/>
+      <c r="BB17" s="15"/>
+      <c r="BC17" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="BD17" s="19"/>
-      <c r="BE17" s="20"/>
-      <c r="BF17" s="18" t="s">
+      <c r="BD17" s="14"/>
+      <c r="BE17" s="15"/>
+      <c r="BF17" s="13" t="s">
         <v>95</v>
       </c>
-      <c r="BG17" s="19"/>
-      <c r="BH17" s="19"/>
-      <c r="BI17" s="19"/>
-      <c r="BJ17" s="19"/>
-      <c r="BK17" s="20"/>
+      <c r="BG17" s="14"/>
+      <c r="BH17" s="14"/>
+      <c r="BI17" s="14"/>
+      <c r="BJ17" s="14"/>
+      <c r="BK17" s="15"/>
       <c r="BL17" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="BM17" s="18" t="s">
+      <c r="BM17" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="BN17" s="19"/>
-      <c r="BO17" s="20"/>
+      <c r="BN17" s="14"/>
+      <c r="BO17" s="15"/>
       <c r="BP17" s="8" t="s">
         <v>98</v>
       </c>
       <c r="BQ17" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="BR17" s="26" t="s">
+      <c r="BR17" s="16" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="18" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B18" s="31"/>
-      <c r="E18" s="13"/>
-      <c r="F18" s="13"/>
-      <c r="G18" s="13"/>
-      <c r="H18" s="13"/>
-      <c r="I18" s="13"/>
-      <c r="J18" s="13"/>
-      <c r="K18" s="13"/>
-      <c r="L18" s="13"/>
-      <c r="M18" s="13"/>
-      <c r="N18" s="13"/>
-      <c r="O18" s="13"/>
-      <c r="P18" s="13"/>
-      <c r="Q18" s="13"/>
-      <c r="R18" s="13"/>
-      <c r="T18" s="13"/>
-      <c r="U18" s="13"/>
-      <c r="V18" s="13"/>
-      <c r="W18" s="13"/>
-      <c r="X18" s="13"/>
-      <c r="Y18" s="13"/>
-      <c r="Z18" s="13"/>
-      <c r="AA18" s="13"/>
-      <c r="AB18" s="13"/>
-      <c r="AC18" s="13"/>
-      <c r="AD18" s="13"/>
-      <c r="AE18" s="13"/>
-      <c r="AF18" s="13"/>
-      <c r="AG18" s="13"/>
-      <c r="AW18" s="18" t="s">
+      <c r="B18" s="17"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3"/>
+      <c r="H18" s="3"/>
+      <c r="I18" s="3"/>
+      <c r="J18" s="3"/>
+      <c r="K18" s="3"/>
+      <c r="L18" s="3"/>
+      <c r="M18" s="3"/>
+      <c r="N18" s="3"/>
+      <c r="O18" s="3"/>
+      <c r="P18" s="3"/>
+      <c r="Q18" s="3"/>
+      <c r="R18" s="3"/>
+      <c r="T18" s="35"/>
+      <c r="U18" s="35"/>
+      <c r="V18" s="35"/>
+      <c r="W18" s="35"/>
+      <c r="X18" s="35"/>
+      <c r="Y18" s="35"/>
+      <c r="Z18" s="35"/>
+      <c r="AA18" s="35"/>
+      <c r="AB18" s="35"/>
+      <c r="AC18" s="35"/>
+      <c r="AD18" s="35"/>
+      <c r="AE18" s="35"/>
+      <c r="AF18" s="35"/>
+      <c r="AG18" s="35"/>
+      <c r="AW18" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="AX18" s="20"/>
-      <c r="AY18" s="18" t="s">
+      <c r="AX18" s="15"/>
+      <c r="AY18" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="AZ18" s="19"/>
-      <c r="BA18" s="19"/>
-      <c r="BB18" s="20"/>
-      <c r="BC18" s="18" t="s">
+      <c r="AZ18" s="14"/>
+      <c r="BA18" s="14"/>
+      <c r="BB18" s="15"/>
+      <c r="BC18" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="BD18" s="19"/>
-      <c r="BE18" s="20"/>
-      <c r="BF18" s="18" t="s">
+      <c r="BD18" s="14"/>
+      <c r="BE18" s="15"/>
+      <c r="BF18" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="BG18" s="19"/>
-      <c r="BH18" s="19"/>
-      <c r="BI18" s="19"/>
-      <c r="BJ18" s="19"/>
-      <c r="BK18" s="20"/>
+      <c r="BG18" s="14"/>
+      <c r="BH18" s="14"/>
+      <c r="BI18" s="14"/>
+      <c r="BJ18" s="14"/>
+      <c r="BK18" s="15"/>
       <c r="BL18" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="BM18" s="18" t="s">
+      <c r="BM18" s="13" t="s">
         <v>105</v>
       </c>
-      <c r="BN18" s="19"/>
-      <c r="BO18" s="20"/>
+      <c r="BN18" s="14"/>
+      <c r="BO18" s="15"/>
       <c r="BP18" s="8" t="s">
         <v>106</v>
       </c>
       <c r="BQ18" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="BR18" s="31"/>
+      <c r="BR18" s="17"/>
     </row>
     <row r="19" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B19" s="31"/>
-      <c r="E19" s="13"/>
-      <c r="F19" s="13"/>
-      <c r="G19" s="13"/>
-      <c r="H19" s="13"/>
-      <c r="I19" s="13"/>
-      <c r="J19" s="13"/>
-      <c r="K19" s="13"/>
-      <c r="L19" s="13"/>
-      <c r="M19" s="13"/>
-      <c r="N19" s="13"/>
-      <c r="O19" s="13"/>
-      <c r="P19" s="13"/>
-      <c r="Q19" s="13"/>
-      <c r="R19" s="13"/>
-      <c r="T19" s="13"/>
-      <c r="U19" s="13"/>
-      <c r="V19" s="13"/>
-      <c r="W19" s="13"/>
-      <c r="X19" s="13"/>
-      <c r="Y19" s="13"/>
-      <c r="Z19" s="13"/>
-      <c r="AA19" s="13"/>
-      <c r="AB19" s="13"/>
-      <c r="AC19" s="13"/>
-      <c r="AD19" s="13"/>
-      <c r="AE19" s="13"/>
-      <c r="AF19" s="13"/>
-      <c r="AG19" s="13"/>
-      <c r="AW19" s="18" t="s">
+      <c r="B19" s="17"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3"/>
+      <c r="H19" s="3"/>
+      <c r="I19" s="3"/>
+      <c r="J19" s="3"/>
+      <c r="K19" s="3"/>
+      <c r="L19" s="3"/>
+      <c r="M19" s="3"/>
+      <c r="N19" s="3"/>
+      <c r="O19" s="3"/>
+      <c r="P19" s="3"/>
+      <c r="Q19" s="3"/>
+      <c r="R19" s="3"/>
+      <c r="T19" s="35"/>
+      <c r="U19" s="35"/>
+      <c r="V19" s="35"/>
+      <c r="W19" s="35"/>
+      <c r="X19" s="35"/>
+      <c r="Y19" s="35"/>
+      <c r="Z19" s="35"/>
+      <c r="AA19" s="35"/>
+      <c r="AB19" s="35"/>
+      <c r="AC19" s="35"/>
+      <c r="AD19" s="35"/>
+      <c r="AE19" s="35"/>
+      <c r="AF19" s="35"/>
+      <c r="AG19" s="35"/>
+      <c r="AW19" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="AX19" s="20"/>
-      <c r="AY19" s="18" t="s">
+      <c r="AX19" s="15"/>
+      <c r="AY19" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="AZ19" s="19"/>
-      <c r="BA19" s="19"/>
-      <c r="BB19" s="20"/>
-      <c r="BC19" s="18" t="s">
+      <c r="AZ19" s="14"/>
+      <c r="BA19" s="14"/>
+      <c r="BB19" s="15"/>
+      <c r="BC19" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="BD19" s="19"/>
-      <c r="BE19" s="20"/>
-      <c r="BF19" s="18" t="s">
+      <c r="BD19" s="14"/>
+      <c r="BE19" s="15"/>
+      <c r="BF19" s="13" t="s">
         <v>111</v>
       </c>
-      <c r="BG19" s="19"/>
-      <c r="BH19" s="19"/>
-      <c r="BI19" s="19"/>
-      <c r="BJ19" s="19"/>
-      <c r="BK19" s="20"/>
+      <c r="BG19" s="14"/>
+      <c r="BH19" s="14"/>
+      <c r="BI19" s="14"/>
+      <c r="BJ19" s="14"/>
+      <c r="BK19" s="15"/>
       <c r="BL19" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="BM19" s="18" t="s">
+      <c r="BM19" s="13" t="s">
         <v>113</v>
       </c>
-      <c r="BN19" s="19"/>
-      <c r="BO19" s="20"/>
+      <c r="BN19" s="14"/>
+      <c r="BO19" s="15"/>
       <c r="BP19" s="8" t="s">
         <v>114</v>
       </c>
       <c r="BQ19" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="BR19" s="31"/>
+      <c r="BR19" s="17"/>
     </row>
     <row r="20" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B20" s="31"/>
-      <c r="E20" s="13"/>
-      <c r="F20" s="13"/>
-      <c r="G20" s="13"/>
-      <c r="H20" s="13"/>
-      <c r="I20" s="13"/>
-      <c r="J20" s="13"/>
-      <c r="K20" s="13"/>
-      <c r="L20" s="13"/>
-      <c r="M20" s="13"/>
-      <c r="N20" s="13"/>
-      <c r="O20" s="13"/>
-      <c r="P20" s="13"/>
-      <c r="Q20" s="13"/>
-      <c r="R20" s="13"/>
-      <c r="T20" s="13"/>
-      <c r="U20" s="13"/>
-      <c r="V20" s="13"/>
-      <c r="W20" s="13"/>
-      <c r="X20" s="13"/>
-      <c r="Y20" s="13"/>
-      <c r="Z20" s="13"/>
-      <c r="AA20" s="13"/>
-      <c r="AB20" s="13"/>
-      <c r="AC20" s="13"/>
-      <c r="AD20" s="13"/>
-      <c r="AE20" s="13"/>
-      <c r="AF20" s="13"/>
-      <c r="AG20" s="13"/>
-      <c r="AW20" s="18" t="s">
+      <c r="B20" s="17"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="3"/>
+      <c r="H20" s="3"/>
+      <c r="I20" s="3"/>
+      <c r="J20" s="3"/>
+      <c r="K20" s="3"/>
+      <c r="L20" s="3"/>
+      <c r="M20" s="3"/>
+      <c r="N20" s="3"/>
+      <c r="O20" s="3"/>
+      <c r="P20" s="3"/>
+      <c r="Q20" s="3"/>
+      <c r="R20" s="3"/>
+      <c r="T20" s="35"/>
+      <c r="U20" s="35"/>
+      <c r="V20" s="35"/>
+      <c r="W20" s="35"/>
+      <c r="X20" s="35"/>
+      <c r="Y20" s="35"/>
+      <c r="Z20" s="35"/>
+      <c r="AA20" s="35"/>
+      <c r="AB20" s="35"/>
+      <c r="AC20" s="35"/>
+      <c r="AD20" s="35"/>
+      <c r="AE20" s="35"/>
+      <c r="AF20" s="35"/>
+      <c r="AG20" s="35"/>
+      <c r="AW20" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="AX20" s="20"/>
-      <c r="AY20" s="18" t="s">
+      <c r="AX20" s="15"/>
+      <c r="AY20" s="13" t="s">
         <v>117</v>
       </c>
-      <c r="AZ20" s="19"/>
-      <c r="BA20" s="19"/>
-      <c r="BB20" s="20"/>
-      <c r="BC20" s="18" t="s">
+      <c r="AZ20" s="14"/>
+      <c r="BA20" s="14"/>
+      <c r="BB20" s="15"/>
+      <c r="BC20" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="BD20" s="19"/>
-      <c r="BE20" s="20"/>
-      <c r="BF20" s="18" t="s">
+      <c r="BD20" s="14"/>
+      <c r="BE20" s="15"/>
+      <c r="BF20" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="BG20" s="19"/>
-      <c r="BH20" s="19"/>
-      <c r="BI20" s="19"/>
-      <c r="BJ20" s="19"/>
-      <c r="BK20" s="20"/>
+      <c r="BG20" s="14"/>
+      <c r="BH20" s="14"/>
+      <c r="BI20" s="14"/>
+      <c r="BJ20" s="14"/>
+      <c r="BK20" s="15"/>
       <c r="BL20" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="BM20" s="18" t="s">
+      <c r="BM20" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="BN20" s="19"/>
-      <c r="BO20" s="20"/>
+      <c r="BN20" s="14"/>
+      <c r="BO20" s="15"/>
       <c r="BP20" s="8" t="s">
         <v>122</v>
       </c>
       <c r="BQ20" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="BR20" s="31"/>
+      <c r="BR20" s="17"/>
     </row>
     <row r="21" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B21" s="31"/>
-      <c r="AW21" s="18" t="s">
+      <c r="B21" s="17"/>
+      <c r="AW21" s="13" t="s">
         <v>124</v>
       </c>
-      <c r="AX21" s="20"/>
-      <c r="AY21" s="18" t="s">
+      <c r="AX21" s="15"/>
+      <c r="AY21" s="13" t="s">
         <v>125</v>
       </c>
-      <c r="AZ21" s="19"/>
-      <c r="BA21" s="19"/>
-      <c r="BB21" s="20"/>
-      <c r="BC21" s="18" t="s">
+      <c r="AZ21" s="14"/>
+      <c r="BA21" s="14"/>
+      <c r="BB21" s="15"/>
+      <c r="BC21" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="BD21" s="19"/>
-      <c r="BE21" s="20"/>
-      <c r="BF21" s="18" t="s">
+      <c r="BD21" s="14"/>
+      <c r="BE21" s="15"/>
+      <c r="BF21" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="BG21" s="19"/>
-      <c r="BH21" s="19"/>
-      <c r="BI21" s="19"/>
-      <c r="BJ21" s="19"/>
-      <c r="BK21" s="20"/>
+      <c r="BG21" s="14"/>
+      <c r="BH21" s="14"/>
+      <c r="BI21" s="14"/>
+      <c r="BJ21" s="14"/>
+      <c r="BK21" s="15"/>
       <c r="BL21" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="BM21" s="18" t="s">
+      <c r="BM21" s="13" t="s">
         <v>129</v>
       </c>
-      <c r="BN21" s="19"/>
-      <c r="BO21" s="20"/>
+      <c r="BN21" s="14"/>
+      <c r="BO21" s="15"/>
       <c r="BP21" s="8" t="s">
         <v>130</v>
       </c>
       <c r="BQ21" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="BR21" s="31"/>
+      <c r="BR21" s="17"/>
     </row>
     <row r="22" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B22" s="31"/>
-      <c r="AW22" s="18" t="s">
+      <c r="B22" s="17"/>
+      <c r="AW22" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="AX22" s="20"/>
-      <c r="AY22" s="18" t="s">
+      <c r="AX22" s="15"/>
+      <c r="AY22" s="13" t="s">
         <v>133</v>
       </c>
-      <c r="AZ22" s="19"/>
-      <c r="BA22" s="19"/>
-      <c r="BB22" s="20"/>
-      <c r="BC22" s="18" t="s">
+      <c r="AZ22" s="14"/>
+      <c r="BA22" s="14"/>
+      <c r="BB22" s="15"/>
+      <c r="BC22" s="13" t="s">
         <v>134</v>
       </c>
-      <c r="BD22" s="19"/>
-      <c r="BE22" s="20"/>
-      <c r="BF22" s="18" t="s">
+      <c r="BD22" s="14"/>
+      <c r="BE22" s="15"/>
+      <c r="BF22" s="13" t="s">
         <v>135</v>
       </c>
-      <c r="BG22" s="19"/>
-      <c r="BH22" s="19"/>
-      <c r="BI22" s="19"/>
-      <c r="BJ22" s="19"/>
-      <c r="BK22" s="20"/>
+      <c r="BG22" s="14"/>
+      <c r="BH22" s="14"/>
+      <c r="BI22" s="14"/>
+      <c r="BJ22" s="14"/>
+      <c r="BK22" s="15"/>
       <c r="BL22" s="8" t="s">
         <v>136</v>
       </c>
-      <c r="BM22" s="18" t="s">
+      <c r="BM22" s="13" t="s">
         <v>137</v>
       </c>
-      <c r="BN22" s="19"/>
-      <c r="BO22" s="20"/>
+      <c r="BN22" s="14"/>
+      <c r="BO22" s="15"/>
       <c r="BP22" s="8" t="s">
         <v>138</v>
       </c>
       <c r="BQ22" s="8" t="s">
         <v>139</v>
       </c>
-      <c r="BR22" s="31"/>
+      <c r="BR22" s="17"/>
     </row>
     <row r="23" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B23" s="31"/>
-      <c r="AW23" s="18" t="s">
+      <c r="B23" s="17"/>
+      <c r="AW23" s="13" t="s">
         <v>140</v>
       </c>
-      <c r="AX23" s="20"/>
-      <c r="AY23" s="18" t="s">
+      <c r="AX23" s="15"/>
+      <c r="AY23" s="13" t="s">
         <v>141</v>
       </c>
-      <c r="AZ23" s="19"/>
-      <c r="BA23" s="19"/>
-      <c r="BB23" s="20"/>
-      <c r="BC23" s="18" t="s">
+      <c r="AZ23" s="14"/>
+      <c r="BA23" s="14"/>
+      <c r="BB23" s="15"/>
+      <c r="BC23" s="13" t="s">
         <v>142</v>
       </c>
-      <c r="BD23" s="19"/>
-      <c r="BE23" s="20"/>
-      <c r="BF23" s="18" t="s">
+      <c r="BD23" s="14"/>
+      <c r="BE23" s="15"/>
+      <c r="BF23" s="13" t="s">
         <v>143</v>
       </c>
-      <c r="BG23" s="19"/>
-      <c r="BH23" s="19"/>
-      <c r="BI23" s="19"/>
-      <c r="BJ23" s="19"/>
-      <c r="BK23" s="20"/>
+      <c r="BG23" s="14"/>
+      <c r="BH23" s="14"/>
+      <c r="BI23" s="14"/>
+      <c r="BJ23" s="14"/>
+      <c r="BK23" s="15"/>
       <c r="BL23" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="BM23" s="18" t="s">
+      <c r="BM23" s="13" t="s">
         <v>145</v>
       </c>
-      <c r="BN23" s="19"/>
-      <c r="BO23" s="20"/>
+      <c r="BN23" s="14"/>
+      <c r="BO23" s="15"/>
       <c r="BP23" s="8" t="s">
         <v>146</v>
       </c>
       <c r="BQ23" s="8" t="s">
         <v>147</v>
       </c>
-      <c r="BR23" s="31"/>
+      <c r="BR23" s="17"/>
     </row>
     <row r="24" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B24" s="31"/>
-      <c r="AW24" s="18" t="s">
+      <c r="B24" s="17"/>
+      <c r="AW24" s="13" t="s">
         <v>148</v>
       </c>
-      <c r="AX24" s="20"/>
-      <c r="AY24" s="18" t="s">
+      <c r="AX24" s="15"/>
+      <c r="AY24" s="13" t="s">
         <v>149</v>
       </c>
-      <c r="AZ24" s="19"/>
-      <c r="BA24" s="19"/>
-      <c r="BB24" s="20"/>
-      <c r="BC24" s="18" t="s">
+      <c r="AZ24" s="14"/>
+      <c r="BA24" s="14"/>
+      <c r="BB24" s="15"/>
+      <c r="BC24" s="13" t="s">
         <v>150</v>
       </c>
-      <c r="BD24" s="19"/>
-      <c r="BE24" s="20"/>
-      <c r="BF24" s="18" t="s">
+      <c r="BD24" s="14"/>
+      <c r="BE24" s="15"/>
+      <c r="BF24" s="13" t="s">
         <v>151</v>
       </c>
-      <c r="BG24" s="19"/>
-      <c r="BH24" s="19"/>
-      <c r="BI24" s="19"/>
-      <c r="BJ24" s="19"/>
-      <c r="BK24" s="20"/>
+      <c r="BG24" s="14"/>
+      <c r="BH24" s="14"/>
+      <c r="BI24" s="14"/>
+      <c r="BJ24" s="14"/>
+      <c r="BK24" s="15"/>
       <c r="BL24" s="8" t="s">
         <v>152</v>
       </c>
-      <c r="BM24" s="18" t="s">
+      <c r="BM24" s="13" t="s">
         <v>153</v>
       </c>
-      <c r="BN24" s="19"/>
-      <c r="BO24" s="20"/>
+      <c r="BN24" s="14"/>
+      <c r="BO24" s="15"/>
       <c r="BP24" s="8" t="s">
         <v>154</v>
       </c>
       <c r="BQ24" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="BR24" s="31"/>
+      <c r="BR24" s="17"/>
     </row>
     <row r="25" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B25" s="31"/>
-      <c r="AW25" s="18" t="s">
-        <v>225</v>
-      </c>
-      <c r="AX25" s="20"/>
-      <c r="AY25" s="28" t="s">
+      <c r="B25" s="17"/>
+      <c r="AW25" s="13" t="s">
+        <v>220</v>
+      </c>
+      <c r="AX25" s="15"/>
+      <c r="AY25" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="AZ25" s="29"/>
-      <c r="BA25" s="29"/>
-      <c r="BB25" s="30"/>
-      <c r="BC25" s="19" t="s">
-        <v>226</v>
-      </c>
-      <c r="BD25" s="19"/>
-      <c r="BE25" s="20"/>
-      <c r="BF25" s="18" t="s">
-        <v>227</v>
-      </c>
-      <c r="BG25" s="19"/>
-      <c r="BH25" s="19"/>
-      <c r="BI25" s="19"/>
-      <c r="BJ25" s="19"/>
-      <c r="BK25" s="20"/>
+      <c r="AZ25" s="33"/>
+      <c r="BA25" s="33"/>
+      <c r="BB25" s="34"/>
+      <c r="BC25" s="14" t="s">
+        <v>221</v>
+      </c>
+      <c r="BD25" s="14"/>
+      <c r="BE25" s="15"/>
+      <c r="BF25" s="13" t="s">
+        <v>222</v>
+      </c>
+      <c r="BG25" s="14"/>
+      <c r="BH25" s="14"/>
+      <c r="BI25" s="14"/>
+      <c r="BJ25" s="14"/>
+      <c r="BK25" s="15"/>
       <c r="BL25" s="8" t="s">
         <v>157</v>
       </c>
-      <c r="BM25" s="18" t="s">
-        <v>228</v>
-      </c>
-      <c r="BN25" s="19"/>
-      <c r="BO25" s="20"/>
+      <c r="BM25" s="13" t="s">
+        <v>223</v>
+      </c>
+      <c r="BN25" s="14"/>
+      <c r="BO25" s="15"/>
       <c r="BP25" s="8" t="s">
         <v>158</v>
       </c>
       <c r="BQ25" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="BR25" s="31"/>
+      <c r="BR25" s="17"/>
     </row>
     <row r="26" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B26" s="31"/>
-      <c r="E26" s="13" t="s">
-        <v>200</v>
-      </c>
-      <c r="F26" s="13"/>
-      <c r="G26" s="13"/>
-      <c r="H26" s="13"/>
-      <c r="I26" s="13"/>
-      <c r="J26" s="13"/>
-      <c r="K26" s="13"/>
-      <c r="L26" s="13"/>
-      <c r="M26" s="13"/>
-      <c r="N26" s="13"/>
-      <c r="O26" s="13"/>
-      <c r="P26" s="13"/>
-      <c r="Q26" s="13"/>
-      <c r="R26" s="13"/>
-      <c r="T26" s="13" t="s">
+      <c r="B26" s="17"/>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="3"/>
+      <c r="H26" s="3"/>
+      <c r="I26" s="3"/>
+      <c r="J26" s="3"/>
+      <c r="K26" s="3"/>
+      <c r="L26" s="3"/>
+      <c r="M26" s="3"/>
+      <c r="N26" s="3"/>
+      <c r="O26" s="3"/>
+      <c r="P26" s="3"/>
+      <c r="Q26" s="3"/>
+      <c r="R26" s="3"/>
+      <c r="T26" s="35" t="s">
         <v>171</v>
       </c>
-      <c r="U26" s="13"/>
-      <c r="V26" s="13"/>
-      <c r="W26" s="13"/>
-      <c r="X26" s="13"/>
-      <c r="Y26" s="13"/>
-      <c r="Z26" s="13"/>
-      <c r="AA26" s="13"/>
-      <c r="AB26" s="13"/>
-      <c r="AC26" s="13"/>
-      <c r="AD26" s="13"/>
-      <c r="AE26" s="13"/>
-      <c r="AF26" s="13"/>
-      <c r="AG26" s="13"/>
-      <c r="AW26" s="18" t="s">
+      <c r="U26" s="35"/>
+      <c r="V26" s="35"/>
+      <c r="W26" s="35"/>
+      <c r="X26" s="35"/>
+      <c r="Y26" s="35"/>
+      <c r="Z26" s="35"/>
+      <c r="AA26" s="35"/>
+      <c r="AB26" s="35"/>
+      <c r="AC26" s="35"/>
+      <c r="AD26" s="35"/>
+      <c r="AE26" s="35"/>
+      <c r="AF26" s="35"/>
+      <c r="AG26" s="35"/>
+      <c r="AW26" s="13" t="s">
         <v>160</v>
       </c>
-      <c r="AX26" s="20"/>
-      <c r="AY26" s="18" t="s">
+      <c r="AX26" s="15"/>
+      <c r="AY26" s="13" t="s">
         <v>161</v>
       </c>
-      <c r="AZ26" s="19"/>
-      <c r="BA26" s="19"/>
-      <c r="BB26" s="20"/>
-      <c r="BC26" s="18" t="s">
+      <c r="AZ26" s="14"/>
+      <c r="BA26" s="14"/>
+      <c r="BB26" s="15"/>
+      <c r="BC26" s="13" t="s">
         <v>162</v>
       </c>
-      <c r="BD26" s="19"/>
-      <c r="BE26" s="20"/>
-      <c r="BF26" s="18" t="s">
+      <c r="BD26" s="14"/>
+      <c r="BE26" s="15"/>
+      <c r="BF26" s="13" t="s">
         <v>163</v>
       </c>
-      <c r="BG26" s="19"/>
-      <c r="BH26" s="19"/>
-      <c r="BI26" s="19"/>
-      <c r="BJ26" s="19"/>
-      <c r="BK26" s="20"/>
+      <c r="BG26" s="14"/>
+      <c r="BH26" s="14"/>
+      <c r="BI26" s="14"/>
+      <c r="BJ26" s="14"/>
+      <c r="BK26" s="15"/>
       <c r="BL26" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="BM26" s="18" t="s">
+      <c r="BM26" s="13" t="s">
         <v>165</v>
       </c>
-      <c r="BN26" s="19"/>
-      <c r="BO26" s="20"/>
+      <c r="BN26" s="14"/>
+      <c r="BO26" s="15"/>
       <c r="BP26" s="7" t="s">
         <v>166</v>
       </c>
       <c r="BQ26" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="BR26" s="31"/>
+      <c r="BR26" s="17"/>
     </row>
     <row r="27" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B27" s="31"/>
-      <c r="E27" s="13"/>
-      <c r="F27" s="13"/>
-      <c r="G27" s="13"/>
-      <c r="H27" s="13"/>
-      <c r="I27" s="13"/>
-      <c r="J27" s="13"/>
-      <c r="K27" s="13"/>
-      <c r="L27" s="13"/>
-      <c r="M27" s="13"/>
-      <c r="N27" s="13"/>
-      <c r="O27" s="13"/>
-      <c r="P27" s="13"/>
-      <c r="Q27" s="13"/>
-      <c r="R27" s="13"/>
-      <c r="T27" s="13"/>
-      <c r="U27" s="13"/>
-      <c r="V27" s="13"/>
-      <c r="W27" s="13"/>
-      <c r="X27" s="13"/>
-      <c r="Y27" s="13"/>
-      <c r="Z27" s="13"/>
-      <c r="AA27" s="13"/>
-      <c r="AB27" s="13"/>
-      <c r="AC27" s="13"/>
-      <c r="AD27" s="13"/>
-      <c r="AE27" s="13"/>
-      <c r="AF27" s="13"/>
-      <c r="AG27" s="13"/>
+      <c r="B27" s="17"/>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="3"/>
+      <c r="H27" s="3"/>
+      <c r="I27" s="3"/>
+      <c r="J27" s="3"/>
+      <c r="K27" s="3"/>
+      <c r="L27" s="3"/>
+      <c r="M27" s="3"/>
+      <c r="N27" s="3"/>
+      <c r="O27" s="3"/>
+      <c r="P27" s="3"/>
+      <c r="Q27" s="3"/>
+      <c r="R27" s="3"/>
+      <c r="T27" s="35"/>
+      <c r="U27" s="35"/>
+      <c r="V27" s="35"/>
+      <c r="W27" s="35"/>
+      <c r="X27" s="35"/>
+      <c r="Y27" s="35"/>
+      <c r="Z27" s="35"/>
+      <c r="AA27" s="35"/>
+      <c r="AB27" s="35"/>
+      <c r="AC27" s="35"/>
+      <c r="AD27" s="35"/>
+      <c r="AE27" s="35"/>
+      <c r="AF27" s="35"/>
+      <c r="AG27" s="35"/>
       <c r="BQ27" s="6"/>
-      <c r="BR27" s="31"/>
+      <c r="BR27" s="17"/>
     </row>
     <row r="28" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B28" s="31"/>
-      <c r="E28" s="13"/>
-      <c r="F28" s="13"/>
-      <c r="G28" s="13"/>
-      <c r="H28" s="13"/>
-      <c r="I28" s="13"/>
-      <c r="J28" s="13"/>
-      <c r="K28" s="13"/>
-      <c r="L28" s="13"/>
-      <c r="M28" s="13"/>
-      <c r="N28" s="13"/>
-      <c r="O28" s="13"/>
-      <c r="P28" s="13"/>
-      <c r="Q28" s="13"/>
-      <c r="R28" s="13"/>
-      <c r="T28" s="13"/>
-      <c r="U28" s="13"/>
-      <c r="V28" s="13"/>
-      <c r="W28" s="13"/>
-      <c r="X28" s="13"/>
-      <c r="Y28" s="13"/>
-      <c r="Z28" s="13"/>
-      <c r="AA28" s="13"/>
-      <c r="AB28" s="13"/>
-      <c r="AC28" s="13"/>
-      <c r="AD28" s="13"/>
-      <c r="AE28" s="13"/>
-      <c r="AF28" s="13"/>
-      <c r="AG28" s="13"/>
+      <c r="B28" s="17"/>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="3"/>
+      <c r="H28" s="3"/>
+      <c r="I28" s="3"/>
+      <c r="J28" s="3"/>
+      <c r="K28" s="3"/>
+      <c r="L28" s="3"/>
+      <c r="M28" s="3"/>
+      <c r="N28" s="3"/>
+      <c r="O28" s="3"/>
+      <c r="P28" s="3"/>
+      <c r="Q28" s="3"/>
+      <c r="R28" s="3"/>
+      <c r="T28" s="35"/>
+      <c r="U28" s="35"/>
+      <c r="V28" s="35"/>
+      <c r="W28" s="35"/>
+      <c r="X28" s="35"/>
+      <c r="Y28" s="35"/>
+      <c r="Z28" s="35"/>
+      <c r="AA28" s="35"/>
+      <c r="AB28" s="35"/>
+      <c r="AC28" s="35"/>
+      <c r="AD28" s="35"/>
+      <c r="AE28" s="35"/>
+      <c r="AF28" s="35"/>
+      <c r="AG28" s="35"/>
       <c r="AI28" s="3"/>
       <c r="AV28" s="6"/>
       <c r="AW28" s="9"/>
@@ -2880,242 +2859,240 @@
       <c r="BO28" s="9"/>
       <c r="BP28" s="9"/>
       <c r="BQ28" s="9"/>
-      <c r="BR28" s="31"/>
+      <c r="BR28" s="17"/>
     </row>
     <row r="29" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B29" s="27"/>
-      <c r="E29" s="13"/>
-      <c r="F29" s="13"/>
-      <c r="G29" s="13"/>
-      <c r="H29" s="13"/>
-      <c r="I29" s="13"/>
-      <c r="J29" s="13"/>
-      <c r="K29" s="13"/>
-      <c r="L29" s="13"/>
-      <c r="M29" s="13"/>
-      <c r="N29" s="13"/>
-      <c r="O29" s="13"/>
-      <c r="P29" s="13"/>
-      <c r="Q29" s="13"/>
-      <c r="R29" s="13"/>
-      <c r="T29" s="13"/>
-      <c r="U29" s="13"/>
-      <c r="V29" s="13"/>
-      <c r="W29" s="13"/>
-      <c r="X29" s="13"/>
-      <c r="Y29" s="13"/>
-      <c r="Z29" s="13"/>
-      <c r="AA29" s="13"/>
-      <c r="AB29" s="13"/>
-      <c r="AC29" s="13"/>
-      <c r="AD29" s="13"/>
-      <c r="AE29" s="13"/>
-      <c r="AF29" s="13"/>
-      <c r="AG29" s="13"/>
+      <c r="B29" s="18"/>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="3"/>
+      <c r="H29" s="3"/>
+      <c r="I29" s="3"/>
+      <c r="J29" s="3"/>
+      <c r="K29" s="3"/>
+      <c r="L29" s="3"/>
+      <c r="M29" s="3"/>
+      <c r="N29" s="3"/>
+      <c r="O29" s="3"/>
+      <c r="P29" s="3"/>
+      <c r="Q29" s="3"/>
+      <c r="R29" s="3"/>
+      <c r="T29" s="35"/>
+      <c r="U29" s="35"/>
+      <c r="V29" s="35"/>
+      <c r="W29" s="35"/>
+      <c r="X29" s="35"/>
+      <c r="Y29" s="35"/>
+      <c r="Z29" s="35"/>
+      <c r="AA29" s="35"/>
+      <c r="AB29" s="35"/>
+      <c r="AC29" s="35"/>
+      <c r="AD29" s="35"/>
+      <c r="AE29" s="35"/>
+      <c r="AF29" s="35"/>
+      <c r="AG29" s="35"/>
       <c r="BQ29" s="6"/>
-      <c r="BR29" s="27"/>
+      <c r="BR29" s="18"/>
     </row>
     <row r="30" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B30" s="26" t="s">
+      <c r="B30" s="16" t="s">
         <v>168</v>
       </c>
-      <c r="BR30" s="26" t="s">
+      <c r="BR30" s="16" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="31" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B31" s="31"/>
-      <c r="AW31" s="21" t="s">
+      <c r="B31" s="17"/>
+      <c r="AW31" s="19" t="s">
         <v>169</v>
       </c>
-      <c r="AX31" s="14"/>
-      <c r="AY31" s="14" t="s">
+      <c r="AX31" s="20"/>
+      <c r="AY31" s="20" t="s">
         <v>170</v>
       </c>
-      <c r="AZ31" s="14"/>
-      <c r="BA31" s="14"/>
-      <c r="BB31" s="14"/>
-      <c r="BC31" s="14"/>
-      <c r="BD31" s="14"/>
-      <c r="BE31" s="14"/>
-      <c r="BF31" s="14"/>
-      <c r="BG31" s="14"/>
-      <c r="BH31" s="14"/>
-      <c r="BI31" s="14"/>
-      <c r="BJ31" s="14"/>
-      <c r="BK31" s="14"/>
-      <c r="BL31" s="14"/>
-      <c r="BM31" s="14"/>
-      <c r="BN31" s="14"/>
-      <c r="BO31" s="14"/>
-      <c r="BP31" s="14"/>
-      <c r="BQ31" s="15"/>
-      <c r="BR31" s="31"/>
+      <c r="AZ31" s="20"/>
+      <c r="BA31" s="20"/>
+      <c r="BB31" s="20"/>
+      <c r="BC31" s="20"/>
+      <c r="BD31" s="20"/>
+      <c r="BE31" s="20"/>
+      <c r="BF31" s="20"/>
+      <c r="BG31" s="20"/>
+      <c r="BH31" s="20"/>
+      <c r="BI31" s="20"/>
+      <c r="BJ31" s="20"/>
+      <c r="BK31" s="20"/>
+      <c r="BL31" s="20"/>
+      <c r="BM31" s="20"/>
+      <c r="BN31" s="20"/>
+      <c r="BO31" s="20"/>
+      <c r="BP31" s="20"/>
+      <c r="BQ31" s="21"/>
+      <c r="BR31" s="17"/>
     </row>
     <row r="32" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B32" s="31"/>
+      <c r="B32" s="17"/>
       <c r="E32" s="3"/>
       <c r="AA32" s="3"/>
       <c r="AW32" s="25"/>
-      <c r="AX32" s="16"/>
-      <c r="AY32" s="16"/>
-      <c r="AZ32" s="16"/>
-      <c r="BA32" s="16"/>
-      <c r="BB32" s="16"/>
-      <c r="BC32" s="16"/>
-      <c r="BD32" s="16"/>
-      <c r="BE32" s="16"/>
-      <c r="BF32" s="16"/>
-      <c r="BG32" s="16"/>
-      <c r="BH32" s="16"/>
-      <c r="BI32" s="16"/>
-      <c r="BJ32" s="16"/>
-      <c r="BK32" s="16"/>
-      <c r="BL32" s="16"/>
-      <c r="BM32" s="16"/>
-      <c r="BN32" s="16"/>
-      <c r="BO32" s="16"/>
-      <c r="BP32" s="16"/>
-      <c r="BQ32" s="17"/>
-      <c r="BR32" s="31"/>
+      <c r="AX32" s="26"/>
+      <c r="AY32" s="26"/>
+      <c r="AZ32" s="26"/>
+      <c r="BA32" s="26"/>
+      <c r="BB32" s="26"/>
+      <c r="BC32" s="26"/>
+      <c r="BD32" s="26"/>
+      <c r="BE32" s="26"/>
+      <c r="BF32" s="26"/>
+      <c r="BG32" s="26"/>
+      <c r="BH32" s="26"/>
+      <c r="BI32" s="26"/>
+      <c r="BJ32" s="26"/>
+      <c r="BK32" s="26"/>
+      <c r="BL32" s="26"/>
+      <c r="BM32" s="26"/>
+      <c r="BN32" s="26"/>
+      <c r="BO32" s="26"/>
+      <c r="BP32" s="26"/>
+      <c r="BQ32" s="27"/>
+      <c r="BR32" s="17"/>
     </row>
     <row r="33" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B33" s="31"/>
+      <c r="B33" s="17"/>
       <c r="AW33" s="25"/>
-      <c r="AX33" s="16"/>
-      <c r="AY33" s="16"/>
-      <c r="AZ33" s="16"/>
-      <c r="BA33" s="16"/>
-      <c r="BB33" s="16"/>
-      <c r="BC33" s="16"/>
-      <c r="BD33" s="16"/>
-      <c r="BE33" s="16"/>
-      <c r="BF33" s="16"/>
-      <c r="BG33" s="16"/>
-      <c r="BH33" s="16"/>
-      <c r="BI33" s="16"/>
-      <c r="BJ33" s="16"/>
-      <c r="BK33" s="16"/>
-      <c r="BL33" s="16"/>
-      <c r="BM33" s="16"/>
-      <c r="BN33" s="16"/>
-      <c r="BO33" s="16"/>
-      <c r="BP33" s="16"/>
-      <c r="BQ33" s="17"/>
-      <c r="BR33" s="31"/>
+      <c r="AX33" s="26"/>
+      <c r="AY33" s="26"/>
+      <c r="AZ33" s="26"/>
+      <c r="BA33" s="26"/>
+      <c r="BB33" s="26"/>
+      <c r="BC33" s="26"/>
+      <c r="BD33" s="26"/>
+      <c r="BE33" s="26"/>
+      <c r="BF33" s="26"/>
+      <c r="BG33" s="26"/>
+      <c r="BH33" s="26"/>
+      <c r="BI33" s="26"/>
+      <c r="BJ33" s="26"/>
+      <c r="BK33" s="26"/>
+      <c r="BL33" s="26"/>
+      <c r="BM33" s="26"/>
+      <c r="BN33" s="26"/>
+      <c r="BO33" s="26"/>
+      <c r="BP33" s="26"/>
+      <c r="BQ33" s="27"/>
+      <c r="BR33" s="17"/>
     </row>
     <row r="34" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B34" s="31"/>
+      <c r="B34" s="17"/>
       <c r="AW34" s="25"/>
-      <c r="AX34" s="16"/>
-      <c r="AY34" s="16"/>
-      <c r="AZ34" s="16"/>
-      <c r="BA34" s="16"/>
-      <c r="BB34" s="16"/>
-      <c r="BC34" s="16"/>
-      <c r="BD34" s="16"/>
-      <c r="BE34" s="16"/>
-      <c r="BF34" s="16"/>
-      <c r="BG34" s="16"/>
-      <c r="BH34" s="16"/>
-      <c r="BI34" s="16"/>
-      <c r="BJ34" s="16"/>
-      <c r="BK34" s="16"/>
-      <c r="BL34" s="16"/>
-      <c r="BM34" s="16"/>
-      <c r="BN34" s="16"/>
-      <c r="BO34" s="16"/>
-      <c r="BP34" s="16"/>
-      <c r="BQ34" s="17"/>
-      <c r="BR34" s="31"/>
+      <c r="AX34" s="26"/>
+      <c r="AY34" s="26"/>
+      <c r="AZ34" s="26"/>
+      <c r="BA34" s="26"/>
+      <c r="BB34" s="26"/>
+      <c r="BC34" s="26"/>
+      <c r="BD34" s="26"/>
+      <c r="BE34" s="26"/>
+      <c r="BF34" s="26"/>
+      <c r="BG34" s="26"/>
+      <c r="BH34" s="26"/>
+      <c r="BI34" s="26"/>
+      <c r="BJ34" s="26"/>
+      <c r="BK34" s="26"/>
+      <c r="BL34" s="26"/>
+      <c r="BM34" s="26"/>
+      <c r="BN34" s="26"/>
+      <c r="BO34" s="26"/>
+      <c r="BP34" s="26"/>
+      <c r="BQ34" s="27"/>
+      <c r="BR34" s="17"/>
     </row>
     <row r="35" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B35" s="31"/>
-      <c r="E35" s="13" t="s">
-        <v>201</v>
-      </c>
-      <c r="F35" s="13"/>
-      <c r="G35" s="13"/>
-      <c r="H35" s="13"/>
-      <c r="I35" s="13"/>
-      <c r="J35" s="13"/>
-      <c r="K35" s="13"/>
-      <c r="L35" s="13"/>
-      <c r="M35" s="13"/>
-      <c r="N35" s="13"/>
-      <c r="O35" s="13"/>
-      <c r="P35" s="13"/>
-      <c r="Q35" s="13"/>
-      <c r="R35" s="13"/>
-      <c r="T35" s="13" t="s">
+      <c r="B35" s="17"/>
+      <c r="E35" s="3"/>
+      <c r="F35" s="3"/>
+      <c r="G35" s="3"/>
+      <c r="H35" s="3"/>
+      <c r="I35" s="3"/>
+      <c r="J35" s="3"/>
+      <c r="K35" s="3"/>
+      <c r="L35" s="3"/>
+      <c r="M35" s="3"/>
+      <c r="N35" s="3"/>
+      <c r="O35" s="3"/>
+      <c r="P35" s="3"/>
+      <c r="Q35" s="3"/>
+      <c r="R35" s="3"/>
+      <c r="T35" s="35" t="s">
         <v>172</v>
       </c>
-      <c r="U35" s="13"/>
-      <c r="V35" s="13"/>
-      <c r="W35" s="13"/>
-      <c r="X35" s="13"/>
-      <c r="Y35" s="13"/>
-      <c r="Z35" s="13"/>
-      <c r="AA35" s="13"/>
-      <c r="AB35" s="13"/>
-      <c r="AC35" s="13"/>
-      <c r="AD35" s="13"/>
-      <c r="AE35" s="13"/>
-      <c r="AF35" s="13"/>
-      <c r="AG35" s="13"/>
+      <c r="U35" s="35"/>
+      <c r="V35" s="35"/>
+      <c r="W35" s="35"/>
+      <c r="X35" s="35"/>
+      <c r="Y35" s="35"/>
+      <c r="Z35" s="35"/>
+      <c r="AA35" s="35"/>
+      <c r="AB35" s="35"/>
+      <c r="AC35" s="35"/>
+      <c r="AD35" s="35"/>
+      <c r="AE35" s="35"/>
+      <c r="AF35" s="35"/>
+      <c r="AG35" s="35"/>
       <c r="AW35" s="25"/>
-      <c r="AX35" s="16"/>
-      <c r="AY35" s="16"/>
-      <c r="AZ35" s="16"/>
-      <c r="BA35" s="16"/>
-      <c r="BB35" s="16"/>
-      <c r="BC35" s="16"/>
-      <c r="BD35" s="16"/>
-      <c r="BE35" s="16"/>
-      <c r="BF35" s="16"/>
-      <c r="BG35" s="16"/>
-      <c r="BH35" s="16"/>
-      <c r="BI35" s="16"/>
-      <c r="BJ35" s="16"/>
-      <c r="BK35" s="16"/>
-      <c r="BL35" s="16"/>
-      <c r="BM35" s="16"/>
-      <c r="BN35" s="16"/>
-      <c r="BO35" s="16"/>
-      <c r="BP35" s="16"/>
-      <c r="BQ35" s="17"/>
-      <c r="BR35" s="31"/>
+      <c r="AX35" s="26"/>
+      <c r="AY35" s="26"/>
+      <c r="AZ35" s="26"/>
+      <c r="BA35" s="26"/>
+      <c r="BB35" s="26"/>
+      <c r="BC35" s="26"/>
+      <c r="BD35" s="26"/>
+      <c r="BE35" s="26"/>
+      <c r="BF35" s="26"/>
+      <c r="BG35" s="26"/>
+      <c r="BH35" s="26"/>
+      <c r="BI35" s="26"/>
+      <c r="BJ35" s="26"/>
+      <c r="BK35" s="26"/>
+      <c r="BL35" s="26"/>
+      <c r="BM35" s="26"/>
+      <c r="BN35" s="26"/>
+      <c r="BO35" s="26"/>
+      <c r="BP35" s="26"/>
+      <c r="BQ35" s="27"/>
+      <c r="BR35" s="17"/>
     </row>
     <row r="36" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B36" s="31"/>
-      <c r="E36" s="13"/>
-      <c r="F36" s="13"/>
-      <c r="G36" s="13"/>
-      <c r="H36" s="13"/>
-      <c r="I36" s="13"/>
-      <c r="J36" s="13"/>
-      <c r="K36" s="13"/>
-      <c r="L36" s="13"/>
-      <c r="M36" s="13"/>
-      <c r="N36" s="13"/>
-      <c r="O36" s="13"/>
-      <c r="P36" s="13"/>
-      <c r="Q36" s="13"/>
-      <c r="R36" s="13"/>
-      <c r="T36" s="13"/>
-      <c r="U36" s="13"/>
-      <c r="V36" s="13"/>
-      <c r="W36" s="13"/>
-      <c r="X36" s="13"/>
-      <c r="Y36" s="13"/>
-      <c r="Z36" s="13"/>
-      <c r="AA36" s="13"/>
-      <c r="AB36" s="13"/>
-      <c r="AC36" s="13"/>
-      <c r="AD36" s="13"/>
-      <c r="AE36" s="13"/>
-      <c r="AF36" s="13"/>
-      <c r="AG36" s="13"/>
+      <c r="B36" s="17"/>
+      <c r="E36" s="3"/>
+      <c r="F36" s="3"/>
+      <c r="G36" s="3"/>
+      <c r="H36" s="3"/>
+      <c r="I36" s="3"/>
+      <c r="J36" s="3"/>
+      <c r="K36" s="3"/>
+      <c r="L36" s="3"/>
+      <c r="M36" s="3"/>
+      <c r="N36" s="3"/>
+      <c r="O36" s="3"/>
+      <c r="P36" s="3"/>
+      <c r="Q36" s="3"/>
+      <c r="R36" s="3"/>
+      <c r="T36" s="35"/>
+      <c r="U36" s="35"/>
+      <c r="V36" s="35"/>
+      <c r="W36" s="35"/>
+      <c r="X36" s="35"/>
+      <c r="Y36" s="35"/>
+      <c r="Z36" s="35"/>
+      <c r="AA36" s="35"/>
+      <c r="AB36" s="35"/>
+      <c r="AC36" s="35"/>
+      <c r="AD36" s="35"/>
+      <c r="AE36" s="35"/>
+      <c r="AF36" s="35"/>
+      <c r="AG36" s="35"/>
       <c r="AW36" s="22"/>
       <c r="AX36" s="23"/>
       <c r="AY36" s="23"/>
@@ -3137,280 +3114,280 @@
       <c r="BO36" s="23"/>
       <c r="BP36" s="23"/>
       <c r="BQ36" s="24"/>
-      <c r="BR36" s="31"/>
+      <c r="BR36" s="17"/>
     </row>
     <row r="37" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B37" s="31"/>
-      <c r="E37" s="13"/>
-      <c r="F37" s="13"/>
-      <c r="G37" s="13"/>
-      <c r="H37" s="13"/>
-      <c r="I37" s="13"/>
-      <c r="J37" s="13"/>
-      <c r="K37" s="13"/>
-      <c r="L37" s="13"/>
-      <c r="M37" s="13"/>
-      <c r="N37" s="13"/>
-      <c r="O37" s="13"/>
-      <c r="P37" s="13"/>
-      <c r="Q37" s="13"/>
-      <c r="R37" s="13"/>
-      <c r="T37" s="13"/>
-      <c r="U37" s="13"/>
-      <c r="V37" s="13"/>
-      <c r="W37" s="13"/>
-      <c r="X37" s="13"/>
-      <c r="Y37" s="13"/>
-      <c r="Z37" s="13"/>
-      <c r="AA37" s="13"/>
-      <c r="AB37" s="13"/>
-      <c r="AC37" s="13"/>
-      <c r="AD37" s="13"/>
-      <c r="AE37" s="13"/>
-      <c r="AF37" s="13"/>
-      <c r="AG37" s="13"/>
-      <c r="BR37" s="31"/>
+      <c r="B37" s="17"/>
+      <c r="E37" s="3"/>
+      <c r="F37" s="3"/>
+      <c r="G37" s="3"/>
+      <c r="H37" s="3"/>
+      <c r="I37" s="3"/>
+      <c r="J37" s="3"/>
+      <c r="K37" s="3"/>
+      <c r="L37" s="3"/>
+      <c r="M37" s="3"/>
+      <c r="N37" s="3"/>
+      <c r="O37" s="3"/>
+      <c r="P37" s="3"/>
+      <c r="Q37" s="3"/>
+      <c r="R37" s="3"/>
+      <c r="T37" s="35"/>
+      <c r="U37" s="35"/>
+      <c r="V37" s="35"/>
+      <c r="W37" s="35"/>
+      <c r="X37" s="35"/>
+      <c r="Y37" s="35"/>
+      <c r="Z37" s="35"/>
+      <c r="AA37" s="35"/>
+      <c r="AB37" s="35"/>
+      <c r="AC37" s="35"/>
+      <c r="AD37" s="35"/>
+      <c r="AE37" s="35"/>
+      <c r="AF37" s="35"/>
+      <c r="AG37" s="35"/>
+      <c r="BR37" s="17"/>
     </row>
     <row r="38" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B38" s="31"/>
-      <c r="E38" s="13"/>
-      <c r="F38" s="13"/>
-      <c r="G38" s="13"/>
-      <c r="H38" s="13"/>
-      <c r="I38" s="13"/>
-      <c r="J38" s="13"/>
-      <c r="K38" s="13"/>
-      <c r="L38" s="13"/>
-      <c r="M38" s="13"/>
-      <c r="N38" s="13"/>
-      <c r="O38" s="13"/>
-      <c r="P38" s="13"/>
-      <c r="Q38" s="13"/>
-      <c r="R38" s="13"/>
-      <c r="T38" s="13"/>
-      <c r="U38" s="13"/>
-      <c r="V38" s="13"/>
-      <c r="W38" s="13"/>
-      <c r="X38" s="13"/>
-      <c r="Y38" s="13"/>
-      <c r="Z38" s="13"/>
-      <c r="AA38" s="13"/>
-      <c r="AB38" s="13"/>
-      <c r="AC38" s="13"/>
-      <c r="AD38" s="13"/>
-      <c r="AE38" s="13"/>
-      <c r="AF38" s="13"/>
-      <c r="AG38" s="13"/>
-      <c r="BR38" s="31"/>
+      <c r="B38" s="17"/>
+      <c r="E38" s="3"/>
+      <c r="F38" s="3"/>
+      <c r="G38" s="3"/>
+      <c r="H38" s="3"/>
+      <c r="I38" s="3"/>
+      <c r="J38" s="3"/>
+      <c r="K38" s="3"/>
+      <c r="L38" s="3"/>
+      <c r="M38" s="3"/>
+      <c r="N38" s="3"/>
+      <c r="O38" s="3"/>
+      <c r="P38" s="3"/>
+      <c r="Q38" s="3"/>
+      <c r="R38" s="3"/>
+      <c r="T38" s="35"/>
+      <c r="U38" s="35"/>
+      <c r="V38" s="35"/>
+      <c r="W38" s="35"/>
+      <c r="X38" s="35"/>
+      <c r="Y38" s="35"/>
+      <c r="Z38" s="35"/>
+      <c r="AA38" s="35"/>
+      <c r="AB38" s="35"/>
+      <c r="AC38" s="35"/>
+      <c r="AD38" s="35"/>
+      <c r="AE38" s="35"/>
+      <c r="AF38" s="35"/>
+      <c r="AG38" s="35"/>
+      <c r="BR38" s="17"/>
     </row>
     <row r="39" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B39" s="31"/>
-      <c r="E39" s="13"/>
-      <c r="F39" s="13"/>
-      <c r="G39" s="13"/>
-      <c r="H39" s="13"/>
-      <c r="I39" s="13"/>
-      <c r="J39" s="13"/>
-      <c r="K39" s="13"/>
-      <c r="L39" s="13"/>
-      <c r="M39" s="13"/>
-      <c r="N39" s="13"/>
-      <c r="O39" s="13"/>
-      <c r="P39" s="13"/>
-      <c r="Q39" s="13"/>
-      <c r="R39" s="13"/>
-      <c r="T39" s="13"/>
-      <c r="U39" s="13"/>
-      <c r="V39" s="13"/>
-      <c r="W39" s="13"/>
-      <c r="X39" s="13"/>
-      <c r="Y39" s="13"/>
-      <c r="Z39" s="13"/>
-      <c r="AA39" s="13"/>
-      <c r="AB39" s="13"/>
-      <c r="AC39" s="13"/>
-      <c r="AD39" s="13"/>
-      <c r="AE39" s="13"/>
-      <c r="AF39" s="13"/>
-      <c r="AG39" s="13"/>
+      <c r="B39" s="17"/>
+      <c r="E39" s="3"/>
+      <c r="F39" s="3"/>
+      <c r="G39" s="3"/>
+      <c r="H39" s="3"/>
+      <c r="I39" s="3"/>
+      <c r="J39" s="3"/>
+      <c r="K39" s="3"/>
+      <c r="L39" s="3"/>
+      <c r="M39" s="3"/>
+      <c r="N39" s="3"/>
+      <c r="O39" s="3"/>
+      <c r="P39" s="3"/>
+      <c r="Q39" s="3"/>
+      <c r="R39" s="3"/>
+      <c r="T39" s="35"/>
+      <c r="U39" s="35"/>
+      <c r="V39" s="35"/>
+      <c r="W39" s="35"/>
+      <c r="X39" s="35"/>
+      <c r="Y39" s="35"/>
+      <c r="Z39" s="35"/>
+      <c r="AA39" s="35"/>
+      <c r="AB39" s="35"/>
+      <c r="AC39" s="35"/>
+      <c r="AD39" s="35"/>
+      <c r="AE39" s="35"/>
+      <c r="AF39" s="35"/>
+      <c r="AG39" s="35"/>
       <c r="AW39" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="AX39" s="18" t="s">
+      <c r="AX39" s="13" t="s">
         <v>174</v>
       </c>
-      <c r="AY39" s="19"/>
-      <c r="AZ39" s="20"/>
-      <c r="BA39" s="18" t="s">
+      <c r="AY39" s="14"/>
+      <c r="AZ39" s="15"/>
+      <c r="BA39" s="13" t="s">
         <v>175</v>
       </c>
-      <c r="BB39" s="19"/>
-      <c r="BC39" s="19"/>
-      <c r="BD39" s="19"/>
-      <c r="BE39" s="19"/>
-      <c r="BF39" s="19"/>
-      <c r="BG39" s="19"/>
-      <c r="BH39" s="20"/>
-      <c r="BI39" s="18" t="s">
+      <c r="BB39" s="14"/>
+      <c r="BC39" s="14"/>
+      <c r="BD39" s="14"/>
+      <c r="BE39" s="14"/>
+      <c r="BF39" s="14"/>
+      <c r="BG39" s="14"/>
+      <c r="BH39" s="15"/>
+      <c r="BI39" s="13" t="s">
         <v>176</v>
       </c>
-      <c r="BJ39" s="19"/>
-      <c r="BK39" s="20"/>
-      <c r="BL39" s="18" t="s">
+      <c r="BJ39" s="14"/>
+      <c r="BK39" s="15"/>
+      <c r="BL39" s="13" t="s">
         <v>177</v>
       </c>
-      <c r="BM39" s="19"/>
-      <c r="BN39" s="20"/>
-      <c r="BO39" s="18" t="s">
+      <c r="BM39" s="14"/>
+      <c r="BN39" s="15"/>
+      <c r="BO39" s="13" t="s">
         <v>178</v>
       </c>
-      <c r="BP39" s="19"/>
-      <c r="BQ39" s="20"/>
-      <c r="BR39" s="31"/>
+      <c r="BP39" s="14"/>
+      <c r="BQ39" s="15"/>
+      <c r="BR39" s="17"/>
     </row>
     <row r="40" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B40" s="31"/>
+      <c r="B40" s="17"/>
       <c r="AW40" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="AX40" s="18" t="s">
+      <c r="AX40" s="13" t="s">
         <v>180</v>
       </c>
-      <c r="AY40" s="19"/>
-      <c r="AZ40" s="20"/>
-      <c r="BA40" s="18" t="s">
+      <c r="AY40" s="14"/>
+      <c r="AZ40" s="15"/>
+      <c r="BA40" s="13" t="s">
         <v>181</v>
       </c>
-      <c r="BB40" s="19"/>
-      <c r="BC40" s="19"/>
-      <c r="BD40" s="19"/>
-      <c r="BE40" s="19"/>
-      <c r="BF40" s="19"/>
-      <c r="BG40" s="19"/>
-      <c r="BH40" s="20"/>
-      <c r="BI40" s="18" t="s">
+      <c r="BB40" s="14"/>
+      <c r="BC40" s="14"/>
+      <c r="BD40" s="14"/>
+      <c r="BE40" s="14"/>
+      <c r="BF40" s="14"/>
+      <c r="BG40" s="14"/>
+      <c r="BH40" s="15"/>
+      <c r="BI40" s="13" t="s">
         <v>182</v>
       </c>
-      <c r="BJ40" s="19"/>
-      <c r="BK40" s="20"/>
-      <c r="BL40" s="18" t="s">
+      <c r="BJ40" s="14"/>
+      <c r="BK40" s="15"/>
+      <c r="BL40" s="13" t="s">
         <v>183</v>
       </c>
-      <c r="BM40" s="19"/>
-      <c r="BN40" s="20"/>
-      <c r="BO40" s="18" t="s">
+      <c r="BM40" s="14"/>
+      <c r="BN40" s="15"/>
+      <c r="BO40" s="13" t="s">
         <v>184</v>
       </c>
-      <c r="BP40" s="19"/>
-      <c r="BQ40" s="20"/>
-      <c r="BR40" s="31"/>
+      <c r="BP40" s="14"/>
+      <c r="BQ40" s="15"/>
+      <c r="BR40" s="17"/>
     </row>
     <row r="41" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B41" s="31"/>
+      <c r="B41" s="17"/>
       <c r="AW41" s="5" t="s">
         <v>185</v>
       </c>
-      <c r="AX41" s="18" t="s">
+      <c r="AX41" s="13" t="s">
         <v>186</v>
       </c>
-      <c r="AY41" s="19"/>
-      <c r="AZ41" s="20"/>
-      <c r="BA41" s="18" t="s">
+      <c r="AY41" s="14"/>
+      <c r="AZ41" s="15"/>
+      <c r="BA41" s="13" t="s">
         <v>187</v>
       </c>
-      <c r="BB41" s="19"/>
-      <c r="BC41" s="19"/>
-      <c r="BD41" s="19"/>
-      <c r="BE41" s="19"/>
-      <c r="BF41" s="19"/>
-      <c r="BG41" s="19"/>
-      <c r="BH41" s="20"/>
-      <c r="BI41" s="18" t="s">
+      <c r="BB41" s="14"/>
+      <c r="BC41" s="14"/>
+      <c r="BD41" s="14"/>
+      <c r="BE41" s="14"/>
+      <c r="BF41" s="14"/>
+      <c r="BG41" s="14"/>
+      <c r="BH41" s="15"/>
+      <c r="BI41" s="13" t="s">
         <v>188</v>
       </c>
-      <c r="BJ41" s="19"/>
-      <c r="BK41" s="20"/>
-      <c r="BL41" s="18" t="s">
+      <c r="BJ41" s="14"/>
+      <c r="BK41" s="15"/>
+      <c r="BL41" s="13" t="s">
         <v>189</v>
       </c>
-      <c r="BM41" s="19"/>
-      <c r="BN41" s="20"/>
-      <c r="BO41" s="18" t="s">
+      <c r="BM41" s="14"/>
+      <c r="BN41" s="15"/>
+      <c r="BO41" s="13" t="s">
         <v>190</v>
       </c>
-      <c r="BP41" s="19"/>
-      <c r="BQ41" s="20"/>
-      <c r="BR41" s="31"/>
+      <c r="BP41" s="14"/>
+      <c r="BQ41" s="15"/>
+      <c r="BR41" s="17"/>
     </row>
     <row r="42" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B42" s="31"/>
+      <c r="B42" s="17"/>
       <c r="AW42" s="5" t="s">
         <v>191</v>
       </c>
-      <c r="AX42" s="18" t="s">
+      <c r="AX42" s="13" t="s">
         <v>192</v>
       </c>
-      <c r="AY42" s="19"/>
-      <c r="AZ42" s="20"/>
-      <c r="BA42" s="18" t="s">
+      <c r="AY42" s="14"/>
+      <c r="AZ42" s="15"/>
+      <c r="BA42" s="13" t="s">
         <v>193</v>
       </c>
-      <c r="BB42" s="19"/>
-      <c r="BC42" s="19"/>
-      <c r="BD42" s="19"/>
-      <c r="BE42" s="19"/>
-      <c r="BF42" s="19"/>
-      <c r="BG42" s="19"/>
-      <c r="BH42" s="20"/>
-      <c r="BI42" s="18" t="s">
+      <c r="BB42" s="14"/>
+      <c r="BC42" s="14"/>
+      <c r="BD42" s="14"/>
+      <c r="BE42" s="14"/>
+      <c r="BF42" s="14"/>
+      <c r="BG42" s="14"/>
+      <c r="BH42" s="15"/>
+      <c r="BI42" s="13" t="s">
         <v>194</v>
       </c>
-      <c r="BJ42" s="19"/>
-      <c r="BK42" s="20"/>
-      <c r="BL42" s="18" t="s">
+      <c r="BJ42" s="14"/>
+      <c r="BK42" s="15"/>
+      <c r="BL42" s="13" t="s">
         <v>195</v>
       </c>
-      <c r="BM42" s="19"/>
-      <c r="BN42" s="20"/>
-      <c r="BO42" s="18" t="s">
+      <c r="BM42" s="14"/>
+      <c r="BN42" s="15"/>
+      <c r="BO42" s="13" t="s">
         <v>196</v>
       </c>
-      <c r="BP42" s="19"/>
-      <c r="BQ42" s="20"/>
-      <c r="BR42" s="31"/>
+      <c r="BP42" s="14"/>
+      <c r="BQ42" s="15"/>
+      <c r="BR42" s="17"/>
     </row>
     <row r="43" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B43" s="27"/>
-      <c r="AW43" s="26" t="s">
+      <c r="B43" s="18"/>
+      <c r="AW43" s="16" t="s">
         <v>197</v>
       </c>
-      <c r="AX43" s="21"/>
-      <c r="AY43" s="14"/>
-      <c r="AZ43" s="15"/>
-      <c r="BA43" s="21"/>
-      <c r="BB43" s="14"/>
-      <c r="BC43" s="14"/>
-      <c r="BD43" s="14"/>
-      <c r="BE43" s="14"/>
-      <c r="BF43" s="14"/>
-      <c r="BG43" s="14"/>
-      <c r="BH43" s="15"/>
-      <c r="BI43" s="21"/>
-      <c r="BJ43" s="14"/>
-      <c r="BK43" s="15"/>
-      <c r="BL43" s="21"/>
-      <c r="BM43" s="14"/>
-      <c r="BN43" s="15"/>
-      <c r="BO43" s="21"/>
-      <c r="BP43" s="14"/>
-      <c r="BQ43" s="15"/>
-      <c r="BR43" s="27"/>
+      <c r="AX43" s="19"/>
+      <c r="AY43" s="20"/>
+      <c r="AZ43" s="21"/>
+      <c r="BA43" s="19"/>
+      <c r="BB43" s="20"/>
+      <c r="BC43" s="20"/>
+      <c r="BD43" s="20"/>
+      <c r="BE43" s="20"/>
+      <c r="BF43" s="20"/>
+      <c r="BG43" s="20"/>
+      <c r="BH43" s="21"/>
+      <c r="BI43" s="19"/>
+      <c r="BJ43" s="20"/>
+      <c r="BK43" s="21"/>
+      <c r="BL43" s="19"/>
+      <c r="BM43" s="20"/>
+      <c r="BN43" s="21"/>
+      <c r="BO43" s="19"/>
+      <c r="BP43" s="20"/>
+      <c r="BQ43" s="21"/>
+      <c r="BR43" s="18"/>
     </row>
     <row r="44" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B44" s="26" t="s">
-        <v>203</v>
-      </c>
-      <c r="AW44" s="27"/>
+      <c r="B44" s="16" t="s">
+        <v>198</v>
+      </c>
+      <c r="AW44" s="18"/>
       <c r="AX44" s="22"/>
       <c r="AY44" s="23"/>
       <c r="AZ44" s="24"/>
@@ -3431,236 +3408,234 @@
       <c r="BO44" s="22"/>
       <c r="BP44" s="23"/>
       <c r="BQ44" s="24"/>
-      <c r="BR44" s="26" t="s">
+      <c r="BR44" s="16" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="45" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B45" s="17"/>
+      <c r="AW45" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="AX45" s="13" t="s">
+        <v>200</v>
+      </c>
+      <c r="AY45" s="14"/>
+      <c r="AZ45" s="15"/>
+      <c r="BA45" s="13" t="s">
+        <v>201</v>
+      </c>
+      <c r="BB45" s="14"/>
+      <c r="BC45" s="14"/>
+      <c r="BD45" s="14"/>
+      <c r="BE45" s="14"/>
+      <c r="BF45" s="14"/>
+      <c r="BG45" s="14"/>
+      <c r="BH45" s="15"/>
+      <c r="BI45" s="13" t="s">
+        <v>202</v>
+      </c>
+      <c r="BJ45" s="14"/>
+      <c r="BK45" s="15"/>
+      <c r="BL45" s="13" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="45" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B45" s="31"/>
-      <c r="AW45" s="5" t="s">
+      <c r="BM45" s="14"/>
+      <c r="BN45" s="15"/>
+      <c r="BO45" s="13" t="s">
         <v>204</v>
       </c>
-      <c r="AX45" s="18" t="s">
+      <c r="BP45" s="14"/>
+      <c r="BQ45" s="15"/>
+      <c r="BR45" s="17"/>
+    </row>
+    <row r="46" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B46" s="17"/>
+      <c r="AW46" s="13" t="s">
         <v>205</v>
       </c>
-      <c r="AY45" s="19"/>
-      <c r="AZ45" s="20"/>
-      <c r="BA45" s="18" t="s">
+      <c r="AX46" s="14"/>
+      <c r="AY46" s="14"/>
+      <c r="AZ46" s="15"/>
+      <c r="BA46" s="13" t="s">
         <v>206</v>
       </c>
-      <c r="BB45" s="19"/>
-      <c r="BC45" s="19"/>
-      <c r="BD45" s="19"/>
-      <c r="BE45" s="19"/>
-      <c r="BF45" s="19"/>
-      <c r="BG45" s="19"/>
-      <c r="BH45" s="20"/>
-      <c r="BI45" s="18" t="s">
+      <c r="BB46" s="14"/>
+      <c r="BC46" s="14"/>
+      <c r="BD46" s="14"/>
+      <c r="BE46" s="14"/>
+      <c r="BF46" s="14"/>
+      <c r="BG46" s="14"/>
+      <c r="BH46" s="15"/>
+      <c r="BI46" s="13" t="s">
         <v>207</v>
       </c>
-      <c r="BJ45" s="19"/>
-      <c r="BK45" s="20"/>
-      <c r="BL45" s="18" t="s">
+      <c r="BJ46" s="14"/>
+      <c r="BK46" s="14"/>
+      <c r="BL46" s="14"/>
+      <c r="BM46" s="14"/>
+      <c r="BN46" s="14"/>
+      <c r="BO46" s="14"/>
+      <c r="BP46" s="14"/>
+      <c r="BQ46" s="15"/>
+      <c r="BR46" s="17"/>
+    </row>
+    <row r="47" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B47" s="17"/>
+      <c r="E47" s="3"/>
+      <c r="F47" s="3"/>
+      <c r="G47" s="3"/>
+      <c r="H47" s="3"/>
+      <c r="I47" s="3"/>
+      <c r="J47" s="3"/>
+      <c r="K47" s="3"/>
+      <c r="L47" s="3"/>
+      <c r="M47" s="3"/>
+      <c r="N47" s="3"/>
+      <c r="O47" s="3"/>
+      <c r="P47" s="3"/>
+      <c r="Q47" s="3"/>
+      <c r="R47" s="3"/>
+      <c r="T47" s="35" t="s">
+        <v>226</v>
+      </c>
+      <c r="U47" s="35"/>
+      <c r="V47" s="35"/>
+      <c r="W47" s="35"/>
+      <c r="X47" s="35"/>
+      <c r="Y47" s="35"/>
+      <c r="Z47" s="35"/>
+      <c r="AA47" s="35"/>
+      <c r="AB47" s="35"/>
+      <c r="AC47" s="35"/>
+      <c r="AD47" s="35"/>
+      <c r="AE47" s="35"/>
+      <c r="AF47" s="35"/>
+      <c r="AG47" s="35"/>
+      <c r="AW47" s="13" t="s">
         <v>208</v>
       </c>
-      <c r="BM45" s="19"/>
-      <c r="BN45" s="20"/>
-      <c r="BO45" s="18" t="s">
+      <c r="AX47" s="14"/>
+      <c r="AY47" s="14"/>
+      <c r="AZ47" s="15"/>
+      <c r="BA47" s="13" t="s">
         <v>209</v>
       </c>
-      <c r="BP45" s="19"/>
-      <c r="BQ45" s="20"/>
-      <c r="BR45" s="31"/>
-    </row>
-    <row r="46" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B46" s="31"/>
-      <c r="AW46" s="18" t="s">
+      <c r="BB47" s="14"/>
+      <c r="BC47" s="14"/>
+      <c r="BD47" s="14"/>
+      <c r="BE47" s="14"/>
+      <c r="BF47" s="14"/>
+      <c r="BG47" s="14"/>
+      <c r="BH47" s="15"/>
+      <c r="BI47" s="13" t="s">
         <v>210</v>
       </c>
-      <c r="AX46" s="19"/>
-      <c r="AY46" s="19"/>
-      <c r="AZ46" s="20"/>
-      <c r="BA46" s="18" t="s">
+      <c r="BJ47" s="14"/>
+      <c r="BK47" s="14"/>
+      <c r="BL47" s="14"/>
+      <c r="BM47" s="14"/>
+      <c r="BN47" s="14"/>
+      <c r="BO47" s="14"/>
+      <c r="BP47" s="14"/>
+      <c r="BQ47" s="15"/>
+      <c r="BR47" s="17"/>
+    </row>
+    <row r="48" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B48" s="17"/>
+      <c r="E48" s="3"/>
+      <c r="F48" s="3"/>
+      <c r="G48" s="3"/>
+      <c r="H48" s="3"/>
+      <c r="I48" s="3"/>
+      <c r="J48" s="3"/>
+      <c r="K48" s="3"/>
+      <c r="L48" s="3"/>
+      <c r="M48" s="3"/>
+      <c r="N48" s="3"/>
+      <c r="O48" s="3"/>
+      <c r="P48" s="3"/>
+      <c r="Q48" s="3"/>
+      <c r="R48" s="3"/>
+      <c r="T48" s="35"/>
+      <c r="U48" s="35"/>
+      <c r="V48" s="35"/>
+      <c r="W48" s="35"/>
+      <c r="X48" s="35"/>
+      <c r="Y48" s="35"/>
+      <c r="Z48" s="35"/>
+      <c r="AA48" s="35"/>
+      <c r="AB48" s="35"/>
+      <c r="AC48" s="35"/>
+      <c r="AD48" s="35"/>
+      <c r="AE48" s="35"/>
+      <c r="AF48" s="35"/>
+      <c r="AG48" s="35"/>
+      <c r="AW48" s="19" t="s">
         <v>211</v>
       </c>
-      <c r="BB46" s="19"/>
-      <c r="BC46" s="19"/>
-      <c r="BD46" s="19"/>
-      <c r="BE46" s="19"/>
-      <c r="BF46" s="19"/>
-      <c r="BG46" s="19"/>
-      <c r="BH46" s="20"/>
-      <c r="BI46" s="18" t="s">
+      <c r="AX48" s="20"/>
+      <c r="AY48" s="20"/>
+      <c r="AZ48" s="20"/>
+      <c r="BA48" s="20"/>
+      <c r="BB48" s="20"/>
+      <c r="BC48" s="20"/>
+      <c r="BD48" s="21"/>
+      <c r="BE48" s="19" t="s">
         <v>212</v>
       </c>
-      <c r="BJ46" s="19"/>
-      <c r="BK46" s="19"/>
-      <c r="BL46" s="19"/>
-      <c r="BM46" s="19"/>
-      <c r="BN46" s="19"/>
-      <c r="BO46" s="19"/>
-      <c r="BP46" s="19"/>
-      <c r="BQ46" s="20"/>
-      <c r="BR46" s="31"/>
-    </row>
-    <row r="47" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B47" s="31"/>
-      <c r="E47" s="13" t="s">
-        <v>202</v>
-      </c>
-      <c r="F47" s="13"/>
-      <c r="G47" s="13"/>
-      <c r="H47" s="13"/>
-      <c r="I47" s="13"/>
-      <c r="J47" s="13"/>
-      <c r="K47" s="13"/>
-      <c r="L47" s="13"/>
-      <c r="M47" s="13"/>
-      <c r="N47" s="13"/>
-      <c r="O47" s="13"/>
-      <c r="P47" s="13"/>
-      <c r="Q47" s="13"/>
-      <c r="R47" s="13"/>
-      <c r="T47" s="13" t="s">
-        <v>231</v>
-      </c>
-      <c r="U47" s="13"/>
-      <c r="V47" s="13"/>
-      <c r="W47" s="13"/>
-      <c r="X47" s="13"/>
-      <c r="Y47" s="13"/>
-      <c r="Z47" s="13"/>
-      <c r="AA47" s="13"/>
-      <c r="AB47" s="13"/>
-      <c r="AC47" s="13"/>
-      <c r="AD47" s="13"/>
-      <c r="AE47" s="13"/>
-      <c r="AF47" s="13"/>
-      <c r="AG47" s="13"/>
-      <c r="AW47" s="18" t="s">
-        <v>213</v>
-      </c>
-      <c r="AX47" s="19"/>
-      <c r="AY47" s="19"/>
-      <c r="AZ47" s="20"/>
-      <c r="BA47" s="18" t="s">
-        <v>214</v>
-      </c>
-      <c r="BB47" s="19"/>
-      <c r="BC47" s="19"/>
-      <c r="BD47" s="19"/>
-      <c r="BE47" s="19"/>
-      <c r="BF47" s="19"/>
-      <c r="BG47" s="19"/>
-      <c r="BH47" s="20"/>
-      <c r="BI47" s="18" t="s">
-        <v>215</v>
-      </c>
-      <c r="BJ47" s="19"/>
-      <c r="BK47" s="19"/>
-      <c r="BL47" s="19"/>
-      <c r="BM47" s="19"/>
-      <c r="BN47" s="19"/>
-      <c r="BO47" s="19"/>
-      <c r="BP47" s="19"/>
-      <c r="BQ47" s="20"/>
-      <c r="BR47" s="31"/>
-    </row>
-    <row r="48" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B48" s="31"/>
-      <c r="E48" s="13"/>
-      <c r="F48" s="13"/>
-      <c r="G48" s="13"/>
-      <c r="H48" s="13"/>
-      <c r="I48" s="13"/>
-      <c r="J48" s="13"/>
-      <c r="K48" s="13"/>
-      <c r="L48" s="13"/>
-      <c r="M48" s="13"/>
-      <c r="N48" s="13"/>
-      <c r="O48" s="13"/>
-      <c r="P48" s="13"/>
-      <c r="Q48" s="13"/>
-      <c r="R48" s="13"/>
-      <c r="T48" s="13"/>
-      <c r="U48" s="13"/>
-      <c r="V48" s="13"/>
-      <c r="W48" s="13"/>
-      <c r="X48" s="13"/>
-      <c r="Y48" s="13"/>
-      <c r="Z48" s="13"/>
-      <c r="AA48" s="13"/>
-      <c r="AB48" s="13"/>
-      <c r="AC48" s="13"/>
-      <c r="AD48" s="13"/>
-      <c r="AE48" s="13"/>
-      <c r="AF48" s="13"/>
-      <c r="AG48" s="13"/>
-      <c r="AW48" s="21" t="s">
-        <v>216</v>
-      </c>
-      <c r="AX48" s="14"/>
-      <c r="AY48" s="14"/>
-      <c r="AZ48" s="14"/>
-      <c r="BA48" s="14"/>
-      <c r="BB48" s="14"/>
-      <c r="BC48" s="14"/>
-      <c r="BD48" s="15"/>
-      <c r="BE48" s="21" t="s">
-        <v>217</v>
-      </c>
-      <c r="BF48" s="14"/>
-      <c r="BG48" s="14"/>
-      <c r="BH48" s="14"/>
-      <c r="BI48" s="14"/>
-      <c r="BJ48" s="14"/>
-      <c r="BK48" s="14"/>
-      <c r="BL48" s="14"/>
-      <c r="BM48" s="14"/>
-      <c r="BN48" s="14"/>
-      <c r="BO48" s="14"/>
-      <c r="BP48" s="14"/>
-      <c r="BQ48" s="15"/>
-      <c r="BR48" s="31"/>
+      <c r="BF48" s="20"/>
+      <c r="BG48" s="20"/>
+      <c r="BH48" s="20"/>
+      <c r="BI48" s="20"/>
+      <c r="BJ48" s="20"/>
+      <c r="BK48" s="20"/>
+      <c r="BL48" s="20"/>
+      <c r="BM48" s="20"/>
+      <c r="BN48" s="20"/>
+      <c r="BO48" s="20"/>
+      <c r="BP48" s="20"/>
+      <c r="BQ48" s="21"/>
+      <c r="BR48" s="17"/>
     </row>
     <row r="49" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B49" s="31"/>
-      <c r="E49" s="13"/>
-      <c r="F49" s="13"/>
-      <c r="G49" s="13"/>
-      <c r="H49" s="13"/>
-      <c r="I49" s="13"/>
-      <c r="J49" s="13"/>
-      <c r="K49" s="13"/>
-      <c r="L49" s="13"/>
-      <c r="M49" s="13"/>
-      <c r="N49" s="13"/>
-      <c r="O49" s="13"/>
-      <c r="P49" s="13"/>
-      <c r="Q49" s="13"/>
-      <c r="R49" s="13"/>
-      <c r="T49" s="13"/>
-      <c r="U49" s="13"/>
-      <c r="V49" s="13"/>
-      <c r="W49" s="13"/>
-      <c r="X49" s="13"/>
-      <c r="Y49" s="13"/>
-      <c r="Z49" s="13"/>
-      <c r="AA49" s="13"/>
-      <c r="AB49" s="13"/>
-      <c r="AC49" s="13"/>
-      <c r="AD49" s="13"/>
-      <c r="AE49" s="13"/>
-      <c r="AF49" s="13"/>
-      <c r="AG49" s="13"/>
+      <c r="B49" s="17"/>
+      <c r="E49" s="3"/>
+      <c r="F49" s="3"/>
+      <c r="G49" s="3"/>
+      <c r="H49" s="3"/>
+      <c r="I49" s="3"/>
+      <c r="J49" s="3"/>
+      <c r="K49" s="3"/>
+      <c r="L49" s="3"/>
+      <c r="M49" s="3"/>
+      <c r="N49" s="3"/>
+      <c r="O49" s="3"/>
+      <c r="P49" s="3"/>
+      <c r="Q49" s="3"/>
+      <c r="R49" s="3"/>
+      <c r="T49" s="35"/>
+      <c r="U49" s="35"/>
+      <c r="V49" s="35"/>
+      <c r="W49" s="35"/>
+      <c r="X49" s="35"/>
+      <c r="Y49" s="35"/>
+      <c r="Z49" s="35"/>
+      <c r="AA49" s="35"/>
+      <c r="AB49" s="35"/>
+      <c r="AC49" s="35"/>
+      <c r="AD49" s="35"/>
+      <c r="AE49" s="35"/>
+      <c r="AF49" s="35"/>
+      <c r="AG49" s="35"/>
       <c r="AW49" s="25"/>
-      <c r="AX49" s="16"/>
-      <c r="AY49" s="16"/>
-      <c r="AZ49" s="16"/>
-      <c r="BA49" s="16"/>
-      <c r="BB49" s="16"/>
-      <c r="BC49" s="16"/>
-      <c r="BD49" s="17"/>
+      <c r="AX49" s="26"/>
+      <c r="AY49" s="26"/>
+      <c r="AZ49" s="26"/>
+      <c r="BA49" s="26"/>
+      <c r="BB49" s="26"/>
+      <c r="BC49" s="26"/>
+      <c r="BD49" s="27"/>
       <c r="BE49" s="22"/>
       <c r="BF49" s="23"/>
       <c r="BG49" s="23"/>
@@ -3674,93 +3649,93 @@
       <c r="BO49" s="23"/>
       <c r="BP49" s="23"/>
       <c r="BQ49" s="24"/>
-      <c r="BR49" s="31"/>
+      <c r="BR49" s="17"/>
     </row>
     <row r="50" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B50" s="31"/>
-      <c r="E50" s="13"/>
-      <c r="F50" s="13"/>
-      <c r="G50" s="13"/>
-      <c r="H50" s="13"/>
-      <c r="I50" s="13"/>
-      <c r="J50" s="13"/>
-      <c r="K50" s="13"/>
-      <c r="L50" s="13"/>
-      <c r="M50" s="13"/>
-      <c r="N50" s="13"/>
-      <c r="O50" s="13"/>
-      <c r="P50" s="13"/>
-      <c r="Q50" s="13"/>
-      <c r="R50" s="13"/>
-      <c r="T50" s="13"/>
-      <c r="U50" s="13"/>
-      <c r="V50" s="13"/>
-      <c r="W50" s="13"/>
-      <c r="X50" s="13"/>
-      <c r="Y50" s="13"/>
-      <c r="Z50" s="13"/>
-      <c r="AA50" s="13"/>
-      <c r="AB50" s="13"/>
-      <c r="AC50" s="13"/>
-      <c r="AD50" s="13"/>
-      <c r="AE50" s="13"/>
-      <c r="AF50" s="13"/>
-      <c r="AG50" s="13"/>
+      <c r="B50" s="17"/>
+      <c r="E50" s="3"/>
+      <c r="F50" s="3"/>
+      <c r="G50" s="3"/>
+      <c r="H50" s="3"/>
+      <c r="I50" s="3"/>
+      <c r="J50" s="3"/>
+      <c r="K50" s="3"/>
+      <c r="L50" s="3"/>
+      <c r="M50" s="3"/>
+      <c r="N50" s="3"/>
+      <c r="O50" s="3"/>
+      <c r="P50" s="3"/>
+      <c r="Q50" s="3"/>
+      <c r="R50" s="3"/>
+      <c r="T50" s="35"/>
+      <c r="U50" s="35"/>
+      <c r="V50" s="35"/>
+      <c r="W50" s="35"/>
+      <c r="X50" s="35"/>
+      <c r="Y50" s="35"/>
+      <c r="Z50" s="35"/>
+      <c r="AA50" s="35"/>
+      <c r="AB50" s="35"/>
+      <c r="AC50" s="35"/>
+      <c r="AD50" s="35"/>
+      <c r="AE50" s="35"/>
+      <c r="AF50" s="35"/>
+      <c r="AG50" s="35"/>
       <c r="AW50" s="25"/>
-      <c r="AX50" s="16"/>
-      <c r="AY50" s="16"/>
-      <c r="AZ50" s="16"/>
-      <c r="BA50" s="16"/>
-      <c r="BB50" s="16"/>
-      <c r="BC50" s="16"/>
-      <c r="BD50" s="17"/>
-      <c r="BE50" s="21" t="s">
-        <v>218</v>
-      </c>
-      <c r="BF50" s="14"/>
-      <c r="BG50" s="14"/>
-      <c r="BH50" s="14"/>
-      <c r="BI50" s="14"/>
-      <c r="BJ50" s="14"/>
-      <c r="BK50" s="14"/>
-      <c r="BL50" s="14"/>
-      <c r="BM50" s="14"/>
-      <c r="BN50" s="14"/>
-      <c r="BO50" s="14"/>
-      <c r="BP50" s="14"/>
-      <c r="BQ50" s="15"/>
-      <c r="BR50" s="31"/>
+      <c r="AX50" s="26"/>
+      <c r="AY50" s="26"/>
+      <c r="AZ50" s="26"/>
+      <c r="BA50" s="26"/>
+      <c r="BB50" s="26"/>
+      <c r="BC50" s="26"/>
+      <c r="BD50" s="27"/>
+      <c r="BE50" s="19" t="s">
+        <v>213</v>
+      </c>
+      <c r="BF50" s="20"/>
+      <c r="BG50" s="20"/>
+      <c r="BH50" s="20"/>
+      <c r="BI50" s="20"/>
+      <c r="BJ50" s="20"/>
+      <c r="BK50" s="20"/>
+      <c r="BL50" s="20"/>
+      <c r="BM50" s="20"/>
+      <c r="BN50" s="20"/>
+      <c r="BO50" s="20"/>
+      <c r="BP50" s="20"/>
+      <c r="BQ50" s="21"/>
+      <c r="BR50" s="17"/>
     </row>
     <row r="51" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B51" s="31"/>
-      <c r="E51" s="13"/>
-      <c r="F51" s="13"/>
-      <c r="G51" s="13"/>
-      <c r="H51" s="13"/>
-      <c r="I51" s="13"/>
-      <c r="J51" s="13"/>
-      <c r="K51" s="13"/>
-      <c r="L51" s="13"/>
-      <c r="M51" s="13"/>
-      <c r="N51" s="13"/>
-      <c r="O51" s="13"/>
-      <c r="P51" s="13"/>
-      <c r="Q51" s="13"/>
-      <c r="R51" s="13"/>
-      <c r="T51" s="13"/>
-      <c r="U51" s="13"/>
-      <c r="V51" s="13"/>
-      <c r="W51" s="13"/>
-      <c r="X51" s="13"/>
-      <c r="Y51" s="13"/>
-      <c r="Z51" s="13"/>
-      <c r="AA51" s="13"/>
-      <c r="AB51" s="13"/>
-      <c r="AC51" s="13"/>
-      <c r="AD51" s="13"/>
-      <c r="AE51" s="13"/>
-      <c r="AF51" s="13"/>
-      <c r="AG51" s="13"/>
+      <c r="B51" s="17"/>
+      <c r="E51" s="3"/>
+      <c r="F51" s="3"/>
+      <c r="G51" s="3"/>
+      <c r="H51" s="3"/>
+      <c r="I51" s="3"/>
+      <c r="J51" s="3"/>
+      <c r="K51" s="3"/>
+      <c r="L51" s="3"/>
+      <c r="M51" s="3"/>
+      <c r="N51" s="3"/>
+      <c r="O51" s="3"/>
+      <c r="P51" s="3"/>
+      <c r="Q51" s="3"/>
+      <c r="R51" s="3"/>
+      <c r="T51" s="35"/>
+      <c r="U51" s="35"/>
+      <c r="V51" s="35"/>
+      <c r="W51" s="35"/>
+      <c r="X51" s="35"/>
+      <c r="Y51" s="35"/>
+      <c r="Z51" s="35"/>
+      <c r="AA51" s="35"/>
+      <c r="AB51" s="35"/>
+      <c r="AC51" s="35"/>
+      <c r="AD51" s="35"/>
+      <c r="AE51" s="35"/>
+      <c r="AF51" s="35"/>
+      <c r="AG51" s="35"/>
       <c r="AW51" s="22"/>
       <c r="AX51" s="23"/>
       <c r="AY51" s="23"/>
@@ -3782,91 +3757,91 @@
       <c r="BO51" s="23"/>
       <c r="BP51" s="23"/>
       <c r="BQ51" s="24"/>
-      <c r="BR51" s="31"/>
+      <c r="BR51" s="17"/>
     </row>
     <row r="52" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B52" s="31"/>
-      <c r="AW52" s="21" t="s">
-        <v>219</v>
-      </c>
-      <c r="AX52" s="14"/>
-      <c r="AY52" s="14"/>
-      <c r="AZ52" s="14"/>
-      <c r="BA52" s="14"/>
-      <c r="BB52" s="14"/>
-      <c r="BC52" s="14"/>
-      <c r="BD52" s="15"/>
-      <c r="BE52" s="21" t="s">
-        <v>220</v>
-      </c>
-      <c r="BF52" s="14"/>
-      <c r="BG52" s="14"/>
-      <c r="BH52" s="14"/>
-      <c r="BI52" s="14"/>
-      <c r="BJ52" s="14"/>
-      <c r="BK52" s="14"/>
-      <c r="BL52" s="14"/>
-      <c r="BM52" s="14"/>
-      <c r="BN52" s="14"/>
-      <c r="BO52" s="14"/>
-      <c r="BP52" s="14"/>
-      <c r="BQ52" s="15"/>
-      <c r="BR52" s="31"/>
+      <c r="B52" s="17"/>
+      <c r="AW52" s="19" t="s">
+        <v>214</v>
+      </c>
+      <c r="AX52" s="20"/>
+      <c r="AY52" s="20"/>
+      <c r="AZ52" s="20"/>
+      <c r="BA52" s="20"/>
+      <c r="BB52" s="20"/>
+      <c r="BC52" s="20"/>
+      <c r="BD52" s="21"/>
+      <c r="BE52" s="19" t="s">
+        <v>215</v>
+      </c>
+      <c r="BF52" s="20"/>
+      <c r="BG52" s="20"/>
+      <c r="BH52" s="20"/>
+      <c r="BI52" s="20"/>
+      <c r="BJ52" s="20"/>
+      <c r="BK52" s="20"/>
+      <c r="BL52" s="20"/>
+      <c r="BM52" s="20"/>
+      <c r="BN52" s="20"/>
+      <c r="BO52" s="20"/>
+      <c r="BP52" s="20"/>
+      <c r="BQ52" s="21"/>
+      <c r="BR52" s="17"/>
     </row>
     <row r="53" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B53" s="31"/>
+      <c r="B53" s="17"/>
       <c r="AW53" s="25" t="s">
-        <v>221</v>
-      </c>
-      <c r="AX53" s="16"/>
-      <c r="AY53" s="16"/>
-      <c r="AZ53" s="16"/>
-      <c r="BA53" s="16"/>
-      <c r="BB53" s="16"/>
-      <c r="BC53" s="16"/>
-      <c r="BD53" s="17"/>
+        <v>216</v>
+      </c>
+      <c r="AX53" s="26"/>
+      <c r="AY53" s="26"/>
+      <c r="AZ53" s="26"/>
+      <c r="BA53" s="26"/>
+      <c r="BB53" s="26"/>
+      <c r="BC53" s="26"/>
+      <c r="BD53" s="27"/>
       <c r="BE53" s="25"/>
-      <c r="BF53" s="16"/>
-      <c r="BG53" s="16"/>
-      <c r="BH53" s="16"/>
-      <c r="BI53" s="16"/>
-      <c r="BJ53" s="16"/>
-      <c r="BK53" s="16"/>
-      <c r="BL53" s="16"/>
-      <c r="BM53" s="16"/>
-      <c r="BN53" s="16"/>
-      <c r="BO53" s="16"/>
-      <c r="BP53" s="16"/>
-      <c r="BQ53" s="17"/>
-      <c r="BR53" s="31"/>
+      <c r="BF53" s="26"/>
+      <c r="BG53" s="26"/>
+      <c r="BH53" s="26"/>
+      <c r="BI53" s="26"/>
+      <c r="BJ53" s="26"/>
+      <c r="BK53" s="26"/>
+      <c r="BL53" s="26"/>
+      <c r="BM53" s="26"/>
+      <c r="BN53" s="26"/>
+      <c r="BO53" s="26"/>
+      <c r="BP53" s="26"/>
+      <c r="BQ53" s="27"/>
+      <c r="BR53" s="17"/>
     </row>
     <row r="54" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B54" s="31"/>
+      <c r="B54" s="17"/>
       <c r="AW54" s="25"/>
-      <c r="AX54" s="16"/>
-      <c r="AY54" s="16"/>
-      <c r="AZ54" s="16"/>
-      <c r="BA54" s="16"/>
-      <c r="BB54" s="16"/>
-      <c r="BC54" s="16"/>
-      <c r="BD54" s="17"/>
+      <c r="AX54" s="26"/>
+      <c r="AY54" s="26"/>
+      <c r="AZ54" s="26"/>
+      <c r="BA54" s="26"/>
+      <c r="BB54" s="26"/>
+      <c r="BC54" s="26"/>
+      <c r="BD54" s="27"/>
       <c r="BE54" s="25"/>
-      <c r="BF54" s="16"/>
-      <c r="BG54" s="16"/>
-      <c r="BH54" s="16"/>
-      <c r="BI54" s="16"/>
-      <c r="BJ54" s="16"/>
-      <c r="BK54" s="16"/>
-      <c r="BL54" s="16"/>
-      <c r="BM54" s="16"/>
-      <c r="BN54" s="16"/>
-      <c r="BO54" s="16"/>
-      <c r="BP54" s="16"/>
-      <c r="BQ54" s="17"/>
-      <c r="BR54" s="31"/>
+      <c r="BF54" s="26"/>
+      <c r="BG54" s="26"/>
+      <c r="BH54" s="26"/>
+      <c r="BI54" s="26"/>
+      <c r="BJ54" s="26"/>
+      <c r="BK54" s="26"/>
+      <c r="BL54" s="26"/>
+      <c r="BM54" s="26"/>
+      <c r="BN54" s="26"/>
+      <c r="BO54" s="26"/>
+      <c r="BP54" s="26"/>
+      <c r="BQ54" s="27"/>
+      <c r="BR54" s="17"/>
     </row>
     <row r="55" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B55" s="31"/>
+      <c r="B55" s="17"/>
       <c r="AW55" s="22"/>
       <c r="AX55" s="23"/>
       <c r="AY55" s="23"/>
@@ -3888,123 +3863,283 @@
       <c r="BO55" s="23"/>
       <c r="BP55" s="23"/>
       <c r="BQ55" s="24"/>
-      <c r="BR55" s="31"/>
+      <c r="BR55" s="17"/>
     </row>
     <row r="56" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B56" s="27"/>
+      <c r="B56" s="18"/>
       <c r="K56" s="3"/>
       <c r="AI56" s="3"/>
-      <c r="AW56" s="18" t="s">
-        <v>222</v>
-      </c>
-      <c r="AX56" s="19"/>
-      <c r="AY56" s="19" t="s">
-        <v>223</v>
-      </c>
-      <c r="AZ56" s="19"/>
-      <c r="BA56" s="19"/>
-      <c r="BB56" s="19"/>
-      <c r="BC56" s="19"/>
-      <c r="BD56" s="19"/>
-      <c r="BE56" s="19"/>
-      <c r="BF56" s="19"/>
-      <c r="BG56" s="19"/>
-      <c r="BH56" s="19"/>
-      <c r="BI56" s="19"/>
-      <c r="BJ56" s="19"/>
-      <c r="BK56" s="19"/>
-      <c r="BL56" s="19"/>
-      <c r="BM56" s="19"/>
-      <c r="BN56" s="19"/>
-      <c r="BO56" s="19"/>
-      <c r="BP56" s="19"/>
-      <c r="BQ56" s="20"/>
-      <c r="BR56" s="27"/>
+      <c r="AW56" s="13" t="s">
+        <v>217</v>
+      </c>
+      <c r="AX56" s="14"/>
+      <c r="AY56" s="14" t="s">
+        <v>218</v>
+      </c>
+      <c r="AZ56" s="14"/>
+      <c r="BA56" s="14"/>
+      <c r="BB56" s="14"/>
+      <c r="BC56" s="14"/>
+      <c r="BD56" s="14"/>
+      <c r="BE56" s="14"/>
+      <c r="BF56" s="14"/>
+      <c r="BG56" s="14"/>
+      <c r="BH56" s="14"/>
+      <c r="BI56" s="14"/>
+      <c r="BJ56" s="14"/>
+      <c r="BK56" s="14"/>
+      <c r="BL56" s="14"/>
+      <c r="BM56" s="14"/>
+      <c r="BN56" s="14"/>
+      <c r="BO56" s="14"/>
+      <c r="BP56" s="14"/>
+      <c r="BQ56" s="15"/>
+      <c r="BR56" s="18"/>
     </row>
     <row r="57" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="C57" s="18">
+      <c r="C57" s="13">
         <v>1</v>
       </c>
-      <c r="D57" s="19"/>
-      <c r="E57" s="19"/>
-      <c r="F57" s="19"/>
-      <c r="G57" s="19"/>
-      <c r="H57" s="19"/>
-      <c r="I57" s="19"/>
-      <c r="J57" s="19"/>
-      <c r="K57" s="19"/>
-      <c r="L57" s="20"/>
-      <c r="M57" s="18">
+      <c r="D57" s="14"/>
+      <c r="E57" s="14"/>
+      <c r="F57" s="14"/>
+      <c r="G57" s="14"/>
+      <c r="H57" s="14"/>
+      <c r="I57" s="14"/>
+      <c r="J57" s="14"/>
+      <c r="K57" s="14"/>
+      <c r="L57" s="15"/>
+      <c r="M57" s="13">
         <v>2</v>
       </c>
-      <c r="N57" s="19"/>
-      <c r="O57" s="19"/>
-      <c r="P57" s="19"/>
-      <c r="Q57" s="19"/>
-      <c r="R57" s="19"/>
-      <c r="S57" s="19"/>
-      <c r="T57" s="19"/>
-      <c r="U57" s="19"/>
-      <c r="V57" s="19"/>
-      <c r="W57" s="19"/>
-      <c r="X57" s="20"/>
-      <c r="Y57" s="18">
+      <c r="N57" s="14"/>
+      <c r="O57" s="14"/>
+      <c r="P57" s="14"/>
+      <c r="Q57" s="14"/>
+      <c r="R57" s="14"/>
+      <c r="S57" s="14"/>
+      <c r="T57" s="14"/>
+      <c r="U57" s="14"/>
+      <c r="V57" s="14"/>
+      <c r="W57" s="14"/>
+      <c r="X57" s="15"/>
+      <c r="Y57" s="13">
         <v>3</v>
       </c>
-      <c r="Z57" s="19"/>
-      <c r="AA57" s="19"/>
-      <c r="AB57" s="19"/>
-      <c r="AC57" s="19"/>
-      <c r="AD57" s="19"/>
-      <c r="AE57" s="19"/>
-      <c r="AF57" s="19"/>
-      <c r="AG57" s="19"/>
-      <c r="AH57" s="19"/>
-      <c r="AI57" s="20"/>
-      <c r="AJ57" s="18">
+      <c r="Z57" s="14"/>
+      <c r="AA57" s="14"/>
+      <c r="AB57" s="14"/>
+      <c r="AC57" s="14"/>
+      <c r="AD57" s="14"/>
+      <c r="AE57" s="14"/>
+      <c r="AF57" s="14"/>
+      <c r="AG57" s="14"/>
+      <c r="AH57" s="14"/>
+      <c r="AI57" s="15"/>
+      <c r="AJ57" s="13">
         <v>4</v>
       </c>
-      <c r="AK57" s="19"/>
-      <c r="AL57" s="19"/>
-      <c r="AM57" s="19"/>
-      <c r="AN57" s="19"/>
-      <c r="AO57" s="19"/>
-      <c r="AP57" s="19"/>
-      <c r="AQ57" s="19"/>
-      <c r="AR57" s="19"/>
-      <c r="AS57" s="19"/>
-      <c r="AT57" s="20"/>
-      <c r="AU57" s="18">
+      <c r="AK57" s="14"/>
+      <c r="AL57" s="14"/>
+      <c r="AM57" s="14"/>
+      <c r="AN57" s="14"/>
+      <c r="AO57" s="14"/>
+      <c r="AP57" s="14"/>
+      <c r="AQ57" s="14"/>
+      <c r="AR57" s="14"/>
+      <c r="AS57" s="14"/>
+      <c r="AT57" s="15"/>
+      <c r="AU57" s="13">
         <v>5</v>
       </c>
-      <c r="AV57" s="19"/>
-      <c r="AW57" s="19"/>
-      <c r="AX57" s="19"/>
-      <c r="AY57" s="19"/>
-      <c r="AZ57" s="19"/>
-      <c r="BA57" s="19"/>
-      <c r="BB57" s="19"/>
-      <c r="BC57" s="19"/>
-      <c r="BD57" s="19"/>
-      <c r="BE57" s="19"/>
-      <c r="BF57" s="20"/>
-      <c r="BG57" s="18">
+      <c r="AV57" s="14"/>
+      <c r="AW57" s="14"/>
+      <c r="AX57" s="14"/>
+      <c r="AY57" s="14"/>
+      <c r="AZ57" s="14"/>
+      <c r="BA57" s="14"/>
+      <c r="BB57" s="14"/>
+      <c r="BC57" s="14"/>
+      <c r="BD57" s="14"/>
+      <c r="BE57" s="14"/>
+      <c r="BF57" s="15"/>
+      <c r="BG57" s="13">
         <v>6</v>
       </c>
-      <c r="BH57" s="19"/>
-      <c r="BI57" s="19"/>
-      <c r="BJ57" s="19"/>
-      <c r="BK57" s="19"/>
-      <c r="BL57" s="19"/>
-      <c r="BM57" s="19"/>
-      <c r="BN57" s="19"/>
-      <c r="BO57" s="19"/>
-      <c r="BP57" s="19"/>
-      <c r="BQ57" s="20"/>
+      <c r="BH57" s="14"/>
+      <c r="BI57" s="14"/>
+      <c r="BJ57" s="14"/>
+      <c r="BK57" s="14"/>
+      <c r="BL57" s="14"/>
+      <c r="BM57" s="14"/>
+      <c r="BN57" s="14"/>
+      <c r="BO57" s="14"/>
+      <c r="BP57" s="14"/>
+      <c r="BQ57" s="15"/>
     </row>
     <row r="58" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4"/>
   </sheetData>
-  <mergeCells count="189">
+  <mergeCells count="184">
+    <mergeCell ref="T47:AG51"/>
+    <mergeCell ref="M2:X2"/>
+    <mergeCell ref="AU2:BF2"/>
+    <mergeCell ref="AW18:AX18"/>
+    <mergeCell ref="BC8:BE8"/>
+    <mergeCell ref="BI43:BK44"/>
+    <mergeCell ref="AU57:BF57"/>
+    <mergeCell ref="AW9:AX9"/>
+    <mergeCell ref="BC22:BE22"/>
+    <mergeCell ref="BA47:BH47"/>
+    <mergeCell ref="BG2:BQ2"/>
+    <mergeCell ref="AJ2:AT2"/>
+    <mergeCell ref="AY56:BQ56"/>
+    <mergeCell ref="Y2:AI2"/>
+    <mergeCell ref="BF9:BK9"/>
+    <mergeCell ref="AY8:BB8"/>
+    <mergeCell ref="AW17:AX17"/>
+    <mergeCell ref="BO43:BQ44"/>
+    <mergeCell ref="BG57:BQ57"/>
+    <mergeCell ref="BC7:BE7"/>
+    <mergeCell ref="BC15:BE15"/>
+    <mergeCell ref="BA40:BH40"/>
+    <mergeCell ref="AW19:AX19"/>
+    <mergeCell ref="AW53:BD55"/>
+    <mergeCell ref="T7:AG11"/>
+    <mergeCell ref="B17:B29"/>
+    <mergeCell ref="AW7:AX7"/>
+    <mergeCell ref="B44:B56"/>
+    <mergeCell ref="BL41:BN41"/>
+    <mergeCell ref="AW3:BQ4"/>
+    <mergeCell ref="BI46:BQ46"/>
+    <mergeCell ref="BM23:BO23"/>
+    <mergeCell ref="BF15:BK15"/>
+    <mergeCell ref="BL5:BL6"/>
+    <mergeCell ref="AY14:BB14"/>
+    <mergeCell ref="AY25:BB25"/>
+    <mergeCell ref="AY31:BQ36"/>
+    <mergeCell ref="AY12:BB12"/>
+    <mergeCell ref="BC14:BE14"/>
+    <mergeCell ref="BM22:BO22"/>
+    <mergeCell ref="AW14:AX14"/>
+    <mergeCell ref="AY7:BB7"/>
+    <mergeCell ref="BC10:BE10"/>
+    <mergeCell ref="BM17:BO17"/>
+    <mergeCell ref="BC23:BE23"/>
+    <mergeCell ref="BF18:BK18"/>
+    <mergeCell ref="AW12:AX12"/>
+    <mergeCell ref="BM14:BO14"/>
+    <mergeCell ref="BA42:BH42"/>
+    <mergeCell ref="AY19:BB19"/>
+    <mergeCell ref="AY13:BB13"/>
+    <mergeCell ref="AX40:AZ40"/>
+    <mergeCell ref="AY22:BB22"/>
+    <mergeCell ref="BA43:BH44"/>
+    <mergeCell ref="BL40:BN40"/>
+    <mergeCell ref="BC12:BE12"/>
+    <mergeCell ref="BL43:BN44"/>
+    <mergeCell ref="C3:D5"/>
+    <mergeCell ref="BM5:BO6"/>
+    <mergeCell ref="AW5:AX6"/>
+    <mergeCell ref="AT3:AV8"/>
+    <mergeCell ref="T17:AG20"/>
+    <mergeCell ref="T26:AG29"/>
+    <mergeCell ref="T35:AG39"/>
+    <mergeCell ref="BE52:BQ55"/>
+    <mergeCell ref="AX42:AZ42"/>
+    <mergeCell ref="AW43:AW44"/>
+    <mergeCell ref="BR30:BR43"/>
+    <mergeCell ref="BM8:BO8"/>
+    <mergeCell ref="AX39:AZ39"/>
+    <mergeCell ref="BM16:BO16"/>
+    <mergeCell ref="BA46:BH46"/>
+    <mergeCell ref="BA39:BH39"/>
+    <mergeCell ref="BM10:BO10"/>
+    <mergeCell ref="AW31:AX36"/>
+    <mergeCell ref="BE48:BQ49"/>
+    <mergeCell ref="BL42:BN42"/>
+    <mergeCell ref="AY23:BB23"/>
+    <mergeCell ref="AX45:AZ45"/>
+    <mergeCell ref="BI42:BK42"/>
+    <mergeCell ref="BF21:BK21"/>
+    <mergeCell ref="BO45:BQ45"/>
+    <mergeCell ref="BR44:BR56"/>
+    <mergeCell ref="AY9:BB9"/>
+    <mergeCell ref="AW25:AX25"/>
+    <mergeCell ref="AW15:AX15"/>
+    <mergeCell ref="BC9:BE9"/>
+    <mergeCell ref="AY18:BB18"/>
+    <mergeCell ref="AY5:BB6"/>
+    <mergeCell ref="AW49:BD51"/>
+    <mergeCell ref="BI45:BK45"/>
+    <mergeCell ref="BC16:BE16"/>
+    <mergeCell ref="BF20:BK20"/>
+    <mergeCell ref="AW20:AX20"/>
+    <mergeCell ref="B30:B43"/>
+    <mergeCell ref="AW47:AZ47"/>
+    <mergeCell ref="BF10:BK10"/>
+    <mergeCell ref="AW10:AX10"/>
+    <mergeCell ref="BF17:BK17"/>
+    <mergeCell ref="AW23:AX23"/>
+    <mergeCell ref="BC18:BE18"/>
+    <mergeCell ref="AW48:BD48"/>
+    <mergeCell ref="BI41:BK41"/>
+    <mergeCell ref="B3:B16"/>
+    <mergeCell ref="BI47:BQ47"/>
+    <mergeCell ref="AW21:AX21"/>
+    <mergeCell ref="BC19:BE19"/>
+    <mergeCell ref="AX41:AZ41"/>
+    <mergeCell ref="BM24:BO24"/>
+    <mergeCell ref="BI39:BK39"/>
+    <mergeCell ref="BC21:BE21"/>
+    <mergeCell ref="AX43:AZ44"/>
+    <mergeCell ref="AY20:BB20"/>
+    <mergeCell ref="AW52:BD52"/>
+    <mergeCell ref="AW16:AX16"/>
+    <mergeCell ref="BF5:BK6"/>
+    <mergeCell ref="BC17:BE17"/>
+    <mergeCell ref="AY24:BB24"/>
+    <mergeCell ref="BC5:BE6"/>
+    <mergeCell ref="BO42:BQ42"/>
+    <mergeCell ref="BP5:BP6"/>
+    <mergeCell ref="BO40:BQ40"/>
+    <mergeCell ref="BQ5:BQ6"/>
+    <mergeCell ref="BM21:BO21"/>
+    <mergeCell ref="BF13:BK13"/>
+    <mergeCell ref="AW13:AX13"/>
+    <mergeCell ref="BA45:BH45"/>
+    <mergeCell ref="AW8:AX8"/>
+    <mergeCell ref="BL45:BN45"/>
+    <mergeCell ref="BF8:BK8"/>
+    <mergeCell ref="BI40:BK40"/>
+    <mergeCell ref="AW46:AZ46"/>
+    <mergeCell ref="BC26:BE26"/>
+    <mergeCell ref="BF26:BK26"/>
+    <mergeCell ref="BM26:BO26"/>
+    <mergeCell ref="BE50:BQ51"/>
+    <mergeCell ref="AY26:BB26"/>
+    <mergeCell ref="BR17:BR29"/>
+    <mergeCell ref="BM9:BO9"/>
+    <mergeCell ref="AY16:BB16"/>
+    <mergeCell ref="BO39:BQ39"/>
+    <mergeCell ref="BM19:BO19"/>
+    <mergeCell ref="BF14:BK14"/>
+    <mergeCell ref="BF23:BK23"/>
+    <mergeCell ref="BM12:BO12"/>
+    <mergeCell ref="BR3:BR16"/>
+    <mergeCell ref="BF25:BK25"/>
+    <mergeCell ref="BF22:BK22"/>
+    <mergeCell ref="BF12:BK12"/>
+    <mergeCell ref="BM20:BO20"/>
+    <mergeCell ref="BF7:BK7"/>
+    <mergeCell ref="AY21:BB21"/>
+    <mergeCell ref="BM18:BO18"/>
+    <mergeCell ref="BF19:BK19"/>
+    <mergeCell ref="BC24:BE24"/>
+    <mergeCell ref="BM7:BO7"/>
+    <mergeCell ref="BM15:BO15"/>
+    <mergeCell ref="BC25:BE25"/>
+    <mergeCell ref="BC13:BE13"/>
+    <mergeCell ref="BM13:BO13"/>
     <mergeCell ref="C57:L57"/>
     <mergeCell ref="M57:X57"/>
     <mergeCell ref="Y57:AI57"/>
@@ -4029,171 +4164,6 @@
     <mergeCell ref="AW22:AX22"/>
     <mergeCell ref="BA41:BH41"/>
     <mergeCell ref="AW26:AX26"/>
-    <mergeCell ref="AY26:BB26"/>
-    <mergeCell ref="BR17:BR29"/>
-    <mergeCell ref="BM9:BO9"/>
-    <mergeCell ref="AY16:BB16"/>
-    <mergeCell ref="BO39:BQ39"/>
-    <mergeCell ref="BM19:BO19"/>
-    <mergeCell ref="BF14:BK14"/>
-    <mergeCell ref="BF23:BK23"/>
-    <mergeCell ref="BM12:BO12"/>
-    <mergeCell ref="BR3:BR16"/>
-    <mergeCell ref="BF25:BK25"/>
-    <mergeCell ref="BF22:BK22"/>
-    <mergeCell ref="BF12:BK12"/>
-    <mergeCell ref="BM20:BO20"/>
-    <mergeCell ref="BF7:BK7"/>
-    <mergeCell ref="AY21:BB21"/>
-    <mergeCell ref="BM18:BO18"/>
-    <mergeCell ref="BF19:BK19"/>
-    <mergeCell ref="BC24:BE24"/>
-    <mergeCell ref="BM7:BO7"/>
-    <mergeCell ref="BM15:BO15"/>
-    <mergeCell ref="BC25:BE25"/>
-    <mergeCell ref="BC13:BE13"/>
-    <mergeCell ref="BM13:BO13"/>
-    <mergeCell ref="AY20:BB20"/>
-    <mergeCell ref="AW52:BD52"/>
-    <mergeCell ref="AW16:AX16"/>
-    <mergeCell ref="BF5:BK6"/>
-    <mergeCell ref="BC17:BE17"/>
-    <mergeCell ref="AY24:BB24"/>
-    <mergeCell ref="BC5:BE6"/>
-    <mergeCell ref="BO42:BQ42"/>
-    <mergeCell ref="BP5:BP6"/>
-    <mergeCell ref="BO40:BQ40"/>
-    <mergeCell ref="BQ5:BQ6"/>
-    <mergeCell ref="BM21:BO21"/>
-    <mergeCell ref="BF13:BK13"/>
-    <mergeCell ref="AW13:AX13"/>
-    <mergeCell ref="BA45:BH45"/>
-    <mergeCell ref="AW8:AX8"/>
-    <mergeCell ref="BL45:BN45"/>
-    <mergeCell ref="BF8:BK8"/>
-    <mergeCell ref="BI40:BK40"/>
-    <mergeCell ref="AW46:AZ46"/>
-    <mergeCell ref="BC26:BE26"/>
-    <mergeCell ref="BF26:BK26"/>
-    <mergeCell ref="BM26:BO26"/>
-    <mergeCell ref="BE50:BQ51"/>
-    <mergeCell ref="AY5:BB6"/>
-    <mergeCell ref="AW49:BD51"/>
-    <mergeCell ref="BI45:BK45"/>
-    <mergeCell ref="BC16:BE16"/>
-    <mergeCell ref="BF20:BK20"/>
-    <mergeCell ref="AW20:AX20"/>
-    <mergeCell ref="B30:B43"/>
-    <mergeCell ref="AW47:AZ47"/>
-    <mergeCell ref="BF10:BK10"/>
-    <mergeCell ref="AW10:AX10"/>
-    <mergeCell ref="BF17:BK17"/>
-    <mergeCell ref="AW23:AX23"/>
-    <mergeCell ref="BC18:BE18"/>
-    <mergeCell ref="AW48:BD48"/>
-    <mergeCell ref="BI41:BK41"/>
-    <mergeCell ref="BE52:BQ55"/>
-    <mergeCell ref="AX42:AZ42"/>
-    <mergeCell ref="AW43:AW44"/>
-    <mergeCell ref="BR30:BR43"/>
-    <mergeCell ref="BM8:BO8"/>
-    <mergeCell ref="AX39:AZ39"/>
-    <mergeCell ref="BM16:BO16"/>
-    <mergeCell ref="BA46:BH46"/>
-    <mergeCell ref="BA39:BH39"/>
-    <mergeCell ref="BM10:BO10"/>
-    <mergeCell ref="AW31:AX36"/>
-    <mergeCell ref="BE48:BQ49"/>
-    <mergeCell ref="BL42:BN42"/>
-    <mergeCell ref="AY23:BB23"/>
-    <mergeCell ref="AX45:AZ45"/>
-    <mergeCell ref="BI42:BK42"/>
-    <mergeCell ref="BF21:BK21"/>
-    <mergeCell ref="BO45:BQ45"/>
-    <mergeCell ref="BR44:BR56"/>
-    <mergeCell ref="AY9:BB9"/>
-    <mergeCell ref="AW25:AX25"/>
-    <mergeCell ref="AW15:AX15"/>
-    <mergeCell ref="B3:B16"/>
-    <mergeCell ref="BC9:BE9"/>
-    <mergeCell ref="AY18:BB18"/>
-    <mergeCell ref="BI47:BQ47"/>
-    <mergeCell ref="AW21:AX21"/>
-    <mergeCell ref="BC19:BE19"/>
-    <mergeCell ref="AX41:AZ41"/>
-    <mergeCell ref="BM24:BO24"/>
-    <mergeCell ref="BI39:BK39"/>
-    <mergeCell ref="BC21:BE21"/>
-    <mergeCell ref="AX43:AZ44"/>
-    <mergeCell ref="AY19:BB19"/>
-    <mergeCell ref="AY13:BB13"/>
-    <mergeCell ref="AX40:AZ40"/>
-    <mergeCell ref="AY22:BB22"/>
-    <mergeCell ref="BA43:BH44"/>
-    <mergeCell ref="BL40:BN40"/>
-    <mergeCell ref="BC12:BE12"/>
-    <mergeCell ref="BL43:BN44"/>
-    <mergeCell ref="C3:D5"/>
-    <mergeCell ref="B17:B29"/>
-    <mergeCell ref="AW7:AX7"/>
-    <mergeCell ref="B44:B56"/>
-    <mergeCell ref="BL41:BN41"/>
-    <mergeCell ref="AW3:BQ4"/>
-    <mergeCell ref="BI46:BQ46"/>
-    <mergeCell ref="BM23:BO23"/>
-    <mergeCell ref="BF15:BK15"/>
-    <mergeCell ref="BL5:BL6"/>
-    <mergeCell ref="AY14:BB14"/>
-    <mergeCell ref="AY25:BB25"/>
-    <mergeCell ref="AY31:BQ36"/>
-    <mergeCell ref="AY12:BB12"/>
-    <mergeCell ref="BC14:BE14"/>
-    <mergeCell ref="BM22:BO22"/>
-    <mergeCell ref="AW14:AX14"/>
-    <mergeCell ref="AY7:BB7"/>
-    <mergeCell ref="BC10:BE10"/>
-    <mergeCell ref="BM17:BO17"/>
-    <mergeCell ref="BC23:BE23"/>
-    <mergeCell ref="BF18:BK18"/>
-    <mergeCell ref="AW12:AX12"/>
-    <mergeCell ref="BM14:BO14"/>
-    <mergeCell ref="BA42:BH42"/>
-    <mergeCell ref="BM5:BO6"/>
-    <mergeCell ref="AW5:AX6"/>
-    <mergeCell ref="AT3:AV8"/>
-    <mergeCell ref="M2:X2"/>
-    <mergeCell ref="AU2:BF2"/>
-    <mergeCell ref="AW18:AX18"/>
-    <mergeCell ref="BC8:BE8"/>
-    <mergeCell ref="BI43:BK44"/>
-    <mergeCell ref="AU57:BF57"/>
-    <mergeCell ref="AW9:AX9"/>
-    <mergeCell ref="BC22:BE22"/>
-    <mergeCell ref="BA47:BH47"/>
-    <mergeCell ref="BG2:BQ2"/>
-    <mergeCell ref="AJ2:AT2"/>
-    <mergeCell ref="AY56:BQ56"/>
-    <mergeCell ref="Y2:AI2"/>
-    <mergeCell ref="BF9:BK9"/>
-    <mergeCell ref="AY8:BB8"/>
-    <mergeCell ref="AW17:AX17"/>
-    <mergeCell ref="BO43:BQ44"/>
-    <mergeCell ref="BG57:BQ57"/>
-    <mergeCell ref="BC7:BE7"/>
-    <mergeCell ref="BC15:BE15"/>
-    <mergeCell ref="BA40:BH40"/>
-    <mergeCell ref="AW19:AX19"/>
-    <mergeCell ref="AW53:BD55"/>
-    <mergeCell ref="T7:AG11"/>
-    <mergeCell ref="T17:AG20"/>
-    <mergeCell ref="T26:AG29"/>
-    <mergeCell ref="T35:AG39"/>
-    <mergeCell ref="T47:AG51"/>
-    <mergeCell ref="E7:R11"/>
-    <mergeCell ref="E17:R20"/>
-    <mergeCell ref="E26:R29"/>
-    <mergeCell ref="E35:R39"/>
-    <mergeCell ref="E47:R51"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/가공도_도면_1.xlsx
+++ b/가공도_도면_1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\duddl\Desktop\Project\a2z\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB449348-C56D-4BBC-A299-DBD3CA25EBF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{660380A4-5322-4233-9727-47280CFCE2E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1920" yWindow="720" windowWidth="20256" windowHeight="11520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -670,9 +670,6 @@
     <t>{Input_3}</t>
   </si>
   <si>
-    <t>{Image}</t>
-  </si>
-  <si>
     <t>TAG NO.</t>
   </si>
   <si>
@@ -723,6 +720,10 @@
   </si>
   <si>
     <t>{Input_199}</t>
+  </si>
+  <si>
+    <t>{Image_3}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -984,9 +985,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -994,6 +992,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1014,15 +1015,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1032,14 +1024,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1052,6 +1044,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1435,98 +1436,98 @@
       <c r="BS1" s="6"/>
     </row>
     <row r="2" spans="1:71" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="C2" s="14">
+      <c r="C2" s="13">
         <v>1</v>
       </c>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
-      <c r="H2" s="15"/>
-      <c r="I2" s="15"/>
-      <c r="J2" s="15"/>
-      <c r="K2" s="15"/>
-      <c r="L2" s="16"/>
-      <c r="M2" s="14">
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="14"/>
+      <c r="J2" s="14"/>
+      <c r="K2" s="14"/>
+      <c r="L2" s="15"/>
+      <c r="M2" s="13">
         <v>2</v>
       </c>
-      <c r="N2" s="15"/>
-      <c r="O2" s="15"/>
-      <c r="P2" s="15"/>
-      <c r="Q2" s="15"/>
-      <c r="R2" s="15"/>
-      <c r="S2" s="15"/>
-      <c r="T2" s="15"/>
-      <c r="U2" s="15"/>
-      <c r="V2" s="15"/>
-      <c r="W2" s="15"/>
-      <c r="X2" s="16"/>
-      <c r="Y2" s="14">
+      <c r="N2" s="14"/>
+      <c r="O2" s="14"/>
+      <c r="P2" s="14"/>
+      <c r="Q2" s="14"/>
+      <c r="R2" s="14"/>
+      <c r="S2" s="14"/>
+      <c r="T2" s="14"/>
+      <c r="U2" s="14"/>
+      <c r="V2" s="14"/>
+      <c r="W2" s="14"/>
+      <c r="X2" s="15"/>
+      <c r="Y2" s="13">
         <v>3</v>
       </c>
-      <c r="Z2" s="15"/>
-      <c r="AA2" s="15"/>
-      <c r="AB2" s="15"/>
-      <c r="AC2" s="15"/>
-      <c r="AD2" s="15"/>
-      <c r="AE2" s="15"/>
-      <c r="AF2" s="15"/>
-      <c r="AG2" s="15"/>
-      <c r="AH2" s="15"/>
-      <c r="AI2" s="16"/>
-      <c r="AJ2" s="14">
+      <c r="Z2" s="14"/>
+      <c r="AA2" s="14"/>
+      <c r="AB2" s="14"/>
+      <c r="AC2" s="14"/>
+      <c r="AD2" s="14"/>
+      <c r="AE2" s="14"/>
+      <c r="AF2" s="14"/>
+      <c r="AG2" s="14"/>
+      <c r="AH2" s="14"/>
+      <c r="AI2" s="15"/>
+      <c r="AJ2" s="13">
         <v>4</v>
       </c>
-      <c r="AK2" s="15"/>
-      <c r="AL2" s="15"/>
-      <c r="AM2" s="15"/>
-      <c r="AN2" s="15"/>
-      <c r="AO2" s="15"/>
-      <c r="AP2" s="15"/>
-      <c r="AQ2" s="15"/>
-      <c r="AR2" s="15"/>
-      <c r="AS2" s="15"/>
-      <c r="AT2" s="16"/>
-      <c r="AU2" s="14">
+      <c r="AK2" s="14"/>
+      <c r="AL2" s="14"/>
+      <c r="AM2" s="14"/>
+      <c r="AN2" s="14"/>
+      <c r="AO2" s="14"/>
+      <c r="AP2" s="14"/>
+      <c r="AQ2" s="14"/>
+      <c r="AR2" s="14"/>
+      <c r="AS2" s="14"/>
+      <c r="AT2" s="15"/>
+      <c r="AU2" s="13">
         <v>5</v>
       </c>
-      <c r="AV2" s="15"/>
-      <c r="AW2" s="15"/>
-      <c r="AX2" s="15"/>
-      <c r="AY2" s="15"/>
-      <c r="AZ2" s="15"/>
-      <c r="BA2" s="15"/>
-      <c r="BB2" s="15"/>
-      <c r="BC2" s="15"/>
-      <c r="BD2" s="15"/>
-      <c r="BE2" s="15"/>
-      <c r="BF2" s="16"/>
-      <c r="BG2" s="14">
+      <c r="AV2" s="14"/>
+      <c r="AW2" s="14"/>
+      <c r="AX2" s="14"/>
+      <c r="AY2" s="14"/>
+      <c r="AZ2" s="14"/>
+      <c r="BA2" s="14"/>
+      <c r="BB2" s="14"/>
+      <c r="BC2" s="14"/>
+      <c r="BD2" s="14"/>
+      <c r="BE2" s="14"/>
+      <c r="BF2" s="15"/>
+      <c r="BG2" s="13">
         <v>6</v>
       </c>
-      <c r="BH2" s="15"/>
-      <c r="BI2" s="15"/>
-      <c r="BJ2" s="15"/>
-      <c r="BK2" s="15"/>
-      <c r="BL2" s="15"/>
-      <c r="BM2" s="15"/>
-      <c r="BN2" s="15"/>
-      <c r="BO2" s="15"/>
-      <c r="BP2" s="15"/>
-      <c r="BQ2" s="16"/>
+      <c r="BH2" s="14"/>
+      <c r="BI2" s="14"/>
+      <c r="BJ2" s="14"/>
+      <c r="BK2" s="14"/>
+      <c r="BL2" s="14"/>
+      <c r="BM2" s="14"/>
+      <c r="BN2" s="14"/>
+      <c r="BO2" s="14"/>
+      <c r="BP2" s="14"/>
+      <c r="BQ2" s="15"/>
       <c r="BR2" s="2"/>
     </row>
     <row r="3" spans="1:71" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B3" s="26" t="s">
+      <c r="B3" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="32" t="s">
-        <v>225</v>
-      </c>
-      <c r="D3" s="33"/>
+      <c r="C3" s="29" t="s">
+        <v>224</v>
+      </c>
+      <c r="D3" s="30"/>
       <c r="Y3" s="3"/>
       <c r="AT3" s="18" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="AU3" s="18"/>
       <c r="AV3" s="19"/>
@@ -1553,19 +1554,19 @@
       <c r="BO3" s="18"/>
       <c r="BP3" s="18"/>
       <c r="BQ3" s="19"/>
-      <c r="BR3" s="26" t="s">
+      <c r="BR3" s="23" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:71" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="27"/>
-      <c r="C4" s="34"/>
-      <c r="D4" s="35"/>
+      <c r="B4" s="24"/>
+      <c r="C4" s="31"/>
+      <c r="D4" s="32"/>
       <c r="E4" s="3"/>
       <c r="AA4" s="3"/>
-      <c r="AT4" s="24"/>
-      <c r="AU4" s="24"/>
-      <c r="AV4" s="25"/>
+      <c r="AT4" s="27"/>
+      <c r="AU4" s="27"/>
+      <c r="AV4" s="28"/>
       <c r="AW4" s="20"/>
       <c r="AX4" s="21"/>
       <c r="AY4" s="21"/>
@@ -1587,17 +1588,17 @@
       <c r="BO4" s="21"/>
       <c r="BP4" s="21"/>
       <c r="BQ4" s="22"/>
-      <c r="BR4" s="27"/>
+      <c r="BR4" s="24"/>
     </row>
     <row r="5" spans="1:71" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B5" s="27"/>
-      <c r="C5" s="34"/>
-      <c r="D5" s="35"/>
-      <c r="AT5" s="24"/>
-      <c r="AU5" s="24"/>
-      <c r="AV5" s="25"/>
+      <c r="B5" s="24"/>
+      <c r="C5" s="31"/>
+      <c r="D5" s="32"/>
+      <c r="AT5" s="27"/>
+      <c r="AU5" s="27"/>
+      <c r="AV5" s="28"/>
       <c r="AW5" s="17" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="AX5" s="19"/>
       <c r="AY5" s="17" t="s">
@@ -1619,7 +1620,7 @@
       <c r="BI5" s="18"/>
       <c r="BJ5" s="18"/>
       <c r="BK5" s="19"/>
-      <c r="BL5" s="26" t="s">
+      <c r="BL5" s="23" t="s">
         <v>7</v>
       </c>
       <c r="BM5" s="17" t="s">
@@ -1627,19 +1628,19 @@
       </c>
       <c r="BN5" s="18"/>
       <c r="BO5" s="19"/>
-      <c r="BP5" s="26" t="s">
+      <c r="BP5" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="BQ5" s="26" t="s">
+      <c r="BQ5" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="BR5" s="27"/>
+      <c r="BR5" s="24"/>
     </row>
     <row r="6" spans="1:71" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B6" s="27"/>
-      <c r="AT6" s="24"/>
-      <c r="AU6" s="24"/>
-      <c r="AV6" s="25"/>
+      <c r="B6" s="24"/>
+      <c r="AT6" s="27"/>
+      <c r="AU6" s="27"/>
+      <c r="AV6" s="28"/>
       <c r="AW6" s="20"/>
       <c r="AX6" s="22"/>
       <c r="AY6" s="20"/>
@@ -1655,1208 +1656,1208 @@
       <c r="BI6" s="21"/>
       <c r="BJ6" s="21"/>
       <c r="BK6" s="22"/>
-      <c r="BL6" s="28"/>
+      <c r="BL6" s="25"/>
       <c r="BM6" s="20"/>
       <c r="BN6" s="21"/>
       <c r="BO6" s="22"/>
-      <c r="BP6" s="28"/>
-      <c r="BQ6" s="28"/>
-      <c r="BR6" s="27"/>
+      <c r="BP6" s="25"/>
+      <c r="BQ6" s="25"/>
+      <c r="BR6" s="24"/>
     </row>
     <row r="7" spans="1:71" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B7" s="27"/>
-      <c r="E7" s="13" t="s">
-        <v>227</v>
-      </c>
-      <c r="F7" s="13"/>
-      <c r="G7" s="13"/>
-      <c r="H7" s="13"/>
-      <c r="I7" s="13"/>
-      <c r="J7" s="13"/>
-      <c r="K7" s="13"/>
-      <c r="L7" s="13"/>
-      <c r="M7" s="13"/>
-      <c r="N7" s="13"/>
-      <c r="O7" s="13"/>
-      <c r="P7" s="13"/>
-      <c r="Q7" s="13"/>
-      <c r="R7" s="13"/>
-      <c r="T7" s="13" t="s">
+      <c r="B7" s="24"/>
+      <c r="E7" s="16" t="s">
+        <v>226</v>
+      </c>
+      <c r="F7" s="16"/>
+      <c r="G7" s="16"/>
+      <c r="H7" s="16"/>
+      <c r="I7" s="16"/>
+      <c r="J7" s="16"/>
+      <c r="K7" s="16"/>
+      <c r="L7" s="16"/>
+      <c r="M7" s="16"/>
+      <c r="N7" s="16"/>
+      <c r="O7" s="16"/>
+      <c r="P7" s="16"/>
+      <c r="Q7" s="16"/>
+      <c r="R7" s="16"/>
+      <c r="T7" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="U7" s="13"/>
-      <c r="V7" s="13"/>
-      <c r="W7" s="13"/>
-      <c r="X7" s="13"/>
-      <c r="Y7" s="13"/>
-      <c r="Z7" s="13"/>
-      <c r="AA7" s="13"/>
-      <c r="AB7" s="13"/>
-      <c r="AC7" s="13"/>
-      <c r="AD7" s="13"/>
-      <c r="AE7" s="13"/>
-      <c r="AF7" s="13"/>
-      <c r="AG7" s="13"/>
-      <c r="AT7" s="24"/>
-      <c r="AU7" s="24"/>
-      <c r="AV7" s="25"/>
-      <c r="AW7" s="14" t="s">
+      <c r="U7" s="16"/>
+      <c r="V7" s="16"/>
+      <c r="W7" s="16"/>
+      <c r="X7" s="16"/>
+      <c r="Y7" s="16"/>
+      <c r="Z7" s="16"/>
+      <c r="AA7" s="16"/>
+      <c r="AB7" s="16"/>
+      <c r="AC7" s="16"/>
+      <c r="AD7" s="16"/>
+      <c r="AE7" s="16"/>
+      <c r="AF7" s="16"/>
+      <c r="AG7" s="16"/>
+      <c r="AT7" s="27"/>
+      <c r="AU7" s="27"/>
+      <c r="AV7" s="28"/>
+      <c r="AW7" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="AX7" s="16"/>
-      <c r="AY7" s="14" t="s">
+      <c r="AX7" s="15"/>
+      <c r="AY7" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="AZ7" s="15"/>
-      <c r="BA7" s="15"/>
-      <c r="BB7" s="16"/>
-      <c r="BC7" s="14" t="s">
+      <c r="AZ7" s="14"/>
+      <c r="BA7" s="14"/>
+      <c r="BB7" s="15"/>
+      <c r="BC7" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="BD7" s="15"/>
-      <c r="BE7" s="16"/>
-      <c r="BF7" s="14" t="s">
+      <c r="BD7" s="14"/>
+      <c r="BE7" s="15"/>
+      <c r="BF7" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="BG7" s="15"/>
-      <c r="BH7" s="15"/>
-      <c r="BI7" s="15"/>
-      <c r="BJ7" s="15"/>
-      <c r="BK7" s="16"/>
+      <c r="BG7" s="14"/>
+      <c r="BH7" s="14"/>
+      <c r="BI7" s="14"/>
+      <c r="BJ7" s="14"/>
+      <c r="BK7" s="15"/>
       <c r="BL7" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="BM7" s="14" t="s">
+      <c r="BM7" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="BN7" s="15"/>
-      <c r="BO7" s="16"/>
+      <c r="BN7" s="14"/>
+      <c r="BO7" s="15"/>
       <c r="BP7" s="4" t="s">
         <v>17</v>
       </c>
       <c r="BQ7" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="BR7" s="27"/>
+      <c r="BR7" s="24"/>
     </row>
     <row r="8" spans="1:71" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B8" s="27"/>
-      <c r="E8" s="13"/>
-      <c r="F8" s="13"/>
-      <c r="G8" s="13"/>
-      <c r="H8" s="13"/>
-      <c r="I8" s="13"/>
-      <c r="J8" s="13"/>
-      <c r="K8" s="13"/>
-      <c r="L8" s="13"/>
-      <c r="M8" s="13"/>
-      <c r="N8" s="13"/>
-      <c r="O8" s="13"/>
-      <c r="P8" s="13"/>
-      <c r="Q8" s="13"/>
-      <c r="R8" s="13"/>
-      <c r="T8" s="13"/>
-      <c r="U8" s="13"/>
-      <c r="V8" s="13"/>
-      <c r="W8" s="13"/>
-      <c r="X8" s="13"/>
-      <c r="Y8" s="13"/>
-      <c r="Z8" s="13"/>
-      <c r="AA8" s="13"/>
-      <c r="AB8" s="13"/>
-      <c r="AC8" s="13"/>
-      <c r="AD8" s="13"/>
-      <c r="AE8" s="13"/>
-      <c r="AF8" s="13"/>
-      <c r="AG8" s="13"/>
-      <c r="AT8" s="24"/>
-      <c r="AU8" s="24"/>
-      <c r="AV8" s="25"/>
-      <c r="AW8" s="14" t="s">
+      <c r="B8" s="24"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="16"/>
+      <c r="I8" s="16"/>
+      <c r="J8" s="16"/>
+      <c r="K8" s="16"/>
+      <c r="L8" s="16"/>
+      <c r="M8" s="16"/>
+      <c r="N8" s="16"/>
+      <c r="O8" s="16"/>
+      <c r="P8" s="16"/>
+      <c r="Q8" s="16"/>
+      <c r="R8" s="16"/>
+      <c r="T8" s="16"/>
+      <c r="U8" s="16"/>
+      <c r="V8" s="16"/>
+      <c r="W8" s="16"/>
+      <c r="X8" s="16"/>
+      <c r="Y8" s="16"/>
+      <c r="Z8" s="16"/>
+      <c r="AA8" s="16"/>
+      <c r="AB8" s="16"/>
+      <c r="AC8" s="16"/>
+      <c r="AD8" s="16"/>
+      <c r="AE8" s="16"/>
+      <c r="AF8" s="16"/>
+      <c r="AG8" s="16"/>
+      <c r="AT8" s="27"/>
+      <c r="AU8" s="27"/>
+      <c r="AV8" s="28"/>
+      <c r="AW8" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="AX8" s="16"/>
-      <c r="AY8" s="14" t="s">
+      <c r="AX8" s="15"/>
+      <c r="AY8" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="AZ8" s="15"/>
-      <c r="BA8" s="15"/>
-      <c r="BB8" s="16"/>
-      <c r="BC8" s="14" t="s">
+      <c r="AZ8" s="14"/>
+      <c r="BA8" s="14"/>
+      <c r="BB8" s="15"/>
+      <c r="BC8" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="BD8" s="15"/>
-      <c r="BE8" s="16"/>
-      <c r="BF8" s="14" t="s">
+      <c r="BD8" s="14"/>
+      <c r="BE8" s="15"/>
+      <c r="BF8" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="BG8" s="15"/>
-      <c r="BH8" s="15"/>
-      <c r="BI8" s="15"/>
-      <c r="BJ8" s="15"/>
-      <c r="BK8" s="16"/>
+      <c r="BG8" s="14"/>
+      <c r="BH8" s="14"/>
+      <c r="BI8" s="14"/>
+      <c r="BJ8" s="14"/>
+      <c r="BK8" s="15"/>
       <c r="BL8" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="BM8" s="14" t="s">
+      <c r="BM8" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="BN8" s="15"/>
-      <c r="BO8" s="16"/>
+      <c r="BN8" s="14"/>
+      <c r="BO8" s="15"/>
       <c r="BP8" s="8" t="s">
         <v>25</v>
       </c>
       <c r="BQ8" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="BR8" s="27"/>
+      <c r="BR8" s="24"/>
     </row>
     <row r="9" spans="1:71" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B9" s="27"/>
-      <c r="E9" s="13"/>
-      <c r="F9" s="13"/>
-      <c r="G9" s="13"/>
-      <c r="H9" s="13"/>
-      <c r="I9" s="13"/>
-      <c r="J9" s="13"/>
-      <c r="K9" s="13"/>
-      <c r="L9" s="13"/>
-      <c r="M9" s="13"/>
-      <c r="N9" s="13"/>
-      <c r="O9" s="13"/>
-      <c r="P9" s="13"/>
-      <c r="Q9" s="13"/>
-      <c r="R9" s="13"/>
-      <c r="T9" s="13"/>
-      <c r="U9" s="13"/>
-      <c r="V9" s="13"/>
-      <c r="W9" s="13"/>
-      <c r="X9" s="13"/>
-      <c r="Y9" s="13"/>
-      <c r="Z9" s="13"/>
-      <c r="AA9" s="13"/>
-      <c r="AB9" s="13"/>
-      <c r="AC9" s="13"/>
-      <c r="AD9" s="13"/>
-      <c r="AE9" s="13"/>
-      <c r="AF9" s="13"/>
-      <c r="AG9" s="13"/>
+      <c r="B9" s="24"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="16"/>
+      <c r="G9" s="16"/>
+      <c r="H9" s="16"/>
+      <c r="I9" s="16"/>
+      <c r="J9" s="16"/>
+      <c r="K9" s="16"/>
+      <c r="L9" s="16"/>
+      <c r="M9" s="16"/>
+      <c r="N9" s="16"/>
+      <c r="O9" s="16"/>
+      <c r="P9" s="16"/>
+      <c r="Q9" s="16"/>
+      <c r="R9" s="16"/>
+      <c r="T9" s="16"/>
+      <c r="U9" s="16"/>
+      <c r="V9" s="16"/>
+      <c r="W9" s="16"/>
+      <c r="X9" s="16"/>
+      <c r="Y9" s="16"/>
+      <c r="Z9" s="16"/>
+      <c r="AA9" s="16"/>
+      <c r="AB9" s="16"/>
+      <c r="AC9" s="16"/>
+      <c r="AD9" s="16"/>
+      <c r="AE9" s="16"/>
+      <c r="AF9" s="16"/>
+      <c r="AG9" s="16"/>
       <c r="AT9" s="11"/>
       <c r="AU9" s="11"/>
       <c r="AV9" s="12"/>
-      <c r="AW9" s="14" t="s">
+      <c r="AW9" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="AX9" s="16"/>
-      <c r="AY9" s="14" t="s">
+      <c r="AX9" s="15"/>
+      <c r="AY9" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="AZ9" s="15"/>
-      <c r="BA9" s="15"/>
-      <c r="BB9" s="16"/>
-      <c r="BC9" s="14" t="s">
+      <c r="AZ9" s="14"/>
+      <c r="BA9" s="14"/>
+      <c r="BB9" s="15"/>
+      <c r="BC9" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="BD9" s="15"/>
-      <c r="BE9" s="16"/>
-      <c r="BF9" s="14" t="s">
+      <c r="BD9" s="14"/>
+      <c r="BE9" s="15"/>
+      <c r="BF9" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="BG9" s="15"/>
-      <c r="BH9" s="15"/>
-      <c r="BI9" s="15"/>
-      <c r="BJ9" s="15"/>
-      <c r="BK9" s="16"/>
+      <c r="BG9" s="14"/>
+      <c r="BH9" s="14"/>
+      <c r="BI9" s="14"/>
+      <c r="BJ9" s="14"/>
+      <c r="BK9" s="15"/>
       <c r="BL9" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="BM9" s="14" t="s">
+      <c r="BM9" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="BN9" s="15"/>
-      <c r="BO9" s="16"/>
+      <c r="BN9" s="14"/>
+      <c r="BO9" s="15"/>
       <c r="BP9" s="8" t="s">
         <v>33</v>
       </c>
       <c r="BQ9" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="BR9" s="27"/>
+      <c r="BR9" s="24"/>
     </row>
     <row r="10" spans="1:71" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B10" s="27"/>
-      <c r="E10" s="13"/>
-      <c r="F10" s="13"/>
-      <c r="G10" s="13"/>
-      <c r="H10" s="13"/>
-      <c r="I10" s="13"/>
-      <c r="J10" s="13"/>
-      <c r="K10" s="13"/>
-      <c r="L10" s="13"/>
-      <c r="M10" s="13"/>
-      <c r="N10" s="13"/>
-      <c r="O10" s="13"/>
-      <c r="P10" s="13"/>
-      <c r="Q10" s="13"/>
-      <c r="R10" s="13"/>
-      <c r="T10" s="13"/>
-      <c r="U10" s="13"/>
-      <c r="V10" s="13"/>
-      <c r="W10" s="13"/>
-      <c r="X10" s="13"/>
-      <c r="Y10" s="13"/>
-      <c r="Z10" s="13"/>
-      <c r="AA10" s="13"/>
-      <c r="AB10" s="13"/>
-      <c r="AC10" s="13"/>
-      <c r="AD10" s="13"/>
-      <c r="AE10" s="13"/>
-      <c r="AF10" s="13"/>
-      <c r="AG10" s="13"/>
+      <c r="B10" s="24"/>
+      <c r="E10" s="16"/>
+      <c r="F10" s="16"/>
+      <c r="G10" s="16"/>
+      <c r="H10" s="16"/>
+      <c r="I10" s="16"/>
+      <c r="J10" s="16"/>
+      <c r="K10" s="16"/>
+      <c r="L10" s="16"/>
+      <c r="M10" s="16"/>
+      <c r="N10" s="16"/>
+      <c r="O10" s="16"/>
+      <c r="P10" s="16"/>
+      <c r="Q10" s="16"/>
+      <c r="R10" s="16"/>
+      <c r="T10" s="16"/>
+      <c r="U10" s="16"/>
+      <c r="V10" s="16"/>
+      <c r="W10" s="16"/>
+      <c r="X10" s="16"/>
+      <c r="Y10" s="16"/>
+      <c r="Z10" s="16"/>
+      <c r="AA10" s="16"/>
+      <c r="AB10" s="16"/>
+      <c r="AC10" s="16"/>
+      <c r="AD10" s="16"/>
+      <c r="AE10" s="16"/>
+      <c r="AF10" s="16"/>
+      <c r="AG10" s="16"/>
       <c r="AT10" s="11"/>
       <c r="AU10" s="11"/>
       <c r="AV10" s="12"/>
-      <c r="AW10" s="14" t="s">
+      <c r="AW10" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="AX10" s="16"/>
-      <c r="AY10" s="14" t="s">
+      <c r="AX10" s="15"/>
+      <c r="AY10" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="AZ10" s="15"/>
-      <c r="BA10" s="15"/>
-      <c r="BB10" s="16"/>
-      <c r="BC10" s="14" t="s">
+      <c r="AZ10" s="14"/>
+      <c r="BA10" s="14"/>
+      <c r="BB10" s="15"/>
+      <c r="BC10" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="BD10" s="15"/>
-      <c r="BE10" s="16"/>
-      <c r="BF10" s="14" t="s">
+      <c r="BD10" s="14"/>
+      <c r="BE10" s="15"/>
+      <c r="BF10" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="BG10" s="15"/>
-      <c r="BH10" s="15"/>
-      <c r="BI10" s="15"/>
-      <c r="BJ10" s="15"/>
-      <c r="BK10" s="16"/>
+      <c r="BG10" s="14"/>
+      <c r="BH10" s="14"/>
+      <c r="BI10" s="14"/>
+      <c r="BJ10" s="14"/>
+      <c r="BK10" s="15"/>
       <c r="BL10" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="BM10" s="14" t="s">
+      <c r="BM10" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="BN10" s="15"/>
-      <c r="BO10" s="16"/>
+      <c r="BN10" s="14"/>
+      <c r="BO10" s="15"/>
       <c r="BP10" s="8" t="s">
         <v>41</v>
       </c>
       <c r="BQ10" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="BR10" s="27"/>
+      <c r="BR10" s="24"/>
     </row>
     <row r="11" spans="1:71" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B11" s="27"/>
-      <c r="E11" s="13"/>
-      <c r="F11" s="13"/>
-      <c r="G11" s="13"/>
-      <c r="H11" s="13"/>
-      <c r="I11" s="13"/>
-      <c r="J11" s="13"/>
-      <c r="K11" s="13"/>
-      <c r="L11" s="13"/>
-      <c r="M11" s="13"/>
-      <c r="N11" s="13"/>
-      <c r="O11" s="13"/>
-      <c r="P11" s="13"/>
-      <c r="Q11" s="13"/>
-      <c r="R11" s="13"/>
-      <c r="T11" s="13"/>
-      <c r="U11" s="13"/>
-      <c r="V11" s="13"/>
-      <c r="W11" s="13"/>
-      <c r="X11" s="13"/>
-      <c r="Y11" s="13"/>
-      <c r="Z11" s="13"/>
-      <c r="AA11" s="13"/>
-      <c r="AB11" s="13"/>
-      <c r="AC11" s="13"/>
-      <c r="AD11" s="13"/>
-      <c r="AE11" s="13"/>
-      <c r="AF11" s="13"/>
-      <c r="AG11" s="13"/>
+      <c r="B11" s="24"/>
+      <c r="E11" s="16"/>
+      <c r="F11" s="16"/>
+      <c r="G11" s="16"/>
+      <c r="H11" s="16"/>
+      <c r="I11" s="16"/>
+      <c r="J11" s="16"/>
+      <c r="K11" s="16"/>
+      <c r="L11" s="16"/>
+      <c r="M11" s="16"/>
+      <c r="N11" s="16"/>
+      <c r="O11" s="16"/>
+      <c r="P11" s="16"/>
+      <c r="Q11" s="16"/>
+      <c r="R11" s="16"/>
+      <c r="T11" s="16"/>
+      <c r="U11" s="16"/>
+      <c r="V11" s="16"/>
+      <c r="W11" s="16"/>
+      <c r="X11" s="16"/>
+      <c r="Y11" s="16"/>
+      <c r="Z11" s="16"/>
+      <c r="AA11" s="16"/>
+      <c r="AB11" s="16"/>
+      <c r="AC11" s="16"/>
+      <c r="AD11" s="16"/>
+      <c r="AE11" s="16"/>
+      <c r="AF11" s="16"/>
+      <c r="AG11" s="16"/>
       <c r="AT11" s="11"/>
       <c r="AU11" s="11"/>
       <c r="AV11" s="12"/>
-      <c r="AW11" s="14" t="s">
+      <c r="AW11" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="AX11" s="16"/>
-      <c r="AY11" s="14" t="s">
+      <c r="AX11" s="15"/>
+      <c r="AY11" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="AZ11" s="15"/>
-      <c r="BA11" s="15"/>
-      <c r="BB11" s="16"/>
-      <c r="BC11" s="14" t="s">
+      <c r="AZ11" s="14"/>
+      <c r="BA11" s="14"/>
+      <c r="BB11" s="15"/>
+      <c r="BC11" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="BD11" s="15"/>
-      <c r="BE11" s="16"/>
-      <c r="BF11" s="14" t="s">
+      <c r="BD11" s="14"/>
+      <c r="BE11" s="15"/>
+      <c r="BF11" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="BG11" s="15"/>
-      <c r="BH11" s="15"/>
-      <c r="BI11" s="15"/>
-      <c r="BJ11" s="15"/>
-      <c r="BK11" s="16"/>
+      <c r="BG11" s="14"/>
+      <c r="BH11" s="14"/>
+      <c r="BI11" s="14"/>
+      <c r="BJ11" s="14"/>
+      <c r="BK11" s="15"/>
       <c r="BL11" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="BM11" s="14" t="s">
+      <c r="BM11" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="BN11" s="15"/>
-      <c r="BO11" s="16"/>
+      <c r="BN11" s="14"/>
+      <c r="BO11" s="15"/>
       <c r="BP11" s="10" t="s">
         <v>49</v>
       </c>
       <c r="BQ11" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="BR11" s="27"/>
+      <c r="BR11" s="24"/>
     </row>
     <row r="12" spans="1:71" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B12" s="27"/>
-      <c r="AW12" s="14" t="s">
+      <c r="B12" s="24"/>
+      <c r="AW12" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="AX12" s="16"/>
-      <c r="AY12" s="14" t="s">
+      <c r="AX12" s="15"/>
+      <c r="AY12" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="AZ12" s="15"/>
-      <c r="BA12" s="15"/>
-      <c r="BB12" s="16"/>
-      <c r="BC12" s="14" t="s">
+      <c r="AZ12" s="14"/>
+      <c r="BA12" s="14"/>
+      <c r="BB12" s="15"/>
+      <c r="BC12" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="BD12" s="15"/>
-      <c r="BE12" s="16"/>
-      <c r="BF12" s="14" t="s">
+      <c r="BD12" s="14"/>
+      <c r="BE12" s="15"/>
+      <c r="BF12" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="BG12" s="15"/>
-      <c r="BH12" s="15"/>
-      <c r="BI12" s="15"/>
-      <c r="BJ12" s="15"/>
-      <c r="BK12" s="16"/>
+      <c r="BG12" s="14"/>
+      <c r="BH12" s="14"/>
+      <c r="BI12" s="14"/>
+      <c r="BJ12" s="14"/>
+      <c r="BK12" s="15"/>
       <c r="BL12" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="BM12" s="14" t="s">
+      <c r="BM12" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="BN12" s="15"/>
-      <c r="BO12" s="16"/>
+      <c r="BN12" s="14"/>
+      <c r="BO12" s="15"/>
       <c r="BP12" s="8" t="s">
         <v>57</v>
       </c>
       <c r="BQ12" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="BR12" s="27"/>
+      <c r="BR12" s="24"/>
     </row>
     <row r="13" spans="1:71" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B13" s="27"/>
-      <c r="AW13" s="14" t="s">
+      <c r="B13" s="24"/>
+      <c r="AW13" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="AX13" s="16"/>
-      <c r="AY13" s="14" t="s">
+      <c r="AX13" s="15"/>
+      <c r="AY13" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="AZ13" s="15"/>
-      <c r="BA13" s="15"/>
-      <c r="BB13" s="16"/>
-      <c r="BC13" s="14" t="s">
+      <c r="AZ13" s="14"/>
+      <c r="BA13" s="14"/>
+      <c r="BB13" s="15"/>
+      <c r="BC13" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="BD13" s="15"/>
-      <c r="BE13" s="16"/>
-      <c r="BF13" s="14" t="s">
+      <c r="BD13" s="14"/>
+      <c r="BE13" s="15"/>
+      <c r="BF13" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="BG13" s="15"/>
-      <c r="BH13" s="15"/>
-      <c r="BI13" s="15"/>
-      <c r="BJ13" s="15"/>
-      <c r="BK13" s="16"/>
+      <c r="BG13" s="14"/>
+      <c r="BH13" s="14"/>
+      <c r="BI13" s="14"/>
+      <c r="BJ13" s="14"/>
+      <c r="BK13" s="15"/>
       <c r="BL13" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="BM13" s="14" t="s">
+      <c r="BM13" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="BN13" s="15"/>
-      <c r="BO13" s="16"/>
+      <c r="BN13" s="14"/>
+      <c r="BO13" s="15"/>
       <c r="BP13" s="8" t="s">
         <v>65</v>
       </c>
       <c r="BQ13" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="BR13" s="27"/>
+      <c r="BR13" s="24"/>
     </row>
     <row r="14" spans="1:71" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B14" s="27"/>
-      <c r="AW14" s="14" t="s">
+      <c r="B14" s="24"/>
+      <c r="AW14" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="AX14" s="16"/>
-      <c r="AY14" s="14" t="s">
+      <c r="AX14" s="15"/>
+      <c r="AY14" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="AZ14" s="15"/>
-      <c r="BA14" s="15"/>
-      <c r="BB14" s="16"/>
-      <c r="BC14" s="14" t="s">
+      <c r="AZ14" s="14"/>
+      <c r="BA14" s="14"/>
+      <c r="BB14" s="15"/>
+      <c r="BC14" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="BD14" s="15"/>
-      <c r="BE14" s="16"/>
-      <c r="BF14" s="14" t="s">
+      <c r="BD14" s="14"/>
+      <c r="BE14" s="15"/>
+      <c r="BF14" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="BG14" s="15"/>
-      <c r="BH14" s="15"/>
-      <c r="BI14" s="15"/>
-      <c r="BJ14" s="15"/>
-      <c r="BK14" s="16"/>
+      <c r="BG14" s="14"/>
+      <c r="BH14" s="14"/>
+      <c r="BI14" s="14"/>
+      <c r="BJ14" s="14"/>
+      <c r="BK14" s="15"/>
       <c r="BL14" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="BM14" s="14" t="s">
+      <c r="BM14" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="BN14" s="15"/>
-      <c r="BO14" s="16"/>
+      <c r="BN14" s="14"/>
+      <c r="BO14" s="15"/>
       <c r="BP14" s="8" t="s">
         <v>73</v>
       </c>
       <c r="BQ14" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="BR14" s="27"/>
+      <c r="BR14" s="24"/>
     </row>
     <row r="15" spans="1:71" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B15" s="27"/>
-      <c r="AW15" s="14" t="s">
+      <c r="B15" s="24"/>
+      <c r="AW15" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="AX15" s="16"/>
-      <c r="AY15" s="14" t="s">
+      <c r="AX15" s="15"/>
+      <c r="AY15" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="AZ15" s="15"/>
-      <c r="BA15" s="15"/>
-      <c r="BB15" s="16"/>
-      <c r="BC15" s="14" t="s">
+      <c r="AZ15" s="14"/>
+      <c r="BA15" s="14"/>
+      <c r="BB15" s="15"/>
+      <c r="BC15" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="BD15" s="15"/>
-      <c r="BE15" s="16"/>
-      <c r="BF15" s="14" t="s">
+      <c r="BD15" s="14"/>
+      <c r="BE15" s="15"/>
+      <c r="BF15" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="BG15" s="15"/>
-      <c r="BH15" s="15"/>
-      <c r="BI15" s="15"/>
-      <c r="BJ15" s="15"/>
-      <c r="BK15" s="16"/>
+      <c r="BG15" s="14"/>
+      <c r="BH15" s="14"/>
+      <c r="BI15" s="14"/>
+      <c r="BJ15" s="14"/>
+      <c r="BK15" s="15"/>
       <c r="BL15" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="BM15" s="14" t="s">
+      <c r="BM15" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="BN15" s="15"/>
-      <c r="BO15" s="16"/>
+      <c r="BN15" s="14"/>
+      <c r="BO15" s="15"/>
       <c r="BP15" s="8" t="s">
         <v>81</v>
       </c>
       <c r="BQ15" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="BR15" s="27"/>
+      <c r="BR15" s="24"/>
     </row>
     <row r="16" spans="1:71" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B16" s="28"/>
-      <c r="AW16" s="14" t="s">
+      <c r="B16" s="25"/>
+      <c r="AW16" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="AX16" s="16"/>
-      <c r="AY16" s="14" t="s">
+      <c r="AX16" s="15"/>
+      <c r="AY16" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="AZ16" s="15"/>
-      <c r="BA16" s="15"/>
-      <c r="BB16" s="16"/>
-      <c r="BC16" s="14" t="s">
+      <c r="AZ16" s="14"/>
+      <c r="BA16" s="14"/>
+      <c r="BB16" s="15"/>
+      <c r="BC16" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="BD16" s="15"/>
-      <c r="BE16" s="16"/>
-      <c r="BF16" s="14" t="s">
+      <c r="BD16" s="14"/>
+      <c r="BE16" s="15"/>
+      <c r="BF16" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="BG16" s="15"/>
-      <c r="BH16" s="15"/>
-      <c r="BI16" s="15"/>
-      <c r="BJ16" s="15"/>
-      <c r="BK16" s="16"/>
+      <c r="BG16" s="14"/>
+      <c r="BH16" s="14"/>
+      <c r="BI16" s="14"/>
+      <c r="BJ16" s="14"/>
+      <c r="BK16" s="15"/>
       <c r="BL16" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="BM16" s="14" t="s">
+      <c r="BM16" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="BN16" s="15"/>
-      <c r="BO16" s="16"/>
+      <c r="BN16" s="14"/>
+      <c r="BO16" s="15"/>
       <c r="BP16" s="8" t="s">
         <v>90</v>
       </c>
       <c r="BQ16" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="BR16" s="28"/>
+      <c r="BR16" s="25"/>
     </row>
     <row r="17" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B17" s="26" t="s">
+      <c r="B17" s="23" t="s">
         <v>83</v>
       </c>
-      <c r="E17" s="13" t="s">
-        <v>228</v>
-      </c>
-      <c r="F17" s="13"/>
-      <c r="G17" s="13"/>
-      <c r="H17" s="13"/>
-      <c r="I17" s="13"/>
-      <c r="J17" s="13"/>
-      <c r="K17" s="13"/>
-      <c r="L17" s="13"/>
-      <c r="M17" s="13"/>
-      <c r="N17" s="13"/>
-      <c r="O17" s="13"/>
-      <c r="P17" s="13"/>
-      <c r="Q17" s="13"/>
-      <c r="R17" s="13"/>
-      <c r="T17" s="13" t="s">
+      <c r="E17" s="16" t="s">
+        <v>227</v>
+      </c>
+      <c r="F17" s="16"/>
+      <c r="G17" s="16"/>
+      <c r="H17" s="16"/>
+      <c r="I17" s="16"/>
+      <c r="J17" s="16"/>
+      <c r="K17" s="16"/>
+      <c r="L17" s="16"/>
+      <c r="M17" s="16"/>
+      <c r="N17" s="16"/>
+      <c r="O17" s="16"/>
+      <c r="P17" s="16"/>
+      <c r="Q17" s="16"/>
+      <c r="R17" s="16"/>
+      <c r="T17" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="U17" s="13"/>
-      <c r="V17" s="13"/>
-      <c r="W17" s="13"/>
-      <c r="X17" s="13"/>
-      <c r="Y17" s="13"/>
-      <c r="Z17" s="13"/>
-      <c r="AA17" s="13"/>
-      <c r="AB17" s="13"/>
-      <c r="AC17" s="13"/>
-      <c r="AD17" s="13"/>
-      <c r="AE17" s="13"/>
-      <c r="AF17" s="13"/>
-      <c r="AG17" s="13"/>
-      <c r="AW17" s="14" t="s">
+      <c r="U17" s="16"/>
+      <c r="V17" s="16"/>
+      <c r="W17" s="16"/>
+      <c r="X17" s="16"/>
+      <c r="Y17" s="16"/>
+      <c r="Z17" s="16"/>
+      <c r="AA17" s="16"/>
+      <c r="AB17" s="16"/>
+      <c r="AC17" s="16"/>
+      <c r="AD17" s="16"/>
+      <c r="AE17" s="16"/>
+      <c r="AF17" s="16"/>
+      <c r="AG17" s="16"/>
+      <c r="AW17" s="13" t="s">
         <v>92</v>
       </c>
-      <c r="AX17" s="16"/>
-      <c r="AY17" s="14" t="s">
+      <c r="AX17" s="15"/>
+      <c r="AY17" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AZ17" s="15"/>
-      <c r="BA17" s="15"/>
-      <c r="BB17" s="16"/>
-      <c r="BC17" s="14" t="s">
+      <c r="AZ17" s="14"/>
+      <c r="BA17" s="14"/>
+      <c r="BB17" s="15"/>
+      <c r="BC17" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="BD17" s="15"/>
-      <c r="BE17" s="16"/>
-      <c r="BF17" s="14" t="s">
+      <c r="BD17" s="14"/>
+      <c r="BE17" s="15"/>
+      <c r="BF17" s="13" t="s">
         <v>95</v>
       </c>
-      <c r="BG17" s="15"/>
-      <c r="BH17" s="15"/>
-      <c r="BI17" s="15"/>
-      <c r="BJ17" s="15"/>
-      <c r="BK17" s="16"/>
+      <c r="BG17" s="14"/>
+      <c r="BH17" s="14"/>
+      <c r="BI17" s="14"/>
+      <c r="BJ17" s="14"/>
+      <c r="BK17" s="15"/>
       <c r="BL17" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="BM17" s="14" t="s">
+      <c r="BM17" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="BN17" s="15"/>
-      <c r="BO17" s="16"/>
+      <c r="BN17" s="14"/>
+      <c r="BO17" s="15"/>
       <c r="BP17" s="8" t="s">
         <v>98</v>
       </c>
       <c r="BQ17" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="BR17" s="26" t="s">
+      <c r="BR17" s="23" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="18" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B18" s="27"/>
-      <c r="E18" s="13"/>
-      <c r="F18" s="13"/>
-      <c r="G18" s="13"/>
-      <c r="H18" s="13"/>
-      <c r="I18" s="13"/>
-      <c r="J18" s="13"/>
-      <c r="K18" s="13"/>
-      <c r="L18" s="13"/>
-      <c r="M18" s="13"/>
-      <c r="N18" s="13"/>
-      <c r="O18" s="13"/>
-      <c r="P18" s="13"/>
-      <c r="Q18" s="13"/>
-      <c r="R18" s="13"/>
-      <c r="T18" s="13"/>
-      <c r="U18" s="13"/>
-      <c r="V18" s="13"/>
-      <c r="W18" s="13"/>
-      <c r="X18" s="13"/>
-      <c r="Y18" s="13"/>
-      <c r="Z18" s="13"/>
-      <c r="AA18" s="13"/>
-      <c r="AB18" s="13"/>
-      <c r="AC18" s="13"/>
-      <c r="AD18" s="13"/>
-      <c r="AE18" s="13"/>
-      <c r="AF18" s="13"/>
-      <c r="AG18" s="13"/>
-      <c r="AW18" s="14" t="s">
+      <c r="B18" s="24"/>
+      <c r="E18" s="16"/>
+      <c r="F18" s="16"/>
+      <c r="G18" s="16"/>
+      <c r="H18" s="16"/>
+      <c r="I18" s="16"/>
+      <c r="J18" s="16"/>
+      <c r="K18" s="16"/>
+      <c r="L18" s="16"/>
+      <c r="M18" s="16"/>
+      <c r="N18" s="16"/>
+      <c r="O18" s="16"/>
+      <c r="P18" s="16"/>
+      <c r="Q18" s="16"/>
+      <c r="R18" s="16"/>
+      <c r="T18" s="16"/>
+      <c r="U18" s="16"/>
+      <c r="V18" s="16"/>
+      <c r="W18" s="16"/>
+      <c r="X18" s="16"/>
+      <c r="Y18" s="16"/>
+      <c r="Z18" s="16"/>
+      <c r="AA18" s="16"/>
+      <c r="AB18" s="16"/>
+      <c r="AC18" s="16"/>
+      <c r="AD18" s="16"/>
+      <c r="AE18" s="16"/>
+      <c r="AF18" s="16"/>
+      <c r="AG18" s="16"/>
+      <c r="AW18" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="AX18" s="16"/>
-      <c r="AY18" s="14" t="s">
+      <c r="AX18" s="15"/>
+      <c r="AY18" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="AZ18" s="15"/>
-      <c r="BA18" s="15"/>
-      <c r="BB18" s="16"/>
-      <c r="BC18" s="14" t="s">
+      <c r="AZ18" s="14"/>
+      <c r="BA18" s="14"/>
+      <c r="BB18" s="15"/>
+      <c r="BC18" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="BD18" s="15"/>
-      <c r="BE18" s="16"/>
-      <c r="BF18" s="14" t="s">
+      <c r="BD18" s="14"/>
+      <c r="BE18" s="15"/>
+      <c r="BF18" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="BG18" s="15"/>
-      <c r="BH18" s="15"/>
-      <c r="BI18" s="15"/>
-      <c r="BJ18" s="15"/>
-      <c r="BK18" s="16"/>
+      <c r="BG18" s="14"/>
+      <c r="BH18" s="14"/>
+      <c r="BI18" s="14"/>
+      <c r="BJ18" s="14"/>
+      <c r="BK18" s="15"/>
       <c r="BL18" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="BM18" s="14" t="s">
+      <c r="BM18" s="13" t="s">
         <v>105</v>
       </c>
-      <c r="BN18" s="15"/>
-      <c r="BO18" s="16"/>
+      <c r="BN18" s="14"/>
+      <c r="BO18" s="15"/>
       <c r="BP18" s="8" t="s">
         <v>106</v>
       </c>
       <c r="BQ18" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="BR18" s="27"/>
+      <c r="BR18" s="24"/>
     </row>
     <row r="19" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B19" s="27"/>
-      <c r="E19" s="13"/>
-      <c r="F19" s="13"/>
-      <c r="G19" s="13"/>
-      <c r="H19" s="13"/>
-      <c r="I19" s="13"/>
-      <c r="J19" s="13"/>
-      <c r="K19" s="13"/>
-      <c r="L19" s="13"/>
-      <c r="M19" s="13"/>
-      <c r="N19" s="13"/>
-      <c r="O19" s="13"/>
-      <c r="P19" s="13"/>
-      <c r="Q19" s="13"/>
-      <c r="R19" s="13"/>
-      <c r="T19" s="13"/>
-      <c r="U19" s="13"/>
-      <c r="V19" s="13"/>
-      <c r="W19" s="13"/>
-      <c r="X19" s="13"/>
-      <c r="Y19" s="13"/>
-      <c r="Z19" s="13"/>
-      <c r="AA19" s="13"/>
-      <c r="AB19" s="13"/>
-      <c r="AC19" s="13"/>
-      <c r="AD19" s="13"/>
-      <c r="AE19" s="13"/>
-      <c r="AF19" s="13"/>
-      <c r="AG19" s="13"/>
-      <c r="AW19" s="14" t="s">
+      <c r="B19" s="24"/>
+      <c r="E19" s="16"/>
+      <c r="F19" s="16"/>
+      <c r="G19" s="16"/>
+      <c r="H19" s="16"/>
+      <c r="I19" s="16"/>
+      <c r="J19" s="16"/>
+      <c r="K19" s="16"/>
+      <c r="L19" s="16"/>
+      <c r="M19" s="16"/>
+      <c r="N19" s="16"/>
+      <c r="O19" s="16"/>
+      <c r="P19" s="16"/>
+      <c r="Q19" s="16"/>
+      <c r="R19" s="16"/>
+      <c r="T19" s="16"/>
+      <c r="U19" s="16"/>
+      <c r="V19" s="16"/>
+      <c r="W19" s="16"/>
+      <c r="X19" s="16"/>
+      <c r="Y19" s="16"/>
+      <c r="Z19" s="16"/>
+      <c r="AA19" s="16"/>
+      <c r="AB19" s="16"/>
+      <c r="AC19" s="16"/>
+      <c r="AD19" s="16"/>
+      <c r="AE19" s="16"/>
+      <c r="AF19" s="16"/>
+      <c r="AG19" s="16"/>
+      <c r="AW19" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="AX19" s="16"/>
-      <c r="AY19" s="14" t="s">
+      <c r="AX19" s="15"/>
+      <c r="AY19" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="AZ19" s="15"/>
-      <c r="BA19" s="15"/>
-      <c r="BB19" s="16"/>
-      <c r="BC19" s="14" t="s">
+      <c r="AZ19" s="14"/>
+      <c r="BA19" s="14"/>
+      <c r="BB19" s="15"/>
+      <c r="BC19" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="BD19" s="15"/>
-      <c r="BE19" s="16"/>
-      <c r="BF19" s="14" t="s">
+      <c r="BD19" s="14"/>
+      <c r="BE19" s="15"/>
+      <c r="BF19" s="13" t="s">
         <v>111</v>
       </c>
-      <c r="BG19" s="15"/>
-      <c r="BH19" s="15"/>
-      <c r="BI19" s="15"/>
-      <c r="BJ19" s="15"/>
-      <c r="BK19" s="16"/>
+      <c r="BG19" s="14"/>
+      <c r="BH19" s="14"/>
+      <c r="BI19" s="14"/>
+      <c r="BJ19" s="14"/>
+      <c r="BK19" s="15"/>
       <c r="BL19" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="BM19" s="14" t="s">
+      <c r="BM19" s="13" t="s">
         <v>113</v>
       </c>
-      <c r="BN19" s="15"/>
-      <c r="BO19" s="16"/>
+      <c r="BN19" s="14"/>
+      <c r="BO19" s="15"/>
       <c r="BP19" s="8" t="s">
         <v>114</v>
       </c>
       <c r="BQ19" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="BR19" s="27"/>
+      <c r="BR19" s="24"/>
     </row>
     <row r="20" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B20" s="27"/>
-      <c r="E20" s="13"/>
-      <c r="F20" s="13"/>
-      <c r="G20" s="13"/>
-      <c r="H20" s="13"/>
-      <c r="I20" s="13"/>
-      <c r="J20" s="13"/>
-      <c r="K20" s="13"/>
-      <c r="L20" s="13"/>
-      <c r="M20" s="13"/>
-      <c r="N20" s="13"/>
-      <c r="O20" s="13"/>
-      <c r="P20" s="13"/>
-      <c r="Q20" s="13"/>
-      <c r="R20" s="13"/>
-      <c r="T20" s="13"/>
-      <c r="U20" s="13"/>
-      <c r="V20" s="13"/>
-      <c r="W20" s="13"/>
-      <c r="X20" s="13"/>
-      <c r="Y20" s="13"/>
-      <c r="Z20" s="13"/>
-      <c r="AA20" s="13"/>
-      <c r="AB20" s="13"/>
-      <c r="AC20" s="13"/>
-      <c r="AD20" s="13"/>
-      <c r="AE20" s="13"/>
-      <c r="AF20" s="13"/>
-      <c r="AG20" s="13"/>
-      <c r="AW20" s="14" t="s">
+      <c r="B20" s="24"/>
+      <c r="E20" s="16"/>
+      <c r="F20" s="16"/>
+      <c r="G20" s="16"/>
+      <c r="H20" s="16"/>
+      <c r="I20" s="16"/>
+      <c r="J20" s="16"/>
+      <c r="K20" s="16"/>
+      <c r="L20" s="16"/>
+      <c r="M20" s="16"/>
+      <c r="N20" s="16"/>
+      <c r="O20" s="16"/>
+      <c r="P20" s="16"/>
+      <c r="Q20" s="16"/>
+      <c r="R20" s="16"/>
+      <c r="T20" s="16"/>
+      <c r="U20" s="16"/>
+      <c r="V20" s="16"/>
+      <c r="W20" s="16"/>
+      <c r="X20" s="16"/>
+      <c r="Y20" s="16"/>
+      <c r="Z20" s="16"/>
+      <c r="AA20" s="16"/>
+      <c r="AB20" s="16"/>
+      <c r="AC20" s="16"/>
+      <c r="AD20" s="16"/>
+      <c r="AE20" s="16"/>
+      <c r="AF20" s="16"/>
+      <c r="AG20" s="16"/>
+      <c r="AW20" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="AX20" s="16"/>
-      <c r="AY20" s="14" t="s">
+      <c r="AX20" s="15"/>
+      <c r="AY20" s="13" t="s">
         <v>117</v>
       </c>
-      <c r="AZ20" s="15"/>
-      <c r="BA20" s="15"/>
-      <c r="BB20" s="16"/>
-      <c r="BC20" s="14" t="s">
+      <c r="AZ20" s="14"/>
+      <c r="BA20" s="14"/>
+      <c r="BB20" s="15"/>
+      <c r="BC20" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="BD20" s="15"/>
-      <c r="BE20" s="16"/>
-      <c r="BF20" s="14" t="s">
+      <c r="BD20" s="14"/>
+      <c r="BE20" s="15"/>
+      <c r="BF20" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="BG20" s="15"/>
-      <c r="BH20" s="15"/>
-      <c r="BI20" s="15"/>
-      <c r="BJ20" s="15"/>
-      <c r="BK20" s="16"/>
+      <c r="BG20" s="14"/>
+      <c r="BH20" s="14"/>
+      <c r="BI20" s="14"/>
+      <c r="BJ20" s="14"/>
+      <c r="BK20" s="15"/>
       <c r="BL20" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="BM20" s="14" t="s">
+      <c r="BM20" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="BN20" s="15"/>
-      <c r="BO20" s="16"/>
+      <c r="BN20" s="14"/>
+      <c r="BO20" s="15"/>
       <c r="BP20" s="8" t="s">
         <v>122</v>
       </c>
       <c r="BQ20" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="BR20" s="27"/>
+      <c r="BR20" s="24"/>
     </row>
     <row r="21" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B21" s="27"/>
-      <c r="AW21" s="14" t="s">
+      <c r="B21" s="24"/>
+      <c r="AW21" s="13" t="s">
         <v>124</v>
       </c>
-      <c r="AX21" s="16"/>
-      <c r="AY21" s="14" t="s">
+      <c r="AX21" s="15"/>
+      <c r="AY21" s="13" t="s">
         <v>125</v>
       </c>
-      <c r="AZ21" s="15"/>
-      <c r="BA21" s="15"/>
-      <c r="BB21" s="16"/>
-      <c r="BC21" s="14" t="s">
+      <c r="AZ21" s="14"/>
+      <c r="BA21" s="14"/>
+      <c r="BB21" s="15"/>
+      <c r="BC21" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="BD21" s="15"/>
-      <c r="BE21" s="16"/>
-      <c r="BF21" s="14" t="s">
+      <c r="BD21" s="14"/>
+      <c r="BE21" s="15"/>
+      <c r="BF21" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="BG21" s="15"/>
-      <c r="BH21" s="15"/>
-      <c r="BI21" s="15"/>
-      <c r="BJ21" s="15"/>
-      <c r="BK21" s="16"/>
+      <c r="BG21" s="14"/>
+      <c r="BH21" s="14"/>
+      <c r="BI21" s="14"/>
+      <c r="BJ21" s="14"/>
+      <c r="BK21" s="15"/>
       <c r="BL21" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="BM21" s="14" t="s">
+      <c r="BM21" s="13" t="s">
         <v>129</v>
       </c>
-      <c r="BN21" s="15"/>
-      <c r="BO21" s="16"/>
+      <c r="BN21" s="14"/>
+      <c r="BO21" s="15"/>
       <c r="BP21" s="8" t="s">
         <v>130</v>
       </c>
       <c r="BQ21" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="BR21" s="27"/>
+      <c r="BR21" s="24"/>
     </row>
     <row r="22" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B22" s="27"/>
-      <c r="AW22" s="14" t="s">
+      <c r="B22" s="24"/>
+      <c r="AW22" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="AX22" s="16"/>
-      <c r="AY22" s="14" t="s">
+      <c r="AX22" s="15"/>
+      <c r="AY22" s="13" t="s">
         <v>133</v>
       </c>
-      <c r="AZ22" s="15"/>
-      <c r="BA22" s="15"/>
-      <c r="BB22" s="16"/>
-      <c r="BC22" s="14" t="s">
+      <c r="AZ22" s="14"/>
+      <c r="BA22" s="14"/>
+      <c r="BB22" s="15"/>
+      <c r="BC22" s="13" t="s">
         <v>134</v>
       </c>
-      <c r="BD22" s="15"/>
-      <c r="BE22" s="16"/>
-      <c r="BF22" s="14" t="s">
+      <c r="BD22" s="14"/>
+      <c r="BE22" s="15"/>
+      <c r="BF22" s="13" t="s">
         <v>135</v>
       </c>
-      <c r="BG22" s="15"/>
-      <c r="BH22" s="15"/>
-      <c r="BI22" s="15"/>
-      <c r="BJ22" s="15"/>
-      <c r="BK22" s="16"/>
+      <c r="BG22" s="14"/>
+      <c r="BH22" s="14"/>
+      <c r="BI22" s="14"/>
+      <c r="BJ22" s="14"/>
+      <c r="BK22" s="15"/>
       <c r="BL22" s="8" t="s">
         <v>136</v>
       </c>
-      <c r="BM22" s="14" t="s">
+      <c r="BM22" s="13" t="s">
         <v>137</v>
       </c>
-      <c r="BN22" s="15"/>
-      <c r="BO22" s="16"/>
+      <c r="BN22" s="14"/>
+      <c r="BO22" s="15"/>
       <c r="BP22" s="8" t="s">
         <v>138</v>
       </c>
       <c r="BQ22" s="8" t="s">
         <v>139</v>
       </c>
-      <c r="BR22" s="27"/>
+      <c r="BR22" s="24"/>
     </row>
     <row r="23" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B23" s="27"/>
-      <c r="AW23" s="14" t="s">
+      <c r="B23" s="24"/>
+      <c r="AW23" s="13" t="s">
         <v>140</v>
       </c>
-      <c r="AX23" s="16"/>
-      <c r="AY23" s="14" t="s">
+      <c r="AX23" s="15"/>
+      <c r="AY23" s="13" t="s">
         <v>141</v>
       </c>
-      <c r="AZ23" s="15"/>
-      <c r="BA23" s="15"/>
-      <c r="BB23" s="16"/>
-      <c r="BC23" s="14" t="s">
+      <c r="AZ23" s="14"/>
+      <c r="BA23" s="14"/>
+      <c r="BB23" s="15"/>
+      <c r="BC23" s="13" t="s">
         <v>142</v>
       </c>
-      <c r="BD23" s="15"/>
-      <c r="BE23" s="16"/>
-      <c r="BF23" s="14" t="s">
+      <c r="BD23" s="14"/>
+      <c r="BE23" s="15"/>
+      <c r="BF23" s="13" t="s">
         <v>143</v>
       </c>
-      <c r="BG23" s="15"/>
-      <c r="BH23" s="15"/>
-      <c r="BI23" s="15"/>
-      <c r="BJ23" s="15"/>
-      <c r="BK23" s="16"/>
+      <c r="BG23" s="14"/>
+      <c r="BH23" s="14"/>
+      <c r="BI23" s="14"/>
+      <c r="BJ23" s="14"/>
+      <c r="BK23" s="15"/>
       <c r="BL23" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="BM23" s="14" t="s">
+      <c r="BM23" s="13" t="s">
         <v>145</v>
       </c>
-      <c r="BN23" s="15"/>
-      <c r="BO23" s="16"/>
+      <c r="BN23" s="14"/>
+      <c r="BO23" s="15"/>
       <c r="BP23" s="8" t="s">
         <v>146</v>
       </c>
       <c r="BQ23" s="8" t="s">
         <v>147</v>
       </c>
-      <c r="BR23" s="27"/>
+      <c r="BR23" s="24"/>
     </row>
     <row r="24" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B24" s="27"/>
-      <c r="AW24" s="14" t="s">
+      <c r="B24" s="24"/>
+      <c r="AW24" s="13" t="s">
         <v>148</v>
       </c>
-      <c r="AX24" s="16"/>
-      <c r="AY24" s="14" t="s">
+      <c r="AX24" s="15"/>
+      <c r="AY24" s="13" t="s">
         <v>149</v>
       </c>
-      <c r="AZ24" s="15"/>
-      <c r="BA24" s="15"/>
-      <c r="BB24" s="16"/>
-      <c r="BC24" s="14" t="s">
+      <c r="AZ24" s="14"/>
+      <c r="BA24" s="14"/>
+      <c r="BB24" s="15"/>
+      <c r="BC24" s="13" t="s">
         <v>150</v>
       </c>
-      <c r="BD24" s="15"/>
-      <c r="BE24" s="16"/>
-      <c r="BF24" s="14" t="s">
+      <c r="BD24" s="14"/>
+      <c r="BE24" s="15"/>
+      <c r="BF24" s="13" t="s">
         <v>151</v>
       </c>
-      <c r="BG24" s="15"/>
-      <c r="BH24" s="15"/>
-      <c r="BI24" s="15"/>
-      <c r="BJ24" s="15"/>
-      <c r="BK24" s="16"/>
+      <c r="BG24" s="14"/>
+      <c r="BH24" s="14"/>
+      <c r="BI24" s="14"/>
+      <c r="BJ24" s="14"/>
+      <c r="BK24" s="15"/>
       <c r="BL24" s="8" t="s">
         <v>152</v>
       </c>
-      <c r="BM24" s="14" t="s">
+      <c r="BM24" s="13" t="s">
         <v>153</v>
       </c>
-      <c r="BN24" s="15"/>
-      <c r="BO24" s="16"/>
+      <c r="BN24" s="14"/>
+      <c r="BO24" s="15"/>
       <c r="BP24" s="8" t="s">
         <v>154</v>
       </c>
       <c r="BQ24" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="BR24" s="27"/>
+      <c r="BR24" s="24"/>
     </row>
     <row r="25" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B25" s="27"/>
-      <c r="AW25" s="14" t="s">
+      <c r="B25" s="24"/>
+      <c r="AW25" s="13" t="s">
+        <v>219</v>
+      </c>
+      <c r="AX25" s="15"/>
+      <c r="AY25" s="33" t="s">
+        <v>156</v>
+      </c>
+      <c r="AZ25" s="34"/>
+      <c r="BA25" s="34"/>
+      <c r="BB25" s="35"/>
+      <c r="BC25" s="14" t="s">
         <v>220</v>
       </c>
-      <c r="AX25" s="16"/>
-      <c r="AY25" s="29" t="s">
-        <v>156</v>
-      </c>
-      <c r="AZ25" s="30"/>
-      <c r="BA25" s="30"/>
-      <c r="BB25" s="31"/>
-      <c r="BC25" s="15" t="s">
+      <c r="BD25" s="14"/>
+      <c r="BE25" s="15"/>
+      <c r="BF25" s="13" t="s">
         <v>221</v>
       </c>
-      <c r="BD25" s="15"/>
-      <c r="BE25" s="16"/>
-      <c r="BF25" s="14" t="s">
-        <v>222</v>
-      </c>
-      <c r="BG25" s="15"/>
-      <c r="BH25" s="15"/>
-      <c r="BI25" s="15"/>
-      <c r="BJ25" s="15"/>
-      <c r="BK25" s="16"/>
+      <c r="BG25" s="14"/>
+      <c r="BH25" s="14"/>
+      <c r="BI25" s="14"/>
+      <c r="BJ25" s="14"/>
+      <c r="BK25" s="15"/>
       <c r="BL25" s="8" t="s">
         <v>157</v>
       </c>
-      <c r="BM25" s="14" t="s">
-        <v>223</v>
-      </c>
-      <c r="BN25" s="15"/>
-      <c r="BO25" s="16"/>
+      <c r="BM25" s="13" t="s">
+        <v>222</v>
+      </c>
+      <c r="BN25" s="14"/>
+      <c r="BO25" s="15"/>
       <c r="BP25" s="8" t="s">
         <v>158</v>
       </c>
       <c r="BQ25" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="BR25" s="27"/>
+      <c r="BR25" s="24"/>
     </row>
     <row r="26" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B26" s="27"/>
-      <c r="E26" s="13" t="s">
-        <v>229</v>
-      </c>
-      <c r="F26" s="13"/>
-      <c r="G26" s="13"/>
-      <c r="H26" s="13"/>
-      <c r="I26" s="13"/>
-      <c r="J26" s="13"/>
-      <c r="K26" s="13"/>
-      <c r="L26" s="13"/>
-      <c r="M26" s="13"/>
-      <c r="N26" s="13"/>
-      <c r="O26" s="13"/>
-      <c r="P26" s="13"/>
-      <c r="Q26" s="13"/>
-      <c r="R26" s="13"/>
-      <c r="T26" s="13" t="s">
+      <c r="B26" s="24"/>
+      <c r="E26" s="16" t="s">
+        <v>228</v>
+      </c>
+      <c r="F26" s="16"/>
+      <c r="G26" s="16"/>
+      <c r="H26" s="16"/>
+      <c r="I26" s="16"/>
+      <c r="J26" s="16"/>
+      <c r="K26" s="16"/>
+      <c r="L26" s="16"/>
+      <c r="M26" s="16"/>
+      <c r="N26" s="16"/>
+      <c r="O26" s="16"/>
+      <c r="P26" s="16"/>
+      <c r="Q26" s="16"/>
+      <c r="R26" s="16"/>
+      <c r="T26" s="16" t="s">
         <v>171</v>
       </c>
-      <c r="U26" s="13"/>
-      <c r="V26" s="13"/>
-      <c r="W26" s="13"/>
-      <c r="X26" s="13"/>
-      <c r="Y26" s="13"/>
-      <c r="Z26" s="13"/>
-      <c r="AA26" s="13"/>
-      <c r="AB26" s="13"/>
-      <c r="AC26" s="13"/>
-      <c r="AD26" s="13"/>
-      <c r="AE26" s="13"/>
-      <c r="AF26" s="13"/>
-      <c r="AG26" s="13"/>
-      <c r="AW26" s="14" t="s">
+      <c r="U26" s="16"/>
+      <c r="V26" s="16"/>
+      <c r="W26" s="16"/>
+      <c r="X26" s="16"/>
+      <c r="Y26" s="16"/>
+      <c r="Z26" s="16"/>
+      <c r="AA26" s="16"/>
+      <c r="AB26" s="16"/>
+      <c r="AC26" s="16"/>
+      <c r="AD26" s="16"/>
+      <c r="AE26" s="16"/>
+      <c r="AF26" s="16"/>
+      <c r="AG26" s="16"/>
+      <c r="AW26" s="13" t="s">
         <v>160</v>
       </c>
-      <c r="AX26" s="16"/>
-      <c r="AY26" s="14" t="s">
+      <c r="AX26" s="15"/>
+      <c r="AY26" s="13" t="s">
         <v>161</v>
       </c>
-      <c r="AZ26" s="15"/>
-      <c r="BA26" s="15"/>
-      <c r="BB26" s="16"/>
-      <c r="BC26" s="14" t="s">
+      <c r="AZ26" s="14"/>
+      <c r="BA26" s="14"/>
+      <c r="BB26" s="15"/>
+      <c r="BC26" s="13" t="s">
         <v>162</v>
       </c>
-      <c r="BD26" s="15"/>
-      <c r="BE26" s="16"/>
-      <c r="BF26" s="14" t="s">
+      <c r="BD26" s="14"/>
+      <c r="BE26" s="15"/>
+      <c r="BF26" s="13" t="s">
         <v>163</v>
       </c>
-      <c r="BG26" s="15"/>
-      <c r="BH26" s="15"/>
-      <c r="BI26" s="15"/>
-      <c r="BJ26" s="15"/>
-      <c r="BK26" s="16"/>
+      <c r="BG26" s="14"/>
+      <c r="BH26" s="14"/>
+      <c r="BI26" s="14"/>
+      <c r="BJ26" s="14"/>
+      <c r="BK26" s="15"/>
       <c r="BL26" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="BM26" s="14" t="s">
+      <c r="BM26" s="13" t="s">
         <v>165</v>
       </c>
-      <c r="BN26" s="15"/>
-      <c r="BO26" s="16"/>
+      <c r="BN26" s="14"/>
+      <c r="BO26" s="15"/>
       <c r="BP26" s="7" t="s">
         <v>166</v>
       </c>
       <c r="BQ26" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="BR26" s="27"/>
+      <c r="BR26" s="24"/>
     </row>
     <row r="27" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B27" s="27"/>
-      <c r="E27" s="13"/>
-      <c r="F27" s="13"/>
-      <c r="G27" s="13"/>
-      <c r="H27" s="13"/>
-      <c r="I27" s="13"/>
-      <c r="J27" s="13"/>
-      <c r="K27" s="13"/>
-      <c r="L27" s="13"/>
-      <c r="M27" s="13"/>
-      <c r="N27" s="13"/>
-      <c r="O27" s="13"/>
-      <c r="P27" s="13"/>
-      <c r="Q27" s="13"/>
-      <c r="R27" s="13"/>
-      <c r="T27" s="13"/>
-      <c r="U27" s="13"/>
-      <c r="V27" s="13"/>
-      <c r="W27" s="13"/>
-      <c r="X27" s="13"/>
-      <c r="Y27" s="13"/>
-      <c r="Z27" s="13"/>
-      <c r="AA27" s="13"/>
-      <c r="AB27" s="13"/>
-      <c r="AC27" s="13"/>
-      <c r="AD27" s="13"/>
-      <c r="AE27" s="13"/>
-      <c r="AF27" s="13"/>
-      <c r="AG27" s="13"/>
+      <c r="B27" s="24"/>
+      <c r="E27" s="16"/>
+      <c r="F27" s="16"/>
+      <c r="G27" s="16"/>
+      <c r="H27" s="16"/>
+      <c r="I27" s="16"/>
+      <c r="J27" s="16"/>
+      <c r="K27" s="16"/>
+      <c r="L27" s="16"/>
+      <c r="M27" s="16"/>
+      <c r="N27" s="16"/>
+      <c r="O27" s="16"/>
+      <c r="P27" s="16"/>
+      <c r="Q27" s="16"/>
+      <c r="R27" s="16"/>
+      <c r="T27" s="16"/>
+      <c r="U27" s="16"/>
+      <c r="V27" s="16"/>
+      <c r="W27" s="16"/>
+      <c r="X27" s="16"/>
+      <c r="Y27" s="16"/>
+      <c r="Z27" s="16"/>
+      <c r="AA27" s="16"/>
+      <c r="AB27" s="16"/>
+      <c r="AC27" s="16"/>
+      <c r="AD27" s="16"/>
+      <c r="AE27" s="16"/>
+      <c r="AF27" s="16"/>
+      <c r="AG27" s="16"/>
       <c r="BQ27" s="6"/>
-      <c r="BR27" s="27"/>
+      <c r="BR27" s="24"/>
     </row>
     <row r="28" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B28" s="27"/>
-      <c r="E28" s="13"/>
-      <c r="F28" s="13"/>
-      <c r="G28" s="13"/>
-      <c r="H28" s="13"/>
-      <c r="I28" s="13"/>
-      <c r="J28" s="13"/>
-      <c r="K28" s="13"/>
-      <c r="L28" s="13"/>
-      <c r="M28" s="13"/>
-      <c r="N28" s="13"/>
-      <c r="O28" s="13"/>
-      <c r="P28" s="13"/>
-      <c r="Q28" s="13"/>
-      <c r="R28" s="13"/>
-      <c r="T28" s="13"/>
-      <c r="U28" s="13"/>
-      <c r="V28" s="13"/>
-      <c r="W28" s="13"/>
-      <c r="X28" s="13"/>
-      <c r="Y28" s="13"/>
-      <c r="Z28" s="13"/>
-      <c r="AA28" s="13"/>
-      <c r="AB28" s="13"/>
-      <c r="AC28" s="13"/>
-      <c r="AD28" s="13"/>
-      <c r="AE28" s="13"/>
-      <c r="AF28" s="13"/>
-      <c r="AG28" s="13"/>
+      <c r="B28" s="24"/>
+      <c r="E28" s="16"/>
+      <c r="F28" s="16"/>
+      <c r="G28" s="16"/>
+      <c r="H28" s="16"/>
+      <c r="I28" s="16"/>
+      <c r="J28" s="16"/>
+      <c r="K28" s="16"/>
+      <c r="L28" s="16"/>
+      <c r="M28" s="16"/>
+      <c r="N28" s="16"/>
+      <c r="O28" s="16"/>
+      <c r="P28" s="16"/>
+      <c r="Q28" s="16"/>
+      <c r="R28" s="16"/>
+      <c r="T28" s="16"/>
+      <c r="U28" s="16"/>
+      <c r="V28" s="16"/>
+      <c r="W28" s="16"/>
+      <c r="X28" s="16"/>
+      <c r="Y28" s="16"/>
+      <c r="Z28" s="16"/>
+      <c r="AA28" s="16"/>
+      <c r="AB28" s="16"/>
+      <c r="AC28" s="16"/>
+      <c r="AD28" s="16"/>
+      <c r="AE28" s="16"/>
+      <c r="AF28" s="16"/>
+      <c r="AG28" s="16"/>
       <c r="AI28" s="3"/>
       <c r="AV28" s="6"/>
       <c r="AW28" s="9"/>
@@ -2880,51 +2881,51 @@
       <c r="BO28" s="9"/>
       <c r="BP28" s="9"/>
       <c r="BQ28" s="9"/>
-      <c r="BR28" s="27"/>
+      <c r="BR28" s="24"/>
     </row>
     <row r="29" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B29" s="28"/>
-      <c r="E29" s="13"/>
-      <c r="F29" s="13"/>
-      <c r="G29" s="13"/>
-      <c r="H29" s="13"/>
-      <c r="I29" s="13"/>
-      <c r="J29" s="13"/>
-      <c r="K29" s="13"/>
-      <c r="L29" s="13"/>
-      <c r="M29" s="13"/>
-      <c r="N29" s="13"/>
-      <c r="O29" s="13"/>
-      <c r="P29" s="13"/>
-      <c r="Q29" s="13"/>
-      <c r="R29" s="13"/>
-      <c r="T29" s="13"/>
-      <c r="U29" s="13"/>
-      <c r="V29" s="13"/>
-      <c r="W29" s="13"/>
-      <c r="X29" s="13"/>
-      <c r="Y29" s="13"/>
-      <c r="Z29" s="13"/>
-      <c r="AA29" s="13"/>
-      <c r="AB29" s="13"/>
-      <c r="AC29" s="13"/>
-      <c r="AD29" s="13"/>
-      <c r="AE29" s="13"/>
-      <c r="AF29" s="13"/>
-      <c r="AG29" s="13"/>
+      <c r="B29" s="25"/>
+      <c r="E29" s="16"/>
+      <c r="F29" s="16"/>
+      <c r="G29" s="16"/>
+      <c r="H29" s="16"/>
+      <c r="I29" s="16"/>
+      <c r="J29" s="16"/>
+      <c r="K29" s="16"/>
+      <c r="L29" s="16"/>
+      <c r="M29" s="16"/>
+      <c r="N29" s="16"/>
+      <c r="O29" s="16"/>
+      <c r="P29" s="16"/>
+      <c r="Q29" s="16"/>
+      <c r="R29" s="16"/>
+      <c r="T29" s="16"/>
+      <c r="U29" s="16"/>
+      <c r="V29" s="16"/>
+      <c r="W29" s="16"/>
+      <c r="X29" s="16"/>
+      <c r="Y29" s="16"/>
+      <c r="Z29" s="16"/>
+      <c r="AA29" s="16"/>
+      <c r="AB29" s="16"/>
+      <c r="AC29" s="16"/>
+      <c r="AD29" s="16"/>
+      <c r="AE29" s="16"/>
+      <c r="AF29" s="16"/>
+      <c r="AG29" s="16"/>
       <c r="BQ29" s="6"/>
-      <c r="BR29" s="28"/>
+      <c r="BR29" s="25"/>
     </row>
     <row r="30" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B30" s="26" t="s">
+      <c r="B30" s="23" t="s">
         <v>168</v>
       </c>
-      <c r="BR30" s="26" t="s">
+      <c r="BR30" s="23" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="31" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B31" s="27"/>
+      <c r="B31" s="24"/>
       <c r="AW31" s="17" t="s">
         <v>169</v>
       </c>
@@ -2950,172 +2951,172 @@
       <c r="BO31" s="18"/>
       <c r="BP31" s="18"/>
       <c r="BQ31" s="19"/>
-      <c r="BR31" s="27"/>
+      <c r="BR31" s="24"/>
     </row>
     <row r="32" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B32" s="27"/>
+      <c r="B32" s="24"/>
       <c r="E32" s="3"/>
       <c r="AA32" s="3"/>
-      <c r="AW32" s="23"/>
-      <c r="AX32" s="24"/>
-      <c r="AY32" s="24"/>
-      <c r="AZ32" s="24"/>
-      <c r="BA32" s="24"/>
-      <c r="BB32" s="24"/>
-      <c r="BC32" s="24"/>
-      <c r="BD32" s="24"/>
-      <c r="BE32" s="24"/>
-      <c r="BF32" s="24"/>
-      <c r="BG32" s="24"/>
-      <c r="BH32" s="24"/>
-      <c r="BI32" s="24"/>
-      <c r="BJ32" s="24"/>
-      <c r="BK32" s="24"/>
-      <c r="BL32" s="24"/>
-      <c r="BM32" s="24"/>
-      <c r="BN32" s="24"/>
-      <c r="BO32" s="24"/>
-      <c r="BP32" s="24"/>
-      <c r="BQ32" s="25"/>
-      <c r="BR32" s="27"/>
+      <c r="AW32" s="26"/>
+      <c r="AX32" s="27"/>
+      <c r="AY32" s="27"/>
+      <c r="AZ32" s="27"/>
+      <c r="BA32" s="27"/>
+      <c r="BB32" s="27"/>
+      <c r="BC32" s="27"/>
+      <c r="BD32" s="27"/>
+      <c r="BE32" s="27"/>
+      <c r="BF32" s="27"/>
+      <c r="BG32" s="27"/>
+      <c r="BH32" s="27"/>
+      <c r="BI32" s="27"/>
+      <c r="BJ32" s="27"/>
+      <c r="BK32" s="27"/>
+      <c r="BL32" s="27"/>
+      <c r="BM32" s="27"/>
+      <c r="BN32" s="27"/>
+      <c r="BO32" s="27"/>
+      <c r="BP32" s="27"/>
+      <c r="BQ32" s="28"/>
+      <c r="BR32" s="24"/>
     </row>
     <row r="33" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B33" s="27"/>
-      <c r="AW33" s="23"/>
-      <c r="AX33" s="24"/>
-      <c r="AY33" s="24"/>
-      <c r="AZ33" s="24"/>
-      <c r="BA33" s="24"/>
-      <c r="BB33" s="24"/>
-      <c r="BC33" s="24"/>
-      <c r="BD33" s="24"/>
-      <c r="BE33" s="24"/>
-      <c r="BF33" s="24"/>
-      <c r="BG33" s="24"/>
-      <c r="BH33" s="24"/>
-      <c r="BI33" s="24"/>
-      <c r="BJ33" s="24"/>
-      <c r="BK33" s="24"/>
-      <c r="BL33" s="24"/>
-      <c r="BM33" s="24"/>
-      <c r="BN33" s="24"/>
-      <c r="BO33" s="24"/>
-      <c r="BP33" s="24"/>
-      <c r="BQ33" s="25"/>
-      <c r="BR33" s="27"/>
+      <c r="B33" s="24"/>
+      <c r="AW33" s="26"/>
+      <c r="AX33" s="27"/>
+      <c r="AY33" s="27"/>
+      <c r="AZ33" s="27"/>
+      <c r="BA33" s="27"/>
+      <c r="BB33" s="27"/>
+      <c r="BC33" s="27"/>
+      <c r="BD33" s="27"/>
+      <c r="BE33" s="27"/>
+      <c r="BF33" s="27"/>
+      <c r="BG33" s="27"/>
+      <c r="BH33" s="27"/>
+      <c r="BI33" s="27"/>
+      <c r="BJ33" s="27"/>
+      <c r="BK33" s="27"/>
+      <c r="BL33" s="27"/>
+      <c r="BM33" s="27"/>
+      <c r="BN33" s="27"/>
+      <c r="BO33" s="27"/>
+      <c r="BP33" s="27"/>
+      <c r="BQ33" s="28"/>
+      <c r="BR33" s="24"/>
     </row>
     <row r="34" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B34" s="27"/>
-      <c r="AW34" s="23"/>
-      <c r="AX34" s="24"/>
-      <c r="AY34" s="24"/>
-      <c r="AZ34" s="24"/>
-      <c r="BA34" s="24"/>
-      <c r="BB34" s="24"/>
-      <c r="BC34" s="24"/>
-      <c r="BD34" s="24"/>
-      <c r="BE34" s="24"/>
-      <c r="BF34" s="24"/>
-      <c r="BG34" s="24"/>
-      <c r="BH34" s="24"/>
-      <c r="BI34" s="24"/>
-      <c r="BJ34" s="24"/>
-      <c r="BK34" s="24"/>
-      <c r="BL34" s="24"/>
-      <c r="BM34" s="24"/>
-      <c r="BN34" s="24"/>
-      <c r="BO34" s="24"/>
-      <c r="BP34" s="24"/>
-      <c r="BQ34" s="25"/>
-      <c r="BR34" s="27"/>
+      <c r="B34" s="24"/>
+      <c r="AW34" s="26"/>
+      <c r="AX34" s="27"/>
+      <c r="AY34" s="27"/>
+      <c r="AZ34" s="27"/>
+      <c r="BA34" s="27"/>
+      <c r="BB34" s="27"/>
+      <c r="BC34" s="27"/>
+      <c r="BD34" s="27"/>
+      <c r="BE34" s="27"/>
+      <c r="BF34" s="27"/>
+      <c r="BG34" s="27"/>
+      <c r="BH34" s="27"/>
+      <c r="BI34" s="27"/>
+      <c r="BJ34" s="27"/>
+      <c r="BK34" s="27"/>
+      <c r="BL34" s="27"/>
+      <c r="BM34" s="27"/>
+      <c r="BN34" s="27"/>
+      <c r="BO34" s="27"/>
+      <c r="BP34" s="27"/>
+      <c r="BQ34" s="28"/>
+      <c r="BR34" s="24"/>
     </row>
     <row r="35" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B35" s="27"/>
-      <c r="E35" s="13" t="s">
-        <v>230</v>
-      </c>
-      <c r="F35" s="13"/>
-      <c r="G35" s="13"/>
-      <c r="H35" s="13"/>
-      <c r="I35" s="13"/>
-      <c r="J35" s="13"/>
-      <c r="K35" s="13"/>
-      <c r="L35" s="13"/>
-      <c r="M35" s="13"/>
-      <c r="N35" s="13"/>
-      <c r="O35" s="13"/>
-      <c r="P35" s="13"/>
-      <c r="Q35" s="13"/>
-      <c r="R35" s="13"/>
-      <c r="T35" s="13" t="s">
+      <c r="B35" s="24"/>
+      <c r="E35" s="16" t="s">
+        <v>229</v>
+      </c>
+      <c r="F35" s="16"/>
+      <c r="G35" s="16"/>
+      <c r="H35" s="16"/>
+      <c r="I35" s="16"/>
+      <c r="J35" s="16"/>
+      <c r="K35" s="16"/>
+      <c r="L35" s="16"/>
+      <c r="M35" s="16"/>
+      <c r="N35" s="16"/>
+      <c r="O35" s="16"/>
+      <c r="P35" s="16"/>
+      <c r="Q35" s="16"/>
+      <c r="R35" s="16"/>
+      <c r="T35" s="16" t="s">
         <v>172</v>
       </c>
-      <c r="U35" s="13"/>
-      <c r="V35" s="13"/>
-      <c r="W35" s="13"/>
-      <c r="X35" s="13"/>
-      <c r="Y35" s="13"/>
-      <c r="Z35" s="13"/>
-      <c r="AA35" s="13"/>
-      <c r="AB35" s="13"/>
-      <c r="AC35" s="13"/>
-      <c r="AD35" s="13"/>
-      <c r="AE35" s="13"/>
-      <c r="AF35" s="13"/>
-      <c r="AG35" s="13"/>
-      <c r="AW35" s="23"/>
-      <c r="AX35" s="24"/>
-      <c r="AY35" s="24"/>
-      <c r="AZ35" s="24"/>
-      <c r="BA35" s="24"/>
-      <c r="BB35" s="24"/>
-      <c r="BC35" s="24"/>
-      <c r="BD35" s="24"/>
-      <c r="BE35" s="24"/>
-      <c r="BF35" s="24"/>
-      <c r="BG35" s="24"/>
-      <c r="BH35" s="24"/>
-      <c r="BI35" s="24"/>
-      <c r="BJ35" s="24"/>
-      <c r="BK35" s="24"/>
-      <c r="BL35" s="24"/>
-      <c r="BM35" s="24"/>
-      <c r="BN35" s="24"/>
-      <c r="BO35" s="24"/>
-      <c r="BP35" s="24"/>
-      <c r="BQ35" s="25"/>
-      <c r="BR35" s="27"/>
+      <c r="U35" s="16"/>
+      <c r="V35" s="16"/>
+      <c r="W35" s="16"/>
+      <c r="X35" s="16"/>
+      <c r="Y35" s="16"/>
+      <c r="Z35" s="16"/>
+      <c r="AA35" s="16"/>
+      <c r="AB35" s="16"/>
+      <c r="AC35" s="16"/>
+      <c r="AD35" s="16"/>
+      <c r="AE35" s="16"/>
+      <c r="AF35" s="16"/>
+      <c r="AG35" s="16"/>
+      <c r="AW35" s="26"/>
+      <c r="AX35" s="27"/>
+      <c r="AY35" s="27"/>
+      <c r="AZ35" s="27"/>
+      <c r="BA35" s="27"/>
+      <c r="BB35" s="27"/>
+      <c r="BC35" s="27"/>
+      <c r="BD35" s="27"/>
+      <c r="BE35" s="27"/>
+      <c r="BF35" s="27"/>
+      <c r="BG35" s="27"/>
+      <c r="BH35" s="27"/>
+      <c r="BI35" s="27"/>
+      <c r="BJ35" s="27"/>
+      <c r="BK35" s="27"/>
+      <c r="BL35" s="27"/>
+      <c r="BM35" s="27"/>
+      <c r="BN35" s="27"/>
+      <c r="BO35" s="27"/>
+      <c r="BP35" s="27"/>
+      <c r="BQ35" s="28"/>
+      <c r="BR35" s="24"/>
     </row>
     <row r="36" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B36" s="27"/>
-      <c r="E36" s="13"/>
-      <c r="F36" s="13"/>
-      <c r="G36" s="13"/>
-      <c r="H36" s="13"/>
-      <c r="I36" s="13"/>
-      <c r="J36" s="13"/>
-      <c r="K36" s="13"/>
-      <c r="L36" s="13"/>
-      <c r="M36" s="13"/>
-      <c r="N36" s="13"/>
-      <c r="O36" s="13"/>
-      <c r="P36" s="13"/>
-      <c r="Q36" s="13"/>
-      <c r="R36" s="13"/>
-      <c r="T36" s="13"/>
-      <c r="U36" s="13"/>
-      <c r="V36" s="13"/>
-      <c r="W36" s="13"/>
-      <c r="X36" s="13"/>
-      <c r="Y36" s="13"/>
-      <c r="Z36" s="13"/>
-      <c r="AA36" s="13"/>
-      <c r="AB36" s="13"/>
-      <c r="AC36" s="13"/>
-      <c r="AD36" s="13"/>
-      <c r="AE36" s="13"/>
-      <c r="AF36" s="13"/>
-      <c r="AG36" s="13"/>
+      <c r="B36" s="24"/>
+      <c r="E36" s="16"/>
+      <c r="F36" s="16"/>
+      <c r="G36" s="16"/>
+      <c r="H36" s="16"/>
+      <c r="I36" s="16"/>
+      <c r="J36" s="16"/>
+      <c r="K36" s="16"/>
+      <c r="L36" s="16"/>
+      <c r="M36" s="16"/>
+      <c r="N36" s="16"/>
+      <c r="O36" s="16"/>
+      <c r="P36" s="16"/>
+      <c r="Q36" s="16"/>
+      <c r="R36" s="16"/>
+      <c r="T36" s="16"/>
+      <c r="U36" s="16"/>
+      <c r="V36" s="16"/>
+      <c r="W36" s="16"/>
+      <c r="X36" s="16"/>
+      <c r="Y36" s="16"/>
+      <c r="Z36" s="16"/>
+      <c r="AA36" s="16"/>
+      <c r="AB36" s="16"/>
+      <c r="AC36" s="16"/>
+      <c r="AD36" s="16"/>
+      <c r="AE36" s="16"/>
+      <c r="AF36" s="16"/>
+      <c r="AG36" s="16"/>
       <c r="AW36" s="20"/>
       <c r="AX36" s="21"/>
       <c r="AY36" s="21"/>
@@ -3137,251 +3138,251 @@
       <c r="BO36" s="21"/>
       <c r="BP36" s="21"/>
       <c r="BQ36" s="22"/>
-      <c r="BR36" s="27"/>
+      <c r="BR36" s="24"/>
     </row>
     <row r="37" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B37" s="27"/>
-      <c r="E37" s="13"/>
-      <c r="F37" s="13"/>
-      <c r="G37" s="13"/>
-      <c r="H37" s="13"/>
-      <c r="I37" s="13"/>
-      <c r="J37" s="13"/>
-      <c r="K37" s="13"/>
-      <c r="L37" s="13"/>
-      <c r="M37" s="13"/>
-      <c r="N37" s="13"/>
-      <c r="O37" s="13"/>
-      <c r="P37" s="13"/>
-      <c r="Q37" s="13"/>
-      <c r="R37" s="13"/>
-      <c r="T37" s="13"/>
-      <c r="U37" s="13"/>
-      <c r="V37" s="13"/>
-      <c r="W37" s="13"/>
-      <c r="X37" s="13"/>
-      <c r="Y37" s="13"/>
-      <c r="Z37" s="13"/>
-      <c r="AA37" s="13"/>
-      <c r="AB37" s="13"/>
-      <c r="AC37" s="13"/>
-      <c r="AD37" s="13"/>
-      <c r="AE37" s="13"/>
-      <c r="AF37" s="13"/>
-      <c r="AG37" s="13"/>
-      <c r="BR37" s="27"/>
+      <c r="B37" s="24"/>
+      <c r="E37" s="16"/>
+      <c r="F37" s="16"/>
+      <c r="G37" s="16"/>
+      <c r="H37" s="16"/>
+      <c r="I37" s="16"/>
+      <c r="J37" s="16"/>
+      <c r="K37" s="16"/>
+      <c r="L37" s="16"/>
+      <c r="M37" s="16"/>
+      <c r="N37" s="16"/>
+      <c r="O37" s="16"/>
+      <c r="P37" s="16"/>
+      <c r="Q37" s="16"/>
+      <c r="R37" s="16"/>
+      <c r="T37" s="16"/>
+      <c r="U37" s="16"/>
+      <c r="V37" s="16"/>
+      <c r="W37" s="16"/>
+      <c r="X37" s="16"/>
+      <c r="Y37" s="16"/>
+      <c r="Z37" s="16"/>
+      <c r="AA37" s="16"/>
+      <c r="AB37" s="16"/>
+      <c r="AC37" s="16"/>
+      <c r="AD37" s="16"/>
+      <c r="AE37" s="16"/>
+      <c r="AF37" s="16"/>
+      <c r="AG37" s="16"/>
+      <c r="BR37" s="24"/>
     </row>
     <row r="38" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B38" s="27"/>
-      <c r="E38" s="13"/>
-      <c r="F38" s="13"/>
-      <c r="G38" s="13"/>
-      <c r="H38" s="13"/>
-      <c r="I38" s="13"/>
-      <c r="J38" s="13"/>
-      <c r="K38" s="13"/>
-      <c r="L38" s="13"/>
-      <c r="M38" s="13"/>
-      <c r="N38" s="13"/>
-      <c r="O38" s="13"/>
-      <c r="P38" s="13"/>
-      <c r="Q38" s="13"/>
-      <c r="R38" s="13"/>
-      <c r="T38" s="13"/>
-      <c r="U38" s="13"/>
-      <c r="V38" s="13"/>
-      <c r="W38" s="13"/>
-      <c r="X38" s="13"/>
-      <c r="Y38" s="13"/>
-      <c r="Z38" s="13"/>
-      <c r="AA38" s="13"/>
-      <c r="AB38" s="13"/>
-      <c r="AC38" s="13"/>
-      <c r="AD38" s="13"/>
-      <c r="AE38" s="13"/>
-      <c r="AF38" s="13"/>
-      <c r="AG38" s="13"/>
-      <c r="BR38" s="27"/>
+      <c r="B38" s="24"/>
+      <c r="E38" s="16"/>
+      <c r="F38" s="16"/>
+      <c r="G38" s="16"/>
+      <c r="H38" s="16"/>
+      <c r="I38" s="16"/>
+      <c r="J38" s="16"/>
+      <c r="K38" s="16"/>
+      <c r="L38" s="16"/>
+      <c r="M38" s="16"/>
+      <c r="N38" s="16"/>
+      <c r="O38" s="16"/>
+      <c r="P38" s="16"/>
+      <c r="Q38" s="16"/>
+      <c r="R38" s="16"/>
+      <c r="T38" s="16"/>
+      <c r="U38" s="16"/>
+      <c r="V38" s="16"/>
+      <c r="W38" s="16"/>
+      <c r="X38" s="16"/>
+      <c r="Y38" s="16"/>
+      <c r="Z38" s="16"/>
+      <c r="AA38" s="16"/>
+      <c r="AB38" s="16"/>
+      <c r="AC38" s="16"/>
+      <c r="AD38" s="16"/>
+      <c r="AE38" s="16"/>
+      <c r="AF38" s="16"/>
+      <c r="AG38" s="16"/>
+      <c r="BR38" s="24"/>
     </row>
     <row r="39" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B39" s="27"/>
-      <c r="E39" s="13"/>
-      <c r="F39" s="13"/>
-      <c r="G39" s="13"/>
-      <c r="H39" s="13"/>
-      <c r="I39" s="13"/>
-      <c r="J39" s="13"/>
-      <c r="K39" s="13"/>
-      <c r="L39" s="13"/>
-      <c r="M39" s="13"/>
-      <c r="N39" s="13"/>
-      <c r="O39" s="13"/>
-      <c r="P39" s="13"/>
-      <c r="Q39" s="13"/>
-      <c r="R39" s="13"/>
-      <c r="T39" s="13"/>
-      <c r="U39" s="13"/>
-      <c r="V39" s="13"/>
-      <c r="W39" s="13"/>
-      <c r="X39" s="13"/>
-      <c r="Y39" s="13"/>
-      <c r="Z39" s="13"/>
-      <c r="AA39" s="13"/>
-      <c r="AB39" s="13"/>
-      <c r="AC39" s="13"/>
-      <c r="AD39" s="13"/>
-      <c r="AE39" s="13"/>
-      <c r="AF39" s="13"/>
-      <c r="AG39" s="13"/>
+      <c r="B39" s="24"/>
+      <c r="E39" s="16"/>
+      <c r="F39" s="16"/>
+      <c r="G39" s="16"/>
+      <c r="H39" s="16"/>
+      <c r="I39" s="16"/>
+      <c r="J39" s="16"/>
+      <c r="K39" s="16"/>
+      <c r="L39" s="16"/>
+      <c r="M39" s="16"/>
+      <c r="N39" s="16"/>
+      <c r="O39" s="16"/>
+      <c r="P39" s="16"/>
+      <c r="Q39" s="16"/>
+      <c r="R39" s="16"/>
+      <c r="T39" s="16"/>
+      <c r="U39" s="16"/>
+      <c r="V39" s="16"/>
+      <c r="W39" s="16"/>
+      <c r="X39" s="16"/>
+      <c r="Y39" s="16"/>
+      <c r="Z39" s="16"/>
+      <c r="AA39" s="16"/>
+      <c r="AB39" s="16"/>
+      <c r="AC39" s="16"/>
+      <c r="AD39" s="16"/>
+      <c r="AE39" s="16"/>
+      <c r="AF39" s="16"/>
+      <c r="AG39" s="16"/>
       <c r="AW39" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="AX39" s="14" t="s">
+      <c r="AX39" s="13" t="s">
         <v>174</v>
       </c>
-      <c r="AY39" s="15"/>
-      <c r="AZ39" s="16"/>
-      <c r="BA39" s="14" t="s">
+      <c r="AY39" s="14"/>
+      <c r="AZ39" s="15"/>
+      <c r="BA39" s="13" t="s">
         <v>175</v>
       </c>
-      <c r="BB39" s="15"/>
-      <c r="BC39" s="15"/>
-      <c r="BD39" s="15"/>
-      <c r="BE39" s="15"/>
-      <c r="BF39" s="15"/>
-      <c r="BG39" s="15"/>
-      <c r="BH39" s="16"/>
-      <c r="BI39" s="14" t="s">
+      <c r="BB39" s="14"/>
+      <c r="BC39" s="14"/>
+      <c r="BD39" s="14"/>
+      <c r="BE39" s="14"/>
+      <c r="BF39" s="14"/>
+      <c r="BG39" s="14"/>
+      <c r="BH39" s="15"/>
+      <c r="BI39" s="13" t="s">
         <v>176</v>
       </c>
-      <c r="BJ39" s="15"/>
-      <c r="BK39" s="16"/>
-      <c r="BL39" s="14" t="s">
+      <c r="BJ39" s="14"/>
+      <c r="BK39" s="15"/>
+      <c r="BL39" s="13" t="s">
         <v>177</v>
       </c>
-      <c r="BM39" s="15"/>
-      <c r="BN39" s="16"/>
-      <c r="BO39" s="14" t="s">
+      <c r="BM39" s="14"/>
+      <c r="BN39" s="15"/>
+      <c r="BO39" s="13" t="s">
         <v>178</v>
       </c>
-      <c r="BP39" s="15"/>
-      <c r="BQ39" s="16"/>
-      <c r="BR39" s="27"/>
+      <c r="BP39" s="14"/>
+      <c r="BQ39" s="15"/>
+      <c r="BR39" s="24"/>
     </row>
     <row r="40" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B40" s="27"/>
+      <c r="B40" s="24"/>
       <c r="AW40" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="AX40" s="14" t="s">
+      <c r="AX40" s="13" t="s">
         <v>180</v>
       </c>
-      <c r="AY40" s="15"/>
-      <c r="AZ40" s="16"/>
-      <c r="BA40" s="14" t="s">
+      <c r="AY40" s="14"/>
+      <c r="AZ40" s="15"/>
+      <c r="BA40" s="13" t="s">
         <v>181</v>
       </c>
-      <c r="BB40" s="15"/>
-      <c r="BC40" s="15"/>
-      <c r="BD40" s="15"/>
-      <c r="BE40" s="15"/>
-      <c r="BF40" s="15"/>
-      <c r="BG40" s="15"/>
-      <c r="BH40" s="16"/>
-      <c r="BI40" s="14" t="s">
+      <c r="BB40" s="14"/>
+      <c r="BC40" s="14"/>
+      <c r="BD40" s="14"/>
+      <c r="BE40" s="14"/>
+      <c r="BF40" s="14"/>
+      <c r="BG40" s="14"/>
+      <c r="BH40" s="15"/>
+      <c r="BI40" s="13" t="s">
         <v>182</v>
       </c>
-      <c r="BJ40" s="15"/>
-      <c r="BK40" s="16"/>
-      <c r="BL40" s="14" t="s">
+      <c r="BJ40" s="14"/>
+      <c r="BK40" s="15"/>
+      <c r="BL40" s="13" t="s">
         <v>183</v>
       </c>
-      <c r="BM40" s="15"/>
-      <c r="BN40" s="16"/>
-      <c r="BO40" s="14" t="s">
+      <c r="BM40" s="14"/>
+      <c r="BN40" s="15"/>
+      <c r="BO40" s="13" t="s">
         <v>184</v>
       </c>
-      <c r="BP40" s="15"/>
-      <c r="BQ40" s="16"/>
-      <c r="BR40" s="27"/>
+      <c r="BP40" s="14"/>
+      <c r="BQ40" s="15"/>
+      <c r="BR40" s="24"/>
     </row>
     <row r="41" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B41" s="27"/>
+      <c r="B41" s="24"/>
       <c r="AW41" s="5" t="s">
         <v>185</v>
       </c>
-      <c r="AX41" s="14" t="s">
+      <c r="AX41" s="13" t="s">
         <v>186</v>
       </c>
-      <c r="AY41" s="15"/>
-      <c r="AZ41" s="16"/>
-      <c r="BA41" s="14" t="s">
+      <c r="AY41" s="14"/>
+      <c r="AZ41" s="15"/>
+      <c r="BA41" s="13" t="s">
         <v>187</v>
       </c>
-      <c r="BB41" s="15"/>
-      <c r="BC41" s="15"/>
-      <c r="BD41" s="15"/>
-      <c r="BE41" s="15"/>
-      <c r="BF41" s="15"/>
-      <c r="BG41" s="15"/>
-      <c r="BH41" s="16"/>
-      <c r="BI41" s="14" t="s">
+      <c r="BB41" s="14"/>
+      <c r="BC41" s="14"/>
+      <c r="BD41" s="14"/>
+      <c r="BE41" s="14"/>
+      <c r="BF41" s="14"/>
+      <c r="BG41" s="14"/>
+      <c r="BH41" s="15"/>
+      <c r="BI41" s="13" t="s">
         <v>188</v>
       </c>
-      <c r="BJ41" s="15"/>
-      <c r="BK41" s="16"/>
-      <c r="BL41" s="14" t="s">
+      <c r="BJ41" s="14"/>
+      <c r="BK41" s="15"/>
+      <c r="BL41" s="13" t="s">
         <v>189</v>
       </c>
-      <c r="BM41" s="15"/>
-      <c r="BN41" s="16"/>
-      <c r="BO41" s="14" t="s">
+      <c r="BM41" s="14"/>
+      <c r="BN41" s="15"/>
+      <c r="BO41" s="13" t="s">
         <v>190</v>
       </c>
-      <c r="BP41" s="15"/>
-      <c r="BQ41" s="16"/>
-      <c r="BR41" s="27"/>
+      <c r="BP41" s="14"/>
+      <c r="BQ41" s="15"/>
+      <c r="BR41" s="24"/>
     </row>
     <row r="42" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B42" s="27"/>
+      <c r="B42" s="24"/>
       <c r="AW42" s="5" t="s">
         <v>191</v>
       </c>
-      <c r="AX42" s="14" t="s">
+      <c r="AX42" s="13" t="s">
         <v>192</v>
       </c>
-      <c r="AY42" s="15"/>
-      <c r="AZ42" s="16"/>
-      <c r="BA42" s="14" t="s">
+      <c r="AY42" s="14"/>
+      <c r="AZ42" s="15"/>
+      <c r="BA42" s="13" t="s">
         <v>193</v>
       </c>
-      <c r="BB42" s="15"/>
-      <c r="BC42" s="15"/>
-      <c r="BD42" s="15"/>
-      <c r="BE42" s="15"/>
-      <c r="BF42" s="15"/>
-      <c r="BG42" s="15"/>
-      <c r="BH42" s="16"/>
-      <c r="BI42" s="14" t="s">
+      <c r="BB42" s="14"/>
+      <c r="BC42" s="14"/>
+      <c r="BD42" s="14"/>
+      <c r="BE42" s="14"/>
+      <c r="BF42" s="14"/>
+      <c r="BG42" s="14"/>
+      <c r="BH42" s="15"/>
+      <c r="BI42" s="13" t="s">
         <v>194</v>
       </c>
-      <c r="BJ42" s="15"/>
-      <c r="BK42" s="16"/>
-      <c r="BL42" s="14" t="s">
+      <c r="BJ42" s="14"/>
+      <c r="BK42" s="15"/>
+      <c r="BL42" s="13" t="s">
         <v>195</v>
       </c>
-      <c r="BM42" s="15"/>
-      <c r="BN42" s="16"/>
-      <c r="BO42" s="14" t="s">
+      <c r="BM42" s="14"/>
+      <c r="BN42" s="15"/>
+      <c r="BO42" s="13" t="s">
         <v>196</v>
       </c>
-      <c r="BP42" s="15"/>
-      <c r="BQ42" s="16"/>
-      <c r="BR42" s="27"/>
+      <c r="BP42" s="14"/>
+      <c r="BQ42" s="15"/>
+      <c r="BR42" s="24"/>
     </row>
     <row r="43" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B43" s="28"/>
-      <c r="AW43" s="26" t="s">
+      <c r="B43" s="25"/>
+      <c r="AW43" s="23" t="s">
         <v>197</v>
       </c>
       <c r="AX43" s="17"/>
@@ -3404,13 +3405,13 @@
       <c r="BO43" s="17"/>
       <c r="BP43" s="18"/>
       <c r="BQ43" s="19"/>
-      <c r="BR43" s="28"/>
+      <c r="BR43" s="25"/>
     </row>
     <row r="44" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B44" s="26" t="s">
+      <c r="B44" s="23" t="s">
         <v>198</v>
       </c>
-      <c r="AW44" s="28"/>
+      <c r="AW44" s="25"/>
       <c r="AX44" s="20"/>
       <c r="AY44" s="21"/>
       <c r="AZ44" s="22"/>
@@ -3431,171 +3432,171 @@
       <c r="BO44" s="20"/>
       <c r="BP44" s="21"/>
       <c r="BQ44" s="22"/>
-      <c r="BR44" s="26" t="s">
+      <c r="BR44" s="23" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="45" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B45" s="27"/>
+      <c r="B45" s="24"/>
       <c r="AW45" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="AX45" s="14" t="s">
+      <c r="AX45" s="13" t="s">
         <v>200</v>
       </c>
-      <c r="AY45" s="15"/>
-      <c r="AZ45" s="16"/>
-      <c r="BA45" s="14" t="s">
+      <c r="AY45" s="14"/>
+      <c r="AZ45" s="15"/>
+      <c r="BA45" s="13" t="s">
         <v>201</v>
       </c>
-      <c r="BB45" s="15"/>
-      <c r="BC45" s="15"/>
-      <c r="BD45" s="15"/>
-      <c r="BE45" s="15"/>
-      <c r="BF45" s="15"/>
-      <c r="BG45" s="15"/>
-      <c r="BH45" s="16"/>
-      <c r="BI45" s="14" t="s">
+      <c r="BB45" s="14"/>
+      <c r="BC45" s="14"/>
+      <c r="BD45" s="14"/>
+      <c r="BE45" s="14"/>
+      <c r="BF45" s="14"/>
+      <c r="BG45" s="14"/>
+      <c r="BH45" s="15"/>
+      <c r="BI45" s="13" t="s">
         <v>202</v>
       </c>
-      <c r="BJ45" s="15"/>
-      <c r="BK45" s="16"/>
-      <c r="BL45" s="14" t="s">
+      <c r="BJ45" s="14"/>
+      <c r="BK45" s="15"/>
+      <c r="BL45" s="13" t="s">
         <v>203</v>
       </c>
-      <c r="BM45" s="15"/>
-      <c r="BN45" s="16"/>
-      <c r="BO45" s="14" t="s">
+      <c r="BM45" s="14"/>
+      <c r="BN45" s="15"/>
+      <c r="BO45" s="13" t="s">
         <v>204</v>
       </c>
-      <c r="BP45" s="15"/>
-      <c r="BQ45" s="16"/>
-      <c r="BR45" s="27"/>
+      <c r="BP45" s="14"/>
+      <c r="BQ45" s="15"/>
+      <c r="BR45" s="24"/>
     </row>
     <row r="46" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B46" s="27"/>
-      <c r="AW46" s="14" t="s">
+      <c r="B46" s="24"/>
+      <c r="AW46" s="13" t="s">
         <v>205</v>
       </c>
-      <c r="AX46" s="15"/>
-      <c r="AY46" s="15"/>
-      <c r="AZ46" s="16"/>
-      <c r="BA46" s="14" t="s">
+      <c r="AX46" s="14"/>
+      <c r="AY46" s="14"/>
+      <c r="AZ46" s="15"/>
+      <c r="BA46" s="13" t="s">
         <v>206</v>
       </c>
-      <c r="BB46" s="15"/>
-      <c r="BC46" s="15"/>
-      <c r="BD46" s="15"/>
-      <c r="BE46" s="15"/>
-      <c r="BF46" s="15"/>
-      <c r="BG46" s="15"/>
-      <c r="BH46" s="16"/>
-      <c r="BI46" s="14" t="s">
+      <c r="BB46" s="14"/>
+      <c r="BC46" s="14"/>
+      <c r="BD46" s="14"/>
+      <c r="BE46" s="14"/>
+      <c r="BF46" s="14"/>
+      <c r="BG46" s="14"/>
+      <c r="BH46" s="15"/>
+      <c r="BI46" s="13" t="s">
         <v>207</v>
       </c>
-      <c r="BJ46" s="15"/>
-      <c r="BK46" s="15"/>
-      <c r="BL46" s="15"/>
-      <c r="BM46" s="15"/>
-      <c r="BN46" s="15"/>
-      <c r="BO46" s="15"/>
-      <c r="BP46" s="15"/>
-      <c r="BQ46" s="16"/>
-      <c r="BR46" s="27"/>
+      <c r="BJ46" s="14"/>
+      <c r="BK46" s="14"/>
+      <c r="BL46" s="14"/>
+      <c r="BM46" s="14"/>
+      <c r="BN46" s="14"/>
+      <c r="BO46" s="14"/>
+      <c r="BP46" s="14"/>
+      <c r="BQ46" s="15"/>
+      <c r="BR46" s="24"/>
     </row>
     <row r="47" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B47" s="27"/>
-      <c r="E47" s="13" t="s">
-        <v>231</v>
-      </c>
-      <c r="F47" s="13"/>
-      <c r="G47" s="13"/>
-      <c r="H47" s="13"/>
-      <c r="I47" s="13"/>
-      <c r="J47" s="13"/>
-      <c r="K47" s="13"/>
-      <c r="L47" s="13"/>
-      <c r="M47" s="13"/>
-      <c r="N47" s="13"/>
-      <c r="O47" s="13"/>
-      <c r="P47" s="13"/>
-      <c r="Q47" s="13"/>
-      <c r="R47" s="13"/>
-      <c r="T47" s="13" t="s">
-        <v>226</v>
-      </c>
-      <c r="U47" s="13"/>
-      <c r="V47" s="13"/>
-      <c r="W47" s="13"/>
-      <c r="X47" s="13"/>
-      <c r="Y47" s="13"/>
-      <c r="Z47" s="13"/>
-      <c r="AA47" s="13"/>
-      <c r="AB47" s="13"/>
-      <c r="AC47" s="13"/>
-      <c r="AD47" s="13"/>
-      <c r="AE47" s="13"/>
-      <c r="AF47" s="13"/>
-      <c r="AG47" s="13"/>
-      <c r="AW47" s="14" t="s">
+      <c r="B47" s="24"/>
+      <c r="E47" s="16" t="s">
+        <v>230</v>
+      </c>
+      <c r="F47" s="16"/>
+      <c r="G47" s="16"/>
+      <c r="H47" s="16"/>
+      <c r="I47" s="16"/>
+      <c r="J47" s="16"/>
+      <c r="K47" s="16"/>
+      <c r="L47" s="16"/>
+      <c r="M47" s="16"/>
+      <c r="N47" s="16"/>
+      <c r="O47" s="16"/>
+      <c r="P47" s="16"/>
+      <c r="Q47" s="16"/>
+      <c r="R47" s="16"/>
+      <c r="T47" s="16" t="s">
+        <v>225</v>
+      </c>
+      <c r="U47" s="16"/>
+      <c r="V47" s="16"/>
+      <c r="W47" s="16"/>
+      <c r="X47" s="16"/>
+      <c r="Y47" s="16"/>
+      <c r="Z47" s="16"/>
+      <c r="AA47" s="16"/>
+      <c r="AB47" s="16"/>
+      <c r="AC47" s="16"/>
+      <c r="AD47" s="16"/>
+      <c r="AE47" s="16"/>
+      <c r="AF47" s="16"/>
+      <c r="AG47" s="16"/>
+      <c r="AW47" s="13" t="s">
         <v>208</v>
       </c>
-      <c r="AX47" s="15"/>
-      <c r="AY47" s="15"/>
-      <c r="AZ47" s="16"/>
-      <c r="BA47" s="14" t="s">
+      <c r="AX47" s="14"/>
+      <c r="AY47" s="14"/>
+      <c r="AZ47" s="15"/>
+      <c r="BA47" s="13" t="s">
         <v>209</v>
       </c>
-      <c r="BB47" s="15"/>
-      <c r="BC47" s="15"/>
-      <c r="BD47" s="15"/>
-      <c r="BE47" s="15"/>
-      <c r="BF47" s="15"/>
-      <c r="BG47" s="15"/>
-      <c r="BH47" s="16"/>
-      <c r="BI47" s="14" t="s">
+      <c r="BB47" s="14"/>
+      <c r="BC47" s="14"/>
+      <c r="BD47" s="14"/>
+      <c r="BE47" s="14"/>
+      <c r="BF47" s="14"/>
+      <c r="BG47" s="14"/>
+      <c r="BH47" s="15"/>
+      <c r="BI47" s="13" t="s">
         <v>210</v>
       </c>
-      <c r="BJ47" s="15"/>
-      <c r="BK47" s="15"/>
-      <c r="BL47" s="15"/>
-      <c r="BM47" s="15"/>
-      <c r="BN47" s="15"/>
-      <c r="BO47" s="15"/>
-      <c r="BP47" s="15"/>
-      <c r="BQ47" s="16"/>
-      <c r="BR47" s="27"/>
+      <c r="BJ47" s="14"/>
+      <c r="BK47" s="14"/>
+      <c r="BL47" s="14"/>
+      <c r="BM47" s="14"/>
+      <c r="BN47" s="14"/>
+      <c r="BO47" s="14"/>
+      <c r="BP47" s="14"/>
+      <c r="BQ47" s="15"/>
+      <c r="BR47" s="24"/>
     </row>
     <row r="48" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B48" s="27"/>
-      <c r="E48" s="13"/>
-      <c r="F48" s="13"/>
-      <c r="G48" s="13"/>
-      <c r="H48" s="13"/>
-      <c r="I48" s="13"/>
-      <c r="J48" s="13"/>
-      <c r="K48" s="13"/>
-      <c r="L48" s="13"/>
-      <c r="M48" s="13"/>
-      <c r="N48" s="13"/>
-      <c r="O48" s="13"/>
-      <c r="P48" s="13"/>
-      <c r="Q48" s="13"/>
-      <c r="R48" s="13"/>
-      <c r="T48" s="13"/>
-      <c r="U48" s="13"/>
-      <c r="V48" s="13"/>
-      <c r="W48" s="13"/>
-      <c r="X48" s="13"/>
-      <c r="Y48" s="13"/>
-      <c r="Z48" s="13"/>
-      <c r="AA48" s="13"/>
-      <c r="AB48" s="13"/>
-      <c r="AC48" s="13"/>
-      <c r="AD48" s="13"/>
-      <c r="AE48" s="13"/>
-      <c r="AF48" s="13"/>
-      <c r="AG48" s="13"/>
+      <c r="B48" s="24"/>
+      <c r="E48" s="16"/>
+      <c r="F48" s="16"/>
+      <c r="G48" s="16"/>
+      <c r="H48" s="16"/>
+      <c r="I48" s="16"/>
+      <c r="J48" s="16"/>
+      <c r="K48" s="16"/>
+      <c r="L48" s="16"/>
+      <c r="M48" s="16"/>
+      <c r="N48" s="16"/>
+      <c r="O48" s="16"/>
+      <c r="P48" s="16"/>
+      <c r="Q48" s="16"/>
+      <c r="R48" s="16"/>
+      <c r="T48" s="16"/>
+      <c r="U48" s="16"/>
+      <c r="V48" s="16"/>
+      <c r="W48" s="16"/>
+      <c r="X48" s="16"/>
+      <c r="Y48" s="16"/>
+      <c r="Z48" s="16"/>
+      <c r="AA48" s="16"/>
+      <c r="AB48" s="16"/>
+      <c r="AC48" s="16"/>
+      <c r="AD48" s="16"/>
+      <c r="AE48" s="16"/>
+      <c r="AF48" s="16"/>
+      <c r="AG48" s="16"/>
       <c r="AW48" s="17" t="s">
         <v>211</v>
       </c>
@@ -3621,46 +3622,46 @@
       <c r="BO48" s="18"/>
       <c r="BP48" s="18"/>
       <c r="BQ48" s="19"/>
-      <c r="BR48" s="27"/>
+      <c r="BR48" s="24"/>
     </row>
     <row r="49" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B49" s="27"/>
-      <c r="E49" s="13"/>
-      <c r="F49" s="13"/>
-      <c r="G49" s="13"/>
-      <c r="H49" s="13"/>
-      <c r="I49" s="13"/>
-      <c r="J49" s="13"/>
-      <c r="K49" s="13"/>
-      <c r="L49" s="13"/>
-      <c r="M49" s="13"/>
-      <c r="N49" s="13"/>
-      <c r="O49" s="13"/>
-      <c r="P49" s="13"/>
-      <c r="Q49" s="13"/>
-      <c r="R49" s="13"/>
-      <c r="T49" s="13"/>
-      <c r="U49" s="13"/>
-      <c r="V49" s="13"/>
-      <c r="W49" s="13"/>
-      <c r="X49" s="13"/>
-      <c r="Y49" s="13"/>
-      <c r="Z49" s="13"/>
-      <c r="AA49" s="13"/>
-      <c r="AB49" s="13"/>
-      <c r="AC49" s="13"/>
-      <c r="AD49" s="13"/>
-      <c r="AE49" s="13"/>
-      <c r="AF49" s="13"/>
-      <c r="AG49" s="13"/>
-      <c r="AW49" s="23"/>
-      <c r="AX49" s="24"/>
-      <c r="AY49" s="24"/>
-      <c r="AZ49" s="24"/>
-      <c r="BA49" s="24"/>
-      <c r="BB49" s="24"/>
-      <c r="BC49" s="24"/>
-      <c r="BD49" s="25"/>
+      <c r="B49" s="24"/>
+      <c r="E49" s="16"/>
+      <c r="F49" s="16"/>
+      <c r="G49" s="16"/>
+      <c r="H49" s="16"/>
+      <c r="I49" s="16"/>
+      <c r="J49" s="16"/>
+      <c r="K49" s="16"/>
+      <c r="L49" s="16"/>
+      <c r="M49" s="16"/>
+      <c r="N49" s="16"/>
+      <c r="O49" s="16"/>
+      <c r="P49" s="16"/>
+      <c r="Q49" s="16"/>
+      <c r="R49" s="16"/>
+      <c r="T49" s="16"/>
+      <c r="U49" s="16"/>
+      <c r="V49" s="16"/>
+      <c r="W49" s="16"/>
+      <c r="X49" s="16"/>
+      <c r="Y49" s="16"/>
+      <c r="Z49" s="16"/>
+      <c r="AA49" s="16"/>
+      <c r="AB49" s="16"/>
+      <c r="AC49" s="16"/>
+      <c r="AD49" s="16"/>
+      <c r="AE49" s="16"/>
+      <c r="AF49" s="16"/>
+      <c r="AG49" s="16"/>
+      <c r="AW49" s="26"/>
+      <c r="AX49" s="27"/>
+      <c r="AY49" s="27"/>
+      <c r="AZ49" s="27"/>
+      <c r="BA49" s="27"/>
+      <c r="BB49" s="27"/>
+      <c r="BC49" s="27"/>
+      <c r="BD49" s="28"/>
       <c r="BE49" s="20"/>
       <c r="BF49" s="21"/>
       <c r="BG49" s="21"/>
@@ -3674,46 +3675,46 @@
       <c r="BO49" s="21"/>
       <c r="BP49" s="21"/>
       <c r="BQ49" s="22"/>
-      <c r="BR49" s="27"/>
+      <c r="BR49" s="24"/>
     </row>
     <row r="50" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B50" s="27"/>
-      <c r="E50" s="13"/>
-      <c r="F50" s="13"/>
-      <c r="G50" s="13"/>
-      <c r="H50" s="13"/>
-      <c r="I50" s="13"/>
-      <c r="J50" s="13"/>
-      <c r="K50" s="13"/>
-      <c r="L50" s="13"/>
-      <c r="M50" s="13"/>
-      <c r="N50" s="13"/>
-      <c r="O50" s="13"/>
-      <c r="P50" s="13"/>
-      <c r="Q50" s="13"/>
-      <c r="R50" s="13"/>
-      <c r="T50" s="13"/>
-      <c r="U50" s="13"/>
-      <c r="V50" s="13"/>
-      <c r="W50" s="13"/>
-      <c r="X50" s="13"/>
-      <c r="Y50" s="13"/>
-      <c r="Z50" s="13"/>
-      <c r="AA50" s="13"/>
-      <c r="AB50" s="13"/>
-      <c r="AC50" s="13"/>
-      <c r="AD50" s="13"/>
-      <c r="AE50" s="13"/>
-      <c r="AF50" s="13"/>
-      <c r="AG50" s="13"/>
-      <c r="AW50" s="23"/>
-      <c r="AX50" s="24"/>
-      <c r="AY50" s="24"/>
-      <c r="AZ50" s="24"/>
-      <c r="BA50" s="24"/>
-      <c r="BB50" s="24"/>
-      <c r="BC50" s="24"/>
-      <c r="BD50" s="25"/>
+      <c r="B50" s="24"/>
+      <c r="E50" s="16"/>
+      <c r="F50" s="16"/>
+      <c r="G50" s="16"/>
+      <c r="H50" s="16"/>
+      <c r="I50" s="16"/>
+      <c r="J50" s="16"/>
+      <c r="K50" s="16"/>
+      <c r="L50" s="16"/>
+      <c r="M50" s="16"/>
+      <c r="N50" s="16"/>
+      <c r="O50" s="16"/>
+      <c r="P50" s="16"/>
+      <c r="Q50" s="16"/>
+      <c r="R50" s="16"/>
+      <c r="T50" s="16"/>
+      <c r="U50" s="16"/>
+      <c r="V50" s="16"/>
+      <c r="W50" s="16"/>
+      <c r="X50" s="16"/>
+      <c r="Y50" s="16"/>
+      <c r="Z50" s="16"/>
+      <c r="AA50" s="16"/>
+      <c r="AB50" s="16"/>
+      <c r="AC50" s="16"/>
+      <c r="AD50" s="16"/>
+      <c r="AE50" s="16"/>
+      <c r="AF50" s="16"/>
+      <c r="AG50" s="16"/>
+      <c r="AW50" s="26"/>
+      <c r="AX50" s="27"/>
+      <c r="AY50" s="27"/>
+      <c r="AZ50" s="27"/>
+      <c r="BA50" s="27"/>
+      <c r="BB50" s="27"/>
+      <c r="BC50" s="27"/>
+      <c r="BD50" s="28"/>
       <c r="BE50" s="17" t="s">
         <v>213</v>
       </c>
@@ -3729,38 +3730,38 @@
       <c r="BO50" s="18"/>
       <c r="BP50" s="18"/>
       <c r="BQ50" s="19"/>
-      <c r="BR50" s="27"/>
+      <c r="BR50" s="24"/>
     </row>
     <row r="51" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B51" s="27"/>
-      <c r="E51" s="13"/>
-      <c r="F51" s="13"/>
-      <c r="G51" s="13"/>
-      <c r="H51" s="13"/>
-      <c r="I51" s="13"/>
-      <c r="J51" s="13"/>
-      <c r="K51" s="13"/>
-      <c r="L51" s="13"/>
-      <c r="M51" s="13"/>
-      <c r="N51" s="13"/>
-      <c r="O51" s="13"/>
-      <c r="P51" s="13"/>
-      <c r="Q51" s="13"/>
-      <c r="R51" s="13"/>
-      <c r="T51" s="13"/>
-      <c r="U51" s="13"/>
-      <c r="V51" s="13"/>
-      <c r="W51" s="13"/>
-      <c r="X51" s="13"/>
-      <c r="Y51" s="13"/>
-      <c r="Z51" s="13"/>
-      <c r="AA51" s="13"/>
-      <c r="AB51" s="13"/>
-      <c r="AC51" s="13"/>
-      <c r="AD51" s="13"/>
-      <c r="AE51" s="13"/>
-      <c r="AF51" s="13"/>
-      <c r="AG51" s="13"/>
+      <c r="B51" s="24"/>
+      <c r="E51" s="16"/>
+      <c r="F51" s="16"/>
+      <c r="G51" s="16"/>
+      <c r="H51" s="16"/>
+      <c r="I51" s="16"/>
+      <c r="J51" s="16"/>
+      <c r="K51" s="16"/>
+      <c r="L51" s="16"/>
+      <c r="M51" s="16"/>
+      <c r="N51" s="16"/>
+      <c r="O51" s="16"/>
+      <c r="P51" s="16"/>
+      <c r="Q51" s="16"/>
+      <c r="R51" s="16"/>
+      <c r="T51" s="16"/>
+      <c r="U51" s="16"/>
+      <c r="V51" s="16"/>
+      <c r="W51" s="16"/>
+      <c r="X51" s="16"/>
+      <c r="Y51" s="16"/>
+      <c r="Z51" s="16"/>
+      <c r="AA51" s="16"/>
+      <c r="AB51" s="16"/>
+      <c r="AC51" s="16"/>
+      <c r="AD51" s="16"/>
+      <c r="AE51" s="16"/>
+      <c r="AF51" s="16"/>
+      <c r="AG51" s="16"/>
       <c r="AW51" s="20"/>
       <c r="AX51" s="21"/>
       <c r="AY51" s="21"/>
@@ -3782,10 +3783,10 @@
       <c r="BO51" s="21"/>
       <c r="BP51" s="21"/>
       <c r="BQ51" s="22"/>
-      <c r="BR51" s="27"/>
+      <c r="BR51" s="24"/>
     </row>
     <row r="52" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B52" s="27"/>
+      <c r="B52" s="24"/>
       <c r="AW52" s="17" t="s">
         <v>214</v>
       </c>
@@ -3811,62 +3812,62 @@
       <c r="BO52" s="18"/>
       <c r="BP52" s="18"/>
       <c r="BQ52" s="19"/>
-      <c r="BR52" s="27"/>
+      <c r="BR52" s="24"/>
     </row>
     <row r="53" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B53" s="27"/>
-      <c r="AW53" s="23" t="s">
-        <v>216</v>
-      </c>
-      <c r="AX53" s="24"/>
-      <c r="AY53" s="24"/>
-      <c r="AZ53" s="24"/>
-      <c r="BA53" s="24"/>
-      <c r="BB53" s="24"/>
-      <c r="BC53" s="24"/>
-      <c r="BD53" s="25"/>
-      <c r="BE53" s="23"/>
-      <c r="BF53" s="24"/>
-      <c r="BG53" s="24"/>
-      <c r="BH53" s="24"/>
-      <c r="BI53" s="24"/>
-      <c r="BJ53" s="24"/>
-      <c r="BK53" s="24"/>
-      <c r="BL53" s="24"/>
-      <c r="BM53" s="24"/>
-      <c r="BN53" s="24"/>
-      <c r="BO53" s="24"/>
-      <c r="BP53" s="24"/>
-      <c r="BQ53" s="25"/>
-      <c r="BR53" s="27"/>
+      <c r="B53" s="24"/>
+      <c r="AW53" s="26" t="s">
+        <v>231</v>
+      </c>
+      <c r="AX53" s="27"/>
+      <c r="AY53" s="27"/>
+      <c r="AZ53" s="27"/>
+      <c r="BA53" s="27"/>
+      <c r="BB53" s="27"/>
+      <c r="BC53" s="27"/>
+      <c r="BD53" s="28"/>
+      <c r="BE53" s="26"/>
+      <c r="BF53" s="27"/>
+      <c r="BG53" s="27"/>
+      <c r="BH53" s="27"/>
+      <c r="BI53" s="27"/>
+      <c r="BJ53" s="27"/>
+      <c r="BK53" s="27"/>
+      <c r="BL53" s="27"/>
+      <c r="BM53" s="27"/>
+      <c r="BN53" s="27"/>
+      <c r="BO53" s="27"/>
+      <c r="BP53" s="27"/>
+      <c r="BQ53" s="28"/>
+      <c r="BR53" s="24"/>
     </row>
     <row r="54" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B54" s="27"/>
-      <c r="AW54" s="23"/>
-      <c r="AX54" s="24"/>
-      <c r="AY54" s="24"/>
-      <c r="AZ54" s="24"/>
-      <c r="BA54" s="24"/>
-      <c r="BB54" s="24"/>
-      <c r="BC54" s="24"/>
-      <c r="BD54" s="25"/>
-      <c r="BE54" s="23"/>
-      <c r="BF54" s="24"/>
-      <c r="BG54" s="24"/>
-      <c r="BH54" s="24"/>
-      <c r="BI54" s="24"/>
-      <c r="BJ54" s="24"/>
-      <c r="BK54" s="24"/>
-      <c r="BL54" s="24"/>
-      <c r="BM54" s="24"/>
-      <c r="BN54" s="24"/>
-      <c r="BO54" s="24"/>
-      <c r="BP54" s="24"/>
-      <c r="BQ54" s="25"/>
-      <c r="BR54" s="27"/>
+      <c r="B54" s="24"/>
+      <c r="AW54" s="26"/>
+      <c r="AX54" s="27"/>
+      <c r="AY54" s="27"/>
+      <c r="AZ54" s="27"/>
+      <c r="BA54" s="27"/>
+      <c r="BB54" s="27"/>
+      <c r="BC54" s="27"/>
+      <c r="BD54" s="28"/>
+      <c r="BE54" s="26"/>
+      <c r="BF54" s="27"/>
+      <c r="BG54" s="27"/>
+      <c r="BH54" s="27"/>
+      <c r="BI54" s="27"/>
+      <c r="BJ54" s="27"/>
+      <c r="BK54" s="27"/>
+      <c r="BL54" s="27"/>
+      <c r="BM54" s="27"/>
+      <c r="BN54" s="27"/>
+      <c r="BO54" s="27"/>
+      <c r="BP54" s="27"/>
+      <c r="BQ54" s="28"/>
+      <c r="BR54" s="24"/>
     </row>
     <row r="55" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B55" s="27"/>
+      <c r="B55" s="24"/>
       <c r="AW55" s="20"/>
       <c r="AX55" s="21"/>
       <c r="AY55" s="21"/>
@@ -3888,123 +3889,288 @@
       <c r="BO55" s="21"/>
       <c r="BP55" s="21"/>
       <c r="BQ55" s="22"/>
-      <c r="BR55" s="27"/>
+      <c r="BR55" s="24"/>
     </row>
     <row r="56" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B56" s="28"/>
+      <c r="B56" s="25"/>
       <c r="K56" s="3"/>
       <c r="AI56" s="3"/>
-      <c r="AW56" s="14" t="s">
+      <c r="AW56" s="13" t="s">
+        <v>216</v>
+      </c>
+      <c r="AX56" s="14"/>
+      <c r="AY56" s="14" t="s">
         <v>217</v>
       </c>
-      <c r="AX56" s="15"/>
-      <c r="AY56" s="15" t="s">
-        <v>218</v>
-      </c>
-      <c r="AZ56" s="15"/>
-      <c r="BA56" s="15"/>
-      <c r="BB56" s="15"/>
-      <c r="BC56" s="15"/>
-      <c r="BD56" s="15"/>
-      <c r="BE56" s="15"/>
-      <c r="BF56" s="15"/>
-      <c r="BG56" s="15"/>
-      <c r="BH56" s="15"/>
-      <c r="BI56" s="15"/>
-      <c r="BJ56" s="15"/>
-      <c r="BK56" s="15"/>
-      <c r="BL56" s="15"/>
-      <c r="BM56" s="15"/>
-      <c r="BN56" s="15"/>
-      <c r="BO56" s="15"/>
-      <c r="BP56" s="15"/>
-      <c r="BQ56" s="16"/>
-      <c r="BR56" s="28"/>
+      <c r="AZ56" s="14"/>
+      <c r="BA56" s="14"/>
+      <c r="BB56" s="14"/>
+      <c r="BC56" s="14"/>
+      <c r="BD56" s="14"/>
+      <c r="BE56" s="14"/>
+      <c r="BF56" s="14"/>
+      <c r="BG56" s="14"/>
+      <c r="BH56" s="14"/>
+      <c r="BI56" s="14"/>
+      <c r="BJ56" s="14"/>
+      <c r="BK56" s="14"/>
+      <c r="BL56" s="14"/>
+      <c r="BM56" s="14"/>
+      <c r="BN56" s="14"/>
+      <c r="BO56" s="14"/>
+      <c r="BP56" s="14"/>
+      <c r="BQ56" s="15"/>
+      <c r="BR56" s="25"/>
     </row>
     <row r="57" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="C57" s="14">
+      <c r="C57" s="13">
         <v>1</v>
       </c>
-      <c r="D57" s="15"/>
-      <c r="E57" s="15"/>
-      <c r="F57" s="15"/>
-      <c r="G57" s="15"/>
-      <c r="H57" s="15"/>
-      <c r="I57" s="15"/>
-      <c r="J57" s="15"/>
-      <c r="K57" s="15"/>
-      <c r="L57" s="16"/>
-      <c r="M57" s="14">
+      <c r="D57" s="14"/>
+      <c r="E57" s="14"/>
+      <c r="F57" s="14"/>
+      <c r="G57" s="14"/>
+      <c r="H57" s="14"/>
+      <c r="I57" s="14"/>
+      <c r="J57" s="14"/>
+      <c r="K57" s="14"/>
+      <c r="L57" s="15"/>
+      <c r="M57" s="13">
         <v>2</v>
       </c>
-      <c r="N57" s="15"/>
-      <c r="O57" s="15"/>
-      <c r="P57" s="15"/>
-      <c r="Q57" s="15"/>
-      <c r="R57" s="15"/>
-      <c r="S57" s="15"/>
-      <c r="T57" s="15"/>
-      <c r="U57" s="15"/>
-      <c r="V57" s="15"/>
-      <c r="W57" s="15"/>
-      <c r="X57" s="16"/>
-      <c r="Y57" s="14">
+      <c r="N57" s="14"/>
+      <c r="O57" s="14"/>
+      <c r="P57" s="14"/>
+      <c r="Q57" s="14"/>
+      <c r="R57" s="14"/>
+      <c r="S57" s="14"/>
+      <c r="T57" s="14"/>
+      <c r="U57" s="14"/>
+      <c r="V57" s="14"/>
+      <c r="W57" s="14"/>
+      <c r="X57" s="15"/>
+      <c r="Y57" s="13">
         <v>3</v>
       </c>
-      <c r="Z57" s="15"/>
-      <c r="AA57" s="15"/>
-      <c r="AB57" s="15"/>
-      <c r="AC57" s="15"/>
-      <c r="AD57" s="15"/>
-      <c r="AE57" s="15"/>
-      <c r="AF57" s="15"/>
-      <c r="AG57" s="15"/>
-      <c r="AH57" s="15"/>
-      <c r="AI57" s="16"/>
-      <c r="AJ57" s="14">
+      <c r="Z57" s="14"/>
+      <c r="AA57" s="14"/>
+      <c r="AB57" s="14"/>
+      <c r="AC57" s="14"/>
+      <c r="AD57" s="14"/>
+      <c r="AE57" s="14"/>
+      <c r="AF57" s="14"/>
+      <c r="AG57" s="14"/>
+      <c r="AH57" s="14"/>
+      <c r="AI57" s="15"/>
+      <c r="AJ57" s="13">
         <v>4</v>
       </c>
-      <c r="AK57" s="15"/>
-      <c r="AL57" s="15"/>
-      <c r="AM57" s="15"/>
-      <c r="AN57" s="15"/>
-      <c r="AO57" s="15"/>
-      <c r="AP57" s="15"/>
-      <c r="AQ57" s="15"/>
-      <c r="AR57" s="15"/>
-      <c r="AS57" s="15"/>
-      <c r="AT57" s="16"/>
-      <c r="AU57" s="14">
+      <c r="AK57" s="14"/>
+      <c r="AL57" s="14"/>
+      <c r="AM57" s="14"/>
+      <c r="AN57" s="14"/>
+      <c r="AO57" s="14"/>
+      <c r="AP57" s="14"/>
+      <c r="AQ57" s="14"/>
+      <c r="AR57" s="14"/>
+      <c r="AS57" s="14"/>
+      <c r="AT57" s="15"/>
+      <c r="AU57" s="13">
         <v>5</v>
       </c>
-      <c r="AV57" s="15"/>
-      <c r="AW57" s="15"/>
-      <c r="AX57" s="15"/>
-      <c r="AY57" s="15"/>
-      <c r="AZ57" s="15"/>
-      <c r="BA57" s="15"/>
-      <c r="BB57" s="15"/>
-      <c r="BC57" s="15"/>
-      <c r="BD57" s="15"/>
-      <c r="BE57" s="15"/>
-      <c r="BF57" s="16"/>
-      <c r="BG57" s="14">
+      <c r="AV57" s="14"/>
+      <c r="AW57" s="14"/>
+      <c r="AX57" s="14"/>
+      <c r="AY57" s="14"/>
+      <c r="AZ57" s="14"/>
+      <c r="BA57" s="14"/>
+      <c r="BB57" s="14"/>
+      <c r="BC57" s="14"/>
+      <c r="BD57" s="14"/>
+      <c r="BE57" s="14"/>
+      <c r="BF57" s="15"/>
+      <c r="BG57" s="13">
         <v>6</v>
       </c>
-      <c r="BH57" s="15"/>
-      <c r="BI57" s="15"/>
-      <c r="BJ57" s="15"/>
-      <c r="BK57" s="15"/>
-      <c r="BL57" s="15"/>
-      <c r="BM57" s="15"/>
-      <c r="BN57" s="15"/>
-      <c r="BO57" s="15"/>
-      <c r="BP57" s="15"/>
-      <c r="BQ57" s="16"/>
+      <c r="BH57" s="14"/>
+      <c r="BI57" s="14"/>
+      <c r="BJ57" s="14"/>
+      <c r="BK57" s="14"/>
+      <c r="BL57" s="14"/>
+      <c r="BM57" s="14"/>
+      <c r="BN57" s="14"/>
+      <c r="BO57" s="14"/>
+      <c r="BP57" s="14"/>
+      <c r="BQ57" s="15"/>
     </row>
     <row r="58" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4"/>
   </sheetData>
   <mergeCells count="189">
+    <mergeCell ref="M2:X2"/>
+    <mergeCell ref="AU2:BF2"/>
+    <mergeCell ref="AW18:AX18"/>
+    <mergeCell ref="BC8:BE8"/>
+    <mergeCell ref="BI43:BK44"/>
+    <mergeCell ref="AU57:BF57"/>
+    <mergeCell ref="AW9:AX9"/>
+    <mergeCell ref="BC22:BE22"/>
+    <mergeCell ref="BA47:BH47"/>
+    <mergeCell ref="BG2:BQ2"/>
+    <mergeCell ref="AJ2:AT2"/>
+    <mergeCell ref="AY56:BQ56"/>
+    <mergeCell ref="Y2:AI2"/>
+    <mergeCell ref="BF9:BK9"/>
+    <mergeCell ref="AY8:BB8"/>
+    <mergeCell ref="AW17:AX17"/>
+    <mergeCell ref="BO43:BQ44"/>
+    <mergeCell ref="BG57:BQ57"/>
+    <mergeCell ref="BC7:BE7"/>
+    <mergeCell ref="BC15:BE15"/>
+    <mergeCell ref="BA40:BH40"/>
+    <mergeCell ref="AW19:AX19"/>
+    <mergeCell ref="AW53:BD55"/>
+    <mergeCell ref="AW3:BQ4"/>
+    <mergeCell ref="BI46:BQ46"/>
+    <mergeCell ref="BM23:BO23"/>
+    <mergeCell ref="BF15:BK15"/>
+    <mergeCell ref="BL5:BL6"/>
+    <mergeCell ref="AY14:BB14"/>
+    <mergeCell ref="AY25:BB25"/>
+    <mergeCell ref="AY31:BQ36"/>
+    <mergeCell ref="AY12:BB12"/>
+    <mergeCell ref="BC14:BE14"/>
+    <mergeCell ref="BM22:BO22"/>
+    <mergeCell ref="AW14:AX14"/>
+    <mergeCell ref="AY7:BB7"/>
+    <mergeCell ref="BC10:BE10"/>
+    <mergeCell ref="BM17:BO17"/>
+    <mergeCell ref="BC23:BE23"/>
+    <mergeCell ref="BF18:BK18"/>
+    <mergeCell ref="AW12:AX12"/>
+    <mergeCell ref="BM14:BO14"/>
+    <mergeCell ref="BC12:BE12"/>
+    <mergeCell ref="BL43:BN44"/>
+    <mergeCell ref="BF19:BK19"/>
+    <mergeCell ref="BC24:BE24"/>
+    <mergeCell ref="T7:AG11"/>
+    <mergeCell ref="B17:B29"/>
+    <mergeCell ref="AW7:AX7"/>
+    <mergeCell ref="B44:B56"/>
+    <mergeCell ref="BL41:BN41"/>
+    <mergeCell ref="T47:AG51"/>
+    <mergeCell ref="C3:D5"/>
+    <mergeCell ref="BM5:BO6"/>
+    <mergeCell ref="AW5:AX6"/>
+    <mergeCell ref="AT3:AV8"/>
+    <mergeCell ref="T17:AG20"/>
+    <mergeCell ref="T26:AG29"/>
+    <mergeCell ref="T35:AG39"/>
+    <mergeCell ref="BE52:BQ55"/>
+    <mergeCell ref="AX42:AZ42"/>
+    <mergeCell ref="AW43:AW44"/>
+    <mergeCell ref="AY5:BB6"/>
+    <mergeCell ref="BF20:BK20"/>
+    <mergeCell ref="AW20:AX20"/>
+    <mergeCell ref="AW52:BD52"/>
+    <mergeCell ref="BO42:BQ42"/>
+    <mergeCell ref="BP5:BP6"/>
+    <mergeCell ref="BO40:BQ40"/>
+    <mergeCell ref="BQ5:BQ6"/>
+    <mergeCell ref="BM21:BO21"/>
+    <mergeCell ref="BF13:BK13"/>
+    <mergeCell ref="AW13:AX13"/>
+    <mergeCell ref="BA45:BH45"/>
+    <mergeCell ref="AW8:AX8"/>
+    <mergeCell ref="BL45:BN45"/>
+    <mergeCell ref="BR30:BR43"/>
+    <mergeCell ref="BM8:BO8"/>
+    <mergeCell ref="AX39:AZ39"/>
+    <mergeCell ref="BM16:BO16"/>
+    <mergeCell ref="BA46:BH46"/>
+    <mergeCell ref="BA39:BH39"/>
+    <mergeCell ref="BM10:BO10"/>
+    <mergeCell ref="AW31:AX36"/>
+    <mergeCell ref="BE48:BQ49"/>
+    <mergeCell ref="BL42:BN42"/>
+    <mergeCell ref="AY23:BB23"/>
+    <mergeCell ref="AX45:AZ45"/>
+    <mergeCell ref="BI42:BK42"/>
+    <mergeCell ref="BF21:BK21"/>
+    <mergeCell ref="BO45:BQ45"/>
+    <mergeCell ref="BR44:BR56"/>
+    <mergeCell ref="AY9:BB9"/>
+    <mergeCell ref="AW25:AX25"/>
+    <mergeCell ref="AW15:AX15"/>
+    <mergeCell ref="BC9:BE9"/>
+    <mergeCell ref="AY18:BB18"/>
+    <mergeCell ref="AW49:BD51"/>
+    <mergeCell ref="BI45:BK45"/>
+    <mergeCell ref="BC16:BE16"/>
+    <mergeCell ref="B30:B43"/>
+    <mergeCell ref="AW47:AZ47"/>
+    <mergeCell ref="BF10:BK10"/>
+    <mergeCell ref="AW10:AX10"/>
+    <mergeCell ref="BF17:BK17"/>
+    <mergeCell ref="AW23:AX23"/>
+    <mergeCell ref="BC18:BE18"/>
+    <mergeCell ref="AW48:BD48"/>
+    <mergeCell ref="BI41:BK41"/>
+    <mergeCell ref="B3:B16"/>
+    <mergeCell ref="BI47:BQ47"/>
+    <mergeCell ref="AW21:AX21"/>
+    <mergeCell ref="BC19:BE19"/>
+    <mergeCell ref="AX41:AZ41"/>
+    <mergeCell ref="BM24:BO24"/>
+    <mergeCell ref="BI39:BK39"/>
+    <mergeCell ref="BC21:BE21"/>
+    <mergeCell ref="AX43:AZ44"/>
+    <mergeCell ref="AY20:BB20"/>
+    <mergeCell ref="AW16:AX16"/>
+    <mergeCell ref="BF5:BK6"/>
+    <mergeCell ref="BC17:BE17"/>
+    <mergeCell ref="AY24:BB24"/>
+    <mergeCell ref="BC5:BE6"/>
+    <mergeCell ref="BF8:BK8"/>
+    <mergeCell ref="BI40:BK40"/>
+    <mergeCell ref="AW46:AZ46"/>
+    <mergeCell ref="BC26:BE26"/>
+    <mergeCell ref="BF26:BK26"/>
+    <mergeCell ref="BM26:BO26"/>
+    <mergeCell ref="BE50:BQ51"/>
+    <mergeCell ref="AY26:BB26"/>
+    <mergeCell ref="BR17:BR29"/>
+    <mergeCell ref="BM9:BO9"/>
+    <mergeCell ref="AY16:BB16"/>
+    <mergeCell ref="BO39:BQ39"/>
+    <mergeCell ref="BM19:BO19"/>
+    <mergeCell ref="BF14:BK14"/>
+    <mergeCell ref="BF23:BK23"/>
+    <mergeCell ref="BM12:BO12"/>
+    <mergeCell ref="BR3:BR16"/>
+    <mergeCell ref="BF25:BK25"/>
+    <mergeCell ref="BF22:BK22"/>
+    <mergeCell ref="BF12:BK12"/>
+    <mergeCell ref="BM20:BO20"/>
+    <mergeCell ref="BF7:BK7"/>
+    <mergeCell ref="AY21:BB21"/>
+    <mergeCell ref="BM18:BO18"/>
+    <mergeCell ref="BC13:BE13"/>
+    <mergeCell ref="BM13:BO13"/>
+    <mergeCell ref="C57:L57"/>
+    <mergeCell ref="M57:X57"/>
+    <mergeCell ref="Y57:AI57"/>
+    <mergeCell ref="AJ57:AT57"/>
+    <mergeCell ref="AW56:AX56"/>
+    <mergeCell ref="BM25:BO25"/>
+    <mergeCell ref="BL39:BN39"/>
+    <mergeCell ref="E47:R51"/>
+    <mergeCell ref="BA42:BH42"/>
+    <mergeCell ref="AY19:BB19"/>
+    <mergeCell ref="AY13:BB13"/>
+    <mergeCell ref="AX40:AZ40"/>
+    <mergeCell ref="AY22:BB22"/>
+    <mergeCell ref="BA43:BH44"/>
+    <mergeCell ref="BL40:BN40"/>
     <mergeCell ref="C2:L2"/>
     <mergeCell ref="BO41:BQ41"/>
     <mergeCell ref="BF16:BK16"/>
@@ -4029,171 +4195,6 @@
     <mergeCell ref="BM7:BO7"/>
     <mergeCell ref="BM15:BO15"/>
     <mergeCell ref="BC25:BE25"/>
-    <mergeCell ref="BC13:BE13"/>
-    <mergeCell ref="BM13:BO13"/>
-    <mergeCell ref="C57:L57"/>
-    <mergeCell ref="M57:X57"/>
-    <mergeCell ref="Y57:AI57"/>
-    <mergeCell ref="AJ57:AT57"/>
-    <mergeCell ref="AW56:AX56"/>
-    <mergeCell ref="BM25:BO25"/>
-    <mergeCell ref="BL39:BN39"/>
-    <mergeCell ref="E47:R51"/>
-    <mergeCell ref="BF8:BK8"/>
-    <mergeCell ref="BI40:BK40"/>
-    <mergeCell ref="AW46:AZ46"/>
-    <mergeCell ref="BC26:BE26"/>
-    <mergeCell ref="BF26:BK26"/>
-    <mergeCell ref="BM26:BO26"/>
-    <mergeCell ref="BE50:BQ51"/>
-    <mergeCell ref="AY26:BB26"/>
-    <mergeCell ref="BR17:BR29"/>
-    <mergeCell ref="BM9:BO9"/>
-    <mergeCell ref="AY16:BB16"/>
-    <mergeCell ref="BO39:BQ39"/>
-    <mergeCell ref="BM19:BO19"/>
-    <mergeCell ref="BF14:BK14"/>
-    <mergeCell ref="BF23:BK23"/>
-    <mergeCell ref="BM12:BO12"/>
-    <mergeCell ref="BR3:BR16"/>
-    <mergeCell ref="BF25:BK25"/>
-    <mergeCell ref="BF22:BK22"/>
-    <mergeCell ref="BF12:BK12"/>
-    <mergeCell ref="BM20:BO20"/>
-    <mergeCell ref="BF7:BK7"/>
-    <mergeCell ref="AY21:BB21"/>
-    <mergeCell ref="BM18:BO18"/>
-    <mergeCell ref="B30:B43"/>
-    <mergeCell ref="AW47:AZ47"/>
-    <mergeCell ref="BF10:BK10"/>
-    <mergeCell ref="AW10:AX10"/>
-    <mergeCell ref="BF17:BK17"/>
-    <mergeCell ref="AW23:AX23"/>
-    <mergeCell ref="BC18:BE18"/>
-    <mergeCell ref="AW48:BD48"/>
-    <mergeCell ref="BI41:BK41"/>
-    <mergeCell ref="B3:B16"/>
-    <mergeCell ref="BI47:BQ47"/>
-    <mergeCell ref="AW21:AX21"/>
-    <mergeCell ref="BC19:BE19"/>
-    <mergeCell ref="AX41:AZ41"/>
-    <mergeCell ref="BM24:BO24"/>
-    <mergeCell ref="BI39:BK39"/>
-    <mergeCell ref="BC21:BE21"/>
-    <mergeCell ref="AX43:AZ44"/>
-    <mergeCell ref="AY20:BB20"/>
-    <mergeCell ref="AW16:AX16"/>
-    <mergeCell ref="BF5:BK6"/>
-    <mergeCell ref="BC17:BE17"/>
-    <mergeCell ref="AY24:BB24"/>
-    <mergeCell ref="BC5:BE6"/>
-    <mergeCell ref="BR30:BR43"/>
-    <mergeCell ref="BM8:BO8"/>
-    <mergeCell ref="AX39:AZ39"/>
-    <mergeCell ref="BM16:BO16"/>
-    <mergeCell ref="BA46:BH46"/>
-    <mergeCell ref="BA39:BH39"/>
-    <mergeCell ref="BM10:BO10"/>
-    <mergeCell ref="AW31:AX36"/>
-    <mergeCell ref="BE48:BQ49"/>
-    <mergeCell ref="BL42:BN42"/>
-    <mergeCell ref="AY23:BB23"/>
-    <mergeCell ref="AX45:AZ45"/>
-    <mergeCell ref="BI42:BK42"/>
-    <mergeCell ref="BF21:BK21"/>
-    <mergeCell ref="BO45:BQ45"/>
-    <mergeCell ref="BR44:BR56"/>
-    <mergeCell ref="AY9:BB9"/>
-    <mergeCell ref="AW25:AX25"/>
-    <mergeCell ref="AW15:AX15"/>
-    <mergeCell ref="BC9:BE9"/>
-    <mergeCell ref="AY18:BB18"/>
-    <mergeCell ref="AW49:BD51"/>
-    <mergeCell ref="BI45:BK45"/>
-    <mergeCell ref="BC16:BE16"/>
-    <mergeCell ref="C3:D5"/>
-    <mergeCell ref="BM5:BO6"/>
-    <mergeCell ref="AW5:AX6"/>
-    <mergeCell ref="AT3:AV8"/>
-    <mergeCell ref="T17:AG20"/>
-    <mergeCell ref="T26:AG29"/>
-    <mergeCell ref="T35:AG39"/>
-    <mergeCell ref="BE52:BQ55"/>
-    <mergeCell ref="AX42:AZ42"/>
-    <mergeCell ref="AW43:AW44"/>
-    <mergeCell ref="AY5:BB6"/>
-    <mergeCell ref="BF20:BK20"/>
-    <mergeCell ref="AW20:AX20"/>
-    <mergeCell ref="AW52:BD52"/>
-    <mergeCell ref="BO42:BQ42"/>
-    <mergeCell ref="BP5:BP6"/>
-    <mergeCell ref="BO40:BQ40"/>
-    <mergeCell ref="BQ5:BQ6"/>
-    <mergeCell ref="BM21:BO21"/>
-    <mergeCell ref="BF13:BK13"/>
-    <mergeCell ref="AW13:AX13"/>
-    <mergeCell ref="BA45:BH45"/>
-    <mergeCell ref="AW8:AX8"/>
-    <mergeCell ref="BL45:BN45"/>
-    <mergeCell ref="BA42:BH42"/>
-    <mergeCell ref="AY19:BB19"/>
-    <mergeCell ref="AY13:BB13"/>
-    <mergeCell ref="AX40:AZ40"/>
-    <mergeCell ref="AY22:BB22"/>
-    <mergeCell ref="BA43:BH44"/>
-    <mergeCell ref="BL40:BN40"/>
-    <mergeCell ref="BC12:BE12"/>
-    <mergeCell ref="BL43:BN44"/>
-    <mergeCell ref="BF19:BK19"/>
-    <mergeCell ref="BC24:BE24"/>
-    <mergeCell ref="T7:AG11"/>
-    <mergeCell ref="B17:B29"/>
-    <mergeCell ref="AW7:AX7"/>
-    <mergeCell ref="B44:B56"/>
-    <mergeCell ref="BL41:BN41"/>
-    <mergeCell ref="AW3:BQ4"/>
-    <mergeCell ref="BI46:BQ46"/>
-    <mergeCell ref="BM23:BO23"/>
-    <mergeCell ref="BF15:BK15"/>
-    <mergeCell ref="BL5:BL6"/>
-    <mergeCell ref="AY14:BB14"/>
-    <mergeCell ref="AY25:BB25"/>
-    <mergeCell ref="AY31:BQ36"/>
-    <mergeCell ref="AY12:BB12"/>
-    <mergeCell ref="BC14:BE14"/>
-    <mergeCell ref="BM22:BO22"/>
-    <mergeCell ref="AW14:AX14"/>
-    <mergeCell ref="AY7:BB7"/>
-    <mergeCell ref="BC10:BE10"/>
-    <mergeCell ref="BM17:BO17"/>
-    <mergeCell ref="BC23:BE23"/>
-    <mergeCell ref="BF18:BK18"/>
-    <mergeCell ref="AW12:AX12"/>
-    <mergeCell ref="BM14:BO14"/>
-    <mergeCell ref="T47:AG51"/>
-    <mergeCell ref="M2:X2"/>
-    <mergeCell ref="AU2:BF2"/>
-    <mergeCell ref="AW18:AX18"/>
-    <mergeCell ref="BC8:BE8"/>
-    <mergeCell ref="BI43:BK44"/>
-    <mergeCell ref="AU57:BF57"/>
-    <mergeCell ref="AW9:AX9"/>
-    <mergeCell ref="BC22:BE22"/>
-    <mergeCell ref="BA47:BH47"/>
-    <mergeCell ref="BG2:BQ2"/>
-    <mergeCell ref="AJ2:AT2"/>
-    <mergeCell ref="AY56:BQ56"/>
-    <mergeCell ref="Y2:AI2"/>
-    <mergeCell ref="BF9:BK9"/>
-    <mergeCell ref="AY8:BB8"/>
-    <mergeCell ref="AW17:AX17"/>
-    <mergeCell ref="BO43:BQ44"/>
-    <mergeCell ref="BG57:BQ57"/>
-    <mergeCell ref="BC7:BE7"/>
-    <mergeCell ref="BC15:BE15"/>
-    <mergeCell ref="BA40:BH40"/>
-    <mergeCell ref="AW19:AX19"/>
-    <mergeCell ref="AW53:BD55"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/가공도_도면_1.xlsx
+++ b/가공도_도면_1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\duddl\Desktop\Project\a2z\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{660380A4-5322-4233-9727-47280CFCE2E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDEB2998-C9AF-484C-A642-9381DB1EC01C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1920" yWindow="720" windowWidth="20256" windowHeight="11520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="231">
   <si>
     <t>A</t>
   </si>
@@ -527,9 +527,6 @@
   </si>
   <si>
     <t>C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Note : </t>
   </si>
   <si>
     <t>{Input_164}</t>
@@ -994,9 +991,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1015,15 +1009,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1031,6 +1016,27 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1044,15 +1050,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1518,189 +1515,189 @@
       <c r="BR2" s="2"/>
     </row>
     <row r="3" spans="1:71" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B3" s="23" t="s">
+      <c r="B3" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="29" t="s">
-        <v>224</v>
-      </c>
-      <c r="D3" s="30"/>
+      <c r="C3" s="32" t="s">
+        <v>223</v>
+      </c>
+      <c r="D3" s="33"/>
       <c r="Y3" s="3"/>
-      <c r="AT3" s="18" t="s">
-        <v>223</v>
-      </c>
-      <c r="AU3" s="18"/>
-      <c r="AV3" s="19"/>
-      <c r="AW3" s="17" t="s">
+      <c r="AT3" s="17" t="s">
+        <v>222</v>
+      </c>
+      <c r="AU3" s="17"/>
+      <c r="AV3" s="18"/>
+      <c r="AW3" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="AX3" s="18"/>
-      <c r="AY3" s="18"/>
-      <c r="AZ3" s="18"/>
-      <c r="BA3" s="18"/>
-      <c r="BB3" s="18"/>
-      <c r="BC3" s="18"/>
-      <c r="BD3" s="18"/>
-      <c r="BE3" s="18"/>
-      <c r="BF3" s="18"/>
-      <c r="BG3" s="18"/>
-      <c r="BH3" s="18"/>
-      <c r="BI3" s="18"/>
-      <c r="BJ3" s="18"/>
-      <c r="BK3" s="18"/>
-      <c r="BL3" s="18"/>
-      <c r="BM3" s="18"/>
-      <c r="BN3" s="18"/>
-      <c r="BO3" s="18"/>
-      <c r="BP3" s="18"/>
-      <c r="BQ3" s="19"/>
-      <c r="BR3" s="23" t="s">
+      <c r="AX3" s="17"/>
+      <c r="AY3" s="17"/>
+      <c r="AZ3" s="17"/>
+      <c r="BA3" s="17"/>
+      <c r="BB3" s="17"/>
+      <c r="BC3" s="17"/>
+      <c r="BD3" s="17"/>
+      <c r="BE3" s="17"/>
+      <c r="BF3" s="17"/>
+      <c r="BG3" s="17"/>
+      <c r="BH3" s="17"/>
+      <c r="BI3" s="17"/>
+      <c r="BJ3" s="17"/>
+      <c r="BK3" s="17"/>
+      <c r="BL3" s="17"/>
+      <c r="BM3" s="17"/>
+      <c r="BN3" s="17"/>
+      <c r="BO3" s="17"/>
+      <c r="BP3" s="17"/>
+      <c r="BQ3" s="18"/>
+      <c r="BR3" s="25" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:71" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="24"/>
-      <c r="C4" s="31"/>
-      <c r="D4" s="32"/>
+      <c r="B4" s="31"/>
+      <c r="C4" s="34"/>
+      <c r="D4" s="35"/>
       <c r="E4" s="3"/>
       <c r="AA4" s="3"/>
-      <c r="AT4" s="27"/>
-      <c r="AU4" s="27"/>
-      <c r="AV4" s="28"/>
-      <c r="AW4" s="20"/>
-      <c r="AX4" s="21"/>
-      <c r="AY4" s="21"/>
-      <c r="AZ4" s="21"/>
-      <c r="BA4" s="21"/>
-      <c r="BB4" s="21"/>
-      <c r="BC4" s="21"/>
-      <c r="BD4" s="21"/>
-      <c r="BE4" s="21"/>
-      <c r="BF4" s="21"/>
-      <c r="BG4" s="21"/>
-      <c r="BH4" s="21"/>
-      <c r="BI4" s="21"/>
-      <c r="BJ4" s="21"/>
-      <c r="BK4" s="21"/>
-      <c r="BL4" s="21"/>
-      <c r="BM4" s="21"/>
-      <c r="BN4" s="21"/>
-      <c r="BO4" s="21"/>
-      <c r="BP4" s="21"/>
-      <c r="BQ4" s="22"/>
-      <c r="BR4" s="24"/>
+      <c r="AT4" s="23"/>
+      <c r="AU4" s="23"/>
+      <c r="AV4" s="24"/>
+      <c r="AW4" s="19"/>
+      <c r="AX4" s="20"/>
+      <c r="AY4" s="20"/>
+      <c r="AZ4" s="20"/>
+      <c r="BA4" s="20"/>
+      <c r="BB4" s="20"/>
+      <c r="BC4" s="20"/>
+      <c r="BD4" s="20"/>
+      <c r="BE4" s="20"/>
+      <c r="BF4" s="20"/>
+      <c r="BG4" s="20"/>
+      <c r="BH4" s="20"/>
+      <c r="BI4" s="20"/>
+      <c r="BJ4" s="20"/>
+      <c r="BK4" s="20"/>
+      <c r="BL4" s="20"/>
+      <c r="BM4" s="20"/>
+      <c r="BN4" s="20"/>
+      <c r="BO4" s="20"/>
+      <c r="BP4" s="20"/>
+      <c r="BQ4" s="21"/>
+      <c r="BR4" s="31"/>
     </row>
     <row r="5" spans="1:71" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B5" s="24"/>
-      <c r="C5" s="31"/>
-      <c r="D5" s="32"/>
-      <c r="AT5" s="27"/>
-      <c r="AU5" s="27"/>
-      <c r="AV5" s="28"/>
-      <c r="AW5" s="17" t="s">
-        <v>218</v>
-      </c>
-      <c r="AX5" s="19"/>
-      <c r="AY5" s="17" t="s">
+      <c r="B5" s="31"/>
+      <c r="C5" s="34"/>
+      <c r="D5" s="35"/>
+      <c r="AT5" s="23"/>
+      <c r="AU5" s="23"/>
+      <c r="AV5" s="24"/>
+      <c r="AW5" s="16" t="s">
+        <v>217</v>
+      </c>
+      <c r="AX5" s="18"/>
+      <c r="AY5" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="AZ5" s="18"/>
-      <c r="BA5" s="18"/>
-      <c r="BB5" s="19"/>
-      <c r="BC5" s="17" t="s">
+      <c r="AZ5" s="17"/>
+      <c r="BA5" s="17"/>
+      <c r="BB5" s="18"/>
+      <c r="BC5" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="BD5" s="18"/>
-      <c r="BE5" s="19"/>
-      <c r="BF5" s="17" t="s">
+      <c r="BD5" s="17"/>
+      <c r="BE5" s="18"/>
+      <c r="BF5" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="BG5" s="18"/>
-      <c r="BH5" s="18"/>
-      <c r="BI5" s="18"/>
-      <c r="BJ5" s="18"/>
-      <c r="BK5" s="19"/>
-      <c r="BL5" s="23" t="s">
+      <c r="BG5" s="17"/>
+      <c r="BH5" s="17"/>
+      <c r="BI5" s="17"/>
+      <c r="BJ5" s="17"/>
+      <c r="BK5" s="18"/>
+      <c r="BL5" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="BM5" s="17" t="s">
+      <c r="BM5" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="BN5" s="18"/>
-      <c r="BO5" s="19"/>
-      <c r="BP5" s="23" t="s">
+      <c r="BN5" s="17"/>
+      <c r="BO5" s="18"/>
+      <c r="BP5" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="BQ5" s="23" t="s">
+      <c r="BQ5" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="BR5" s="24"/>
+      <c r="BR5" s="31"/>
     </row>
     <row r="6" spans="1:71" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B6" s="24"/>
-      <c r="AT6" s="27"/>
-      <c r="AU6" s="27"/>
-      <c r="AV6" s="28"/>
-      <c r="AW6" s="20"/>
-      <c r="AX6" s="22"/>
-      <c r="AY6" s="20"/>
-      <c r="AZ6" s="21"/>
-      <c r="BA6" s="21"/>
-      <c r="BB6" s="22"/>
-      <c r="BC6" s="20"/>
-      <c r="BD6" s="21"/>
-      <c r="BE6" s="22"/>
-      <c r="BF6" s="20"/>
-      <c r="BG6" s="21"/>
-      <c r="BH6" s="21"/>
-      <c r="BI6" s="21"/>
-      <c r="BJ6" s="21"/>
-      <c r="BK6" s="22"/>
-      <c r="BL6" s="25"/>
-      <c r="BM6" s="20"/>
-      <c r="BN6" s="21"/>
-      <c r="BO6" s="22"/>
-      <c r="BP6" s="25"/>
-      <c r="BQ6" s="25"/>
-      <c r="BR6" s="24"/>
+      <c r="B6" s="31"/>
+      <c r="AT6" s="23"/>
+      <c r="AU6" s="23"/>
+      <c r="AV6" s="24"/>
+      <c r="AW6" s="19"/>
+      <c r="AX6" s="21"/>
+      <c r="AY6" s="19"/>
+      <c r="AZ6" s="20"/>
+      <c r="BA6" s="20"/>
+      <c r="BB6" s="21"/>
+      <c r="BC6" s="19"/>
+      <c r="BD6" s="20"/>
+      <c r="BE6" s="21"/>
+      <c r="BF6" s="19"/>
+      <c r="BG6" s="20"/>
+      <c r="BH6" s="20"/>
+      <c r="BI6" s="20"/>
+      <c r="BJ6" s="20"/>
+      <c r="BK6" s="21"/>
+      <c r="BL6" s="26"/>
+      <c r="BM6" s="19"/>
+      <c r="BN6" s="20"/>
+      <c r="BO6" s="21"/>
+      <c r="BP6" s="26"/>
+      <c r="BQ6" s="26"/>
+      <c r="BR6" s="31"/>
     </row>
     <row r="7" spans="1:71" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B7" s="24"/>
-      <c r="E7" s="16" t="s">
-        <v>226</v>
-      </c>
-      <c r="F7" s="16"/>
-      <c r="G7" s="16"/>
-      <c r="H7" s="16"/>
-      <c r="I7" s="16"/>
-      <c r="J7" s="16"/>
-      <c r="K7" s="16"/>
-      <c r="L7" s="16"/>
-      <c r="M7" s="16"/>
-      <c r="N7" s="16"/>
-      <c r="O7" s="16"/>
-      <c r="P7" s="16"/>
-      <c r="Q7" s="16"/>
-      <c r="R7" s="16"/>
-      <c r="T7" s="16" t="s">
+      <c r="B7" s="31"/>
+      <c r="E7" s="30" t="s">
+        <v>225</v>
+      </c>
+      <c r="F7" s="30"/>
+      <c r="G7" s="30"/>
+      <c r="H7" s="30"/>
+      <c r="I7" s="30"/>
+      <c r="J7" s="30"/>
+      <c r="K7" s="30"/>
+      <c r="L7" s="30"/>
+      <c r="M7" s="30"/>
+      <c r="N7" s="30"/>
+      <c r="O7" s="30"/>
+      <c r="P7" s="30"/>
+      <c r="Q7" s="30"/>
+      <c r="R7" s="30"/>
+      <c r="T7" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="U7" s="16"/>
-      <c r="V7" s="16"/>
-      <c r="W7" s="16"/>
-      <c r="X7" s="16"/>
-      <c r="Y7" s="16"/>
-      <c r="Z7" s="16"/>
-      <c r="AA7" s="16"/>
-      <c r="AB7" s="16"/>
-      <c r="AC7" s="16"/>
-      <c r="AD7" s="16"/>
-      <c r="AE7" s="16"/>
-      <c r="AF7" s="16"/>
-      <c r="AG7" s="16"/>
-      <c r="AT7" s="27"/>
-      <c r="AU7" s="27"/>
-      <c r="AV7" s="28"/>
+      <c r="U7" s="30"/>
+      <c r="V7" s="30"/>
+      <c r="W7" s="30"/>
+      <c r="X7" s="30"/>
+      <c r="Y7" s="30"/>
+      <c r="Z7" s="30"/>
+      <c r="AA7" s="30"/>
+      <c r="AB7" s="30"/>
+      <c r="AC7" s="30"/>
+      <c r="AD7" s="30"/>
+      <c r="AE7" s="30"/>
+      <c r="AF7" s="30"/>
+      <c r="AG7" s="30"/>
+      <c r="AT7" s="23"/>
+      <c r="AU7" s="23"/>
+      <c r="AV7" s="24"/>
       <c r="AW7" s="13" t="s">
         <v>11</v>
       </c>
@@ -1738,41 +1735,41 @@
       <c r="BQ7" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="BR7" s="24"/>
+      <c r="BR7" s="31"/>
     </row>
     <row r="8" spans="1:71" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B8" s="24"/>
-      <c r="E8" s="16"/>
-      <c r="F8" s="16"/>
-      <c r="G8" s="16"/>
-      <c r="H8" s="16"/>
-      <c r="I8" s="16"/>
-      <c r="J8" s="16"/>
-      <c r="K8" s="16"/>
-      <c r="L8" s="16"/>
-      <c r="M8" s="16"/>
-      <c r="N8" s="16"/>
-      <c r="O8" s="16"/>
-      <c r="P8" s="16"/>
-      <c r="Q8" s="16"/>
-      <c r="R8" s="16"/>
-      <c r="T8" s="16"/>
-      <c r="U8" s="16"/>
-      <c r="V8" s="16"/>
-      <c r="W8" s="16"/>
-      <c r="X8" s="16"/>
-      <c r="Y8" s="16"/>
-      <c r="Z8" s="16"/>
-      <c r="AA8" s="16"/>
-      <c r="AB8" s="16"/>
-      <c r="AC8" s="16"/>
-      <c r="AD8" s="16"/>
-      <c r="AE8" s="16"/>
-      <c r="AF8" s="16"/>
-      <c r="AG8" s="16"/>
-      <c r="AT8" s="27"/>
-      <c r="AU8" s="27"/>
-      <c r="AV8" s="28"/>
+      <c r="B8" s="31"/>
+      <c r="E8" s="30"/>
+      <c r="F8" s="30"/>
+      <c r="G8" s="30"/>
+      <c r="H8" s="30"/>
+      <c r="I8" s="30"/>
+      <c r="J8" s="30"/>
+      <c r="K8" s="30"/>
+      <c r="L8" s="30"/>
+      <c r="M8" s="30"/>
+      <c r="N8" s="30"/>
+      <c r="O8" s="30"/>
+      <c r="P8" s="30"/>
+      <c r="Q8" s="30"/>
+      <c r="R8" s="30"/>
+      <c r="T8" s="30"/>
+      <c r="U8" s="30"/>
+      <c r="V8" s="30"/>
+      <c r="W8" s="30"/>
+      <c r="X8" s="30"/>
+      <c r="Y8" s="30"/>
+      <c r="Z8" s="30"/>
+      <c r="AA8" s="30"/>
+      <c r="AB8" s="30"/>
+      <c r="AC8" s="30"/>
+      <c r="AD8" s="30"/>
+      <c r="AE8" s="30"/>
+      <c r="AF8" s="30"/>
+      <c r="AG8" s="30"/>
+      <c r="AT8" s="23"/>
+      <c r="AU8" s="23"/>
+      <c r="AV8" s="24"/>
       <c r="AW8" s="13" t="s">
         <v>19</v>
       </c>
@@ -1810,38 +1807,38 @@
       <c r="BQ8" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="BR8" s="24"/>
+      <c r="BR8" s="31"/>
     </row>
     <row r="9" spans="1:71" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B9" s="24"/>
-      <c r="E9" s="16"/>
-      <c r="F9" s="16"/>
-      <c r="G9" s="16"/>
-      <c r="H9" s="16"/>
-      <c r="I9" s="16"/>
-      <c r="J9" s="16"/>
-      <c r="K9" s="16"/>
-      <c r="L9" s="16"/>
-      <c r="M9" s="16"/>
-      <c r="N9" s="16"/>
-      <c r="O9" s="16"/>
-      <c r="P9" s="16"/>
-      <c r="Q9" s="16"/>
-      <c r="R9" s="16"/>
-      <c r="T9" s="16"/>
-      <c r="U9" s="16"/>
-      <c r="V9" s="16"/>
-      <c r="W9" s="16"/>
-      <c r="X9" s="16"/>
-      <c r="Y9" s="16"/>
-      <c r="Z9" s="16"/>
-      <c r="AA9" s="16"/>
-      <c r="AB9" s="16"/>
-      <c r="AC9" s="16"/>
-      <c r="AD9" s="16"/>
-      <c r="AE9" s="16"/>
-      <c r="AF9" s="16"/>
-      <c r="AG9" s="16"/>
+      <c r="B9" s="31"/>
+      <c r="E9" s="30"/>
+      <c r="F9" s="30"/>
+      <c r="G9" s="30"/>
+      <c r="H9" s="30"/>
+      <c r="I9" s="30"/>
+      <c r="J9" s="30"/>
+      <c r="K9" s="30"/>
+      <c r="L9" s="30"/>
+      <c r="M9" s="30"/>
+      <c r="N9" s="30"/>
+      <c r="O9" s="30"/>
+      <c r="P9" s="30"/>
+      <c r="Q9" s="30"/>
+      <c r="R9" s="30"/>
+      <c r="T9" s="30"/>
+      <c r="U9" s="30"/>
+      <c r="V9" s="30"/>
+      <c r="W9" s="30"/>
+      <c r="X9" s="30"/>
+      <c r="Y9" s="30"/>
+      <c r="Z9" s="30"/>
+      <c r="AA9" s="30"/>
+      <c r="AB9" s="30"/>
+      <c r="AC9" s="30"/>
+      <c r="AD9" s="30"/>
+      <c r="AE9" s="30"/>
+      <c r="AF9" s="30"/>
+      <c r="AG9" s="30"/>
       <c r="AT9" s="11"/>
       <c r="AU9" s="11"/>
       <c r="AV9" s="12"/>
@@ -1882,38 +1879,38 @@
       <c r="BQ9" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="BR9" s="24"/>
+      <c r="BR9" s="31"/>
     </row>
     <row r="10" spans="1:71" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B10" s="24"/>
-      <c r="E10" s="16"/>
-      <c r="F10" s="16"/>
-      <c r="G10" s="16"/>
-      <c r="H10" s="16"/>
-      <c r="I10" s="16"/>
-      <c r="J10" s="16"/>
-      <c r="K10" s="16"/>
-      <c r="L10" s="16"/>
-      <c r="M10" s="16"/>
-      <c r="N10" s="16"/>
-      <c r="O10" s="16"/>
-      <c r="P10" s="16"/>
-      <c r="Q10" s="16"/>
-      <c r="R10" s="16"/>
-      <c r="T10" s="16"/>
-      <c r="U10" s="16"/>
-      <c r="V10" s="16"/>
-      <c r="W10" s="16"/>
-      <c r="X10" s="16"/>
-      <c r="Y10" s="16"/>
-      <c r="Z10" s="16"/>
-      <c r="AA10" s="16"/>
-      <c r="AB10" s="16"/>
-      <c r="AC10" s="16"/>
-      <c r="AD10" s="16"/>
-      <c r="AE10" s="16"/>
-      <c r="AF10" s="16"/>
-      <c r="AG10" s="16"/>
+      <c r="B10" s="31"/>
+      <c r="E10" s="30"/>
+      <c r="F10" s="30"/>
+      <c r="G10" s="30"/>
+      <c r="H10" s="30"/>
+      <c r="I10" s="30"/>
+      <c r="J10" s="30"/>
+      <c r="K10" s="30"/>
+      <c r="L10" s="30"/>
+      <c r="M10" s="30"/>
+      <c r="N10" s="30"/>
+      <c r="O10" s="30"/>
+      <c r="P10" s="30"/>
+      <c r="Q10" s="30"/>
+      <c r="R10" s="30"/>
+      <c r="T10" s="30"/>
+      <c r="U10" s="30"/>
+      <c r="V10" s="30"/>
+      <c r="W10" s="30"/>
+      <c r="X10" s="30"/>
+      <c r="Y10" s="30"/>
+      <c r="Z10" s="30"/>
+      <c r="AA10" s="30"/>
+      <c r="AB10" s="30"/>
+      <c r="AC10" s="30"/>
+      <c r="AD10" s="30"/>
+      <c r="AE10" s="30"/>
+      <c r="AF10" s="30"/>
+      <c r="AG10" s="30"/>
       <c r="AT10" s="11"/>
       <c r="AU10" s="11"/>
       <c r="AV10" s="12"/>
@@ -1954,38 +1951,38 @@
       <c r="BQ10" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="BR10" s="24"/>
+      <c r="BR10" s="31"/>
     </row>
     <row r="11" spans="1:71" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B11" s="24"/>
-      <c r="E11" s="16"/>
-      <c r="F11" s="16"/>
-      <c r="G11" s="16"/>
-      <c r="H11" s="16"/>
-      <c r="I11" s="16"/>
-      <c r="J11" s="16"/>
-      <c r="K11" s="16"/>
-      <c r="L11" s="16"/>
-      <c r="M11" s="16"/>
-      <c r="N11" s="16"/>
-      <c r="O11" s="16"/>
-      <c r="P11" s="16"/>
-      <c r="Q11" s="16"/>
-      <c r="R11" s="16"/>
-      <c r="T11" s="16"/>
-      <c r="U11" s="16"/>
-      <c r="V11" s="16"/>
-      <c r="W11" s="16"/>
-      <c r="X11" s="16"/>
-      <c r="Y11" s="16"/>
-      <c r="Z11" s="16"/>
-      <c r="AA11" s="16"/>
-      <c r="AB11" s="16"/>
-      <c r="AC11" s="16"/>
-      <c r="AD11" s="16"/>
-      <c r="AE11" s="16"/>
-      <c r="AF11" s="16"/>
-      <c r="AG11" s="16"/>
+      <c r="B11" s="31"/>
+      <c r="E11" s="30"/>
+      <c r="F11" s="30"/>
+      <c r="G11" s="30"/>
+      <c r="H11" s="30"/>
+      <c r="I11" s="30"/>
+      <c r="J11" s="30"/>
+      <c r="K11" s="30"/>
+      <c r="L11" s="30"/>
+      <c r="M11" s="30"/>
+      <c r="N11" s="30"/>
+      <c r="O11" s="30"/>
+      <c r="P11" s="30"/>
+      <c r="Q11" s="30"/>
+      <c r="R11" s="30"/>
+      <c r="T11" s="30"/>
+      <c r="U11" s="30"/>
+      <c r="V11" s="30"/>
+      <c r="W11" s="30"/>
+      <c r="X11" s="30"/>
+      <c r="Y11" s="30"/>
+      <c r="Z11" s="30"/>
+      <c r="AA11" s="30"/>
+      <c r="AB11" s="30"/>
+      <c r="AC11" s="30"/>
+      <c r="AD11" s="30"/>
+      <c r="AE11" s="30"/>
+      <c r="AF11" s="30"/>
+      <c r="AG11" s="30"/>
       <c r="AT11" s="11"/>
       <c r="AU11" s="11"/>
       <c r="AV11" s="12"/>
@@ -2026,10 +2023,10 @@
       <c r="BQ11" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="BR11" s="24"/>
+      <c r="BR11" s="31"/>
     </row>
     <row r="12" spans="1:71" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B12" s="24"/>
+      <c r="B12" s="31"/>
       <c r="AW12" s="13" t="s">
         <v>51</v>
       </c>
@@ -2067,10 +2064,10 @@
       <c r="BQ12" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="BR12" s="24"/>
+      <c r="BR12" s="31"/>
     </row>
     <row r="13" spans="1:71" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B13" s="24"/>
+      <c r="B13" s="31"/>
       <c r="AW13" s="13" t="s">
         <v>59</v>
       </c>
@@ -2108,10 +2105,10 @@
       <c r="BQ13" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="BR13" s="24"/>
+      <c r="BR13" s="31"/>
     </row>
     <row r="14" spans="1:71" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B14" s="24"/>
+      <c r="B14" s="31"/>
       <c r="AW14" s="13" t="s">
         <v>67</v>
       </c>
@@ -2149,10 +2146,10 @@
       <c r="BQ14" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="BR14" s="24"/>
+      <c r="BR14" s="31"/>
     </row>
     <row r="15" spans="1:71" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B15" s="24"/>
+      <c r="B15" s="31"/>
       <c r="AW15" s="13" t="s">
         <v>75</v>
       </c>
@@ -2190,10 +2187,10 @@
       <c r="BQ15" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="BR15" s="24"/>
+      <c r="BR15" s="31"/>
     </row>
     <row r="16" spans="1:71" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B16" s="25"/>
+      <c r="B16" s="26"/>
       <c r="AW16" s="13" t="s">
         <v>84</v>
       </c>
@@ -2231,44 +2228,44 @@
       <c r="BQ16" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="BR16" s="25"/>
+      <c r="BR16" s="26"/>
     </row>
     <row r="17" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B17" s="23" t="s">
+      <c r="B17" s="25" t="s">
         <v>83</v>
       </c>
-      <c r="E17" s="16" t="s">
-        <v>227</v>
-      </c>
-      <c r="F17" s="16"/>
-      <c r="G17" s="16"/>
-      <c r="H17" s="16"/>
-      <c r="I17" s="16"/>
-      <c r="J17" s="16"/>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16"/>
-      <c r="M17" s="16"/>
-      <c r="N17" s="16"/>
-      <c r="O17" s="16"/>
-      <c r="P17" s="16"/>
-      <c r="Q17" s="16"/>
-      <c r="R17" s="16"/>
-      <c r="T17" s="16" t="s">
+      <c r="E17" s="30" t="s">
+        <v>226</v>
+      </c>
+      <c r="F17" s="30"/>
+      <c r="G17" s="30"/>
+      <c r="H17" s="30"/>
+      <c r="I17" s="30"/>
+      <c r="J17" s="30"/>
+      <c r="K17" s="30"/>
+      <c r="L17" s="30"/>
+      <c r="M17" s="30"/>
+      <c r="N17" s="30"/>
+      <c r="O17" s="30"/>
+      <c r="P17" s="30"/>
+      <c r="Q17" s="30"/>
+      <c r="R17" s="30"/>
+      <c r="T17" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="U17" s="16"/>
-      <c r="V17" s="16"/>
-      <c r="W17" s="16"/>
-      <c r="X17" s="16"/>
-      <c r="Y17" s="16"/>
-      <c r="Z17" s="16"/>
-      <c r="AA17" s="16"/>
-      <c r="AB17" s="16"/>
-      <c r="AC17" s="16"/>
-      <c r="AD17" s="16"/>
-      <c r="AE17" s="16"/>
-      <c r="AF17" s="16"/>
-      <c r="AG17" s="16"/>
+      <c r="U17" s="30"/>
+      <c r="V17" s="30"/>
+      <c r="W17" s="30"/>
+      <c r="X17" s="30"/>
+      <c r="Y17" s="30"/>
+      <c r="Z17" s="30"/>
+      <c r="AA17" s="30"/>
+      <c r="AB17" s="30"/>
+      <c r="AC17" s="30"/>
+      <c r="AD17" s="30"/>
+      <c r="AE17" s="30"/>
+      <c r="AF17" s="30"/>
+      <c r="AG17" s="30"/>
       <c r="AW17" s="13" t="s">
         <v>92</v>
       </c>
@@ -2306,40 +2303,40 @@
       <c r="BQ17" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="BR17" s="23" t="s">
+      <c r="BR17" s="25" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="18" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B18" s="24"/>
-      <c r="E18" s="16"/>
-      <c r="F18" s="16"/>
-      <c r="G18" s="16"/>
-      <c r="H18" s="16"/>
-      <c r="I18" s="16"/>
-      <c r="J18" s="16"/>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
-      <c r="N18" s="16"/>
-      <c r="O18" s="16"/>
-      <c r="P18" s="16"/>
-      <c r="Q18" s="16"/>
-      <c r="R18" s="16"/>
-      <c r="T18" s="16"/>
-      <c r="U18" s="16"/>
-      <c r="V18" s="16"/>
-      <c r="W18" s="16"/>
-      <c r="X18" s="16"/>
-      <c r="Y18" s="16"/>
-      <c r="Z18" s="16"/>
-      <c r="AA18" s="16"/>
-      <c r="AB18" s="16"/>
-      <c r="AC18" s="16"/>
-      <c r="AD18" s="16"/>
-      <c r="AE18" s="16"/>
-      <c r="AF18" s="16"/>
-      <c r="AG18" s="16"/>
+      <c r="B18" s="31"/>
+      <c r="E18" s="30"/>
+      <c r="F18" s="30"/>
+      <c r="G18" s="30"/>
+      <c r="H18" s="30"/>
+      <c r="I18" s="30"/>
+      <c r="J18" s="30"/>
+      <c r="K18" s="30"/>
+      <c r="L18" s="30"/>
+      <c r="M18" s="30"/>
+      <c r="N18" s="30"/>
+      <c r="O18" s="30"/>
+      <c r="P18" s="30"/>
+      <c r="Q18" s="30"/>
+      <c r="R18" s="30"/>
+      <c r="T18" s="30"/>
+      <c r="U18" s="30"/>
+      <c r="V18" s="30"/>
+      <c r="W18" s="30"/>
+      <c r="X18" s="30"/>
+      <c r="Y18" s="30"/>
+      <c r="Z18" s="30"/>
+      <c r="AA18" s="30"/>
+      <c r="AB18" s="30"/>
+      <c r="AC18" s="30"/>
+      <c r="AD18" s="30"/>
+      <c r="AE18" s="30"/>
+      <c r="AF18" s="30"/>
+      <c r="AG18" s="30"/>
       <c r="AW18" s="13" t="s">
         <v>100</v>
       </c>
@@ -2377,38 +2374,38 @@
       <c r="BQ18" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="BR18" s="24"/>
+      <c r="BR18" s="31"/>
     </row>
     <row r="19" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B19" s="24"/>
-      <c r="E19" s="16"/>
-      <c r="F19" s="16"/>
-      <c r="G19" s="16"/>
-      <c r="H19" s="16"/>
-      <c r="I19" s="16"/>
-      <c r="J19" s="16"/>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="16"/>
-      <c r="N19" s="16"/>
-      <c r="O19" s="16"/>
-      <c r="P19" s="16"/>
-      <c r="Q19" s="16"/>
-      <c r="R19" s="16"/>
-      <c r="T19" s="16"/>
-      <c r="U19" s="16"/>
-      <c r="V19" s="16"/>
-      <c r="W19" s="16"/>
-      <c r="X19" s="16"/>
-      <c r="Y19" s="16"/>
-      <c r="Z19" s="16"/>
-      <c r="AA19" s="16"/>
-      <c r="AB19" s="16"/>
-      <c r="AC19" s="16"/>
-      <c r="AD19" s="16"/>
-      <c r="AE19" s="16"/>
-      <c r="AF19" s="16"/>
-      <c r="AG19" s="16"/>
+      <c r="B19" s="31"/>
+      <c r="E19" s="30"/>
+      <c r="F19" s="30"/>
+      <c r="G19" s="30"/>
+      <c r="H19" s="30"/>
+      <c r="I19" s="30"/>
+      <c r="J19" s="30"/>
+      <c r="K19" s="30"/>
+      <c r="L19" s="30"/>
+      <c r="M19" s="30"/>
+      <c r="N19" s="30"/>
+      <c r="O19" s="30"/>
+      <c r="P19" s="30"/>
+      <c r="Q19" s="30"/>
+      <c r="R19" s="30"/>
+      <c r="T19" s="30"/>
+      <c r="U19" s="30"/>
+      <c r="V19" s="30"/>
+      <c r="W19" s="30"/>
+      <c r="X19" s="30"/>
+      <c r="Y19" s="30"/>
+      <c r="Z19" s="30"/>
+      <c r="AA19" s="30"/>
+      <c r="AB19" s="30"/>
+      <c r="AC19" s="30"/>
+      <c r="AD19" s="30"/>
+      <c r="AE19" s="30"/>
+      <c r="AF19" s="30"/>
+      <c r="AG19" s="30"/>
       <c r="AW19" s="13" t="s">
         <v>108</v>
       </c>
@@ -2446,38 +2443,38 @@
       <c r="BQ19" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="BR19" s="24"/>
+      <c r="BR19" s="31"/>
     </row>
     <row r="20" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B20" s="24"/>
-      <c r="E20" s="16"/>
-      <c r="F20" s="16"/>
-      <c r="G20" s="16"/>
-      <c r="H20" s="16"/>
-      <c r="I20" s="16"/>
-      <c r="J20" s="16"/>
-      <c r="K20" s="16"/>
-      <c r="L20" s="16"/>
-      <c r="M20" s="16"/>
-      <c r="N20" s="16"/>
-      <c r="O20" s="16"/>
-      <c r="P20" s="16"/>
-      <c r="Q20" s="16"/>
-      <c r="R20" s="16"/>
-      <c r="T20" s="16"/>
-      <c r="U20" s="16"/>
-      <c r="V20" s="16"/>
-      <c r="W20" s="16"/>
-      <c r="X20" s="16"/>
-      <c r="Y20" s="16"/>
-      <c r="Z20" s="16"/>
-      <c r="AA20" s="16"/>
-      <c r="AB20" s="16"/>
-      <c r="AC20" s="16"/>
-      <c r="AD20" s="16"/>
-      <c r="AE20" s="16"/>
-      <c r="AF20" s="16"/>
-      <c r="AG20" s="16"/>
+      <c r="B20" s="31"/>
+      <c r="E20" s="30"/>
+      <c r="F20" s="30"/>
+      <c r="G20" s="30"/>
+      <c r="H20" s="30"/>
+      <c r="I20" s="30"/>
+      <c r="J20" s="30"/>
+      <c r="K20" s="30"/>
+      <c r="L20" s="30"/>
+      <c r="M20" s="30"/>
+      <c r="N20" s="30"/>
+      <c r="O20" s="30"/>
+      <c r="P20" s="30"/>
+      <c r="Q20" s="30"/>
+      <c r="R20" s="30"/>
+      <c r="T20" s="30"/>
+      <c r="U20" s="30"/>
+      <c r="V20" s="30"/>
+      <c r="W20" s="30"/>
+      <c r="X20" s="30"/>
+      <c r="Y20" s="30"/>
+      <c r="Z20" s="30"/>
+      <c r="AA20" s="30"/>
+      <c r="AB20" s="30"/>
+      <c r="AC20" s="30"/>
+      <c r="AD20" s="30"/>
+      <c r="AE20" s="30"/>
+      <c r="AF20" s="30"/>
+      <c r="AG20" s="30"/>
       <c r="AW20" s="13" t="s">
         <v>116</v>
       </c>
@@ -2515,10 +2512,10 @@
       <c r="BQ20" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="BR20" s="24"/>
+      <c r="BR20" s="31"/>
     </row>
     <row r="21" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B21" s="24"/>
+      <c r="B21" s="31"/>
       <c r="AW21" s="13" t="s">
         <v>124</v>
       </c>
@@ -2556,10 +2553,10 @@
       <c r="BQ21" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="BR21" s="24"/>
+      <c r="BR21" s="31"/>
     </row>
     <row r="22" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B22" s="24"/>
+      <c r="B22" s="31"/>
       <c r="AW22" s="13" t="s">
         <v>132</v>
       </c>
@@ -2597,10 +2594,10 @@
       <c r="BQ22" s="8" t="s">
         <v>139</v>
       </c>
-      <c r="BR22" s="24"/>
+      <c r="BR22" s="31"/>
     </row>
     <row r="23" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B23" s="24"/>
+      <c r="B23" s="31"/>
       <c r="AW23" s="13" t="s">
         <v>140</v>
       </c>
@@ -2638,10 +2635,10 @@
       <c r="BQ23" s="8" t="s">
         <v>147</v>
       </c>
-      <c r="BR23" s="24"/>
+      <c r="BR23" s="31"/>
     </row>
     <row r="24" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B24" s="24"/>
+      <c r="B24" s="31"/>
       <c r="AW24" s="13" t="s">
         <v>148</v>
       </c>
@@ -2679,27 +2676,27 @@
       <c r="BQ24" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="BR24" s="24"/>
+      <c r="BR24" s="31"/>
     </row>
     <row r="25" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B25" s="24"/>
+      <c r="B25" s="31"/>
       <c r="AW25" s="13" t="s">
+        <v>218</v>
+      </c>
+      <c r="AX25" s="15"/>
+      <c r="AY25" s="27" t="s">
+        <v>156</v>
+      </c>
+      <c r="AZ25" s="28"/>
+      <c r="BA25" s="28"/>
+      <c r="BB25" s="29"/>
+      <c r="BC25" s="14" t="s">
         <v>219</v>
-      </c>
-      <c r="AX25" s="15"/>
-      <c r="AY25" s="33" t="s">
-        <v>156</v>
-      </c>
-      <c r="AZ25" s="34"/>
-      <c r="BA25" s="34"/>
-      <c r="BB25" s="35"/>
-      <c r="BC25" s="14" t="s">
-        <v>220</v>
       </c>
       <c r="BD25" s="14"/>
       <c r="BE25" s="15"/>
       <c r="BF25" s="13" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="BG25" s="14"/>
       <c r="BH25" s="14"/>
@@ -2710,7 +2707,7 @@
         <v>157</v>
       </c>
       <c r="BM25" s="13" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="BN25" s="14"/>
       <c r="BO25" s="15"/>
@@ -2720,42 +2717,42 @@
       <c r="BQ25" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="BR25" s="24"/>
+      <c r="BR25" s="31"/>
     </row>
     <row r="26" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B26" s="24"/>
-      <c r="E26" s="16" t="s">
-        <v>228</v>
-      </c>
-      <c r="F26" s="16"/>
-      <c r="G26" s="16"/>
-      <c r="H26" s="16"/>
-      <c r="I26" s="16"/>
-      <c r="J26" s="16"/>
-      <c r="K26" s="16"/>
-      <c r="L26" s="16"/>
-      <c r="M26" s="16"/>
-      <c r="N26" s="16"/>
-      <c r="O26" s="16"/>
-      <c r="P26" s="16"/>
-      <c r="Q26" s="16"/>
-      <c r="R26" s="16"/>
-      <c r="T26" s="16" t="s">
-        <v>171</v>
-      </c>
-      <c r="U26" s="16"/>
-      <c r="V26" s="16"/>
-      <c r="W26" s="16"/>
-      <c r="X26" s="16"/>
-      <c r="Y26" s="16"/>
-      <c r="Z26" s="16"/>
-      <c r="AA26" s="16"/>
-      <c r="AB26" s="16"/>
-      <c r="AC26" s="16"/>
-      <c r="AD26" s="16"/>
-      <c r="AE26" s="16"/>
-      <c r="AF26" s="16"/>
-      <c r="AG26" s="16"/>
+      <c r="B26" s="31"/>
+      <c r="E26" s="30" t="s">
+        <v>227</v>
+      </c>
+      <c r="F26" s="30"/>
+      <c r="G26" s="30"/>
+      <c r="H26" s="30"/>
+      <c r="I26" s="30"/>
+      <c r="J26" s="30"/>
+      <c r="K26" s="30"/>
+      <c r="L26" s="30"/>
+      <c r="M26" s="30"/>
+      <c r="N26" s="30"/>
+      <c r="O26" s="30"/>
+      <c r="P26" s="30"/>
+      <c r="Q26" s="30"/>
+      <c r="R26" s="30"/>
+      <c r="T26" s="30" t="s">
+        <v>170</v>
+      </c>
+      <c r="U26" s="30"/>
+      <c r="V26" s="30"/>
+      <c r="W26" s="30"/>
+      <c r="X26" s="30"/>
+      <c r="Y26" s="30"/>
+      <c r="Z26" s="30"/>
+      <c r="AA26" s="30"/>
+      <c r="AB26" s="30"/>
+      <c r="AC26" s="30"/>
+      <c r="AD26" s="30"/>
+      <c r="AE26" s="30"/>
+      <c r="AF26" s="30"/>
+      <c r="AG26" s="30"/>
       <c r="AW26" s="13" t="s">
         <v>160</v>
       </c>
@@ -2793,71 +2790,71 @@
       <c r="BQ26" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="BR26" s="24"/>
+      <c r="BR26" s="31"/>
     </row>
     <row r="27" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B27" s="24"/>
-      <c r="E27" s="16"/>
-      <c r="F27" s="16"/>
-      <c r="G27" s="16"/>
-      <c r="H27" s="16"/>
-      <c r="I27" s="16"/>
-      <c r="J27" s="16"/>
-      <c r="K27" s="16"/>
-      <c r="L27" s="16"/>
-      <c r="M27" s="16"/>
-      <c r="N27" s="16"/>
-      <c r="O27" s="16"/>
-      <c r="P27" s="16"/>
-      <c r="Q27" s="16"/>
-      <c r="R27" s="16"/>
-      <c r="T27" s="16"/>
-      <c r="U27" s="16"/>
-      <c r="V27" s="16"/>
-      <c r="W27" s="16"/>
-      <c r="X27" s="16"/>
-      <c r="Y27" s="16"/>
-      <c r="Z27" s="16"/>
-      <c r="AA27" s="16"/>
-      <c r="AB27" s="16"/>
-      <c r="AC27" s="16"/>
-      <c r="AD27" s="16"/>
-      <c r="AE27" s="16"/>
-      <c r="AF27" s="16"/>
-      <c r="AG27" s="16"/>
+      <c r="B27" s="31"/>
+      <c r="E27" s="30"/>
+      <c r="F27" s="30"/>
+      <c r="G27" s="30"/>
+      <c r="H27" s="30"/>
+      <c r="I27" s="30"/>
+      <c r="J27" s="30"/>
+      <c r="K27" s="30"/>
+      <c r="L27" s="30"/>
+      <c r="M27" s="30"/>
+      <c r="N27" s="30"/>
+      <c r="O27" s="30"/>
+      <c r="P27" s="30"/>
+      <c r="Q27" s="30"/>
+      <c r="R27" s="30"/>
+      <c r="T27" s="30"/>
+      <c r="U27" s="30"/>
+      <c r="V27" s="30"/>
+      <c r="W27" s="30"/>
+      <c r="X27" s="30"/>
+      <c r="Y27" s="30"/>
+      <c r="Z27" s="30"/>
+      <c r="AA27" s="30"/>
+      <c r="AB27" s="30"/>
+      <c r="AC27" s="30"/>
+      <c r="AD27" s="30"/>
+      <c r="AE27" s="30"/>
+      <c r="AF27" s="30"/>
+      <c r="AG27" s="30"/>
       <c r="BQ27" s="6"/>
-      <c r="BR27" s="24"/>
+      <c r="BR27" s="31"/>
     </row>
     <row r="28" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B28" s="24"/>
-      <c r="E28" s="16"/>
-      <c r="F28" s="16"/>
-      <c r="G28" s="16"/>
-      <c r="H28" s="16"/>
-      <c r="I28" s="16"/>
-      <c r="J28" s="16"/>
-      <c r="K28" s="16"/>
-      <c r="L28" s="16"/>
-      <c r="M28" s="16"/>
-      <c r="N28" s="16"/>
-      <c r="O28" s="16"/>
-      <c r="P28" s="16"/>
-      <c r="Q28" s="16"/>
-      <c r="R28" s="16"/>
-      <c r="T28" s="16"/>
-      <c r="U28" s="16"/>
-      <c r="V28" s="16"/>
-      <c r="W28" s="16"/>
-      <c r="X28" s="16"/>
-      <c r="Y28" s="16"/>
-      <c r="Z28" s="16"/>
-      <c r="AA28" s="16"/>
-      <c r="AB28" s="16"/>
-      <c r="AC28" s="16"/>
-      <c r="AD28" s="16"/>
-      <c r="AE28" s="16"/>
-      <c r="AF28" s="16"/>
-      <c r="AG28" s="16"/>
+      <c r="B28" s="31"/>
+      <c r="E28" s="30"/>
+      <c r="F28" s="30"/>
+      <c r="G28" s="30"/>
+      <c r="H28" s="30"/>
+      <c r="I28" s="30"/>
+      <c r="J28" s="30"/>
+      <c r="K28" s="30"/>
+      <c r="L28" s="30"/>
+      <c r="M28" s="30"/>
+      <c r="N28" s="30"/>
+      <c r="O28" s="30"/>
+      <c r="P28" s="30"/>
+      <c r="Q28" s="30"/>
+      <c r="R28" s="30"/>
+      <c r="T28" s="30"/>
+      <c r="U28" s="30"/>
+      <c r="V28" s="30"/>
+      <c r="W28" s="30"/>
+      <c r="X28" s="30"/>
+      <c r="Y28" s="30"/>
+      <c r="Z28" s="30"/>
+      <c r="AA28" s="30"/>
+      <c r="AB28" s="30"/>
+      <c r="AC28" s="30"/>
+      <c r="AD28" s="30"/>
+      <c r="AE28" s="30"/>
+      <c r="AF28" s="30"/>
+      <c r="AG28" s="30"/>
       <c r="AI28" s="3"/>
       <c r="AV28" s="6"/>
       <c r="AW28" s="9"/>
@@ -2881,369 +2878,367 @@
       <c r="BO28" s="9"/>
       <c r="BP28" s="9"/>
       <c r="BQ28" s="9"/>
-      <c r="BR28" s="24"/>
+      <c r="BR28" s="31"/>
     </row>
     <row r="29" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B29" s="25"/>
-      <c r="E29" s="16"/>
-      <c r="F29" s="16"/>
-      <c r="G29" s="16"/>
-      <c r="H29" s="16"/>
-      <c r="I29" s="16"/>
-      <c r="J29" s="16"/>
-      <c r="K29" s="16"/>
-      <c r="L29" s="16"/>
-      <c r="M29" s="16"/>
-      <c r="N29" s="16"/>
-      <c r="O29" s="16"/>
-      <c r="P29" s="16"/>
-      <c r="Q29" s="16"/>
-      <c r="R29" s="16"/>
-      <c r="T29" s="16"/>
-      <c r="U29" s="16"/>
-      <c r="V29" s="16"/>
-      <c r="W29" s="16"/>
-      <c r="X29" s="16"/>
-      <c r="Y29" s="16"/>
-      <c r="Z29" s="16"/>
-      <c r="AA29" s="16"/>
-      <c r="AB29" s="16"/>
-      <c r="AC29" s="16"/>
-      <c r="AD29" s="16"/>
-      <c r="AE29" s="16"/>
-      <c r="AF29" s="16"/>
-      <c r="AG29" s="16"/>
+      <c r="B29" s="26"/>
+      <c r="E29" s="30"/>
+      <c r="F29" s="30"/>
+      <c r="G29" s="30"/>
+      <c r="H29" s="30"/>
+      <c r="I29" s="30"/>
+      <c r="J29" s="30"/>
+      <c r="K29" s="30"/>
+      <c r="L29" s="30"/>
+      <c r="M29" s="30"/>
+      <c r="N29" s="30"/>
+      <c r="O29" s="30"/>
+      <c r="P29" s="30"/>
+      <c r="Q29" s="30"/>
+      <c r="R29" s="30"/>
+      <c r="T29" s="30"/>
+      <c r="U29" s="30"/>
+      <c r="V29" s="30"/>
+      <c r="W29" s="30"/>
+      <c r="X29" s="30"/>
+      <c r="Y29" s="30"/>
+      <c r="Z29" s="30"/>
+      <c r="AA29" s="30"/>
+      <c r="AB29" s="30"/>
+      <c r="AC29" s="30"/>
+      <c r="AD29" s="30"/>
+      <c r="AE29" s="30"/>
+      <c r="AF29" s="30"/>
+      <c r="AG29" s="30"/>
       <c r="BQ29" s="6"/>
-      <c r="BR29" s="25"/>
+      <c r="BR29" s="26"/>
     </row>
     <row r="30" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B30" s="23" t="s">
+      <c r="B30" s="25" t="s">
         <v>168</v>
       </c>
-      <c r="BR30" s="23" t="s">
+      <c r="BR30" s="25" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="31" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B31" s="24"/>
-      <c r="AW31" s="17" t="s">
+      <c r="B31" s="31"/>
+      <c r="AW31" s="16"/>
+      <c r="AX31" s="17"/>
+      <c r="AY31" s="17" t="s">
         <v>169</v>
       </c>
-      <c r="AX31" s="18"/>
-      <c r="AY31" s="18" t="s">
-        <v>170</v>
-      </c>
-      <c r="AZ31" s="18"/>
-      <c r="BA31" s="18"/>
-      <c r="BB31" s="18"/>
-      <c r="BC31" s="18"/>
-      <c r="BD31" s="18"/>
-      <c r="BE31" s="18"/>
-      <c r="BF31" s="18"/>
-      <c r="BG31" s="18"/>
-      <c r="BH31" s="18"/>
-      <c r="BI31" s="18"/>
-      <c r="BJ31" s="18"/>
-      <c r="BK31" s="18"/>
-      <c r="BL31" s="18"/>
-      <c r="BM31" s="18"/>
-      <c r="BN31" s="18"/>
-      <c r="BO31" s="18"/>
-      <c r="BP31" s="18"/>
-      <c r="BQ31" s="19"/>
-      <c r="BR31" s="24"/>
+      <c r="AZ31" s="17"/>
+      <c r="BA31" s="17"/>
+      <c r="BB31" s="17"/>
+      <c r="BC31" s="17"/>
+      <c r="BD31" s="17"/>
+      <c r="BE31" s="17"/>
+      <c r="BF31" s="17"/>
+      <c r="BG31" s="17"/>
+      <c r="BH31" s="17"/>
+      <c r="BI31" s="17"/>
+      <c r="BJ31" s="17"/>
+      <c r="BK31" s="17"/>
+      <c r="BL31" s="17"/>
+      <c r="BM31" s="17"/>
+      <c r="BN31" s="17"/>
+      <c r="BO31" s="17"/>
+      <c r="BP31" s="17"/>
+      <c r="BQ31" s="18"/>
+      <c r="BR31" s="31"/>
     </row>
     <row r="32" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B32" s="24"/>
+      <c r="B32" s="31"/>
       <c r="E32" s="3"/>
       <c r="AA32" s="3"/>
-      <c r="AW32" s="26"/>
-      <c r="AX32" s="27"/>
-      <c r="AY32" s="27"/>
-      <c r="AZ32" s="27"/>
-      <c r="BA32" s="27"/>
-      <c r="BB32" s="27"/>
-      <c r="BC32" s="27"/>
-      <c r="BD32" s="27"/>
-      <c r="BE32" s="27"/>
-      <c r="BF32" s="27"/>
-      <c r="BG32" s="27"/>
-      <c r="BH32" s="27"/>
-      <c r="BI32" s="27"/>
-      <c r="BJ32" s="27"/>
-      <c r="BK32" s="27"/>
-      <c r="BL32" s="27"/>
-      <c r="BM32" s="27"/>
-      <c r="BN32" s="27"/>
-      <c r="BO32" s="27"/>
-      <c r="BP32" s="27"/>
-      <c r="BQ32" s="28"/>
-      <c r="BR32" s="24"/>
+      <c r="AW32" s="22"/>
+      <c r="AX32" s="23"/>
+      <c r="AY32" s="23"/>
+      <c r="AZ32" s="23"/>
+      <c r="BA32" s="23"/>
+      <c r="BB32" s="23"/>
+      <c r="BC32" s="23"/>
+      <c r="BD32" s="23"/>
+      <c r="BE32" s="23"/>
+      <c r="BF32" s="23"/>
+      <c r="BG32" s="23"/>
+      <c r="BH32" s="23"/>
+      <c r="BI32" s="23"/>
+      <c r="BJ32" s="23"/>
+      <c r="BK32" s="23"/>
+      <c r="BL32" s="23"/>
+      <c r="BM32" s="23"/>
+      <c r="BN32" s="23"/>
+      <c r="BO32" s="23"/>
+      <c r="BP32" s="23"/>
+      <c r="BQ32" s="24"/>
+      <c r="BR32" s="31"/>
     </row>
     <row r="33" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B33" s="24"/>
-      <c r="AW33" s="26"/>
-      <c r="AX33" s="27"/>
-      <c r="AY33" s="27"/>
-      <c r="AZ33" s="27"/>
-      <c r="BA33" s="27"/>
-      <c r="BB33" s="27"/>
-      <c r="BC33" s="27"/>
-      <c r="BD33" s="27"/>
-      <c r="BE33" s="27"/>
-      <c r="BF33" s="27"/>
-      <c r="BG33" s="27"/>
-      <c r="BH33" s="27"/>
-      <c r="BI33" s="27"/>
-      <c r="BJ33" s="27"/>
-      <c r="BK33" s="27"/>
-      <c r="BL33" s="27"/>
-      <c r="BM33" s="27"/>
-      <c r="BN33" s="27"/>
-      <c r="BO33" s="27"/>
-      <c r="BP33" s="27"/>
-      <c r="BQ33" s="28"/>
-      <c r="BR33" s="24"/>
+      <c r="B33" s="31"/>
+      <c r="AW33" s="22"/>
+      <c r="AX33" s="23"/>
+      <c r="AY33" s="23"/>
+      <c r="AZ33" s="23"/>
+      <c r="BA33" s="23"/>
+      <c r="BB33" s="23"/>
+      <c r="BC33" s="23"/>
+      <c r="BD33" s="23"/>
+      <c r="BE33" s="23"/>
+      <c r="BF33" s="23"/>
+      <c r="BG33" s="23"/>
+      <c r="BH33" s="23"/>
+      <c r="BI33" s="23"/>
+      <c r="BJ33" s="23"/>
+      <c r="BK33" s="23"/>
+      <c r="BL33" s="23"/>
+      <c r="BM33" s="23"/>
+      <c r="BN33" s="23"/>
+      <c r="BO33" s="23"/>
+      <c r="BP33" s="23"/>
+      <c r="BQ33" s="24"/>
+      <c r="BR33" s="31"/>
     </row>
     <row r="34" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B34" s="24"/>
-      <c r="AW34" s="26"/>
-      <c r="AX34" s="27"/>
-      <c r="AY34" s="27"/>
-      <c r="AZ34" s="27"/>
-      <c r="BA34" s="27"/>
-      <c r="BB34" s="27"/>
-      <c r="BC34" s="27"/>
-      <c r="BD34" s="27"/>
-      <c r="BE34" s="27"/>
-      <c r="BF34" s="27"/>
-      <c r="BG34" s="27"/>
-      <c r="BH34" s="27"/>
-      <c r="BI34" s="27"/>
-      <c r="BJ34" s="27"/>
-      <c r="BK34" s="27"/>
-      <c r="BL34" s="27"/>
-      <c r="BM34" s="27"/>
-      <c r="BN34" s="27"/>
-      <c r="BO34" s="27"/>
-      <c r="BP34" s="27"/>
-      <c r="BQ34" s="28"/>
-      <c r="BR34" s="24"/>
+      <c r="B34" s="31"/>
+      <c r="AW34" s="22"/>
+      <c r="AX34" s="23"/>
+      <c r="AY34" s="23"/>
+      <c r="AZ34" s="23"/>
+      <c r="BA34" s="23"/>
+      <c r="BB34" s="23"/>
+      <c r="BC34" s="23"/>
+      <c r="BD34" s="23"/>
+      <c r="BE34" s="23"/>
+      <c r="BF34" s="23"/>
+      <c r="BG34" s="23"/>
+      <c r="BH34" s="23"/>
+      <c r="BI34" s="23"/>
+      <c r="BJ34" s="23"/>
+      <c r="BK34" s="23"/>
+      <c r="BL34" s="23"/>
+      <c r="BM34" s="23"/>
+      <c r="BN34" s="23"/>
+      <c r="BO34" s="23"/>
+      <c r="BP34" s="23"/>
+      <c r="BQ34" s="24"/>
+      <c r="BR34" s="31"/>
     </row>
     <row r="35" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B35" s="24"/>
-      <c r="E35" s="16" t="s">
-        <v>229</v>
-      </c>
-      <c r="F35" s="16"/>
-      <c r="G35" s="16"/>
-      <c r="H35" s="16"/>
-      <c r="I35" s="16"/>
-      <c r="J35" s="16"/>
-      <c r="K35" s="16"/>
-      <c r="L35" s="16"/>
-      <c r="M35" s="16"/>
-      <c r="N35" s="16"/>
-      <c r="O35" s="16"/>
-      <c r="P35" s="16"/>
-      <c r="Q35" s="16"/>
-      <c r="R35" s="16"/>
-      <c r="T35" s="16" t="s">
+      <c r="B35" s="31"/>
+      <c r="E35" s="30" t="s">
+        <v>228</v>
+      </c>
+      <c r="F35" s="30"/>
+      <c r="G35" s="30"/>
+      <c r="H35" s="30"/>
+      <c r="I35" s="30"/>
+      <c r="J35" s="30"/>
+      <c r="K35" s="30"/>
+      <c r="L35" s="30"/>
+      <c r="M35" s="30"/>
+      <c r="N35" s="30"/>
+      <c r="O35" s="30"/>
+      <c r="P35" s="30"/>
+      <c r="Q35" s="30"/>
+      <c r="R35" s="30"/>
+      <c r="T35" s="30" t="s">
+        <v>171</v>
+      </c>
+      <c r="U35" s="30"/>
+      <c r="V35" s="30"/>
+      <c r="W35" s="30"/>
+      <c r="X35" s="30"/>
+      <c r="Y35" s="30"/>
+      <c r="Z35" s="30"/>
+      <c r="AA35" s="30"/>
+      <c r="AB35" s="30"/>
+      <c r="AC35" s="30"/>
+      <c r="AD35" s="30"/>
+      <c r="AE35" s="30"/>
+      <c r="AF35" s="30"/>
+      <c r="AG35" s="30"/>
+      <c r="AW35" s="22"/>
+      <c r="AX35" s="23"/>
+      <c r="AY35" s="23"/>
+      <c r="AZ35" s="23"/>
+      <c r="BA35" s="23"/>
+      <c r="BB35" s="23"/>
+      <c r="BC35" s="23"/>
+      <c r="BD35" s="23"/>
+      <c r="BE35" s="23"/>
+      <c r="BF35" s="23"/>
+      <c r="BG35" s="23"/>
+      <c r="BH35" s="23"/>
+      <c r="BI35" s="23"/>
+      <c r="BJ35" s="23"/>
+      <c r="BK35" s="23"/>
+      <c r="BL35" s="23"/>
+      <c r="BM35" s="23"/>
+      <c r="BN35" s="23"/>
+      <c r="BO35" s="23"/>
+      <c r="BP35" s="23"/>
+      <c r="BQ35" s="24"/>
+      <c r="BR35" s="31"/>
+    </row>
+    <row r="36" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B36" s="31"/>
+      <c r="E36" s="30"/>
+      <c r="F36" s="30"/>
+      <c r="G36" s="30"/>
+      <c r="H36" s="30"/>
+      <c r="I36" s="30"/>
+      <c r="J36" s="30"/>
+      <c r="K36" s="30"/>
+      <c r="L36" s="30"/>
+      <c r="M36" s="30"/>
+      <c r="N36" s="30"/>
+      <c r="O36" s="30"/>
+      <c r="P36" s="30"/>
+      <c r="Q36" s="30"/>
+      <c r="R36" s="30"/>
+      <c r="T36" s="30"/>
+      <c r="U36" s="30"/>
+      <c r="V36" s="30"/>
+      <c r="W36" s="30"/>
+      <c r="X36" s="30"/>
+      <c r="Y36" s="30"/>
+      <c r="Z36" s="30"/>
+      <c r="AA36" s="30"/>
+      <c r="AB36" s="30"/>
+      <c r="AC36" s="30"/>
+      <c r="AD36" s="30"/>
+      <c r="AE36" s="30"/>
+      <c r="AF36" s="30"/>
+      <c r="AG36" s="30"/>
+      <c r="AW36" s="19"/>
+      <c r="AX36" s="20"/>
+      <c r="AY36" s="20"/>
+      <c r="AZ36" s="20"/>
+      <c r="BA36" s="20"/>
+      <c r="BB36" s="20"/>
+      <c r="BC36" s="20"/>
+      <c r="BD36" s="20"/>
+      <c r="BE36" s="20"/>
+      <c r="BF36" s="20"/>
+      <c r="BG36" s="20"/>
+      <c r="BH36" s="20"/>
+      <c r="BI36" s="20"/>
+      <c r="BJ36" s="20"/>
+      <c r="BK36" s="20"/>
+      <c r="BL36" s="20"/>
+      <c r="BM36" s="20"/>
+      <c r="BN36" s="20"/>
+      <c r="BO36" s="20"/>
+      <c r="BP36" s="20"/>
+      <c r="BQ36" s="21"/>
+      <c r="BR36" s="31"/>
+    </row>
+    <row r="37" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B37" s="31"/>
+      <c r="E37" s="30"/>
+      <c r="F37" s="30"/>
+      <c r="G37" s="30"/>
+      <c r="H37" s="30"/>
+      <c r="I37" s="30"/>
+      <c r="J37" s="30"/>
+      <c r="K37" s="30"/>
+      <c r="L37" s="30"/>
+      <c r="M37" s="30"/>
+      <c r="N37" s="30"/>
+      <c r="O37" s="30"/>
+      <c r="P37" s="30"/>
+      <c r="Q37" s="30"/>
+      <c r="R37" s="30"/>
+      <c r="T37" s="30"/>
+      <c r="U37" s="30"/>
+      <c r="V37" s="30"/>
+      <c r="W37" s="30"/>
+      <c r="X37" s="30"/>
+      <c r="Y37" s="30"/>
+      <c r="Z37" s="30"/>
+      <c r="AA37" s="30"/>
+      <c r="AB37" s="30"/>
+      <c r="AC37" s="30"/>
+      <c r="AD37" s="30"/>
+      <c r="AE37" s="30"/>
+      <c r="AF37" s="30"/>
+      <c r="AG37" s="30"/>
+      <c r="BR37" s="31"/>
+    </row>
+    <row r="38" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B38" s="31"/>
+      <c r="E38" s="30"/>
+      <c r="F38" s="30"/>
+      <c r="G38" s="30"/>
+      <c r="H38" s="30"/>
+      <c r="I38" s="30"/>
+      <c r="J38" s="30"/>
+      <c r="K38" s="30"/>
+      <c r="L38" s="30"/>
+      <c r="M38" s="30"/>
+      <c r="N38" s="30"/>
+      <c r="O38" s="30"/>
+      <c r="P38" s="30"/>
+      <c r="Q38" s="30"/>
+      <c r="R38" s="30"/>
+      <c r="T38" s="30"/>
+      <c r="U38" s="30"/>
+      <c r="V38" s="30"/>
+      <c r="W38" s="30"/>
+      <c r="X38" s="30"/>
+      <c r="Y38" s="30"/>
+      <c r="Z38" s="30"/>
+      <c r="AA38" s="30"/>
+      <c r="AB38" s="30"/>
+      <c r="AC38" s="30"/>
+      <c r="AD38" s="30"/>
+      <c r="AE38" s="30"/>
+      <c r="AF38" s="30"/>
+      <c r="AG38" s="30"/>
+      <c r="BR38" s="31"/>
+    </row>
+    <row r="39" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B39" s="31"/>
+      <c r="E39" s="30"/>
+      <c r="F39" s="30"/>
+      <c r="G39" s="30"/>
+      <c r="H39" s="30"/>
+      <c r="I39" s="30"/>
+      <c r="J39" s="30"/>
+      <c r="K39" s="30"/>
+      <c r="L39" s="30"/>
+      <c r="M39" s="30"/>
+      <c r="N39" s="30"/>
+      <c r="O39" s="30"/>
+      <c r="P39" s="30"/>
+      <c r="Q39" s="30"/>
+      <c r="R39" s="30"/>
+      <c r="T39" s="30"/>
+      <c r="U39" s="30"/>
+      <c r="V39" s="30"/>
+      <c r="W39" s="30"/>
+      <c r="X39" s="30"/>
+      <c r="Y39" s="30"/>
+      <c r="Z39" s="30"/>
+      <c r="AA39" s="30"/>
+      <c r="AB39" s="30"/>
+      <c r="AC39" s="30"/>
+      <c r="AD39" s="30"/>
+      <c r="AE39" s="30"/>
+      <c r="AF39" s="30"/>
+      <c r="AG39" s="30"/>
+      <c r="AW39" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="U35" s="16"/>
-      <c r="V35" s="16"/>
-      <c r="W35" s="16"/>
-      <c r="X35" s="16"/>
-      <c r="Y35" s="16"/>
-      <c r="Z35" s="16"/>
-      <c r="AA35" s="16"/>
-      <c r="AB35" s="16"/>
-      <c r="AC35" s="16"/>
-      <c r="AD35" s="16"/>
-      <c r="AE35" s="16"/>
-      <c r="AF35" s="16"/>
-      <c r="AG35" s="16"/>
-      <c r="AW35" s="26"/>
-      <c r="AX35" s="27"/>
-      <c r="AY35" s="27"/>
-      <c r="AZ35" s="27"/>
-      <c r="BA35" s="27"/>
-      <c r="BB35" s="27"/>
-      <c r="BC35" s="27"/>
-      <c r="BD35" s="27"/>
-      <c r="BE35" s="27"/>
-      <c r="BF35" s="27"/>
-      <c r="BG35" s="27"/>
-      <c r="BH35" s="27"/>
-      <c r="BI35" s="27"/>
-      <c r="BJ35" s="27"/>
-      <c r="BK35" s="27"/>
-      <c r="BL35" s="27"/>
-      <c r="BM35" s="27"/>
-      <c r="BN35" s="27"/>
-      <c r="BO35" s="27"/>
-      <c r="BP35" s="27"/>
-      <c r="BQ35" s="28"/>
-      <c r="BR35" s="24"/>
-    </row>
-    <row r="36" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B36" s="24"/>
-      <c r="E36" s="16"/>
-      <c r="F36" s="16"/>
-      <c r="G36" s="16"/>
-      <c r="H36" s="16"/>
-      <c r="I36" s="16"/>
-      <c r="J36" s="16"/>
-      <c r="K36" s="16"/>
-      <c r="L36" s="16"/>
-      <c r="M36" s="16"/>
-      <c r="N36" s="16"/>
-      <c r="O36" s="16"/>
-      <c r="P36" s="16"/>
-      <c r="Q36" s="16"/>
-      <c r="R36" s="16"/>
-      <c r="T36" s="16"/>
-      <c r="U36" s="16"/>
-      <c r="V36" s="16"/>
-      <c r="W36" s="16"/>
-      <c r="X36" s="16"/>
-      <c r="Y36" s="16"/>
-      <c r="Z36" s="16"/>
-      <c r="AA36" s="16"/>
-      <c r="AB36" s="16"/>
-      <c r="AC36" s="16"/>
-      <c r="AD36" s="16"/>
-      <c r="AE36" s="16"/>
-      <c r="AF36" s="16"/>
-      <c r="AG36" s="16"/>
-      <c r="AW36" s="20"/>
-      <c r="AX36" s="21"/>
-      <c r="AY36" s="21"/>
-      <c r="AZ36" s="21"/>
-      <c r="BA36" s="21"/>
-      <c r="BB36" s="21"/>
-      <c r="BC36" s="21"/>
-      <c r="BD36" s="21"/>
-      <c r="BE36" s="21"/>
-      <c r="BF36" s="21"/>
-      <c r="BG36" s="21"/>
-      <c r="BH36" s="21"/>
-      <c r="BI36" s="21"/>
-      <c r="BJ36" s="21"/>
-      <c r="BK36" s="21"/>
-      <c r="BL36" s="21"/>
-      <c r="BM36" s="21"/>
-      <c r="BN36" s="21"/>
-      <c r="BO36" s="21"/>
-      <c r="BP36" s="21"/>
-      <c r="BQ36" s="22"/>
-      <c r="BR36" s="24"/>
-    </row>
-    <row r="37" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B37" s="24"/>
-      <c r="E37" s="16"/>
-      <c r="F37" s="16"/>
-      <c r="G37" s="16"/>
-      <c r="H37" s="16"/>
-      <c r="I37" s="16"/>
-      <c r="J37" s="16"/>
-      <c r="K37" s="16"/>
-      <c r="L37" s="16"/>
-      <c r="M37" s="16"/>
-      <c r="N37" s="16"/>
-      <c r="O37" s="16"/>
-      <c r="P37" s="16"/>
-      <c r="Q37" s="16"/>
-      <c r="R37" s="16"/>
-      <c r="T37" s="16"/>
-      <c r="U37" s="16"/>
-      <c r="V37" s="16"/>
-      <c r="W37" s="16"/>
-      <c r="X37" s="16"/>
-      <c r="Y37" s="16"/>
-      <c r="Z37" s="16"/>
-      <c r="AA37" s="16"/>
-      <c r="AB37" s="16"/>
-      <c r="AC37" s="16"/>
-      <c r="AD37" s="16"/>
-      <c r="AE37" s="16"/>
-      <c r="AF37" s="16"/>
-      <c r="AG37" s="16"/>
-      <c r="BR37" s="24"/>
-    </row>
-    <row r="38" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B38" s="24"/>
-      <c r="E38" s="16"/>
-      <c r="F38" s="16"/>
-      <c r="G38" s="16"/>
-      <c r="H38" s="16"/>
-      <c r="I38" s="16"/>
-      <c r="J38" s="16"/>
-      <c r="K38" s="16"/>
-      <c r="L38" s="16"/>
-      <c r="M38" s="16"/>
-      <c r="N38" s="16"/>
-      <c r="O38" s="16"/>
-      <c r="P38" s="16"/>
-      <c r="Q38" s="16"/>
-      <c r="R38" s="16"/>
-      <c r="T38" s="16"/>
-      <c r="U38" s="16"/>
-      <c r="V38" s="16"/>
-      <c r="W38" s="16"/>
-      <c r="X38" s="16"/>
-      <c r="Y38" s="16"/>
-      <c r="Z38" s="16"/>
-      <c r="AA38" s="16"/>
-      <c r="AB38" s="16"/>
-      <c r="AC38" s="16"/>
-      <c r="AD38" s="16"/>
-      <c r="AE38" s="16"/>
-      <c r="AF38" s="16"/>
-      <c r="AG38" s="16"/>
-      <c r="BR38" s="24"/>
-    </row>
-    <row r="39" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B39" s="24"/>
-      <c r="E39" s="16"/>
-      <c r="F39" s="16"/>
-      <c r="G39" s="16"/>
-      <c r="H39" s="16"/>
-      <c r="I39" s="16"/>
-      <c r="J39" s="16"/>
-      <c r="K39" s="16"/>
-      <c r="L39" s="16"/>
-      <c r="M39" s="16"/>
-      <c r="N39" s="16"/>
-      <c r="O39" s="16"/>
-      <c r="P39" s="16"/>
-      <c r="Q39" s="16"/>
-      <c r="R39" s="16"/>
-      <c r="T39" s="16"/>
-      <c r="U39" s="16"/>
-      <c r="V39" s="16"/>
-      <c r="W39" s="16"/>
-      <c r="X39" s="16"/>
-      <c r="Y39" s="16"/>
-      <c r="Z39" s="16"/>
-      <c r="AA39" s="16"/>
-      <c r="AB39" s="16"/>
-      <c r="AC39" s="16"/>
-      <c r="AD39" s="16"/>
-      <c r="AE39" s="16"/>
-      <c r="AF39" s="16"/>
-      <c r="AG39" s="16"/>
-      <c r="AW39" s="1" t="s">
+      <c r="AX39" s="13" t="s">
         <v>173</v>
-      </c>
-      <c r="AX39" s="13" t="s">
-        <v>174</v>
       </c>
       <c r="AY39" s="14"/>
       <c r="AZ39" s="15"/>
       <c r="BA39" s="13" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="BB39" s="14"/>
       <c r="BC39" s="14"/>
@@ -3253,34 +3248,34 @@
       <c r="BG39" s="14"/>
       <c r="BH39" s="15"/>
       <c r="BI39" s="13" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="BJ39" s="14"/>
       <c r="BK39" s="15"/>
       <c r="BL39" s="13" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="BM39" s="14"/>
       <c r="BN39" s="15"/>
       <c r="BO39" s="13" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="BP39" s="14"/>
       <c r="BQ39" s="15"/>
-      <c r="BR39" s="24"/>
+      <c r="BR39" s="31"/>
     </row>
     <row r="40" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B40" s="24"/>
+      <c r="B40" s="31"/>
       <c r="AW40" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="AX40" s="13" t="s">
         <v>179</v>
-      </c>
-      <c r="AX40" s="13" t="s">
-        <v>180</v>
       </c>
       <c r="AY40" s="14"/>
       <c r="AZ40" s="15"/>
       <c r="BA40" s="13" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="BB40" s="14"/>
       <c r="BC40" s="14"/>
@@ -3290,34 +3285,34 @@
       <c r="BG40" s="14"/>
       <c r="BH40" s="15"/>
       <c r="BI40" s="13" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="BJ40" s="14"/>
       <c r="BK40" s="15"/>
       <c r="BL40" s="13" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="BM40" s="14"/>
       <c r="BN40" s="15"/>
       <c r="BO40" s="13" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="BP40" s="14"/>
       <c r="BQ40" s="15"/>
-      <c r="BR40" s="24"/>
+      <c r="BR40" s="31"/>
     </row>
     <row r="41" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B41" s="24"/>
+      <c r="B41" s="31"/>
       <c r="AW41" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="AX41" s="13" t="s">
         <v>185</v>
-      </c>
-      <c r="AX41" s="13" t="s">
-        <v>186</v>
       </c>
       <c r="AY41" s="14"/>
       <c r="AZ41" s="15"/>
       <c r="BA41" s="13" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="BB41" s="14"/>
       <c r="BC41" s="14"/>
@@ -3327,34 +3322,34 @@
       <c r="BG41" s="14"/>
       <c r="BH41" s="15"/>
       <c r="BI41" s="13" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="BJ41" s="14"/>
       <c r="BK41" s="15"/>
       <c r="BL41" s="13" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="BM41" s="14"/>
       <c r="BN41" s="15"/>
       <c r="BO41" s="13" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="BP41" s="14"/>
       <c r="BQ41" s="15"/>
-      <c r="BR41" s="24"/>
+      <c r="BR41" s="31"/>
     </row>
     <row r="42" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B42" s="24"/>
+      <c r="B42" s="31"/>
       <c r="AW42" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="AX42" s="13" t="s">
         <v>191</v>
-      </c>
-      <c r="AX42" s="13" t="s">
-        <v>192</v>
       </c>
       <c r="AY42" s="14"/>
       <c r="AZ42" s="15"/>
       <c r="BA42" s="13" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="BB42" s="14"/>
       <c r="BC42" s="14"/>
@@ -3364,90 +3359,90 @@
       <c r="BG42" s="14"/>
       <c r="BH42" s="15"/>
       <c r="BI42" s="13" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="BJ42" s="14"/>
       <c r="BK42" s="15"/>
       <c r="BL42" s="13" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="BM42" s="14"/>
       <c r="BN42" s="15"/>
       <c r="BO42" s="13" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="BP42" s="14"/>
       <c r="BQ42" s="15"/>
-      <c r="BR42" s="24"/>
+      <c r="BR42" s="31"/>
     </row>
     <row r="43" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B43" s="25"/>
-      <c r="AW43" s="23" t="s">
+      <c r="B43" s="26"/>
+      <c r="AW43" s="25" t="s">
+        <v>196</v>
+      </c>
+      <c r="AX43" s="16"/>
+      <c r="AY43" s="17"/>
+      <c r="AZ43" s="18"/>
+      <c r="BA43" s="16"/>
+      <c r="BB43" s="17"/>
+      <c r="BC43" s="17"/>
+      <c r="BD43" s="17"/>
+      <c r="BE43" s="17"/>
+      <c r="BF43" s="17"/>
+      <c r="BG43" s="17"/>
+      <c r="BH43" s="18"/>
+      <c r="BI43" s="16"/>
+      <c r="BJ43" s="17"/>
+      <c r="BK43" s="18"/>
+      <c r="BL43" s="16"/>
+      <c r="BM43" s="17"/>
+      <c r="BN43" s="18"/>
+      <c r="BO43" s="16"/>
+      <c r="BP43" s="17"/>
+      <c r="BQ43" s="18"/>
+      <c r="BR43" s="26"/>
+    </row>
+    <row r="44" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B44" s="25" t="s">
         <v>197</v>
       </c>
-      <c r="AX43" s="17"/>
-      <c r="AY43" s="18"/>
-      <c r="AZ43" s="19"/>
-      <c r="BA43" s="17"/>
-      <c r="BB43" s="18"/>
-      <c r="BC43" s="18"/>
-      <c r="BD43" s="18"/>
-      <c r="BE43" s="18"/>
-      <c r="BF43" s="18"/>
-      <c r="BG43" s="18"/>
-      <c r="BH43" s="19"/>
-      <c r="BI43" s="17"/>
-      <c r="BJ43" s="18"/>
-      <c r="BK43" s="19"/>
-      <c r="BL43" s="17"/>
-      <c r="BM43" s="18"/>
-      <c r="BN43" s="19"/>
-      <c r="BO43" s="17"/>
-      <c r="BP43" s="18"/>
-      <c r="BQ43" s="19"/>
-      <c r="BR43" s="25"/>
-    </row>
-    <row r="44" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B44" s="23" t="s">
+      <c r="AW44" s="26"/>
+      <c r="AX44" s="19"/>
+      <c r="AY44" s="20"/>
+      <c r="AZ44" s="21"/>
+      <c r="BA44" s="19"/>
+      <c r="BB44" s="20"/>
+      <c r="BC44" s="20"/>
+      <c r="BD44" s="20"/>
+      <c r="BE44" s="20"/>
+      <c r="BF44" s="20"/>
+      <c r="BG44" s="20"/>
+      <c r="BH44" s="21"/>
+      <c r="BI44" s="19"/>
+      <c r="BJ44" s="20"/>
+      <c r="BK44" s="21"/>
+      <c r="BL44" s="19"/>
+      <c r="BM44" s="20"/>
+      <c r="BN44" s="21"/>
+      <c r="BO44" s="19"/>
+      <c r="BP44" s="20"/>
+      <c r="BQ44" s="21"/>
+      <c r="BR44" s="25" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="45" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B45" s="31"/>
+      <c r="AW45" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="AW44" s="25"/>
-      <c r="AX44" s="20"/>
-      <c r="AY44" s="21"/>
-      <c r="AZ44" s="22"/>
-      <c r="BA44" s="20"/>
-      <c r="BB44" s="21"/>
-      <c r="BC44" s="21"/>
-      <c r="BD44" s="21"/>
-      <c r="BE44" s="21"/>
-      <c r="BF44" s="21"/>
-      <c r="BG44" s="21"/>
-      <c r="BH44" s="22"/>
-      <c r="BI44" s="20"/>
-      <c r="BJ44" s="21"/>
-      <c r="BK44" s="22"/>
-      <c r="BL44" s="20"/>
-      <c r="BM44" s="21"/>
-      <c r="BN44" s="22"/>
-      <c r="BO44" s="20"/>
-      <c r="BP44" s="21"/>
-      <c r="BQ44" s="22"/>
-      <c r="BR44" s="23" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="45" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B45" s="24"/>
-      <c r="AW45" s="5" t="s">
+      <c r="AX45" s="13" t="s">
         <v>199</v>
-      </c>
-      <c r="AX45" s="13" t="s">
-        <v>200</v>
       </c>
       <c r="AY45" s="14"/>
       <c r="AZ45" s="15"/>
       <c r="BA45" s="13" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="BB45" s="14"/>
       <c r="BC45" s="14"/>
@@ -3457,32 +3452,32 @@
       <c r="BG45" s="14"/>
       <c r="BH45" s="15"/>
       <c r="BI45" s="13" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="BJ45" s="14"/>
       <c r="BK45" s="15"/>
       <c r="BL45" s="13" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="BM45" s="14"/>
       <c r="BN45" s="15"/>
       <c r="BO45" s="13" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="BP45" s="14"/>
       <c r="BQ45" s="15"/>
-      <c r="BR45" s="24"/>
+      <c r="BR45" s="31"/>
     </row>
     <row r="46" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B46" s="24"/>
+      <c r="B46" s="31"/>
       <c r="AW46" s="13" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AX46" s="14"/>
       <c r="AY46" s="14"/>
       <c r="AZ46" s="15"/>
       <c r="BA46" s="13" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="BB46" s="14"/>
       <c r="BC46" s="14"/>
@@ -3492,7 +3487,7 @@
       <c r="BG46" s="14"/>
       <c r="BH46" s="15"/>
       <c r="BI46" s="13" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="BJ46" s="14"/>
       <c r="BK46" s="14"/>
@@ -3502,50 +3497,50 @@
       <c r="BO46" s="14"/>
       <c r="BP46" s="14"/>
       <c r="BQ46" s="15"/>
-      <c r="BR46" s="24"/>
+      <c r="BR46" s="31"/>
     </row>
     <row r="47" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B47" s="24"/>
-      <c r="E47" s="16" t="s">
-        <v>230</v>
-      </c>
-      <c r="F47" s="16"/>
-      <c r="G47" s="16"/>
-      <c r="H47" s="16"/>
-      <c r="I47" s="16"/>
-      <c r="J47" s="16"/>
-      <c r="K47" s="16"/>
-      <c r="L47" s="16"/>
-      <c r="M47" s="16"/>
-      <c r="N47" s="16"/>
-      <c r="O47" s="16"/>
-      <c r="P47" s="16"/>
-      <c r="Q47" s="16"/>
-      <c r="R47" s="16"/>
-      <c r="T47" s="16" t="s">
-        <v>225</v>
-      </c>
-      <c r="U47" s="16"/>
-      <c r="V47" s="16"/>
-      <c r="W47" s="16"/>
-      <c r="X47" s="16"/>
-      <c r="Y47" s="16"/>
-      <c r="Z47" s="16"/>
-      <c r="AA47" s="16"/>
-      <c r="AB47" s="16"/>
-      <c r="AC47" s="16"/>
-      <c r="AD47" s="16"/>
-      <c r="AE47" s="16"/>
-      <c r="AF47" s="16"/>
-      <c r="AG47" s="16"/>
+      <c r="B47" s="31"/>
+      <c r="E47" s="30" t="s">
+        <v>229</v>
+      </c>
+      <c r="F47" s="30"/>
+      <c r="G47" s="30"/>
+      <c r="H47" s="30"/>
+      <c r="I47" s="30"/>
+      <c r="J47" s="30"/>
+      <c r="K47" s="30"/>
+      <c r="L47" s="30"/>
+      <c r="M47" s="30"/>
+      <c r="N47" s="30"/>
+      <c r="O47" s="30"/>
+      <c r="P47" s="30"/>
+      <c r="Q47" s="30"/>
+      <c r="R47" s="30"/>
+      <c r="T47" s="30" t="s">
+        <v>224</v>
+      </c>
+      <c r="U47" s="30"/>
+      <c r="V47" s="30"/>
+      <c r="W47" s="30"/>
+      <c r="X47" s="30"/>
+      <c r="Y47" s="30"/>
+      <c r="Z47" s="30"/>
+      <c r="AA47" s="30"/>
+      <c r="AB47" s="30"/>
+      <c r="AC47" s="30"/>
+      <c r="AD47" s="30"/>
+      <c r="AE47" s="30"/>
+      <c r="AF47" s="30"/>
+      <c r="AG47" s="30"/>
       <c r="AW47" s="13" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AX47" s="14"/>
       <c r="AY47" s="14"/>
       <c r="AZ47" s="15"/>
       <c r="BA47" s="13" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="BB47" s="14"/>
       <c r="BC47" s="14"/>
@@ -3555,7 +3550,7 @@
       <c r="BG47" s="14"/>
       <c r="BH47" s="15"/>
       <c r="BI47" s="13" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BJ47" s="14"/>
       <c r="BK47" s="14"/>
@@ -3565,342 +3560,342 @@
       <c r="BO47" s="14"/>
       <c r="BP47" s="14"/>
       <c r="BQ47" s="15"/>
-      <c r="BR47" s="24"/>
+      <c r="BR47" s="31"/>
     </row>
     <row r="48" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B48" s="24"/>
-      <c r="E48" s="16"/>
-      <c r="F48" s="16"/>
-      <c r="G48" s="16"/>
-      <c r="H48" s="16"/>
-      <c r="I48" s="16"/>
-      <c r="J48" s="16"/>
-      <c r="K48" s="16"/>
-      <c r="L48" s="16"/>
-      <c r="M48" s="16"/>
-      <c r="N48" s="16"/>
-      <c r="O48" s="16"/>
-      <c r="P48" s="16"/>
-      <c r="Q48" s="16"/>
-      <c r="R48" s="16"/>
-      <c r="T48" s="16"/>
-      <c r="U48" s="16"/>
-      <c r="V48" s="16"/>
-      <c r="W48" s="16"/>
-      <c r="X48" s="16"/>
-      <c r="Y48" s="16"/>
-      <c r="Z48" s="16"/>
-      <c r="AA48" s="16"/>
-      <c r="AB48" s="16"/>
-      <c r="AC48" s="16"/>
-      <c r="AD48" s="16"/>
-      <c r="AE48" s="16"/>
-      <c r="AF48" s="16"/>
-      <c r="AG48" s="16"/>
-      <c r="AW48" s="17" t="s">
+      <c r="B48" s="31"/>
+      <c r="E48" s="30"/>
+      <c r="F48" s="30"/>
+      <c r="G48" s="30"/>
+      <c r="H48" s="30"/>
+      <c r="I48" s="30"/>
+      <c r="J48" s="30"/>
+      <c r="K48" s="30"/>
+      <c r="L48" s="30"/>
+      <c r="M48" s="30"/>
+      <c r="N48" s="30"/>
+      <c r="O48" s="30"/>
+      <c r="P48" s="30"/>
+      <c r="Q48" s="30"/>
+      <c r="R48" s="30"/>
+      <c r="T48" s="30"/>
+      <c r="U48" s="30"/>
+      <c r="V48" s="30"/>
+      <c r="W48" s="30"/>
+      <c r="X48" s="30"/>
+      <c r="Y48" s="30"/>
+      <c r="Z48" s="30"/>
+      <c r="AA48" s="30"/>
+      <c r="AB48" s="30"/>
+      <c r="AC48" s="30"/>
+      <c r="AD48" s="30"/>
+      <c r="AE48" s="30"/>
+      <c r="AF48" s="30"/>
+      <c r="AG48" s="30"/>
+      <c r="AW48" s="16" t="s">
+        <v>210</v>
+      </c>
+      <c r="AX48" s="17"/>
+      <c r="AY48" s="17"/>
+      <c r="AZ48" s="17"/>
+      <c r="BA48" s="17"/>
+      <c r="BB48" s="17"/>
+      <c r="BC48" s="17"/>
+      <c r="BD48" s="18"/>
+      <c r="BE48" s="16" t="s">
         <v>211</v>
       </c>
-      <c r="AX48" s="18"/>
-      <c r="AY48" s="18"/>
-      <c r="AZ48" s="18"/>
-      <c r="BA48" s="18"/>
-      <c r="BB48" s="18"/>
-      <c r="BC48" s="18"/>
-      <c r="BD48" s="19"/>
-      <c r="BE48" s="17" t="s">
+      <c r="BF48" s="17"/>
+      <c r="BG48" s="17"/>
+      <c r="BH48" s="17"/>
+      <c r="BI48" s="17"/>
+      <c r="BJ48" s="17"/>
+      <c r="BK48" s="17"/>
+      <c r="BL48" s="17"/>
+      <c r="BM48" s="17"/>
+      <c r="BN48" s="17"/>
+      <c r="BO48" s="17"/>
+      <c r="BP48" s="17"/>
+      <c r="BQ48" s="18"/>
+      <c r="BR48" s="31"/>
+    </row>
+    <row r="49" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B49" s="31"/>
+      <c r="E49" s="30"/>
+      <c r="F49" s="30"/>
+      <c r="G49" s="30"/>
+      <c r="H49" s="30"/>
+      <c r="I49" s="30"/>
+      <c r="J49" s="30"/>
+      <c r="K49" s="30"/>
+      <c r="L49" s="30"/>
+      <c r="M49" s="30"/>
+      <c r="N49" s="30"/>
+      <c r="O49" s="30"/>
+      <c r="P49" s="30"/>
+      <c r="Q49" s="30"/>
+      <c r="R49" s="30"/>
+      <c r="T49" s="30"/>
+      <c r="U49" s="30"/>
+      <c r="V49" s="30"/>
+      <c r="W49" s="30"/>
+      <c r="X49" s="30"/>
+      <c r="Y49" s="30"/>
+      <c r="Z49" s="30"/>
+      <c r="AA49" s="30"/>
+      <c r="AB49" s="30"/>
+      <c r="AC49" s="30"/>
+      <c r="AD49" s="30"/>
+      <c r="AE49" s="30"/>
+      <c r="AF49" s="30"/>
+      <c r="AG49" s="30"/>
+      <c r="AW49" s="22"/>
+      <c r="AX49" s="23"/>
+      <c r="AY49" s="23"/>
+      <c r="AZ49" s="23"/>
+      <c r="BA49" s="23"/>
+      <c r="BB49" s="23"/>
+      <c r="BC49" s="23"/>
+      <c r="BD49" s="24"/>
+      <c r="BE49" s="19"/>
+      <c r="BF49" s="20"/>
+      <c r="BG49" s="20"/>
+      <c r="BH49" s="20"/>
+      <c r="BI49" s="20"/>
+      <c r="BJ49" s="20"/>
+      <c r="BK49" s="20"/>
+      <c r="BL49" s="20"/>
+      <c r="BM49" s="20"/>
+      <c r="BN49" s="20"/>
+      <c r="BO49" s="20"/>
+      <c r="BP49" s="20"/>
+      <c r="BQ49" s="21"/>
+      <c r="BR49" s="31"/>
+    </row>
+    <row r="50" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B50" s="31"/>
+      <c r="E50" s="30"/>
+      <c r="F50" s="30"/>
+      <c r="G50" s="30"/>
+      <c r="H50" s="30"/>
+      <c r="I50" s="30"/>
+      <c r="J50" s="30"/>
+      <c r="K50" s="30"/>
+      <c r="L50" s="30"/>
+      <c r="M50" s="30"/>
+      <c r="N50" s="30"/>
+      <c r="O50" s="30"/>
+      <c r="P50" s="30"/>
+      <c r="Q50" s="30"/>
+      <c r="R50" s="30"/>
+      <c r="T50" s="30"/>
+      <c r="U50" s="30"/>
+      <c r="V50" s="30"/>
+      <c r="W50" s="30"/>
+      <c r="X50" s="30"/>
+      <c r="Y50" s="30"/>
+      <c r="Z50" s="30"/>
+      <c r="AA50" s="30"/>
+      <c r="AB50" s="30"/>
+      <c r="AC50" s="30"/>
+      <c r="AD50" s="30"/>
+      <c r="AE50" s="30"/>
+      <c r="AF50" s="30"/>
+      <c r="AG50" s="30"/>
+      <c r="AW50" s="22"/>
+      <c r="AX50" s="23"/>
+      <c r="AY50" s="23"/>
+      <c r="AZ50" s="23"/>
+      <c r="BA50" s="23"/>
+      <c r="BB50" s="23"/>
+      <c r="BC50" s="23"/>
+      <c r="BD50" s="24"/>
+      <c r="BE50" s="16" t="s">
         <v>212</v>
       </c>
-      <c r="BF48" s="18"/>
-      <c r="BG48" s="18"/>
-      <c r="BH48" s="18"/>
-      <c r="BI48" s="18"/>
-      <c r="BJ48" s="18"/>
-      <c r="BK48" s="18"/>
-      <c r="BL48" s="18"/>
-      <c r="BM48" s="18"/>
-      <c r="BN48" s="18"/>
-      <c r="BO48" s="18"/>
-      <c r="BP48" s="18"/>
-      <c r="BQ48" s="19"/>
-      <c r="BR48" s="24"/>
-    </row>
-    <row r="49" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B49" s="24"/>
-      <c r="E49" s="16"/>
-      <c r="F49" s="16"/>
-      <c r="G49" s="16"/>
-      <c r="H49" s="16"/>
-      <c r="I49" s="16"/>
-      <c r="J49" s="16"/>
-      <c r="K49" s="16"/>
-      <c r="L49" s="16"/>
-      <c r="M49" s="16"/>
-      <c r="N49" s="16"/>
-      <c r="O49" s="16"/>
-      <c r="P49" s="16"/>
-      <c r="Q49" s="16"/>
-      <c r="R49" s="16"/>
-      <c r="T49" s="16"/>
-      <c r="U49" s="16"/>
-      <c r="V49" s="16"/>
-      <c r="W49" s="16"/>
-      <c r="X49" s="16"/>
-      <c r="Y49" s="16"/>
-      <c r="Z49" s="16"/>
-      <c r="AA49" s="16"/>
-      <c r="AB49" s="16"/>
-      <c r="AC49" s="16"/>
-      <c r="AD49" s="16"/>
-      <c r="AE49" s="16"/>
-      <c r="AF49" s="16"/>
-      <c r="AG49" s="16"/>
-      <c r="AW49" s="26"/>
-      <c r="AX49" s="27"/>
-      <c r="AY49" s="27"/>
-      <c r="AZ49" s="27"/>
-      <c r="BA49" s="27"/>
-      <c r="BB49" s="27"/>
-      <c r="BC49" s="27"/>
-      <c r="BD49" s="28"/>
-      <c r="BE49" s="20"/>
-      <c r="BF49" s="21"/>
-      <c r="BG49" s="21"/>
-      <c r="BH49" s="21"/>
-      <c r="BI49" s="21"/>
-      <c r="BJ49" s="21"/>
-      <c r="BK49" s="21"/>
-      <c r="BL49" s="21"/>
-      <c r="BM49" s="21"/>
-      <c r="BN49" s="21"/>
-      <c r="BO49" s="21"/>
-      <c r="BP49" s="21"/>
-      <c r="BQ49" s="22"/>
-      <c r="BR49" s="24"/>
-    </row>
-    <row r="50" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B50" s="24"/>
-      <c r="E50" s="16"/>
-      <c r="F50" s="16"/>
-      <c r="G50" s="16"/>
-      <c r="H50" s="16"/>
-      <c r="I50" s="16"/>
-      <c r="J50" s="16"/>
-      <c r="K50" s="16"/>
-      <c r="L50" s="16"/>
-      <c r="M50" s="16"/>
-      <c r="N50" s="16"/>
-      <c r="O50" s="16"/>
-      <c r="P50" s="16"/>
-      <c r="Q50" s="16"/>
-      <c r="R50" s="16"/>
-      <c r="T50" s="16"/>
-      <c r="U50" s="16"/>
-      <c r="V50" s="16"/>
-      <c r="W50" s="16"/>
-      <c r="X50" s="16"/>
-      <c r="Y50" s="16"/>
-      <c r="Z50" s="16"/>
-      <c r="AA50" s="16"/>
-      <c r="AB50" s="16"/>
-      <c r="AC50" s="16"/>
-      <c r="AD50" s="16"/>
-      <c r="AE50" s="16"/>
-      <c r="AF50" s="16"/>
-      <c r="AG50" s="16"/>
-      <c r="AW50" s="26"/>
-      <c r="AX50" s="27"/>
-      <c r="AY50" s="27"/>
-      <c r="AZ50" s="27"/>
-      <c r="BA50" s="27"/>
-      <c r="BB50" s="27"/>
-      <c r="BC50" s="27"/>
-      <c r="BD50" s="28"/>
-      <c r="BE50" s="17" t="s">
+      <c r="BF50" s="17"/>
+      <c r="BG50" s="17"/>
+      <c r="BH50" s="17"/>
+      <c r="BI50" s="17"/>
+      <c r="BJ50" s="17"/>
+      <c r="BK50" s="17"/>
+      <c r="BL50" s="17"/>
+      <c r="BM50" s="17"/>
+      <c r="BN50" s="17"/>
+      <c r="BO50" s="17"/>
+      <c r="BP50" s="17"/>
+      <c r="BQ50" s="18"/>
+      <c r="BR50" s="31"/>
+    </row>
+    <row r="51" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B51" s="31"/>
+      <c r="E51" s="30"/>
+      <c r="F51" s="30"/>
+      <c r="G51" s="30"/>
+      <c r="H51" s="30"/>
+      <c r="I51" s="30"/>
+      <c r="J51" s="30"/>
+      <c r="K51" s="30"/>
+      <c r="L51" s="30"/>
+      <c r="M51" s="30"/>
+      <c r="N51" s="30"/>
+      <c r="O51" s="30"/>
+      <c r="P51" s="30"/>
+      <c r="Q51" s="30"/>
+      <c r="R51" s="30"/>
+      <c r="T51" s="30"/>
+      <c r="U51" s="30"/>
+      <c r="V51" s="30"/>
+      <c r="W51" s="30"/>
+      <c r="X51" s="30"/>
+      <c r="Y51" s="30"/>
+      <c r="Z51" s="30"/>
+      <c r="AA51" s="30"/>
+      <c r="AB51" s="30"/>
+      <c r="AC51" s="30"/>
+      <c r="AD51" s="30"/>
+      <c r="AE51" s="30"/>
+      <c r="AF51" s="30"/>
+      <c r="AG51" s="30"/>
+      <c r="AW51" s="19"/>
+      <c r="AX51" s="20"/>
+      <c r="AY51" s="20"/>
+      <c r="AZ51" s="20"/>
+      <c r="BA51" s="20"/>
+      <c r="BB51" s="20"/>
+      <c r="BC51" s="20"/>
+      <c r="BD51" s="21"/>
+      <c r="BE51" s="19"/>
+      <c r="BF51" s="20"/>
+      <c r="BG51" s="20"/>
+      <c r="BH51" s="20"/>
+      <c r="BI51" s="20"/>
+      <c r="BJ51" s="20"/>
+      <c r="BK51" s="20"/>
+      <c r="BL51" s="20"/>
+      <c r="BM51" s="20"/>
+      <c r="BN51" s="20"/>
+      <c r="BO51" s="20"/>
+      <c r="BP51" s="20"/>
+      <c r="BQ51" s="21"/>
+      <c r="BR51" s="31"/>
+    </row>
+    <row r="52" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B52" s="31"/>
+      <c r="AW52" s="16" t="s">
         <v>213</v>
       </c>
-      <c r="BF50" s="18"/>
-      <c r="BG50" s="18"/>
-      <c r="BH50" s="18"/>
-      <c r="BI50" s="18"/>
-      <c r="BJ50" s="18"/>
-      <c r="BK50" s="18"/>
-      <c r="BL50" s="18"/>
-      <c r="BM50" s="18"/>
-      <c r="BN50" s="18"/>
-      <c r="BO50" s="18"/>
-      <c r="BP50" s="18"/>
-      <c r="BQ50" s="19"/>
-      <c r="BR50" s="24"/>
-    </row>
-    <row r="51" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B51" s="24"/>
-      <c r="E51" s="16"/>
-      <c r="F51" s="16"/>
-      <c r="G51" s="16"/>
-      <c r="H51" s="16"/>
-      <c r="I51" s="16"/>
-      <c r="J51" s="16"/>
-      <c r="K51" s="16"/>
-      <c r="L51" s="16"/>
-      <c r="M51" s="16"/>
-      <c r="N51" s="16"/>
-      <c r="O51" s="16"/>
-      <c r="P51" s="16"/>
-      <c r="Q51" s="16"/>
-      <c r="R51" s="16"/>
-      <c r="T51" s="16"/>
-      <c r="U51" s="16"/>
-      <c r="V51" s="16"/>
-      <c r="W51" s="16"/>
-      <c r="X51" s="16"/>
-      <c r="Y51" s="16"/>
-      <c r="Z51" s="16"/>
-      <c r="AA51" s="16"/>
-      <c r="AB51" s="16"/>
-      <c r="AC51" s="16"/>
-      <c r="AD51" s="16"/>
-      <c r="AE51" s="16"/>
-      <c r="AF51" s="16"/>
-      <c r="AG51" s="16"/>
-      <c r="AW51" s="20"/>
-      <c r="AX51" s="21"/>
-      <c r="AY51" s="21"/>
-      <c r="AZ51" s="21"/>
-      <c r="BA51" s="21"/>
-      <c r="BB51" s="21"/>
-      <c r="BC51" s="21"/>
-      <c r="BD51" s="22"/>
-      <c r="BE51" s="20"/>
-      <c r="BF51" s="21"/>
-      <c r="BG51" s="21"/>
-      <c r="BH51" s="21"/>
-      <c r="BI51" s="21"/>
-      <c r="BJ51" s="21"/>
-      <c r="BK51" s="21"/>
-      <c r="BL51" s="21"/>
-      <c r="BM51" s="21"/>
-      <c r="BN51" s="21"/>
-      <c r="BO51" s="21"/>
-      <c r="BP51" s="21"/>
-      <c r="BQ51" s="22"/>
-      <c r="BR51" s="24"/>
-    </row>
-    <row r="52" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B52" s="24"/>
-      <c r="AW52" s="17" t="s">
+      <c r="AX52" s="17"/>
+      <c r="AY52" s="17"/>
+      <c r="AZ52" s="17"/>
+      <c r="BA52" s="17"/>
+      <c r="BB52" s="17"/>
+      <c r="BC52" s="17"/>
+      <c r="BD52" s="18"/>
+      <c r="BE52" s="16" t="s">
         <v>214</v>
       </c>
-      <c r="AX52" s="18"/>
-      <c r="AY52" s="18"/>
-      <c r="AZ52" s="18"/>
-      <c r="BA52" s="18"/>
-      <c r="BB52" s="18"/>
-      <c r="BC52" s="18"/>
-      <c r="BD52" s="19"/>
-      <c r="BE52" s="17" t="s">
-        <v>215</v>
-      </c>
-      <c r="BF52" s="18"/>
-      <c r="BG52" s="18"/>
-      <c r="BH52" s="18"/>
-      <c r="BI52" s="18"/>
-      <c r="BJ52" s="18"/>
-      <c r="BK52" s="18"/>
-      <c r="BL52" s="18"/>
-      <c r="BM52" s="18"/>
-      <c r="BN52" s="18"/>
-      <c r="BO52" s="18"/>
-      <c r="BP52" s="18"/>
-      <c r="BQ52" s="19"/>
-      <c r="BR52" s="24"/>
+      <c r="BF52" s="17"/>
+      <c r="BG52" s="17"/>
+      <c r="BH52" s="17"/>
+      <c r="BI52" s="17"/>
+      <c r="BJ52" s="17"/>
+      <c r="BK52" s="17"/>
+      <c r="BL52" s="17"/>
+      <c r="BM52" s="17"/>
+      <c r="BN52" s="17"/>
+      <c r="BO52" s="17"/>
+      <c r="BP52" s="17"/>
+      <c r="BQ52" s="18"/>
+      <c r="BR52" s="31"/>
     </row>
     <row r="53" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B53" s="24"/>
-      <c r="AW53" s="26" t="s">
-        <v>231</v>
-      </c>
-      <c r="AX53" s="27"/>
-      <c r="AY53" s="27"/>
-      <c r="AZ53" s="27"/>
-      <c r="BA53" s="27"/>
-      <c r="BB53" s="27"/>
-      <c r="BC53" s="27"/>
-      <c r="BD53" s="28"/>
-      <c r="BE53" s="26"/>
-      <c r="BF53" s="27"/>
-      <c r="BG53" s="27"/>
-      <c r="BH53" s="27"/>
-      <c r="BI53" s="27"/>
-      <c r="BJ53" s="27"/>
-      <c r="BK53" s="27"/>
-      <c r="BL53" s="27"/>
-      <c r="BM53" s="27"/>
-      <c r="BN53" s="27"/>
-      <c r="BO53" s="27"/>
-      <c r="BP53" s="27"/>
-      <c r="BQ53" s="28"/>
-      <c r="BR53" s="24"/>
+      <c r="B53" s="31"/>
+      <c r="AW53" s="22" t="s">
+        <v>230</v>
+      </c>
+      <c r="AX53" s="23"/>
+      <c r="AY53" s="23"/>
+      <c r="AZ53" s="23"/>
+      <c r="BA53" s="23"/>
+      <c r="BB53" s="23"/>
+      <c r="BC53" s="23"/>
+      <c r="BD53" s="24"/>
+      <c r="BE53" s="22"/>
+      <c r="BF53" s="23"/>
+      <c r="BG53" s="23"/>
+      <c r="BH53" s="23"/>
+      <c r="BI53" s="23"/>
+      <c r="BJ53" s="23"/>
+      <c r="BK53" s="23"/>
+      <c r="BL53" s="23"/>
+      <c r="BM53" s="23"/>
+      <c r="BN53" s="23"/>
+      <c r="BO53" s="23"/>
+      <c r="BP53" s="23"/>
+      <c r="BQ53" s="24"/>
+      <c r="BR53" s="31"/>
     </row>
     <row r="54" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B54" s="24"/>
-      <c r="AW54" s="26"/>
-      <c r="AX54" s="27"/>
-      <c r="AY54" s="27"/>
-      <c r="AZ54" s="27"/>
-      <c r="BA54" s="27"/>
-      <c r="BB54" s="27"/>
-      <c r="BC54" s="27"/>
-      <c r="BD54" s="28"/>
-      <c r="BE54" s="26"/>
-      <c r="BF54" s="27"/>
-      <c r="BG54" s="27"/>
-      <c r="BH54" s="27"/>
-      <c r="BI54" s="27"/>
-      <c r="BJ54" s="27"/>
-      <c r="BK54" s="27"/>
-      <c r="BL54" s="27"/>
-      <c r="BM54" s="27"/>
-      <c r="BN54" s="27"/>
-      <c r="BO54" s="27"/>
-      <c r="BP54" s="27"/>
-      <c r="BQ54" s="28"/>
-      <c r="BR54" s="24"/>
+      <c r="B54" s="31"/>
+      <c r="AW54" s="22"/>
+      <c r="AX54" s="23"/>
+      <c r="AY54" s="23"/>
+      <c r="AZ54" s="23"/>
+      <c r="BA54" s="23"/>
+      <c r="BB54" s="23"/>
+      <c r="BC54" s="23"/>
+      <c r="BD54" s="24"/>
+      <c r="BE54" s="22"/>
+      <c r="BF54" s="23"/>
+      <c r="BG54" s="23"/>
+      <c r="BH54" s="23"/>
+      <c r="BI54" s="23"/>
+      <c r="BJ54" s="23"/>
+      <c r="BK54" s="23"/>
+      <c r="BL54" s="23"/>
+      <c r="BM54" s="23"/>
+      <c r="BN54" s="23"/>
+      <c r="BO54" s="23"/>
+      <c r="BP54" s="23"/>
+      <c r="BQ54" s="24"/>
+      <c r="BR54" s="31"/>
     </row>
     <row r="55" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B55" s="24"/>
-      <c r="AW55" s="20"/>
-      <c r="AX55" s="21"/>
-      <c r="AY55" s="21"/>
-      <c r="AZ55" s="21"/>
-      <c r="BA55" s="21"/>
-      <c r="BB55" s="21"/>
-      <c r="BC55" s="21"/>
-      <c r="BD55" s="22"/>
-      <c r="BE55" s="20"/>
-      <c r="BF55" s="21"/>
-      <c r="BG55" s="21"/>
-      <c r="BH55" s="21"/>
-      <c r="BI55" s="21"/>
-      <c r="BJ55" s="21"/>
-      <c r="BK55" s="21"/>
-      <c r="BL55" s="21"/>
-      <c r="BM55" s="21"/>
-      <c r="BN55" s="21"/>
-      <c r="BO55" s="21"/>
-      <c r="BP55" s="21"/>
-      <c r="BQ55" s="22"/>
-      <c r="BR55" s="24"/>
+      <c r="B55" s="31"/>
+      <c r="AW55" s="19"/>
+      <c r="AX55" s="20"/>
+      <c r="AY55" s="20"/>
+      <c r="AZ55" s="20"/>
+      <c r="BA55" s="20"/>
+      <c r="BB55" s="20"/>
+      <c r="BC55" s="20"/>
+      <c r="BD55" s="21"/>
+      <c r="BE55" s="19"/>
+      <c r="BF55" s="20"/>
+      <c r="BG55" s="20"/>
+      <c r="BH55" s="20"/>
+      <c r="BI55" s="20"/>
+      <c r="BJ55" s="20"/>
+      <c r="BK55" s="20"/>
+      <c r="BL55" s="20"/>
+      <c r="BM55" s="20"/>
+      <c r="BN55" s="20"/>
+      <c r="BO55" s="20"/>
+      <c r="BP55" s="20"/>
+      <c r="BQ55" s="21"/>
+      <c r="BR55" s="31"/>
     </row>
     <row r="56" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B56" s="25"/>
+      <c r="B56" s="26"/>
       <c r="K56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AW56" s="13" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="AX56" s="14"/>
       <c r="AY56" s="14" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="AZ56" s="14"/>
       <c r="BA56" s="14"/>
@@ -3920,7 +3915,7 @@
       <c r="BO56" s="14"/>
       <c r="BP56" s="14"/>
       <c r="BQ56" s="15"/>
-      <c r="BR56" s="25"/>
+      <c r="BR56" s="26"/>
     </row>
     <row r="57" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C57" s="13">
@@ -4006,6 +4001,171 @@
     <row r="58" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4"/>
   </sheetData>
   <mergeCells count="189">
+    <mergeCell ref="C2:L2"/>
+    <mergeCell ref="BO41:BQ41"/>
+    <mergeCell ref="BF16:BK16"/>
+    <mergeCell ref="AY10:BB10"/>
+    <mergeCell ref="AW11:AX11"/>
+    <mergeCell ref="AY11:BB11"/>
+    <mergeCell ref="BC11:BE11"/>
+    <mergeCell ref="BF11:BK11"/>
+    <mergeCell ref="BM11:BO11"/>
+    <mergeCell ref="AY17:BB17"/>
+    <mergeCell ref="AW24:AX24"/>
+    <mergeCell ref="BF24:BK24"/>
+    <mergeCell ref="BC20:BE20"/>
+    <mergeCell ref="AY15:BB15"/>
+    <mergeCell ref="AW22:AX22"/>
+    <mergeCell ref="BA41:BH41"/>
+    <mergeCell ref="AW26:AX26"/>
+    <mergeCell ref="E7:R11"/>
+    <mergeCell ref="E17:R20"/>
+    <mergeCell ref="E26:R29"/>
+    <mergeCell ref="E35:R39"/>
+    <mergeCell ref="BM7:BO7"/>
+    <mergeCell ref="BM15:BO15"/>
+    <mergeCell ref="BC25:BE25"/>
+    <mergeCell ref="C57:L57"/>
+    <mergeCell ref="M57:X57"/>
+    <mergeCell ref="Y57:AI57"/>
+    <mergeCell ref="AJ57:AT57"/>
+    <mergeCell ref="AW56:AX56"/>
+    <mergeCell ref="BM25:BO25"/>
+    <mergeCell ref="BL39:BN39"/>
+    <mergeCell ref="E47:R51"/>
+    <mergeCell ref="BA42:BH42"/>
+    <mergeCell ref="AX40:AZ40"/>
+    <mergeCell ref="BA43:BH44"/>
+    <mergeCell ref="BL40:BN40"/>
+    <mergeCell ref="BE50:BQ51"/>
+    <mergeCell ref="AY26:BB26"/>
+    <mergeCell ref="BR17:BR29"/>
+    <mergeCell ref="BM9:BO9"/>
+    <mergeCell ref="AY16:BB16"/>
+    <mergeCell ref="BO39:BQ39"/>
+    <mergeCell ref="BM19:BO19"/>
+    <mergeCell ref="BF14:BK14"/>
+    <mergeCell ref="BF23:BK23"/>
+    <mergeCell ref="BM12:BO12"/>
+    <mergeCell ref="BR3:BR16"/>
+    <mergeCell ref="BF25:BK25"/>
+    <mergeCell ref="BF22:BK22"/>
+    <mergeCell ref="BF12:BK12"/>
+    <mergeCell ref="BM20:BO20"/>
+    <mergeCell ref="BF7:BK7"/>
+    <mergeCell ref="AY21:BB21"/>
+    <mergeCell ref="BM18:BO18"/>
+    <mergeCell ref="BC13:BE13"/>
+    <mergeCell ref="BM13:BO13"/>
+    <mergeCell ref="AY19:BB19"/>
+    <mergeCell ref="AY13:BB13"/>
+    <mergeCell ref="AY22:BB22"/>
+    <mergeCell ref="B30:B43"/>
+    <mergeCell ref="AW47:AZ47"/>
+    <mergeCell ref="BF10:BK10"/>
+    <mergeCell ref="AW10:AX10"/>
+    <mergeCell ref="BF17:BK17"/>
+    <mergeCell ref="AW23:AX23"/>
+    <mergeCell ref="BC18:BE18"/>
+    <mergeCell ref="AW48:BD48"/>
+    <mergeCell ref="BI41:BK41"/>
+    <mergeCell ref="B3:B16"/>
+    <mergeCell ref="BI47:BQ47"/>
+    <mergeCell ref="AW21:AX21"/>
+    <mergeCell ref="BC19:BE19"/>
+    <mergeCell ref="AX41:AZ41"/>
+    <mergeCell ref="BM24:BO24"/>
+    <mergeCell ref="BI39:BK39"/>
+    <mergeCell ref="BC21:BE21"/>
+    <mergeCell ref="AX43:AZ44"/>
+    <mergeCell ref="AY20:BB20"/>
+    <mergeCell ref="AW16:AX16"/>
+    <mergeCell ref="BF5:BK6"/>
+    <mergeCell ref="BC17:BE17"/>
+    <mergeCell ref="AY24:BB24"/>
+    <mergeCell ref="BC5:BE6"/>
+    <mergeCell ref="BR30:BR43"/>
+    <mergeCell ref="BM8:BO8"/>
+    <mergeCell ref="AX39:AZ39"/>
+    <mergeCell ref="BM16:BO16"/>
+    <mergeCell ref="BA46:BH46"/>
+    <mergeCell ref="BA39:BH39"/>
+    <mergeCell ref="BM10:BO10"/>
+    <mergeCell ref="AW31:AX36"/>
+    <mergeCell ref="BE48:BQ49"/>
+    <mergeCell ref="BL42:BN42"/>
+    <mergeCell ref="AY23:BB23"/>
+    <mergeCell ref="AX45:AZ45"/>
+    <mergeCell ref="BI42:BK42"/>
+    <mergeCell ref="BF21:BK21"/>
+    <mergeCell ref="BO45:BQ45"/>
+    <mergeCell ref="BR44:BR56"/>
+    <mergeCell ref="AY9:BB9"/>
+    <mergeCell ref="AW25:AX25"/>
+    <mergeCell ref="AW15:AX15"/>
+    <mergeCell ref="BC9:BE9"/>
+    <mergeCell ref="AY18:BB18"/>
+    <mergeCell ref="AW49:BD51"/>
+    <mergeCell ref="BI45:BK45"/>
+    <mergeCell ref="BC16:BE16"/>
+    <mergeCell ref="T7:AG11"/>
+    <mergeCell ref="B17:B29"/>
+    <mergeCell ref="AW7:AX7"/>
+    <mergeCell ref="B44:B56"/>
+    <mergeCell ref="BL41:BN41"/>
+    <mergeCell ref="T47:AG51"/>
+    <mergeCell ref="C3:D5"/>
+    <mergeCell ref="BM5:BO6"/>
+    <mergeCell ref="AW5:AX6"/>
+    <mergeCell ref="AT3:AV8"/>
+    <mergeCell ref="T17:AG20"/>
+    <mergeCell ref="T26:AG29"/>
+    <mergeCell ref="T35:AG39"/>
+    <mergeCell ref="BE52:BQ55"/>
+    <mergeCell ref="AX42:AZ42"/>
+    <mergeCell ref="AW43:AW44"/>
+    <mergeCell ref="AY5:BB6"/>
+    <mergeCell ref="BF20:BK20"/>
+    <mergeCell ref="AW20:AX20"/>
+    <mergeCell ref="AW52:BD52"/>
+    <mergeCell ref="BO42:BQ42"/>
+    <mergeCell ref="BP5:BP6"/>
+    <mergeCell ref="BO40:BQ40"/>
+    <mergeCell ref="BQ5:BQ6"/>
+    <mergeCell ref="AW14:AX14"/>
+    <mergeCell ref="AY7:BB7"/>
+    <mergeCell ref="BC10:BE10"/>
+    <mergeCell ref="BM17:BO17"/>
+    <mergeCell ref="BC23:BE23"/>
+    <mergeCell ref="BF18:BK18"/>
+    <mergeCell ref="AW12:AX12"/>
+    <mergeCell ref="BM14:BO14"/>
+    <mergeCell ref="BC12:BE12"/>
+    <mergeCell ref="BF19:BK19"/>
+    <mergeCell ref="BM21:BO21"/>
+    <mergeCell ref="BF13:BK13"/>
+    <mergeCell ref="AW13:AX13"/>
+    <mergeCell ref="AW8:AX8"/>
+    <mergeCell ref="BF8:BK8"/>
+    <mergeCell ref="BI46:BQ46"/>
+    <mergeCell ref="BM23:BO23"/>
+    <mergeCell ref="BF15:BK15"/>
+    <mergeCell ref="BL5:BL6"/>
+    <mergeCell ref="AY14:BB14"/>
+    <mergeCell ref="AY25:BB25"/>
+    <mergeCell ref="AY31:BQ36"/>
+    <mergeCell ref="AY12:BB12"/>
+    <mergeCell ref="BC14:BE14"/>
+    <mergeCell ref="BM22:BO22"/>
+    <mergeCell ref="BL43:BN44"/>
+    <mergeCell ref="BC24:BE24"/>
+    <mergeCell ref="BA45:BH45"/>
+    <mergeCell ref="BL45:BN45"/>
+    <mergeCell ref="BI40:BK40"/>
+    <mergeCell ref="AW46:AZ46"/>
+    <mergeCell ref="BC26:BE26"/>
+    <mergeCell ref="BF26:BK26"/>
+    <mergeCell ref="BM26:BO26"/>
     <mergeCell ref="M2:X2"/>
     <mergeCell ref="AU2:BF2"/>
     <mergeCell ref="AW18:AX18"/>
@@ -4030,171 +4190,6 @@
     <mergeCell ref="AW19:AX19"/>
     <mergeCell ref="AW53:BD55"/>
     <mergeCell ref="AW3:BQ4"/>
-    <mergeCell ref="BI46:BQ46"/>
-    <mergeCell ref="BM23:BO23"/>
-    <mergeCell ref="BF15:BK15"/>
-    <mergeCell ref="BL5:BL6"/>
-    <mergeCell ref="AY14:BB14"/>
-    <mergeCell ref="AY25:BB25"/>
-    <mergeCell ref="AY31:BQ36"/>
-    <mergeCell ref="AY12:BB12"/>
-    <mergeCell ref="BC14:BE14"/>
-    <mergeCell ref="BM22:BO22"/>
-    <mergeCell ref="AW14:AX14"/>
-    <mergeCell ref="AY7:BB7"/>
-    <mergeCell ref="BC10:BE10"/>
-    <mergeCell ref="BM17:BO17"/>
-    <mergeCell ref="BC23:BE23"/>
-    <mergeCell ref="BF18:BK18"/>
-    <mergeCell ref="AW12:AX12"/>
-    <mergeCell ref="BM14:BO14"/>
-    <mergeCell ref="BC12:BE12"/>
-    <mergeCell ref="BL43:BN44"/>
-    <mergeCell ref="BF19:BK19"/>
-    <mergeCell ref="BC24:BE24"/>
-    <mergeCell ref="T7:AG11"/>
-    <mergeCell ref="B17:B29"/>
-    <mergeCell ref="AW7:AX7"/>
-    <mergeCell ref="B44:B56"/>
-    <mergeCell ref="BL41:BN41"/>
-    <mergeCell ref="T47:AG51"/>
-    <mergeCell ref="C3:D5"/>
-    <mergeCell ref="BM5:BO6"/>
-    <mergeCell ref="AW5:AX6"/>
-    <mergeCell ref="AT3:AV8"/>
-    <mergeCell ref="T17:AG20"/>
-    <mergeCell ref="T26:AG29"/>
-    <mergeCell ref="T35:AG39"/>
-    <mergeCell ref="BE52:BQ55"/>
-    <mergeCell ref="AX42:AZ42"/>
-    <mergeCell ref="AW43:AW44"/>
-    <mergeCell ref="AY5:BB6"/>
-    <mergeCell ref="BF20:BK20"/>
-    <mergeCell ref="AW20:AX20"/>
-    <mergeCell ref="AW52:BD52"/>
-    <mergeCell ref="BO42:BQ42"/>
-    <mergeCell ref="BP5:BP6"/>
-    <mergeCell ref="BO40:BQ40"/>
-    <mergeCell ref="BQ5:BQ6"/>
-    <mergeCell ref="BM21:BO21"/>
-    <mergeCell ref="BF13:BK13"/>
-    <mergeCell ref="AW13:AX13"/>
-    <mergeCell ref="BA45:BH45"/>
-    <mergeCell ref="AW8:AX8"/>
-    <mergeCell ref="BL45:BN45"/>
-    <mergeCell ref="BR30:BR43"/>
-    <mergeCell ref="BM8:BO8"/>
-    <mergeCell ref="AX39:AZ39"/>
-    <mergeCell ref="BM16:BO16"/>
-    <mergeCell ref="BA46:BH46"/>
-    <mergeCell ref="BA39:BH39"/>
-    <mergeCell ref="BM10:BO10"/>
-    <mergeCell ref="AW31:AX36"/>
-    <mergeCell ref="BE48:BQ49"/>
-    <mergeCell ref="BL42:BN42"/>
-    <mergeCell ref="AY23:BB23"/>
-    <mergeCell ref="AX45:AZ45"/>
-    <mergeCell ref="BI42:BK42"/>
-    <mergeCell ref="BF21:BK21"/>
-    <mergeCell ref="BO45:BQ45"/>
-    <mergeCell ref="BR44:BR56"/>
-    <mergeCell ref="AY9:BB9"/>
-    <mergeCell ref="AW25:AX25"/>
-    <mergeCell ref="AW15:AX15"/>
-    <mergeCell ref="BC9:BE9"/>
-    <mergeCell ref="AY18:BB18"/>
-    <mergeCell ref="AW49:BD51"/>
-    <mergeCell ref="BI45:BK45"/>
-    <mergeCell ref="BC16:BE16"/>
-    <mergeCell ref="B30:B43"/>
-    <mergeCell ref="AW47:AZ47"/>
-    <mergeCell ref="BF10:BK10"/>
-    <mergeCell ref="AW10:AX10"/>
-    <mergeCell ref="BF17:BK17"/>
-    <mergeCell ref="AW23:AX23"/>
-    <mergeCell ref="BC18:BE18"/>
-    <mergeCell ref="AW48:BD48"/>
-    <mergeCell ref="BI41:BK41"/>
-    <mergeCell ref="B3:B16"/>
-    <mergeCell ref="BI47:BQ47"/>
-    <mergeCell ref="AW21:AX21"/>
-    <mergeCell ref="BC19:BE19"/>
-    <mergeCell ref="AX41:AZ41"/>
-    <mergeCell ref="BM24:BO24"/>
-    <mergeCell ref="BI39:BK39"/>
-    <mergeCell ref="BC21:BE21"/>
-    <mergeCell ref="AX43:AZ44"/>
-    <mergeCell ref="AY20:BB20"/>
-    <mergeCell ref="AW16:AX16"/>
-    <mergeCell ref="BF5:BK6"/>
-    <mergeCell ref="BC17:BE17"/>
-    <mergeCell ref="AY24:BB24"/>
-    <mergeCell ref="BC5:BE6"/>
-    <mergeCell ref="BF8:BK8"/>
-    <mergeCell ref="BI40:BK40"/>
-    <mergeCell ref="AW46:AZ46"/>
-    <mergeCell ref="BC26:BE26"/>
-    <mergeCell ref="BF26:BK26"/>
-    <mergeCell ref="BM26:BO26"/>
-    <mergeCell ref="BE50:BQ51"/>
-    <mergeCell ref="AY26:BB26"/>
-    <mergeCell ref="BR17:BR29"/>
-    <mergeCell ref="BM9:BO9"/>
-    <mergeCell ref="AY16:BB16"/>
-    <mergeCell ref="BO39:BQ39"/>
-    <mergeCell ref="BM19:BO19"/>
-    <mergeCell ref="BF14:BK14"/>
-    <mergeCell ref="BF23:BK23"/>
-    <mergeCell ref="BM12:BO12"/>
-    <mergeCell ref="BR3:BR16"/>
-    <mergeCell ref="BF25:BK25"/>
-    <mergeCell ref="BF22:BK22"/>
-    <mergeCell ref="BF12:BK12"/>
-    <mergeCell ref="BM20:BO20"/>
-    <mergeCell ref="BF7:BK7"/>
-    <mergeCell ref="AY21:BB21"/>
-    <mergeCell ref="BM18:BO18"/>
-    <mergeCell ref="BC13:BE13"/>
-    <mergeCell ref="BM13:BO13"/>
-    <mergeCell ref="C57:L57"/>
-    <mergeCell ref="M57:X57"/>
-    <mergeCell ref="Y57:AI57"/>
-    <mergeCell ref="AJ57:AT57"/>
-    <mergeCell ref="AW56:AX56"/>
-    <mergeCell ref="BM25:BO25"/>
-    <mergeCell ref="BL39:BN39"/>
-    <mergeCell ref="E47:R51"/>
-    <mergeCell ref="BA42:BH42"/>
-    <mergeCell ref="AY19:BB19"/>
-    <mergeCell ref="AY13:BB13"/>
-    <mergeCell ref="AX40:AZ40"/>
-    <mergeCell ref="AY22:BB22"/>
-    <mergeCell ref="BA43:BH44"/>
-    <mergeCell ref="BL40:BN40"/>
-    <mergeCell ref="C2:L2"/>
-    <mergeCell ref="BO41:BQ41"/>
-    <mergeCell ref="BF16:BK16"/>
-    <mergeCell ref="AY10:BB10"/>
-    <mergeCell ref="AW11:AX11"/>
-    <mergeCell ref="AY11:BB11"/>
-    <mergeCell ref="BC11:BE11"/>
-    <mergeCell ref="BF11:BK11"/>
-    <mergeCell ref="BM11:BO11"/>
-    <mergeCell ref="AY17:BB17"/>
-    <mergeCell ref="AW24:AX24"/>
-    <mergeCell ref="BF24:BK24"/>
-    <mergeCell ref="BC20:BE20"/>
-    <mergeCell ref="AY15:BB15"/>
-    <mergeCell ref="AW22:AX22"/>
-    <mergeCell ref="BA41:BH41"/>
-    <mergeCell ref="AW26:AX26"/>
-    <mergeCell ref="E7:R11"/>
-    <mergeCell ref="E17:R20"/>
-    <mergeCell ref="E26:R29"/>
-    <mergeCell ref="E35:R39"/>
-    <mergeCell ref="BM7:BO7"/>
-    <mergeCell ref="BM15:BO15"/>
-    <mergeCell ref="BC25:BE25"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/가공도_도면_1.xlsx
+++ b/가공도_도면_1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\duddl\AppData\Local\Temp\claude\C--Users-duddl-Desktop-Project-a2z\774260fd-2622-4588-9572-6413dbe29bb1\scratchpad\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\duddl\Desktop\Project\a2z\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E3CB389-5B70-4510-8688-39F1A570CAD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5DE3541-91FD-4955-98A3-84D950897497}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2784" yWindow="720" windowWidth="20256" windowHeight="11520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1177,7 +1177,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1232,6 +1232,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1241,6 +1244,57 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1250,8 +1304,77 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1272,130 +1395,10 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1779,723 +1782,723 @@
       <c r="BS1" s="6"/>
     </row>
     <row r="2" spans="1:71" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="C2" s="20">
+      <c r="C2" s="21">
         <v>1</v>
       </c>
-      <c r="D2" s="21"/>
-      <c r="E2" s="21"/>
-      <c r="F2" s="21"/>
-      <c r="G2" s="21"/>
-      <c r="H2" s="21"/>
-      <c r="I2" s="21"/>
-      <c r="J2" s="21"/>
-      <c r="K2" s="21"/>
-      <c r="L2" s="22"/>
-      <c r="M2" s="20">
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
+      <c r="I2" s="22"/>
+      <c r="J2" s="22"/>
+      <c r="K2" s="22"/>
+      <c r="L2" s="23"/>
+      <c r="M2" s="21">
         <v>2</v>
       </c>
-      <c r="N2" s="21"/>
-      <c r="O2" s="21"/>
-      <c r="P2" s="21"/>
-      <c r="Q2" s="21"/>
-      <c r="R2" s="21"/>
-      <c r="S2" s="21"/>
-      <c r="T2" s="21"/>
-      <c r="U2" s="21"/>
-      <c r="V2" s="21"/>
-      <c r="W2" s="21"/>
-      <c r="X2" s="22"/>
-      <c r="Y2" s="20">
+      <c r="N2" s="22"/>
+      <c r="O2" s="22"/>
+      <c r="P2" s="22"/>
+      <c r="Q2" s="22"/>
+      <c r="R2" s="22"/>
+      <c r="S2" s="22"/>
+      <c r="T2" s="22"/>
+      <c r="U2" s="22"/>
+      <c r="V2" s="22"/>
+      <c r="W2" s="22"/>
+      <c r="X2" s="23"/>
+      <c r="Y2" s="21">
         <v>3</v>
       </c>
-      <c r="Z2" s="21"/>
-      <c r="AA2" s="21"/>
-      <c r="AB2" s="21"/>
-      <c r="AC2" s="21"/>
-      <c r="AD2" s="21"/>
-      <c r="AE2" s="21"/>
-      <c r="AF2" s="21"/>
-      <c r="AG2" s="21"/>
-      <c r="AH2" s="21"/>
-      <c r="AI2" s="22"/>
-      <c r="AJ2" s="20">
+      <c r="Z2" s="22"/>
+      <c r="AA2" s="22"/>
+      <c r="AB2" s="22"/>
+      <c r="AC2" s="22"/>
+      <c r="AD2" s="22"/>
+      <c r="AE2" s="22"/>
+      <c r="AF2" s="22"/>
+      <c r="AG2" s="22"/>
+      <c r="AH2" s="22"/>
+      <c r="AI2" s="23"/>
+      <c r="AJ2" s="21">
         <v>4</v>
       </c>
-      <c r="AK2" s="21"/>
-      <c r="AL2" s="21"/>
-      <c r="AM2" s="21"/>
-      <c r="AN2" s="21"/>
-      <c r="AO2" s="21"/>
-      <c r="AP2" s="21"/>
-      <c r="AQ2" s="21"/>
-      <c r="AR2" s="21"/>
-      <c r="AS2" s="21"/>
-      <c r="AT2" s="22"/>
-      <c r="AU2" s="20">
+      <c r="AK2" s="22"/>
+      <c r="AL2" s="22"/>
+      <c r="AM2" s="22"/>
+      <c r="AN2" s="22"/>
+      <c r="AO2" s="22"/>
+      <c r="AP2" s="22"/>
+      <c r="AQ2" s="22"/>
+      <c r="AR2" s="22"/>
+      <c r="AS2" s="22"/>
+      <c r="AT2" s="23"/>
+      <c r="AU2" s="21">
         <v>5</v>
       </c>
-      <c r="AV2" s="21"/>
-      <c r="AW2" s="21"/>
-      <c r="AX2" s="21"/>
-      <c r="AY2" s="21"/>
-      <c r="AZ2" s="21"/>
-      <c r="BA2" s="21"/>
-      <c r="BB2" s="21"/>
-      <c r="BC2" s="21"/>
-      <c r="BD2" s="21"/>
-      <c r="BE2" s="21"/>
-      <c r="BF2" s="22"/>
-      <c r="BG2" s="20">
+      <c r="AV2" s="22"/>
+      <c r="AW2" s="22"/>
+      <c r="AX2" s="22"/>
+      <c r="AY2" s="22"/>
+      <c r="AZ2" s="22"/>
+      <c r="BA2" s="22"/>
+      <c r="BB2" s="22"/>
+      <c r="BC2" s="22"/>
+      <c r="BD2" s="22"/>
+      <c r="BE2" s="22"/>
+      <c r="BF2" s="23"/>
+      <c r="BG2" s="21">
         <v>6</v>
       </c>
-      <c r="BH2" s="21"/>
-      <c r="BI2" s="21"/>
-      <c r="BJ2" s="21"/>
-      <c r="BK2" s="21"/>
-      <c r="BL2" s="21"/>
-      <c r="BM2" s="21"/>
-      <c r="BN2" s="21"/>
-      <c r="BO2" s="21"/>
-      <c r="BP2" s="21"/>
-      <c r="BQ2" s="22"/>
+      <c r="BH2" s="22"/>
+      <c r="BI2" s="22"/>
+      <c r="BJ2" s="22"/>
+      <c r="BK2" s="22"/>
+      <c r="BL2" s="22"/>
+      <c r="BM2" s="22"/>
+      <c r="BN2" s="22"/>
+      <c r="BO2" s="22"/>
+      <c r="BP2" s="22"/>
+      <c r="BQ2" s="23"/>
       <c r="BR2" s="2"/>
     </row>
     <row r="3" spans="1:71" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B3" s="23" t="s">
+      <c r="B3" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="51" t="s">
+      <c r="C3" s="44" t="s">
         <v>221</v>
       </c>
-      <c r="D3" s="52"/>
+      <c r="D3" s="45"/>
       <c r="Y3" s="3"/>
-      <c r="AT3" s="43" t="s">
+      <c r="AT3" s="54" t="s">
         <v>220</v>
       </c>
-      <c r="AU3" s="43"/>
-      <c r="AV3" s="48"/>
-      <c r="AW3" s="66" t="s">
+      <c r="AU3" s="54"/>
+      <c r="AV3" s="55"/>
+      <c r="AW3" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="AX3" s="67"/>
-      <c r="AY3" s="67"/>
-      <c r="AZ3" s="67"/>
-      <c r="BA3" s="67"/>
-      <c r="BB3" s="67"/>
-      <c r="BC3" s="67"/>
-      <c r="BD3" s="67"/>
-      <c r="BE3" s="67"/>
-      <c r="BF3" s="67"/>
-      <c r="BG3" s="67"/>
-      <c r="BH3" s="67"/>
-      <c r="BI3" s="67"/>
-      <c r="BJ3" s="67"/>
-      <c r="BK3" s="67"/>
-      <c r="BL3" s="67"/>
-      <c r="BM3" s="67"/>
-      <c r="BN3" s="67"/>
-      <c r="BO3" s="67"/>
-      <c r="BP3" s="67"/>
-      <c r="BQ3" s="68"/>
-      <c r="BR3" s="23" t="s">
+      <c r="AX3" s="31"/>
+      <c r="AY3" s="31"/>
+      <c r="AZ3" s="31"/>
+      <c r="BA3" s="31"/>
+      <c r="BB3" s="31"/>
+      <c r="BC3" s="31"/>
+      <c r="BD3" s="31"/>
+      <c r="BE3" s="31"/>
+      <c r="BF3" s="31"/>
+      <c r="BG3" s="31"/>
+      <c r="BH3" s="31"/>
+      <c r="BI3" s="31"/>
+      <c r="BJ3" s="31"/>
+      <c r="BK3" s="31"/>
+      <c r="BL3" s="31"/>
+      <c r="BM3" s="31"/>
+      <c r="BN3" s="31"/>
+      <c r="BO3" s="31"/>
+      <c r="BP3" s="31"/>
+      <c r="BQ3" s="32"/>
+      <c r="BR3" s="41" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:71" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="24"/>
-      <c r="C4" s="53"/>
-      <c r="D4" s="54"/>
+      <c r="B4" s="42"/>
+      <c r="C4" s="46"/>
+      <c r="D4" s="47"/>
       <c r="E4" s="3"/>
       <c r="AA4" s="3"/>
-      <c r="AT4" s="45"/>
-      <c r="AU4" s="45"/>
-      <c r="AV4" s="49"/>
-      <c r="AW4" s="69"/>
-      <c r="AX4" s="70"/>
-      <c r="AY4" s="70"/>
-      <c r="AZ4" s="70"/>
-      <c r="BA4" s="70"/>
-      <c r="BB4" s="70"/>
-      <c r="BC4" s="70"/>
-      <c r="BD4" s="70"/>
-      <c r="BE4" s="70"/>
-      <c r="BF4" s="70"/>
-      <c r="BG4" s="70"/>
-      <c r="BH4" s="70"/>
-      <c r="BI4" s="70"/>
-      <c r="BJ4" s="70"/>
-      <c r="BK4" s="70"/>
-      <c r="BL4" s="70"/>
-      <c r="BM4" s="70"/>
-      <c r="BN4" s="70"/>
-      <c r="BO4" s="70"/>
-      <c r="BP4" s="70"/>
-      <c r="BQ4" s="71"/>
-      <c r="BR4" s="24"/>
+      <c r="AT4" s="25"/>
+      <c r="AU4" s="25"/>
+      <c r="AV4" s="26"/>
+      <c r="AW4" s="33"/>
+      <c r="AX4" s="34"/>
+      <c r="AY4" s="34"/>
+      <c r="AZ4" s="34"/>
+      <c r="BA4" s="34"/>
+      <c r="BB4" s="34"/>
+      <c r="BC4" s="34"/>
+      <c r="BD4" s="34"/>
+      <c r="BE4" s="34"/>
+      <c r="BF4" s="34"/>
+      <c r="BG4" s="34"/>
+      <c r="BH4" s="34"/>
+      <c r="BI4" s="34"/>
+      <c r="BJ4" s="34"/>
+      <c r="BK4" s="34"/>
+      <c r="BL4" s="34"/>
+      <c r="BM4" s="34"/>
+      <c r="BN4" s="34"/>
+      <c r="BO4" s="34"/>
+      <c r="BP4" s="34"/>
+      <c r="BQ4" s="35"/>
+      <c r="BR4" s="42"/>
     </row>
     <row r="5" spans="1:71" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B5" s="24"/>
-      <c r="C5" s="53"/>
-      <c r="D5" s="54"/>
-      <c r="AT5" s="45"/>
-      <c r="AU5" s="45"/>
-      <c r="AV5" s="49"/>
-      <c r="AW5" s="36" t="s">
+      <c r="B5" s="42"/>
+      <c r="C5" s="46"/>
+      <c r="D5" s="47"/>
+      <c r="AT5" s="25"/>
+      <c r="AU5" s="25"/>
+      <c r="AV5" s="26"/>
+      <c r="AW5" s="48" t="s">
         <v>215</v>
       </c>
-      <c r="AX5" s="38"/>
-      <c r="AY5" s="36" t="s">
+      <c r="AX5" s="50"/>
+      <c r="AY5" s="48" t="s">
         <v>4</v>
       </c>
-      <c r="AZ5" s="37"/>
-      <c r="BA5" s="37"/>
-      <c r="BB5" s="38"/>
-      <c r="BC5" s="36" t="s">
+      <c r="AZ5" s="49"/>
+      <c r="BA5" s="49"/>
+      <c r="BB5" s="50"/>
+      <c r="BC5" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="BD5" s="37"/>
-      <c r="BE5" s="38"/>
-      <c r="BF5" s="36" t="s">
+      <c r="BD5" s="49"/>
+      <c r="BE5" s="50"/>
+      <c r="BF5" s="48" t="s">
         <v>6</v>
       </c>
-      <c r="BG5" s="37"/>
-      <c r="BH5" s="37"/>
-      <c r="BI5" s="37"/>
-      <c r="BJ5" s="37"/>
-      <c r="BK5" s="38"/>
-      <c r="BL5" s="64" t="s">
+      <c r="BG5" s="49"/>
+      <c r="BH5" s="49"/>
+      <c r="BI5" s="49"/>
+      <c r="BJ5" s="49"/>
+      <c r="BK5" s="50"/>
+      <c r="BL5" s="36" t="s">
         <v>7</v>
       </c>
-      <c r="BM5" s="36" t="s">
+      <c r="BM5" s="48" t="s">
         <v>8</v>
       </c>
-      <c r="BN5" s="37"/>
-      <c r="BO5" s="38"/>
-      <c r="BP5" s="64" t="s">
+      <c r="BN5" s="49"/>
+      <c r="BO5" s="50"/>
+      <c r="BP5" s="36" t="s">
         <v>9</v>
       </c>
-      <c r="BQ5" s="64" t="s">
+      <c r="BQ5" s="36" t="s">
         <v>10</v>
       </c>
-      <c r="BR5" s="24"/>
+      <c r="BR5" s="42"/>
     </row>
     <row r="6" spans="1:71" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B6" s="24"/>
-      <c r="AT6" s="45"/>
-      <c r="AU6" s="45"/>
-      <c r="AV6" s="49"/>
-      <c r="AW6" s="39"/>
-      <c r="AX6" s="41"/>
-      <c r="AY6" s="39"/>
-      <c r="AZ6" s="40"/>
-      <c r="BA6" s="40"/>
-      <c r="BB6" s="41"/>
-      <c r="BC6" s="39"/>
-      <c r="BD6" s="40"/>
-      <c r="BE6" s="41"/>
-      <c r="BF6" s="39"/>
-      <c r="BG6" s="40"/>
-      <c r="BH6" s="40"/>
-      <c r="BI6" s="40"/>
-      <c r="BJ6" s="40"/>
-      <c r="BK6" s="41"/>
-      <c r="BL6" s="65"/>
-      <c r="BM6" s="39"/>
-      <c r="BN6" s="40"/>
-      <c r="BO6" s="41"/>
-      <c r="BP6" s="65"/>
-      <c r="BQ6" s="65"/>
-      <c r="BR6" s="24"/>
+      <c r="B6" s="42"/>
+      <c r="AT6" s="25"/>
+      <c r="AU6" s="25"/>
+      <c r="AV6" s="26"/>
+      <c r="AW6" s="51"/>
+      <c r="AX6" s="53"/>
+      <c r="AY6" s="51"/>
+      <c r="AZ6" s="52"/>
+      <c r="BA6" s="52"/>
+      <c r="BB6" s="53"/>
+      <c r="BC6" s="51"/>
+      <c r="BD6" s="52"/>
+      <c r="BE6" s="53"/>
+      <c r="BF6" s="51"/>
+      <c r="BG6" s="52"/>
+      <c r="BH6" s="52"/>
+      <c r="BI6" s="52"/>
+      <c r="BJ6" s="52"/>
+      <c r="BK6" s="53"/>
+      <c r="BL6" s="37"/>
+      <c r="BM6" s="51"/>
+      <c r="BN6" s="52"/>
+      <c r="BO6" s="53"/>
+      <c r="BP6" s="37"/>
+      <c r="BQ6" s="37"/>
+      <c r="BR6" s="42"/>
     </row>
     <row r="7" spans="1:71" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B7" s="24"/>
-      <c r="E7" s="26" t="s">
+      <c r="B7" s="42"/>
+      <c r="E7" s="75" t="s">
         <v>268</v>
       </c>
-      <c r="F7" s="26"/>
-      <c r="G7" s="26"/>
-      <c r="H7" s="26"/>
-      <c r="I7" s="26"/>
-      <c r="J7" s="26"/>
-      <c r="K7" s="26"/>
-      <c r="L7" s="26"/>
-      <c r="M7" s="26"/>
-      <c r="N7" s="26"/>
-      <c r="O7" s="26"/>
-      <c r="P7" s="26"/>
-      <c r="Q7" s="26"/>
-      <c r="R7" s="26"/>
-      <c r="T7" s="26" t="s">
+      <c r="F7" s="75"/>
+      <c r="G7" s="75"/>
+      <c r="H7" s="75"/>
+      <c r="I7" s="75"/>
+      <c r="J7" s="75"/>
+      <c r="K7" s="75"/>
+      <c r="L7" s="75"/>
+      <c r="M7" s="75"/>
+      <c r="N7" s="75"/>
+      <c r="O7" s="75"/>
+      <c r="P7" s="75"/>
+      <c r="Q7" s="75"/>
+      <c r="R7" s="75"/>
+      <c r="T7" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="U7" s="26"/>
-      <c r="V7" s="26"/>
-      <c r="W7" s="26"/>
-      <c r="X7" s="26"/>
-      <c r="Y7" s="26"/>
-      <c r="Z7" s="26"/>
-      <c r="AA7" s="26"/>
-      <c r="AB7" s="26"/>
-      <c r="AC7" s="26"/>
-      <c r="AD7" s="26"/>
-      <c r="AE7" s="26"/>
-      <c r="AF7" s="26"/>
-      <c r="AG7" s="26"/>
-      <c r="AT7" s="45"/>
-      <c r="AU7" s="45"/>
-      <c r="AV7" s="49"/>
-      <c r="AW7" s="20" t="s">
+      <c r="U7" s="20"/>
+      <c r="V7" s="20"/>
+      <c r="W7" s="20"/>
+      <c r="X7" s="20"/>
+      <c r="Y7" s="20"/>
+      <c r="Z7" s="20"/>
+      <c r="AA7" s="20"/>
+      <c r="AB7" s="20"/>
+      <c r="AC7" s="20"/>
+      <c r="AD7" s="20"/>
+      <c r="AE7" s="20"/>
+      <c r="AF7" s="20"/>
+      <c r="AG7" s="20"/>
+      <c r="AT7" s="25"/>
+      <c r="AU7" s="25"/>
+      <c r="AV7" s="26"/>
+      <c r="AW7" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="AX7" s="22"/>
-      <c r="AY7" s="20" t="s">
+      <c r="AX7" s="23"/>
+      <c r="AY7" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="AZ7" s="21"/>
-      <c r="BA7" s="21"/>
-      <c r="BB7" s="22"/>
-      <c r="BC7" s="20" t="s">
+      <c r="AZ7" s="22"/>
+      <c r="BA7" s="22"/>
+      <c r="BB7" s="23"/>
+      <c r="BC7" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="BD7" s="21"/>
-      <c r="BE7" s="22"/>
-      <c r="BF7" s="20" t="s">
+      <c r="BD7" s="22"/>
+      <c r="BE7" s="23"/>
+      <c r="BF7" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="BG7" s="21"/>
-      <c r="BH7" s="21"/>
-      <c r="BI7" s="21"/>
-      <c r="BJ7" s="21"/>
-      <c r="BK7" s="22"/>
+      <c r="BG7" s="22"/>
+      <c r="BH7" s="22"/>
+      <c r="BI7" s="22"/>
+      <c r="BJ7" s="22"/>
+      <c r="BK7" s="23"/>
       <c r="BL7" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="BM7" s="20" t="s">
+      <c r="BM7" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="BN7" s="21"/>
-      <c r="BO7" s="22"/>
+      <c r="BN7" s="22"/>
+      <c r="BO7" s="23"/>
       <c r="BP7" s="4" t="s">
         <v>17</v>
       </c>
       <c r="BQ7" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="BR7" s="24"/>
+      <c r="BR7" s="42"/>
     </row>
     <row r="8" spans="1:71" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B8" s="24"/>
-      <c r="E8" s="26"/>
-      <c r="F8" s="26"/>
-      <c r="G8" s="26"/>
-      <c r="H8" s="26"/>
-      <c r="I8" s="26"/>
-      <c r="J8" s="26"/>
-      <c r="K8" s="26"/>
-      <c r="L8" s="26"/>
-      <c r="M8" s="26"/>
-      <c r="N8" s="26"/>
-      <c r="O8" s="26"/>
-      <c r="P8" s="26"/>
-      <c r="Q8" s="26"/>
-      <c r="R8" s="26"/>
-      <c r="T8" s="26"/>
-      <c r="U8" s="26"/>
-      <c r="V8" s="26"/>
-      <c r="W8" s="26"/>
-      <c r="X8" s="26"/>
-      <c r="Y8" s="26"/>
-      <c r="Z8" s="26"/>
-      <c r="AA8" s="26"/>
-      <c r="AB8" s="26"/>
-      <c r="AC8" s="26"/>
-      <c r="AD8" s="26"/>
-      <c r="AE8" s="26"/>
-      <c r="AF8" s="26"/>
-      <c r="AG8" s="26"/>
-      <c r="AT8" s="45"/>
-      <c r="AU8" s="45"/>
-      <c r="AV8" s="49"/>
-      <c r="AW8" s="20" t="s">
+      <c r="B8" s="42"/>
+      <c r="E8" s="75"/>
+      <c r="F8" s="75"/>
+      <c r="G8" s="75"/>
+      <c r="H8" s="75"/>
+      <c r="I8" s="75"/>
+      <c r="J8" s="75"/>
+      <c r="K8" s="75"/>
+      <c r="L8" s="75"/>
+      <c r="M8" s="75"/>
+      <c r="N8" s="75"/>
+      <c r="O8" s="75"/>
+      <c r="P8" s="75"/>
+      <c r="Q8" s="75"/>
+      <c r="R8" s="75"/>
+      <c r="T8" s="20"/>
+      <c r="U8" s="20"/>
+      <c r="V8" s="20"/>
+      <c r="W8" s="20"/>
+      <c r="X8" s="20"/>
+      <c r="Y8" s="20"/>
+      <c r="Z8" s="20"/>
+      <c r="AA8" s="20"/>
+      <c r="AB8" s="20"/>
+      <c r="AC8" s="20"/>
+      <c r="AD8" s="20"/>
+      <c r="AE8" s="20"/>
+      <c r="AF8" s="20"/>
+      <c r="AG8" s="20"/>
+      <c r="AT8" s="25"/>
+      <c r="AU8" s="25"/>
+      <c r="AV8" s="26"/>
+      <c r="AW8" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="AX8" s="22"/>
-      <c r="AY8" s="20" t="s">
+      <c r="AX8" s="23"/>
+      <c r="AY8" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="AZ8" s="21"/>
-      <c r="BA8" s="21"/>
-      <c r="BB8" s="22"/>
-      <c r="BC8" s="20" t="s">
+      <c r="AZ8" s="22"/>
+      <c r="BA8" s="22"/>
+      <c r="BB8" s="23"/>
+      <c r="BC8" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="BD8" s="21"/>
-      <c r="BE8" s="22"/>
-      <c r="BF8" s="20" t="s">
+      <c r="BD8" s="22"/>
+      <c r="BE8" s="23"/>
+      <c r="BF8" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="BG8" s="21"/>
-      <c r="BH8" s="21"/>
-      <c r="BI8" s="21"/>
-      <c r="BJ8" s="21"/>
-      <c r="BK8" s="22"/>
+      <c r="BG8" s="22"/>
+      <c r="BH8" s="22"/>
+      <c r="BI8" s="22"/>
+      <c r="BJ8" s="22"/>
+      <c r="BK8" s="23"/>
       <c r="BL8" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="BM8" s="20" t="s">
+      <c r="BM8" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="BN8" s="21"/>
-      <c r="BO8" s="22"/>
+      <c r="BN8" s="22"/>
+      <c r="BO8" s="23"/>
       <c r="BP8" s="8" t="s">
         <v>25</v>
       </c>
       <c r="BQ8" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="BR8" s="24"/>
+      <c r="BR8" s="42"/>
     </row>
     <row r="9" spans="1:71" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B9" s="24"/>
-      <c r="E9" s="26"/>
-      <c r="F9" s="26"/>
-      <c r="G9" s="26"/>
-      <c r="H9" s="26"/>
-      <c r="I9" s="26"/>
-      <c r="J9" s="26"/>
-      <c r="K9" s="26"/>
-      <c r="L9" s="26"/>
-      <c r="M9" s="26"/>
-      <c r="N9" s="26"/>
-      <c r="O9" s="26"/>
-      <c r="P9" s="26"/>
-      <c r="Q9" s="26"/>
-      <c r="R9" s="26"/>
-      <c r="T9" s="26"/>
-      <c r="U9" s="26"/>
-      <c r="V9" s="26"/>
-      <c r="W9" s="26"/>
-      <c r="X9" s="26"/>
-      <c r="Y9" s="26"/>
-      <c r="Z9" s="26"/>
-      <c r="AA9" s="26"/>
-      <c r="AB9" s="26"/>
-      <c r="AC9" s="26"/>
-      <c r="AD9" s="26"/>
-      <c r="AE9" s="26"/>
-      <c r="AF9" s="26"/>
-      <c r="AG9" s="26"/>
+      <c r="B9" s="42"/>
+      <c r="E9" s="75"/>
+      <c r="F9" s="75"/>
+      <c r="G9" s="75"/>
+      <c r="H9" s="75"/>
+      <c r="I9" s="75"/>
+      <c r="J9" s="75"/>
+      <c r="K9" s="75"/>
+      <c r="L9" s="75"/>
+      <c r="M9" s="75"/>
+      <c r="N9" s="75"/>
+      <c r="O9" s="75"/>
+      <c r="P9" s="75"/>
+      <c r="Q9" s="75"/>
+      <c r="R9" s="75"/>
+      <c r="T9" s="20"/>
+      <c r="U9" s="20"/>
+      <c r="V9" s="20"/>
+      <c r="W9" s="20"/>
+      <c r="X9" s="20"/>
+      <c r="Y9" s="20"/>
+      <c r="Z9" s="20"/>
+      <c r="AA9" s="20"/>
+      <c r="AB9" s="20"/>
+      <c r="AC9" s="20"/>
+      <c r="AD9" s="20"/>
+      <c r="AE9" s="20"/>
+      <c r="AF9" s="20"/>
+      <c r="AG9" s="20"/>
       <c r="AT9" s="11"/>
       <c r="AU9" s="11"/>
       <c r="AV9" s="12"/>
-      <c r="AW9" s="20" t="s">
+      <c r="AW9" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="AX9" s="22"/>
-      <c r="AY9" s="20" t="s">
+      <c r="AX9" s="23"/>
+      <c r="AY9" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="AZ9" s="21"/>
-      <c r="BA9" s="21"/>
-      <c r="BB9" s="22"/>
-      <c r="BC9" s="20" t="s">
+      <c r="AZ9" s="22"/>
+      <c r="BA9" s="22"/>
+      <c r="BB9" s="23"/>
+      <c r="BC9" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="BD9" s="21"/>
-      <c r="BE9" s="22"/>
-      <c r="BF9" s="20" t="s">
+      <c r="BD9" s="22"/>
+      <c r="BE9" s="23"/>
+      <c r="BF9" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="BG9" s="21"/>
-      <c r="BH9" s="21"/>
-      <c r="BI9" s="21"/>
-      <c r="BJ9" s="21"/>
-      <c r="BK9" s="22"/>
+      <c r="BG9" s="22"/>
+      <c r="BH9" s="22"/>
+      <c r="BI9" s="22"/>
+      <c r="BJ9" s="22"/>
+      <c r="BK9" s="23"/>
       <c r="BL9" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="BM9" s="20" t="s">
+      <c r="BM9" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="BN9" s="21"/>
-      <c r="BO9" s="22"/>
+      <c r="BN9" s="22"/>
+      <c r="BO9" s="23"/>
       <c r="BP9" s="8" t="s">
         <v>33</v>
       </c>
       <c r="BQ9" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="BR9" s="24"/>
+      <c r="BR9" s="42"/>
     </row>
     <row r="10" spans="1:71" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B10" s="24"/>
-      <c r="E10" s="26"/>
-      <c r="F10" s="26"/>
-      <c r="G10" s="26"/>
-      <c r="H10" s="26"/>
-      <c r="I10" s="26"/>
-      <c r="J10" s="26"/>
-      <c r="K10" s="26"/>
-      <c r="L10" s="26"/>
-      <c r="M10" s="26"/>
-      <c r="N10" s="26"/>
-      <c r="O10" s="26"/>
-      <c r="P10" s="26"/>
-      <c r="Q10" s="26"/>
-      <c r="R10" s="26"/>
-      <c r="T10" s="26"/>
-      <c r="U10" s="26"/>
-      <c r="V10" s="26"/>
-      <c r="W10" s="26"/>
-      <c r="X10" s="26"/>
-      <c r="Y10" s="26"/>
-      <c r="Z10" s="26"/>
-      <c r="AA10" s="26"/>
-      <c r="AB10" s="26"/>
-      <c r="AC10" s="26"/>
-      <c r="AD10" s="26"/>
-      <c r="AE10" s="26"/>
-      <c r="AF10" s="26"/>
-      <c r="AG10" s="26"/>
+      <c r="B10" s="42"/>
+      <c r="E10" s="75"/>
+      <c r="F10" s="75"/>
+      <c r="G10" s="75"/>
+      <c r="H10" s="75"/>
+      <c r="I10" s="75"/>
+      <c r="J10" s="75"/>
+      <c r="K10" s="75"/>
+      <c r="L10" s="75"/>
+      <c r="M10" s="75"/>
+      <c r="N10" s="75"/>
+      <c r="O10" s="75"/>
+      <c r="P10" s="75"/>
+      <c r="Q10" s="75"/>
+      <c r="R10" s="75"/>
+      <c r="T10" s="20"/>
+      <c r="U10" s="20"/>
+      <c r="V10" s="20"/>
+      <c r="W10" s="20"/>
+      <c r="X10" s="20"/>
+      <c r="Y10" s="20"/>
+      <c r="Z10" s="20"/>
+      <c r="AA10" s="20"/>
+      <c r="AB10" s="20"/>
+      <c r="AC10" s="20"/>
+      <c r="AD10" s="20"/>
+      <c r="AE10" s="20"/>
+      <c r="AF10" s="20"/>
+      <c r="AG10" s="20"/>
       <c r="AT10" s="11"/>
       <c r="AU10" s="11"/>
       <c r="AV10" s="12"/>
-      <c r="AW10" s="20" t="s">
+      <c r="AW10" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="AX10" s="22"/>
-      <c r="AY10" s="20" t="s">
+      <c r="AX10" s="23"/>
+      <c r="AY10" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="AZ10" s="21"/>
-      <c r="BA10" s="21"/>
-      <c r="BB10" s="22"/>
-      <c r="BC10" s="20" t="s">
+      <c r="AZ10" s="22"/>
+      <c r="BA10" s="22"/>
+      <c r="BB10" s="23"/>
+      <c r="BC10" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="BD10" s="21"/>
-      <c r="BE10" s="22"/>
-      <c r="BF10" s="20" t="s">
+      <c r="BD10" s="22"/>
+      <c r="BE10" s="23"/>
+      <c r="BF10" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="BG10" s="21"/>
-      <c r="BH10" s="21"/>
-      <c r="BI10" s="21"/>
-      <c r="BJ10" s="21"/>
-      <c r="BK10" s="22"/>
+      <c r="BG10" s="22"/>
+      <c r="BH10" s="22"/>
+      <c r="BI10" s="22"/>
+      <c r="BJ10" s="22"/>
+      <c r="BK10" s="23"/>
       <c r="BL10" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="BM10" s="20" t="s">
+      <c r="BM10" s="21" t="s">
         <v>40</v>
       </c>
-      <c r="BN10" s="21"/>
-      <c r="BO10" s="22"/>
+      <c r="BN10" s="22"/>
+      <c r="BO10" s="23"/>
       <c r="BP10" s="8" t="s">
         <v>41</v>
       </c>
       <c r="BQ10" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="BR10" s="24"/>
+      <c r="BR10" s="42"/>
     </row>
     <row r="11" spans="1:71" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B11" s="24"/>
-      <c r="E11" s="26"/>
-      <c r="F11" s="26"/>
-      <c r="G11" s="26"/>
-      <c r="H11" s="26"/>
-      <c r="I11" s="26"/>
-      <c r="J11" s="26"/>
-      <c r="K11" s="26"/>
-      <c r="L11" s="26"/>
-      <c r="M11" s="26"/>
-      <c r="N11" s="26"/>
-      <c r="O11" s="26"/>
-      <c r="P11" s="26"/>
-      <c r="Q11" s="26"/>
-      <c r="R11" s="26"/>
-      <c r="T11" s="26"/>
-      <c r="U11" s="26"/>
-      <c r="V11" s="26"/>
-      <c r="W11" s="26"/>
-      <c r="X11" s="26"/>
-      <c r="Y11" s="26"/>
-      <c r="Z11" s="26"/>
-      <c r="AA11" s="26"/>
-      <c r="AB11" s="26"/>
-      <c r="AC11" s="26"/>
-      <c r="AD11" s="26"/>
-      <c r="AE11" s="26"/>
-      <c r="AF11" s="26"/>
-      <c r="AG11" s="26"/>
+      <c r="B11" s="42"/>
+      <c r="E11" s="75"/>
+      <c r="F11" s="75"/>
+      <c r="G11" s="75"/>
+      <c r="H11" s="75"/>
+      <c r="I11" s="75"/>
+      <c r="J11" s="75"/>
+      <c r="K11" s="75"/>
+      <c r="L11" s="75"/>
+      <c r="M11" s="75"/>
+      <c r="N11" s="75"/>
+      <c r="O11" s="75"/>
+      <c r="P11" s="75"/>
+      <c r="Q11" s="75"/>
+      <c r="R11" s="75"/>
+      <c r="T11" s="20"/>
+      <c r="U11" s="20"/>
+      <c r="V11" s="20"/>
+      <c r="W11" s="20"/>
+      <c r="X11" s="20"/>
+      <c r="Y11" s="20"/>
+      <c r="Z11" s="20"/>
+      <c r="AA11" s="20"/>
+      <c r="AB11" s="20"/>
+      <c r="AC11" s="20"/>
+      <c r="AD11" s="20"/>
+      <c r="AE11" s="20"/>
+      <c r="AF11" s="20"/>
+      <c r="AG11" s="20"/>
       <c r="AT11" s="11"/>
       <c r="AU11" s="11"/>
       <c r="AV11" s="12"/>
-      <c r="AW11" s="20" t="s">
+      <c r="AW11" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="AX11" s="22"/>
-      <c r="AY11" s="20" t="s">
+      <c r="AX11" s="23"/>
+      <c r="AY11" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="AZ11" s="21"/>
-      <c r="BA11" s="21"/>
-      <c r="BB11" s="22"/>
-      <c r="BC11" s="20" t="s">
+      <c r="AZ11" s="22"/>
+      <c r="BA11" s="22"/>
+      <c r="BB11" s="23"/>
+      <c r="BC11" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="BD11" s="21"/>
-      <c r="BE11" s="22"/>
-      <c r="BF11" s="20" t="s">
+      <c r="BD11" s="22"/>
+      <c r="BE11" s="23"/>
+      <c r="BF11" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="BG11" s="21"/>
-      <c r="BH11" s="21"/>
-      <c r="BI11" s="21"/>
-      <c r="BJ11" s="21"/>
-      <c r="BK11" s="22"/>
+      <c r="BG11" s="22"/>
+      <c r="BH11" s="22"/>
+      <c r="BI11" s="22"/>
+      <c r="BJ11" s="22"/>
+      <c r="BK11" s="23"/>
       <c r="BL11" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="BM11" s="20" t="s">
+      <c r="BM11" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="BN11" s="21"/>
-      <c r="BO11" s="22"/>
+      <c r="BN11" s="22"/>
+      <c r="BO11" s="23"/>
       <c r="BP11" s="10" t="s">
         <v>49</v>
       </c>
       <c r="BQ11" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="BR11" s="24"/>
+      <c r="BR11" s="42"/>
     </row>
     <row r="12" spans="1:71" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B12" s="24"/>
-      <c r="AW12" s="20" t="s">
+      <c r="B12" s="42"/>
+      <c r="AW12" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="AX12" s="22"/>
-      <c r="AY12" s="20" t="s">
+      <c r="AX12" s="23"/>
+      <c r="AY12" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="AZ12" s="21"/>
-      <c r="BA12" s="21"/>
-      <c r="BB12" s="22"/>
-      <c r="BC12" s="20" t="s">
+      <c r="AZ12" s="22"/>
+      <c r="BA12" s="22"/>
+      <c r="BB12" s="23"/>
+      <c r="BC12" s="21" t="s">
         <v>53</v>
       </c>
-      <c r="BD12" s="21"/>
-      <c r="BE12" s="22"/>
-      <c r="BF12" s="20" t="s">
+      <c r="BD12" s="22"/>
+      <c r="BE12" s="23"/>
+      <c r="BF12" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="BG12" s="21"/>
-      <c r="BH12" s="21"/>
-      <c r="BI12" s="21"/>
-      <c r="BJ12" s="21"/>
-      <c r="BK12" s="22"/>
+      <c r="BG12" s="22"/>
+      <c r="BH12" s="22"/>
+      <c r="BI12" s="22"/>
+      <c r="BJ12" s="22"/>
+      <c r="BK12" s="23"/>
       <c r="BL12" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="BM12" s="20" t="s">
+      <c r="BM12" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="BN12" s="21"/>
-      <c r="BO12" s="22"/>
+      <c r="BN12" s="22"/>
+      <c r="BO12" s="23"/>
       <c r="BP12" s="8" t="s">
         <v>57</v>
       </c>
       <c r="BQ12" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="BR12" s="24"/>
+      <c r="BR12" s="42"/>
     </row>
     <row r="13" spans="1:71" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B13" s="24"/>
-      <c r="AW13" s="20" t="s">
+      <c r="B13" s="42"/>
+      <c r="AW13" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="AX13" s="22"/>
-      <c r="AY13" s="20" t="s">
+      <c r="AX13" s="23"/>
+      <c r="AY13" s="21" t="s">
         <v>60</v>
       </c>
-      <c r="AZ13" s="21"/>
-      <c r="BA13" s="21"/>
-      <c r="BB13" s="22"/>
-      <c r="BC13" s="20" t="s">
+      <c r="AZ13" s="22"/>
+      <c r="BA13" s="22"/>
+      <c r="BB13" s="23"/>
+      <c r="BC13" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="BD13" s="21"/>
-      <c r="BE13" s="22"/>
-      <c r="BF13" s="20" t="s">
+      <c r="BD13" s="22"/>
+      <c r="BE13" s="23"/>
+      <c r="BF13" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="BG13" s="21"/>
-      <c r="BH13" s="21"/>
-      <c r="BI13" s="21"/>
-      <c r="BJ13" s="21"/>
-      <c r="BK13" s="22"/>
+      <c r="BG13" s="22"/>
+      <c r="BH13" s="22"/>
+      <c r="BI13" s="22"/>
+      <c r="BJ13" s="22"/>
+      <c r="BK13" s="23"/>
       <c r="BL13" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="BM13" s="20" t="s">
+      <c r="BM13" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="BN13" s="21"/>
-      <c r="BO13" s="22"/>
+      <c r="BN13" s="22"/>
+      <c r="BO13" s="23"/>
       <c r="BP13" s="8" t="s">
         <v>65</v>
       </c>
       <c r="BQ13" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="BR13" s="24"/>
+      <c r="BR13" s="42"/>
     </row>
     <row r="14" spans="1:71" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B14" s="24"/>
-      <c r="AW14" s="20" t="s">
+      <c r="B14" s="42"/>
+      <c r="AW14" s="21" t="s">
         <v>67</v>
       </c>
-      <c r="AX14" s="22"/>
-      <c r="AY14" s="20" t="s">
+      <c r="AX14" s="23"/>
+      <c r="AY14" s="21" t="s">
         <v>68</v>
       </c>
-      <c r="AZ14" s="21"/>
-      <c r="BA14" s="21"/>
-      <c r="BB14" s="22"/>
-      <c r="BC14" s="20" t="s">
+      <c r="AZ14" s="22"/>
+      <c r="BA14" s="22"/>
+      <c r="BB14" s="23"/>
+      <c r="BC14" s="21" t="s">
         <v>69</v>
       </c>
-      <c r="BD14" s="21"/>
-      <c r="BE14" s="22"/>
-      <c r="BF14" s="20" t="s">
+      <c r="BD14" s="22"/>
+      <c r="BE14" s="23"/>
+      <c r="BF14" s="21" t="s">
         <v>70</v>
       </c>
-      <c r="BG14" s="21"/>
-      <c r="BH14" s="21"/>
-      <c r="BI14" s="21"/>
-      <c r="BJ14" s="21"/>
-      <c r="BK14" s="22"/>
+      <c r="BG14" s="22"/>
+      <c r="BH14" s="22"/>
+      <c r="BI14" s="22"/>
+      <c r="BJ14" s="22"/>
+      <c r="BK14" s="23"/>
       <c r="BL14" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="BM14" s="20" t="s">
+      <c r="BM14" s="21" t="s">
         <v>72</v>
       </c>
-      <c r="BN14" s="21"/>
-      <c r="BO14" s="22"/>
+      <c r="BN14" s="22"/>
+      <c r="BO14" s="23"/>
       <c r="BP14" s="8" t="s">
         <v>73</v>
       </c>
       <c r="BQ14" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="BR14" s="24"/>
+      <c r="BR14" s="42"/>
     </row>
     <row r="15" spans="1:71" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B15" s="24"/>
+      <c r="B15" s="42"/>
       <c r="U15" s="19"/>
       <c r="V15" s="19"/>
       <c r="W15" s="19"/>
@@ -2509,47 +2512,47 @@
       <c r="AE15" s="19"/>
       <c r="AF15" s="19"/>
       <c r="AG15" s="19"/>
-      <c r="AW15" s="20" t="s">
+      <c r="AW15" s="21" t="s">
         <v>75</v>
       </c>
-      <c r="AX15" s="22"/>
-      <c r="AY15" s="20" t="s">
+      <c r="AX15" s="23"/>
+      <c r="AY15" s="21" t="s">
         <v>76</v>
       </c>
-      <c r="AZ15" s="21"/>
-      <c r="BA15" s="21"/>
-      <c r="BB15" s="22"/>
-      <c r="BC15" s="20" t="s">
+      <c r="AZ15" s="22"/>
+      <c r="BA15" s="22"/>
+      <c r="BB15" s="23"/>
+      <c r="BC15" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="BD15" s="21"/>
-      <c r="BE15" s="22"/>
-      <c r="BF15" s="20" t="s">
+      <c r="BD15" s="22"/>
+      <c r="BE15" s="23"/>
+      <c r="BF15" s="21" t="s">
         <v>78</v>
       </c>
-      <c r="BG15" s="21"/>
-      <c r="BH15" s="21"/>
-      <c r="BI15" s="21"/>
-      <c r="BJ15" s="21"/>
-      <c r="BK15" s="22"/>
+      <c r="BG15" s="22"/>
+      <c r="BH15" s="22"/>
+      <c r="BI15" s="22"/>
+      <c r="BJ15" s="22"/>
+      <c r="BK15" s="23"/>
       <c r="BL15" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="BM15" s="20" t="s">
+      <c r="BM15" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="BN15" s="21"/>
-      <c r="BO15" s="22"/>
+      <c r="BN15" s="22"/>
+      <c r="BO15" s="23"/>
       <c r="BP15" s="8" t="s">
         <v>81</v>
       </c>
       <c r="BQ15" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="BR15" s="24"/>
+      <c r="BR15" s="42"/>
     </row>
     <row r="16" spans="1:71" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B16" s="25"/>
+      <c r="B16" s="43"/>
       <c r="U16" s="19"/>
       <c r="V16" s="19"/>
       <c r="W16" s="19"/>
@@ -2563,441 +2566,441 @@
       <c r="AE16" s="19"/>
       <c r="AF16" s="19"/>
       <c r="AG16" s="19"/>
-      <c r="AW16" s="20" t="s">
+      <c r="AW16" s="21" t="s">
         <v>84</v>
       </c>
-      <c r="AX16" s="22"/>
-      <c r="AY16" s="20" t="s">
+      <c r="AX16" s="23"/>
+      <c r="AY16" s="21" t="s">
         <v>85</v>
       </c>
-      <c r="AZ16" s="21"/>
-      <c r="BA16" s="21"/>
-      <c r="BB16" s="22"/>
-      <c r="BC16" s="20" t="s">
+      <c r="AZ16" s="22"/>
+      <c r="BA16" s="22"/>
+      <c r="BB16" s="23"/>
+      <c r="BC16" s="21" t="s">
         <v>86</v>
       </c>
-      <c r="BD16" s="21"/>
-      <c r="BE16" s="22"/>
-      <c r="BF16" s="20" t="s">
+      <c r="BD16" s="22"/>
+      <c r="BE16" s="23"/>
+      <c r="BF16" s="21" t="s">
         <v>87</v>
       </c>
-      <c r="BG16" s="21"/>
-      <c r="BH16" s="21"/>
-      <c r="BI16" s="21"/>
-      <c r="BJ16" s="21"/>
-      <c r="BK16" s="22"/>
+      <c r="BG16" s="22"/>
+      <c r="BH16" s="22"/>
+      <c r="BI16" s="22"/>
+      <c r="BJ16" s="22"/>
+      <c r="BK16" s="23"/>
       <c r="BL16" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="BM16" s="20" t="s">
+      <c r="BM16" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="BN16" s="21"/>
-      <c r="BO16" s="22"/>
+      <c r="BN16" s="22"/>
+      <c r="BO16" s="23"/>
       <c r="BP16" s="8" t="s">
         <v>90</v>
       </c>
       <c r="BQ16" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="BR16" s="25"/>
+      <c r="BR16" s="43"/>
     </row>
     <row r="17" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B17" s="23" t="s">
+      <c r="B17" s="41" t="s">
         <v>83</v>
       </c>
-      <c r="E17" s="26" t="s">
+      <c r="E17" s="75" t="s">
         <v>269</v>
       </c>
-      <c r="F17" s="26"/>
-      <c r="G17" s="26"/>
-      <c r="H17" s="26"/>
-      <c r="I17" s="26"/>
-      <c r="J17" s="26"/>
-      <c r="K17" s="26"/>
-      <c r="L17" s="26"/>
-      <c r="M17" s="26"/>
-      <c r="N17" s="26"/>
-      <c r="O17" s="26"/>
-      <c r="P17" s="26"/>
-      <c r="Q17" s="26"/>
-      <c r="R17" s="26"/>
-      <c r="T17" s="26" t="s">
+      <c r="F17" s="75"/>
+      <c r="G17" s="75"/>
+      <c r="H17" s="75"/>
+      <c r="I17" s="75"/>
+      <c r="J17" s="75"/>
+      <c r="K17" s="75"/>
+      <c r="L17" s="75"/>
+      <c r="M17" s="75"/>
+      <c r="N17" s="75"/>
+      <c r="O17" s="75"/>
+      <c r="P17" s="75"/>
+      <c r="Q17" s="75"/>
+      <c r="R17" s="75"/>
+      <c r="T17" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="U17" s="26"/>
-      <c r="V17" s="26"/>
-      <c r="W17" s="26"/>
-      <c r="X17" s="26"/>
-      <c r="Y17" s="26"/>
-      <c r="Z17" s="26"/>
-      <c r="AA17" s="26"/>
-      <c r="AB17" s="26"/>
-      <c r="AC17" s="26"/>
-      <c r="AD17" s="26"/>
-      <c r="AE17" s="26"/>
-      <c r="AF17" s="26"/>
-      <c r="AG17" s="26"/>
-      <c r="AW17" s="20" t="s">
+      <c r="U17" s="20"/>
+      <c r="V17" s="20"/>
+      <c r="W17" s="20"/>
+      <c r="X17" s="20"/>
+      <c r="Y17" s="20"/>
+      <c r="Z17" s="20"/>
+      <c r="AA17" s="20"/>
+      <c r="AB17" s="20"/>
+      <c r="AC17" s="20"/>
+      <c r="AD17" s="20"/>
+      <c r="AE17" s="20"/>
+      <c r="AF17" s="20"/>
+      <c r="AG17" s="20"/>
+      <c r="AW17" s="21" t="s">
         <v>92</v>
       </c>
-      <c r="AX17" s="22"/>
-      <c r="AY17" s="20" t="s">
+      <c r="AX17" s="23"/>
+      <c r="AY17" s="21" t="s">
         <v>93</v>
       </c>
-      <c r="AZ17" s="21"/>
-      <c r="BA17" s="21"/>
-      <c r="BB17" s="22"/>
-      <c r="BC17" s="20" t="s">
+      <c r="AZ17" s="22"/>
+      <c r="BA17" s="22"/>
+      <c r="BB17" s="23"/>
+      <c r="BC17" s="21" t="s">
         <v>94</v>
       </c>
-      <c r="BD17" s="21"/>
-      <c r="BE17" s="22"/>
-      <c r="BF17" s="20" t="s">
+      <c r="BD17" s="22"/>
+      <c r="BE17" s="23"/>
+      <c r="BF17" s="21" t="s">
         <v>95</v>
       </c>
-      <c r="BG17" s="21"/>
-      <c r="BH17" s="21"/>
-      <c r="BI17" s="21"/>
-      <c r="BJ17" s="21"/>
-      <c r="BK17" s="22"/>
+      <c r="BG17" s="22"/>
+      <c r="BH17" s="22"/>
+      <c r="BI17" s="22"/>
+      <c r="BJ17" s="22"/>
+      <c r="BK17" s="23"/>
       <c r="BL17" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="BM17" s="20" t="s">
+      <c r="BM17" s="21" t="s">
         <v>97</v>
       </c>
-      <c r="BN17" s="21"/>
-      <c r="BO17" s="22"/>
+      <c r="BN17" s="22"/>
+      <c r="BO17" s="23"/>
       <c r="BP17" s="8" t="s">
         <v>98</v>
       </c>
       <c r="BQ17" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="BR17" s="23" t="s">
+      <c r="BR17" s="41" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="18" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B18" s="24"/>
-      <c r="E18" s="26"/>
-      <c r="F18" s="26"/>
-      <c r="G18" s="26"/>
-      <c r="H18" s="26"/>
-      <c r="I18" s="26"/>
-      <c r="J18" s="26"/>
-      <c r="K18" s="26"/>
-      <c r="L18" s="26"/>
-      <c r="M18" s="26"/>
-      <c r="N18" s="26"/>
-      <c r="O18" s="26"/>
-      <c r="P18" s="26"/>
-      <c r="Q18" s="26"/>
-      <c r="R18" s="26"/>
-      <c r="T18" s="26"/>
-      <c r="U18" s="26"/>
-      <c r="V18" s="26"/>
-      <c r="W18" s="26"/>
-      <c r="X18" s="26"/>
-      <c r="Y18" s="26"/>
-      <c r="Z18" s="26"/>
-      <c r="AA18" s="26"/>
-      <c r="AB18" s="26"/>
-      <c r="AC18" s="26"/>
-      <c r="AD18" s="26"/>
-      <c r="AE18" s="26"/>
-      <c r="AF18" s="26"/>
-      <c r="AG18" s="26"/>
-      <c r="AW18" s="20" t="s">
+      <c r="B18" s="42"/>
+      <c r="E18" s="75"/>
+      <c r="F18" s="75"/>
+      <c r="G18" s="75"/>
+      <c r="H18" s="75"/>
+      <c r="I18" s="75"/>
+      <c r="J18" s="75"/>
+      <c r="K18" s="75"/>
+      <c r="L18" s="75"/>
+      <c r="M18" s="75"/>
+      <c r="N18" s="75"/>
+      <c r="O18" s="75"/>
+      <c r="P18" s="75"/>
+      <c r="Q18" s="75"/>
+      <c r="R18" s="75"/>
+      <c r="T18" s="20"/>
+      <c r="U18" s="20"/>
+      <c r="V18" s="20"/>
+      <c r="W18" s="20"/>
+      <c r="X18" s="20"/>
+      <c r="Y18" s="20"/>
+      <c r="Z18" s="20"/>
+      <c r="AA18" s="20"/>
+      <c r="AB18" s="20"/>
+      <c r="AC18" s="20"/>
+      <c r="AD18" s="20"/>
+      <c r="AE18" s="20"/>
+      <c r="AF18" s="20"/>
+      <c r="AG18" s="20"/>
+      <c r="AW18" s="21" t="s">
         <v>100</v>
       </c>
-      <c r="AX18" s="22"/>
-      <c r="AY18" s="20" t="s">
+      <c r="AX18" s="23"/>
+      <c r="AY18" s="21" t="s">
         <v>101</v>
       </c>
-      <c r="AZ18" s="21"/>
-      <c r="BA18" s="21"/>
-      <c r="BB18" s="22"/>
-      <c r="BC18" s="20" t="s">
+      <c r="AZ18" s="22"/>
+      <c r="BA18" s="22"/>
+      <c r="BB18" s="23"/>
+      <c r="BC18" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="BD18" s="21"/>
-      <c r="BE18" s="22"/>
-      <c r="BF18" s="20" t="s">
+      <c r="BD18" s="22"/>
+      <c r="BE18" s="23"/>
+      <c r="BF18" s="21" t="s">
         <v>103</v>
       </c>
-      <c r="BG18" s="21"/>
-      <c r="BH18" s="21"/>
-      <c r="BI18" s="21"/>
-      <c r="BJ18" s="21"/>
-      <c r="BK18" s="22"/>
+      <c r="BG18" s="22"/>
+      <c r="BH18" s="22"/>
+      <c r="BI18" s="22"/>
+      <c r="BJ18" s="22"/>
+      <c r="BK18" s="23"/>
       <c r="BL18" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="BM18" s="20" t="s">
+      <c r="BM18" s="21" t="s">
         <v>105</v>
       </c>
-      <c r="BN18" s="21"/>
-      <c r="BO18" s="22"/>
+      <c r="BN18" s="22"/>
+      <c r="BO18" s="23"/>
       <c r="BP18" s="8" t="s">
         <v>106</v>
       </c>
       <c r="BQ18" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="BR18" s="24"/>
+      <c r="BR18" s="42"/>
     </row>
     <row r="19" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B19" s="24"/>
-      <c r="E19" s="26"/>
-      <c r="F19" s="26"/>
-      <c r="G19" s="26"/>
-      <c r="H19" s="26"/>
-      <c r="I19" s="26"/>
-      <c r="J19" s="26"/>
-      <c r="K19" s="26"/>
-      <c r="L19" s="26"/>
-      <c r="M19" s="26"/>
-      <c r="N19" s="26"/>
-      <c r="O19" s="26"/>
-      <c r="P19" s="26"/>
-      <c r="Q19" s="26"/>
-      <c r="R19" s="26"/>
-      <c r="T19" s="26"/>
-      <c r="U19" s="26"/>
-      <c r="V19" s="26"/>
-      <c r="W19" s="26"/>
-      <c r="X19" s="26"/>
-      <c r="Y19" s="26"/>
-      <c r="Z19" s="26"/>
-      <c r="AA19" s="26"/>
-      <c r="AB19" s="26"/>
-      <c r="AC19" s="26"/>
-      <c r="AD19" s="26"/>
-      <c r="AE19" s="26"/>
-      <c r="AF19" s="26"/>
-      <c r="AG19" s="26"/>
-      <c r="AW19" s="20" t="s">
+      <c r="B19" s="42"/>
+      <c r="E19" s="75"/>
+      <c r="F19" s="75"/>
+      <c r="G19" s="75"/>
+      <c r="H19" s="75"/>
+      <c r="I19" s="75"/>
+      <c r="J19" s="75"/>
+      <c r="K19" s="75"/>
+      <c r="L19" s="75"/>
+      <c r="M19" s="75"/>
+      <c r="N19" s="75"/>
+      <c r="O19" s="75"/>
+      <c r="P19" s="75"/>
+      <c r="Q19" s="75"/>
+      <c r="R19" s="75"/>
+      <c r="T19" s="20"/>
+      <c r="U19" s="20"/>
+      <c r="V19" s="20"/>
+      <c r="W19" s="20"/>
+      <c r="X19" s="20"/>
+      <c r="Y19" s="20"/>
+      <c r="Z19" s="20"/>
+      <c r="AA19" s="20"/>
+      <c r="AB19" s="20"/>
+      <c r="AC19" s="20"/>
+      <c r="AD19" s="20"/>
+      <c r="AE19" s="20"/>
+      <c r="AF19" s="20"/>
+      <c r="AG19" s="20"/>
+      <c r="AW19" s="21" t="s">
         <v>108</v>
       </c>
-      <c r="AX19" s="22"/>
-      <c r="AY19" s="20" t="s">
+      <c r="AX19" s="23"/>
+      <c r="AY19" s="21" t="s">
         <v>109</v>
       </c>
-      <c r="AZ19" s="21"/>
-      <c r="BA19" s="21"/>
-      <c r="BB19" s="22"/>
-      <c r="BC19" s="20" t="s">
+      <c r="AZ19" s="22"/>
+      <c r="BA19" s="22"/>
+      <c r="BB19" s="23"/>
+      <c r="BC19" s="21" t="s">
         <v>110</v>
       </c>
-      <c r="BD19" s="21"/>
-      <c r="BE19" s="22"/>
-      <c r="BF19" s="20" t="s">
+      <c r="BD19" s="22"/>
+      <c r="BE19" s="23"/>
+      <c r="BF19" s="21" t="s">
         <v>111</v>
       </c>
-      <c r="BG19" s="21"/>
-      <c r="BH19" s="21"/>
-      <c r="BI19" s="21"/>
-      <c r="BJ19" s="21"/>
-      <c r="BK19" s="22"/>
+      <c r="BG19" s="22"/>
+      <c r="BH19" s="22"/>
+      <c r="BI19" s="22"/>
+      <c r="BJ19" s="22"/>
+      <c r="BK19" s="23"/>
       <c r="BL19" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="BM19" s="20" t="s">
+      <c r="BM19" s="21" t="s">
         <v>113</v>
       </c>
-      <c r="BN19" s="21"/>
-      <c r="BO19" s="22"/>
+      <c r="BN19" s="22"/>
+      <c r="BO19" s="23"/>
       <c r="BP19" s="8" t="s">
         <v>114</v>
       </c>
       <c r="BQ19" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="BR19" s="24"/>
+      <c r="BR19" s="42"/>
     </row>
     <row r="20" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B20" s="24"/>
-      <c r="E20" s="26"/>
-      <c r="F20" s="26"/>
-      <c r="G20" s="26"/>
-      <c r="H20" s="26"/>
-      <c r="I20" s="26"/>
-      <c r="J20" s="26"/>
-      <c r="K20" s="26"/>
-      <c r="L20" s="26"/>
-      <c r="M20" s="26"/>
-      <c r="N20" s="26"/>
-      <c r="O20" s="26"/>
-      <c r="P20" s="26"/>
-      <c r="Q20" s="26"/>
-      <c r="R20" s="26"/>
-      <c r="T20" s="26"/>
-      <c r="U20" s="26"/>
-      <c r="V20" s="26"/>
-      <c r="W20" s="26"/>
-      <c r="X20" s="26"/>
-      <c r="Y20" s="26"/>
-      <c r="Z20" s="26"/>
-      <c r="AA20" s="26"/>
-      <c r="AB20" s="26"/>
-      <c r="AC20" s="26"/>
-      <c r="AD20" s="26"/>
-      <c r="AE20" s="26"/>
-      <c r="AF20" s="26"/>
-      <c r="AG20" s="26"/>
-      <c r="AW20" s="20" t="s">
+      <c r="B20" s="42"/>
+      <c r="E20" s="75"/>
+      <c r="F20" s="75"/>
+      <c r="G20" s="75"/>
+      <c r="H20" s="75"/>
+      <c r="I20" s="75"/>
+      <c r="J20" s="75"/>
+      <c r="K20" s="75"/>
+      <c r="L20" s="75"/>
+      <c r="M20" s="75"/>
+      <c r="N20" s="75"/>
+      <c r="O20" s="75"/>
+      <c r="P20" s="75"/>
+      <c r="Q20" s="75"/>
+      <c r="R20" s="75"/>
+      <c r="T20" s="20"/>
+      <c r="U20" s="20"/>
+      <c r="V20" s="20"/>
+      <c r="W20" s="20"/>
+      <c r="X20" s="20"/>
+      <c r="Y20" s="20"/>
+      <c r="Z20" s="20"/>
+      <c r="AA20" s="20"/>
+      <c r="AB20" s="20"/>
+      <c r="AC20" s="20"/>
+      <c r="AD20" s="20"/>
+      <c r="AE20" s="20"/>
+      <c r="AF20" s="20"/>
+      <c r="AG20" s="20"/>
+      <c r="AW20" s="21" t="s">
         <v>116</v>
       </c>
-      <c r="AX20" s="22"/>
-      <c r="AY20" s="20" t="s">
+      <c r="AX20" s="23"/>
+      <c r="AY20" s="21" t="s">
         <v>117</v>
       </c>
-      <c r="AZ20" s="21"/>
-      <c r="BA20" s="21"/>
-      <c r="BB20" s="22"/>
-      <c r="BC20" s="20" t="s">
+      <c r="AZ20" s="22"/>
+      <c r="BA20" s="22"/>
+      <c r="BB20" s="23"/>
+      <c r="BC20" s="21" t="s">
         <v>118</v>
       </c>
-      <c r="BD20" s="21"/>
-      <c r="BE20" s="22"/>
-      <c r="BF20" s="20" t="s">
+      <c r="BD20" s="22"/>
+      <c r="BE20" s="23"/>
+      <c r="BF20" s="21" t="s">
         <v>119</v>
       </c>
-      <c r="BG20" s="21"/>
-      <c r="BH20" s="21"/>
-      <c r="BI20" s="21"/>
-      <c r="BJ20" s="21"/>
-      <c r="BK20" s="22"/>
+      <c r="BG20" s="22"/>
+      <c r="BH20" s="22"/>
+      <c r="BI20" s="22"/>
+      <c r="BJ20" s="22"/>
+      <c r="BK20" s="23"/>
       <c r="BL20" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="BM20" s="20" t="s">
+      <c r="BM20" s="21" t="s">
         <v>121</v>
       </c>
-      <c r="BN20" s="21"/>
-      <c r="BO20" s="22"/>
+      <c r="BN20" s="22"/>
+      <c r="BO20" s="23"/>
       <c r="BP20" s="8" t="s">
         <v>122</v>
       </c>
       <c r="BQ20" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="BR20" s="24"/>
+      <c r="BR20" s="42"/>
     </row>
     <row r="21" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B21" s="24"/>
-      <c r="E21" s="26"/>
-      <c r="F21" s="26"/>
-      <c r="G21" s="26"/>
-      <c r="H21" s="26"/>
-      <c r="I21" s="26"/>
-      <c r="J21" s="26"/>
-      <c r="K21" s="26"/>
-      <c r="L21" s="26"/>
-      <c r="M21" s="26"/>
-      <c r="N21" s="26"/>
-      <c r="O21" s="26"/>
-      <c r="P21" s="26"/>
-      <c r="Q21" s="26"/>
-      <c r="R21" s="26"/>
-      <c r="T21" s="26"/>
-      <c r="U21" s="26"/>
-      <c r="V21" s="26"/>
-      <c r="W21" s="26"/>
-      <c r="X21" s="26"/>
-      <c r="Y21" s="26"/>
-      <c r="Z21" s="26"/>
-      <c r="AA21" s="26"/>
-      <c r="AB21" s="26"/>
-      <c r="AC21" s="26"/>
-      <c r="AD21" s="26"/>
-      <c r="AE21" s="26"/>
-      <c r="AF21" s="26"/>
-      <c r="AG21" s="26"/>
-      <c r="AW21" s="20" t="s">
+      <c r="B21" s="42"/>
+      <c r="E21" s="75"/>
+      <c r="F21" s="75"/>
+      <c r="G21" s="75"/>
+      <c r="H21" s="75"/>
+      <c r="I21" s="75"/>
+      <c r="J21" s="75"/>
+      <c r="K21" s="75"/>
+      <c r="L21" s="75"/>
+      <c r="M21" s="75"/>
+      <c r="N21" s="75"/>
+      <c r="O21" s="75"/>
+      <c r="P21" s="75"/>
+      <c r="Q21" s="75"/>
+      <c r="R21" s="75"/>
+      <c r="T21" s="20"/>
+      <c r="U21" s="20"/>
+      <c r="V21" s="20"/>
+      <c r="W21" s="20"/>
+      <c r="X21" s="20"/>
+      <c r="Y21" s="20"/>
+      <c r="Z21" s="20"/>
+      <c r="AA21" s="20"/>
+      <c r="AB21" s="20"/>
+      <c r="AC21" s="20"/>
+      <c r="AD21" s="20"/>
+      <c r="AE21" s="20"/>
+      <c r="AF21" s="20"/>
+      <c r="AG21" s="20"/>
+      <c r="AW21" s="21" t="s">
         <v>124</v>
       </c>
-      <c r="AX21" s="22"/>
-      <c r="AY21" s="20" t="s">
+      <c r="AX21" s="23"/>
+      <c r="AY21" s="21" t="s">
         <v>125</v>
       </c>
-      <c r="AZ21" s="21"/>
-      <c r="BA21" s="21"/>
-      <c r="BB21" s="22"/>
-      <c r="BC21" s="20" t="s">
+      <c r="AZ21" s="22"/>
+      <c r="BA21" s="22"/>
+      <c r="BB21" s="23"/>
+      <c r="BC21" s="21" t="s">
         <v>126</v>
       </c>
-      <c r="BD21" s="21"/>
-      <c r="BE21" s="22"/>
-      <c r="BF21" s="20" t="s">
+      <c r="BD21" s="22"/>
+      <c r="BE21" s="23"/>
+      <c r="BF21" s="21" t="s">
         <v>127</v>
       </c>
-      <c r="BG21" s="21"/>
-      <c r="BH21" s="21"/>
-      <c r="BI21" s="21"/>
-      <c r="BJ21" s="21"/>
-      <c r="BK21" s="22"/>
+      <c r="BG21" s="22"/>
+      <c r="BH21" s="22"/>
+      <c r="BI21" s="22"/>
+      <c r="BJ21" s="22"/>
+      <c r="BK21" s="23"/>
       <c r="BL21" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="BM21" s="20" t="s">
+      <c r="BM21" s="21" t="s">
         <v>129</v>
       </c>
-      <c r="BN21" s="21"/>
-      <c r="BO21" s="22"/>
+      <c r="BN21" s="22"/>
+      <c r="BO21" s="23"/>
       <c r="BP21" s="8" t="s">
         <v>130</v>
       </c>
       <c r="BQ21" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="BR21" s="24"/>
+      <c r="BR21" s="42"/>
     </row>
     <row r="22" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B22" s="24"/>
-      <c r="AW22" s="20" t="s">
+      <c r="B22" s="42"/>
+      <c r="AW22" s="21" t="s">
         <v>132</v>
       </c>
-      <c r="AX22" s="22"/>
-      <c r="AY22" s="20" t="s">
+      <c r="AX22" s="23"/>
+      <c r="AY22" s="21" t="s">
         <v>133</v>
       </c>
-      <c r="AZ22" s="21"/>
-      <c r="BA22" s="21"/>
-      <c r="BB22" s="22"/>
-      <c r="BC22" s="20" t="s">
+      <c r="AZ22" s="22"/>
+      <c r="BA22" s="22"/>
+      <c r="BB22" s="23"/>
+      <c r="BC22" s="21" t="s">
         <v>134</v>
       </c>
-      <c r="BD22" s="21"/>
-      <c r="BE22" s="22"/>
-      <c r="BF22" s="20" t="s">
+      <c r="BD22" s="22"/>
+      <c r="BE22" s="23"/>
+      <c r="BF22" s="21" t="s">
         <v>135</v>
       </c>
-      <c r="BG22" s="21"/>
-      <c r="BH22" s="21"/>
-      <c r="BI22" s="21"/>
-      <c r="BJ22" s="21"/>
-      <c r="BK22" s="22"/>
+      <c r="BG22" s="22"/>
+      <c r="BH22" s="22"/>
+      <c r="BI22" s="22"/>
+      <c r="BJ22" s="22"/>
+      <c r="BK22" s="23"/>
       <c r="BL22" s="8" t="s">
         <v>136</v>
       </c>
-      <c r="BM22" s="20" t="s">
+      <c r="BM22" s="21" t="s">
         <v>137</v>
       </c>
-      <c r="BN22" s="21"/>
-      <c r="BO22" s="22"/>
+      <c r="BN22" s="22"/>
+      <c r="BO22" s="23"/>
       <c r="BP22" s="8" t="s">
         <v>138</v>
       </c>
       <c r="BQ22" s="8" t="s">
         <v>139</v>
       </c>
-      <c r="BR22" s="24"/>
+      <c r="BR22" s="42"/>
     </row>
     <row r="23" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B23" s="24"/>
+      <c r="B23" s="42"/>
       <c r="U23" s="19"/>
       <c r="V23" s="19"/>
       <c r="W23" s="19"/>
@@ -3011,47 +3014,47 @@
       <c r="AE23" s="19"/>
       <c r="AF23" s="19"/>
       <c r="AG23" s="19"/>
-      <c r="AW23" s="20" t="s">
+      <c r="AW23" s="21" t="s">
         <v>140</v>
       </c>
-      <c r="AX23" s="22"/>
-      <c r="AY23" s="20" t="s">
+      <c r="AX23" s="23"/>
+      <c r="AY23" s="21" t="s">
         <v>141</v>
       </c>
-      <c r="AZ23" s="21"/>
-      <c r="BA23" s="21"/>
-      <c r="BB23" s="22"/>
-      <c r="BC23" s="20" t="s">
+      <c r="AZ23" s="22"/>
+      <c r="BA23" s="22"/>
+      <c r="BB23" s="23"/>
+      <c r="BC23" s="21" t="s">
         <v>142</v>
       </c>
-      <c r="BD23" s="21"/>
-      <c r="BE23" s="22"/>
-      <c r="BF23" s="20" t="s">
+      <c r="BD23" s="22"/>
+      <c r="BE23" s="23"/>
+      <c r="BF23" s="21" t="s">
         <v>143</v>
       </c>
-      <c r="BG23" s="21"/>
-      <c r="BH23" s="21"/>
-      <c r="BI23" s="21"/>
-      <c r="BJ23" s="21"/>
-      <c r="BK23" s="22"/>
+      <c r="BG23" s="22"/>
+      <c r="BH23" s="22"/>
+      <c r="BI23" s="22"/>
+      <c r="BJ23" s="22"/>
+      <c r="BK23" s="23"/>
       <c r="BL23" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="BM23" s="20" t="s">
+      <c r="BM23" s="21" t="s">
         <v>145</v>
       </c>
-      <c r="BN23" s="21"/>
-      <c r="BO23" s="22"/>
+      <c r="BN23" s="22"/>
+      <c r="BO23" s="23"/>
       <c r="BP23" s="8" t="s">
         <v>146</v>
       </c>
       <c r="BQ23" s="8" t="s">
         <v>147</v>
       </c>
-      <c r="BR23" s="24"/>
+      <c r="BR23" s="42"/>
     </row>
     <row r="24" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B24" s="24"/>
+      <c r="B24" s="42"/>
       <c r="T24" s="19"/>
       <c r="U24" s="19"/>
       <c r="V24" s="19"/>
@@ -3066,47 +3069,47 @@
       <c r="AE24" s="19"/>
       <c r="AF24" s="19"/>
       <c r="AG24" s="19"/>
-      <c r="AW24" s="20" t="s">
+      <c r="AW24" s="21" t="s">
         <v>148</v>
       </c>
-      <c r="AX24" s="22"/>
-      <c r="AY24" s="20" t="s">
+      <c r="AX24" s="23"/>
+      <c r="AY24" s="21" t="s">
         <v>149</v>
       </c>
-      <c r="AZ24" s="21"/>
-      <c r="BA24" s="21"/>
-      <c r="BB24" s="22"/>
-      <c r="BC24" s="20" t="s">
+      <c r="AZ24" s="22"/>
+      <c r="BA24" s="22"/>
+      <c r="BB24" s="23"/>
+      <c r="BC24" s="21" t="s">
         <v>150</v>
       </c>
-      <c r="BD24" s="21"/>
-      <c r="BE24" s="22"/>
-      <c r="BF24" s="20" t="s">
+      <c r="BD24" s="22"/>
+      <c r="BE24" s="23"/>
+      <c r="BF24" s="21" t="s">
         <v>151</v>
       </c>
-      <c r="BG24" s="21"/>
-      <c r="BH24" s="21"/>
-      <c r="BI24" s="21"/>
-      <c r="BJ24" s="21"/>
-      <c r="BK24" s="22"/>
+      <c r="BG24" s="22"/>
+      <c r="BH24" s="22"/>
+      <c r="BI24" s="22"/>
+      <c r="BJ24" s="22"/>
+      <c r="BK24" s="23"/>
       <c r="BL24" s="8" t="s">
         <v>152</v>
       </c>
-      <c r="BM24" s="20" t="s">
+      <c r="BM24" s="21" t="s">
         <v>153</v>
       </c>
-      <c r="BN24" s="21"/>
-      <c r="BO24" s="22"/>
+      <c r="BN24" s="22"/>
+      <c r="BO24" s="23"/>
       <c r="BP24" s="8" t="s">
         <v>154</v>
       </c>
       <c r="BQ24" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="BR24" s="24"/>
+      <c r="BR24" s="42"/>
     </row>
     <row r="25" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B25" s="24"/>
+      <c r="B25" s="42"/>
       <c r="U25" s="19"/>
       <c r="V25" s="19"/>
       <c r="W25" s="19"/>
@@ -3120,47 +3123,47 @@
       <c r="AE25" s="19"/>
       <c r="AF25" s="19"/>
       <c r="AG25" s="19"/>
-      <c r="AW25" s="20" t="s">
+      <c r="AW25" s="21" t="s">
         <v>216</v>
       </c>
-      <c r="AX25" s="22"/>
-      <c r="AY25" s="72" t="s">
+      <c r="AX25" s="23"/>
+      <c r="AY25" s="38" t="s">
         <v>156</v>
       </c>
-      <c r="AZ25" s="73"/>
-      <c r="BA25" s="73"/>
-      <c r="BB25" s="74"/>
-      <c r="BC25" s="20" t="s">
+      <c r="AZ25" s="39"/>
+      <c r="BA25" s="39"/>
+      <c r="BB25" s="40"/>
+      <c r="BC25" s="21" t="s">
         <v>217</v>
       </c>
-      <c r="BD25" s="21"/>
-      <c r="BE25" s="22"/>
-      <c r="BF25" s="20" t="s">
+      <c r="BD25" s="22"/>
+      <c r="BE25" s="23"/>
+      <c r="BF25" s="21" t="s">
         <v>218</v>
       </c>
-      <c r="BG25" s="21"/>
-      <c r="BH25" s="21"/>
-      <c r="BI25" s="21"/>
-      <c r="BJ25" s="21"/>
-      <c r="BK25" s="22"/>
+      <c r="BG25" s="22"/>
+      <c r="BH25" s="22"/>
+      <c r="BI25" s="22"/>
+      <c r="BJ25" s="22"/>
+      <c r="BK25" s="23"/>
       <c r="BL25" s="8" t="s">
         <v>157</v>
       </c>
-      <c r="BM25" s="20" t="s">
+      <c r="BM25" s="21" t="s">
         <v>219</v>
       </c>
-      <c r="BN25" s="21"/>
-      <c r="BO25" s="22"/>
+      <c r="BN25" s="22"/>
+      <c r="BO25" s="23"/>
       <c r="BP25" s="8" t="s">
         <v>158</v>
       </c>
       <c r="BQ25" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="BR25" s="24"/>
+      <c r="BR25" s="42"/>
     </row>
     <row r="26" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B26" s="24"/>
+      <c r="B26" s="42"/>
       <c r="F26" s="19"/>
       <c r="G26" s="19"/>
       <c r="H26" s="19"/>
@@ -3188,402 +3191,402 @@
       <c r="AE26" s="19"/>
       <c r="AF26" s="19"/>
       <c r="AG26" s="19"/>
-      <c r="AW26" s="20" t="s">
+      <c r="AW26" s="21" t="s">
         <v>160</v>
       </c>
-      <c r="AX26" s="22"/>
-      <c r="AY26" s="20" t="s">
+      <c r="AX26" s="23"/>
+      <c r="AY26" s="21" t="s">
         <v>161</v>
       </c>
-      <c r="AZ26" s="21"/>
-      <c r="BA26" s="21"/>
-      <c r="BB26" s="22"/>
-      <c r="BC26" s="20" t="s">
+      <c r="AZ26" s="22"/>
+      <c r="BA26" s="22"/>
+      <c r="BB26" s="23"/>
+      <c r="BC26" s="21" t="s">
         <v>162</v>
       </c>
-      <c r="BD26" s="21"/>
-      <c r="BE26" s="22"/>
-      <c r="BF26" s="20" t="s">
+      <c r="BD26" s="22"/>
+      <c r="BE26" s="23"/>
+      <c r="BF26" s="21" t="s">
         <v>163</v>
       </c>
-      <c r="BG26" s="21"/>
-      <c r="BH26" s="21"/>
-      <c r="BI26" s="21"/>
-      <c r="BJ26" s="21"/>
-      <c r="BK26" s="22"/>
+      <c r="BG26" s="22"/>
+      <c r="BH26" s="22"/>
+      <c r="BI26" s="22"/>
+      <c r="BJ26" s="22"/>
+      <c r="BK26" s="23"/>
       <c r="BL26" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="BM26" s="20" t="s">
+      <c r="BM26" s="21" t="s">
         <v>165</v>
       </c>
-      <c r="BN26" s="21"/>
-      <c r="BO26" s="22"/>
+      <c r="BN26" s="22"/>
+      <c r="BO26" s="23"/>
       <c r="BP26" s="7" t="s">
         <v>166</v>
       </c>
       <c r="BQ26" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="BR26" s="24"/>
+      <c r="BR26" s="42"/>
     </row>
     <row r="27" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B27" s="24"/>
-      <c r="E27" s="26" t="s">
+      <c r="B27" s="42"/>
+      <c r="E27" s="75" t="s">
         <v>270</v>
       </c>
-      <c r="F27" s="26"/>
-      <c r="G27" s="26"/>
-      <c r="H27" s="26"/>
-      <c r="I27" s="26"/>
-      <c r="J27" s="26"/>
-      <c r="K27" s="26"/>
-      <c r="L27" s="26"/>
-      <c r="M27" s="26"/>
-      <c r="N27" s="26"/>
-      <c r="O27" s="26"/>
-      <c r="P27" s="26"/>
-      <c r="Q27" s="26"/>
-      <c r="R27" s="26"/>
-      <c r="T27" s="26" t="s">
+      <c r="F27" s="75"/>
+      <c r="G27" s="75"/>
+      <c r="H27" s="75"/>
+      <c r="I27" s="75"/>
+      <c r="J27" s="75"/>
+      <c r="K27" s="75"/>
+      <c r="L27" s="75"/>
+      <c r="M27" s="75"/>
+      <c r="N27" s="75"/>
+      <c r="O27" s="75"/>
+      <c r="P27" s="75"/>
+      <c r="Q27" s="75"/>
+      <c r="R27" s="75"/>
+      <c r="T27" s="20" t="s">
         <v>170</v>
       </c>
-      <c r="U27" s="26"/>
-      <c r="V27" s="26"/>
-      <c r="W27" s="26"/>
-      <c r="X27" s="26"/>
-      <c r="Y27" s="26"/>
-      <c r="Z27" s="26"/>
-      <c r="AA27" s="26"/>
-      <c r="AB27" s="26"/>
-      <c r="AC27" s="26"/>
-      <c r="AD27" s="26"/>
-      <c r="AE27" s="26"/>
-      <c r="AF27" s="26"/>
-      <c r="AG27" s="26"/>
-      <c r="AW27" s="20" t="s">
+      <c r="U27" s="20"/>
+      <c r="V27" s="20"/>
+      <c r="W27" s="20"/>
+      <c r="X27" s="20"/>
+      <c r="Y27" s="20"/>
+      <c r="Z27" s="20"/>
+      <c r="AA27" s="20"/>
+      <c r="AB27" s="20"/>
+      <c r="AC27" s="20"/>
+      <c r="AD27" s="20"/>
+      <c r="AE27" s="20"/>
+      <c r="AF27" s="20"/>
+      <c r="AG27" s="20"/>
+      <c r="AW27" s="21" t="s">
         <v>224</v>
       </c>
-      <c r="AX27" s="22"/>
-      <c r="AY27" s="20" t="s">
+      <c r="AX27" s="23"/>
+      <c r="AY27" s="21" t="s">
         <v>225</v>
       </c>
-      <c r="AZ27" s="21"/>
-      <c r="BA27" s="21"/>
-      <c r="BB27" s="22"/>
-      <c r="BC27" s="20" t="s">
+      <c r="AZ27" s="22"/>
+      <c r="BA27" s="22"/>
+      <c r="BB27" s="23"/>
+      <c r="BC27" s="21" t="s">
         <v>226</v>
       </c>
-      <c r="BD27" s="21"/>
-      <c r="BE27" s="22"/>
-      <c r="BF27" s="20" t="s">
+      <c r="BD27" s="22"/>
+      <c r="BE27" s="23"/>
+      <c r="BF27" s="21" t="s">
         <v>227</v>
       </c>
-      <c r="BG27" s="21"/>
-      <c r="BH27" s="21"/>
-      <c r="BI27" s="21"/>
-      <c r="BJ27" s="21"/>
-      <c r="BK27" s="22"/>
+      <c r="BG27" s="22"/>
+      <c r="BH27" s="22"/>
+      <c r="BI27" s="22"/>
+      <c r="BJ27" s="22"/>
+      <c r="BK27" s="23"/>
       <c r="BL27" s="7" t="s">
         <v>228</v>
       </c>
-      <c r="BM27" s="20" t="s">
+      <c r="BM27" s="21" t="s">
         <v>229</v>
       </c>
-      <c r="BN27" s="21"/>
-      <c r="BO27" s="22"/>
+      <c r="BN27" s="22"/>
+      <c r="BO27" s="23"/>
       <c r="BP27" s="7" t="s">
         <v>230</v>
       </c>
       <c r="BQ27" s="7" t="s">
         <v>231</v>
       </c>
-      <c r="BR27" s="24"/>
+      <c r="BR27" s="42"/>
     </row>
     <row r="28" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B28" s="24"/>
-      <c r="E28" s="26"/>
-      <c r="F28" s="26"/>
-      <c r="G28" s="26"/>
-      <c r="H28" s="26"/>
-      <c r="I28" s="26"/>
-      <c r="J28" s="26"/>
-      <c r="K28" s="26"/>
-      <c r="L28" s="26"/>
-      <c r="M28" s="26"/>
-      <c r="N28" s="26"/>
-      <c r="O28" s="26"/>
-      <c r="P28" s="26"/>
-      <c r="Q28" s="26"/>
-      <c r="R28" s="26"/>
-      <c r="T28" s="26"/>
-      <c r="U28" s="26"/>
-      <c r="V28" s="26"/>
-      <c r="W28" s="26"/>
-      <c r="X28" s="26"/>
-      <c r="Y28" s="26"/>
-      <c r="Z28" s="26"/>
-      <c r="AA28" s="26"/>
-      <c r="AB28" s="26"/>
-      <c r="AC28" s="26"/>
-      <c r="AD28" s="26"/>
-      <c r="AE28" s="26"/>
-      <c r="AF28" s="26"/>
-      <c r="AG28" s="26"/>
+      <c r="B28" s="42"/>
+      <c r="E28" s="75"/>
+      <c r="F28" s="75"/>
+      <c r="G28" s="75"/>
+      <c r="H28" s="75"/>
+      <c r="I28" s="75"/>
+      <c r="J28" s="75"/>
+      <c r="K28" s="75"/>
+      <c r="L28" s="75"/>
+      <c r="M28" s="75"/>
+      <c r="N28" s="75"/>
+      <c r="O28" s="75"/>
+      <c r="P28" s="75"/>
+      <c r="Q28" s="75"/>
+      <c r="R28" s="75"/>
+      <c r="T28" s="20"/>
+      <c r="U28" s="20"/>
+      <c r="V28" s="20"/>
+      <c r="W28" s="20"/>
+      <c r="X28" s="20"/>
+      <c r="Y28" s="20"/>
+      <c r="Z28" s="20"/>
+      <c r="AA28" s="20"/>
+      <c r="AB28" s="20"/>
+      <c r="AC28" s="20"/>
+      <c r="AD28" s="20"/>
+      <c r="AE28" s="20"/>
+      <c r="AF28" s="20"/>
+      <c r="AG28" s="20"/>
       <c r="AI28" s="3"/>
       <c r="AV28" s="6"/>
-      <c r="AW28" s="20" t="s">
+      <c r="AW28" s="21" t="s">
         <v>232</v>
       </c>
-      <c r="AX28" s="22"/>
-      <c r="AY28" s="20" t="s">
+      <c r="AX28" s="23"/>
+      <c r="AY28" s="21" t="s">
         <v>233</v>
       </c>
-      <c r="AZ28" s="21"/>
-      <c r="BA28" s="21"/>
-      <c r="BB28" s="22"/>
-      <c r="BC28" s="20" t="s">
+      <c r="AZ28" s="22"/>
+      <c r="BA28" s="22"/>
+      <c r="BB28" s="23"/>
+      <c r="BC28" s="21" t="s">
         <v>234</v>
       </c>
-      <c r="BD28" s="21"/>
-      <c r="BE28" s="22"/>
-      <c r="BF28" s="20" t="s">
+      <c r="BD28" s="22"/>
+      <c r="BE28" s="23"/>
+      <c r="BF28" s="21" t="s">
         <v>235</v>
       </c>
-      <c r="BG28" s="21"/>
-      <c r="BH28" s="21"/>
-      <c r="BI28" s="21"/>
-      <c r="BJ28" s="21"/>
-      <c r="BK28" s="22"/>
+      <c r="BG28" s="22"/>
+      <c r="BH28" s="22"/>
+      <c r="BI28" s="22"/>
+      <c r="BJ28" s="22"/>
+      <c r="BK28" s="23"/>
       <c r="BL28" s="7" t="s">
         <v>236</v>
       </c>
-      <c r="BM28" s="20" t="s">
+      <c r="BM28" s="21" t="s">
         <v>237</v>
       </c>
-      <c r="BN28" s="21"/>
-      <c r="BO28" s="22"/>
+      <c r="BN28" s="22"/>
+      <c r="BO28" s="23"/>
       <c r="BP28" s="7" t="s">
         <v>238</v>
       </c>
       <c r="BQ28" s="7" t="s">
         <v>239</v>
       </c>
-      <c r="BR28" s="24"/>
+      <c r="BR28" s="42"/>
     </row>
     <row r="29" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B29" s="25"/>
-      <c r="E29" s="26"/>
-      <c r="F29" s="26"/>
-      <c r="G29" s="26"/>
-      <c r="H29" s="26"/>
-      <c r="I29" s="26"/>
-      <c r="J29" s="26"/>
-      <c r="K29" s="26"/>
-      <c r="L29" s="26"/>
-      <c r="M29" s="26"/>
-      <c r="N29" s="26"/>
-      <c r="O29" s="26"/>
-      <c r="P29" s="26"/>
-      <c r="Q29" s="26"/>
-      <c r="R29" s="26"/>
-      <c r="T29" s="26"/>
-      <c r="U29" s="26"/>
-      <c r="V29" s="26"/>
-      <c r="W29" s="26"/>
-      <c r="X29" s="26"/>
-      <c r="Y29" s="26"/>
-      <c r="Z29" s="26"/>
-      <c r="AA29" s="26"/>
-      <c r="AB29" s="26"/>
-      <c r="AC29" s="26"/>
-      <c r="AD29" s="26"/>
-      <c r="AE29" s="26"/>
-      <c r="AF29" s="26"/>
-      <c r="AG29" s="26"/>
-      <c r="AW29" s="20" t="s">
+      <c r="B29" s="43"/>
+      <c r="E29" s="75"/>
+      <c r="F29" s="75"/>
+      <c r="G29" s="75"/>
+      <c r="H29" s="75"/>
+      <c r="I29" s="75"/>
+      <c r="J29" s="75"/>
+      <c r="K29" s="75"/>
+      <c r="L29" s="75"/>
+      <c r="M29" s="75"/>
+      <c r="N29" s="75"/>
+      <c r="O29" s="75"/>
+      <c r="P29" s="75"/>
+      <c r="Q29" s="75"/>
+      <c r="R29" s="75"/>
+      <c r="T29" s="20"/>
+      <c r="U29" s="20"/>
+      <c r="V29" s="20"/>
+      <c r="W29" s="20"/>
+      <c r="X29" s="20"/>
+      <c r="Y29" s="20"/>
+      <c r="Z29" s="20"/>
+      <c r="AA29" s="20"/>
+      <c r="AB29" s="20"/>
+      <c r="AC29" s="20"/>
+      <c r="AD29" s="20"/>
+      <c r="AE29" s="20"/>
+      <c r="AF29" s="20"/>
+      <c r="AG29" s="20"/>
+      <c r="AW29" s="21" t="s">
         <v>240</v>
       </c>
-      <c r="AX29" s="22"/>
-      <c r="AY29" s="20" t="s">
+      <c r="AX29" s="23"/>
+      <c r="AY29" s="21" t="s">
         <v>241</v>
       </c>
-      <c r="AZ29" s="21"/>
-      <c r="BA29" s="21"/>
-      <c r="BB29" s="22"/>
-      <c r="BC29" s="20" t="s">
+      <c r="AZ29" s="22"/>
+      <c r="BA29" s="22"/>
+      <c r="BB29" s="23"/>
+      <c r="BC29" s="21" t="s">
         <v>242</v>
       </c>
-      <c r="BD29" s="21"/>
-      <c r="BE29" s="22"/>
-      <c r="BF29" s="20" t="s">
+      <c r="BD29" s="22"/>
+      <c r="BE29" s="23"/>
+      <c r="BF29" s="21" t="s">
         <v>243</v>
       </c>
-      <c r="BG29" s="21"/>
-      <c r="BH29" s="21"/>
-      <c r="BI29" s="21"/>
-      <c r="BJ29" s="21"/>
-      <c r="BK29" s="22"/>
+      <c r="BG29" s="22"/>
+      <c r="BH29" s="22"/>
+      <c r="BI29" s="22"/>
+      <c r="BJ29" s="22"/>
+      <c r="BK29" s="23"/>
       <c r="BL29" s="7" t="s">
         <v>244</v>
       </c>
-      <c r="BM29" s="20" t="s">
+      <c r="BM29" s="21" t="s">
         <v>245</v>
       </c>
-      <c r="BN29" s="21"/>
-      <c r="BO29" s="22"/>
+      <c r="BN29" s="22"/>
+      <c r="BO29" s="23"/>
       <c r="BP29" s="7" t="s">
         <v>246</v>
       </c>
       <c r="BQ29" s="7" t="s">
         <v>247</v>
       </c>
-      <c r="BR29" s="25"/>
+      <c r="BR29" s="43"/>
     </row>
     <row r="30" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B30" s="23" t="s">
+      <c r="B30" s="41" t="s">
         <v>168</v>
       </c>
-      <c r="E30" s="26"/>
-      <c r="F30" s="26"/>
-      <c r="G30" s="26"/>
-      <c r="H30" s="26"/>
-      <c r="I30" s="26"/>
-      <c r="J30" s="26"/>
-      <c r="K30" s="26"/>
-      <c r="L30" s="26"/>
-      <c r="M30" s="26"/>
-      <c r="N30" s="26"/>
-      <c r="O30" s="26"/>
-      <c r="P30" s="26"/>
-      <c r="Q30" s="26"/>
-      <c r="R30" s="26"/>
-      <c r="T30" s="26"/>
-      <c r="U30" s="26"/>
-      <c r="V30" s="26"/>
-      <c r="W30" s="26"/>
-      <c r="X30" s="26"/>
-      <c r="Y30" s="26"/>
-      <c r="Z30" s="26"/>
-      <c r="AA30" s="26"/>
-      <c r="AB30" s="26"/>
-      <c r="AC30" s="26"/>
-      <c r="AD30" s="26"/>
-      <c r="AE30" s="26"/>
-      <c r="AF30" s="26"/>
-      <c r="AG30" s="26"/>
-      <c r="AW30" s="20" t="s">
+      <c r="E30" s="75"/>
+      <c r="F30" s="75"/>
+      <c r="G30" s="75"/>
+      <c r="H30" s="75"/>
+      <c r="I30" s="75"/>
+      <c r="J30" s="75"/>
+      <c r="K30" s="75"/>
+      <c r="L30" s="75"/>
+      <c r="M30" s="75"/>
+      <c r="N30" s="75"/>
+      <c r="O30" s="75"/>
+      <c r="P30" s="75"/>
+      <c r="Q30" s="75"/>
+      <c r="R30" s="75"/>
+      <c r="T30" s="20"/>
+      <c r="U30" s="20"/>
+      <c r="V30" s="20"/>
+      <c r="W30" s="20"/>
+      <c r="X30" s="20"/>
+      <c r="Y30" s="20"/>
+      <c r="Z30" s="20"/>
+      <c r="AA30" s="20"/>
+      <c r="AB30" s="20"/>
+      <c r="AC30" s="20"/>
+      <c r="AD30" s="20"/>
+      <c r="AE30" s="20"/>
+      <c r="AF30" s="20"/>
+      <c r="AG30" s="20"/>
+      <c r="AW30" s="21" t="s">
         <v>248</v>
       </c>
-      <c r="AX30" s="22"/>
-      <c r="AY30" s="20" t="s">
+      <c r="AX30" s="23"/>
+      <c r="AY30" s="21" t="s">
         <v>249</v>
       </c>
-      <c r="AZ30" s="21"/>
-      <c r="BA30" s="21"/>
-      <c r="BB30" s="22"/>
-      <c r="BC30" s="20" t="s">
+      <c r="AZ30" s="22"/>
+      <c r="BA30" s="22"/>
+      <c r="BB30" s="23"/>
+      <c r="BC30" s="21" t="s">
         <v>250</v>
       </c>
-      <c r="BD30" s="21"/>
-      <c r="BE30" s="22"/>
-      <c r="BF30" s="20" t="s">
+      <c r="BD30" s="22"/>
+      <c r="BE30" s="23"/>
+      <c r="BF30" s="21" t="s">
         <v>251</v>
       </c>
-      <c r="BG30" s="21"/>
-      <c r="BH30" s="21"/>
-      <c r="BI30" s="21"/>
-      <c r="BJ30" s="21"/>
-      <c r="BK30" s="22"/>
+      <c r="BG30" s="22"/>
+      <c r="BH30" s="22"/>
+      <c r="BI30" s="22"/>
+      <c r="BJ30" s="22"/>
+      <c r="BK30" s="23"/>
       <c r="BL30" s="7" t="s">
         <v>252</v>
       </c>
-      <c r="BM30" s="20" t="s">
+      <c r="BM30" s="21" t="s">
         <v>253</v>
       </c>
-      <c r="BN30" s="21"/>
-      <c r="BO30" s="22"/>
+      <c r="BN30" s="22"/>
+      <c r="BO30" s="23"/>
       <c r="BP30" s="7" t="s">
         <v>254</v>
       </c>
       <c r="BQ30" s="15" t="s">
         <v>255</v>
       </c>
-      <c r="BR30" s="23" t="s">
+      <c r="BR30" s="41" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="31" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B31" s="24"/>
-      <c r="E31" s="26"/>
-      <c r="F31" s="26"/>
-      <c r="G31" s="26"/>
-      <c r="H31" s="26"/>
-      <c r="I31" s="26"/>
-      <c r="J31" s="26"/>
-      <c r="K31" s="26"/>
-      <c r="L31" s="26"/>
-      <c r="M31" s="26"/>
-      <c r="N31" s="26"/>
-      <c r="O31" s="26"/>
-      <c r="P31" s="26"/>
-      <c r="Q31" s="26"/>
-      <c r="R31" s="26"/>
-      <c r="T31" s="26"/>
-      <c r="U31" s="26"/>
-      <c r="V31" s="26"/>
-      <c r="W31" s="26"/>
-      <c r="X31" s="26"/>
-      <c r="Y31" s="26"/>
-      <c r="Z31" s="26"/>
-      <c r="AA31" s="26"/>
-      <c r="AB31" s="26"/>
-      <c r="AC31" s="26"/>
-      <c r="AD31" s="26"/>
-      <c r="AE31" s="26"/>
-      <c r="AF31" s="26"/>
-      <c r="AG31" s="26"/>
-      <c r="AW31" s="20" t="s">
+      <c r="B31" s="42"/>
+      <c r="E31" s="75"/>
+      <c r="F31" s="75"/>
+      <c r="G31" s="75"/>
+      <c r="H31" s="75"/>
+      <c r="I31" s="75"/>
+      <c r="J31" s="75"/>
+      <c r="K31" s="75"/>
+      <c r="L31" s="75"/>
+      <c r="M31" s="75"/>
+      <c r="N31" s="75"/>
+      <c r="O31" s="75"/>
+      <c r="P31" s="75"/>
+      <c r="Q31" s="75"/>
+      <c r="R31" s="75"/>
+      <c r="T31" s="20"/>
+      <c r="U31" s="20"/>
+      <c r="V31" s="20"/>
+      <c r="W31" s="20"/>
+      <c r="X31" s="20"/>
+      <c r="Y31" s="20"/>
+      <c r="Z31" s="20"/>
+      <c r="AA31" s="20"/>
+      <c r="AB31" s="20"/>
+      <c r="AC31" s="20"/>
+      <c r="AD31" s="20"/>
+      <c r="AE31" s="20"/>
+      <c r="AF31" s="20"/>
+      <c r="AG31" s="20"/>
+      <c r="AW31" s="21" t="s">
         <v>256</v>
       </c>
-      <c r="AX31" s="22"/>
-      <c r="AY31" s="20" t="s">
+      <c r="AX31" s="23"/>
+      <c r="AY31" s="21" t="s">
         <v>257</v>
       </c>
-      <c r="AZ31" s="21"/>
-      <c r="BA31" s="21"/>
-      <c r="BB31" s="22"/>
-      <c r="BC31" s="20" t="s">
+      <c r="AZ31" s="22"/>
+      <c r="BA31" s="22"/>
+      <c r="BB31" s="23"/>
+      <c r="BC31" s="21" t="s">
         <v>258</v>
       </c>
-      <c r="BD31" s="21"/>
-      <c r="BE31" s="22"/>
-      <c r="BF31" s="20" t="s">
+      <c r="BD31" s="22"/>
+      <c r="BE31" s="23"/>
+      <c r="BF31" s="21" t="s">
         <v>259</v>
       </c>
-      <c r="BG31" s="21"/>
-      <c r="BH31" s="21"/>
-      <c r="BI31" s="21"/>
-      <c r="BJ31" s="21"/>
-      <c r="BK31" s="22"/>
+      <c r="BG31" s="22"/>
+      <c r="BH31" s="22"/>
+      <c r="BI31" s="22"/>
+      <c r="BJ31" s="22"/>
+      <c r="BK31" s="23"/>
       <c r="BL31" s="7" t="s">
         <v>260</v>
       </c>
-      <c r="BM31" s="20" t="s">
+      <c r="BM31" s="21" t="s">
         <v>261</v>
       </c>
-      <c r="BN31" s="21"/>
-      <c r="BO31" s="22"/>
+      <c r="BN31" s="22"/>
+      <c r="BO31" s="23"/>
       <c r="BP31" s="7" t="s">
         <v>262</v>
       </c>
       <c r="BQ31" s="15" t="s">
         <v>263</v>
       </c>
-      <c r="BR31" s="24"/>
+      <c r="BR31" s="42"/>
     </row>
     <row r="32" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B32" s="24"/>
+      <c r="B32" s="42"/>
       <c r="E32" s="3"/>
       <c r="T32" s="19"/>
       <c r="U32" s="19"/>
@@ -3620,10 +3623,10 @@
       <c r="BO32" s="9"/>
       <c r="BP32" s="9"/>
       <c r="BQ32" s="9"/>
-      <c r="BR32" s="24"/>
+      <c r="BR32" s="42"/>
     </row>
     <row r="33" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B33" s="24"/>
+      <c r="B33" s="42"/>
       <c r="T33" s="19"/>
       <c r="U33" s="19"/>
       <c r="V33" s="19"/>
@@ -3638,35 +3641,35 @@
       <c r="AE33" s="19"/>
       <c r="AF33" s="19"/>
       <c r="AG33" s="19"/>
-      <c r="AW33" s="42" t="s">
+      <c r="AW33" s="74" t="s">
         <v>264</v>
       </c>
-      <c r="AX33" s="43"/>
-      <c r="AY33" s="43" t="s">
+      <c r="AX33" s="54"/>
+      <c r="AY33" s="54" t="s">
         <v>169</v>
       </c>
-      <c r="AZ33" s="43"/>
-      <c r="BA33" s="43"/>
-      <c r="BB33" s="43"/>
-      <c r="BC33" s="43"/>
-      <c r="BD33" s="43"/>
-      <c r="BE33" s="43"/>
-      <c r="BF33" s="43"/>
-      <c r="BG33" s="43"/>
-      <c r="BH33" s="43"/>
-      <c r="BI33" s="43"/>
-      <c r="BJ33" s="43"/>
-      <c r="BK33" s="43"/>
-      <c r="BL33" s="43"/>
-      <c r="BM33" s="43"/>
-      <c r="BN33" s="43"/>
-      <c r="BO33" s="43"/>
-      <c r="BP33" s="43"/>
-      <c r="BQ33" s="48"/>
-      <c r="BR33" s="24"/>
+      <c r="AZ33" s="54"/>
+      <c r="BA33" s="54"/>
+      <c r="BB33" s="54"/>
+      <c r="BC33" s="54"/>
+      <c r="BD33" s="54"/>
+      <c r="BE33" s="54"/>
+      <c r="BF33" s="54"/>
+      <c r="BG33" s="54"/>
+      <c r="BH33" s="54"/>
+      <c r="BI33" s="54"/>
+      <c r="BJ33" s="54"/>
+      <c r="BK33" s="54"/>
+      <c r="BL33" s="54"/>
+      <c r="BM33" s="54"/>
+      <c r="BN33" s="54"/>
+      <c r="BO33" s="54"/>
+      <c r="BP33" s="54"/>
+      <c r="BQ33" s="55"/>
+      <c r="BR33" s="42"/>
     </row>
     <row r="34" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B34" s="24"/>
+      <c r="B34" s="42"/>
       <c r="U34" s="19"/>
       <c r="V34" s="19"/>
       <c r="W34" s="19"/>
@@ -3680,31 +3683,31 @@
       <c r="AE34" s="19"/>
       <c r="AF34" s="19"/>
       <c r="AG34" s="19"/>
-      <c r="AW34" s="44"/>
-      <c r="AX34" s="45"/>
-      <c r="AY34" s="45"/>
-      <c r="AZ34" s="45"/>
-      <c r="BA34" s="45"/>
-      <c r="BB34" s="45"/>
-      <c r="BC34" s="45"/>
-      <c r="BD34" s="45"/>
-      <c r="BE34" s="45"/>
-      <c r="BF34" s="45"/>
-      <c r="BG34" s="45"/>
-      <c r="BH34" s="45"/>
-      <c r="BI34" s="45"/>
-      <c r="BJ34" s="45"/>
-      <c r="BK34" s="45"/>
-      <c r="BL34" s="45"/>
-      <c r="BM34" s="45"/>
-      <c r="BN34" s="45"/>
-      <c r="BO34" s="45"/>
-      <c r="BP34" s="45"/>
-      <c r="BQ34" s="49"/>
-      <c r="BR34" s="24"/>
+      <c r="AW34" s="24"/>
+      <c r="AX34" s="25"/>
+      <c r="AY34" s="25"/>
+      <c r="AZ34" s="25"/>
+      <c r="BA34" s="25"/>
+      <c r="BB34" s="25"/>
+      <c r="BC34" s="25"/>
+      <c r="BD34" s="25"/>
+      <c r="BE34" s="25"/>
+      <c r="BF34" s="25"/>
+      <c r="BG34" s="25"/>
+      <c r="BH34" s="25"/>
+      <c r="BI34" s="25"/>
+      <c r="BJ34" s="25"/>
+      <c r="BK34" s="25"/>
+      <c r="BL34" s="25"/>
+      <c r="BM34" s="25"/>
+      <c r="BN34" s="25"/>
+      <c r="BO34" s="25"/>
+      <c r="BP34" s="25"/>
+      <c r="BQ34" s="26"/>
+      <c r="BR34" s="42"/>
     </row>
     <row r="35" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B35" s="24"/>
+      <c r="B35" s="42"/>
       <c r="F35" s="19"/>
       <c r="G35" s="19"/>
       <c r="H35" s="19"/>
@@ -3732,31 +3735,31 @@
       <c r="AE35" s="19"/>
       <c r="AF35" s="19"/>
       <c r="AG35" s="19"/>
-      <c r="AW35" s="44"/>
-      <c r="AX35" s="45"/>
-      <c r="AY35" s="45"/>
-      <c r="AZ35" s="45"/>
-      <c r="BA35" s="45"/>
-      <c r="BB35" s="45"/>
-      <c r="BC35" s="45"/>
-      <c r="BD35" s="45"/>
-      <c r="BE35" s="45"/>
-      <c r="BF35" s="45"/>
-      <c r="BG35" s="45"/>
-      <c r="BH35" s="45"/>
-      <c r="BI35" s="45"/>
-      <c r="BJ35" s="45"/>
-      <c r="BK35" s="45"/>
-      <c r="BL35" s="45"/>
-      <c r="BM35" s="45"/>
-      <c r="BN35" s="45"/>
-      <c r="BO35" s="45"/>
-      <c r="BP35" s="45"/>
-      <c r="BQ35" s="49"/>
-      <c r="BR35" s="24"/>
+      <c r="AW35" s="24"/>
+      <c r="AX35" s="25"/>
+      <c r="AY35" s="25"/>
+      <c r="AZ35" s="25"/>
+      <c r="BA35" s="25"/>
+      <c r="BB35" s="25"/>
+      <c r="BC35" s="25"/>
+      <c r="BD35" s="25"/>
+      <c r="BE35" s="25"/>
+      <c r="BF35" s="25"/>
+      <c r="BG35" s="25"/>
+      <c r="BH35" s="25"/>
+      <c r="BI35" s="25"/>
+      <c r="BJ35" s="25"/>
+      <c r="BK35" s="25"/>
+      <c r="BL35" s="25"/>
+      <c r="BM35" s="25"/>
+      <c r="BN35" s="25"/>
+      <c r="BO35" s="25"/>
+      <c r="BP35" s="25"/>
+      <c r="BQ35" s="26"/>
+      <c r="BR35" s="42"/>
     </row>
     <row r="36" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B36" s="24"/>
+      <c r="B36" s="42"/>
       <c r="E36" s="19"/>
       <c r="F36" s="19"/>
       <c r="G36" s="19"/>
@@ -3785,169 +3788,169 @@
       <c r="AE36" s="19"/>
       <c r="AF36" s="19"/>
       <c r="AG36" s="19"/>
-      <c r="AW36" s="44"/>
-      <c r="AX36" s="45"/>
-      <c r="AY36" s="45"/>
-      <c r="AZ36" s="45"/>
-      <c r="BA36" s="45"/>
-      <c r="BB36" s="45"/>
-      <c r="BC36" s="45"/>
-      <c r="BD36" s="45"/>
-      <c r="BE36" s="45"/>
-      <c r="BF36" s="45"/>
-      <c r="BG36" s="45"/>
-      <c r="BH36" s="45"/>
-      <c r="BI36" s="45"/>
-      <c r="BJ36" s="45"/>
-      <c r="BK36" s="45"/>
-      <c r="BL36" s="45"/>
-      <c r="BM36" s="45"/>
-      <c r="BN36" s="45"/>
-      <c r="BO36" s="45"/>
-      <c r="BP36" s="45"/>
-      <c r="BQ36" s="49"/>
-      <c r="BR36" s="24"/>
+      <c r="AW36" s="24"/>
+      <c r="AX36" s="25"/>
+      <c r="AY36" s="25"/>
+      <c r="AZ36" s="25"/>
+      <c r="BA36" s="25"/>
+      <c r="BB36" s="25"/>
+      <c r="BC36" s="25"/>
+      <c r="BD36" s="25"/>
+      <c r="BE36" s="25"/>
+      <c r="BF36" s="25"/>
+      <c r="BG36" s="25"/>
+      <c r="BH36" s="25"/>
+      <c r="BI36" s="25"/>
+      <c r="BJ36" s="25"/>
+      <c r="BK36" s="25"/>
+      <c r="BL36" s="25"/>
+      <c r="BM36" s="25"/>
+      <c r="BN36" s="25"/>
+      <c r="BO36" s="25"/>
+      <c r="BP36" s="25"/>
+      <c r="BQ36" s="26"/>
+      <c r="BR36" s="42"/>
     </row>
     <row r="37" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B37" s="24"/>
-      <c r="E37" s="26" t="s">
+      <c r="B37" s="42"/>
+      <c r="E37" s="75" t="s">
         <v>271</v>
       </c>
-      <c r="F37" s="26"/>
-      <c r="G37" s="26"/>
-      <c r="H37" s="26"/>
-      <c r="I37" s="26"/>
-      <c r="J37" s="26"/>
-      <c r="K37" s="26"/>
-      <c r="L37" s="26"/>
-      <c r="M37" s="26"/>
-      <c r="N37" s="26"/>
-      <c r="O37" s="26"/>
-      <c r="P37" s="26"/>
-      <c r="Q37" s="26"/>
-      <c r="R37" s="26"/>
-      <c r="T37" s="26" t="s">
+      <c r="F37" s="75"/>
+      <c r="G37" s="75"/>
+      <c r="H37" s="75"/>
+      <c r="I37" s="75"/>
+      <c r="J37" s="75"/>
+      <c r="K37" s="75"/>
+      <c r="L37" s="75"/>
+      <c r="M37" s="75"/>
+      <c r="N37" s="75"/>
+      <c r="O37" s="75"/>
+      <c r="P37" s="75"/>
+      <c r="Q37" s="75"/>
+      <c r="R37" s="75"/>
+      <c r="T37" s="20" t="s">
         <v>171</v>
       </c>
-      <c r="U37" s="26"/>
-      <c r="V37" s="26"/>
-      <c r="W37" s="26"/>
-      <c r="X37" s="26"/>
-      <c r="Y37" s="26"/>
-      <c r="Z37" s="26"/>
-      <c r="AA37" s="26"/>
-      <c r="AB37" s="26"/>
-      <c r="AC37" s="26"/>
-      <c r="AD37" s="26"/>
-      <c r="AE37" s="26"/>
-      <c r="AF37" s="26"/>
-      <c r="AG37" s="26"/>
-      <c r="AW37" s="44"/>
-      <c r="AX37" s="45"/>
-      <c r="AY37" s="45"/>
-      <c r="AZ37" s="45"/>
-      <c r="BA37" s="45"/>
-      <c r="BB37" s="45"/>
-      <c r="BC37" s="45"/>
-      <c r="BD37" s="45"/>
-      <c r="BE37" s="45"/>
-      <c r="BF37" s="45"/>
-      <c r="BG37" s="45"/>
-      <c r="BH37" s="45"/>
-      <c r="BI37" s="45"/>
-      <c r="BJ37" s="45"/>
-      <c r="BK37" s="45"/>
-      <c r="BL37" s="45"/>
-      <c r="BM37" s="45"/>
-      <c r="BN37" s="45"/>
-      <c r="BO37" s="45"/>
-      <c r="BP37" s="45"/>
-      <c r="BQ37" s="49"/>
-      <c r="BR37" s="24"/>
+      <c r="U37" s="20"/>
+      <c r="V37" s="20"/>
+      <c r="W37" s="20"/>
+      <c r="X37" s="20"/>
+      <c r="Y37" s="20"/>
+      <c r="Z37" s="20"/>
+      <c r="AA37" s="20"/>
+      <c r="AB37" s="20"/>
+      <c r="AC37" s="20"/>
+      <c r="AD37" s="20"/>
+      <c r="AE37" s="20"/>
+      <c r="AF37" s="20"/>
+      <c r="AG37" s="20"/>
+      <c r="AW37" s="24"/>
+      <c r="AX37" s="25"/>
+      <c r="AY37" s="25"/>
+      <c r="AZ37" s="25"/>
+      <c r="BA37" s="25"/>
+      <c r="BB37" s="25"/>
+      <c r="BC37" s="25"/>
+      <c r="BD37" s="25"/>
+      <c r="BE37" s="25"/>
+      <c r="BF37" s="25"/>
+      <c r="BG37" s="25"/>
+      <c r="BH37" s="25"/>
+      <c r="BI37" s="25"/>
+      <c r="BJ37" s="25"/>
+      <c r="BK37" s="25"/>
+      <c r="BL37" s="25"/>
+      <c r="BM37" s="25"/>
+      <c r="BN37" s="25"/>
+      <c r="BO37" s="25"/>
+      <c r="BP37" s="25"/>
+      <c r="BQ37" s="26"/>
+      <c r="BR37" s="42"/>
     </row>
     <row r="38" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B38" s="24"/>
-      <c r="E38" s="26"/>
-      <c r="F38" s="26"/>
-      <c r="G38" s="26"/>
-      <c r="H38" s="26"/>
-      <c r="I38" s="26"/>
-      <c r="J38" s="26"/>
-      <c r="K38" s="26"/>
-      <c r="L38" s="26"/>
-      <c r="M38" s="26"/>
-      <c r="N38" s="26"/>
-      <c r="O38" s="26"/>
-      <c r="P38" s="26"/>
-      <c r="Q38" s="26"/>
-      <c r="R38" s="26"/>
-      <c r="T38" s="26"/>
-      <c r="U38" s="26"/>
-      <c r="V38" s="26"/>
-      <c r="W38" s="26"/>
-      <c r="X38" s="26"/>
-      <c r="Y38" s="26"/>
-      <c r="Z38" s="26"/>
-      <c r="AA38" s="26"/>
-      <c r="AB38" s="26"/>
-      <c r="AC38" s="26"/>
-      <c r="AD38" s="26"/>
-      <c r="AE38" s="26"/>
-      <c r="AF38" s="26"/>
-      <c r="AG38" s="26"/>
-      <c r="AW38" s="46"/>
-      <c r="AX38" s="47"/>
-      <c r="AY38" s="47"/>
-      <c r="AZ38" s="47"/>
-      <c r="BA38" s="47"/>
-      <c r="BB38" s="47"/>
-      <c r="BC38" s="47"/>
-      <c r="BD38" s="47"/>
-      <c r="BE38" s="47"/>
-      <c r="BF38" s="47"/>
-      <c r="BG38" s="47"/>
-      <c r="BH38" s="47"/>
-      <c r="BI38" s="47"/>
-      <c r="BJ38" s="47"/>
-      <c r="BK38" s="47"/>
-      <c r="BL38" s="47"/>
-      <c r="BM38" s="47"/>
-      <c r="BN38" s="47"/>
-      <c r="BO38" s="47"/>
-      <c r="BP38" s="47"/>
-      <c r="BQ38" s="50"/>
-      <c r="BR38" s="24"/>
+      <c r="B38" s="42"/>
+      <c r="E38" s="75"/>
+      <c r="F38" s="75"/>
+      <c r="G38" s="75"/>
+      <c r="H38" s="75"/>
+      <c r="I38" s="75"/>
+      <c r="J38" s="75"/>
+      <c r="K38" s="75"/>
+      <c r="L38" s="75"/>
+      <c r="M38" s="75"/>
+      <c r="N38" s="75"/>
+      <c r="O38" s="75"/>
+      <c r="P38" s="75"/>
+      <c r="Q38" s="75"/>
+      <c r="R38" s="75"/>
+      <c r="T38" s="20"/>
+      <c r="U38" s="20"/>
+      <c r="V38" s="20"/>
+      <c r="W38" s="20"/>
+      <c r="X38" s="20"/>
+      <c r="Y38" s="20"/>
+      <c r="Z38" s="20"/>
+      <c r="AA38" s="20"/>
+      <c r="AB38" s="20"/>
+      <c r="AC38" s="20"/>
+      <c r="AD38" s="20"/>
+      <c r="AE38" s="20"/>
+      <c r="AF38" s="20"/>
+      <c r="AG38" s="20"/>
+      <c r="AW38" s="27"/>
+      <c r="AX38" s="28"/>
+      <c r="AY38" s="28"/>
+      <c r="AZ38" s="28"/>
+      <c r="BA38" s="28"/>
+      <c r="BB38" s="28"/>
+      <c r="BC38" s="28"/>
+      <c r="BD38" s="28"/>
+      <c r="BE38" s="28"/>
+      <c r="BF38" s="28"/>
+      <c r="BG38" s="28"/>
+      <c r="BH38" s="28"/>
+      <c r="BI38" s="28"/>
+      <c r="BJ38" s="28"/>
+      <c r="BK38" s="28"/>
+      <c r="BL38" s="28"/>
+      <c r="BM38" s="28"/>
+      <c r="BN38" s="28"/>
+      <c r="BO38" s="28"/>
+      <c r="BP38" s="28"/>
+      <c r="BQ38" s="29"/>
+      <c r="BR38" s="42"/>
     </row>
     <row r="39" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B39" s="24"/>
-      <c r="E39" s="26"/>
-      <c r="F39" s="26"/>
-      <c r="G39" s="26"/>
-      <c r="H39" s="26"/>
-      <c r="I39" s="26"/>
-      <c r="J39" s="26"/>
-      <c r="K39" s="26"/>
-      <c r="L39" s="26"/>
-      <c r="M39" s="26"/>
-      <c r="N39" s="26"/>
-      <c r="O39" s="26"/>
-      <c r="P39" s="26"/>
-      <c r="Q39" s="26"/>
-      <c r="R39" s="26"/>
-      <c r="T39" s="26"/>
-      <c r="U39" s="26"/>
-      <c r="V39" s="26"/>
-      <c r="W39" s="26"/>
-      <c r="X39" s="26"/>
-      <c r="Y39" s="26"/>
-      <c r="Z39" s="26"/>
-      <c r="AA39" s="26"/>
-      <c r="AB39" s="26"/>
-      <c r="AC39" s="26"/>
-      <c r="AD39" s="26"/>
-      <c r="AE39" s="26"/>
-      <c r="AF39" s="26"/>
-      <c r="AG39" s="26"/>
+      <c r="B39" s="42"/>
+      <c r="E39" s="75"/>
+      <c r="F39" s="75"/>
+      <c r="G39" s="75"/>
+      <c r="H39" s="75"/>
+      <c r="I39" s="75"/>
+      <c r="J39" s="75"/>
+      <c r="K39" s="75"/>
+      <c r="L39" s="75"/>
+      <c r="M39" s="75"/>
+      <c r="N39" s="75"/>
+      <c r="O39" s="75"/>
+      <c r="P39" s="75"/>
+      <c r="Q39" s="75"/>
+      <c r="R39" s="75"/>
+      <c r="T39" s="20"/>
+      <c r="U39" s="20"/>
+      <c r="V39" s="20"/>
+      <c r="W39" s="20"/>
+      <c r="X39" s="20"/>
+      <c r="Y39" s="20"/>
+      <c r="Z39" s="20"/>
+      <c r="AA39" s="20"/>
+      <c r="AB39" s="20"/>
+      <c r="AC39" s="20"/>
+      <c r="AD39" s="20"/>
+      <c r="AE39" s="20"/>
+      <c r="AF39" s="20"/>
+      <c r="AG39" s="20"/>
       <c r="AW39" s="14"/>
       <c r="AX39" s="9"/>
       <c r="AY39" s="9"/>
@@ -3969,121 +3972,121 @@
       <c r="BO39" s="9"/>
       <c r="BP39" s="9"/>
       <c r="BQ39" s="9"/>
-      <c r="BR39" s="24"/>
+      <c r="BR39" s="42"/>
     </row>
     <row r="40" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B40" s="24"/>
-      <c r="E40" s="26"/>
-      <c r="F40" s="26"/>
-      <c r="G40" s="26"/>
-      <c r="H40" s="26"/>
-      <c r="I40" s="26"/>
-      <c r="J40" s="26"/>
-      <c r="K40" s="26"/>
-      <c r="L40" s="26"/>
-      <c r="M40" s="26"/>
-      <c r="N40" s="26"/>
-      <c r="O40" s="26"/>
-      <c r="P40" s="26"/>
-      <c r="Q40" s="26"/>
-      <c r="R40" s="26"/>
-      <c r="T40" s="26"/>
-      <c r="U40" s="26"/>
-      <c r="V40" s="26"/>
-      <c r="W40" s="26"/>
-      <c r="X40" s="26"/>
-      <c r="Y40" s="26"/>
-      <c r="Z40" s="26"/>
-      <c r="AA40" s="26"/>
-      <c r="AB40" s="26"/>
-      <c r="AC40" s="26"/>
-      <c r="AD40" s="26"/>
-      <c r="AE40" s="26"/>
-      <c r="AF40" s="26"/>
-      <c r="AG40" s="26"/>
+      <c r="B40" s="42"/>
+      <c r="E40" s="75"/>
+      <c r="F40" s="75"/>
+      <c r="G40" s="75"/>
+      <c r="H40" s="75"/>
+      <c r="I40" s="75"/>
+      <c r="J40" s="75"/>
+      <c r="K40" s="75"/>
+      <c r="L40" s="75"/>
+      <c r="M40" s="75"/>
+      <c r="N40" s="75"/>
+      <c r="O40" s="75"/>
+      <c r="P40" s="75"/>
+      <c r="Q40" s="75"/>
+      <c r="R40" s="75"/>
+      <c r="T40" s="20"/>
+      <c r="U40" s="20"/>
+      <c r="V40" s="20"/>
+      <c r="W40" s="20"/>
+      <c r="X40" s="20"/>
+      <c r="Y40" s="20"/>
+      <c r="Z40" s="20"/>
+      <c r="AA40" s="20"/>
+      <c r="AB40" s="20"/>
+      <c r="AC40" s="20"/>
+      <c r="AD40" s="20"/>
+      <c r="AE40" s="20"/>
+      <c r="AF40" s="20"/>
+      <c r="AG40" s="20"/>
       <c r="AW40" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="AX40" s="20" t="s">
+      <c r="AX40" s="21" t="s">
         <v>173</v>
       </c>
-      <c r="AY40" s="21"/>
-      <c r="AZ40" s="22"/>
-      <c r="BA40" s="20" t="s">
+      <c r="AY40" s="22"/>
+      <c r="AZ40" s="23"/>
+      <c r="BA40" s="21" t="s">
         <v>174</v>
       </c>
-      <c r="BB40" s="21"/>
-      <c r="BC40" s="21"/>
-      <c r="BD40" s="21"/>
-      <c r="BE40" s="21"/>
-      <c r="BF40" s="21"/>
-      <c r="BG40" s="21"/>
-      <c r="BH40" s="22"/>
-      <c r="BI40" s="20" t="s">
+      <c r="BB40" s="22"/>
+      <c r="BC40" s="22"/>
+      <c r="BD40" s="22"/>
+      <c r="BE40" s="22"/>
+      <c r="BF40" s="22"/>
+      <c r="BG40" s="22"/>
+      <c r="BH40" s="23"/>
+      <c r="BI40" s="21" t="s">
         <v>175</v>
       </c>
-      <c r="BJ40" s="21"/>
-      <c r="BK40" s="22"/>
-      <c r="BL40" s="20" t="s">
+      <c r="BJ40" s="22"/>
+      <c r="BK40" s="23"/>
+      <c r="BL40" s="21" t="s">
         <v>176</v>
       </c>
-      <c r="BM40" s="21"/>
-      <c r="BN40" s="22"/>
-      <c r="BO40" s="20" t="s">
+      <c r="BM40" s="22"/>
+      <c r="BN40" s="23"/>
+      <c r="BO40" s="21" t="s">
         <v>177</v>
       </c>
-      <c r="BP40" s="21"/>
-      <c r="BQ40" s="22"/>
-      <c r="BR40" s="24"/>
+      <c r="BP40" s="22"/>
+      <c r="BQ40" s="23"/>
+      <c r="BR40" s="42"/>
     </row>
     <row r="41" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B41" s="24"/>
-      <c r="E41" s="26"/>
-      <c r="F41" s="26"/>
-      <c r="G41" s="26"/>
-      <c r="H41" s="26"/>
-      <c r="I41" s="26"/>
-      <c r="J41" s="26"/>
-      <c r="K41" s="26"/>
-      <c r="L41" s="26"/>
-      <c r="M41" s="26"/>
-      <c r="N41" s="26"/>
-      <c r="O41" s="26"/>
-      <c r="P41" s="26"/>
-      <c r="Q41" s="26"/>
-      <c r="R41" s="26"/>
-      <c r="T41" s="26"/>
-      <c r="U41" s="26"/>
-      <c r="V41" s="26"/>
-      <c r="W41" s="26"/>
-      <c r="X41" s="26"/>
-      <c r="Y41" s="26"/>
-      <c r="Z41" s="26"/>
-      <c r="AA41" s="26"/>
-      <c r="AB41" s="26"/>
-      <c r="AC41" s="26"/>
-      <c r="AD41" s="26"/>
-      <c r="AE41" s="26"/>
-      <c r="AF41" s="26"/>
-      <c r="AG41" s="26"/>
+      <c r="B41" s="42"/>
+      <c r="E41" s="75"/>
+      <c r="F41" s="75"/>
+      <c r="G41" s="75"/>
+      <c r="H41" s="75"/>
+      <c r="I41" s="75"/>
+      <c r="J41" s="75"/>
+      <c r="K41" s="75"/>
+      <c r="L41" s="75"/>
+      <c r="M41" s="75"/>
+      <c r="N41" s="75"/>
+      <c r="O41" s="75"/>
+      <c r="P41" s="75"/>
+      <c r="Q41" s="75"/>
+      <c r="R41" s="75"/>
+      <c r="T41" s="20"/>
+      <c r="U41" s="20"/>
+      <c r="V41" s="20"/>
+      <c r="W41" s="20"/>
+      <c r="X41" s="20"/>
+      <c r="Y41" s="20"/>
+      <c r="Z41" s="20"/>
+      <c r="AA41" s="20"/>
+      <c r="AB41" s="20"/>
+      <c r="AC41" s="20"/>
+      <c r="AD41" s="20"/>
+      <c r="AE41" s="20"/>
+      <c r="AF41" s="20"/>
+      <c r="AG41" s="20"/>
       <c r="AW41" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="AX41" s="20" t="s">
+      <c r="AX41" s="21" t="s">
         <v>179</v>
       </c>
-      <c r="AY41" s="21"/>
-      <c r="AZ41" s="22"/>
-      <c r="BA41" s="20" t="s">
+      <c r="AY41" s="22"/>
+      <c r="AZ41" s="23"/>
+      <c r="BA41" s="21" t="s">
         <v>180</v>
       </c>
-      <c r="BB41" s="21"/>
-      <c r="BC41" s="21"/>
-      <c r="BD41" s="21"/>
-      <c r="BE41" s="21"/>
-      <c r="BF41" s="21"/>
-      <c r="BG41" s="21"/>
-      <c r="BH41" s="22"/>
+      <c r="BB41" s="22"/>
+      <c r="BC41" s="22"/>
+      <c r="BD41" s="22"/>
+      <c r="BE41" s="22"/>
+      <c r="BF41" s="22"/>
+      <c r="BG41" s="22"/>
+      <c r="BH41" s="23"/>
       <c r="BI41" s="16" t="s">
         <v>181</v>
       </c>
@@ -4099,10 +4102,10 @@
       </c>
       <c r="BP41" s="17"/>
       <c r="BQ41" s="17"/>
-      <c r="BR41" s="24"/>
+      <c r="BR41" s="42"/>
     </row>
     <row r="42" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B42" s="24"/>
+      <c r="B42" s="42"/>
       <c r="U42" s="19"/>
       <c r="V42" s="19"/>
       <c r="W42" s="19"/>
@@ -4119,40 +4122,40 @@
       <c r="AW42" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="AX42" s="20" t="s">
+      <c r="AX42" s="21" t="s">
         <v>185</v>
       </c>
-      <c r="AY42" s="21"/>
-      <c r="AZ42" s="22"/>
-      <c r="BA42" s="20" t="s">
+      <c r="AY42" s="22"/>
+      <c r="AZ42" s="23"/>
+      <c r="BA42" s="21" t="s">
         <v>186</v>
       </c>
-      <c r="BB42" s="21"/>
-      <c r="BC42" s="21"/>
-      <c r="BD42" s="21"/>
-      <c r="BE42" s="21"/>
-      <c r="BF42" s="21"/>
-      <c r="BG42" s="21"/>
-      <c r="BH42" s="22"/>
-      <c r="BI42" s="20" t="s">
+      <c r="BB42" s="22"/>
+      <c r="BC42" s="22"/>
+      <c r="BD42" s="22"/>
+      <c r="BE42" s="22"/>
+      <c r="BF42" s="22"/>
+      <c r="BG42" s="22"/>
+      <c r="BH42" s="23"/>
+      <c r="BI42" s="21" t="s">
         <v>187</v>
       </c>
-      <c r="BJ42" s="21"/>
-      <c r="BK42" s="22"/>
-      <c r="BL42" s="20" t="s">
+      <c r="BJ42" s="22"/>
+      <c r="BK42" s="23"/>
+      <c r="BL42" s="21" t="s">
         <v>188</v>
       </c>
-      <c r="BM42" s="21"/>
-      <c r="BN42" s="22"/>
-      <c r="BO42" s="20" t="s">
+      <c r="BM42" s="22"/>
+      <c r="BN42" s="23"/>
+      <c r="BO42" s="21" t="s">
         <v>189</v>
       </c>
-      <c r="BP42" s="21"/>
-      <c r="BQ42" s="22"/>
-      <c r="BR42" s="24"/>
+      <c r="BP42" s="22"/>
+      <c r="BQ42" s="23"/>
+      <c r="BR42" s="42"/>
     </row>
     <row r="43" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B43" s="25"/>
+      <c r="B43" s="43"/>
       <c r="T43" s="19"/>
       <c r="U43" s="19"/>
       <c r="V43" s="19"/>
@@ -4170,40 +4173,40 @@
       <c r="AW43" s="5" t="s">
         <v>190</v>
       </c>
-      <c r="AX43" s="20" t="s">
+      <c r="AX43" s="21" t="s">
         <v>191</v>
       </c>
-      <c r="AY43" s="21"/>
-      <c r="AZ43" s="22"/>
-      <c r="BA43" s="20" t="s">
+      <c r="AY43" s="22"/>
+      <c r="AZ43" s="23"/>
+      <c r="BA43" s="21" t="s">
         <v>192</v>
       </c>
-      <c r="BB43" s="21"/>
-      <c r="BC43" s="21"/>
-      <c r="BD43" s="21"/>
-      <c r="BE43" s="21"/>
-      <c r="BF43" s="21"/>
-      <c r="BG43" s="21"/>
-      <c r="BH43" s="22"/>
-      <c r="BI43" s="20" t="s">
+      <c r="BB43" s="22"/>
+      <c r="BC43" s="22"/>
+      <c r="BD43" s="22"/>
+      <c r="BE43" s="22"/>
+      <c r="BF43" s="22"/>
+      <c r="BG43" s="22"/>
+      <c r="BH43" s="23"/>
+      <c r="BI43" s="21" t="s">
         <v>193</v>
       </c>
-      <c r="BJ43" s="21"/>
-      <c r="BK43" s="22"/>
-      <c r="BL43" s="20" t="s">
+      <c r="BJ43" s="22"/>
+      <c r="BK43" s="23"/>
+      <c r="BL43" s="21" t="s">
         <v>194</v>
       </c>
-      <c r="BM43" s="21"/>
-      <c r="BN43" s="22"/>
-      <c r="BO43" s="20" t="s">
+      <c r="BM43" s="22"/>
+      <c r="BN43" s="23"/>
+      <c r="BO43" s="21" t="s">
         <v>195</v>
       </c>
-      <c r="BP43" s="21"/>
-      <c r="BQ43" s="22"/>
-      <c r="BR43" s="25"/>
+      <c r="BP43" s="22"/>
+      <c r="BQ43" s="23"/>
+      <c r="BR43" s="43"/>
     </row>
     <row r="44" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B44" s="23" t="s">
+      <c r="B44" s="41" t="s">
         <v>196</v>
       </c>
       <c r="T44" s="19"/>
@@ -4223,42 +4226,42 @@
       <c r="AW44" s="13" t="s">
         <v>265</v>
       </c>
-      <c r="AX44" s="20" t="s">
+      <c r="AX44" s="21" t="s">
         <v>273</v>
       </c>
-      <c r="AY44" s="21"/>
-      <c r="AZ44" s="22"/>
-      <c r="BA44" s="20" t="s">
+      <c r="AY44" s="22"/>
+      <c r="AZ44" s="23"/>
+      <c r="BA44" s="21" t="s">
         <v>274</v>
       </c>
-      <c r="BB44" s="21"/>
-      <c r="BC44" s="21"/>
-      <c r="BD44" s="21"/>
-      <c r="BE44" s="21"/>
-      <c r="BF44" s="21"/>
-      <c r="BG44" s="21"/>
-      <c r="BH44" s="22"/>
-      <c r="BI44" s="20" t="s">
+      <c r="BB44" s="22"/>
+      <c r="BC44" s="22"/>
+      <c r="BD44" s="22"/>
+      <c r="BE44" s="22"/>
+      <c r="BF44" s="22"/>
+      <c r="BG44" s="22"/>
+      <c r="BH44" s="23"/>
+      <c r="BI44" s="21" t="s">
         <v>275</v>
       </c>
-      <c r="BJ44" s="21"/>
-      <c r="BK44" s="22"/>
-      <c r="BL44" s="20" t="s">
+      <c r="BJ44" s="22"/>
+      <c r="BK44" s="23"/>
+      <c r="BL44" s="21" t="s">
         <v>276</v>
       </c>
-      <c r="BM44" s="21"/>
-      <c r="BN44" s="22"/>
-      <c r="BO44" s="20" t="s">
+      <c r="BM44" s="22"/>
+      <c r="BN44" s="23"/>
+      <c r="BO44" s="21" t="s">
         <v>277</v>
       </c>
-      <c r="BP44" s="21"/>
-      <c r="BQ44" s="22"/>
-      <c r="BR44" s="23" t="s">
+      <c r="BP44" s="22"/>
+      <c r="BQ44" s="23"/>
+      <c r="BR44" s="41" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="45" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B45" s="24"/>
+      <c r="B45" s="42"/>
       <c r="T45" s="19"/>
       <c r="U45" s="19"/>
       <c r="V45" s="19"/>
@@ -4276,354 +4279,354 @@
       <c r="AW45" s="5" t="s">
         <v>266</v>
       </c>
-      <c r="AX45" s="20" t="s">
+      <c r="AX45" s="21" t="s">
         <v>197</v>
       </c>
-      <c r="AY45" s="21"/>
-      <c r="AZ45" s="22"/>
-      <c r="BA45" s="20" t="s">
+      <c r="AY45" s="22"/>
+      <c r="AZ45" s="23"/>
+      <c r="BA45" s="21" t="s">
         <v>198</v>
       </c>
-      <c r="BB45" s="21"/>
-      <c r="BC45" s="21"/>
-      <c r="BD45" s="21"/>
-      <c r="BE45" s="21"/>
-      <c r="BF45" s="21"/>
-      <c r="BG45" s="21"/>
-      <c r="BH45" s="22"/>
-      <c r="BI45" s="20" t="s">
+      <c r="BB45" s="22"/>
+      <c r="BC45" s="22"/>
+      <c r="BD45" s="22"/>
+      <c r="BE45" s="22"/>
+      <c r="BF45" s="22"/>
+      <c r="BG45" s="22"/>
+      <c r="BH45" s="23"/>
+      <c r="BI45" s="21" t="s">
         <v>199</v>
       </c>
-      <c r="BJ45" s="21"/>
-      <c r="BK45" s="22"/>
-      <c r="BL45" s="20" t="s">
+      <c r="BJ45" s="22"/>
+      <c r="BK45" s="23"/>
+      <c r="BL45" s="21" t="s">
         <v>200</v>
       </c>
-      <c r="BM45" s="21"/>
-      <c r="BN45" s="22"/>
-      <c r="BO45" s="20" t="s">
+      <c r="BM45" s="22"/>
+      <c r="BN45" s="23"/>
+      <c r="BO45" s="21" t="s">
         <v>201</v>
       </c>
-      <c r="BP45" s="21"/>
-      <c r="BQ45" s="22"/>
-      <c r="BR45" s="24"/>
+      <c r="BP45" s="22"/>
+      <c r="BQ45" s="23"/>
+      <c r="BR45" s="42"/>
     </row>
     <row r="46" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B46" s="24"/>
-      <c r="AW46" s="20" t="s">
+      <c r="B46" s="42"/>
+      <c r="AW46" s="21" t="s">
         <v>202</v>
       </c>
-      <c r="AX46" s="21"/>
-      <c r="AY46" s="21"/>
-      <c r="AZ46" s="22"/>
-      <c r="BA46" s="20" t="s">
+      <c r="AX46" s="22"/>
+      <c r="AY46" s="22"/>
+      <c r="AZ46" s="23"/>
+      <c r="BA46" s="21" t="s">
         <v>203</v>
       </c>
-      <c r="BB46" s="21"/>
-      <c r="BC46" s="21"/>
-      <c r="BD46" s="21"/>
-      <c r="BE46" s="21"/>
-      <c r="BF46" s="21"/>
-      <c r="BG46" s="21"/>
-      <c r="BH46" s="22"/>
-      <c r="BI46" s="20" t="s">
+      <c r="BB46" s="22"/>
+      <c r="BC46" s="22"/>
+      <c r="BD46" s="22"/>
+      <c r="BE46" s="22"/>
+      <c r="BF46" s="22"/>
+      <c r="BG46" s="22"/>
+      <c r="BH46" s="23"/>
+      <c r="BI46" s="21" t="s">
         <v>204</v>
       </c>
-      <c r="BJ46" s="21"/>
-      <c r="BK46" s="21"/>
-      <c r="BL46" s="21"/>
-      <c r="BM46" s="21"/>
-      <c r="BN46" s="21"/>
-      <c r="BO46" s="21"/>
-      <c r="BP46" s="21"/>
-      <c r="BQ46" s="22"/>
-      <c r="BR46" s="24"/>
+      <c r="BJ46" s="22"/>
+      <c r="BK46" s="22"/>
+      <c r="BL46" s="22"/>
+      <c r="BM46" s="22"/>
+      <c r="BN46" s="22"/>
+      <c r="BO46" s="22"/>
+      <c r="BP46" s="22"/>
+      <c r="BQ46" s="23"/>
+      <c r="BR46" s="42"/>
     </row>
     <row r="47" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B47" s="24"/>
-      <c r="E47" s="26" t="s">
+      <c r="B47" s="42"/>
+      <c r="E47" s="75" t="s">
         <v>272</v>
       </c>
-      <c r="F47" s="26"/>
-      <c r="G47" s="26"/>
-      <c r="H47" s="26"/>
-      <c r="I47" s="26"/>
-      <c r="J47" s="26"/>
-      <c r="K47" s="26"/>
-      <c r="L47" s="26"/>
-      <c r="M47" s="26"/>
-      <c r="N47" s="26"/>
-      <c r="O47" s="26"/>
-      <c r="P47" s="26"/>
-      <c r="Q47" s="26"/>
-      <c r="R47" s="26"/>
-      <c r="T47" s="26" t="s">
+      <c r="F47" s="75"/>
+      <c r="G47" s="75"/>
+      <c r="H47" s="75"/>
+      <c r="I47" s="75"/>
+      <c r="J47" s="75"/>
+      <c r="K47" s="75"/>
+      <c r="L47" s="75"/>
+      <c r="M47" s="75"/>
+      <c r="N47" s="75"/>
+      <c r="O47" s="75"/>
+      <c r="P47" s="75"/>
+      <c r="Q47" s="75"/>
+      <c r="R47" s="75"/>
+      <c r="T47" s="20" t="s">
         <v>222</v>
       </c>
-      <c r="U47" s="26"/>
-      <c r="V47" s="26"/>
-      <c r="W47" s="26"/>
-      <c r="X47" s="26"/>
-      <c r="Y47" s="26"/>
-      <c r="Z47" s="26"/>
-      <c r="AA47" s="26"/>
-      <c r="AB47" s="26"/>
-      <c r="AC47" s="26"/>
-      <c r="AD47" s="26"/>
-      <c r="AE47" s="26"/>
-      <c r="AF47" s="26"/>
-      <c r="AG47" s="26"/>
-      <c r="AW47" s="20" t="s">
+      <c r="U47" s="20"/>
+      <c r="V47" s="20"/>
+      <c r="W47" s="20"/>
+      <c r="X47" s="20"/>
+      <c r="Y47" s="20"/>
+      <c r="Z47" s="20"/>
+      <c r="AA47" s="20"/>
+      <c r="AB47" s="20"/>
+      <c r="AC47" s="20"/>
+      <c r="AD47" s="20"/>
+      <c r="AE47" s="20"/>
+      <c r="AF47" s="20"/>
+      <c r="AG47" s="20"/>
+      <c r="AW47" s="21" t="s">
         <v>205</v>
       </c>
-      <c r="AX47" s="21"/>
-      <c r="AY47" s="21"/>
-      <c r="AZ47" s="22"/>
-      <c r="BA47" s="20" t="s">
+      <c r="AX47" s="22"/>
+      <c r="AY47" s="22"/>
+      <c r="AZ47" s="23"/>
+      <c r="BA47" s="21" t="s">
         <v>206</v>
       </c>
-      <c r="BB47" s="21"/>
-      <c r="BC47" s="21"/>
-      <c r="BD47" s="21"/>
-      <c r="BE47" s="21"/>
-      <c r="BF47" s="21"/>
-      <c r="BG47" s="21"/>
-      <c r="BH47" s="22"/>
-      <c r="BI47" s="20" t="s">
+      <c r="BB47" s="22"/>
+      <c r="BC47" s="22"/>
+      <c r="BD47" s="22"/>
+      <c r="BE47" s="22"/>
+      <c r="BF47" s="22"/>
+      <c r="BG47" s="22"/>
+      <c r="BH47" s="23"/>
+      <c r="BI47" s="21" t="s">
         <v>207</v>
       </c>
-      <c r="BJ47" s="21"/>
-      <c r="BK47" s="21"/>
-      <c r="BL47" s="21"/>
-      <c r="BM47" s="21"/>
-      <c r="BN47" s="21"/>
-      <c r="BO47" s="21"/>
-      <c r="BP47" s="21"/>
-      <c r="BQ47" s="22"/>
-      <c r="BR47" s="24"/>
+      <c r="BJ47" s="22"/>
+      <c r="BK47" s="22"/>
+      <c r="BL47" s="22"/>
+      <c r="BM47" s="22"/>
+      <c r="BN47" s="22"/>
+      <c r="BO47" s="22"/>
+      <c r="BP47" s="22"/>
+      <c r="BQ47" s="23"/>
+      <c r="BR47" s="42"/>
     </row>
     <row r="48" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B48" s="24"/>
-      <c r="E48" s="26"/>
-      <c r="F48" s="26"/>
-      <c r="G48" s="26"/>
-      <c r="H48" s="26"/>
-      <c r="I48" s="26"/>
-      <c r="J48" s="26"/>
-      <c r="K48" s="26"/>
-      <c r="L48" s="26"/>
-      <c r="M48" s="26"/>
-      <c r="N48" s="26"/>
-      <c r="O48" s="26"/>
-      <c r="P48" s="26"/>
-      <c r="Q48" s="26"/>
-      <c r="R48" s="26"/>
-      <c r="T48" s="26"/>
-      <c r="U48" s="26"/>
-      <c r="V48" s="26"/>
-      <c r="W48" s="26"/>
-      <c r="X48" s="26"/>
-      <c r="Y48" s="26"/>
-      <c r="Z48" s="26"/>
-      <c r="AA48" s="26"/>
-      <c r="AB48" s="26"/>
-      <c r="AC48" s="26"/>
-      <c r="AD48" s="26"/>
-      <c r="AE48" s="26"/>
-      <c r="AF48" s="26"/>
-      <c r="AG48" s="26"/>
-      <c r="AW48" s="33" t="s">
+      <c r="B48" s="42"/>
+      <c r="E48" s="75"/>
+      <c r="F48" s="75"/>
+      <c r="G48" s="75"/>
+      <c r="H48" s="75"/>
+      <c r="I48" s="75"/>
+      <c r="J48" s="75"/>
+      <c r="K48" s="75"/>
+      <c r="L48" s="75"/>
+      <c r="M48" s="75"/>
+      <c r="N48" s="75"/>
+      <c r="O48" s="75"/>
+      <c r="P48" s="75"/>
+      <c r="Q48" s="75"/>
+      <c r="R48" s="75"/>
+      <c r="T48" s="20"/>
+      <c r="U48" s="20"/>
+      <c r="V48" s="20"/>
+      <c r="W48" s="20"/>
+      <c r="X48" s="20"/>
+      <c r="Y48" s="20"/>
+      <c r="Z48" s="20"/>
+      <c r="AA48" s="20"/>
+      <c r="AB48" s="20"/>
+      <c r="AC48" s="20"/>
+      <c r="AD48" s="20"/>
+      <c r="AE48" s="20"/>
+      <c r="AF48" s="20"/>
+      <c r="AG48" s="20"/>
+      <c r="AW48" s="65" t="s">
         <v>208</v>
       </c>
-      <c r="AX48" s="34"/>
-      <c r="AY48" s="34"/>
-      <c r="AZ48" s="34"/>
-      <c r="BA48" s="34"/>
-      <c r="BB48" s="34"/>
-      <c r="BC48" s="34"/>
-      <c r="BD48" s="35"/>
-      <c r="BE48" s="27" t="s">
+      <c r="AX48" s="66"/>
+      <c r="AY48" s="66"/>
+      <c r="AZ48" s="66"/>
+      <c r="BA48" s="66"/>
+      <c r="BB48" s="66"/>
+      <c r="BC48" s="66"/>
+      <c r="BD48" s="67"/>
+      <c r="BE48" s="68" t="s">
         <v>209</v>
       </c>
-      <c r="BF48" s="28"/>
-      <c r="BG48" s="28"/>
-      <c r="BH48" s="28"/>
-      <c r="BI48" s="28"/>
-      <c r="BJ48" s="28"/>
-      <c r="BK48" s="28"/>
-      <c r="BL48" s="28"/>
-      <c r="BM48" s="28"/>
-      <c r="BN48" s="28"/>
-      <c r="BO48" s="28"/>
-      <c r="BP48" s="28"/>
-      <c r="BQ48" s="29"/>
-      <c r="BR48" s="24"/>
+      <c r="BF48" s="69"/>
+      <c r="BG48" s="69"/>
+      <c r="BH48" s="69"/>
+      <c r="BI48" s="69"/>
+      <c r="BJ48" s="69"/>
+      <c r="BK48" s="69"/>
+      <c r="BL48" s="69"/>
+      <c r="BM48" s="69"/>
+      <c r="BN48" s="69"/>
+      <c r="BO48" s="69"/>
+      <c r="BP48" s="69"/>
+      <c r="BQ48" s="70"/>
+      <c r="BR48" s="42"/>
     </row>
     <row r="49" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B49" s="24"/>
-      <c r="E49" s="26"/>
-      <c r="F49" s="26"/>
-      <c r="G49" s="26"/>
-      <c r="H49" s="26"/>
-      <c r="I49" s="26"/>
-      <c r="J49" s="26"/>
-      <c r="K49" s="26"/>
-      <c r="L49" s="26"/>
-      <c r="M49" s="26"/>
-      <c r="N49" s="26"/>
-      <c r="O49" s="26"/>
-      <c r="P49" s="26"/>
-      <c r="Q49" s="26"/>
-      <c r="R49" s="26"/>
-      <c r="T49" s="26"/>
-      <c r="U49" s="26"/>
-      <c r="V49" s="26"/>
-      <c r="W49" s="26"/>
-      <c r="X49" s="26"/>
-      <c r="Y49" s="26"/>
-      <c r="Z49" s="26"/>
-      <c r="AA49" s="26"/>
-      <c r="AB49" s="26"/>
-      <c r="AC49" s="26"/>
-      <c r="AD49" s="26"/>
-      <c r="AE49" s="26"/>
-      <c r="AF49" s="26"/>
-      <c r="AG49" s="26"/>
-      <c r="AW49" s="44" t="s">
+      <c r="B49" s="42"/>
+      <c r="E49" s="75"/>
+      <c r="F49" s="75"/>
+      <c r="G49" s="75"/>
+      <c r="H49" s="75"/>
+      <c r="I49" s="75"/>
+      <c r="J49" s="75"/>
+      <c r="K49" s="75"/>
+      <c r="L49" s="75"/>
+      <c r="M49" s="75"/>
+      <c r="N49" s="75"/>
+      <c r="O49" s="75"/>
+      <c r="P49" s="75"/>
+      <c r="Q49" s="75"/>
+      <c r="R49" s="75"/>
+      <c r="T49" s="20"/>
+      <c r="U49" s="20"/>
+      <c r="V49" s="20"/>
+      <c r="W49" s="20"/>
+      <c r="X49" s="20"/>
+      <c r="Y49" s="20"/>
+      <c r="Z49" s="20"/>
+      <c r="AA49" s="20"/>
+      <c r="AB49" s="20"/>
+      <c r="AC49" s="20"/>
+      <c r="AD49" s="20"/>
+      <c r="AE49" s="20"/>
+      <c r="AF49" s="20"/>
+      <c r="AG49" s="20"/>
+      <c r="AW49" s="24" t="s">
         <v>267</v>
       </c>
-      <c r="AX49" s="45"/>
-      <c r="AY49" s="45"/>
-      <c r="AZ49" s="45"/>
-      <c r="BA49" s="45"/>
-      <c r="BB49" s="45"/>
-      <c r="BC49" s="45"/>
-      <c r="BD49" s="49"/>
-      <c r="BE49" s="30"/>
-      <c r="BF49" s="31"/>
-      <c r="BG49" s="31"/>
-      <c r="BH49" s="31"/>
-      <c r="BI49" s="31"/>
-      <c r="BJ49" s="31"/>
-      <c r="BK49" s="31"/>
-      <c r="BL49" s="31"/>
-      <c r="BM49" s="31"/>
-      <c r="BN49" s="31"/>
-      <c r="BO49" s="31"/>
-      <c r="BP49" s="31"/>
-      <c r="BQ49" s="32"/>
-      <c r="BR49" s="24"/>
+      <c r="AX49" s="25"/>
+      <c r="AY49" s="25"/>
+      <c r="AZ49" s="25"/>
+      <c r="BA49" s="25"/>
+      <c r="BB49" s="25"/>
+      <c r="BC49" s="25"/>
+      <c r="BD49" s="26"/>
+      <c r="BE49" s="71"/>
+      <c r="BF49" s="72"/>
+      <c r="BG49" s="72"/>
+      <c r="BH49" s="72"/>
+      <c r="BI49" s="72"/>
+      <c r="BJ49" s="72"/>
+      <c r="BK49" s="72"/>
+      <c r="BL49" s="72"/>
+      <c r="BM49" s="72"/>
+      <c r="BN49" s="72"/>
+      <c r="BO49" s="72"/>
+      <c r="BP49" s="72"/>
+      <c r="BQ49" s="73"/>
+      <c r="BR49" s="42"/>
     </row>
     <row r="50" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B50" s="24"/>
-      <c r="E50" s="26"/>
-      <c r="F50" s="26"/>
-      <c r="G50" s="26"/>
-      <c r="H50" s="26"/>
-      <c r="I50" s="26"/>
-      <c r="J50" s="26"/>
-      <c r="K50" s="26"/>
-      <c r="L50" s="26"/>
-      <c r="M50" s="26"/>
-      <c r="N50" s="26"/>
-      <c r="O50" s="26"/>
-      <c r="P50" s="26"/>
-      <c r="Q50" s="26"/>
-      <c r="R50" s="26"/>
-      <c r="T50" s="26"/>
-      <c r="U50" s="26"/>
-      <c r="V50" s="26"/>
-      <c r="W50" s="26"/>
-      <c r="X50" s="26"/>
-      <c r="Y50" s="26"/>
-      <c r="Z50" s="26"/>
-      <c r="AA50" s="26"/>
-      <c r="AB50" s="26"/>
-      <c r="AC50" s="26"/>
-      <c r="AD50" s="26"/>
-      <c r="AE50" s="26"/>
-      <c r="AF50" s="26"/>
-      <c r="AG50" s="26"/>
-      <c r="AW50" s="44"/>
-      <c r="AX50" s="45"/>
-      <c r="AY50" s="45"/>
-      <c r="AZ50" s="45"/>
-      <c r="BA50" s="45"/>
-      <c r="BB50" s="45"/>
-      <c r="BC50" s="45"/>
-      <c r="BD50" s="49"/>
-      <c r="BE50" s="27" t="s">
+      <c r="B50" s="42"/>
+      <c r="E50" s="75"/>
+      <c r="F50" s="75"/>
+      <c r="G50" s="75"/>
+      <c r="H50" s="75"/>
+      <c r="I50" s="75"/>
+      <c r="J50" s="75"/>
+      <c r="K50" s="75"/>
+      <c r="L50" s="75"/>
+      <c r="M50" s="75"/>
+      <c r="N50" s="75"/>
+      <c r="O50" s="75"/>
+      <c r="P50" s="75"/>
+      <c r="Q50" s="75"/>
+      <c r="R50" s="75"/>
+      <c r="T50" s="20"/>
+      <c r="U50" s="20"/>
+      <c r="V50" s="20"/>
+      <c r="W50" s="20"/>
+      <c r="X50" s="20"/>
+      <c r="Y50" s="20"/>
+      <c r="Z50" s="20"/>
+      <c r="AA50" s="20"/>
+      <c r="AB50" s="20"/>
+      <c r="AC50" s="20"/>
+      <c r="AD50" s="20"/>
+      <c r="AE50" s="20"/>
+      <c r="AF50" s="20"/>
+      <c r="AG50" s="20"/>
+      <c r="AW50" s="24"/>
+      <c r="AX50" s="25"/>
+      <c r="AY50" s="25"/>
+      <c r="AZ50" s="25"/>
+      <c r="BA50" s="25"/>
+      <c r="BB50" s="25"/>
+      <c r="BC50" s="25"/>
+      <c r="BD50" s="26"/>
+      <c r="BE50" s="68" t="s">
         <v>210</v>
       </c>
-      <c r="BF50" s="28"/>
-      <c r="BG50" s="28"/>
-      <c r="BH50" s="28"/>
-      <c r="BI50" s="28"/>
-      <c r="BJ50" s="28"/>
-      <c r="BK50" s="28"/>
-      <c r="BL50" s="28"/>
-      <c r="BM50" s="28"/>
-      <c r="BN50" s="28"/>
-      <c r="BO50" s="28"/>
-      <c r="BP50" s="28"/>
-      <c r="BQ50" s="29"/>
-      <c r="BR50" s="24"/>
+      <c r="BF50" s="69"/>
+      <c r="BG50" s="69"/>
+      <c r="BH50" s="69"/>
+      <c r="BI50" s="69"/>
+      <c r="BJ50" s="69"/>
+      <c r="BK50" s="69"/>
+      <c r="BL50" s="69"/>
+      <c r="BM50" s="69"/>
+      <c r="BN50" s="69"/>
+      <c r="BO50" s="69"/>
+      <c r="BP50" s="69"/>
+      <c r="BQ50" s="70"/>
+      <c r="BR50" s="42"/>
     </row>
     <row r="51" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B51" s="24"/>
-      <c r="E51" s="26"/>
-      <c r="F51" s="26"/>
-      <c r="G51" s="26"/>
-      <c r="H51" s="26"/>
-      <c r="I51" s="26"/>
-      <c r="J51" s="26"/>
-      <c r="K51" s="26"/>
-      <c r="L51" s="26"/>
-      <c r="M51" s="26"/>
-      <c r="N51" s="26"/>
-      <c r="O51" s="26"/>
-      <c r="P51" s="26"/>
-      <c r="Q51" s="26"/>
-      <c r="R51" s="26"/>
-      <c r="T51" s="26"/>
-      <c r="U51" s="26"/>
-      <c r="V51" s="26"/>
-      <c r="W51" s="26"/>
-      <c r="X51" s="26"/>
-      <c r="Y51" s="26"/>
-      <c r="Z51" s="26"/>
-      <c r="AA51" s="26"/>
-      <c r="AB51" s="26"/>
-      <c r="AC51" s="26"/>
-      <c r="AD51" s="26"/>
-      <c r="AE51" s="26"/>
-      <c r="AF51" s="26"/>
-      <c r="AG51" s="26"/>
-      <c r="AW51" s="46"/>
-      <c r="AX51" s="47"/>
-      <c r="AY51" s="47"/>
-      <c r="AZ51" s="47"/>
-      <c r="BA51" s="47"/>
-      <c r="BB51" s="47"/>
-      <c r="BC51" s="47"/>
-      <c r="BD51" s="50"/>
-      <c r="BE51" s="30"/>
-      <c r="BF51" s="31"/>
-      <c r="BG51" s="31"/>
-      <c r="BH51" s="31"/>
-      <c r="BI51" s="31"/>
-      <c r="BJ51" s="31"/>
-      <c r="BK51" s="31"/>
-      <c r="BL51" s="31"/>
-      <c r="BM51" s="31"/>
-      <c r="BN51" s="31"/>
-      <c r="BO51" s="31"/>
-      <c r="BP51" s="31"/>
-      <c r="BQ51" s="32"/>
-      <c r="BR51" s="24"/>
+      <c r="B51" s="42"/>
+      <c r="E51" s="75"/>
+      <c r="F51" s="75"/>
+      <c r="G51" s="75"/>
+      <c r="H51" s="75"/>
+      <c r="I51" s="75"/>
+      <c r="J51" s="75"/>
+      <c r="K51" s="75"/>
+      <c r="L51" s="75"/>
+      <c r="M51" s="75"/>
+      <c r="N51" s="75"/>
+      <c r="O51" s="75"/>
+      <c r="P51" s="75"/>
+      <c r="Q51" s="75"/>
+      <c r="R51" s="75"/>
+      <c r="T51" s="20"/>
+      <c r="U51" s="20"/>
+      <c r="V51" s="20"/>
+      <c r="W51" s="20"/>
+      <c r="X51" s="20"/>
+      <c r="Y51" s="20"/>
+      <c r="Z51" s="20"/>
+      <c r="AA51" s="20"/>
+      <c r="AB51" s="20"/>
+      <c r="AC51" s="20"/>
+      <c r="AD51" s="20"/>
+      <c r="AE51" s="20"/>
+      <c r="AF51" s="20"/>
+      <c r="AG51" s="20"/>
+      <c r="AW51" s="27"/>
+      <c r="AX51" s="28"/>
+      <c r="AY51" s="28"/>
+      <c r="AZ51" s="28"/>
+      <c r="BA51" s="28"/>
+      <c r="BB51" s="28"/>
+      <c r="BC51" s="28"/>
+      <c r="BD51" s="29"/>
+      <c r="BE51" s="71"/>
+      <c r="BF51" s="72"/>
+      <c r="BG51" s="72"/>
+      <c r="BH51" s="72"/>
+      <c r="BI51" s="72"/>
+      <c r="BJ51" s="72"/>
+      <c r="BK51" s="72"/>
+      <c r="BL51" s="72"/>
+      <c r="BM51" s="72"/>
+      <c r="BN51" s="72"/>
+      <c r="BO51" s="72"/>
+      <c r="BP51" s="72"/>
+      <c r="BQ51" s="73"/>
+      <c r="BR51" s="42"/>
     </row>
     <row r="52" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B52" s="24"/>
+      <c r="B52" s="42"/>
       <c r="T52" s="19"/>
       <c r="U52" s="19"/>
       <c r="V52" s="19"/>
@@ -4638,35 +4641,35 @@
       <c r="AE52" s="19"/>
       <c r="AF52" s="19"/>
       <c r="AG52" s="19"/>
-      <c r="AW52" s="33" t="s">
+      <c r="AW52" s="65" t="s">
         <v>211</v>
       </c>
-      <c r="AX52" s="34"/>
-      <c r="AY52" s="34"/>
-      <c r="AZ52" s="34"/>
-      <c r="BA52" s="34"/>
-      <c r="BB52" s="34"/>
-      <c r="BC52" s="34"/>
-      <c r="BD52" s="35"/>
-      <c r="BE52" s="55" t="s">
+      <c r="AX52" s="66"/>
+      <c r="AY52" s="66"/>
+      <c r="AZ52" s="66"/>
+      <c r="BA52" s="66"/>
+      <c r="BB52" s="66"/>
+      <c r="BC52" s="66"/>
+      <c r="BD52" s="67"/>
+      <c r="BE52" s="56" t="s">
         <v>212</v>
       </c>
-      <c r="BF52" s="56"/>
-      <c r="BG52" s="56"/>
-      <c r="BH52" s="56"/>
-      <c r="BI52" s="56"/>
-      <c r="BJ52" s="56"/>
-      <c r="BK52" s="56"/>
-      <c r="BL52" s="56"/>
-      <c r="BM52" s="56"/>
-      <c r="BN52" s="56"/>
-      <c r="BO52" s="56"/>
-      <c r="BP52" s="56"/>
-      <c r="BQ52" s="57"/>
-      <c r="BR52" s="24"/>
+      <c r="BF52" s="57"/>
+      <c r="BG52" s="57"/>
+      <c r="BH52" s="57"/>
+      <c r="BI52" s="57"/>
+      <c r="BJ52" s="57"/>
+      <c r="BK52" s="57"/>
+      <c r="BL52" s="57"/>
+      <c r="BM52" s="57"/>
+      <c r="BN52" s="57"/>
+      <c r="BO52" s="57"/>
+      <c r="BP52" s="57"/>
+      <c r="BQ52" s="58"/>
+      <c r="BR52" s="42"/>
     </row>
     <row r="53" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B53" s="24"/>
+      <c r="B53" s="42"/>
       <c r="T53" s="19"/>
       <c r="U53" s="19"/>
       <c r="V53" s="19"/>
@@ -4681,33 +4684,33 @@
       <c r="AE53" s="19"/>
       <c r="AF53" s="19"/>
       <c r="AG53" s="19"/>
-      <c r="AW53" s="44" t="s">
+      <c r="AW53" s="24" t="s">
         <v>223</v>
       </c>
-      <c r="AX53" s="45"/>
-      <c r="AY53" s="45"/>
-      <c r="AZ53" s="45"/>
-      <c r="BA53" s="45"/>
-      <c r="BB53" s="45"/>
-      <c r="BC53" s="45"/>
-      <c r="BD53" s="49"/>
-      <c r="BE53" s="58"/>
-      <c r="BF53" s="59"/>
-      <c r="BG53" s="59"/>
-      <c r="BH53" s="59"/>
-      <c r="BI53" s="59"/>
-      <c r="BJ53" s="59"/>
-      <c r="BK53" s="59"/>
-      <c r="BL53" s="59"/>
-      <c r="BM53" s="59"/>
-      <c r="BN53" s="59"/>
-      <c r="BO53" s="59"/>
-      <c r="BP53" s="59"/>
-      <c r="BQ53" s="60"/>
-      <c r="BR53" s="24"/>
+      <c r="AX53" s="25"/>
+      <c r="AY53" s="25"/>
+      <c r="AZ53" s="25"/>
+      <c r="BA53" s="25"/>
+      <c r="BB53" s="25"/>
+      <c r="BC53" s="25"/>
+      <c r="BD53" s="26"/>
+      <c r="BE53" s="59"/>
+      <c r="BF53" s="60"/>
+      <c r="BG53" s="60"/>
+      <c r="BH53" s="60"/>
+      <c r="BI53" s="60"/>
+      <c r="BJ53" s="60"/>
+      <c r="BK53" s="60"/>
+      <c r="BL53" s="60"/>
+      <c r="BM53" s="60"/>
+      <c r="BN53" s="60"/>
+      <c r="BO53" s="60"/>
+      <c r="BP53" s="60"/>
+      <c r="BQ53" s="61"/>
+      <c r="BR53" s="42"/>
     </row>
     <row r="54" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B54" s="24"/>
+      <c r="B54" s="42"/>
       <c r="T54" s="19"/>
       <c r="U54" s="19"/>
       <c r="V54" s="19"/>
@@ -4722,31 +4725,31 @@
       <c r="AE54" s="19"/>
       <c r="AF54" s="19"/>
       <c r="AG54" s="19"/>
-      <c r="AW54" s="44"/>
-      <c r="AX54" s="45"/>
-      <c r="AY54" s="45"/>
-      <c r="AZ54" s="45"/>
-      <c r="BA54" s="45"/>
-      <c r="BB54" s="45"/>
-      <c r="BC54" s="45"/>
-      <c r="BD54" s="49"/>
-      <c r="BE54" s="58"/>
-      <c r="BF54" s="59"/>
-      <c r="BG54" s="59"/>
-      <c r="BH54" s="59"/>
-      <c r="BI54" s="59"/>
-      <c r="BJ54" s="59"/>
-      <c r="BK54" s="59"/>
-      <c r="BL54" s="59"/>
-      <c r="BM54" s="59"/>
-      <c r="BN54" s="59"/>
-      <c r="BO54" s="59"/>
-      <c r="BP54" s="59"/>
-      <c r="BQ54" s="60"/>
-      <c r="BR54" s="24"/>
+      <c r="AW54" s="24"/>
+      <c r="AX54" s="25"/>
+      <c r="AY54" s="25"/>
+      <c r="AZ54" s="25"/>
+      <c r="BA54" s="25"/>
+      <c r="BB54" s="25"/>
+      <c r="BC54" s="25"/>
+      <c r="BD54" s="26"/>
+      <c r="BE54" s="59"/>
+      <c r="BF54" s="60"/>
+      <c r="BG54" s="60"/>
+      <c r="BH54" s="60"/>
+      <c r="BI54" s="60"/>
+      <c r="BJ54" s="60"/>
+      <c r="BK54" s="60"/>
+      <c r="BL54" s="60"/>
+      <c r="BM54" s="60"/>
+      <c r="BN54" s="60"/>
+      <c r="BO54" s="60"/>
+      <c r="BP54" s="60"/>
+      <c r="BQ54" s="61"/>
+      <c r="BR54" s="42"/>
     </row>
     <row r="55" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B55" s="24"/>
+      <c r="B55" s="42"/>
       <c r="T55" s="19"/>
       <c r="U55" s="19"/>
       <c r="V55" s="19"/>
@@ -4761,162 +4764,306 @@
       <c r="AE55" s="19"/>
       <c r="AF55" s="19"/>
       <c r="AG55" s="19"/>
-      <c r="AW55" s="46"/>
-      <c r="AX55" s="47"/>
-      <c r="AY55" s="47"/>
-      <c r="AZ55" s="47"/>
-      <c r="BA55" s="47"/>
-      <c r="BB55" s="47"/>
-      <c r="BC55" s="47"/>
-      <c r="BD55" s="50"/>
-      <c r="BE55" s="61"/>
-      <c r="BF55" s="62"/>
-      <c r="BG55" s="62"/>
-      <c r="BH55" s="62"/>
-      <c r="BI55" s="62"/>
-      <c r="BJ55" s="62"/>
-      <c r="BK55" s="62"/>
-      <c r="BL55" s="62"/>
-      <c r="BM55" s="62"/>
-      <c r="BN55" s="62"/>
-      <c r="BO55" s="62"/>
-      <c r="BP55" s="62"/>
-      <c r="BQ55" s="63"/>
-      <c r="BR55" s="24"/>
+      <c r="AW55" s="27"/>
+      <c r="AX55" s="28"/>
+      <c r="AY55" s="28"/>
+      <c r="AZ55" s="28"/>
+      <c r="BA55" s="28"/>
+      <c r="BB55" s="28"/>
+      <c r="BC55" s="28"/>
+      <c r="BD55" s="29"/>
+      <c r="BE55" s="62"/>
+      <c r="BF55" s="63"/>
+      <c r="BG55" s="63"/>
+      <c r="BH55" s="63"/>
+      <c r="BI55" s="63"/>
+      <c r="BJ55" s="63"/>
+      <c r="BK55" s="63"/>
+      <c r="BL55" s="63"/>
+      <c r="BM55" s="63"/>
+      <c r="BN55" s="63"/>
+      <c r="BO55" s="63"/>
+      <c r="BP55" s="63"/>
+      <c r="BQ55" s="64"/>
+      <c r="BR55" s="42"/>
     </row>
     <row r="56" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B56" s="25"/>
+      <c r="B56" s="43"/>
       <c r="K56" s="3"/>
       <c r="AI56" s="3"/>
-      <c r="AW56" s="20" t="s">
+      <c r="AW56" s="21" t="s">
         <v>213</v>
       </c>
-      <c r="AX56" s="21"/>
-      <c r="AY56" s="21" t="s">
+      <c r="AX56" s="22"/>
+      <c r="AY56" s="22" t="s">
         <v>214</v>
       </c>
-      <c r="AZ56" s="21"/>
-      <c r="BA56" s="21"/>
-      <c r="BB56" s="21"/>
-      <c r="BC56" s="21"/>
-      <c r="BD56" s="21"/>
-      <c r="BE56" s="21"/>
-      <c r="BF56" s="21"/>
-      <c r="BG56" s="21"/>
-      <c r="BH56" s="21"/>
-      <c r="BI56" s="21"/>
-      <c r="BJ56" s="21"/>
-      <c r="BK56" s="21"/>
-      <c r="BL56" s="21"/>
-      <c r="BM56" s="21"/>
-      <c r="BN56" s="21"/>
-      <c r="BO56" s="21"/>
-      <c r="BP56" s="21"/>
-      <c r="BQ56" s="22"/>
-      <c r="BR56" s="25"/>
+      <c r="AZ56" s="22"/>
+      <c r="BA56" s="22"/>
+      <c r="BB56" s="22"/>
+      <c r="BC56" s="22"/>
+      <c r="BD56" s="22"/>
+      <c r="BE56" s="22"/>
+      <c r="BF56" s="22"/>
+      <c r="BG56" s="22"/>
+      <c r="BH56" s="22"/>
+      <c r="BI56" s="22"/>
+      <c r="BJ56" s="22"/>
+      <c r="BK56" s="22"/>
+      <c r="BL56" s="22"/>
+      <c r="BM56" s="22"/>
+      <c r="BN56" s="22"/>
+      <c r="BO56" s="22"/>
+      <c r="BP56" s="22"/>
+      <c r="BQ56" s="23"/>
+      <c r="BR56" s="43"/>
     </row>
     <row r="57" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="C57" s="20">
+      <c r="C57" s="21">
         <v>1</v>
       </c>
-      <c r="D57" s="21"/>
-      <c r="E57" s="21"/>
-      <c r="F57" s="21"/>
-      <c r="G57" s="21"/>
-      <c r="H57" s="21"/>
-      <c r="I57" s="21"/>
-      <c r="J57" s="21"/>
-      <c r="K57" s="21"/>
-      <c r="L57" s="22"/>
-      <c r="M57" s="20">
+      <c r="D57" s="22"/>
+      <c r="E57" s="22"/>
+      <c r="F57" s="22"/>
+      <c r="G57" s="22"/>
+      <c r="H57" s="22"/>
+      <c r="I57" s="22"/>
+      <c r="J57" s="22"/>
+      <c r="K57" s="22"/>
+      <c r="L57" s="23"/>
+      <c r="M57" s="21">
         <v>2</v>
       </c>
-      <c r="N57" s="21"/>
-      <c r="O57" s="21"/>
-      <c r="P57" s="21"/>
-      <c r="Q57" s="21"/>
-      <c r="R57" s="21"/>
-      <c r="S57" s="21"/>
-      <c r="T57" s="21"/>
-      <c r="U57" s="21"/>
-      <c r="V57" s="21"/>
-      <c r="W57" s="21"/>
-      <c r="X57" s="22"/>
-      <c r="Y57" s="20">
+      <c r="N57" s="22"/>
+      <c r="O57" s="22"/>
+      <c r="P57" s="22"/>
+      <c r="Q57" s="22"/>
+      <c r="R57" s="22"/>
+      <c r="S57" s="22"/>
+      <c r="T57" s="22"/>
+      <c r="U57" s="22"/>
+      <c r="V57" s="22"/>
+      <c r="W57" s="22"/>
+      <c r="X57" s="23"/>
+      <c r="Y57" s="21">
         <v>3</v>
       </c>
-      <c r="Z57" s="21"/>
-      <c r="AA57" s="21"/>
-      <c r="AB57" s="21"/>
-      <c r="AC57" s="21"/>
-      <c r="AD57" s="21"/>
-      <c r="AE57" s="21"/>
-      <c r="AF57" s="21"/>
-      <c r="AG57" s="21"/>
-      <c r="AH57" s="21"/>
-      <c r="AI57" s="22"/>
-      <c r="AJ57" s="20">
+      <c r="Z57" s="22"/>
+      <c r="AA57" s="22"/>
+      <c r="AB57" s="22"/>
+      <c r="AC57" s="22"/>
+      <c r="AD57" s="22"/>
+      <c r="AE57" s="22"/>
+      <c r="AF57" s="22"/>
+      <c r="AG57" s="22"/>
+      <c r="AH57" s="22"/>
+      <c r="AI57" s="23"/>
+      <c r="AJ57" s="21">
         <v>4</v>
       </c>
-      <c r="AK57" s="21"/>
-      <c r="AL57" s="21"/>
-      <c r="AM57" s="21"/>
-      <c r="AN57" s="21"/>
-      <c r="AO57" s="21"/>
-      <c r="AP57" s="21"/>
-      <c r="AQ57" s="21"/>
-      <c r="AR57" s="21"/>
-      <c r="AS57" s="21"/>
-      <c r="AT57" s="22"/>
-      <c r="AU57" s="20">
+      <c r="AK57" s="22"/>
+      <c r="AL57" s="22"/>
+      <c r="AM57" s="22"/>
+      <c r="AN57" s="22"/>
+      <c r="AO57" s="22"/>
+      <c r="AP57" s="22"/>
+      <c r="AQ57" s="22"/>
+      <c r="AR57" s="22"/>
+      <c r="AS57" s="22"/>
+      <c r="AT57" s="23"/>
+      <c r="AU57" s="21">
         <v>5</v>
       </c>
-      <c r="AV57" s="21"/>
-      <c r="AW57" s="21"/>
-      <c r="AX57" s="21"/>
-      <c r="AY57" s="21"/>
-      <c r="AZ57" s="21"/>
-      <c r="BA57" s="21"/>
-      <c r="BB57" s="21"/>
-      <c r="BC57" s="21"/>
-      <c r="BD57" s="21"/>
-      <c r="BE57" s="21"/>
-      <c r="BF57" s="22"/>
-      <c r="BG57" s="20">
+      <c r="AV57" s="22"/>
+      <c r="AW57" s="22"/>
+      <c r="AX57" s="22"/>
+      <c r="AY57" s="22"/>
+      <c r="AZ57" s="22"/>
+      <c r="BA57" s="22"/>
+      <c r="BB57" s="22"/>
+      <c r="BC57" s="22"/>
+      <c r="BD57" s="22"/>
+      <c r="BE57" s="22"/>
+      <c r="BF57" s="23"/>
+      <c r="BG57" s="21">
         <v>6</v>
       </c>
-      <c r="BH57" s="21"/>
-      <c r="BI57" s="21"/>
-      <c r="BJ57" s="21"/>
-      <c r="BK57" s="21"/>
-      <c r="BL57" s="21"/>
-      <c r="BM57" s="21"/>
-      <c r="BN57" s="21"/>
-      <c r="BO57" s="21"/>
-      <c r="BP57" s="21"/>
-      <c r="BQ57" s="22"/>
+      <c r="BH57" s="22"/>
+      <c r="BI57" s="22"/>
+      <c r="BJ57" s="22"/>
+      <c r="BK57" s="22"/>
+      <c r="BL57" s="22"/>
+      <c r="BM57" s="22"/>
+      <c r="BN57" s="22"/>
+      <c r="BO57" s="22"/>
+      <c r="BP57" s="22"/>
+      <c r="BQ57" s="23"/>
     </row>
     <row r="58" spans="2:70" ht="13.95" customHeight="1" x14ac:dyDescent="0.4"/>
   </sheetData>
   <mergeCells count="210">
-    <mergeCell ref="E17:R21"/>
-    <mergeCell ref="E27:R31"/>
-    <mergeCell ref="E37:R41"/>
-    <mergeCell ref="T17:AG21"/>
-    <mergeCell ref="T27:AG31"/>
-    <mergeCell ref="T37:AG41"/>
-    <mergeCell ref="M2:X2"/>
-    <mergeCell ref="AU2:BF2"/>
-    <mergeCell ref="AW18:AX18"/>
-    <mergeCell ref="BC8:BE8"/>
-    <mergeCell ref="BC24:BE24"/>
-    <mergeCell ref="AY7:BB7"/>
-    <mergeCell ref="BC10:BE10"/>
-    <mergeCell ref="AW8:AX8"/>
-    <mergeCell ref="BF8:BK8"/>
-    <mergeCell ref="T7:AG11"/>
-    <mergeCell ref="C2:L2"/>
-    <mergeCell ref="E7:R11"/>
+    <mergeCell ref="BM7:BO7"/>
+    <mergeCell ref="BM15:BO15"/>
+    <mergeCell ref="BC25:BE25"/>
+    <mergeCell ref="BR30:BR43"/>
+    <mergeCell ref="BM8:BO8"/>
+    <mergeCell ref="C57:L57"/>
+    <mergeCell ref="M57:X57"/>
+    <mergeCell ref="Y57:AI57"/>
+    <mergeCell ref="AJ57:AT57"/>
+    <mergeCell ref="AW56:AX56"/>
+    <mergeCell ref="BM25:BO25"/>
+    <mergeCell ref="E47:R51"/>
+    <mergeCell ref="BA42:BH42"/>
+    <mergeCell ref="AX40:AZ40"/>
+    <mergeCell ref="BL40:BN40"/>
+    <mergeCell ref="BE50:BQ51"/>
+    <mergeCell ref="AY26:BB26"/>
+    <mergeCell ref="BA44:BH44"/>
+    <mergeCell ref="BI44:BK44"/>
+    <mergeCell ref="BL44:BN44"/>
+    <mergeCell ref="BO44:BQ44"/>
+    <mergeCell ref="T47:AG51"/>
+    <mergeCell ref="BF16:BK16"/>
+    <mergeCell ref="AY10:BB10"/>
+    <mergeCell ref="AW11:AX11"/>
+    <mergeCell ref="AY11:BB11"/>
+    <mergeCell ref="BC11:BE11"/>
+    <mergeCell ref="BR17:BR29"/>
+    <mergeCell ref="BM9:BO9"/>
+    <mergeCell ref="AY16:BB16"/>
+    <mergeCell ref="BM19:BO19"/>
+    <mergeCell ref="BF14:BK14"/>
+    <mergeCell ref="BF23:BK23"/>
+    <mergeCell ref="BM12:BO12"/>
+    <mergeCell ref="BR3:BR16"/>
+    <mergeCell ref="BF25:BK25"/>
+    <mergeCell ref="BF22:BK22"/>
+    <mergeCell ref="BF12:BK12"/>
+    <mergeCell ref="BM20:BO20"/>
+    <mergeCell ref="BF7:BK7"/>
+    <mergeCell ref="AY21:BB21"/>
+    <mergeCell ref="BM18:BO18"/>
+    <mergeCell ref="BC13:BE13"/>
+    <mergeCell ref="BM13:BO13"/>
+    <mergeCell ref="AY19:BB19"/>
+    <mergeCell ref="AY13:BB13"/>
+    <mergeCell ref="AY22:BB22"/>
+    <mergeCell ref="BF11:BK11"/>
+    <mergeCell ref="BM11:BO11"/>
+    <mergeCell ref="AY17:BB17"/>
+    <mergeCell ref="BF24:BK24"/>
+    <mergeCell ref="B30:B43"/>
+    <mergeCell ref="AW47:AZ47"/>
+    <mergeCell ref="BF10:BK10"/>
+    <mergeCell ref="AW10:AX10"/>
+    <mergeCell ref="BF17:BK17"/>
+    <mergeCell ref="AW23:AX23"/>
+    <mergeCell ref="BC18:BE18"/>
+    <mergeCell ref="AW33:AX38"/>
+    <mergeCell ref="AY33:BQ38"/>
+    <mergeCell ref="AX43:AZ43"/>
+    <mergeCell ref="BA43:BH43"/>
+    <mergeCell ref="BI43:BK43"/>
+    <mergeCell ref="BL43:BN43"/>
+    <mergeCell ref="BO43:BQ43"/>
+    <mergeCell ref="AX44:AZ44"/>
+    <mergeCell ref="AW22:AX22"/>
+    <mergeCell ref="BA41:BH41"/>
+    <mergeCell ref="AW26:AX26"/>
+    <mergeCell ref="B17:B29"/>
+    <mergeCell ref="BC23:BE23"/>
+    <mergeCell ref="BF18:BK18"/>
+    <mergeCell ref="AW48:BD48"/>
+    <mergeCell ref="B3:B16"/>
+    <mergeCell ref="BI47:BQ47"/>
+    <mergeCell ref="AW21:AX21"/>
+    <mergeCell ref="BC19:BE19"/>
+    <mergeCell ref="AX41:AZ41"/>
+    <mergeCell ref="BM24:BO24"/>
+    <mergeCell ref="BC21:BE21"/>
+    <mergeCell ref="AY20:BB20"/>
+    <mergeCell ref="AW16:AX16"/>
+    <mergeCell ref="BF5:BK6"/>
+    <mergeCell ref="BC17:BE17"/>
+    <mergeCell ref="AY24:BB24"/>
+    <mergeCell ref="BC5:BE6"/>
+    <mergeCell ref="AW24:AX24"/>
+    <mergeCell ref="BC20:BE20"/>
+    <mergeCell ref="AY15:BB15"/>
+    <mergeCell ref="BI42:BK42"/>
+    <mergeCell ref="BF21:BK21"/>
+    <mergeCell ref="BO45:BQ45"/>
+    <mergeCell ref="AY31:BB31"/>
+    <mergeCell ref="BC31:BE31"/>
+    <mergeCell ref="BF31:BK31"/>
+    <mergeCell ref="BM31:BO31"/>
+    <mergeCell ref="BR44:BR56"/>
+    <mergeCell ref="AY9:BB9"/>
+    <mergeCell ref="AW25:AX25"/>
+    <mergeCell ref="AW15:AX15"/>
+    <mergeCell ref="BC9:BE9"/>
+    <mergeCell ref="AY18:BB18"/>
+    <mergeCell ref="AW49:BD51"/>
+    <mergeCell ref="BI45:BK45"/>
+    <mergeCell ref="BC16:BE16"/>
+    <mergeCell ref="AW14:AX14"/>
+    <mergeCell ref="BI46:BQ46"/>
+    <mergeCell ref="BA45:BH45"/>
+    <mergeCell ref="BL45:BN45"/>
+    <mergeCell ref="AW46:AZ46"/>
+    <mergeCell ref="AW27:AX27"/>
+    <mergeCell ref="AW28:AX28"/>
+    <mergeCell ref="AW29:AX29"/>
+    <mergeCell ref="BM29:BO29"/>
+    <mergeCell ref="AW30:AX30"/>
+    <mergeCell ref="AY30:BB30"/>
+    <mergeCell ref="BC30:BE30"/>
+    <mergeCell ref="BF30:BK30"/>
+    <mergeCell ref="BM30:BO30"/>
+    <mergeCell ref="AW31:AX31"/>
+    <mergeCell ref="AW7:AX7"/>
+    <mergeCell ref="B44:B56"/>
+    <mergeCell ref="C3:D5"/>
+    <mergeCell ref="BM5:BO6"/>
+    <mergeCell ref="AW5:AX6"/>
+    <mergeCell ref="AT3:AV8"/>
+    <mergeCell ref="BE52:BQ55"/>
+    <mergeCell ref="AX42:AZ42"/>
+    <mergeCell ref="AY5:BB6"/>
+    <mergeCell ref="BF20:BK20"/>
+    <mergeCell ref="AW20:AX20"/>
+    <mergeCell ref="AW52:BD52"/>
+    <mergeCell ref="BO42:BQ42"/>
+    <mergeCell ref="BP5:BP6"/>
+    <mergeCell ref="BO40:BQ40"/>
+    <mergeCell ref="BQ5:BQ6"/>
+    <mergeCell ref="BM16:BO16"/>
+    <mergeCell ref="BA46:BH46"/>
+    <mergeCell ref="BM10:BO10"/>
+    <mergeCell ref="BE48:BQ49"/>
+    <mergeCell ref="BL42:BN42"/>
+    <mergeCell ref="AY23:BB23"/>
+    <mergeCell ref="AX45:AZ45"/>
+    <mergeCell ref="BM17:BO17"/>
+    <mergeCell ref="AW12:AX12"/>
+    <mergeCell ref="BM14:BO14"/>
+    <mergeCell ref="BC12:BE12"/>
+    <mergeCell ref="BF19:BK19"/>
+    <mergeCell ref="BM21:BO21"/>
+    <mergeCell ref="BF13:BK13"/>
+    <mergeCell ref="AW13:AX13"/>
+    <mergeCell ref="BM23:BO23"/>
+    <mergeCell ref="BF15:BK15"/>
+    <mergeCell ref="BM26:BO26"/>
+    <mergeCell ref="AY27:BB27"/>
+    <mergeCell ref="BC27:BE27"/>
+    <mergeCell ref="BF27:BK27"/>
+    <mergeCell ref="BM27:BO27"/>
+    <mergeCell ref="AY28:BB28"/>
+    <mergeCell ref="BC28:BE28"/>
+    <mergeCell ref="BF28:BK28"/>
+    <mergeCell ref="BM28:BO28"/>
     <mergeCell ref="AU57:BF57"/>
     <mergeCell ref="AW9:AX9"/>
     <mergeCell ref="BC22:BE22"/>
@@ -4941,174 +5088,30 @@
     <mergeCell ref="AY12:BB12"/>
     <mergeCell ref="BC14:BE14"/>
     <mergeCell ref="BM22:BO22"/>
+    <mergeCell ref="E17:R21"/>
+    <mergeCell ref="E27:R31"/>
+    <mergeCell ref="E37:R41"/>
+    <mergeCell ref="T17:AG21"/>
+    <mergeCell ref="T27:AG31"/>
+    <mergeCell ref="T37:AG41"/>
+    <mergeCell ref="M2:X2"/>
+    <mergeCell ref="AU2:BF2"/>
+    <mergeCell ref="AW18:AX18"/>
+    <mergeCell ref="BC8:BE8"/>
+    <mergeCell ref="BC24:BE24"/>
+    <mergeCell ref="AY7:BB7"/>
+    <mergeCell ref="BC10:BE10"/>
+    <mergeCell ref="AW8:AX8"/>
+    <mergeCell ref="BF8:BK8"/>
+    <mergeCell ref="T7:AG11"/>
+    <mergeCell ref="C2:L2"/>
+    <mergeCell ref="E7:R11"/>
     <mergeCell ref="BI40:BK40"/>
     <mergeCell ref="BC26:BE26"/>
     <mergeCell ref="BF26:BK26"/>
-    <mergeCell ref="BM26:BO26"/>
-    <mergeCell ref="AY27:BB27"/>
-    <mergeCell ref="BC27:BE27"/>
-    <mergeCell ref="BF27:BK27"/>
-    <mergeCell ref="BM27:BO27"/>
-    <mergeCell ref="AY28:BB28"/>
-    <mergeCell ref="BC28:BE28"/>
-    <mergeCell ref="BF28:BK28"/>
-    <mergeCell ref="BM28:BO28"/>
     <mergeCell ref="AY29:BB29"/>
     <mergeCell ref="BC29:BE29"/>
     <mergeCell ref="BF29:BK29"/>
-    <mergeCell ref="AW12:AX12"/>
-    <mergeCell ref="BM14:BO14"/>
-    <mergeCell ref="BC12:BE12"/>
-    <mergeCell ref="BF19:BK19"/>
-    <mergeCell ref="BM21:BO21"/>
-    <mergeCell ref="BF13:BK13"/>
-    <mergeCell ref="AW13:AX13"/>
-    <mergeCell ref="BM23:BO23"/>
-    <mergeCell ref="BF15:BK15"/>
-    <mergeCell ref="AW7:AX7"/>
-    <mergeCell ref="B44:B56"/>
-    <mergeCell ref="C3:D5"/>
-    <mergeCell ref="BM5:BO6"/>
-    <mergeCell ref="AW5:AX6"/>
-    <mergeCell ref="AT3:AV8"/>
-    <mergeCell ref="BE52:BQ55"/>
-    <mergeCell ref="AX42:AZ42"/>
-    <mergeCell ref="AY5:BB6"/>
-    <mergeCell ref="BF20:BK20"/>
-    <mergeCell ref="AW20:AX20"/>
-    <mergeCell ref="AW52:BD52"/>
-    <mergeCell ref="BO42:BQ42"/>
-    <mergeCell ref="BP5:BP6"/>
-    <mergeCell ref="BO40:BQ40"/>
-    <mergeCell ref="BQ5:BQ6"/>
-    <mergeCell ref="BM16:BO16"/>
-    <mergeCell ref="BA46:BH46"/>
-    <mergeCell ref="BM10:BO10"/>
-    <mergeCell ref="BE48:BQ49"/>
-    <mergeCell ref="BL42:BN42"/>
-    <mergeCell ref="AY23:BB23"/>
-    <mergeCell ref="AX45:AZ45"/>
-    <mergeCell ref="BM17:BO17"/>
-    <mergeCell ref="BR44:BR56"/>
-    <mergeCell ref="AY9:BB9"/>
-    <mergeCell ref="AW25:AX25"/>
-    <mergeCell ref="AW15:AX15"/>
-    <mergeCell ref="BC9:BE9"/>
-    <mergeCell ref="AY18:BB18"/>
-    <mergeCell ref="AW49:BD51"/>
-    <mergeCell ref="BI45:BK45"/>
-    <mergeCell ref="BC16:BE16"/>
-    <mergeCell ref="AW14:AX14"/>
-    <mergeCell ref="BI46:BQ46"/>
-    <mergeCell ref="BA45:BH45"/>
-    <mergeCell ref="BL45:BN45"/>
-    <mergeCell ref="AW46:AZ46"/>
-    <mergeCell ref="AW27:AX27"/>
-    <mergeCell ref="AW28:AX28"/>
-    <mergeCell ref="AW29:AX29"/>
-    <mergeCell ref="BM29:BO29"/>
-    <mergeCell ref="AW30:AX30"/>
-    <mergeCell ref="AY30:BB30"/>
-    <mergeCell ref="BC30:BE30"/>
-    <mergeCell ref="BF30:BK30"/>
-    <mergeCell ref="BM30:BO30"/>
-    <mergeCell ref="AW31:AX31"/>
-    <mergeCell ref="AW48:BD48"/>
-    <mergeCell ref="B3:B16"/>
-    <mergeCell ref="BI47:BQ47"/>
-    <mergeCell ref="AW21:AX21"/>
-    <mergeCell ref="BC19:BE19"/>
-    <mergeCell ref="AX41:AZ41"/>
-    <mergeCell ref="BM24:BO24"/>
-    <mergeCell ref="BC21:BE21"/>
-    <mergeCell ref="AY20:BB20"/>
-    <mergeCell ref="AW16:AX16"/>
-    <mergeCell ref="BF5:BK6"/>
-    <mergeCell ref="BC17:BE17"/>
-    <mergeCell ref="AY24:BB24"/>
-    <mergeCell ref="BC5:BE6"/>
-    <mergeCell ref="AW24:AX24"/>
-    <mergeCell ref="BC20:BE20"/>
-    <mergeCell ref="AY15:BB15"/>
-    <mergeCell ref="BI42:BK42"/>
-    <mergeCell ref="BF21:BK21"/>
-    <mergeCell ref="BO45:BQ45"/>
-    <mergeCell ref="AY31:BB31"/>
-    <mergeCell ref="BC31:BE31"/>
-    <mergeCell ref="BF31:BK31"/>
-    <mergeCell ref="BM31:BO31"/>
-    <mergeCell ref="BM11:BO11"/>
-    <mergeCell ref="AY17:BB17"/>
-    <mergeCell ref="BF24:BK24"/>
-    <mergeCell ref="B30:B43"/>
-    <mergeCell ref="AW47:AZ47"/>
-    <mergeCell ref="BF10:BK10"/>
-    <mergeCell ref="AW10:AX10"/>
-    <mergeCell ref="BF17:BK17"/>
-    <mergeCell ref="AW23:AX23"/>
-    <mergeCell ref="BC18:BE18"/>
-    <mergeCell ref="AW33:AX38"/>
-    <mergeCell ref="AY33:BQ38"/>
-    <mergeCell ref="AX43:AZ43"/>
-    <mergeCell ref="BA43:BH43"/>
-    <mergeCell ref="BI43:BK43"/>
-    <mergeCell ref="BL43:BN43"/>
-    <mergeCell ref="BO43:BQ43"/>
-    <mergeCell ref="AX44:AZ44"/>
-    <mergeCell ref="AW22:AX22"/>
-    <mergeCell ref="BA41:BH41"/>
-    <mergeCell ref="AW26:AX26"/>
-    <mergeCell ref="B17:B29"/>
-    <mergeCell ref="BC23:BE23"/>
-    <mergeCell ref="BF18:BK18"/>
-    <mergeCell ref="AW11:AX11"/>
-    <mergeCell ref="AY11:BB11"/>
-    <mergeCell ref="BC11:BE11"/>
-    <mergeCell ref="BR17:BR29"/>
-    <mergeCell ref="BM9:BO9"/>
-    <mergeCell ref="AY16:BB16"/>
-    <mergeCell ref="BM19:BO19"/>
-    <mergeCell ref="BF14:BK14"/>
-    <mergeCell ref="BF23:BK23"/>
-    <mergeCell ref="BM12:BO12"/>
-    <mergeCell ref="BR3:BR16"/>
-    <mergeCell ref="BF25:BK25"/>
-    <mergeCell ref="BF22:BK22"/>
-    <mergeCell ref="BF12:BK12"/>
-    <mergeCell ref="BM20:BO20"/>
-    <mergeCell ref="BF7:BK7"/>
-    <mergeCell ref="AY21:BB21"/>
-    <mergeCell ref="BM18:BO18"/>
-    <mergeCell ref="BC13:BE13"/>
-    <mergeCell ref="BM13:BO13"/>
-    <mergeCell ref="AY19:BB19"/>
-    <mergeCell ref="AY13:BB13"/>
-    <mergeCell ref="AY22:BB22"/>
-    <mergeCell ref="BF11:BK11"/>
-    <mergeCell ref="BM7:BO7"/>
-    <mergeCell ref="BM15:BO15"/>
-    <mergeCell ref="BC25:BE25"/>
-    <mergeCell ref="BR30:BR43"/>
-    <mergeCell ref="BM8:BO8"/>
-    <mergeCell ref="C57:L57"/>
-    <mergeCell ref="M57:X57"/>
-    <mergeCell ref="Y57:AI57"/>
-    <mergeCell ref="AJ57:AT57"/>
-    <mergeCell ref="AW56:AX56"/>
-    <mergeCell ref="BM25:BO25"/>
-    <mergeCell ref="E47:R51"/>
-    <mergeCell ref="BA42:BH42"/>
-    <mergeCell ref="AX40:AZ40"/>
-    <mergeCell ref="BL40:BN40"/>
-    <mergeCell ref="BE50:BQ51"/>
-    <mergeCell ref="AY26:BB26"/>
-    <mergeCell ref="BA44:BH44"/>
-    <mergeCell ref="BI44:BK44"/>
-    <mergeCell ref="BL44:BN44"/>
-    <mergeCell ref="BO44:BQ44"/>
-    <mergeCell ref="T47:AG51"/>
-    <mergeCell ref="BF16:BK16"/>
-    <mergeCell ref="AY10:BB10"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
